--- a/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
+++ b/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11595CEA-ACFE-4896-B506-423459079D0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBDF5C1C-8EF7-4C09-A9EF-301FAD73A005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
   </bookViews>
   <sheets>
     <sheet name="LISTA DE PONTOS" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1833" uniqueCount="844">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1845" uniqueCount="856">
   <si>
     <t>WKT</t>
   </si>
@@ -2575,14 +2575,51 @@
   </si>
   <si>
     <t>456ECE0050S0</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -4,791155°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -40,827958°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -4,702947°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -40,549088°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -4,752180°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -40,837868°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -4,748082°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -40,788863°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -4,931354°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -40,527044°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -4,567784°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -41,220273°</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000000"/>
+    <numFmt numFmtId="165" formatCode="0.00000"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -2701,7 +2738,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2749,6 +2786,22 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2764,25 +2817,12 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4198,10 +4238,10 @@
         <v>11</v>
       </c>
       <c r="C2" s="5">
-        <v>-4.7531330000000001</v>
+        <v>-4.7521800000000001</v>
       </c>
       <c r="D2" s="5">
-        <v>-40.838349999999998</v>
+        <v>-40.837868</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>12</v>
@@ -4233,10 +4273,10 @@
         <v>20</v>
       </c>
       <c r="C3" s="5">
-        <v>-4.7543660000000001</v>
+        <v>-4.7480820000000001</v>
       </c>
       <c r="D3" s="5">
-        <v>-40.819200000000002</v>
+        <v>-40.788862999999999</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>12</v>
@@ -4618,10 +4658,10 @@
         <v>209</v>
       </c>
       <c r="C14" s="5">
-        <v>-4.9426909999999999</v>
+        <v>-4.9313539999999998</v>
       </c>
       <c r="D14" s="5">
-        <v>-40.539197000000001</v>
+        <v>-40.527043999999997</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>210</v>
@@ -5353,10 +5393,10 @@
         <v>305</v>
       </c>
       <c r="C35" s="5">
-        <v>-4.7343099999999998</v>
+        <v>-4.5677839999999996</v>
       </c>
       <c r="D35" s="5">
-        <v>-40.935896</v>
+        <v>-41.220272999999999</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>306</v>
@@ -5913,10 +5953,10 @@
         <v>349</v>
       </c>
       <c r="C51" s="5">
-        <v>-4.7058160000000004</v>
+        <v>-4.702947</v>
       </c>
       <c r="D51" s="5">
-        <v>-40.534300000000002</v>
+        <v>-40.549087999999998</v>
       </c>
       <c r="E51" s="4" t="s">
         <v>12</v>
@@ -8083,10 +8123,10 @@
         <v>624</v>
       </c>
       <c r="C113" s="5">
-        <v>-4.7604660000000001</v>
+        <v>-4.7911549999999998</v>
       </c>
       <c r="D113" s="5">
-        <v>-40.830300000000001</v>
+        <v>-40.827958000000002</v>
       </c>
       <c r="E113" s="4" t="s">
         <v>625</v>
@@ -9423,8 +9463,8 @@
     <col min="1" max="1" width="9.140625" style="15"/>
     <col min="2" max="2" width="11" customWidth="1"/>
     <col min="3" max="3" width="19" customWidth="1"/>
-    <col min="4" max="4" width="19.140625" style="30" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.5703125" style="30" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="23" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" style="23" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.85546875" customWidth="1"/>
     <col min="7" max="7" width="17.42578125" style="16" customWidth="1"/>
     <col min="8" max="10" width="9.42578125" style="16" customWidth="1"/>
@@ -9437,97 +9477,97 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="C1" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="30" t="s">
         <v>812</v>
       </c>
-      <c r="E1" s="28"/>
-      <c r="F1" s="24" t="s">
+      <c r="E1" s="30"/>
+      <c r="F1" s="31" t="s">
         <v>813</v>
       </c>
-      <c r="G1" s="24"/>
-      <c r="H1" s="21" t="s">
+      <c r="G1" s="31"/>
+      <c r="H1" s="27" t="s">
         <v>814</v>
       </c>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21"/>
-      <c r="O1" s="21"/>
-      <c r="P1" s="21"/>
-      <c r="Q1" s="21"/>
-      <c r="R1" s="21"/>
-      <c r="S1" s="21"/>
-      <c r="T1" s="21"/>
-      <c r="U1" s="21"/>
-      <c r="V1" s="21"/>
-      <c r="W1" s="21"/>
-      <c r="X1" s="21"/>
-      <c r="Y1" s="21"/>
-      <c r="Z1" s="21"/>
-      <c r="AA1" s="21"/>
-      <c r="AB1" s="21"/>
-      <c r="AC1" s="19" t="s">
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
+      <c r="P1" s="27"/>
+      <c r="Q1" s="27"/>
+      <c r="R1" s="27"/>
+      <c r="S1" s="27"/>
+      <c r="T1" s="27"/>
+      <c r="U1" s="27"/>
+      <c r="V1" s="27"/>
+      <c r="W1" s="27"/>
+      <c r="X1" s="27"/>
+      <c r="Y1" s="27"/>
+      <c r="Z1" s="27"/>
+      <c r="AA1" s="27"/>
+      <c r="AB1" s="27"/>
+      <c r="AC1" s="25" t="s">
         <v>815</v>
       </c>
     </row>
     <row r="2" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="22"/>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="20" t="s">
+      <c r="A2" s="28"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="26" t="s">
         <v>816</v>
       </c>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
       <c r="K2" s="9" t="s">
         <v>817</v>
       </c>
       <c r="L2" s="9" t="s">
         <v>817</v>
       </c>
-      <c r="M2" s="21" t="s">
+      <c r="M2" s="27" t="s">
         <v>818</v>
       </c>
-      <c r="N2" s="21"/>
-      <c r="O2" s="21"/>
-      <c r="P2" s="21"/>
-      <c r="Q2" s="21"/>
-      <c r="R2" s="21"/>
-      <c r="S2" s="21"/>
-      <c r="T2" s="21"/>
-      <c r="U2" s="21"/>
-      <c r="V2" s="21"/>
-      <c r="W2" s="21"/>
-      <c r="X2" s="21"/>
-      <c r="Y2" s="21"/>
-      <c r="Z2" s="21"/>
-      <c r="AA2" s="21"/>
-      <c r="AB2" s="21"/>
-      <c r="AC2" s="19"/>
+      <c r="N2" s="27"/>
+      <c r="O2" s="27"/>
+      <c r="P2" s="27"/>
+      <c r="Q2" s="27"/>
+      <c r="R2" s="27"/>
+      <c r="S2" s="27"/>
+      <c r="T2" s="27"/>
+      <c r="U2" s="27"/>
+      <c r="V2" s="27"/>
+      <c r="W2" s="27"/>
+      <c r="X2" s="27"/>
+      <c r="Y2" s="27"/>
+      <c r="Z2" s="27"/>
+      <c r="AA2" s="27"/>
+      <c r="AB2" s="27"/>
+      <c r="AC2" s="25"/>
     </row>
     <row r="3" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="22"/>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
+      <c r="A3" s="28"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
       <c r="H3" s="8" t="s">
         <v>819</v>
       </c>
@@ -9591,20 +9631,20 @@
       <c r="AB3" s="7" t="s">
         <v>839</v>
       </c>
-      <c r="AC3" s="19"/>
+      <c r="AC3" s="25"/>
     </row>
     <row r="4" spans="1:29" ht="104.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="22"/>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="29" t="s">
+      <c r="A4" s="28"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="29" t="s">
+      <c r="E4" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="24"/>
-      <c r="G4" s="24"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
       <c r="H4" s="10"/>
       <c r="I4" s="10"/>
       <c r="J4" s="10"/>
@@ -9626,22 +9666,22 @@
       <c r="Z4" s="11"/>
       <c r="AA4" s="11"/>
       <c r="AB4" s="11"/>
-      <c r="AC4" s="19"/>
+      <c r="AC4" s="25"/>
     </row>
     <row r="5" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="D5" s="27"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26">
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20">
         <f>F5+2</f>
         <v>2</v>
       </c>
@@ -9672,19 +9712,19 @@
       </c>
     </row>
     <row r="6" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="C6" s="25" t="s">
+      <c r="C6" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26">
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20">
         <f t="shared" ref="G6:G69" si="0">F6+2</f>
         <v>2</v>
       </c>
@@ -9715,19 +9755,19 @@
       </c>
     </row>
     <row r="7" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="25" t="s">
+      <c r="A7" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26">
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -9758,19 +9798,19 @@
       </c>
     </row>
     <row r="8" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="C8" s="25" t="s">
+      <c r="C8" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26">
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -9801,19 +9841,19 @@
       </c>
     </row>
     <row r="9" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="D9" s="27"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="26">
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -9844,19 +9884,19 @@
       </c>
     </row>
     <row r="10" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="25" t="s">
+      <c r="A10" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="C10" s="25" t="s">
+      <c r="C10" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="26">
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -9887,25 +9927,25 @@
       </c>
     </row>
     <row r="11" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="25" t="s">
+      <c r="A11" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="C11" s="25" t="s">
+      <c r="C11" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="D11" s="27">
+      <c r="D11" s="21">
         <v>-5.194903</v>
       </c>
-      <c r="E11" s="27">
+      <c r="E11" s="21">
         <v>-40.633378</v>
       </c>
-      <c r="F11" s="26">
+      <c r="F11" s="20">
         <v>46125</v>
       </c>
-      <c r="G11" s="26">
+      <c r="G11" s="20">
         <f t="shared" si="0"/>
         <v>46127</v>
       </c>
@@ -9978,19 +10018,19 @@
       </c>
     </row>
     <row r="12" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="25" t="s">
+      <c r="A12" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="C12" s="25" t="s">
+      <c r="C12" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="26">
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -10021,19 +10061,19 @@
       </c>
     </row>
     <row r="13" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="25" t="s">
+      <c r="A13" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="B13" s="25" t="s">
+      <c r="B13" s="19" t="s">
         <v>593</v>
       </c>
-      <c r="C13" s="25" t="s">
+      <c r="C13" s="19" t="s">
         <v>840</v>
       </c>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="26">
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -10064,19 +10104,19 @@
       </c>
     </row>
     <row r="14" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="25" t="s">
+      <c r="A14" s="19" t="s">
         <v>159</v>
       </c>
-      <c r="B14" s="25" t="s">
+      <c r="B14" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="C14" s="25" t="s">
+      <c r="C14" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="D14" s="27"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="26">
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -10107,19 +10147,19 @@
       </c>
     </row>
     <row r="15" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="25" t="s">
+      <c r="A15" s="19" t="s">
         <v>175</v>
       </c>
-      <c r="B15" s="25" t="s">
+      <c r="B15" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="C15" s="25" t="s">
+      <c r="C15" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D15" s="27"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="26">
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -10150,19 +10190,19 @@
       </c>
     </row>
     <row r="16" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="25" t="s">
+      <c r="A16" s="19" t="s">
         <v>182</v>
       </c>
-      <c r="B16" s="25" t="s">
+      <c r="B16" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="C16" s="25" t="s">
+      <c r="C16" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="D16" s="27"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="26"/>
-      <c r="G16" s="26">
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -10193,19 +10233,19 @@
       </c>
     </row>
     <row r="17" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="19" t="s">
         <v>187</v>
       </c>
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="C17" s="25" t="s">
+      <c r="C17" s="19" t="s">
         <v>188</v>
       </c>
-      <c r="D17" s="27"/>
-      <c r="E17" s="27"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="26">
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -10236,19 +10276,19 @@
       </c>
     </row>
     <row r="18" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="25" t="s">
+      <c r="A18" s="19" t="s">
         <v>192</v>
       </c>
-      <c r="B18" s="25" t="s">
+      <c r="B18" s="19" t="s">
         <v>193</v>
       </c>
-      <c r="C18" s="25" t="s">
+      <c r="C18" s="19" t="s">
         <v>194</v>
       </c>
-      <c r="D18" s="27"/>
-      <c r="E18" s="27"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="26">
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -10279,19 +10319,19 @@
       </c>
     </row>
     <row r="19" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="25" t="s">
+      <c r="A19" s="19" t="s">
         <v>198</v>
       </c>
-      <c r="B19" s="25" t="s">
+      <c r="B19" s="19" t="s">
         <v>199</v>
       </c>
-      <c r="C19" s="25" t="s">
+      <c r="C19" s="19" t="s">
         <v>200</v>
       </c>
-      <c r="D19" s="27"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="26">
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -10322,25 +10362,25 @@
       </c>
     </row>
     <row r="20" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="25" t="s">
+      <c r="A20" s="19" t="s">
         <v>613</v>
       </c>
-      <c r="B20" s="25" t="s">
+      <c r="B20" s="19" t="s">
         <v>614</v>
       </c>
-      <c r="C20" s="25" t="s">
+      <c r="C20" s="19" t="s">
         <v>615</v>
       </c>
-      <c r="D20" s="27">
+      <c r="D20" s="21">
         <v>-3.7752400000000002</v>
       </c>
-      <c r="E20" s="27">
+      <c r="E20" s="21">
         <v>-40.496578999999997</v>
       </c>
-      <c r="F20" s="26">
+      <c r="F20" s="20">
         <v>46120</v>
       </c>
-      <c r="G20" s="26">
+      <c r="G20" s="20">
         <f t="shared" si="0"/>
         <v>46122</v>
       </c>
@@ -10413,19 +10453,19 @@
       </c>
     </row>
     <row r="21" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="25" t="s">
+      <c r="A21" s="19" t="s">
         <v>619</v>
       </c>
-      <c r="B21" s="25" t="s">
+      <c r="B21" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="C21" s="25" t="s">
+      <c r="C21" s="19" t="s">
         <v>620</v>
       </c>
-      <c r="D21" s="27"/>
-      <c r="E21" s="27"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="26">
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20">
         <f>F21+2</f>
         <v>2</v>
       </c>
@@ -10456,21 +10496,27 @@
       </c>
     </row>
     <row r="22" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="25" t="s">
+      <c r="A22" s="19" t="s">
         <v>624</v>
       </c>
-      <c r="B22" s="25" t="s">
+      <c r="B22" s="19" t="s">
         <v>625</v>
       </c>
-      <c r="C22" s="25" t="s">
+      <c r="C22" s="19" t="s">
         <v>626</v>
       </c>
-      <c r="D22" s="27"/>
-      <c r="E22" s="27"/>
-      <c r="F22" s="26"/>
-      <c r="G22" s="26">
-        <f t="shared" si="0"/>
-        <v>2</v>
+      <c r="D22" s="24" t="s">
+        <v>844</v>
+      </c>
+      <c r="E22" s="24" t="s">
+        <v>845</v>
+      </c>
+      <c r="F22" s="20">
+        <v>46128</v>
+      </c>
+      <c r="G22" s="20">
+        <f t="shared" ref="G22" si="2">F22+2</f>
+        <v>46130</v>
       </c>
       <c r="H22" s="12"/>
       <c r="I22" s="12"/>
@@ -10499,19 +10545,19 @@
       </c>
     </row>
     <row r="23" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="25" t="s">
+      <c r="A23" s="19" t="s">
         <v>630</v>
       </c>
-      <c r="B23" s="25" t="s">
+      <c r="B23" s="19" t="s">
         <v>417</v>
       </c>
-      <c r="C23" s="25" t="s">
+      <c r="C23" s="19" t="s">
         <v>631</v>
       </c>
-      <c r="D23" s="27"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="26">
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -10542,19 +10588,19 @@
       </c>
     </row>
     <row r="24" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="25" t="s">
+      <c r="A24" s="19" t="s">
         <v>635</v>
       </c>
-      <c r="B24" s="25" t="s">
+      <c r="B24" s="19" t="s">
         <v>636</v>
       </c>
-      <c r="C24" s="25" t="s">
+      <c r="C24" s="19" t="s">
         <v>637</v>
       </c>
-      <c r="D24" s="27"/>
-      <c r="E24" s="27"/>
-      <c r="F24" s="26"/>
-      <c r="G24" s="26">
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -10585,19 +10631,19 @@
       </c>
     </row>
     <row r="25" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="25" t="s">
+      <c r="A25" s="19" t="s">
         <v>641</v>
       </c>
-      <c r="B25" s="25" t="s">
+      <c r="B25" s="19" t="s">
         <v>237</v>
       </c>
-      <c r="C25" s="25" t="s">
+      <c r="C25" s="19" t="s">
         <v>642</v>
       </c>
-      <c r="D25" s="27"/>
-      <c r="E25" s="27"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="26">
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -10628,19 +10674,19 @@
       </c>
     </row>
     <row r="26" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="25" t="s">
+      <c r="A26" s="19" t="s">
         <v>646</v>
       </c>
-      <c r="B26" s="25" t="s">
+      <c r="B26" s="19" t="s">
         <v>480</v>
       </c>
-      <c r="C26" s="25" t="s">
+      <c r="C26" s="19" t="s">
         <v>647</v>
       </c>
-      <c r="D26" s="27"/>
-      <c r="E26" s="27"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="26">
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -10671,19 +10717,19 @@
       </c>
     </row>
     <row r="27" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="25" t="s">
+      <c r="A27" s="19" t="s">
         <v>651</v>
       </c>
-      <c r="B27" s="25" t="s">
+      <c r="B27" s="19" t="s">
         <v>512</v>
       </c>
-      <c r="C27" s="25" t="s">
+      <c r="C27" s="19" t="s">
         <v>652</v>
       </c>
-      <c r="D27" s="27"/>
-      <c r="E27" s="27"/>
-      <c r="F27" s="26"/>
-      <c r="G27" s="26">
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -10714,19 +10760,19 @@
       </c>
     </row>
     <row r="28" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="25" t="s">
+      <c r="A28" s="19" t="s">
         <v>204</v>
       </c>
-      <c r="B28" s="25" t="s">
+      <c r="B28" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="C28" s="25" t="s">
+      <c r="C28" s="19" t="s">
         <v>205</v>
       </c>
-      <c r="D28" s="27"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="26"/>
-      <c r="G28" s="26">
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -10757,19 +10803,19 @@
       </c>
     </row>
     <row r="29" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="25" t="s">
+      <c r="A29" s="19" t="s">
         <v>656</v>
       </c>
-      <c r="B29" s="25" t="s">
+      <c r="B29" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="C29" s="25" t="s">
+      <c r="C29" s="19" t="s">
         <v>657</v>
       </c>
-      <c r="D29" s="27"/>
-      <c r="E29" s="27"/>
-      <c r="F29" s="26"/>
-      <c r="G29" s="26">
+      <c r="D29" s="21"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -10800,19 +10846,19 @@
       </c>
     </row>
     <row r="30" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="25" t="s">
+      <c r="A30" s="19" t="s">
         <v>661</v>
       </c>
-      <c r="B30" s="25" t="s">
+      <c r="B30" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="C30" s="25" t="s">
+      <c r="C30" s="19" t="s">
         <v>662</v>
       </c>
-      <c r="D30" s="27"/>
-      <c r="E30" s="27"/>
-      <c r="F30" s="26"/>
-      <c r="G30" s="26">
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -10843,25 +10889,25 @@
       </c>
     </row>
     <row r="31" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="25" t="s">
+      <c r="A31" s="19" t="s">
         <v>666</v>
       </c>
-      <c r="B31" s="25" t="s">
+      <c r="B31" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="C31" s="25" t="s">
+      <c r="C31" s="19" t="s">
         <v>667</v>
       </c>
-      <c r="D31" s="27">
+      <c r="D31" s="21">
         <v>-4.2869089999999996</v>
       </c>
-      <c r="E31" s="27">
+      <c r="E31" s="21">
         <v>-38.934477999999999</v>
       </c>
-      <c r="F31" s="26">
+      <c r="F31" s="20">
         <v>46104</v>
       </c>
-      <c r="G31" s="26">
+      <c r="G31" s="20">
         <f>F31+2</f>
         <v>46106</v>
       </c>
@@ -10934,19 +10980,19 @@
       </c>
     </row>
     <row r="32" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="25" t="s">
+      <c r="A32" s="19" t="s">
         <v>670</v>
       </c>
-      <c r="B32" s="25" t="s">
+      <c r="B32" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="C32" s="25" t="s">
+      <c r="C32" s="19" t="s">
         <v>671</v>
       </c>
-      <c r="D32" s="27"/>
-      <c r="E32" s="27"/>
-      <c r="F32" s="26"/>
-      <c r="G32" s="26">
+      <c r="D32" s="21"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -10977,19 +11023,19 @@
       </c>
     </row>
     <row r="33" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="25" t="s">
+      <c r="A33" s="19" t="s">
         <v>675</v>
       </c>
-      <c r="B33" s="25" t="s">
+      <c r="B33" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="C33" s="25" t="s">
+      <c r="C33" s="19" t="s">
         <v>676</v>
       </c>
-      <c r="D33" s="27"/>
-      <c r="E33" s="27"/>
-      <c r="F33" s="26"/>
-      <c r="G33" s="26">
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -11020,19 +11066,19 @@
       </c>
     </row>
     <row r="34" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="25" t="s">
+      <c r="A34" s="19" t="s">
         <v>680</v>
       </c>
-      <c r="B34" s="25" t="s">
+      <c r="B34" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="C34" s="25" t="s">
+      <c r="C34" s="19" t="s">
         <v>681</v>
       </c>
-      <c r="D34" s="27"/>
-      <c r="E34" s="27"/>
-      <c r="F34" s="26"/>
-      <c r="G34" s="26">
+      <c r="D34" s="21"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -11063,19 +11109,19 @@
       </c>
     </row>
     <row r="35" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="25" t="s">
+      <c r="A35" s="19" t="s">
         <v>684</v>
       </c>
-      <c r="B35" s="25" t="s">
+      <c r="B35" s="19" t="s">
         <v>193</v>
       </c>
-      <c r="C35" s="25" t="s">
+      <c r="C35" s="19" t="s">
         <v>685</v>
       </c>
-      <c r="D35" s="27"/>
-      <c r="E35" s="27"/>
-      <c r="F35" s="26"/>
-      <c r="G35" s="26">
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -11106,19 +11152,19 @@
       </c>
     </row>
     <row r="36" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="25" t="s">
+      <c r="A36" s="19" t="s">
         <v>689</v>
       </c>
-      <c r="B36" s="25" t="s">
+      <c r="B36" s="19" t="s">
         <v>193</v>
       </c>
-      <c r="C36" s="25" t="s">
+      <c r="C36" s="19" t="s">
         <v>690</v>
       </c>
-      <c r="D36" s="27"/>
-      <c r="E36" s="27"/>
-      <c r="F36" s="26"/>
-      <c r="G36" s="26">
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -11149,19 +11195,19 @@
       </c>
     </row>
     <row r="37" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="25" t="s">
+      <c r="A37" s="19" t="s">
         <v>694</v>
       </c>
-      <c r="B37" s="25" t="s">
+      <c r="B37" s="19" t="s">
         <v>695</v>
       </c>
-      <c r="C37" s="25" t="s">
+      <c r="C37" s="19" t="s">
         <v>696</v>
       </c>
-      <c r="D37" s="27"/>
-      <c r="E37" s="27"/>
-      <c r="F37" s="26"/>
-      <c r="G37" s="26">
+      <c r="D37" s="21"/>
+      <c r="E37" s="21"/>
+      <c r="F37" s="20"/>
+      <c r="G37" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -11192,19 +11238,19 @@
       </c>
     </row>
     <row r="38" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="25" t="s">
+      <c r="A38" s="19" t="s">
         <v>700</v>
       </c>
-      <c r="B38" s="25" t="s">
+      <c r="B38" s="19" t="s">
         <v>695</v>
       </c>
-      <c r="C38" s="25" t="s">
+      <c r="C38" s="19" t="s">
         <v>701</v>
       </c>
-      <c r="D38" s="27"/>
-      <c r="E38" s="27"/>
-      <c r="F38" s="26"/>
-      <c r="G38" s="26">
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="20"/>
+      <c r="G38" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -11235,19 +11281,19 @@
       </c>
     </row>
     <row r="39" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="25" t="s">
+      <c r="A39" s="19" t="s">
         <v>705</v>
       </c>
-      <c r="B39" s="25" t="s">
+      <c r="B39" s="19" t="s">
         <v>706</v>
       </c>
-      <c r="C39" s="25" t="s">
+      <c r="C39" s="19" t="s">
         <v>707</v>
       </c>
-      <c r="D39" s="27"/>
-      <c r="E39" s="27"/>
-      <c r="F39" s="26"/>
-      <c r="G39" s="26">
+      <c r="D39" s="21"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="20"/>
+      <c r="G39" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -11278,19 +11324,19 @@
       </c>
     </row>
     <row r="40" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="25" t="s">
+      <c r="A40" s="19" t="s">
         <v>711</v>
       </c>
-      <c r="B40" s="25" t="s">
+      <c r="B40" s="19" t="s">
         <v>712</v>
       </c>
-      <c r="C40" s="25" t="s">
+      <c r="C40" s="19" t="s">
         <v>713</v>
       </c>
-      <c r="D40" s="27"/>
-      <c r="E40" s="27"/>
-      <c r="F40" s="26"/>
-      <c r="G40" s="26">
+      <c r="D40" s="21"/>
+      <c r="E40" s="21"/>
+      <c r="F40" s="20"/>
+      <c r="G40" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -11321,19 +11367,19 @@
       </c>
     </row>
     <row r="41" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="25" t="s">
+      <c r="A41" s="19" t="s">
         <v>715</v>
       </c>
-      <c r="B41" s="25" t="s">
+      <c r="B41" s="19" t="s">
         <v>716</v>
       </c>
-      <c r="C41" s="25" t="s">
+      <c r="C41" s="19" t="s">
         <v>717</v>
       </c>
-      <c r="D41" s="27"/>
-      <c r="E41" s="27"/>
-      <c r="F41" s="26"/>
-      <c r="G41" s="26">
+      <c r="D41" s="21"/>
+      <c r="E41" s="21"/>
+      <c r="F41" s="20"/>
+      <c r="G41" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -11364,19 +11410,19 @@
       </c>
     </row>
     <row r="42" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="25" t="s">
+      <c r="A42" s="19" t="s">
         <v>721</v>
       </c>
-      <c r="B42" s="25" t="s">
+      <c r="B42" s="19" t="s">
         <v>199</v>
       </c>
-      <c r="C42" s="25" t="s">
+      <c r="C42" s="19" t="s">
         <v>722</v>
       </c>
-      <c r="D42" s="27"/>
-      <c r="E42" s="27"/>
-      <c r="F42" s="26"/>
-      <c r="G42" s="26">
+      <c r="D42" s="21"/>
+      <c r="E42" s="21"/>
+      <c r="F42" s="20"/>
+      <c r="G42" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -11407,19 +11453,19 @@
       </c>
     </row>
     <row r="43" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="25" t="s">
+      <c r="A43" s="19" t="s">
         <v>726</v>
       </c>
-      <c r="B43" s="25" t="s">
+      <c r="B43" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="C43" s="25" t="s">
+      <c r="C43" s="19" t="s">
         <v>727</v>
       </c>
-      <c r="D43" s="27"/>
-      <c r="E43" s="27"/>
-      <c r="F43" s="26"/>
-      <c r="G43" s="26">
+      <c r="D43" s="21"/>
+      <c r="E43" s="21"/>
+      <c r="F43" s="20"/>
+      <c r="G43" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -11450,19 +11496,19 @@
       </c>
     </row>
     <row r="44" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="25" t="s">
+      <c r="A44" s="19" t="s">
         <v>731</v>
       </c>
-      <c r="B44" s="25" t="s">
+      <c r="B44" s="19" t="s">
         <v>268</v>
       </c>
-      <c r="C44" s="25" t="s">
+      <c r="C44" s="19" t="s">
         <v>732</v>
       </c>
-      <c r="D44" s="27"/>
-      <c r="E44" s="27"/>
-      <c r="F44" s="26"/>
-      <c r="G44" s="26">
+      <c r="D44" s="21"/>
+      <c r="E44" s="21"/>
+      <c r="F44" s="20"/>
+      <c r="G44" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -11493,19 +11539,19 @@
       </c>
     </row>
     <row r="45" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="25" t="s">
+      <c r="A45" s="19" t="s">
         <v>736</v>
       </c>
-      <c r="B45" s="25" t="s">
+      <c r="B45" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="C45" s="25" t="s">
+      <c r="C45" s="19" t="s">
         <v>737</v>
       </c>
-      <c r="D45" s="27"/>
-      <c r="E45" s="27"/>
-      <c r="F45" s="26"/>
-      <c r="G45" s="26">
+      <c r="D45" s="21"/>
+      <c r="E45" s="21"/>
+      <c r="F45" s="20"/>
+      <c r="G45" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -11536,19 +11582,19 @@
       </c>
     </row>
     <row r="46" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="25" t="s">
+      <c r="A46" s="19" t="s">
         <v>740</v>
       </c>
-      <c r="B46" s="25" t="s">
+      <c r="B46" s="19" t="s">
         <v>243</v>
       </c>
-      <c r="C46" s="25" t="s">
+      <c r="C46" s="19" t="s">
         <v>741</v>
       </c>
-      <c r="D46" s="27"/>
-      <c r="E46" s="27"/>
-      <c r="F46" s="26"/>
-      <c r="G46" s="26">
+      <c r="D46" s="21"/>
+      <c r="E46" s="21"/>
+      <c r="F46" s="20"/>
+      <c r="G46" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -11579,25 +11625,25 @@
       </c>
     </row>
     <row r="47" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="25" t="s">
+      <c r="A47" s="19" t="s">
         <v>745</v>
       </c>
-      <c r="B47" s="25" t="s">
+      <c r="B47" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="C47" s="25" t="s">
+      <c r="C47" s="19" t="s">
         <v>746</v>
       </c>
-      <c r="D47" s="27">
+      <c r="D47" s="21">
         <v>-5.4055679999999997</v>
       </c>
-      <c r="E47" s="27">
+      <c r="E47" s="21">
         <v>-40.298172000000001</v>
       </c>
-      <c r="F47" s="26">
+      <c r="F47" s="20">
         <v>46125</v>
       </c>
-      <c r="G47" s="26">
+      <c r="G47" s="20">
         <f t="shared" si="0"/>
         <v>46127</v>
       </c>
@@ -11670,19 +11716,19 @@
       </c>
     </row>
     <row r="48" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="25" t="s">
+      <c r="A48" s="19" t="s">
         <v>750</v>
       </c>
-      <c r="B48" s="25" t="s">
+      <c r="B48" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="C48" s="25" t="s">
+      <c r="C48" s="19" t="s">
         <v>751</v>
       </c>
-      <c r="D48" s="27"/>
-      <c r="E48" s="27"/>
-      <c r="F48" s="26"/>
-      <c r="G48" s="26">
+      <c r="D48" s="21"/>
+      <c r="E48" s="21"/>
+      <c r="F48" s="20"/>
+      <c r="G48" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -11713,19 +11759,19 @@
       </c>
     </row>
     <row r="49" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="25" t="s">
+      <c r="A49" s="19" t="s">
         <v>755</v>
       </c>
-      <c r="B49" s="25" t="s">
+      <c r="B49" s="19" t="s">
         <v>566</v>
       </c>
-      <c r="C49" s="25" t="s">
+      <c r="C49" s="19" t="s">
         <v>756</v>
       </c>
-      <c r="D49" s="27"/>
-      <c r="E49" s="27"/>
-      <c r="F49" s="26"/>
-      <c r="G49" s="26">
+      <c r="D49" s="21"/>
+      <c r="E49" s="21"/>
+      <c r="F49" s="20"/>
+      <c r="G49" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -11756,25 +11802,25 @@
       </c>
     </row>
     <row r="50" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="25" t="s">
+      <c r="A50" s="19" t="s">
         <v>760</v>
       </c>
-      <c r="B50" s="25" t="s">
+      <c r="B50" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="C50" s="25" t="s">
+      <c r="C50" s="19" t="s">
         <v>761</v>
       </c>
-      <c r="D50" s="27">
+      <c r="D50" s="21">
         <v>-3.697114</v>
       </c>
-      <c r="E50" s="27">
+      <c r="E50" s="21">
         <v>-40.304628999999998</v>
       </c>
-      <c r="F50" s="26">
+      <c r="F50" s="20">
         <v>46119</v>
       </c>
-      <c r="G50" s="26">
+      <c r="G50" s="20">
         <f t="shared" si="0"/>
         <v>46121</v>
       </c>
@@ -11847,25 +11893,25 @@
       </c>
     </row>
     <row r="51" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="25" t="s">
+      <c r="A51" s="19" t="s">
         <v>764</v>
       </c>
-      <c r="B51" s="25" t="s">
+      <c r="B51" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="C51" s="25" t="s">
+      <c r="C51" s="19" t="s">
         <v>765</v>
       </c>
-      <c r="D51" s="27">
+      <c r="D51" s="21">
         <v>-3.7188409999999998</v>
       </c>
-      <c r="E51" s="27">
+      <c r="E51" s="21">
         <v>-40.335732</v>
       </c>
-      <c r="F51" s="26">
+      <c r="F51" s="20">
         <v>46119</v>
       </c>
-      <c r="G51" s="26">
+      <c r="G51" s="20">
         <f t="shared" si="0"/>
         <v>46121</v>
       </c>
@@ -11938,19 +11984,19 @@
       </c>
     </row>
     <row r="52" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="25" t="s">
+      <c r="A52" s="19" t="s">
         <v>769</v>
       </c>
-      <c r="B52" s="25" t="s">
+      <c r="B52" s="19" t="s">
         <v>614</v>
       </c>
-      <c r="C52" s="25" t="s">
+      <c r="C52" s="19" t="s">
         <v>770</v>
       </c>
-      <c r="D52" s="27"/>
-      <c r="E52" s="27"/>
-      <c r="F52" s="26"/>
-      <c r="G52" s="26">
+      <c r="D52" s="21"/>
+      <c r="E52" s="21"/>
+      <c r="F52" s="20"/>
+      <c r="G52" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -11981,19 +12027,19 @@
       </c>
     </row>
     <row r="53" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="25" t="s">
+      <c r="A53" s="19" t="s">
         <v>773</v>
       </c>
-      <c r="B53" s="25" t="s">
+      <c r="B53" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="C53" s="25" t="s">
+      <c r="C53" s="19" t="s">
         <v>774</v>
       </c>
-      <c r="D53" s="27"/>
-      <c r="E53" s="27"/>
-      <c r="F53" s="26"/>
-      <c r="G53" s="26">
+      <c r="D53" s="21"/>
+      <c r="E53" s="21"/>
+      <c r="F53" s="20"/>
+      <c r="G53" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -12024,19 +12070,19 @@
       </c>
     </row>
     <row r="54" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="25" t="s">
+      <c r="A54" s="19" t="s">
         <v>778</v>
       </c>
-      <c r="B54" s="25" t="s">
+      <c r="B54" s="19" t="s">
         <v>625</v>
       </c>
-      <c r="C54" s="25" t="s">
+      <c r="C54" s="19" t="s">
         <v>779</v>
       </c>
-      <c r="D54" s="27"/>
-      <c r="E54" s="27"/>
-      <c r="F54" s="26"/>
-      <c r="G54" s="26">
+      <c r="D54" s="21"/>
+      <c r="E54" s="21"/>
+      <c r="F54" s="20"/>
+      <c r="G54" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -12067,25 +12113,25 @@
       </c>
     </row>
     <row r="55" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="25" t="s">
+      <c r="A55" s="19" t="s">
         <v>783</v>
       </c>
-      <c r="B55" s="25" t="s">
+      <c r="B55" s="19" t="s">
         <v>625</v>
       </c>
-      <c r="C55" s="25" t="s">
+      <c r="C55" s="19" t="s">
         <v>784</v>
       </c>
-      <c r="D55" s="27">
+      <c r="D55" s="21">
         <v>-5.1463979999999996</v>
       </c>
-      <c r="E55" s="27">
+      <c r="E55" s="21">
         <v>-40.670636000000002</v>
       </c>
-      <c r="F55" s="26">
+      <c r="F55" s="20">
         <v>46125</v>
       </c>
-      <c r="G55" s="26">
+      <c r="G55" s="20">
         <f t="shared" si="0"/>
         <v>46127</v>
       </c>
@@ -12158,19 +12204,19 @@
       </c>
     </row>
     <row r="56" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="25" t="s">
+      <c r="A56" s="19" t="s">
         <v>788</v>
       </c>
-      <c r="B56" s="25" t="s">
+      <c r="B56" s="19" t="s">
         <v>789</v>
       </c>
-      <c r="C56" s="25" t="s">
+      <c r="C56" s="19" t="s">
         <v>790</v>
       </c>
-      <c r="D56" s="27"/>
-      <c r="E56" s="27"/>
-      <c r="F56" s="26"/>
-      <c r="G56" s="26">
+      <c r="D56" s="21"/>
+      <c r="E56" s="21"/>
+      <c r="F56" s="20"/>
+      <c r="G56" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -12201,19 +12247,19 @@
       </c>
     </row>
     <row r="57" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="25" t="s">
+      <c r="A57" s="19" t="s">
         <v>794</v>
       </c>
-      <c r="B57" s="25" t="s">
+      <c r="B57" s="19" t="s">
         <v>795</v>
       </c>
-      <c r="C57" s="25" t="s">
+      <c r="C57" s="19" t="s">
         <v>796</v>
       </c>
-      <c r="D57" s="27"/>
-      <c r="E57" s="27"/>
-      <c r="F57" s="26"/>
-      <c r="G57" s="26">
+      <c r="D57" s="21"/>
+      <c r="E57" s="21"/>
+      <c r="F57" s="20"/>
+      <c r="G57" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -12244,19 +12290,19 @@
       </c>
     </row>
     <row r="58" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="25" t="s">
+      <c r="A58" s="19" t="s">
         <v>800</v>
       </c>
-      <c r="B58" s="25" t="s">
+      <c r="B58" s="19" t="s">
         <v>795</v>
       </c>
-      <c r="C58" s="25" t="s">
+      <c r="C58" s="19" t="s">
         <v>801</v>
       </c>
-      <c r="D58" s="27"/>
-      <c r="E58" s="27"/>
-      <c r="F58" s="26"/>
-      <c r="G58" s="26">
+      <c r="D58" s="21"/>
+      <c r="E58" s="21"/>
+      <c r="F58" s="20"/>
+      <c r="G58" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -12287,19 +12333,19 @@
       </c>
     </row>
     <row r="59" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="25" t="s">
+      <c r="A59" s="19" t="s">
         <v>805</v>
       </c>
-      <c r="B59" s="25" t="s">
+      <c r="B59" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="C59" s="25" t="s">
+      <c r="C59" s="19" t="s">
         <v>806</v>
       </c>
-      <c r="D59" s="27"/>
-      <c r="E59" s="27"/>
-      <c r="F59" s="26"/>
-      <c r="G59" s="26">
+      <c r="D59" s="21"/>
+      <c r="E59" s="21"/>
+      <c r="F59" s="20"/>
+      <c r="G59" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -12330,25 +12376,25 @@
       </c>
     </row>
     <row r="60" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="25" t="s">
+      <c r="A60" s="19" t="s">
         <v>317</v>
       </c>
-      <c r="B60" s="25" t="s">
+      <c r="B60" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="C60" s="25" t="s">
+      <c r="C60" s="19" t="s">
         <v>318</v>
       </c>
-      <c r="D60" s="27">
+      <c r="D60" s="21">
         <v>-4.228675</v>
       </c>
-      <c r="E60" s="27">
+      <c r="E60" s="21">
         <v>-38.906652000000001</v>
       </c>
-      <c r="F60" s="26">
+      <c r="F60" s="20">
         <v>46104</v>
       </c>
-      <c r="G60" s="26">
+      <c r="G60" s="20">
         <f t="shared" si="0"/>
         <v>46106</v>
       </c>
@@ -12421,19 +12467,19 @@
       </c>
     </row>
     <row r="61" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="25" t="s">
+      <c r="A61" s="19" t="s">
         <v>322</v>
       </c>
-      <c r="B61" s="25" t="s">
+      <c r="B61" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="C61" s="25" t="s">
+      <c r="C61" s="19" t="s">
         <v>323</v>
       </c>
-      <c r="D61" s="27"/>
-      <c r="E61" s="27"/>
-      <c r="F61" s="26"/>
-      <c r="G61" s="26">
+      <c r="D61" s="21"/>
+      <c r="E61" s="21"/>
+      <c r="F61" s="20"/>
+      <c r="G61" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -12464,19 +12510,19 @@
       </c>
     </row>
     <row r="62" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="25" t="s">
+      <c r="A62" s="19" t="s">
         <v>327</v>
       </c>
-      <c r="B62" s="25" t="s">
+      <c r="B62" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="C62" s="25" t="s">
+      <c r="C62" s="19" t="s">
         <v>328</v>
       </c>
-      <c r="D62" s="27"/>
-      <c r="E62" s="27"/>
-      <c r="F62" s="26"/>
-      <c r="G62" s="26">
+      <c r="D62" s="21"/>
+      <c r="E62" s="21"/>
+      <c r="F62" s="20"/>
+      <c r="G62" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -12507,19 +12553,19 @@
       </c>
     </row>
     <row r="63" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="25" t="s">
+      <c r="A63" s="19" t="s">
         <v>332</v>
       </c>
-      <c r="B63" s="25" t="s">
+      <c r="B63" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="C63" s="25" t="s">
+      <c r="C63" s="19" t="s">
         <v>333</v>
       </c>
-      <c r="D63" s="27"/>
-      <c r="E63" s="27"/>
-      <c r="F63" s="26"/>
-      <c r="G63" s="26">
+      <c r="D63" s="21"/>
+      <c r="E63" s="21"/>
+      <c r="F63" s="20"/>
+      <c r="G63" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -12550,19 +12596,19 @@
       </c>
     </row>
     <row r="64" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="25" t="s">
+      <c r="A64" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="B64" s="25" t="s">
+      <c r="B64" s="19" t="s">
         <v>338</v>
       </c>
-      <c r="C64" s="25" t="s">
+      <c r="C64" s="19" t="s">
         <v>339</v>
       </c>
-      <c r="D64" s="27"/>
-      <c r="E64" s="27"/>
-      <c r="F64" s="26"/>
-      <c r="G64" s="26">
+      <c r="D64" s="21"/>
+      <c r="E64" s="21"/>
+      <c r="F64" s="20"/>
+      <c r="G64" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -12593,19 +12639,19 @@
       </c>
     </row>
     <row r="65" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="25" t="s">
+      <c r="A65" s="19" t="s">
         <v>343</v>
       </c>
-      <c r="B65" s="25" t="s">
+      <c r="B65" s="19" t="s">
         <v>344</v>
       </c>
-      <c r="C65" s="25" t="s">
+      <c r="C65" s="19" t="s">
         <v>345</v>
       </c>
-      <c r="D65" s="27"/>
-      <c r="E65" s="27"/>
-      <c r="F65" s="26"/>
-      <c r="G65" s="26">
+      <c r="D65" s="21"/>
+      <c r="E65" s="21"/>
+      <c r="F65" s="20"/>
+      <c r="G65" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -12636,25 +12682,25 @@
       </c>
     </row>
     <row r="66" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="25" t="s">
+      <c r="A66" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="B66" s="25" t="s">
+      <c r="B66" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="C66" s="25" t="s">
+      <c r="C66" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="D66" s="27">
+      <c r="D66" s="21">
         <v>-4.9633900000000004</v>
       </c>
-      <c r="E66" s="27">
+      <c r="E66" s="21">
         <v>-39.039115000000002</v>
       </c>
-      <c r="F66" s="26">
+      <c r="F66" s="20">
         <v>46111</v>
       </c>
-      <c r="G66" s="26">
+      <c r="G66" s="20">
         <f t="shared" si="0"/>
         <v>46113</v>
       </c>
@@ -12727,21 +12773,27 @@
       </c>
     </row>
     <row r="67" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="25" t="s">
+      <c r="A67" s="19" t="s">
         <v>349</v>
       </c>
-      <c r="B67" s="25" t="s">
+      <c r="B67" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="C67" s="25" t="s">
+      <c r="C67" s="19" t="s">
         <v>350</v>
       </c>
-      <c r="D67" s="27"/>
-      <c r="E67" s="27"/>
-      <c r="F67" s="26"/>
-      <c r="G67" s="26">
+      <c r="D67" s="24" t="s">
+        <v>846</v>
+      </c>
+      <c r="E67" s="24" t="s">
+        <v>847</v>
+      </c>
+      <c r="F67" s="20">
+        <v>46128</v>
+      </c>
+      <c r="G67" s="20">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>46130</v>
       </c>
       <c r="H67" s="12"/>
       <c r="I67" s="12"/>
@@ -12770,19 +12822,19 @@
       </c>
     </row>
     <row r="68" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="25" t="s">
+      <c r="A68" s="19" t="s">
         <v>353</v>
       </c>
-      <c r="B68" s="25" t="s">
+      <c r="B68" s="19" t="s">
         <v>354</v>
       </c>
-      <c r="C68" s="25" t="s">
+      <c r="C68" s="19" t="s">
         <v>355</v>
       </c>
-      <c r="D68" s="27"/>
-      <c r="E68" s="27"/>
-      <c r="F68" s="26"/>
-      <c r="G68" s="26">
+      <c r="D68" s="21"/>
+      <c r="E68" s="21"/>
+      <c r="F68" s="20"/>
+      <c r="G68" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -12813,19 +12865,19 @@
       </c>
     </row>
     <row r="69" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="25" t="s">
+      <c r="A69" s="19" t="s">
         <v>359</v>
       </c>
-      <c r="B69" s="25" t="s">
+      <c r="B69" s="19" t="s">
         <v>360</v>
       </c>
-      <c r="C69" s="25" t="s">
+      <c r="C69" s="19" t="s">
         <v>361</v>
       </c>
-      <c r="D69" s="27"/>
-      <c r="E69" s="27"/>
-      <c r="F69" s="26"/>
-      <c r="G69" s="26">
+      <c r="D69" s="21"/>
+      <c r="E69" s="21"/>
+      <c r="F69" s="20"/>
+      <c r="G69" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -12856,20 +12908,20 @@
       </c>
     </row>
     <row r="70" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="25" t="s">
+      <c r="A70" s="19" t="s">
         <v>364</v>
       </c>
-      <c r="B70" s="25" t="s">
+      <c r="B70" s="19" t="s">
         <v>365</v>
       </c>
-      <c r="C70" s="25" t="s">
+      <c r="C70" s="19" t="s">
         <v>366</v>
       </c>
-      <c r="D70" s="27"/>
-      <c r="E70" s="27"/>
-      <c r="F70" s="26"/>
-      <c r="G70" s="26">
-        <f t="shared" ref="G70:G133" si="2">F70+2</f>
+      <c r="D70" s="21"/>
+      <c r="E70" s="21"/>
+      <c r="F70" s="20"/>
+      <c r="G70" s="20">
+        <f t="shared" ref="G70:G133" si="3">F70+2</f>
         <v>2</v>
       </c>
       <c r="H70" s="12"/>
@@ -12894,25 +12946,25 @@
       <c r="AA70" s="12"/>
       <c r="AB70" s="12"/>
       <c r="AC70" s="13">
-        <f t="shared" ref="AC70:AC133" si="3">SUM(H70:AB70)</f>
+        <f t="shared" ref="AC70:AC133" si="4">SUM(H70:AB70)</f>
         <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="25" t="s">
+      <c r="A71" s="19" t="s">
         <v>370</v>
       </c>
-      <c r="B71" s="25" t="s">
+      <c r="B71" s="19" t="s">
         <v>371</v>
       </c>
-      <c r="C71" s="25" t="s">
+      <c r="C71" s="19" t="s">
         <v>372</v>
       </c>
-      <c r="D71" s="27"/>
-      <c r="E71" s="27"/>
-      <c r="F71" s="26"/>
-      <c r="G71" s="26">
-        <f t="shared" si="2"/>
+      <c r="D71" s="21"/>
+      <c r="E71" s="21"/>
+      <c r="F71" s="20"/>
+      <c r="G71" s="20">
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="H71" s="12"/>
@@ -12937,25 +12989,25 @@
       <c r="AA71" s="12"/>
       <c r="AB71" s="12"/>
       <c r="AC71" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="19" t="s">
+        <v>376</v>
+      </c>
+      <c r="B72" s="19" t="s">
+        <v>377</v>
+      </c>
+      <c r="C72" s="19" t="s">
+        <v>378</v>
+      </c>
+      <c r="D72" s="21"/>
+      <c r="E72" s="21"/>
+      <c r="F72" s="20"/>
+      <c r="G72" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="25" t="s">
-        <v>376</v>
-      </c>
-      <c r="B72" s="25" t="s">
-        <v>377</v>
-      </c>
-      <c r="C72" s="25" t="s">
-        <v>378</v>
-      </c>
-      <c r="D72" s="27"/>
-      <c r="E72" s="27"/>
-      <c r="F72" s="26"/>
-      <c r="G72" s="26">
-        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H72" s="12"/>
@@ -12980,25 +13032,25 @@
       <c r="AA72" s="12"/>
       <c r="AB72" s="12"/>
       <c r="AC72" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="B73" s="19" t="s">
+        <v>383</v>
+      </c>
+      <c r="C73" s="19" t="s">
+        <v>384</v>
+      </c>
+      <c r="D73" s="21"/>
+      <c r="E73" s="21"/>
+      <c r="F73" s="20"/>
+      <c r="G73" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="25" t="s">
-        <v>382</v>
-      </c>
-      <c r="B73" s="25" t="s">
-        <v>383</v>
-      </c>
-      <c r="C73" s="25" t="s">
-        <v>384</v>
-      </c>
-      <c r="D73" s="27"/>
-      <c r="E73" s="27"/>
-      <c r="F73" s="26"/>
-      <c r="G73" s="26">
-        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H73" s="12"/>
@@ -13023,25 +13075,25 @@
       <c r="AA73" s="12"/>
       <c r="AB73" s="12"/>
       <c r="AC73" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="19" t="s">
+        <v>388</v>
+      </c>
+      <c r="B74" s="19" t="s">
+        <v>383</v>
+      </c>
+      <c r="C74" s="19" t="s">
+        <v>389</v>
+      </c>
+      <c r="D74" s="21"/>
+      <c r="E74" s="21"/>
+      <c r="F74" s="20"/>
+      <c r="G74" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="25" t="s">
-        <v>388</v>
-      </c>
-      <c r="B74" s="25" t="s">
-        <v>383</v>
-      </c>
-      <c r="C74" s="25" t="s">
-        <v>389</v>
-      </c>
-      <c r="D74" s="27"/>
-      <c r="E74" s="27"/>
-      <c r="F74" s="26"/>
-      <c r="G74" s="26">
-        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H74" s="12"/>
@@ -13066,25 +13118,25 @@
       <c r="AA74" s="12"/>
       <c r="AB74" s="12"/>
       <c r="AC74" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="19" t="s">
+        <v>393</v>
+      </c>
+      <c r="B75" s="19" t="s">
+        <v>394</v>
+      </c>
+      <c r="C75" s="19" t="s">
+        <v>395</v>
+      </c>
+      <c r="D75" s="21"/>
+      <c r="E75" s="21"/>
+      <c r="F75" s="20"/>
+      <c r="G75" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="25" t="s">
-        <v>393</v>
-      </c>
-      <c r="B75" s="25" t="s">
-        <v>394</v>
-      </c>
-      <c r="C75" s="25" t="s">
-        <v>395</v>
-      </c>
-      <c r="D75" s="27"/>
-      <c r="E75" s="27"/>
-      <c r="F75" s="26"/>
-      <c r="G75" s="26">
-        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H75" s="12"/>
@@ -13109,25 +13161,25 @@
       <c r="AA75" s="12"/>
       <c r="AB75" s="12"/>
       <c r="AC75" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="19" t="s">
+        <v>399</v>
+      </c>
+      <c r="B76" s="19" t="s">
+        <v>400</v>
+      </c>
+      <c r="C76" s="19" t="s">
+        <v>401</v>
+      </c>
+      <c r="D76" s="21"/>
+      <c r="E76" s="21"/>
+      <c r="F76" s="20"/>
+      <c r="G76" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="25" t="s">
-        <v>399</v>
-      </c>
-      <c r="B76" s="25" t="s">
-        <v>400</v>
-      </c>
-      <c r="C76" s="25" t="s">
-        <v>401</v>
-      </c>
-      <c r="D76" s="27"/>
-      <c r="E76" s="27"/>
-      <c r="F76" s="26"/>
-      <c r="G76" s="26">
-        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H76" s="12"/>
@@ -13152,25 +13204,25 @@
       <c r="AA76" s="12"/>
       <c r="AB76" s="12"/>
       <c r="AC76" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="19" t="s">
+        <v>405</v>
+      </c>
+      <c r="B77" s="19" t="s">
+        <v>274</v>
+      </c>
+      <c r="C77" s="19" t="s">
+        <v>406</v>
+      </c>
+      <c r="D77" s="21"/>
+      <c r="E77" s="21"/>
+      <c r="F77" s="20"/>
+      <c r="G77" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="25" t="s">
-        <v>405</v>
-      </c>
-      <c r="B77" s="25" t="s">
-        <v>274</v>
-      </c>
-      <c r="C77" s="25" t="s">
-        <v>406</v>
-      </c>
-      <c r="D77" s="27"/>
-      <c r="E77" s="27"/>
-      <c r="F77" s="26"/>
-      <c r="G77" s="26">
-        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H77" s="12"/>
@@ -13195,25 +13247,25 @@
       <c r="AA77" s="12"/>
       <c r="AB77" s="12"/>
       <c r="AC77" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="B78" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="C78" s="19" t="s">
+        <v>412</v>
+      </c>
+      <c r="D78" s="21"/>
+      <c r="E78" s="21"/>
+      <c r="F78" s="20"/>
+      <c r="G78" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="25" t="s">
-        <v>410</v>
-      </c>
-      <c r="B78" s="25" t="s">
-        <v>411</v>
-      </c>
-      <c r="C78" s="25" t="s">
-        <v>412</v>
-      </c>
-      <c r="D78" s="27"/>
-      <c r="E78" s="27"/>
-      <c r="F78" s="26"/>
-      <c r="G78" s="26">
-        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H78" s="12"/>
@@ -13238,25 +13290,25 @@
       <c r="AA78" s="12"/>
       <c r="AB78" s="12"/>
       <c r="AC78" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="B79" s="19" t="s">
+        <v>417</v>
+      </c>
+      <c r="C79" s="19" t="s">
+        <v>418</v>
+      </c>
+      <c r="D79" s="21"/>
+      <c r="E79" s="21"/>
+      <c r="F79" s="20"/>
+      <c r="G79" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="25" t="s">
-        <v>416</v>
-      </c>
-      <c r="B79" s="25" t="s">
-        <v>417</v>
-      </c>
-      <c r="C79" s="25" t="s">
-        <v>418</v>
-      </c>
-      <c r="D79" s="27"/>
-      <c r="E79" s="27"/>
-      <c r="F79" s="26"/>
-      <c r="G79" s="26">
-        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H79" s="12"/>
@@ -13281,25 +13333,25 @@
       <c r="AA79" s="12"/>
       <c r="AB79" s="12"/>
       <c r="AC79" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="19" t="s">
+        <v>422</v>
+      </c>
+      <c r="B80" s="19" t="s">
+        <v>268</v>
+      </c>
+      <c r="C80" s="19" t="s">
+        <v>423</v>
+      </c>
+      <c r="D80" s="21"/>
+      <c r="E80" s="21"/>
+      <c r="F80" s="20"/>
+      <c r="G80" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="25" t="s">
-        <v>422</v>
-      </c>
-      <c r="B80" s="25" t="s">
-        <v>268</v>
-      </c>
-      <c r="C80" s="25" t="s">
-        <v>423</v>
-      </c>
-      <c r="D80" s="27"/>
-      <c r="E80" s="27"/>
-      <c r="F80" s="26"/>
-      <c r="G80" s="26">
-        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H80" s="12"/>
@@ -13324,25 +13376,25 @@
       <c r="AA80" s="12"/>
       <c r="AB80" s="12"/>
       <c r="AC80" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="19" t="s">
+        <v>427</v>
+      </c>
+      <c r="B81" s="19" t="s">
+        <v>428</v>
+      </c>
+      <c r="C81" s="19" t="s">
+        <v>429</v>
+      </c>
+      <c r="D81" s="21"/>
+      <c r="E81" s="21"/>
+      <c r="F81" s="20"/>
+      <c r="G81" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="25" t="s">
-        <v>427</v>
-      </c>
-      <c r="B81" s="25" t="s">
-        <v>428</v>
-      </c>
-      <c r="C81" s="25" t="s">
-        <v>429</v>
-      </c>
-      <c r="D81" s="27"/>
-      <c r="E81" s="27"/>
-      <c r="F81" s="26"/>
-      <c r="G81" s="26">
-        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H81" s="12"/>
@@ -13367,25 +13419,25 @@
       <c r="AA81" s="12"/>
       <c r="AB81" s="12"/>
       <c r="AC81" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="B82" s="19" t="s">
+        <v>417</v>
+      </c>
+      <c r="C82" s="19" t="s">
+        <v>434</v>
+      </c>
+      <c r="D82" s="21"/>
+      <c r="E82" s="21"/>
+      <c r="F82" s="20"/>
+      <c r="G82" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="25" t="s">
-        <v>433</v>
-      </c>
-      <c r="B82" s="25" t="s">
-        <v>417</v>
-      </c>
-      <c r="C82" s="25" t="s">
-        <v>434</v>
-      </c>
-      <c r="D82" s="27"/>
-      <c r="E82" s="27"/>
-      <c r="F82" s="26"/>
-      <c r="G82" s="26">
-        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H82" s="12"/>
@@ -13410,31 +13462,31 @@
       <c r="AA82" s="12"/>
       <c r="AB82" s="12"/>
       <c r="AC82" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="19" t="s">
+        <v>438</v>
+      </c>
+      <c r="B83" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="C83" s="19" t="s">
+        <v>439</v>
+      </c>
+      <c r="D83" s="21">
+        <v>-4.3755519999999999</v>
+      </c>
+      <c r="E83" s="21">
+        <v>-38.834249999999997</v>
+      </c>
+      <c r="F83" s="20">
+        <v>46107</v>
+      </c>
+      <c r="G83" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="25" t="s">
-        <v>438</v>
-      </c>
-      <c r="B83" s="25" t="s">
-        <v>231</v>
-      </c>
-      <c r="C83" s="25" t="s">
-        <v>439</v>
-      </c>
-      <c r="D83" s="27">
-        <v>-4.3755519999999999</v>
-      </c>
-      <c r="E83" s="27">
-        <v>-38.834249999999997</v>
-      </c>
-      <c r="F83" s="26">
-        <v>46107</v>
-      </c>
-      <c r="G83" s="26">
-        <f t="shared" si="2"/>
         <v>46109</v>
       </c>
       <c r="H83" s="12">
@@ -13501,25 +13553,25 @@
         <v>0</v>
       </c>
       <c r="AC83" s="13">
+        <f t="shared" si="4"/>
+        <v>6031</v>
+      </c>
+    </row>
+    <row r="84" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="19" t="s">
+        <v>442</v>
+      </c>
+      <c r="B84" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="C84" s="19" t="s">
+        <v>443</v>
+      </c>
+      <c r="D84" s="21"/>
+      <c r="E84" s="21"/>
+      <c r="F84" s="20"/>
+      <c r="G84" s="20">
         <f t="shared" si="3"/>
-        <v>6031</v>
-      </c>
-    </row>
-    <row r="84" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="25" t="s">
-        <v>442</v>
-      </c>
-      <c r="B84" s="25" t="s">
-        <v>231</v>
-      </c>
-      <c r="C84" s="25" t="s">
-        <v>443</v>
-      </c>
-      <c r="D84" s="27"/>
-      <c r="E84" s="27"/>
-      <c r="F84" s="26"/>
-      <c r="G84" s="26">
-        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H84" s="12"/>
@@ -13544,25 +13596,25 @@
       <c r="AA84" s="12"/>
       <c r="AB84" s="12"/>
       <c r="AC84" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="19" t="s">
+        <v>447</v>
+      </c>
+      <c r="B85" s="19" t="s">
+        <v>448</v>
+      </c>
+      <c r="C85" s="19" t="s">
+        <v>449</v>
+      </c>
+      <c r="D85" s="21"/>
+      <c r="E85" s="21"/>
+      <c r="F85" s="20"/>
+      <c r="G85" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="25" t="s">
-        <v>447</v>
-      </c>
-      <c r="B85" s="25" t="s">
-        <v>448</v>
-      </c>
-      <c r="C85" s="25" t="s">
-        <v>449</v>
-      </c>
-      <c r="D85" s="27"/>
-      <c r="E85" s="27"/>
-      <c r="F85" s="26"/>
-      <c r="G85" s="26">
-        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H85" s="12"/>
@@ -13587,25 +13639,25 @@
       <c r="AA85" s="12"/>
       <c r="AB85" s="12"/>
       <c r="AC85" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="19" t="s">
+        <v>453</v>
+      </c>
+      <c r="B86" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="C86" s="19" t="s">
+        <v>454</v>
+      </c>
+      <c r="D86" s="21"/>
+      <c r="E86" s="21"/>
+      <c r="F86" s="20"/>
+      <c r="G86" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="25" t="s">
-        <v>453</v>
-      </c>
-      <c r="B86" s="25" t="s">
-        <v>97</v>
-      </c>
-      <c r="C86" s="25" t="s">
-        <v>454</v>
-      </c>
-      <c r="D86" s="27"/>
-      <c r="E86" s="27"/>
-      <c r="F86" s="26"/>
-      <c r="G86" s="26">
-        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H86" s="12"/>
@@ -13630,25 +13682,25 @@
       <c r="AA86" s="12"/>
       <c r="AB86" s="12"/>
       <c r="AC86" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="19" t="s">
+        <v>458</v>
+      </c>
+      <c r="B87" s="19" t="s">
+        <v>237</v>
+      </c>
+      <c r="C87" s="19" t="s">
+        <v>459</v>
+      </c>
+      <c r="D87" s="21"/>
+      <c r="E87" s="21"/>
+      <c r="F87" s="20"/>
+      <c r="G87" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="25" t="s">
-        <v>458</v>
-      </c>
-      <c r="B87" s="25" t="s">
-        <v>237</v>
-      </c>
-      <c r="C87" s="25" t="s">
-        <v>459</v>
-      </c>
-      <c r="D87" s="27"/>
-      <c r="E87" s="27"/>
-      <c r="F87" s="26"/>
-      <c r="G87" s="26">
-        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H87" s="12"/>
@@ -13673,31 +13725,31 @@
       <c r="AA87" s="12"/>
       <c r="AB87" s="12"/>
       <c r="AC87" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="19" t="s">
+        <v>463</v>
+      </c>
+      <c r="B88" s="19" t="s">
+        <v>237</v>
+      </c>
+      <c r="C88" s="19" t="s">
+        <v>464</v>
+      </c>
+      <c r="D88" s="21">
+        <v>-3.6184599999999998</v>
+      </c>
+      <c r="E88" s="21">
+        <v>-40.352547000000001</v>
+      </c>
+      <c r="F88" s="20">
+        <v>46119</v>
+      </c>
+      <c r="G88" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="25" t="s">
-        <v>463</v>
-      </c>
-      <c r="B88" s="25" t="s">
-        <v>237</v>
-      </c>
-      <c r="C88" s="25" t="s">
-        <v>464</v>
-      </c>
-      <c r="D88" s="27">
-        <v>-3.6184599999999998</v>
-      </c>
-      <c r="E88" s="27">
-        <v>-40.352547000000001</v>
-      </c>
-      <c r="F88" s="26">
-        <v>46119</v>
-      </c>
-      <c r="G88" s="26">
-        <f t="shared" si="2"/>
         <v>46121</v>
       </c>
       <c r="H88" s="12">
@@ -13764,25 +13816,25 @@
         <v>1</v>
       </c>
       <c r="AC88" s="13">
+        <f t="shared" si="4"/>
+        <v>6697</v>
+      </c>
+    </row>
+    <row r="89" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="19" t="s">
+        <v>468</v>
+      </c>
+      <c r="B89" s="19" t="s">
+        <v>237</v>
+      </c>
+      <c r="C89" s="19" t="s">
+        <v>469</v>
+      </c>
+      <c r="D89" s="21"/>
+      <c r="E89" s="21"/>
+      <c r="F89" s="20"/>
+      <c r="G89" s="20">
         <f t="shared" si="3"/>
-        <v>6697</v>
-      </c>
-    </row>
-    <row r="89" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="25" t="s">
-        <v>468</v>
-      </c>
-      <c r="B89" s="25" t="s">
-        <v>237</v>
-      </c>
-      <c r="C89" s="25" t="s">
-        <v>469</v>
-      </c>
-      <c r="D89" s="27"/>
-      <c r="E89" s="27"/>
-      <c r="F89" s="26"/>
-      <c r="G89" s="26">
-        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H89" s="12"/>
@@ -13807,25 +13859,25 @@
       <c r="AA89" s="12"/>
       <c r="AB89" s="12"/>
       <c r="AC89" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="19" t="s">
+        <v>473</v>
+      </c>
+      <c r="B90" s="19" t="s">
+        <v>474</v>
+      </c>
+      <c r="C90" s="19" t="s">
+        <v>475</v>
+      </c>
+      <c r="D90" s="21"/>
+      <c r="E90" s="21"/>
+      <c r="F90" s="20"/>
+      <c r="G90" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="25" t="s">
-        <v>473</v>
-      </c>
-      <c r="B90" s="25" t="s">
-        <v>474</v>
-      </c>
-      <c r="C90" s="25" t="s">
-        <v>475</v>
-      </c>
-      <c r="D90" s="27"/>
-      <c r="E90" s="27"/>
-      <c r="F90" s="26"/>
-      <c r="G90" s="26">
-        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H90" s="12"/>
@@ -13850,25 +13902,25 @@
       <c r="AA90" s="12"/>
       <c r="AB90" s="12"/>
       <c r="AC90" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="19" t="s">
+        <v>479</v>
+      </c>
+      <c r="B91" s="19" t="s">
+        <v>480</v>
+      </c>
+      <c r="C91" s="19" t="s">
+        <v>481</v>
+      </c>
+      <c r="D91" s="21"/>
+      <c r="E91" s="21"/>
+      <c r="F91" s="20"/>
+      <c r="G91" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="25" t="s">
-        <v>479</v>
-      </c>
-      <c r="B91" s="25" t="s">
-        <v>480</v>
-      </c>
-      <c r="C91" s="25" t="s">
-        <v>481</v>
-      </c>
-      <c r="D91" s="27"/>
-      <c r="E91" s="27"/>
-      <c r="F91" s="26"/>
-      <c r="G91" s="26">
-        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H91" s="12"/>
@@ -13893,25 +13945,25 @@
       <c r="AA91" s="12"/>
       <c r="AB91" s="12"/>
       <c r="AC91" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="19" t="s">
+        <v>485</v>
+      </c>
+      <c r="B92" s="19" t="s">
+        <v>480</v>
+      </c>
+      <c r="C92" s="19" t="s">
+        <v>486</v>
+      </c>
+      <c r="D92" s="21"/>
+      <c r="E92" s="21"/>
+      <c r="F92" s="20"/>
+      <c r="G92" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="25" t="s">
-        <v>485</v>
-      </c>
-      <c r="B92" s="25" t="s">
-        <v>480</v>
-      </c>
-      <c r="C92" s="25" t="s">
-        <v>486</v>
-      </c>
-      <c r="D92" s="27"/>
-      <c r="E92" s="27"/>
-      <c r="F92" s="26"/>
-      <c r="G92" s="26">
-        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H92" s="12"/>
@@ -13936,25 +13988,25 @@
       <c r="AA92" s="12"/>
       <c r="AB92" s="12"/>
       <c r="AC92" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="19" t="s">
+        <v>489</v>
+      </c>
+      <c r="B93" s="19" t="s">
+        <v>490</v>
+      </c>
+      <c r="C93" s="19" t="s">
+        <v>491</v>
+      </c>
+      <c r="D93" s="21"/>
+      <c r="E93" s="21"/>
+      <c r="F93" s="20"/>
+      <c r="G93" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="25" t="s">
-        <v>489</v>
-      </c>
-      <c r="B93" s="25" t="s">
-        <v>490</v>
-      </c>
-      <c r="C93" s="25" t="s">
-        <v>491</v>
-      </c>
-      <c r="D93" s="27"/>
-      <c r="E93" s="27"/>
-      <c r="F93" s="26"/>
-      <c r="G93" s="26">
-        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H93" s="12"/>
@@ -13979,31 +14031,31 @@
       <c r="AA93" s="12"/>
       <c r="AB93" s="12"/>
       <c r="AC93" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="B94" s="19" t="s">
+        <v>841</v>
+      </c>
+      <c r="C94" s="19" t="s">
+        <v>842</v>
+      </c>
+      <c r="D94" s="21">
+        <v>-5.0822029999999998</v>
+      </c>
+      <c r="E94" s="21">
+        <v>-39.054245999999999</v>
+      </c>
+      <c r="F94" s="20">
+        <v>46111</v>
+      </c>
+      <c r="G94" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="B94" s="25" t="s">
-        <v>841</v>
-      </c>
-      <c r="C94" s="25" t="s">
-        <v>842</v>
-      </c>
-      <c r="D94" s="27">
-        <v>-5.0822029999999998</v>
-      </c>
-      <c r="E94" s="27">
-        <v>-39.054245999999999</v>
-      </c>
-      <c r="F94" s="26">
-        <v>46111</v>
-      </c>
-      <c r="G94" s="26">
-        <f t="shared" si="2"/>
         <v>46113</v>
       </c>
       <c r="H94" s="12">
@@ -14070,25 +14122,25 @@
         <v>2</v>
       </c>
       <c r="AC94" s="13">
+        <f t="shared" si="4"/>
+        <v>2883</v>
+      </c>
+    </row>
+    <row r="95" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="19" t="s">
+        <v>495</v>
+      </c>
+      <c r="B95" s="19" t="s">
+        <v>496</v>
+      </c>
+      <c r="C95" s="19" t="s">
+        <v>497</v>
+      </c>
+      <c r="D95" s="21"/>
+      <c r="E95" s="21"/>
+      <c r="F95" s="20"/>
+      <c r="G95" s="20">
         <f t="shared" si="3"/>
-        <v>2883</v>
-      </c>
-    </row>
-    <row r="95" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="25" t="s">
-        <v>495</v>
-      </c>
-      <c r="B95" s="25" t="s">
-        <v>496</v>
-      </c>
-      <c r="C95" s="25" t="s">
-        <v>497</v>
-      </c>
-      <c r="D95" s="27"/>
-      <c r="E95" s="27"/>
-      <c r="F95" s="26"/>
-      <c r="G95" s="26">
-        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H95" s="12"/>
@@ -14113,25 +14165,25 @@
       <c r="AA95" s="12"/>
       <c r="AB95" s="12"/>
       <c r="AC95" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="19" t="s">
+        <v>501</v>
+      </c>
+      <c r="B96" s="19" t="s">
+        <v>496</v>
+      </c>
+      <c r="C96" s="19" t="s">
+        <v>502</v>
+      </c>
+      <c r="D96" s="21"/>
+      <c r="E96" s="21"/>
+      <c r="F96" s="20"/>
+      <c r="G96" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="25" t="s">
-        <v>501</v>
-      </c>
-      <c r="B96" s="25" t="s">
-        <v>496</v>
-      </c>
-      <c r="C96" s="25" t="s">
-        <v>502</v>
-      </c>
-      <c r="D96" s="27"/>
-      <c r="E96" s="27"/>
-      <c r="F96" s="26"/>
-      <c r="G96" s="26">
-        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H96" s="12"/>
@@ -14156,25 +14208,25 @@
       <c r="AA96" s="12"/>
       <c r="AB96" s="12"/>
       <c r="AC96" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="19" t="s">
+        <v>506</v>
+      </c>
+      <c r="B97" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="C97" s="19" t="s">
+        <v>507</v>
+      </c>
+      <c r="D97" s="21"/>
+      <c r="E97" s="21"/>
+      <c r="F97" s="20"/>
+      <c r="G97" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="25" t="s">
-        <v>506</v>
-      </c>
-      <c r="B97" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="C97" s="25" t="s">
-        <v>507</v>
-      </c>
-      <c r="D97" s="27"/>
-      <c r="E97" s="27"/>
-      <c r="F97" s="26"/>
-      <c r="G97" s="26">
-        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H97" s="12"/>
@@ -14199,25 +14251,25 @@
       <c r="AA97" s="12"/>
       <c r="AB97" s="12"/>
       <c r="AC97" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="19" t="s">
+        <v>511</v>
+      </c>
+      <c r="B98" s="19" t="s">
+        <v>512</v>
+      </c>
+      <c r="C98" s="19" t="s">
+        <v>513</v>
+      </c>
+      <c r="D98" s="21"/>
+      <c r="E98" s="21"/>
+      <c r="F98" s="20"/>
+      <c r="G98" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="25" t="s">
-        <v>511</v>
-      </c>
-      <c r="B98" s="25" t="s">
-        <v>512</v>
-      </c>
-      <c r="C98" s="25" t="s">
-        <v>513</v>
-      </c>
-      <c r="D98" s="27"/>
-      <c r="E98" s="27"/>
-      <c r="F98" s="26"/>
-      <c r="G98" s="26">
-        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H98" s="12"/>
@@ -14242,25 +14294,25 @@
       <c r="AA98" s="12"/>
       <c r="AB98" s="12"/>
       <c r="AC98" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="19" t="s">
+        <v>517</v>
+      </c>
+      <c r="B99" s="19" t="s">
+        <v>512</v>
+      </c>
+      <c r="C99" s="19" t="s">
+        <v>518</v>
+      </c>
+      <c r="D99" s="21"/>
+      <c r="E99" s="21"/>
+      <c r="F99" s="20"/>
+      <c r="G99" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="25" t="s">
-        <v>517</v>
-      </c>
-      <c r="B99" s="25" t="s">
-        <v>512</v>
-      </c>
-      <c r="C99" s="25" t="s">
-        <v>518</v>
-      </c>
-      <c r="D99" s="27"/>
-      <c r="E99" s="27"/>
-      <c r="F99" s="26"/>
-      <c r="G99" s="26">
-        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H99" s="12"/>
@@ -14285,25 +14337,25 @@
       <c r="AA99" s="12"/>
       <c r="AB99" s="12"/>
       <c r="AC99" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="19" t="s">
+        <v>522</v>
+      </c>
+      <c r="B100" s="19" t="s">
+        <v>383</v>
+      </c>
+      <c r="C100" s="19" t="s">
+        <v>523</v>
+      </c>
+      <c r="D100" s="21"/>
+      <c r="E100" s="21"/>
+      <c r="F100" s="20"/>
+      <c r="G100" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="25" t="s">
-        <v>522</v>
-      </c>
-      <c r="B100" s="25" t="s">
-        <v>383</v>
-      </c>
-      <c r="C100" s="25" t="s">
-        <v>523</v>
-      </c>
-      <c r="D100" s="27"/>
-      <c r="E100" s="27"/>
-      <c r="F100" s="26"/>
-      <c r="G100" s="26">
-        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H100" s="12"/>
@@ -14328,25 +14380,25 @@
       <c r="AA100" s="12"/>
       <c r="AB100" s="12"/>
       <c r="AC100" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="19" t="s">
+        <v>527</v>
+      </c>
+      <c r="B101" s="19" t="s">
+        <v>528</v>
+      </c>
+      <c r="C101" s="19" t="s">
+        <v>529</v>
+      </c>
+      <c r="D101" s="21"/>
+      <c r="E101" s="21"/>
+      <c r="F101" s="20"/>
+      <c r="G101" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="25" t="s">
-        <v>527</v>
-      </c>
-      <c r="B101" s="25" t="s">
-        <v>528</v>
-      </c>
-      <c r="C101" s="25" t="s">
-        <v>529</v>
-      </c>
-      <c r="D101" s="27"/>
-      <c r="E101" s="27"/>
-      <c r="F101" s="26"/>
-      <c r="G101" s="26">
-        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H101" s="12"/>
@@ -14371,25 +14423,25 @@
       <c r="AA101" s="12"/>
       <c r="AB101" s="12"/>
       <c r="AC101" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="19" t="s">
+        <v>533</v>
+      </c>
+      <c r="B102" s="19" t="s">
+        <v>534</v>
+      </c>
+      <c r="C102" s="19" t="s">
+        <v>535</v>
+      </c>
+      <c r="D102" s="21"/>
+      <c r="E102" s="21"/>
+      <c r="F102" s="20"/>
+      <c r="G102" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="25" t="s">
-        <v>533</v>
-      </c>
-      <c r="B102" s="25" t="s">
-        <v>534</v>
-      </c>
-      <c r="C102" s="25" t="s">
-        <v>535</v>
-      </c>
-      <c r="D102" s="27"/>
-      <c r="E102" s="27"/>
-      <c r="F102" s="26"/>
-      <c r="G102" s="26">
-        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H102" s="12"/>
@@ -14414,31 +14466,31 @@
       <c r="AA102" s="12"/>
       <c r="AB102" s="12"/>
       <c r="AC102" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="B103" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="C103" s="19" t="s">
+        <v>843</v>
+      </c>
+      <c r="D103" s="21">
+        <v>-4.8596729999999999</v>
+      </c>
+      <c r="E103" s="21">
+        <v>-39.052987999999999</v>
+      </c>
+      <c r="F103" s="20">
+        <v>46111</v>
+      </c>
+      <c r="G103" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="25" t="s">
-        <v>164</v>
-      </c>
-      <c r="B103" s="25" t="s">
-        <v>165</v>
-      </c>
-      <c r="C103" s="25" t="s">
-        <v>843</v>
-      </c>
-      <c r="D103" s="27">
-        <v>-4.8596729999999999</v>
-      </c>
-      <c r="E103" s="27">
-        <v>-39.052987999999999</v>
-      </c>
-      <c r="F103" s="26">
-        <v>46111</v>
-      </c>
-      <c r="G103" s="26">
-        <f t="shared" si="2"/>
         <v>46113</v>
       </c>
       <c r="H103" s="12">
@@ -14505,31 +14557,31 @@
         <v>0</v>
       </c>
       <c r="AC103" s="13">
+        <f t="shared" si="4"/>
+        <v>2499</v>
+      </c>
+    </row>
+    <row r="104" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="19" t="s">
+        <v>539</v>
+      </c>
+      <c r="B104" s="19" t="s">
+        <v>540</v>
+      </c>
+      <c r="C104" s="19" t="s">
+        <v>541</v>
+      </c>
+      <c r="D104" s="21">
+        <v>-4.4447369999999999</v>
+      </c>
+      <c r="E104" s="21">
+        <v>-38.662745999999999</v>
+      </c>
+      <c r="F104" s="20">
+        <v>46107</v>
+      </c>
+      <c r="G104" s="20">
         <f t="shared" si="3"/>
-        <v>2499</v>
-      </c>
-    </row>
-    <row r="104" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="25" t="s">
-        <v>539</v>
-      </c>
-      <c r="B104" s="25" t="s">
-        <v>540</v>
-      </c>
-      <c r="C104" s="25" t="s">
-        <v>541</v>
-      </c>
-      <c r="D104" s="27">
-        <v>-4.4447369999999999</v>
-      </c>
-      <c r="E104" s="27">
-        <v>-38.662745999999999</v>
-      </c>
-      <c r="F104" s="26">
-        <v>46107</v>
-      </c>
-      <c r="G104" s="26">
-        <f t="shared" si="2"/>
         <v>46109</v>
       </c>
       <c r="H104" s="12">
@@ -14596,31 +14648,31 @@
         <v>1</v>
       </c>
       <c r="AC104" s="13">
+        <f t="shared" si="4"/>
+        <v>2533</v>
+      </c>
+    </row>
+    <row r="105" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="19" t="s">
+        <v>545</v>
+      </c>
+      <c r="B105" s="19" t="s">
+        <v>546</v>
+      </c>
+      <c r="C105" s="19" t="s">
+        <v>547</v>
+      </c>
+      <c r="D105" s="21">
+        <v>-5.1705110000000003</v>
+      </c>
+      <c r="E105" s="21">
+        <v>-40.708150000000003</v>
+      </c>
+      <c r="F105" s="20">
+        <v>46125</v>
+      </c>
+      <c r="G105" s="20">
         <f t="shared" si="3"/>
-        <v>2533</v>
-      </c>
-    </row>
-    <row r="105" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="25" t="s">
-        <v>545</v>
-      </c>
-      <c r="B105" s="25" t="s">
-        <v>546</v>
-      </c>
-      <c r="C105" s="25" t="s">
-        <v>547</v>
-      </c>
-      <c r="D105" s="27">
-        <v>-5.1705110000000003</v>
-      </c>
-      <c r="E105" s="27">
-        <v>-40.708150000000003</v>
-      </c>
-      <c r="F105" s="26">
-        <v>46125</v>
-      </c>
-      <c r="G105" s="26">
-        <f t="shared" si="2"/>
         <v>46127</v>
       </c>
       <c r="H105" s="12">
@@ -14687,25 +14739,25 @@
         <v>1</v>
       </c>
       <c r="AC105" s="13">
+        <f t="shared" si="4"/>
+        <v>2124</v>
+      </c>
+    </row>
+    <row r="106" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="19" t="s">
+        <v>551</v>
+      </c>
+      <c r="B106" s="19" t="s">
+        <v>496</v>
+      </c>
+      <c r="C106" s="19" t="s">
+        <v>552</v>
+      </c>
+      <c r="D106" s="21"/>
+      <c r="E106" s="21"/>
+      <c r="F106" s="20"/>
+      <c r="G106" s="20">
         <f t="shared" si="3"/>
-        <v>2124</v>
-      </c>
-    </row>
-    <row r="106" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="25" t="s">
-        <v>551</v>
-      </c>
-      <c r="B106" s="25" t="s">
-        <v>496</v>
-      </c>
-      <c r="C106" s="25" t="s">
-        <v>552</v>
-      </c>
-      <c r="D106" s="27"/>
-      <c r="E106" s="27"/>
-      <c r="F106" s="26"/>
-      <c r="G106" s="26">
-        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H106" s="12"/>
@@ -14730,25 +14782,25 @@
       <c r="AA106" s="12"/>
       <c r="AB106" s="12"/>
       <c r="AC106" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="19" t="s">
+        <v>556</v>
+      </c>
+      <c r="B107" s="19" t="s">
+        <v>360</v>
+      </c>
+      <c r="C107" s="19" t="s">
+        <v>557</v>
+      </c>
+      <c r="D107" s="21"/>
+      <c r="E107" s="21"/>
+      <c r="F107" s="20"/>
+      <c r="G107" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="25" t="s">
-        <v>556</v>
-      </c>
-      <c r="B107" s="25" t="s">
-        <v>360</v>
-      </c>
-      <c r="C107" s="25" t="s">
-        <v>557</v>
-      </c>
-      <c r="D107" s="27"/>
-      <c r="E107" s="27"/>
-      <c r="F107" s="26"/>
-      <c r="G107" s="26">
-        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H107" s="12"/>
@@ -14773,25 +14825,25 @@
       <c r="AA107" s="12"/>
       <c r="AB107" s="12"/>
       <c r="AC107" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="B108" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C108" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="D108" s="21"/>
+      <c r="E108" s="21"/>
+      <c r="F108" s="20"/>
+      <c r="G108" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="25" t="s">
-        <v>170</v>
-      </c>
-      <c r="B108" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="C108" s="25" t="s">
-        <v>171</v>
-      </c>
-      <c r="D108" s="27"/>
-      <c r="E108" s="27"/>
-      <c r="F108" s="26"/>
-      <c r="G108" s="26">
-        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H108" s="12"/>
@@ -14816,25 +14868,25 @@
       <c r="AA108" s="12"/>
       <c r="AB108" s="12"/>
       <c r="AC108" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="19" t="s">
+        <v>561</v>
+      </c>
+      <c r="B109" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="C109" s="19" t="s">
+        <v>562</v>
+      </c>
+      <c r="D109" s="21"/>
+      <c r="E109" s="21"/>
+      <c r="F109" s="20"/>
+      <c r="G109" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="25" t="s">
-        <v>561</v>
-      </c>
-      <c r="B109" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="C109" s="25" t="s">
-        <v>562</v>
-      </c>
-      <c r="D109" s="27"/>
-      <c r="E109" s="27"/>
-      <c r="F109" s="26"/>
-      <c r="G109" s="26">
-        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H109" s="12"/>
@@ -14859,31 +14911,31 @@
       <c r="AA109" s="12"/>
       <c r="AB109" s="12"/>
       <c r="AC109" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="19" t="s">
+        <v>565</v>
+      </c>
+      <c r="B110" s="19" t="s">
+        <v>566</v>
+      </c>
+      <c r="C110" s="19" t="s">
+        <v>567</v>
+      </c>
+      <c r="D110" s="21">
+        <v>-3.6978119999999999</v>
+      </c>
+      <c r="E110" s="21">
+        <v>-40.307443999999997</v>
+      </c>
+      <c r="F110" s="20">
+        <v>46119</v>
+      </c>
+      <c r="G110" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="25" t="s">
-        <v>565</v>
-      </c>
-      <c r="B110" s="25" t="s">
-        <v>566</v>
-      </c>
-      <c r="C110" s="25" t="s">
-        <v>567</v>
-      </c>
-      <c r="D110" s="27">
-        <v>-3.6978119999999999</v>
-      </c>
-      <c r="E110" s="27">
-        <v>-40.307443999999997</v>
-      </c>
-      <c r="F110" s="26">
-        <v>46119</v>
-      </c>
-      <c r="G110" s="26">
-        <f t="shared" si="2"/>
         <v>46121</v>
       </c>
       <c r="H110" s="12">
@@ -14950,31 +15002,31 @@
         <v>0</v>
       </c>
       <c r="AC110" s="13">
+        <f t="shared" si="4"/>
+        <v>5171</v>
+      </c>
+    </row>
+    <row r="111" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="19" t="s">
+        <v>571</v>
+      </c>
+      <c r="B111" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="C111" s="19" t="s">
+        <v>572</v>
+      </c>
+      <c r="D111" s="21">
+        <v>-5.2113269999999998</v>
+      </c>
+      <c r="E111" s="21">
+        <v>-40.696823000000002</v>
+      </c>
+      <c r="F111" s="20">
+        <v>46125</v>
+      </c>
+      <c r="G111" s="20">
         <f t="shared" si="3"/>
-        <v>5171</v>
-      </c>
-    </row>
-    <row r="111" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="25" t="s">
-        <v>571</v>
-      </c>
-      <c r="B111" s="25" t="s">
-        <v>210</v>
-      </c>
-      <c r="C111" s="25" t="s">
-        <v>572</v>
-      </c>
-      <c r="D111" s="27">
-        <v>-5.2113269999999998</v>
-      </c>
-      <c r="E111" s="27">
-        <v>-40.696823000000002</v>
-      </c>
-      <c r="F111" s="26">
-        <v>46125</v>
-      </c>
-      <c r="G111" s="26">
-        <f t="shared" si="2"/>
         <v>46127</v>
       </c>
       <c r="H111" s="12">
@@ -15041,25 +15093,25 @@
         <v>1</v>
       </c>
       <c r="AC111" s="13">
+        <f t="shared" si="4"/>
+        <v>5543</v>
+      </c>
+    </row>
+    <row r="112" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="19" t="s">
+        <v>576</v>
+      </c>
+      <c r="B112" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="C112" s="19" t="s">
+        <v>577</v>
+      </c>
+      <c r="D112" s="21"/>
+      <c r="E112" s="21"/>
+      <c r="F112" s="20"/>
+      <c r="G112" s="20">
         <f t="shared" si="3"/>
-        <v>5543</v>
-      </c>
-    </row>
-    <row r="112" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="25" t="s">
-        <v>576</v>
-      </c>
-      <c r="B112" s="25" t="s">
-        <v>210</v>
-      </c>
-      <c r="C112" s="25" t="s">
-        <v>577</v>
-      </c>
-      <c r="D112" s="27"/>
-      <c r="E112" s="27"/>
-      <c r="F112" s="26"/>
-      <c r="G112" s="26">
-        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H112" s="12"/>
@@ -15084,25 +15136,25 @@
       <c r="AA112" s="12"/>
       <c r="AB112" s="12"/>
       <c r="AC112" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="19" t="s">
+        <v>581</v>
+      </c>
+      <c r="B113" s="19" t="s">
+        <v>582</v>
+      </c>
+      <c r="C113" s="19" t="s">
+        <v>583</v>
+      </c>
+      <c r="D113" s="21"/>
+      <c r="E113" s="21"/>
+      <c r="F113" s="20"/>
+      <c r="G113" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="25" t="s">
-        <v>581</v>
-      </c>
-      <c r="B113" s="25" t="s">
-        <v>582</v>
-      </c>
-      <c r="C113" s="25" t="s">
-        <v>583</v>
-      </c>
-      <c r="D113" s="27"/>
-      <c r="E113" s="27"/>
-      <c r="F113" s="26"/>
-      <c r="G113" s="26">
-        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H113" s="12"/>
@@ -15127,25 +15179,25 @@
       <c r="AA113" s="12"/>
       <c r="AB113" s="12"/>
       <c r="AC113" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="19" t="s">
+        <v>587</v>
+      </c>
+      <c r="B114" s="19" t="s">
+        <v>496</v>
+      </c>
+      <c r="C114" s="19" t="s">
+        <v>588</v>
+      </c>
+      <c r="D114" s="21"/>
+      <c r="E114" s="21"/>
+      <c r="F114" s="20"/>
+      <c r="G114" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="25" t="s">
-        <v>587</v>
-      </c>
-      <c r="B114" s="25" t="s">
-        <v>496</v>
-      </c>
-      <c r="C114" s="25" t="s">
-        <v>588</v>
-      </c>
-      <c r="D114" s="27"/>
-      <c r="E114" s="27"/>
-      <c r="F114" s="26"/>
-      <c r="G114" s="26">
-        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H114" s="12"/>
@@ -15170,25 +15222,25 @@
       <c r="AA114" s="12"/>
       <c r="AB114" s="12"/>
       <c r="AC114" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="19" t="s">
+        <v>592</v>
+      </c>
+      <c r="B115" s="19" t="s">
+        <v>593</v>
+      </c>
+      <c r="C115" s="19" t="s">
+        <v>594</v>
+      </c>
+      <c r="D115" s="21"/>
+      <c r="E115" s="21"/>
+      <c r="F115" s="20"/>
+      <c r="G115" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="25" t="s">
-        <v>592</v>
-      </c>
-      <c r="B115" s="25" t="s">
-        <v>593</v>
-      </c>
-      <c r="C115" s="25" t="s">
-        <v>594</v>
-      </c>
-      <c r="D115" s="27"/>
-      <c r="E115" s="27"/>
-      <c r="F115" s="26"/>
-      <c r="G115" s="26">
-        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H115" s="12"/>
@@ -15213,25 +15265,25 @@
       <c r="AA115" s="12"/>
       <c r="AB115" s="12"/>
       <c r="AC115" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="19" t="s">
+        <v>598</v>
+      </c>
+      <c r="B116" s="19" t="s">
+        <v>599</v>
+      </c>
+      <c r="C116" s="19" t="s">
+        <v>600</v>
+      </c>
+      <c r="D116" s="21"/>
+      <c r="E116" s="21"/>
+      <c r="F116" s="20"/>
+      <c r="G116" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="25" t="s">
-        <v>598</v>
-      </c>
-      <c r="B116" s="25" t="s">
-        <v>599</v>
-      </c>
-      <c r="C116" s="25" t="s">
-        <v>600</v>
-      </c>
-      <c r="D116" s="27"/>
-      <c r="E116" s="27"/>
-      <c r="F116" s="26"/>
-      <c r="G116" s="26">
-        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H116" s="12"/>
@@ -15256,25 +15308,25 @@
       <c r="AA116" s="12"/>
       <c r="AB116" s="12"/>
       <c r="AC116" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="19" t="s">
+        <v>603</v>
+      </c>
+      <c r="B117" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="C117" s="19" t="s">
+        <v>604</v>
+      </c>
+      <c r="D117" s="21"/>
+      <c r="E117" s="21"/>
+      <c r="F117" s="20"/>
+      <c r="G117" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="25" t="s">
-        <v>603</v>
-      </c>
-      <c r="B117" s="25" t="s">
-        <v>142</v>
-      </c>
-      <c r="C117" s="25" t="s">
-        <v>604</v>
-      </c>
-      <c r="D117" s="27"/>
-      <c r="E117" s="27"/>
-      <c r="F117" s="26"/>
-      <c r="G117" s="26">
-        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H117" s="12"/>
@@ -15299,25 +15351,25 @@
       <c r="AA117" s="12"/>
       <c r="AB117" s="12"/>
       <c r="AC117" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="19" t="s">
+        <v>608</v>
+      </c>
+      <c r="B118" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="C118" s="19" t="s">
+        <v>609</v>
+      </c>
+      <c r="D118" s="21"/>
+      <c r="E118" s="21"/>
+      <c r="F118" s="20"/>
+      <c r="G118" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="25" t="s">
-        <v>608</v>
-      </c>
-      <c r="B118" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="C118" s="25" t="s">
-        <v>609</v>
-      </c>
-      <c r="D118" s="27"/>
-      <c r="E118" s="27"/>
-      <c r="F118" s="26"/>
-      <c r="G118" s="26">
-        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H118" s="12"/>
@@ -15342,26 +15394,32 @@
       <c r="AA118" s="12"/>
       <c r="AB118" s="12"/>
       <c r="AC118" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B119" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C119" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D119" s="24" t="s">
+        <v>848</v>
+      </c>
+      <c r="E119" s="24" t="s">
+        <v>849</v>
+      </c>
+      <c r="F119" s="20">
+        <v>46128</v>
+      </c>
+      <c r="G119" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="B119" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="C119" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="D119" s="27"/>
-      <c r="E119" s="27"/>
-      <c r="F119" s="26"/>
-      <c r="G119" s="26">
-        <f t="shared" si="2"/>
-        <v>2</v>
+        <v>46130</v>
       </c>
       <c r="H119" s="12"/>
       <c r="I119" s="12"/>
@@ -15385,26 +15443,32 @@
       <c r="AA119" s="12"/>
       <c r="AB119" s="12"/>
       <c r="AC119" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B120" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C120" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D120" s="24" t="s">
+        <v>850</v>
+      </c>
+      <c r="E120" s="24" t="s">
+        <v>851</v>
+      </c>
+      <c r="F120" s="20">
+        <v>46128</v>
+      </c>
+      <c r="G120" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="B120" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="C120" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="D120" s="27"/>
-      <c r="E120" s="27"/>
-      <c r="F120" s="26"/>
-      <c r="G120" s="26">
-        <f t="shared" si="2"/>
-        <v>2</v>
+        <v>46130</v>
       </c>
       <c r="H120" s="12"/>
       <c r="I120" s="12"/>
@@ -15428,25 +15492,25 @@
       <c r="AA120" s="12"/>
       <c r="AB120" s="12"/>
       <c r="AC120" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="B121" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C121" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="D121" s="21"/>
+      <c r="E121" s="21"/>
+      <c r="F121" s="20"/>
+      <c r="G121" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="B121" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="C121" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="D121" s="27"/>
-      <c r="E121" s="27"/>
-      <c r="F121" s="26"/>
-      <c r="G121" s="26">
-        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H121" s="12"/>
@@ -15471,31 +15535,31 @@
       <c r="AA121" s="12"/>
       <c r="AB121" s="12"/>
       <c r="AC121" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="B122" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C122" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="D122" s="21">
+        <v>-4.9643360000000003</v>
+      </c>
+      <c r="E122" s="21">
+        <v>-38.996361</v>
+      </c>
+      <c r="F122" s="20">
+        <v>46111</v>
+      </c>
+      <c r="G122" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="B122" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="C122" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="D122" s="27">
-        <v>-4.9643360000000003</v>
-      </c>
-      <c r="E122" s="27">
-        <v>-38.996361</v>
-      </c>
-      <c r="F122" s="26">
-        <v>46111</v>
-      </c>
-      <c r="G122" s="26">
-        <f t="shared" si="2"/>
         <v>46113</v>
       </c>
       <c r="H122" s="12">
@@ -15562,25 +15626,25 @@
         <v>8</v>
       </c>
       <c r="AC122" s="13">
+        <f t="shared" si="4"/>
+        <v>4915</v>
+      </c>
+    </row>
+    <row r="123" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="B123" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C123" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="D123" s="21"/>
+      <c r="E123" s="21"/>
+      <c r="F123" s="20"/>
+      <c r="G123" s="20">
         <f t="shared" si="3"/>
-        <v>4915</v>
-      </c>
-    </row>
-    <row r="123" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="B123" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="C123" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="D123" s="27"/>
-      <c r="E123" s="27"/>
-      <c r="F123" s="26"/>
-      <c r="G123" s="26">
-        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H123" s="12"/>
@@ -15605,25 +15669,25 @@
       <c r="AA123" s="12"/>
       <c r="AB123" s="12"/>
       <c r="AC123" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="B124" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="C124" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="D124" s="21"/>
+      <c r="E124" s="21"/>
+      <c r="F124" s="20"/>
+      <c r="G124" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="B124" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="C124" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="D124" s="27"/>
-      <c r="E124" s="27"/>
-      <c r="F124" s="26"/>
-      <c r="G124" s="26">
-        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H124" s="12"/>
@@ -15648,25 +15712,25 @@
       <c r="AA124" s="12"/>
       <c r="AB124" s="12"/>
       <c r="AC124" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="B125" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="C125" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="D125" s="21"/>
+      <c r="E125" s="21"/>
+      <c r="F125" s="20"/>
+      <c r="G125" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="B125" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="C125" s="25" t="s">
-        <v>65</v>
-      </c>
-      <c r="D125" s="27"/>
-      <c r="E125" s="27"/>
-      <c r="F125" s="26"/>
-      <c r="G125" s="26">
-        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H125" s="12"/>
@@ -15691,25 +15755,25 @@
       <c r="AA125" s="12"/>
       <c r="AB125" s="12"/>
       <c r="AC125" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="B126" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="C126" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="D126" s="21"/>
+      <c r="E126" s="21"/>
+      <c r="F126" s="20"/>
+      <c r="G126" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="25" t="s">
-        <v>69</v>
-      </c>
-      <c r="B126" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C126" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="D126" s="27"/>
-      <c r="E126" s="27"/>
-      <c r="F126" s="26"/>
-      <c r="G126" s="26">
-        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H126" s="12"/>
@@ -15734,25 +15798,25 @@
       <c r="AA126" s="12"/>
       <c r="AB126" s="12"/>
       <c r="AC126" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="B127" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="C127" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="D127" s="21"/>
+      <c r="E127" s="21"/>
+      <c r="F127" s="20"/>
+      <c r="G127" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="25" t="s">
-        <v>215</v>
-      </c>
-      <c r="B127" s="25" t="s">
-        <v>210</v>
-      </c>
-      <c r="C127" s="25" t="s">
-        <v>216</v>
-      </c>
-      <c r="D127" s="27"/>
-      <c r="E127" s="27"/>
-      <c r="F127" s="26"/>
-      <c r="G127" s="26">
-        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H127" s="12"/>
@@ -15777,25 +15841,25 @@
       <c r="AA127" s="12"/>
       <c r="AB127" s="12"/>
       <c r="AC127" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="19" t="s">
+        <v>267</v>
+      </c>
+      <c r="B128" s="19" t="s">
+        <v>268</v>
+      </c>
+      <c r="C128" s="19" t="s">
+        <v>269</v>
+      </c>
+      <c r="D128" s="21"/>
+      <c r="E128" s="21"/>
+      <c r="F128" s="20"/>
+      <c r="G128" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="25" t="s">
-        <v>267</v>
-      </c>
-      <c r="B128" s="25" t="s">
-        <v>268</v>
-      </c>
-      <c r="C128" s="25" t="s">
-        <v>269</v>
-      </c>
-      <c r="D128" s="27"/>
-      <c r="E128" s="27"/>
-      <c r="F128" s="26"/>
-      <c r="G128" s="26">
-        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H128" s="12"/>
@@ -15820,25 +15884,25 @@
       <c r="AA128" s="12"/>
       <c r="AB128" s="12"/>
       <c r="AC128" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="19" t="s">
+        <v>273</v>
+      </c>
+      <c r="B129" s="19" t="s">
+        <v>274</v>
+      </c>
+      <c r="C129" s="19" t="s">
+        <v>275</v>
+      </c>
+      <c r="D129" s="21"/>
+      <c r="E129" s="21"/>
+      <c r="F129" s="20"/>
+      <c r="G129" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="25" t="s">
-        <v>273</v>
-      </c>
-      <c r="B129" s="25" t="s">
-        <v>274</v>
-      </c>
-      <c r="C129" s="25" t="s">
-        <v>275</v>
-      </c>
-      <c r="D129" s="27"/>
-      <c r="E129" s="27"/>
-      <c r="F129" s="26"/>
-      <c r="G129" s="26">
-        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H129" s="12"/>
@@ -15863,31 +15927,31 @@
       <c r="AA129" s="12"/>
       <c r="AB129" s="12"/>
       <c r="AC129" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="19" t="s">
+        <v>279</v>
+      </c>
+      <c r="B130" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C130" s="19" t="s">
+        <v>280</v>
+      </c>
+      <c r="D130" s="21">
+        <v>-4.1980709999999997</v>
+      </c>
+      <c r="E130" s="21">
+        <v>-38.904389999999999</v>
+      </c>
+      <c r="F130" s="20">
+        <v>46104</v>
+      </c>
+      <c r="G130" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="25" t="s">
-        <v>279</v>
-      </c>
-      <c r="B130" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="C130" s="25" t="s">
-        <v>280</v>
-      </c>
-      <c r="D130" s="27">
-        <v>-4.1980709999999997</v>
-      </c>
-      <c r="E130" s="27">
-        <v>-38.904389999999999</v>
-      </c>
-      <c r="F130" s="26">
-        <v>46104</v>
-      </c>
-      <c r="G130" s="26">
-        <f t="shared" si="2"/>
         <v>46106</v>
       </c>
       <c r="H130" s="12">
@@ -15954,31 +16018,31 @@
         <v>0</v>
       </c>
       <c r="AC130" s="13">
+        <f t="shared" si="4"/>
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="131" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="B131" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C131" s="19" t="s">
+        <v>285</v>
+      </c>
+      <c r="D131" s="21">
+        <v>-4.2305849999999996</v>
+      </c>
+      <c r="E131" s="21">
+        <v>-38.930357000000001</v>
+      </c>
+      <c r="F131" s="20">
+        <v>46104</v>
+      </c>
+      <c r="G131" s="20">
         <f t="shared" si="3"/>
-        <v>1145</v>
-      </c>
-    </row>
-    <row r="131" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="25" t="s">
-        <v>284</v>
-      </c>
-      <c r="B131" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="C131" s="25" t="s">
-        <v>285</v>
-      </c>
-      <c r="D131" s="27">
-        <v>-4.2305849999999996</v>
-      </c>
-      <c r="E131" s="27">
-        <v>-38.930357000000001</v>
-      </c>
-      <c r="F131" s="26">
-        <v>46104</v>
-      </c>
-      <c r="G131" s="26">
-        <f t="shared" si="2"/>
         <v>46106</v>
       </c>
       <c r="H131" s="12">
@@ -16045,31 +16109,31 @@
         <v>0</v>
       </c>
       <c r="AC131" s="13">
+        <f t="shared" si="4"/>
+        <v>1984</v>
+      </c>
+    </row>
+    <row r="132" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="B132" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C132" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="D132" s="21">
+        <v>-4.4056509999999998</v>
+      </c>
+      <c r="E132" s="21">
+        <v>-39.049227999999999</v>
+      </c>
+      <c r="F132" s="20">
+        <v>46107</v>
+      </c>
+      <c r="G132" s="20">
         <f t="shared" si="3"/>
-        <v>1984</v>
-      </c>
-    </row>
-    <row r="132" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="25" t="s">
-        <v>81</v>
-      </c>
-      <c r="B132" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="C132" s="25" t="s">
-        <v>82</v>
-      </c>
-      <c r="D132" s="27">
-        <v>-4.4056509999999998</v>
-      </c>
-      <c r="E132" s="27">
-        <v>-39.049227999999999</v>
-      </c>
-      <c r="F132" s="26">
-        <v>46107</v>
-      </c>
-      <c r="G132" s="26">
-        <f t="shared" si="2"/>
         <v>46109</v>
       </c>
       <c r="H132" s="12">
@@ -16136,31 +16200,31 @@
         <v>0</v>
       </c>
       <c r="AC132" s="13">
+        <f t="shared" si="4"/>
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="133" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="B133" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="C133" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="D133" s="21">
+        <v>-4.4364990000000004</v>
+      </c>
+      <c r="E133" s="21">
+        <v>-39.025733000000002</v>
+      </c>
+      <c r="F133" s="20">
+        <v>46107</v>
+      </c>
+      <c r="G133" s="20">
         <f t="shared" si="3"/>
-        <v>2597</v>
-      </c>
-    </row>
-    <row r="133" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="25" t="s">
-        <v>86</v>
-      </c>
-      <c r="B133" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="C133" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="D133" s="27">
-        <v>-4.4364990000000004</v>
-      </c>
-      <c r="E133" s="27">
-        <v>-39.025733000000002</v>
-      </c>
-      <c r="F133" s="26">
-        <v>46107</v>
-      </c>
-      <c r="G133" s="26">
-        <f t="shared" si="2"/>
         <v>46109</v>
       </c>
       <c r="H133" s="12">
@@ -16227,31 +16291,31 @@
         <v>0</v>
       </c>
       <c r="AC133" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1733</v>
       </c>
     </row>
     <row r="134" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="25" t="s">
+      <c r="A134" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="B134" s="25" t="s">
+      <c r="B134" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="C134" s="25" t="s">
+      <c r="C134" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="D134" s="27">
+      <c r="D134" s="21">
         <v>-4.4102269999999999</v>
       </c>
-      <c r="E134" s="27">
+      <c r="E134" s="21">
         <v>-39.059131999999998</v>
       </c>
-      <c r="F134" s="26">
+      <c r="F134" s="20">
         <v>46107</v>
       </c>
-      <c r="G134" s="26">
-        <f t="shared" ref="G134:G153" si="4">F134+2</f>
+      <c r="G134" s="20">
+        <f t="shared" ref="G134:G153" si="5">F134+2</f>
         <v>46109</v>
       </c>
       <c r="H134" s="12">
@@ -16318,25 +16382,25 @@
         <v>0</v>
       </c>
       <c r="AC134" s="13">
-        <f t="shared" ref="AC134:AC153" si="5">SUM(H134:AB134)</f>
+        <f t="shared" ref="AC134:AC153" si="6">SUM(H134:AB134)</f>
         <v>1724</v>
       </c>
     </row>
     <row r="135" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="25" t="s">
+      <c r="A135" s="19" t="s">
         <v>289</v>
       </c>
-      <c r="B135" s="25" t="s">
+      <c r="B135" s="19" t="s">
         <v>290</v>
       </c>
-      <c r="C135" s="25" t="s">
+      <c r="C135" s="19" t="s">
         <v>291</v>
       </c>
-      <c r="D135" s="27"/>
-      <c r="E135" s="27"/>
-      <c r="F135" s="26"/>
-      <c r="G135" s="26">
-        <f t="shared" si="4"/>
+      <c r="D135" s="21"/>
+      <c r="E135" s="21"/>
+      <c r="F135" s="20"/>
+      <c r="G135" s="20">
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="H135" s="12"/>
@@ -16361,25 +16425,25 @@
       <c r="AA135" s="12"/>
       <c r="AB135" s="12"/>
       <c r="AC135" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A136" s="19" t="s">
+        <v>294</v>
+      </c>
+      <c r="B136" s="19" t="s">
+        <v>295</v>
+      </c>
+      <c r="C136" s="19" t="s">
+        <v>296</v>
+      </c>
+      <c r="D136" s="21"/>
+      <c r="E136" s="21"/>
+      <c r="F136" s="20"/>
+      <c r="G136" s="20">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="25" t="s">
-        <v>294</v>
-      </c>
-      <c r="B136" s="25" t="s">
-        <v>295</v>
-      </c>
-      <c r="C136" s="25" t="s">
-        <v>296</v>
-      </c>
-      <c r="D136" s="27"/>
-      <c r="E136" s="27"/>
-      <c r="F136" s="26"/>
-      <c r="G136" s="26">
-        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="H136" s="12"/>
@@ -16404,25 +16468,25 @@
       <c r="AA136" s="12"/>
       <c r="AB136" s="12"/>
       <c r="AC136" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A137" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="B137" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="C137" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="D137" s="21"/>
+      <c r="E137" s="21"/>
+      <c r="F137" s="20"/>
+      <c r="G137" s="20">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="B137" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="C137" s="25" t="s">
-        <v>49</v>
-      </c>
-      <c r="D137" s="27"/>
-      <c r="E137" s="27"/>
-      <c r="F137" s="26"/>
-      <c r="G137" s="26">
-        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="H137" s="12"/>
@@ -16447,25 +16511,25 @@
       <c r="AA137" s="12"/>
       <c r="AB137" s="12"/>
       <c r="AC137" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A138" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B138" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="C138" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="D138" s="21"/>
+      <c r="E138" s="21"/>
+      <c r="F138" s="20"/>
+      <c r="G138" s="20">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="25" t="s">
-        <v>53</v>
-      </c>
-      <c r="B138" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="C138" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="D138" s="27"/>
-      <c r="E138" s="27"/>
-      <c r="F138" s="26"/>
-      <c r="G138" s="26">
-        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="H138" s="12"/>
@@ -16490,25 +16554,25 @@
       <c r="AA138" s="12"/>
       <c r="AB138" s="12"/>
       <c r="AC138" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="B139" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="C139" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="D139" s="21"/>
+      <c r="E139" s="21"/>
+      <c r="F139" s="20"/>
+      <c r="G139" s="20">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="B139" s="25" t="s">
-        <v>58</v>
-      </c>
-      <c r="C139" s="25" t="s">
-        <v>59</v>
-      </c>
-      <c r="D139" s="27"/>
-      <c r="E139" s="27"/>
-      <c r="F139" s="26"/>
-      <c r="G139" s="26">
-        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="H139" s="12"/>
@@ -16533,31 +16597,31 @@
       <c r="AA139" s="12"/>
       <c r="AB139" s="12"/>
       <c r="AC139" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="B140" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="C140" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="D140" s="21">
+        <v>-4.8604089999999998</v>
+      </c>
+      <c r="E140" s="21">
+        <v>-39.051761999999997</v>
+      </c>
+      <c r="F140" s="20">
+        <v>46111</v>
+      </c>
+      <c r="G140" s="20">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="25" t="s">
-        <v>75</v>
-      </c>
-      <c r="B140" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="C140" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="D140" s="27">
-        <v>-4.8604089999999998</v>
-      </c>
-      <c r="E140" s="27">
-        <v>-39.051761999999997</v>
-      </c>
-      <c r="F140" s="26">
-        <v>46111</v>
-      </c>
-      <c r="G140" s="26">
-        <f t="shared" si="4"/>
         <v>46113</v>
       </c>
       <c r="H140" s="12">
@@ -16624,26 +16688,32 @@
         <v>1</v>
       </c>
       <c r="AC140" s="13">
+        <f t="shared" si="6"/>
+        <v>1839</v>
+      </c>
+    </row>
+    <row r="141" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="B141" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="C141" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="D141" s="24" t="s">
+        <v>852</v>
+      </c>
+      <c r="E141" s="24" t="s">
+        <v>853</v>
+      </c>
+      <c r="F141" s="20">
+        <v>46128</v>
+      </c>
+      <c r="G141" s="20">
         <f t="shared" si="5"/>
-        <v>1839</v>
-      </c>
-    </row>
-    <row r="141" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="25" t="s">
-        <v>209</v>
-      </c>
-      <c r="B141" s="25" t="s">
-        <v>210</v>
-      </c>
-      <c r="C141" s="25" t="s">
-        <v>211</v>
-      </c>
-      <c r="D141" s="27"/>
-      <c r="E141" s="27"/>
-      <c r="F141" s="26"/>
-      <c r="G141" s="26">
-        <f t="shared" si="4"/>
-        <v>2</v>
+        <v>46130</v>
       </c>
       <c r="H141" s="12"/>
       <c r="I141" s="12"/>
@@ -16667,25 +16737,25 @@
       <c r="AA141" s="12"/>
       <c r="AB141" s="12"/>
       <c r="AC141" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A142" s="19" t="s">
+        <v>220</v>
+      </c>
+      <c r="B142" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="C142" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="D142" s="21"/>
+      <c r="E142" s="21"/>
+      <c r="F142" s="20"/>
+      <c r="G142" s="20">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="25" t="s">
-        <v>220</v>
-      </c>
-      <c r="B142" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="C142" s="25" t="s">
-        <v>221</v>
-      </c>
-      <c r="D142" s="27"/>
-      <c r="E142" s="27"/>
-      <c r="F142" s="26"/>
-      <c r="G142" s="26">
-        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="H142" s="12"/>
@@ -16710,25 +16780,25 @@
       <c r="AA142" s="12"/>
       <c r="AB142" s="12"/>
       <c r="AC142" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A143" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="B143" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="C143" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="D143" s="21"/>
+      <c r="E143" s="21"/>
+      <c r="F143" s="20"/>
+      <c r="G143" s="20">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="25" t="s">
-        <v>225</v>
-      </c>
-      <c r="B143" s="25" t="s">
-        <v>148</v>
-      </c>
-      <c r="C143" s="25" t="s">
-        <v>226</v>
-      </c>
-      <c r="D143" s="27"/>
-      <c r="E143" s="27"/>
-      <c r="F143" s="26"/>
-      <c r="G143" s="26">
-        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="H143" s="12"/>
@@ -16753,31 +16823,31 @@
       <c r="AA143" s="12"/>
       <c r="AB143" s="12"/>
       <c r="AC143" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="B144" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="C144" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="D144" s="21">
+        <v>-4.2870549999999996</v>
+      </c>
+      <c r="E144" s="21">
+        <v>-38.933565000000002</v>
+      </c>
+      <c r="F144" s="20">
+        <v>46104</v>
+      </c>
+      <c r="G144" s="20">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="25" t="s">
-        <v>230</v>
-      </c>
-      <c r="B144" s="25" t="s">
-        <v>231</v>
-      </c>
-      <c r="C144" s="25" t="s">
-        <v>232</v>
-      </c>
-      <c r="D144" s="27">
-        <v>-4.2870549999999996</v>
-      </c>
-      <c r="E144" s="27">
-        <v>-38.933565000000002</v>
-      </c>
-      <c r="F144" s="26">
-        <v>46104</v>
-      </c>
-      <c r="G144" s="26">
-        <f t="shared" si="4"/>
         <v>46106</v>
       </c>
       <c r="H144" s="12">
@@ -16844,25 +16914,25 @@
         <v>0</v>
       </c>
       <c r="AC144" s="13">
+        <f t="shared" si="6"/>
+        <v>2854</v>
+      </c>
+    </row>
+    <row r="145" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="B145" s="19" t="s">
+        <v>237</v>
+      </c>
+      <c r="C145" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="D145" s="21"/>
+      <c r="E145" s="21"/>
+      <c r="F145" s="20"/>
+      <c r="G145" s="20">
         <f t="shared" si="5"/>
-        <v>2854</v>
-      </c>
-    </row>
-    <row r="145" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="25" t="s">
-        <v>236</v>
-      </c>
-      <c r="B145" s="25" t="s">
-        <v>237</v>
-      </c>
-      <c r="C145" s="25" t="s">
-        <v>238</v>
-      </c>
-      <c r="D145" s="27"/>
-      <c r="E145" s="27"/>
-      <c r="F145" s="26"/>
-      <c r="G145" s="26">
-        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="H145" s="12"/>
@@ -16887,25 +16957,25 @@
       <c r="AA145" s="12"/>
       <c r="AB145" s="12"/>
       <c r="AC145" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A146" s="19" t="s">
+        <v>242</v>
+      </c>
+      <c r="B146" s="19" t="s">
+        <v>243</v>
+      </c>
+      <c r="C146" s="19" t="s">
+        <v>244</v>
+      </c>
+      <c r="D146" s="21"/>
+      <c r="E146" s="21"/>
+      <c r="F146" s="20"/>
+      <c r="G146" s="20">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="25" t="s">
-        <v>242</v>
-      </c>
-      <c r="B146" s="25" t="s">
-        <v>243</v>
-      </c>
-      <c r="C146" s="25" t="s">
-        <v>244</v>
-      </c>
-      <c r="D146" s="27"/>
-      <c r="E146" s="27"/>
-      <c r="F146" s="26"/>
-      <c r="G146" s="26">
-        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="H146" s="12"/>
@@ -16930,25 +17000,25 @@
       <c r="AA146" s="12"/>
       <c r="AB146" s="12"/>
       <c r="AC146" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A147" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="B147" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="C147" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="D147" s="21"/>
+      <c r="E147" s="21"/>
+      <c r="F147" s="20"/>
+      <c r="G147" s="20">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="25" t="s">
-        <v>248</v>
-      </c>
-      <c r="B147" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="C147" s="25" t="s">
-        <v>249</v>
-      </c>
-      <c r="D147" s="27"/>
-      <c r="E147" s="27"/>
-      <c r="F147" s="26"/>
-      <c r="G147" s="26">
-        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="H147" s="12"/>
@@ -16973,25 +17043,25 @@
       <c r="AA147" s="12"/>
       <c r="AB147" s="12"/>
       <c r="AC147" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="B148" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="C148" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="D148" s="21"/>
+      <c r="E148" s="21"/>
+      <c r="F148" s="20"/>
+      <c r="G148" s="20">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="25" t="s">
-        <v>253</v>
-      </c>
-      <c r="B148" s="25" t="s">
-        <v>193</v>
-      </c>
-      <c r="C148" s="25" t="s">
-        <v>254</v>
-      </c>
-      <c r="D148" s="27"/>
-      <c r="E148" s="27"/>
-      <c r="F148" s="26"/>
-      <c r="G148" s="26">
-        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="H148" s="12"/>
@@ -17016,25 +17086,25 @@
       <c r="AA148" s="12"/>
       <c r="AB148" s="12"/>
       <c r="AC148" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="19" t="s">
+        <v>258</v>
+      </c>
+      <c r="B149" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="C149" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="D149" s="21"/>
+      <c r="E149" s="21"/>
+      <c r="F149" s="20"/>
+      <c r="G149" s="20">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="25" t="s">
-        <v>258</v>
-      </c>
-      <c r="B149" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="C149" s="25" t="s">
-        <v>259</v>
-      </c>
-      <c r="D149" s="27"/>
-      <c r="E149" s="27"/>
-      <c r="F149" s="26"/>
-      <c r="G149" s="26">
-        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="H149" s="12"/>
@@ -17059,25 +17129,25 @@
       <c r="AA149" s="12"/>
       <c r="AB149" s="12"/>
       <c r="AC149" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A150" s="19" t="s">
+        <v>263</v>
+      </c>
+      <c r="B150" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="C150" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="D150" s="21"/>
+      <c r="E150" s="21"/>
+      <c r="F150" s="20"/>
+      <c r="G150" s="20">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="25" t="s">
-        <v>263</v>
-      </c>
-      <c r="B150" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="C150" s="25" t="s">
-        <v>264</v>
-      </c>
-      <c r="D150" s="27"/>
-      <c r="E150" s="27"/>
-      <c r="F150" s="26"/>
-      <c r="G150" s="26">
-        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="H150" s="12"/>
@@ -17102,25 +17172,25 @@
       <c r="AA150" s="12"/>
       <c r="AB150" s="12"/>
       <c r="AC150" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A151" s="19" t="s">
+        <v>300</v>
+      </c>
+      <c r="B151" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="C151" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D151" s="21"/>
+      <c r="E151" s="21"/>
+      <c r="F151" s="20"/>
+      <c r="G151" s="20">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="25" t="s">
-        <v>300</v>
-      </c>
-      <c r="B151" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="C151" s="25" t="s">
-        <v>301</v>
-      </c>
-      <c r="D151" s="27"/>
-      <c r="E151" s="27"/>
-      <c r="F151" s="26"/>
-      <c r="G151" s="26">
-        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="H151" s="12"/>
@@ -17145,26 +17215,32 @@
       <c r="AA151" s="12"/>
       <c r="AB151" s="12"/>
       <c r="AC151" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="19" t="s">
+        <v>305</v>
+      </c>
+      <c r="B152" s="19" t="s">
+        <v>306</v>
+      </c>
+      <c r="C152" s="19" t="s">
+        <v>307</v>
+      </c>
+      <c r="D152" s="24" t="s">
+        <v>854</v>
+      </c>
+      <c r="E152" s="24" t="s">
+        <v>855</v>
+      </c>
+      <c r="F152" s="20">
+        <v>46131</v>
+      </c>
+      <c r="G152" s="20">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="25" t="s">
-        <v>305</v>
-      </c>
-      <c r="B152" s="25" t="s">
-        <v>306</v>
-      </c>
-      <c r="C152" s="25" t="s">
-        <v>307</v>
-      </c>
-      <c r="D152" s="27"/>
-      <c r="E152" s="27"/>
-      <c r="F152" s="26"/>
-      <c r="G152" s="26">
-        <f t="shared" si="4"/>
-        <v>2</v>
+        <v>46133</v>
       </c>
       <c r="H152" s="12"/>
       <c r="I152" s="12"/>
@@ -17188,25 +17264,25 @@
       <c r="AA152" s="12"/>
       <c r="AB152" s="12"/>
       <c r="AC152" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A153" s="19" t="s">
+        <v>312</v>
+      </c>
+      <c r="B153" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="C153" s="19" t="s">
+        <v>313</v>
+      </c>
+      <c r="D153" s="21"/>
+      <c r="E153" s="21"/>
+      <c r="F153" s="20"/>
+      <c r="G153" s="20">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="25" t="s">
-        <v>312</v>
-      </c>
-      <c r="B153" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="C153" s="25" t="s">
-        <v>313</v>
-      </c>
-      <c r="D153" s="27"/>
-      <c r="E153" s="27"/>
-      <c r="F153" s="26"/>
-      <c r="G153" s="26">
-        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="H153" s="12"/>
@@ -17231,7 +17307,7 @@
       <c r="AA153" s="12"/>
       <c r="AB153" s="12"/>
       <c r="AC153" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>

--- a/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
+++ b/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBDF5C1C-8EF7-4C09-A9EF-301FAD73A005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AF84285-5E55-4420-980E-347E807F4178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
   </bookViews>
   <sheets>
     <sheet name="LISTA DE PONTOS" sheetId="1" r:id="rId1"/>
     <sheet name="DADOS COLETADOS" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'DADOS COLETADOS'!$A$4:$AC$153</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'LISTA DE PONTOS'!$A$1:$K$150</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'LISTA DE PONTOS'!$A$1:$K$150</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'LISTA DE PONTOS'!$1:$1</definedName>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1845" uniqueCount="856">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1833" uniqueCount="844">
   <si>
     <t>WKT</t>
   </si>
@@ -2575,51 +2576,14 @@
   </si>
   <si>
     <t>456ECE0050S0</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -4,791155°</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -40,827958°</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -4,702947°</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -40,549088°</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -4,752180°</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -40,837868°</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -4,748082°</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -40,788863°</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -4,931354°</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -40,527044°</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -4,567784°</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -41,220273°</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000000"/>
-    <numFmt numFmtId="165" formatCode="0.00000"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -2738,7 +2702,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2799,9 +2763,6 @@
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4259,7 +4220,7 @@
         <v>16</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="K2" s="6" t="s">
         <v>18</v>
@@ -4294,7 +4255,7 @@
         <v>16</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="K3" s="6" t="s">
         <v>18</v>
@@ -4679,7 +4640,7 @@
         <v>16</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="K14" s="6" t="s">
         <v>18</v>
@@ -4728,10 +4689,10 @@
         <v>220</v>
       </c>
       <c r="C16" s="5">
-        <v>-4.4024999999999999</v>
+        <v>-4.3993669999999998</v>
       </c>
       <c r="D16" s="5">
-        <v>-40.700612999999997</v>
+        <v>-40.711840000000002</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>87</v>
@@ -4749,7 +4710,7 @@
         <v>16</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>17</v>
+        <v>810</v>
       </c>
       <c r="K16" s="6" t="s">
         <v>18</v>
@@ -5414,7 +5375,7 @@
         <v>16</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>17</v>
+        <v>810</v>
       </c>
       <c r="K35" s="6" t="s">
         <v>310</v>
@@ -5778,10 +5739,10 @@
         <v>332</v>
       </c>
       <c r="C46" s="5">
-        <v>-4.5646829999999996</v>
+        <v>-4.5644640000000001</v>
       </c>
       <c r="D46" s="5">
-        <v>-40.746032999999997</v>
+        <v>-40.746068999999999</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>87</v>
@@ -5799,7 +5760,7 @@
         <v>101</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>17</v>
+        <v>810</v>
       </c>
       <c r="K46" s="6" t="s">
         <v>18</v>
@@ -5974,7 +5935,7 @@
         <v>151</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="K51" s="6" t="s">
         <v>18</v>
@@ -7633,10 +7594,10 @@
         <v>576</v>
       </c>
       <c r="C99" s="5">
-        <v>-4.3929830000000001</v>
+        <v>-4.3822749999999999</v>
       </c>
       <c r="D99" s="5">
-        <v>-40.714516000000003</v>
+        <v>-40.712611000000003</v>
       </c>
       <c r="E99" s="4" t="s">
         <v>210</v>
@@ -7654,7 +7615,7 @@
         <v>151</v>
       </c>
       <c r="J99" s="6" t="s">
-        <v>17</v>
+        <v>810</v>
       </c>
       <c r="K99" s="6" t="s">
         <v>18</v>
@@ -8144,7 +8105,7 @@
         <v>101</v>
       </c>
       <c r="J113" s="6" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="K113" s="6" t="s">
         <v>18</v>
@@ -9243,10 +9204,10 @@
         <v>778</v>
       </c>
       <c r="C145" s="5">
-        <v>-4.5586159999999998</v>
+        <v>-4.5583349999999996</v>
       </c>
       <c r="D145" s="5">
-        <v>-40.729683000000001</v>
+        <v>-40.729585999999998</v>
       </c>
       <c r="E145" s="4" t="s">
         <v>625</v>
@@ -9264,7 +9225,7 @@
         <v>101</v>
       </c>
       <c r="J145" s="6" t="s">
-        <v>17</v>
+        <v>810</v>
       </c>
       <c r="K145" s="6" t="s">
         <v>18</v>
@@ -9477,97 +9438,97 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="29" t="s">
+      <c r="B1" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="30" t="s">
+      <c r="D1" s="29" t="s">
         <v>812</v>
       </c>
-      <c r="E1" s="30"/>
-      <c r="F1" s="31" t="s">
+      <c r="E1" s="29"/>
+      <c r="F1" s="30" t="s">
         <v>813</v>
       </c>
-      <c r="G1" s="31"/>
-      <c r="H1" s="27" t="s">
+      <c r="G1" s="30"/>
+      <c r="H1" s="26" t="s">
         <v>814</v>
       </c>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
-      <c r="P1" s="27"/>
-      <c r="Q1" s="27"/>
-      <c r="R1" s="27"/>
-      <c r="S1" s="27"/>
-      <c r="T1" s="27"/>
-      <c r="U1" s="27"/>
-      <c r="V1" s="27"/>
-      <c r="W1" s="27"/>
-      <c r="X1" s="27"/>
-      <c r="Y1" s="27"/>
-      <c r="Z1" s="27"/>
-      <c r="AA1" s="27"/>
-      <c r="AB1" s="27"/>
-      <c r="AC1" s="25" t="s">
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="26"/>
+      <c r="P1" s="26"/>
+      <c r="Q1" s="26"/>
+      <c r="R1" s="26"/>
+      <c r="S1" s="26"/>
+      <c r="T1" s="26"/>
+      <c r="U1" s="26"/>
+      <c r="V1" s="26"/>
+      <c r="W1" s="26"/>
+      <c r="X1" s="26"/>
+      <c r="Y1" s="26"/>
+      <c r="Z1" s="26"/>
+      <c r="AA1" s="26"/>
+      <c r="AB1" s="26"/>
+      <c r="AC1" s="24" t="s">
         <v>815</v>
       </c>
     </row>
     <row r="2" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="28"/>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="26" t="s">
+      <c r="A2" s="27"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="25" t="s">
         <v>816</v>
       </c>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
       <c r="K2" s="9" t="s">
         <v>817</v>
       </c>
       <c r="L2" s="9" t="s">
         <v>817</v>
       </c>
-      <c r="M2" s="27" t="s">
+      <c r="M2" s="26" t="s">
         <v>818</v>
       </c>
-      <c r="N2" s="27"/>
-      <c r="O2" s="27"/>
-      <c r="P2" s="27"/>
-      <c r="Q2" s="27"/>
-      <c r="R2" s="27"/>
-      <c r="S2" s="27"/>
-      <c r="T2" s="27"/>
-      <c r="U2" s="27"/>
-      <c r="V2" s="27"/>
-      <c r="W2" s="27"/>
-      <c r="X2" s="27"/>
-      <c r="Y2" s="27"/>
-      <c r="Z2" s="27"/>
-      <c r="AA2" s="27"/>
-      <c r="AB2" s="27"/>
-      <c r="AC2" s="25"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="26"/>
+      <c r="R2" s="26"/>
+      <c r="S2" s="26"/>
+      <c r="T2" s="26"/>
+      <c r="U2" s="26"/>
+      <c r="V2" s="26"/>
+      <c r="W2" s="26"/>
+      <c r="X2" s="26"/>
+      <c r="Y2" s="26"/>
+      <c r="Z2" s="26"/>
+      <c r="AA2" s="26"/>
+      <c r="AB2" s="26"/>
+      <c r="AC2" s="24"/>
     </row>
     <row r="3" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="28"/>
-      <c r="B3" s="29"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
+      <c r="A3" s="27"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
       <c r="H3" s="8" t="s">
         <v>819</v>
       </c>
@@ -9631,20 +9592,20 @@
       <c r="AB3" s="7" t="s">
         <v>839</v>
       </c>
-      <c r="AC3" s="25"/>
+      <c r="AC3" s="24"/>
     </row>
     <row r="4" spans="1:29" ht="104.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="28"/>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
+      <c r="A4" s="27"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
       <c r="D4" s="22" t="s">
         <v>2</v>
       </c>
       <c r="E4" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
       <c r="H4" s="10"/>
       <c r="I4" s="10"/>
       <c r="J4" s="10"/>
@@ -9666,7 +9627,7 @@
       <c r="Z4" s="11"/>
       <c r="AA4" s="11"/>
       <c r="AB4" s="11"/>
-      <c r="AC4" s="25"/>
+      <c r="AC4" s="24"/>
     </row>
     <row r="5" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="19" t="s">
@@ -10505,11 +10466,11 @@
       <c r="C22" s="19" t="s">
         <v>626</v>
       </c>
-      <c r="D22" s="24" t="s">
-        <v>844</v>
-      </c>
-      <c r="E22" s="24" t="s">
-        <v>845</v>
+      <c r="D22" s="21">
+        <v>-4.7911549999999998</v>
+      </c>
+      <c r="E22" s="21">
+        <v>-40.827958000000002</v>
       </c>
       <c r="F22" s="20">
         <v>46128</v>
@@ -10518,30 +10479,72 @@
         <f t="shared" ref="G22" si="2">F22+2</f>
         <v>46130</v>
       </c>
-      <c r="H22" s="12"/>
-      <c r="I22" s="12"/>
-      <c r="J22" s="12"/>
-      <c r="K22" s="12"/>
-      <c r="L22" s="12"/>
-      <c r="M22" s="12"/>
-      <c r="N22" s="12"/>
-      <c r="O22" s="12"/>
-      <c r="P22" s="12"/>
-      <c r="Q22" s="12"/>
-      <c r="R22" s="12"/>
-      <c r="S22" s="12"/>
-      <c r="T22" s="12"/>
-      <c r="U22" s="12"/>
-      <c r="V22" s="12"/>
-      <c r="W22" s="12"/>
-      <c r="X22" s="12"/>
-      <c r="Y22" s="12"/>
-      <c r="Z22" s="12"/>
-      <c r="AA22" s="12"/>
-      <c r="AB22" s="12"/>
+      <c r="H22" s="12">
+        <v>1240</v>
+      </c>
+      <c r="I22" s="12">
+        <v>600</v>
+      </c>
+      <c r="J22" s="12">
+        <v>10</v>
+      </c>
+      <c r="K22" s="12">
+        <v>134</v>
+      </c>
+      <c r="L22" s="12">
+        <v>19</v>
+      </c>
+      <c r="M22" s="12">
+        <v>9</v>
+      </c>
+      <c r="N22" s="12">
+        <v>3</v>
+      </c>
+      <c r="O22" s="12">
+        <v>1</v>
+      </c>
+      <c r="P22" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="12">
+        <v>0</v>
+      </c>
+      <c r="R22" s="12">
+        <v>2</v>
+      </c>
+      <c r="S22" s="12">
+        <v>0</v>
+      </c>
+      <c r="T22" s="12">
+        <v>20</v>
+      </c>
+      <c r="U22" s="12">
+        <v>0</v>
+      </c>
+      <c r="V22" s="12">
+        <v>0</v>
+      </c>
+      <c r="W22" s="12">
+        <v>0</v>
+      </c>
+      <c r="X22" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="12">
+        <v>0</v>
+      </c>
       <c r="AC22" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="23" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -12079,12 +12082,18 @@
       <c r="C54" s="19" t="s">
         <v>779</v>
       </c>
-      <c r="D54" s="21"/>
-      <c r="E54" s="21"/>
-      <c r="F54" s="20"/>
+      <c r="D54" s="21">
+        <v>-4.5583349999999996</v>
+      </c>
+      <c r="E54" s="21">
+        <v>-40.729585999999998</v>
+      </c>
+      <c r="F54" s="20">
+        <v>46131</v>
+      </c>
       <c r="G54" s="20">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>46133</v>
       </c>
       <c r="H54" s="12"/>
       <c r="I54" s="12"/>
@@ -12562,12 +12571,18 @@
       <c r="C63" s="19" t="s">
         <v>333</v>
       </c>
-      <c r="D63" s="21"/>
-      <c r="E63" s="21"/>
-      <c r="F63" s="20"/>
+      <c r="D63" s="21">
+        <v>-4.5644640000000001</v>
+      </c>
+      <c r="E63" s="21">
+        <v>-40.746068999999999</v>
+      </c>
+      <c r="F63" s="20">
+        <v>46131</v>
+      </c>
       <c r="G63" s="20">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>46133</v>
       </c>
       <c r="H63" s="12"/>
       <c r="I63" s="12"/>
@@ -12782,11 +12797,11 @@
       <c r="C67" s="19" t="s">
         <v>350</v>
       </c>
-      <c r="D67" s="24" t="s">
-        <v>846</v>
-      </c>
-      <c r="E67" s="24" t="s">
-        <v>847</v>
+      <c r="D67" s="21">
+        <v>-4.702947</v>
+      </c>
+      <c r="E67" s="21">
+        <v>-40.549087999999998</v>
       </c>
       <c r="F67" s="20">
         <v>46128</v>
@@ -12795,30 +12810,72 @@
         <f t="shared" si="0"/>
         <v>46130</v>
       </c>
-      <c r="H67" s="12"/>
-      <c r="I67" s="12"/>
-      <c r="J67" s="12"/>
-      <c r="K67" s="12"/>
-      <c r="L67" s="12"/>
-      <c r="M67" s="12"/>
-      <c r="N67" s="12"/>
-      <c r="O67" s="12"/>
-      <c r="P67" s="12"/>
-      <c r="Q67" s="12"/>
-      <c r="R67" s="12"/>
-      <c r="S67" s="12"/>
-      <c r="T67" s="12"/>
-      <c r="U67" s="12"/>
-      <c r="V67" s="12"/>
-      <c r="W67" s="12"/>
-      <c r="X67" s="12"/>
-      <c r="Y67" s="12"/>
-      <c r="Z67" s="12"/>
-      <c r="AA67" s="12"/>
-      <c r="AB67" s="12"/>
+      <c r="H67" s="12">
+        <v>1256</v>
+      </c>
+      <c r="I67" s="12">
+        <v>1821</v>
+      </c>
+      <c r="J67" s="12">
+        <v>19</v>
+      </c>
+      <c r="K67" s="12">
+        <v>139</v>
+      </c>
+      <c r="L67" s="12">
+        <v>31</v>
+      </c>
+      <c r="M67" s="12">
+        <v>14</v>
+      </c>
+      <c r="N67" s="12">
+        <v>12</v>
+      </c>
+      <c r="O67" s="12">
+        <v>0</v>
+      </c>
+      <c r="P67" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q67" s="12">
+        <v>2</v>
+      </c>
+      <c r="R67" s="12">
+        <v>0</v>
+      </c>
+      <c r="S67" s="12">
+        <v>0</v>
+      </c>
+      <c r="T67" s="12">
+        <v>36</v>
+      </c>
+      <c r="U67" s="12">
+        <v>0</v>
+      </c>
+      <c r="V67" s="12">
+        <v>0</v>
+      </c>
+      <c r="W67" s="12">
+        <v>0</v>
+      </c>
+      <c r="X67" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y67" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z67" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA67" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB67" s="12">
+        <v>0</v>
+      </c>
       <c r="AC67" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3330</v>
       </c>
     </row>
     <row r="68" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -15107,12 +15164,18 @@
       <c r="C112" s="19" t="s">
         <v>577</v>
       </c>
-      <c r="D112" s="21"/>
-      <c r="E112" s="21"/>
-      <c r="F112" s="20"/>
+      <c r="D112" s="21">
+        <v>-4.3822749999999999</v>
+      </c>
+      <c r="E112" s="21">
+        <v>-40.712611000000003</v>
+      </c>
+      <c r="F112" s="20">
+        <v>46131</v>
+      </c>
       <c r="G112" s="20">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>46133</v>
       </c>
       <c r="H112" s="12"/>
       <c r="I112" s="12"/>
@@ -15408,11 +15471,11 @@
       <c r="C119" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="D119" s="24" t="s">
-        <v>848</v>
-      </c>
-      <c r="E119" s="24" t="s">
-        <v>849</v>
+      <c r="D119" s="21">
+        <v>-4.7521800000000001</v>
+      </c>
+      <c r="E119" s="21">
+        <v>-40.837868</v>
       </c>
       <c r="F119" s="20">
         <v>46128</v>
@@ -15421,30 +15484,72 @@
         <f t="shared" si="3"/>
         <v>46130</v>
       </c>
-      <c r="H119" s="12"/>
-      <c r="I119" s="12"/>
-      <c r="J119" s="12"/>
-      <c r="K119" s="12"/>
-      <c r="L119" s="12"/>
-      <c r="M119" s="12"/>
-      <c r="N119" s="12"/>
-      <c r="O119" s="12"/>
-      <c r="P119" s="12"/>
-      <c r="Q119" s="12"/>
-      <c r="R119" s="12"/>
-      <c r="S119" s="12"/>
-      <c r="T119" s="12"/>
-      <c r="U119" s="12"/>
-      <c r="V119" s="12"/>
-      <c r="W119" s="12"/>
-      <c r="X119" s="12"/>
-      <c r="Y119" s="12"/>
-      <c r="Z119" s="12"/>
-      <c r="AA119" s="12"/>
-      <c r="AB119" s="12"/>
+      <c r="H119" s="12">
+        <v>611</v>
+      </c>
+      <c r="I119" s="12">
+        <v>498</v>
+      </c>
+      <c r="J119" s="12">
+        <v>41</v>
+      </c>
+      <c r="K119" s="12">
+        <v>117</v>
+      </c>
+      <c r="L119" s="12">
+        <v>27</v>
+      </c>
+      <c r="M119" s="12">
+        <v>4</v>
+      </c>
+      <c r="N119" s="12">
+        <v>1</v>
+      </c>
+      <c r="O119" s="12">
+        <v>0</v>
+      </c>
+      <c r="P119" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q119" s="12">
+        <v>0</v>
+      </c>
+      <c r="R119" s="12">
+        <v>1</v>
+      </c>
+      <c r="S119" s="12">
+        <v>0</v>
+      </c>
+      <c r="T119" s="12">
+        <v>20</v>
+      </c>
+      <c r="U119" s="12">
+        <v>0</v>
+      </c>
+      <c r="V119" s="12">
+        <v>0</v>
+      </c>
+      <c r="W119" s="12">
+        <v>0</v>
+      </c>
+      <c r="X119" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y119" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z119" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA119" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB119" s="12">
+        <v>0</v>
+      </c>
       <c r="AC119" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="120" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -15457,11 +15562,11 @@
       <c r="C120" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="D120" s="24" t="s">
-        <v>850</v>
-      </c>
-      <c r="E120" s="24" t="s">
-        <v>851</v>
+      <c r="D120" s="21">
+        <v>-4.7480820000000001</v>
+      </c>
+      <c r="E120" s="21">
+        <v>-40.788862999999999</v>
       </c>
       <c r="F120" s="20">
         <v>46128</v>
@@ -15470,30 +15575,72 @@
         <f t="shared" si="3"/>
         <v>46130</v>
       </c>
-      <c r="H120" s="12"/>
-      <c r="I120" s="12"/>
-      <c r="J120" s="12"/>
-      <c r="K120" s="12"/>
-      <c r="L120" s="12"/>
-      <c r="M120" s="12"/>
-      <c r="N120" s="12"/>
-      <c r="O120" s="12"/>
-      <c r="P120" s="12"/>
-      <c r="Q120" s="12"/>
-      <c r="R120" s="12"/>
-      <c r="S120" s="12"/>
-      <c r="T120" s="12"/>
-      <c r="U120" s="12"/>
-      <c r="V120" s="12"/>
-      <c r="W120" s="12"/>
-      <c r="X120" s="12"/>
-      <c r="Y120" s="12"/>
-      <c r="Z120" s="12"/>
-      <c r="AA120" s="12"/>
-      <c r="AB120" s="12"/>
+      <c r="H120" s="12">
+        <v>1028</v>
+      </c>
+      <c r="I120" s="12">
+        <v>538</v>
+      </c>
+      <c r="J120" s="12">
+        <v>18</v>
+      </c>
+      <c r="K120" s="12">
+        <v>133</v>
+      </c>
+      <c r="L120" s="12">
+        <v>20</v>
+      </c>
+      <c r="M120" s="12">
+        <v>11</v>
+      </c>
+      <c r="N120" s="12">
+        <v>1</v>
+      </c>
+      <c r="O120" s="12">
+        <v>0</v>
+      </c>
+      <c r="P120" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q120" s="12">
+        <v>0</v>
+      </c>
+      <c r="R120" s="12">
+        <v>0</v>
+      </c>
+      <c r="S120" s="12">
+        <v>0</v>
+      </c>
+      <c r="T120" s="12">
+        <v>24</v>
+      </c>
+      <c r="U120" s="12">
+        <v>0</v>
+      </c>
+      <c r="V120" s="12">
+        <v>0</v>
+      </c>
+      <c r="W120" s="12">
+        <v>0</v>
+      </c>
+      <c r="X120" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y120" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z120" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA120" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB120" s="12">
+        <v>0</v>
+      </c>
       <c r="AC120" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="121" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -16702,11 +16849,11 @@
       <c r="C141" s="19" t="s">
         <v>211</v>
       </c>
-      <c r="D141" s="24" t="s">
-        <v>852</v>
-      </c>
-      <c r="E141" s="24" t="s">
-        <v>853</v>
+      <c r="D141" s="21">
+        <v>-4.9313539999999998</v>
+      </c>
+      <c r="E141" s="21">
+        <v>-40.527043999999997</v>
       </c>
       <c r="F141" s="20">
         <v>46128</v>
@@ -16715,30 +16862,72 @@
         <f t="shared" si="5"/>
         <v>46130</v>
       </c>
-      <c r="H141" s="12"/>
-      <c r="I141" s="12"/>
-      <c r="J141" s="12"/>
-      <c r="K141" s="12"/>
-      <c r="L141" s="12"/>
-      <c r="M141" s="12"/>
-      <c r="N141" s="12"/>
-      <c r="O141" s="12"/>
-      <c r="P141" s="12"/>
-      <c r="Q141" s="12"/>
-      <c r="R141" s="12"/>
-      <c r="S141" s="12"/>
-      <c r="T141" s="12"/>
-      <c r="U141" s="12"/>
-      <c r="V141" s="12"/>
-      <c r="W141" s="12"/>
-      <c r="X141" s="12"/>
-      <c r="Y141" s="12"/>
-      <c r="Z141" s="12"/>
-      <c r="AA141" s="12"/>
-      <c r="AB141" s="12"/>
+      <c r="H141" s="12">
+        <v>740</v>
+      </c>
+      <c r="I141" s="12">
+        <v>1769</v>
+      </c>
+      <c r="J141" s="12">
+        <v>25</v>
+      </c>
+      <c r="K141" s="12">
+        <v>225</v>
+      </c>
+      <c r="L141" s="12">
+        <v>38</v>
+      </c>
+      <c r="M141" s="12">
+        <v>10</v>
+      </c>
+      <c r="N141" s="12">
+        <v>5</v>
+      </c>
+      <c r="O141" s="12">
+        <v>0</v>
+      </c>
+      <c r="P141" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q141" s="12">
+        <v>0</v>
+      </c>
+      <c r="R141" s="12">
+        <v>3</v>
+      </c>
+      <c r="S141" s="12">
+        <v>0</v>
+      </c>
+      <c r="T141" s="12">
+        <v>23</v>
+      </c>
+      <c r="U141" s="12">
+        <v>1</v>
+      </c>
+      <c r="V141" s="12">
+        <v>0</v>
+      </c>
+      <c r="W141" s="12">
+        <v>0</v>
+      </c>
+      <c r="X141" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y141" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z141" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA141" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB141" s="12">
+        <v>0</v>
+      </c>
       <c r="AC141" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2840</v>
       </c>
     </row>
     <row r="142" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -16751,12 +16940,18 @@
       <c r="C142" s="19" t="s">
         <v>221</v>
       </c>
-      <c r="D142" s="21"/>
-      <c r="E142" s="21"/>
-      <c r="F142" s="20"/>
+      <c r="D142" s="21">
+        <v>-4.3993669999999998</v>
+      </c>
+      <c r="E142" s="21">
+        <v>-40.711840000000002</v>
+      </c>
+      <c r="F142" s="20">
+        <v>46131</v>
+      </c>
       <c r="G142" s="20">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>46133</v>
       </c>
       <c r="H142" s="12"/>
       <c r="I142" s="12"/>
@@ -17229,11 +17424,11 @@
       <c r="C152" s="19" t="s">
         <v>307</v>
       </c>
-      <c r="D152" s="24" t="s">
-        <v>854</v>
-      </c>
-      <c r="E152" s="24" t="s">
-        <v>855</v>
+      <c r="D152" s="21">
+        <v>-4.5677839999999996</v>
+      </c>
+      <c r="E152" s="21">
+        <v>-41.220272999999999</v>
       </c>
       <c r="F152" s="20">
         <v>46131</v>
@@ -17330,6 +17525,9 @@
       <c r="J157" s="18"/>
     </row>
   </sheetData>
+  <autoFilter ref="A4:AC153" xr:uid="{1D18A476-0271-4A84-BE9E-901865A86FD3}">
+    <filterColumn colId="5" showButton="0"/>
+  </autoFilter>
   <mergeCells count="9">
     <mergeCell ref="AC1:AC4"/>
     <mergeCell ref="H2:J2"/>

--- a/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
+++ b/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AF84285-5E55-4420-980E-347E807F4178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1CB0B2A-0249-4286-93D7-F0EFFD6D4942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
   </bookViews>
   <sheets>
     <sheet name="LISTA DE PONTOS" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1833" uniqueCount="844">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1833" uniqueCount="843">
   <si>
     <t>WKT</t>
   </si>
@@ -2473,9 +2473,6 @@
   </si>
   <si>
     <t>STATUS DE EXECUÇÃO</t>
-  </si>
-  <si>
-    <t>EM ANDAMENTO</t>
   </si>
   <si>
     <t>CONCLUÍDO</t>
@@ -4220,7 +4217,7 @@
         <v>16</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="K2" s="6" t="s">
         <v>18</v>
@@ -4255,7 +4252,7 @@
         <v>16</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="K3" s="6" t="s">
         <v>18</v>
@@ -4325,7 +4322,7 @@
         <v>16</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="K5" s="6" t="s">
         <v>18</v>
@@ -4605,7 +4602,7 @@
         <v>16</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="K13" s="6" t="s">
         <v>18</v>
@@ -4640,7 +4637,7 @@
         <v>16</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="K14" s="6" t="s">
         <v>18</v>
@@ -4780,7 +4777,7 @@
         <v>16</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="K18" s="6" t="s">
         <v>18</v>
@@ -5095,7 +5092,7 @@
         <v>16</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="K27" s="6" t="s">
         <v>18</v>
@@ -5130,7 +5127,7 @@
         <v>16</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="K28" s="6" t="s">
         <v>18</v>
@@ -5165,7 +5162,7 @@
         <v>16</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="K29" s="6" t="s">
         <v>18</v>
@@ -5200,7 +5197,7 @@
         <v>16</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="K30" s="6" t="s">
         <v>18</v>
@@ -5235,7 +5232,7 @@
         <v>16</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="K31" s="6" t="s">
         <v>18</v>
@@ -5655,7 +5652,7 @@
         <v>151</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="K43" s="6" t="s">
         <v>18</v>
@@ -5865,7 +5862,7 @@
         <v>101</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="K49" s="6" t="s">
         <v>18</v>
@@ -5900,7 +5897,7 @@
         <v>101</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="K50" s="6" t="s">
         <v>18</v>
@@ -5935,7 +5932,7 @@
         <v>151</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="K51" s="6" t="s">
         <v>18</v>
@@ -6565,7 +6562,7 @@
         <v>101</v>
       </c>
       <c r="J69" s="6" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="K69" s="6" t="s">
         <v>18</v>
@@ -6740,7 +6737,7 @@
         <v>101</v>
       </c>
       <c r="J74" s="6" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="K74" s="6" t="s">
         <v>18</v>
@@ -6950,7 +6947,7 @@
         <v>101</v>
       </c>
       <c r="J80" s="6" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="K80" s="6" t="s">
         <v>18</v>
@@ -7300,7 +7297,7 @@
         <v>151</v>
       </c>
       <c r="J90" s="6" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="K90" s="6" t="s">
         <v>18</v>
@@ -7335,7 +7332,7 @@
         <v>101</v>
       </c>
       <c r="J91" s="6" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="K91" s="6" t="s">
         <v>18</v>
@@ -7370,7 +7367,7 @@
         <v>101</v>
       </c>
       <c r="J92" s="6" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="K92" s="6" t="s">
         <v>18</v>
@@ -7545,7 +7542,7 @@
         <v>151</v>
       </c>
       <c r="J97" s="6" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="K97" s="6" t="s">
         <v>18</v>
@@ -7580,7 +7577,7 @@
         <v>101</v>
       </c>
       <c r="J98" s="6" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="K98" s="6" t="s">
         <v>18</v>
@@ -8035,7 +8032,7 @@
         <v>101</v>
       </c>
       <c r="J111" s="6" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="K111" s="6" t="s">
         <v>18</v>
@@ -8105,7 +8102,7 @@
         <v>101</v>
       </c>
       <c r="J113" s="6" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="K113" s="6" t="s">
         <v>18</v>
@@ -8420,7 +8417,7 @@
         <v>151</v>
       </c>
       <c r="J122" s="6" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="K122" s="6" t="s">
         <v>18</v>
@@ -8980,7 +8977,7 @@
         <v>101</v>
       </c>
       <c r="J138" s="6" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="K138" s="6" t="s">
         <v>18</v>
@@ -9085,7 +9082,7 @@
         <v>151</v>
       </c>
       <c r="J141" s="6" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="K141" s="6" t="s">
         <v>18</v>
@@ -9120,7 +9117,7 @@
         <v>101</v>
       </c>
       <c r="J142" s="6" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="K142" s="6" t="s">
         <v>18</v>
@@ -9260,7 +9257,7 @@
         <v>101</v>
       </c>
       <c r="J146" s="6" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="K146" s="6" t="s">
         <v>18</v>
@@ -9448,15 +9445,15 @@
         <v>5</v>
       </c>
       <c r="D1" s="29" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="E1" s="29"/>
       <c r="F1" s="30" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="G1" s="30"/>
       <c r="H1" s="26" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="I1" s="26"/>
       <c r="J1" s="26"/>
@@ -9479,7 +9476,7 @@
       <c r="AA1" s="26"/>
       <c r="AB1" s="26"/>
       <c r="AC1" s="24" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="2" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9491,18 +9488,18 @@
       <c r="F2" s="30"/>
       <c r="G2" s="30"/>
       <c r="H2" s="25" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="I2" s="25"/>
       <c r="J2" s="25"/>
       <c r="K2" s="9" t="s">
+        <v>816</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>816</v>
+      </c>
+      <c r="M2" s="26" t="s">
         <v>817</v>
-      </c>
-      <c r="L2" s="9" t="s">
-        <v>817</v>
-      </c>
-      <c r="M2" s="26" t="s">
-        <v>818</v>
       </c>
       <c r="N2" s="26"/>
       <c r="O2" s="26"/>
@@ -9530,67 +9527,67 @@
       <c r="F3" s="30"/>
       <c r="G3" s="30"/>
       <c r="H3" s="8" t="s">
+        <v>818</v>
+      </c>
+      <c r="I3" s="8" t="s">
         <v>819</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="J3" s="8" t="s">
         <v>820</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="K3" s="7" t="s">
         <v>821</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="L3" s="7" t="s">
         <v>822</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="M3" s="7" t="s">
         <v>823</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="N3" s="7" t="s">
         <v>824</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="O3" s="7" t="s">
         <v>825</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="P3" s="7" t="s">
         <v>826</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="Q3" s="7" t="s">
         <v>827</v>
       </c>
-      <c r="Q3" s="7" t="s">
+      <c r="R3" s="7" t="s">
         <v>828</v>
       </c>
-      <c r="R3" s="7" t="s">
+      <c r="S3" s="7" t="s">
         <v>829</v>
       </c>
-      <c r="S3" s="7" t="s">
+      <c r="T3" s="7" t="s">
         <v>830</v>
       </c>
-      <c r="T3" s="7" t="s">
+      <c r="U3" s="7" t="s">
         <v>831</v>
       </c>
-      <c r="U3" s="7" t="s">
+      <c r="V3" s="7" t="s">
         <v>832</v>
       </c>
-      <c r="V3" s="7" t="s">
+      <c r="W3" s="7" t="s">
         <v>833</v>
       </c>
-      <c r="W3" s="7" t="s">
+      <c r="X3" s="7" t="s">
         <v>834</v>
       </c>
-      <c r="X3" s="7" t="s">
+      <c r="Y3" s="7" t="s">
         <v>835</v>
       </c>
-      <c r="Y3" s="7" t="s">
+      <c r="Z3" s="7" t="s">
         <v>836</v>
       </c>
-      <c r="Z3" s="7" t="s">
+      <c r="AA3" s="7" t="s">
         <v>837</v>
       </c>
-      <c r="AA3" s="7" t="s">
+      <c r="AB3" s="7" t="s">
         <v>838</v>
-      </c>
-      <c r="AB3" s="7" t="s">
-        <v>839</v>
       </c>
       <c r="AC3" s="24"/>
     </row>
@@ -10029,7 +10026,7 @@
         <v>593</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="D13" s="21"/>
       <c r="E13" s="21"/>
@@ -12095,30 +12092,72 @@
         <f t="shared" si="0"/>
         <v>46133</v>
       </c>
-      <c r="H54" s="12"/>
-      <c r="I54" s="12"/>
-      <c r="J54" s="12"/>
-      <c r="K54" s="12"/>
-      <c r="L54" s="12"/>
-      <c r="M54" s="12"/>
-      <c r="N54" s="12"/>
-      <c r="O54" s="12"/>
-      <c r="P54" s="12"/>
-      <c r="Q54" s="12"/>
-      <c r="R54" s="12"/>
-      <c r="S54" s="12"/>
-      <c r="T54" s="12"/>
-      <c r="U54" s="12"/>
-      <c r="V54" s="12"/>
-      <c r="W54" s="12"/>
-      <c r="X54" s="12"/>
-      <c r="Y54" s="12"/>
-      <c r="Z54" s="12"/>
-      <c r="AA54" s="12"/>
-      <c r="AB54" s="12"/>
+      <c r="H54" s="12">
+        <v>877</v>
+      </c>
+      <c r="I54" s="12">
+        <v>567</v>
+      </c>
+      <c r="J54" s="12">
+        <v>17</v>
+      </c>
+      <c r="K54" s="12">
+        <v>61</v>
+      </c>
+      <c r="L54" s="12">
+        <v>4</v>
+      </c>
+      <c r="M54" s="12">
+        <v>2</v>
+      </c>
+      <c r="N54" s="12">
+        <v>4</v>
+      </c>
+      <c r="O54" s="12">
+        <v>0</v>
+      </c>
+      <c r="P54" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="12">
+        <v>0</v>
+      </c>
+      <c r="R54" s="12">
+        <v>0</v>
+      </c>
+      <c r="S54" s="12">
+        <v>0</v>
+      </c>
+      <c r="T54" s="12">
+        <v>28</v>
+      </c>
+      <c r="U54" s="12">
+        <v>0</v>
+      </c>
+      <c r="V54" s="12">
+        <v>0</v>
+      </c>
+      <c r="W54" s="12">
+        <v>0</v>
+      </c>
+      <c r="X54" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y54" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z54" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA54" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB54" s="12">
+        <v>0</v>
+      </c>
       <c r="AC54" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="55" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -12584,30 +12623,72 @@
         <f t="shared" si="0"/>
         <v>46133</v>
       </c>
-      <c r="H63" s="12"/>
-      <c r="I63" s="12"/>
-      <c r="J63" s="12"/>
-      <c r="K63" s="12"/>
-      <c r="L63" s="12"/>
-      <c r="M63" s="12"/>
-      <c r="N63" s="12"/>
-      <c r="O63" s="12"/>
-      <c r="P63" s="12"/>
-      <c r="Q63" s="12"/>
-      <c r="R63" s="12"/>
-      <c r="S63" s="12"/>
-      <c r="T63" s="12"/>
-      <c r="U63" s="12"/>
-      <c r="V63" s="12"/>
-      <c r="W63" s="12"/>
-      <c r="X63" s="12"/>
-      <c r="Y63" s="12"/>
-      <c r="Z63" s="12"/>
-      <c r="AA63" s="12"/>
-      <c r="AB63" s="12"/>
+      <c r="H63" s="12">
+        <v>1420</v>
+      </c>
+      <c r="I63" s="12">
+        <v>1421</v>
+      </c>
+      <c r="J63" s="12">
+        <v>2</v>
+      </c>
+      <c r="K63" s="12">
+        <v>5</v>
+      </c>
+      <c r="L63" s="12">
+        <v>15</v>
+      </c>
+      <c r="M63" s="12">
+        <v>1</v>
+      </c>
+      <c r="N63" s="12">
+        <v>0</v>
+      </c>
+      <c r="O63" s="12">
+        <v>0</v>
+      </c>
+      <c r="P63" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="12">
+        <v>0</v>
+      </c>
+      <c r="R63" s="12">
+        <v>0</v>
+      </c>
+      <c r="S63" s="12">
+        <v>0</v>
+      </c>
+      <c r="T63" s="12">
+        <v>41</v>
+      </c>
+      <c r="U63" s="12">
+        <v>1</v>
+      </c>
+      <c r="V63" s="12">
+        <v>0</v>
+      </c>
+      <c r="W63" s="12">
+        <v>0</v>
+      </c>
+      <c r="X63" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA63" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB63" s="12">
+        <v>0</v>
+      </c>
       <c r="AC63" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2906</v>
       </c>
     </row>
     <row r="64" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -14097,10 +14178,10 @@
         <v>153</v>
       </c>
       <c r="B94" s="19" t="s">
+        <v>840</v>
+      </c>
+      <c r="C94" s="19" t="s">
         <v>841</v>
-      </c>
-      <c r="C94" s="19" t="s">
-        <v>842</v>
       </c>
       <c r="D94" s="21">
         <v>-5.0822029999999998</v>
@@ -14535,7 +14616,7 @@
         <v>165</v>
       </c>
       <c r="C103" s="19" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="D103" s="21">
         <v>-4.8596729999999999</v>
@@ -15177,30 +15258,72 @@
         <f t="shared" si="3"/>
         <v>46133</v>
       </c>
-      <c r="H112" s="12"/>
-      <c r="I112" s="12"/>
-      <c r="J112" s="12"/>
-      <c r="K112" s="12"/>
-      <c r="L112" s="12"/>
-      <c r="M112" s="12"/>
-      <c r="N112" s="12"/>
-      <c r="O112" s="12"/>
-      <c r="P112" s="12"/>
-      <c r="Q112" s="12"/>
-      <c r="R112" s="12"/>
-      <c r="S112" s="12"/>
-      <c r="T112" s="12"/>
-      <c r="U112" s="12"/>
-      <c r="V112" s="12"/>
-      <c r="W112" s="12"/>
-      <c r="X112" s="12"/>
-      <c r="Y112" s="12"/>
-      <c r="Z112" s="12"/>
-      <c r="AA112" s="12"/>
-      <c r="AB112" s="12"/>
+      <c r="H112" s="12">
+        <v>1509</v>
+      </c>
+      <c r="I112" s="12">
+        <v>2008</v>
+      </c>
+      <c r="J112" s="12">
+        <v>31</v>
+      </c>
+      <c r="K112" s="12">
+        <v>343</v>
+      </c>
+      <c r="L112" s="12">
+        <v>110</v>
+      </c>
+      <c r="M112" s="12">
+        <v>16</v>
+      </c>
+      <c r="N112" s="12">
+        <v>31</v>
+      </c>
+      <c r="O112" s="12">
+        <v>2</v>
+      </c>
+      <c r="P112" s="12">
+        <v>1</v>
+      </c>
+      <c r="Q112" s="12">
+        <v>4</v>
+      </c>
+      <c r="R112" s="12">
+        <v>2</v>
+      </c>
+      <c r="S112" s="12">
+        <v>9</v>
+      </c>
+      <c r="T112" s="12">
+        <v>65</v>
+      </c>
+      <c r="U112" s="12">
+        <v>0</v>
+      </c>
+      <c r="V112" s="12">
+        <v>1</v>
+      </c>
+      <c r="W112" s="12">
+        <v>2</v>
+      </c>
+      <c r="X112" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y112" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z112" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA112" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB112" s="12">
+        <v>0</v>
+      </c>
       <c r="AC112" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4135</v>
       </c>
     </row>
     <row r="113" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -16953,30 +17076,72 @@
         <f t="shared" si="5"/>
         <v>46133</v>
       </c>
-      <c r="H142" s="12"/>
-      <c r="I142" s="12"/>
-      <c r="J142" s="12"/>
-      <c r="K142" s="12"/>
-      <c r="L142" s="12"/>
-      <c r="M142" s="12"/>
-      <c r="N142" s="12"/>
-      <c r="O142" s="12"/>
-      <c r="P142" s="12"/>
-      <c r="Q142" s="12"/>
-      <c r="R142" s="12"/>
-      <c r="S142" s="12"/>
-      <c r="T142" s="12"/>
-      <c r="U142" s="12"/>
-      <c r="V142" s="12"/>
-      <c r="W142" s="12"/>
-      <c r="X142" s="12"/>
-      <c r="Y142" s="12"/>
-      <c r="Z142" s="12"/>
-      <c r="AA142" s="12"/>
-      <c r="AB142" s="12"/>
+      <c r="H142" s="12">
+        <v>476</v>
+      </c>
+      <c r="I142" s="12">
+        <v>685</v>
+      </c>
+      <c r="J142" s="12">
+        <v>16</v>
+      </c>
+      <c r="K142" s="12">
+        <v>142</v>
+      </c>
+      <c r="L142" s="12">
+        <v>90</v>
+      </c>
+      <c r="M142" s="12">
+        <v>11</v>
+      </c>
+      <c r="N142" s="12">
+        <v>2</v>
+      </c>
+      <c r="O142" s="12">
+        <v>2</v>
+      </c>
+      <c r="P142" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q142" s="12">
+        <v>3</v>
+      </c>
+      <c r="R142" s="12">
+        <v>1</v>
+      </c>
+      <c r="S142" s="12">
+        <v>1</v>
+      </c>
+      <c r="T142" s="12">
+        <v>22</v>
+      </c>
+      <c r="U142" s="12">
+        <v>0</v>
+      </c>
+      <c r="V142" s="12">
+        <v>0</v>
+      </c>
+      <c r="W142" s="12">
+        <v>0</v>
+      </c>
+      <c r="X142" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y142" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z142" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA142" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB142" s="12">
+        <v>0</v>
+      </c>
       <c r="AC142" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="143" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -17437,30 +17602,72 @@
         <f t="shared" si="5"/>
         <v>46133</v>
       </c>
-      <c r="H152" s="12"/>
-      <c r="I152" s="12"/>
-      <c r="J152" s="12"/>
-      <c r="K152" s="12"/>
-      <c r="L152" s="12"/>
-      <c r="M152" s="12"/>
-      <c r="N152" s="12"/>
-      <c r="O152" s="12"/>
-      <c r="P152" s="12"/>
-      <c r="Q152" s="12"/>
-      <c r="R152" s="12"/>
-      <c r="S152" s="12"/>
-      <c r="T152" s="12"/>
-      <c r="U152" s="12"/>
-      <c r="V152" s="12"/>
-      <c r="W152" s="12"/>
-      <c r="X152" s="12"/>
-      <c r="Y152" s="12"/>
-      <c r="Z152" s="12"/>
-      <c r="AA152" s="12"/>
-      <c r="AB152" s="12"/>
+      <c r="H152" s="12">
+        <v>62</v>
+      </c>
+      <c r="I152" s="12">
+        <v>65</v>
+      </c>
+      <c r="J152" s="12">
+        <v>1</v>
+      </c>
+      <c r="K152" s="12">
+        <v>31</v>
+      </c>
+      <c r="L152" s="12">
+        <v>25</v>
+      </c>
+      <c r="M152" s="12">
+        <v>0</v>
+      </c>
+      <c r="N152" s="12">
+        <v>0</v>
+      </c>
+      <c r="O152" s="12">
+        <v>0</v>
+      </c>
+      <c r="P152" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q152" s="12">
+        <v>0</v>
+      </c>
+      <c r="R152" s="12">
+        <v>0</v>
+      </c>
+      <c r="S152" s="12">
+        <v>0</v>
+      </c>
+      <c r="T152" s="12">
+        <v>0</v>
+      </c>
+      <c r="U152" s="12">
+        <v>0</v>
+      </c>
+      <c r="V152" s="12">
+        <v>0</v>
+      </c>
+      <c r="W152" s="12">
+        <v>0</v>
+      </c>
+      <c r="X152" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y152" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z152" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA152" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB152" s="12">
+        <v>0</v>
+      </c>
       <c r="AC152" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>184</v>
       </c>
     </row>
     <row r="153" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">

--- a/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
+++ b/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1CB0B2A-0249-4286-93D7-F0EFFD6D4942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6D803DB-C3DB-4078-B4C3-24F4505583C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
   </bookViews>
   <sheets>
     <sheet name="LISTA DE PONTOS" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1833" uniqueCount="843">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1833" uniqueCount="844">
   <si>
     <t>WKT</t>
   </si>
@@ -2573,6 +2573,9 @@
   </si>
   <si>
     <t>456ECE0050S0</t>
+  </si>
+  <si>
+    <t>EM ANDAMENTO</t>
   </si>
 </sst>
 </file>
@@ -6807,7 +6810,7 @@
         <v>101</v>
       </c>
       <c r="J76" s="6" t="s">
-        <v>17</v>
+        <v>843</v>
       </c>
       <c r="K76" s="6" t="s">
         <v>310</v>
@@ -7017,7 +7020,7 @@
         <v>101</v>
       </c>
       <c r="J82" s="6" t="s">
-        <v>17</v>
+        <v>843</v>
       </c>
       <c r="K82" s="6" t="s">
         <v>18</v>
@@ -7052,7 +7055,7 @@
         <v>101</v>
       </c>
       <c r="J83" s="6" t="s">
-        <v>17</v>
+        <v>843</v>
       </c>
       <c r="K83" s="6" t="s">
         <v>18</v>
@@ -8347,7 +8350,7 @@
         <v>101</v>
       </c>
       <c r="J120" s="6" t="s">
-        <v>17</v>
+        <v>843</v>
       </c>
       <c r="K120" s="6" t="s">
         <v>18</v>
@@ -8802,7 +8805,7 @@
         <v>101</v>
       </c>
       <c r="J133" s="6" t="s">
-        <v>17</v>
+        <v>843</v>
       </c>
       <c r="K133" s="6" t="s">
         <v>18</v>

--- a/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
+++ b/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6D803DB-C3DB-4078-B4C3-24F4505583C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12245B61-4064-46BD-931F-B14F7CD6273A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1833" uniqueCount="844">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1833" uniqueCount="846">
   <si>
     <t>WKT</t>
   </si>
@@ -1471,12 +1471,6 @@
   </si>
   <si>
     <t>363ECE0010N0</t>
-  </si>
-  <si>
-    <t>ENTR. BR-226/CE-166 (SENADOR POMPEU)</t>
-  </si>
-  <si>
-    <t>ENTR. CE-060(A)</t>
   </si>
   <si>
     <t>POINT (-38.569200 -5.402150)</t>
@@ -2576,6 +2570,18 @@
   </si>
   <si>
     <t>EM ANDAMENTO</t>
+  </si>
+  <si>
+    <t>166ECE0110S0</t>
+  </si>
+  <si>
+    <t>ENTR. BR-226(B)</t>
+  </si>
+  <si>
+    <t>ENGº. JOSÉ LOPES</t>
+  </si>
+  <si>
+    <t>PAVIMENTADA</t>
   </si>
 </sst>
 </file>
@@ -4185,7 +4191,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>9</v>
@@ -4220,7 +4226,7 @@
         <v>16</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="K2" s="6" t="s">
         <v>18</v>
@@ -4255,7 +4261,7 @@
         <v>16</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="K3" s="6" t="s">
         <v>18</v>
@@ -4325,7 +4331,7 @@
         <v>16</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="K5" s="6" t="s">
         <v>18</v>
@@ -4605,7 +4611,7 @@
         <v>16</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="K13" s="6" t="s">
         <v>18</v>
@@ -4640,7 +4646,7 @@
         <v>16</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="K14" s="6" t="s">
         <v>18</v>
@@ -4710,7 +4716,7 @@
         <v>16</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="K16" s="6" t="s">
         <v>18</v>
@@ -4780,7 +4786,7 @@
         <v>16</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="K18" s="6" t="s">
         <v>18</v>
@@ -5095,7 +5101,7 @@
         <v>16</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="K27" s="6" t="s">
         <v>18</v>
@@ -5130,7 +5136,7 @@
         <v>16</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="K28" s="6" t="s">
         <v>18</v>
@@ -5165,7 +5171,7 @@
         <v>16</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="K29" s="6" t="s">
         <v>18</v>
@@ -5200,7 +5206,7 @@
         <v>16</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="K30" s="6" t="s">
         <v>18</v>
@@ -5235,7 +5241,7 @@
         <v>16</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="K31" s="6" t="s">
         <v>18</v>
@@ -5375,7 +5381,7 @@
         <v>16</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="K35" s="6" t="s">
         <v>310</v>
@@ -5655,7 +5661,7 @@
         <v>151</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="K43" s="6" t="s">
         <v>18</v>
@@ -5760,7 +5766,7 @@
         <v>101</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="K46" s="6" t="s">
         <v>18</v>
@@ -5865,7 +5871,7 @@
         <v>101</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="K49" s="6" t="s">
         <v>18</v>
@@ -5900,7 +5906,7 @@
         <v>101</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="K50" s="6" t="s">
         <v>18</v>
@@ -5935,7 +5941,7 @@
         <v>151</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="K51" s="6" t="s">
         <v>18</v>
@@ -6565,7 +6571,7 @@
         <v>101</v>
       </c>
       <c r="J69" s="6" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="K69" s="6" t="s">
         <v>18</v>
@@ -6740,7 +6746,7 @@
         <v>101</v>
       </c>
       <c r="J74" s="6" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="K74" s="6" t="s">
         <v>18</v>
@@ -6789,39 +6795,39 @@
         <v>473</v>
       </c>
       <c r="C76" s="5">
-        <v>-5.5925830000000003</v>
+        <v>-5.6781480000000002</v>
       </c>
       <c r="D76" s="5">
-        <v>-39.391033</v>
+        <v>-39.430067000000001</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>474</v>
+        <v>199</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>475</v>
+        <v>842</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>476</v>
+        <v>843</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>477</v>
+        <v>844</v>
       </c>
       <c r="I76" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J76" s="6" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="K76" s="6" t="s">
-        <v>310</v>
+        <v>845</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C77" s="5">
         <v>-3.4014500000000001</v>
@@ -6830,16 +6836,16 @@
         <v>-40.686549999999997</v>
       </c>
       <c r="E77" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="G77" s="4" t="s">
         <v>480</v>
       </c>
-      <c r="F77" s="4" t="s">
+      <c r="H77" s="4" t="s">
         <v>481</v>
-      </c>
-      <c r="G77" s="4" t="s">
-        <v>482</v>
-      </c>
-      <c r="H77" s="4" t="s">
-        <v>483</v>
       </c>
       <c r="I77" s="4" t="s">
         <v>101</v>
@@ -6853,10 +6859,10 @@
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C78" s="5">
         <v>-3.5714160000000001</v>
@@ -6865,13 +6871,13 @@
         <v>-40.6374</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="H78" s="4" t="s">
         <v>385</v>
@@ -6888,10 +6894,10 @@
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C79" s="5">
         <v>-4.761266</v>
@@ -6900,16 +6906,16 @@
         <v>-39.490850000000002</v>
       </c>
       <c r="E79" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="G79" s="4" t="s">
         <v>490</v>
       </c>
-      <c r="F79" s="4" t="s">
+      <c r="H79" s="4" t="s">
         <v>491</v>
-      </c>
-      <c r="G79" s="4" t="s">
-        <v>492</v>
-      </c>
-      <c r="H79" s="4" t="s">
-        <v>493</v>
       </c>
       <c r="I79" s="4" t="s">
         <v>101</v>
@@ -6950,7 +6956,7 @@
         <v>101</v>
       </c>
       <c r="J80" s="6" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="K80" s="6" t="s">
         <v>18</v>
@@ -6958,10 +6964,10 @@
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C81" s="5">
         <v>-5.4021499999999998</v>
@@ -6970,16 +6976,16 @@
         <v>-38.571483000000001</v>
       </c>
       <c r="E81" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="G81" s="4" t="s">
         <v>496</v>
       </c>
-      <c r="F81" s="4" t="s">
+      <c r="H81" s="4" t="s">
         <v>497</v>
-      </c>
-      <c r="G81" s="4" t="s">
-        <v>498</v>
-      </c>
-      <c r="H81" s="4" t="s">
-        <v>499</v>
       </c>
       <c r="I81" s="4" t="s">
         <v>101</v>
@@ -6993,10 +6999,10 @@
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C82" s="5">
         <v>-5.7368329999999998</v>
@@ -7005,22 +7011,22 @@
         <v>-39.028033000000001</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="F82" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="G82" s="4" t="s">
+        <v>501</v>
+      </c>
+      <c r="H82" s="4" t="s">
         <v>502</v>
-      </c>
-      <c r="G82" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="H82" s="4" t="s">
-        <v>504</v>
       </c>
       <c r="I82" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J82" s="6" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="K82" s="6" t="s">
         <v>18</v>
@@ -7028,10 +7034,10 @@
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C83" s="5">
         <v>-5.6816329999999997</v>
@@ -7043,19 +7049,19 @@
         <v>136</v>
       </c>
       <c r="F83" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="G83" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="H83" s="4" t="s">
         <v>507</v>
-      </c>
-      <c r="G83" s="4" t="s">
-        <v>508</v>
-      </c>
-      <c r="H83" s="4" t="s">
-        <v>509</v>
       </c>
       <c r="I83" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J83" s="6" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="K83" s="6" t="s">
         <v>18</v>
@@ -7063,10 +7069,10 @@
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C84" s="5">
         <v>-5.0811999999999999</v>
@@ -7075,16 +7081,16 @@
         <v>-38.004565999999997</v>
       </c>
       <c r="E84" s="4" t="s">
+        <v>510</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="G84" s="4" t="s">
         <v>512</v>
       </c>
-      <c r="F84" s="4" t="s">
+      <c r="H84" s="4" t="s">
         <v>513</v>
-      </c>
-      <c r="G84" s="4" t="s">
-        <v>514</v>
-      </c>
-      <c r="H84" s="4" t="s">
-        <v>515</v>
       </c>
       <c r="I84" s="4" t="s">
         <v>101</v>
@@ -7098,10 +7104,10 @@
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C85" s="5">
         <v>-5.2329999999999997</v>
@@ -7110,16 +7116,16 @@
         <v>-38.194850000000002</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="F85" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="G85" s="4" t="s">
+        <v>517</v>
+      </c>
+      <c r="H85" s="4" t="s">
         <v>518</v>
-      </c>
-      <c r="G85" s="4" t="s">
-        <v>519</v>
-      </c>
-      <c r="H85" s="4" t="s">
-        <v>520</v>
       </c>
       <c r="I85" s="4" t="s">
         <v>101</v>
@@ -7168,10 +7174,10 @@
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C87" s="5">
         <v>-3.9741499999999998</v>
@@ -7183,13 +7189,13 @@
         <v>383</v>
       </c>
       <c r="F87" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="G87" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="H87" s="4" t="s">
         <v>523</v>
-      </c>
-      <c r="G87" s="4" t="s">
-        <v>524</v>
-      </c>
-      <c r="H87" s="4" t="s">
-        <v>525</v>
       </c>
       <c r="I87" s="4" t="s">
         <v>151</v>
@@ -7203,10 +7209,10 @@
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C88" s="5">
         <v>-3.962866</v>
@@ -7215,16 +7221,16 @@
         <v>-38.357016000000002</v>
       </c>
       <c r="E88" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>527</v>
+      </c>
+      <c r="G88" s="4" t="s">
         <v>528</v>
       </c>
-      <c r="F88" s="4" t="s">
+      <c r="H88" s="4" t="s">
         <v>529</v>
-      </c>
-      <c r="G88" s="4" t="s">
-        <v>530</v>
-      </c>
-      <c r="H88" s="4" t="s">
-        <v>531</v>
       </c>
       <c r="I88" s="4" t="s">
         <v>101</v>
@@ -7238,10 +7244,10 @@
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C89" s="5">
         <v>-4.0425329999999997</v>
@@ -7250,16 +7256,16 @@
         <v>-38.206499999999998</v>
       </c>
       <c r="E89" s="4" t="s">
+        <v>532</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>533</v>
+      </c>
+      <c r="G89" s="4" t="s">
         <v>534</v>
       </c>
-      <c r="F89" s="4" t="s">
+      <c r="H89" s="4" t="s">
         <v>535</v>
-      </c>
-      <c r="G89" s="4" t="s">
-        <v>536</v>
-      </c>
-      <c r="H89" s="4" t="s">
-        <v>537</v>
       </c>
       <c r="I89" s="4" t="s">
         <v>151</v>
@@ -7300,7 +7306,7 @@
         <v>151</v>
       </c>
       <c r="J90" s="6" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="K90" s="6" t="s">
         <v>18</v>
@@ -7308,10 +7314,10 @@
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C91" s="5">
         <v>-4.4447369999999999</v>
@@ -7320,22 +7326,22 @@
         <v>-38.662745999999999</v>
       </c>
       <c r="E91" s="4" t="s">
+        <v>538</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="G91" s="4" t="s">
         <v>540</v>
       </c>
-      <c r="F91" s="4" t="s">
+      <c r="H91" s="4" t="s">
         <v>541</v>
-      </c>
-      <c r="G91" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="H91" s="4" t="s">
-        <v>543</v>
       </c>
       <c r="I91" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J91" s="6" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="K91" s="6" t="s">
         <v>18</v>
@@ -7343,10 +7349,10 @@
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="C92" s="5">
         <v>-5.1705110000000003</v>
@@ -7355,22 +7361,22 @@
         <v>-40.708150000000003</v>
       </c>
       <c r="E92" s="4" t="s">
+        <v>544</v>
+      </c>
+      <c r="F92" s="4" t="s">
+        <v>545</v>
+      </c>
+      <c r="G92" s="4" t="s">
         <v>546</v>
       </c>
-      <c r="F92" s="4" t="s">
+      <c r="H92" s="4" t="s">
         <v>547</v>
-      </c>
-      <c r="G92" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="H92" s="4" t="s">
-        <v>549</v>
       </c>
       <c r="I92" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J92" s="6" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="K92" s="6" t="s">
         <v>18</v>
@@ -7378,10 +7384,10 @@
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C93" s="5">
         <v>-4.5725499999999997</v>
@@ -7390,16 +7396,16 @@
         <v>-37.736899999999999</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="F93" s="4" t="s">
+        <v>550</v>
+      </c>
+      <c r="G93" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="H93" s="4" t="s">
         <v>552</v>
-      </c>
-      <c r="G93" s="4" t="s">
-        <v>553</v>
-      </c>
-      <c r="H93" s="4" t="s">
-        <v>554</v>
       </c>
       <c r="I93" s="4" t="s">
         <v>101</v>
@@ -7413,10 +7419,10 @@
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C94" s="5">
         <v>-5.1207330000000004</v>
@@ -7428,13 +7434,13 @@
         <v>360</v>
       </c>
       <c r="F94" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="G94" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="H94" s="4" t="s">
         <v>557</v>
-      </c>
-      <c r="G94" s="4" t="s">
-        <v>558</v>
-      </c>
-      <c r="H94" s="4" t="s">
-        <v>559</v>
       </c>
       <c r="I94" s="4" t="s">
         <v>101</v>
@@ -7483,10 +7489,10 @@
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C96" s="5">
         <v>-3.6957</v>
@@ -7498,13 +7504,13 @@
         <v>42</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="G96" s="4" t="s">
         <v>303</v>
       </c>
       <c r="H96" s="4" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="I96" s="4" t="s">
         <v>101</v>
@@ -7518,10 +7524,10 @@
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C97" s="5">
         <v>-3.6978119999999999</v>
@@ -7530,22 +7536,22 @@
         <v>-40.307443999999997</v>
       </c>
       <c r="E97" s="4" t="s">
+        <v>564</v>
+      </c>
+      <c r="F97" s="4" t="s">
+        <v>565</v>
+      </c>
+      <c r="G97" s="4" t="s">
         <v>566</v>
       </c>
-      <c r="F97" s="4" t="s">
+      <c r="H97" s="4" t="s">
         <v>567</v>
-      </c>
-      <c r="G97" s="4" t="s">
-        <v>568</v>
-      </c>
-      <c r="H97" s="4" t="s">
-        <v>569</v>
       </c>
       <c r="I97" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J97" s="6" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="K97" s="6" t="s">
         <v>18</v>
@@ -7553,10 +7559,10 @@
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C98" s="5">
         <v>-5.2113269999999998</v>
@@ -7568,19 +7574,19 @@
         <v>210</v>
       </c>
       <c r="F98" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="G98" s="4" t="s">
+        <v>571</v>
+      </c>
+      <c r="H98" s="4" t="s">
         <v>572</v>
-      </c>
-      <c r="G98" s="4" t="s">
-        <v>573</v>
-      </c>
-      <c r="H98" s="4" t="s">
-        <v>574</v>
       </c>
       <c r="I98" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J98" s="6" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="K98" s="6" t="s">
         <v>18</v>
@@ -7588,10 +7594,10 @@
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C99" s="5">
         <v>-4.3822749999999999</v>
@@ -7603,19 +7609,19 @@
         <v>210</v>
       </c>
       <c r="F99" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="G99" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="H99" s="4" t="s">
         <v>577</v>
-      </c>
-      <c r="G99" s="4" t="s">
-        <v>578</v>
-      </c>
-      <c r="H99" s="4" t="s">
-        <v>579</v>
       </c>
       <c r="I99" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J99" s="6" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="K99" s="6" t="s">
         <v>18</v>
@@ -7623,10 +7629,10 @@
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C100" s="5">
         <v>-6.0296659999999997</v>
@@ -7635,16 +7641,16 @@
         <v>-38.340949999999999</v>
       </c>
       <c r="E100" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>581</v>
+      </c>
+      <c r="G100" s="4" t="s">
         <v>582</v>
       </c>
-      <c r="F100" s="4" t="s">
+      <c r="H100" s="4" t="s">
         <v>583</v>
-      </c>
-      <c r="G100" s="4" t="s">
-        <v>584</v>
-      </c>
-      <c r="H100" s="4" t="s">
-        <v>585</v>
       </c>
       <c r="I100" s="4" t="s">
         <v>101</v>
@@ -7658,10 +7664,10 @@
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="C101" s="5">
         <v>-5.2479829999999996</v>
@@ -7670,16 +7676,16 @@
         <v>-38.491466000000003</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="F101" s="4" t="s">
+        <v>586</v>
+      </c>
+      <c r="G101" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="H101" s="4" t="s">
         <v>588</v>
-      </c>
-      <c r="G101" s="4" t="s">
-        <v>589</v>
-      </c>
-      <c r="H101" s="4" t="s">
-        <v>590</v>
       </c>
       <c r="I101" s="4" t="s">
         <v>151</v>
@@ -7693,10 +7699,10 @@
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C102" s="5">
         <v>-4.2260499999999999</v>
@@ -7705,16 +7711,16 @@
         <v>-38.112082999999998</v>
       </c>
       <c r="E102" s="4" t="s">
+        <v>591</v>
+      </c>
+      <c r="F102" s="4" t="s">
+        <v>592</v>
+      </c>
+      <c r="G102" s="4" t="s">
         <v>593</v>
       </c>
-      <c r="F102" s="4" t="s">
+      <c r="H102" s="4" t="s">
         <v>594</v>
-      </c>
-      <c r="G102" s="4" t="s">
-        <v>595</v>
-      </c>
-      <c r="H102" s="4" t="s">
-        <v>596</v>
       </c>
       <c r="I102" s="4" t="s">
         <v>151</v>
@@ -7728,10 +7734,10 @@
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="C103" s="5">
         <v>-4.2283499999999998</v>
@@ -7740,16 +7746,16 @@
         <v>-38.112932999999998</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="G103" s="4" t="s">
         <v>73</v>
       </c>
       <c r="H103" s="4" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="I103" s="4" t="s">
         <v>101</v>
@@ -7763,10 +7769,10 @@
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C104" s="5">
         <v>-4.5906500000000001</v>
@@ -7778,13 +7784,13 @@
         <v>142</v>
       </c>
       <c r="F104" s="4" t="s">
+        <v>602</v>
+      </c>
+      <c r="G104" s="4" t="s">
+        <v>603</v>
+      </c>
+      <c r="H104" s="4" t="s">
         <v>604</v>
-      </c>
-      <c r="G104" s="4" t="s">
-        <v>605</v>
-      </c>
-      <c r="H104" s="4" t="s">
-        <v>606</v>
       </c>
       <c r="I104" s="4" t="s">
         <v>101</v>
@@ -7798,10 +7804,10 @@
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C105" s="5">
         <v>-3.9187500000000002</v>
@@ -7813,13 +7819,13 @@
         <v>104</v>
       </c>
       <c r="F105" s="4" t="s">
+        <v>607</v>
+      </c>
+      <c r="G105" s="4" t="s">
+        <v>608</v>
+      </c>
+      <c r="H105" s="4" t="s">
         <v>609</v>
-      </c>
-      <c r="G105" s="4" t="s">
-        <v>610</v>
-      </c>
-      <c r="H105" s="4" t="s">
-        <v>611</v>
       </c>
       <c r="I105" s="4" t="s">
         <v>101</v>
@@ -8008,10 +8014,10 @@
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="C111" s="5">
         <v>-3.7752400000000002</v>
@@ -8020,22 +8026,22 @@
         <v>-40.496578999999997</v>
       </c>
       <c r="E111" s="4" t="s">
+        <v>612</v>
+      </c>
+      <c r="F111" s="4" t="s">
+        <v>613</v>
+      </c>
+      <c r="G111" s="4" t="s">
         <v>614</v>
       </c>
-      <c r="F111" s="4" t="s">
+      <c r="H111" s="4" t="s">
         <v>615</v>
-      </c>
-      <c r="G111" s="4" t="s">
-        <v>616</v>
-      </c>
-      <c r="H111" s="4" t="s">
-        <v>617</v>
       </c>
       <c r="I111" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J111" s="6" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="K111" s="6" t="s">
         <v>18</v>
@@ -8043,10 +8049,10 @@
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="C112" s="5">
         <v>-3.9438659999999999</v>
@@ -8058,13 +8064,13 @@
         <v>210</v>
       </c>
       <c r="F112" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="G112" s="4" t="s">
+        <v>619</v>
+      </c>
+      <c r="H112" s="4" t="s">
         <v>620</v>
-      </c>
-      <c r="G112" s="4" t="s">
-        <v>621</v>
-      </c>
-      <c r="H112" s="4" t="s">
-        <v>622</v>
       </c>
       <c r="I112" s="4" t="s">
         <v>101</v>
@@ -8078,10 +8084,10 @@
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="C113" s="5">
         <v>-4.7911549999999998</v>
@@ -8090,22 +8096,22 @@
         <v>-40.827958000000002</v>
       </c>
       <c r="E113" s="4" t="s">
+        <v>623</v>
+      </c>
+      <c r="F113" s="4" t="s">
+        <v>624</v>
+      </c>
+      <c r="G113" s="4" t="s">
         <v>625</v>
       </c>
-      <c r="F113" s="4" t="s">
+      <c r="H113" s="4" t="s">
         <v>626</v>
-      </c>
-      <c r="G113" s="4" t="s">
-        <v>627</v>
-      </c>
-      <c r="H113" s="4" t="s">
-        <v>628</v>
       </c>
       <c r="I113" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J113" s="6" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="K113" s="6" t="s">
         <v>18</v>
@@ -8113,10 +8119,10 @@
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="C114" s="5">
         <v>-3.4767329999999999</v>
@@ -8128,13 +8134,13 @@
         <v>417</v>
       </c>
       <c r="F114" s="4" t="s">
+        <v>629</v>
+      </c>
+      <c r="G114" s="4" t="s">
+        <v>630</v>
+      </c>
+      <c r="H114" s="4" t="s">
         <v>631</v>
-      </c>
-      <c r="G114" s="4" t="s">
-        <v>632</v>
-      </c>
-      <c r="H114" s="4" t="s">
-        <v>633</v>
       </c>
       <c r="I114" s="4" t="s">
         <v>101</v>
@@ -8148,10 +8154,10 @@
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C115" s="5">
         <v>-4.5871829999999996</v>
@@ -8160,16 +8166,16 @@
         <v>-38.620182999999997</v>
       </c>
       <c r="E115" s="4" t="s">
+        <v>634</v>
+      </c>
+      <c r="F115" s="4" t="s">
+        <v>635</v>
+      </c>
+      <c r="G115" s="4" t="s">
         <v>636</v>
       </c>
-      <c r="F115" s="4" t="s">
+      <c r="H115" s="4" t="s">
         <v>637</v>
-      </c>
-      <c r="G115" s="4" t="s">
-        <v>638</v>
-      </c>
-      <c r="H115" s="4" t="s">
-        <v>639</v>
       </c>
       <c r="I115" s="4" t="s">
         <v>101</v>
@@ -8183,10 +8189,10 @@
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C116" s="5">
         <v>-3.4662999999999999</v>
@@ -8198,13 +8204,13 @@
         <v>237</v>
       </c>
       <c r="F116" s="4" t="s">
+        <v>640</v>
+      </c>
+      <c r="G116" s="4" t="s">
+        <v>641</v>
+      </c>
+      <c r="H116" s="4" t="s">
         <v>642</v>
-      </c>
-      <c r="G116" s="4" t="s">
-        <v>643</v>
-      </c>
-      <c r="H116" s="4" t="s">
-        <v>644</v>
       </c>
       <c r="I116" s="4" t="s">
         <v>151</v>
@@ -8218,10 +8224,10 @@
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="C117" s="5">
         <v>-3.2141000000000002</v>
@@ -8230,16 +8236,16 @@
         <v>-40.864533000000002</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="F117" s="4" t="s">
+        <v>645</v>
+      </c>
+      <c r="G117" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="H117" s="4" t="s">
         <v>647</v>
-      </c>
-      <c r="G117" s="4" t="s">
-        <v>648</v>
-      </c>
-      <c r="H117" s="4" t="s">
-        <v>649</v>
       </c>
       <c r="I117" s="4" t="s">
         <v>101</v>
@@ -8253,10 +8259,10 @@
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C118" s="5">
         <v>-5.0508829999999998</v>
@@ -8265,16 +8271,16 @@
         <v>-37.779632999999997</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="F118" s="4" t="s">
+        <v>650</v>
+      </c>
+      <c r="G118" s="4" t="s">
+        <v>651</v>
+      </c>
+      <c r="H118" s="4" t="s">
         <v>652</v>
-      </c>
-      <c r="G118" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="H118" s="4" t="s">
-        <v>654</v>
       </c>
       <c r="I118" s="4" t="s">
         <v>151</v>
@@ -8323,34 +8329,34 @@
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="C120" s="5">
-        <v>-5.5281500000000001</v>
+        <v>-5.5281140000000004</v>
       </c>
       <c r="D120" s="5">
-        <v>-39.517183000000003</v>
+        <v>-39.517207999999997</v>
       </c>
       <c r="E120" s="4" t="s">
         <v>76</v>
       </c>
       <c r="F120" s="4" t="s">
+        <v>655</v>
+      </c>
+      <c r="G120" s="4" t="s">
+        <v>656</v>
+      </c>
+      <c r="H120" s="4" t="s">
         <v>657</v>
-      </c>
-      <c r="G120" s="4" t="s">
-        <v>658</v>
-      </c>
-      <c r="H120" s="4" t="s">
-        <v>659</v>
       </c>
       <c r="I120" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J120" s="6" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="K120" s="6" t="s">
         <v>18</v>
@@ -8358,10 +8364,10 @@
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C121" s="5">
         <v>-4.338266</v>
@@ -8373,13 +8379,13 @@
         <v>104</v>
       </c>
       <c r="F121" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="G121" s="4" t="s">
+        <v>661</v>
+      </c>
+      <c r="H121" s="4" t="s">
         <v>662</v>
-      </c>
-      <c r="G121" s="4" t="s">
-        <v>663</v>
-      </c>
-      <c r="H121" s="4" t="s">
-        <v>664</v>
       </c>
       <c r="I121" s="4" t="s">
         <v>101</v>
@@ -8393,10 +8399,10 @@
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C122" s="5">
         <v>-4.2869089999999996</v>
@@ -8408,10 +8414,10 @@
         <v>36</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="H122" s="4" t="s">
         <v>83</v>
@@ -8420,7 +8426,7 @@
         <v>151</v>
       </c>
       <c r="J122" s="6" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="K122" s="6" t="s">
         <v>18</v>
@@ -8428,10 +8434,10 @@
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C123" s="5">
         <v>-3.372366</v>
@@ -8443,13 +8449,13 @@
         <v>176</v>
       </c>
       <c r="F123" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="G123" s="4" t="s">
+        <v>670</v>
+      </c>
+      <c r="H123" s="4" t="s">
         <v>671</v>
-      </c>
-      <c r="G123" s="4" t="s">
-        <v>672</v>
-      </c>
-      <c r="H123" s="4" t="s">
-        <v>673</v>
       </c>
       <c r="I123" s="4" t="s">
         <v>151</v>
@@ -8463,10 +8469,10 @@
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="C124" s="5">
         <v>-2.8939659999999998</v>
@@ -8478,13 +8484,13 @@
         <v>176</v>
       </c>
       <c r="F124" s="4" t="s">
+        <v>674</v>
+      </c>
+      <c r="G124" s="4" t="s">
+        <v>675</v>
+      </c>
+      <c r="H124" s="4" t="s">
         <v>676</v>
-      </c>
-      <c r="G124" s="4" t="s">
-        <v>677</v>
-      </c>
-      <c r="H124" s="4" t="s">
-        <v>678</v>
       </c>
       <c r="I124" s="4" t="s">
         <v>101</v>
@@ -8498,10 +8504,10 @@
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="C125" s="5">
         <v>-4.7071329999999998</v>
@@ -8513,10 +8519,10 @@
         <v>25</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="H125" s="4" t="s">
         <v>27</v>
@@ -8533,10 +8539,10 @@
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="C126" s="5">
         <v>-4.0460330000000004</v>
@@ -8548,13 +8554,13 @@
         <v>193</v>
       </c>
       <c r="F126" s="4" t="s">
+        <v>683</v>
+      </c>
+      <c r="G126" s="4" t="s">
+        <v>684</v>
+      </c>
+      <c r="H126" s="4" t="s">
         <v>685</v>
-      </c>
-      <c r="G126" s="4" t="s">
-        <v>686</v>
-      </c>
-      <c r="H126" s="4" t="s">
-        <v>687</v>
       </c>
       <c r="I126" s="4" t="s">
         <v>101</v>
@@ -8568,10 +8574,10 @@
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C127" s="5">
         <v>-5.5796159999999997</v>
@@ -8583,13 +8589,13 @@
         <v>193</v>
       </c>
       <c r="F127" s="4" t="s">
+        <v>688</v>
+      </c>
+      <c r="G127" s="4" t="s">
+        <v>689</v>
+      </c>
+      <c r="H127" s="4" t="s">
         <v>690</v>
-      </c>
-      <c r="G127" s="4" t="s">
-        <v>691</v>
-      </c>
-      <c r="H127" s="4" t="s">
-        <v>692</v>
       </c>
       <c r="I127" s="4" t="s">
         <v>151</v>
@@ -8603,10 +8609,10 @@
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="C128" s="5">
         <v>-5.3889829999999996</v>
@@ -8615,16 +8621,16 @@
         <v>-38.911766</v>
       </c>
       <c r="E128" s="4" t="s">
+        <v>693</v>
+      </c>
+      <c r="F128" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="G128" s="4" t="s">
         <v>695</v>
       </c>
-      <c r="F128" s="4" t="s">
+      <c r="H128" s="4" t="s">
         <v>696</v>
-      </c>
-      <c r="G128" s="4" t="s">
-        <v>697</v>
-      </c>
-      <c r="H128" s="4" t="s">
-        <v>698</v>
       </c>
       <c r="I128" s="4" t="s">
         <v>101</v>
@@ -8638,10 +8644,10 @@
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="C129" s="5">
         <v>-5.9808000000000003</v>
@@ -8650,16 +8656,16 @@
         <v>-38.884349999999998</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="F129" s="4" t="s">
+        <v>699</v>
+      </c>
+      <c r="G129" s="4" t="s">
+        <v>700</v>
+      </c>
+      <c r="H129" s="4" t="s">
         <v>701</v>
-      </c>
-      <c r="G129" s="4" t="s">
-        <v>702</v>
-      </c>
-      <c r="H129" s="4" t="s">
-        <v>703</v>
       </c>
       <c r="I129" s="4" t="s">
         <v>101</v>
@@ -8673,10 +8679,10 @@
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="C130" s="5">
         <v>-3.5994000000000002</v>
@@ -8685,16 +8691,16 @@
         <v>-38.898966000000001</v>
       </c>
       <c r="E130" s="4" t="s">
+        <v>704</v>
+      </c>
+      <c r="F130" s="4" t="s">
+        <v>705</v>
+      </c>
+      <c r="G130" s="4" t="s">
         <v>706</v>
       </c>
-      <c r="F130" s="4" t="s">
+      <c r="H130" s="4" t="s">
         <v>707</v>
-      </c>
-      <c r="G130" s="4" t="s">
-        <v>708</v>
-      </c>
-      <c r="H130" s="4" t="s">
-        <v>709</v>
       </c>
       <c r="I130" s="4" t="s">
         <v>101</v>
@@ -8708,10 +8714,10 @@
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="C131" s="5">
         <v>-4.1112159999999998</v>
@@ -8720,10 +8726,10 @@
         <v>-39.226599999999998</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="G131" s="4" t="s">
         <v>286</v>
@@ -8743,10 +8749,10 @@
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C132" s="5">
         <v>-3.3707829999999999</v>
@@ -8755,16 +8761,16 @@
         <v>-39.293933000000003</v>
       </c>
       <c r="E132" s="4" t="s">
+        <v>714</v>
+      </c>
+      <c r="F132" s="4" t="s">
+        <v>715</v>
+      </c>
+      <c r="G132" s="4" t="s">
         <v>716</v>
       </c>
-      <c r="F132" s="4" t="s">
+      <c r="H132" s="4" t="s">
         <v>717</v>
-      </c>
-      <c r="G132" s="4" t="s">
-        <v>718</v>
-      </c>
-      <c r="H132" s="4" t="s">
-        <v>719</v>
       </c>
       <c r="I132" s="4" t="s">
         <v>101</v>
@@ -8778,10 +8784,10 @@
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="C133" s="5">
         <v>-5.8101659999999997</v>
@@ -8793,19 +8799,19 @@
         <v>199</v>
       </c>
       <c r="F133" s="4" t="s">
+        <v>720</v>
+      </c>
+      <c r="G133" s="4" t="s">
+        <v>721</v>
+      </c>
+      <c r="H133" s="4" t="s">
         <v>722</v>
-      </c>
-      <c r="G133" s="4" t="s">
-        <v>723</v>
-      </c>
-      <c r="H133" s="4" t="s">
-        <v>724</v>
       </c>
       <c r="I133" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J133" s="6" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="K133" s="6" t="s">
         <v>18</v>
@@ -8813,10 +8819,10 @@
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="C134" s="5">
         <v>-3.304783</v>
@@ -8828,13 +8834,13 @@
         <v>176</v>
       </c>
       <c r="F134" s="4" t="s">
+        <v>725</v>
+      </c>
+      <c r="G134" s="4" t="s">
+        <v>726</v>
+      </c>
+      <c r="H134" s="4" t="s">
         <v>727</v>
-      </c>
-      <c r="G134" s="4" t="s">
-        <v>728</v>
-      </c>
-      <c r="H134" s="4" t="s">
-        <v>729</v>
       </c>
       <c r="I134" s="4" t="s">
         <v>101</v>
@@ -8848,10 +8854,10 @@
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="C135" s="5">
         <v>-5.1408160000000001</v>
@@ -8863,13 +8869,13 @@
         <v>268</v>
       </c>
       <c r="F135" s="4" t="s">
+        <v>730</v>
+      </c>
+      <c r="G135" s="4" t="s">
+        <v>731</v>
+      </c>
+      <c r="H135" s="4" t="s">
         <v>732</v>
-      </c>
-      <c r="G135" s="4" t="s">
-        <v>733</v>
-      </c>
-      <c r="H135" s="4" t="s">
-        <v>734</v>
       </c>
       <c r="I135" s="4" t="s">
         <v>101</v>
@@ -8883,10 +8889,10 @@
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="C136" s="5">
         <v>-3.4787659999999998</v>
@@ -8898,13 +8904,13 @@
         <v>48</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="G136" s="4" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="H136" s="4" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="I136" s="4" t="s">
         <v>101</v>
@@ -8918,10 +8924,10 @@
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="C137" s="5">
         <v>-3.5617000000000001</v>
@@ -8933,13 +8939,13 @@
         <v>243</v>
       </c>
       <c r="F137" s="4" t="s">
+        <v>739</v>
+      </c>
+      <c r="G137" s="4" t="s">
+        <v>740</v>
+      </c>
+      <c r="H137" s="4" t="s">
         <v>741</v>
-      </c>
-      <c r="G137" s="4" t="s">
-        <v>742</v>
-      </c>
-      <c r="H137" s="4" t="s">
-        <v>743</v>
       </c>
       <c r="I137" s="4" t="s">
         <v>151</v>
@@ -8953,10 +8959,10 @@
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C138" s="5">
         <v>-5.4055679999999997</v>
@@ -8968,19 +8974,19 @@
         <v>136</v>
       </c>
       <c r="F138" s="4" t="s">
+        <v>744</v>
+      </c>
+      <c r="G138" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="H138" s="4" t="s">
         <v>746</v>
-      </c>
-      <c r="G138" s="4" t="s">
-        <v>747</v>
-      </c>
-      <c r="H138" s="4" t="s">
-        <v>748</v>
       </c>
       <c r="I138" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J138" s="6" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="K138" s="6" t="s">
         <v>18</v>
@@ -8988,10 +8994,10 @@
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="C139" s="5">
         <v>-2.9782660000000001</v>
@@ -9003,13 +9009,13 @@
         <v>176</v>
       </c>
       <c r="F139" s="4" t="s">
+        <v>749</v>
+      </c>
+      <c r="G139" s="4" t="s">
+        <v>750</v>
+      </c>
+      <c r="H139" s="4" t="s">
         <v>751</v>
-      </c>
-      <c r="G139" s="4" t="s">
-        <v>752</v>
-      </c>
-      <c r="H139" s="4" t="s">
-        <v>753</v>
       </c>
       <c r="I139" s="4" t="s">
         <v>151</v>
@@ -9023,10 +9029,10 @@
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="C140" s="5">
         <v>-2.9087830000000001</v>
@@ -9035,16 +9041,16 @@
         <v>-40.118616000000003</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="F140" s="4" t="s">
+        <v>754</v>
+      </c>
+      <c r="G140" s="4" t="s">
+        <v>755</v>
+      </c>
+      <c r="H140" s="4" t="s">
         <v>756</v>
-      </c>
-      <c r="G140" s="4" t="s">
-        <v>757</v>
-      </c>
-      <c r="H140" s="4" t="s">
-        <v>758</v>
       </c>
       <c r="I140" s="4" t="s">
         <v>101</v>
@@ -9058,10 +9064,10 @@
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="C141" s="5">
         <v>-3.697114</v>
@@ -9073,19 +9079,19 @@
         <v>48</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="G141" s="4" t="s">
         <v>51</v>
       </c>
       <c r="H141" s="4" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="I141" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J141" s="6" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="K141" s="6" t="s">
         <v>18</v>
@@ -9093,10 +9099,10 @@
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="C142" s="5">
         <v>-3.7188409999999998</v>
@@ -9108,19 +9114,19 @@
         <v>58</v>
       </c>
       <c r="F142" s="4" t="s">
+        <v>763</v>
+      </c>
+      <c r="G142" s="4" t="s">
+        <v>764</v>
+      </c>
+      <c r="H142" s="4" t="s">
         <v>765</v>
-      </c>
-      <c r="G142" s="4" t="s">
-        <v>766</v>
-      </c>
-      <c r="H142" s="4" t="s">
-        <v>767</v>
       </c>
       <c r="I142" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J142" s="6" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="K142" s="6" t="s">
         <v>18</v>
@@ -9128,10 +9134,10 @@
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="C143" s="5">
         <v>-4.0392330000000003</v>
@@ -9140,16 +9146,16 @@
         <v>-40.474150000000002</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="G143" s="4" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="H143" s="4" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="I143" s="4" t="s">
         <v>151</v>
@@ -9163,10 +9169,10 @@
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="C144" s="5">
         <v>-4.1177159999999997</v>
@@ -9178,13 +9184,13 @@
         <v>210</v>
       </c>
       <c r="F144" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="G144" s="4" t="s">
+        <v>773</v>
+      </c>
+      <c r="H144" s="4" t="s">
         <v>774</v>
-      </c>
-      <c r="G144" s="4" t="s">
-        <v>775</v>
-      </c>
-      <c r="H144" s="4" t="s">
-        <v>776</v>
       </c>
       <c r="I144" s="4" t="s">
         <v>101</v>
@@ -9198,10 +9204,10 @@
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="C145" s="5">
         <v>-4.5583349999999996</v>
@@ -9210,22 +9216,22 @@
         <v>-40.729585999999998</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="F145" s="4" t="s">
+        <v>777</v>
+      </c>
+      <c r="G145" s="4" t="s">
+        <v>778</v>
+      </c>
+      <c r="H145" s="4" t="s">
         <v>779</v>
-      </c>
-      <c r="G145" s="4" t="s">
-        <v>780</v>
-      </c>
-      <c r="H145" s="4" t="s">
-        <v>781</v>
       </c>
       <c r="I145" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J145" s="6" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="K145" s="6" t="s">
         <v>18</v>
@@ -9233,10 +9239,10 @@
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C146" s="5">
         <v>-5.1463979999999996</v>
@@ -9245,22 +9251,22 @@
         <v>-40.670636000000002</v>
       </c>
       <c r="E146" s="4" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="F146" s="4" t="s">
+        <v>782</v>
+      </c>
+      <c r="G146" s="4" t="s">
+        <v>783</v>
+      </c>
+      <c r="H146" s="4" t="s">
         <v>784</v>
-      </c>
-      <c r="G146" s="4" t="s">
-        <v>785</v>
-      </c>
-      <c r="H146" s="4" t="s">
-        <v>786</v>
       </c>
       <c r="I146" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J146" s="6" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="K146" s="6" t="s">
         <v>18</v>
@@ -9268,10 +9274,10 @@
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="C147" s="5">
         <v>-4.0631500000000003</v>
@@ -9280,16 +9286,16 @@
         <v>-40.957650000000001</v>
       </c>
       <c r="E147" s="4" t="s">
+        <v>787</v>
+      </c>
+      <c r="F147" s="4" t="s">
+        <v>788</v>
+      </c>
+      <c r="G147" s="4" t="s">
         <v>789</v>
       </c>
-      <c r="F147" s="4" t="s">
+      <c r="H147" s="4" t="s">
         <v>790</v>
-      </c>
-      <c r="G147" s="4" t="s">
-        <v>791</v>
-      </c>
-      <c r="H147" s="4" t="s">
-        <v>792</v>
       </c>
       <c r="I147" s="4" t="s">
         <v>101</v>
@@ -9303,10 +9309,10 @@
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="C148" s="5">
         <v>-3.4559829999999998</v>
@@ -9315,16 +9321,16 @@
         <v>-40.210115999999999</v>
       </c>
       <c r="E148" s="4" t="s">
+        <v>793</v>
+      </c>
+      <c r="F148" s="4" t="s">
+        <v>794</v>
+      </c>
+      <c r="G148" s="4" t="s">
         <v>795</v>
       </c>
-      <c r="F148" s="4" t="s">
+      <c r="H148" s="4" t="s">
         <v>796</v>
-      </c>
-      <c r="G148" s="4" t="s">
-        <v>797</v>
-      </c>
-      <c r="H148" s="4" t="s">
-        <v>798</v>
       </c>
       <c r="I148" s="4" t="s">
         <v>151</v>
@@ -9338,10 +9344,10 @@
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="C149" s="5">
         <v>-3.5106660000000001</v>
@@ -9350,16 +9356,16 @@
         <v>-40.385066000000002</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="F149" s="4" t="s">
+        <v>799</v>
+      </c>
+      <c r="G149" s="4" t="s">
+        <v>800</v>
+      </c>
+      <c r="H149" s="4" t="s">
         <v>801</v>
-      </c>
-      <c r="G149" s="4" t="s">
-        <v>802</v>
-      </c>
-      <c r="H149" s="4" t="s">
-        <v>803</v>
       </c>
       <c r="I149" s="4" t="s">
         <v>101</v>
@@ -9373,10 +9379,10 @@
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="C150" s="5">
         <v>-3.5546000000000002</v>
@@ -9388,13 +9394,13 @@
         <v>48</v>
       </c>
       <c r="F150" s="4" t="s">
+        <v>804</v>
+      </c>
+      <c r="G150" s="4" t="s">
+        <v>805</v>
+      </c>
+      <c r="H150" s="4" t="s">
         <v>806</v>
-      </c>
-      <c r="G150" s="4" t="s">
-        <v>807</v>
-      </c>
-      <c r="H150" s="4" t="s">
-        <v>808</v>
       </c>
       <c r="I150" s="4" t="s">
         <v>151</v>
@@ -9448,15 +9454,15 @@
         <v>5</v>
       </c>
       <c r="D1" s="29" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="E1" s="29"/>
       <c r="F1" s="30" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="G1" s="30"/>
       <c r="H1" s="26" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="I1" s="26"/>
       <c r="J1" s="26"/>
@@ -9479,7 +9485,7 @@
       <c r="AA1" s="26"/>
       <c r="AB1" s="26"/>
       <c r="AC1" s="24" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
     </row>
     <row r="2" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9491,18 +9497,18 @@
       <c r="F2" s="30"/>
       <c r="G2" s="30"/>
       <c r="H2" s="25" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="I2" s="25"/>
       <c r="J2" s="25"/>
       <c r="K2" s="9" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="M2" s="26" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="N2" s="26"/>
       <c r="O2" s="26"/>
@@ -9530,67 +9536,67 @@
       <c r="F3" s="30"/>
       <c r="G3" s="30"/>
       <c r="H3" s="8" t="s">
+        <v>816</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>817</v>
+      </c>
+      <c r="J3" s="8" t="s">
         <v>818</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="K3" s="7" t="s">
         <v>819</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="L3" s="7" t="s">
         <v>820</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="M3" s="7" t="s">
         <v>821</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="N3" s="7" t="s">
         <v>822</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="O3" s="7" t="s">
         <v>823</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="P3" s="7" t="s">
         <v>824</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="Q3" s="7" t="s">
         <v>825</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="R3" s="7" t="s">
         <v>826</v>
       </c>
-      <c r="Q3" s="7" t="s">
+      <c r="S3" s="7" t="s">
         <v>827</v>
       </c>
-      <c r="R3" s="7" t="s">
+      <c r="T3" s="7" t="s">
         <v>828</v>
       </c>
-      <c r="S3" s="7" t="s">
+      <c r="U3" s="7" t="s">
         <v>829</v>
       </c>
-      <c r="T3" s="7" t="s">
+      <c r="V3" s="7" t="s">
         <v>830</v>
       </c>
-      <c r="U3" s="7" t="s">
+      <c r="W3" s="7" t="s">
         <v>831</v>
       </c>
-      <c r="V3" s="7" t="s">
+      <c r="X3" s="7" t="s">
         <v>832</v>
       </c>
-      <c r="W3" s="7" t="s">
+      <c r="Y3" s="7" t="s">
         <v>833</v>
       </c>
-      <c r="X3" s="7" t="s">
+      <c r="Z3" s="7" t="s">
         <v>834</v>
       </c>
-      <c r="Y3" s="7" t="s">
+      <c r="AA3" s="7" t="s">
         <v>835</v>
       </c>
-      <c r="Z3" s="7" t="s">
+      <c r="AB3" s="7" t="s">
         <v>836</v>
-      </c>
-      <c r="AA3" s="7" t="s">
-        <v>837</v>
-      </c>
-      <c r="AB3" s="7" t="s">
-        <v>838</v>
       </c>
       <c r="AC3" s="24"/>
     </row>
@@ -10026,10 +10032,10 @@
         <v>147</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="D13" s="21"/>
       <c r="E13" s="21"/>
@@ -10324,13 +10330,13 @@
     </row>
     <row r="20" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="19" t="s">
+        <v>611</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>612</v>
+      </c>
+      <c r="C20" s="19" t="s">
         <v>613</v>
-      </c>
-      <c r="B20" s="19" t="s">
-        <v>614</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>615</v>
       </c>
       <c r="D20" s="21">
         <v>-3.7752400000000002</v>
@@ -10415,13 +10421,13 @@
     </row>
     <row r="21" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="19" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="B21" s="19" t="s">
         <v>210</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="D21" s="21"/>
       <c r="E21" s="21"/>
@@ -10458,13 +10464,13 @@
     </row>
     <row r="22" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="19" t="s">
+        <v>622</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>623</v>
+      </c>
+      <c r="C22" s="19" t="s">
         <v>624</v>
-      </c>
-      <c r="B22" s="19" t="s">
-        <v>625</v>
-      </c>
-      <c r="C22" s="19" t="s">
-        <v>626</v>
       </c>
       <c r="D22" s="21">
         <v>-4.7911549999999998</v>
@@ -10549,13 +10555,13 @@
     </row>
     <row r="23" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="19" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B23" s="19" t="s">
         <v>417</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="D23" s="21"/>
       <c r="E23" s="21"/>
@@ -10592,13 +10598,13 @@
     </row>
     <row r="24" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="19" t="s">
+        <v>633</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>634</v>
+      </c>
+      <c r="C24" s="19" t="s">
         <v>635</v>
-      </c>
-      <c r="B24" s="19" t="s">
-        <v>636</v>
-      </c>
-      <c r="C24" s="19" t="s">
-        <v>637</v>
       </c>
       <c r="D24" s="21"/>
       <c r="E24" s="21"/>
@@ -10635,13 +10641,13 @@
     </row>
     <row r="25" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="19" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B25" s="19" t="s">
         <v>237</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="D25" s="21"/>
       <c r="E25" s="21"/>
@@ -10678,13 +10684,13 @@
     </row>
     <row r="26" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="19" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="D26" s="21"/>
       <c r="E26" s="21"/>
@@ -10721,13 +10727,13 @@
     </row>
     <row r="27" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="19" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D27" s="21"/>
       <c r="E27" s="21"/>
@@ -10807,13 +10813,13 @@
     </row>
     <row r="29" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B29" s="19" t="s">
         <v>76</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="D29" s="21"/>
       <c r="E29" s="21"/>
@@ -10850,13 +10856,13 @@
     </row>
     <row r="30" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B30" s="19" t="s">
         <v>104</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="D30" s="21"/>
       <c r="E30" s="21"/>
@@ -10893,13 +10899,13 @@
     </row>
     <row r="31" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="B31" s="19" t="s">
         <v>36</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="D31" s="21">
         <v>-4.2869089999999996</v>
@@ -10984,13 +10990,13 @@
     </row>
     <row r="32" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B32" s="19" t="s">
         <v>176</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="D32" s="21"/>
       <c r="E32" s="21"/>
@@ -11027,13 +11033,13 @@
     </row>
     <row r="33" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="B33" s="19" t="s">
         <v>176</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="D33" s="21"/>
       <c r="E33" s="21"/>
@@ -11070,13 +11076,13 @@
     </row>
     <row r="34" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="19" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="B34" s="19" t="s">
         <v>25</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="D34" s="21"/>
       <c r="E34" s="21"/>
@@ -11113,13 +11119,13 @@
     </row>
     <row r="35" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="B35" s="19" t="s">
         <v>193</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="D35" s="21"/>
       <c r="E35" s="21"/>
@@ -11156,13 +11162,13 @@
     </row>
     <row r="36" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="B36" s="19" t="s">
         <v>193</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="D36" s="21"/>
       <c r="E36" s="21"/>
@@ -11199,13 +11205,13 @@
     </row>
     <row r="37" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
+        <v>692</v>
+      </c>
+      <c r="B37" s="19" t="s">
+        <v>693</v>
+      </c>
+      <c r="C37" s="19" t="s">
         <v>694</v>
-      </c>
-      <c r="B37" s="19" t="s">
-        <v>695</v>
-      </c>
-      <c r="C37" s="19" t="s">
-        <v>696</v>
       </c>
       <c r="D37" s="21"/>
       <c r="E37" s="21"/>
@@ -11242,13 +11248,13 @@
     </row>
     <row r="38" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="19" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D38" s="21"/>
       <c r="E38" s="21"/>
@@ -11285,13 +11291,13 @@
     </row>
     <row r="39" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="19" t="s">
+        <v>703</v>
+      </c>
+      <c r="B39" s="19" t="s">
+        <v>704</v>
+      </c>
+      <c r="C39" s="19" t="s">
         <v>705</v>
-      </c>
-      <c r="B39" s="19" t="s">
-        <v>706</v>
-      </c>
-      <c r="C39" s="19" t="s">
-        <v>707</v>
       </c>
       <c r="D39" s="21"/>
       <c r="E39" s="21"/>
@@ -11328,13 +11334,13 @@
     </row>
     <row r="40" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="19" t="s">
+        <v>709</v>
+      </c>
+      <c r="B40" s="19" t="s">
+        <v>710</v>
+      </c>
+      <c r="C40" s="19" t="s">
         <v>711</v>
-      </c>
-      <c r="B40" s="19" t="s">
-        <v>712</v>
-      </c>
-      <c r="C40" s="19" t="s">
-        <v>713</v>
       </c>
       <c r="D40" s="21"/>
       <c r="E40" s="21"/>
@@ -11371,13 +11377,13 @@
     </row>
     <row r="41" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="19" t="s">
+        <v>713</v>
+      </c>
+      <c r="B41" s="19" t="s">
+        <v>714</v>
+      </c>
+      <c r="C41" s="19" t="s">
         <v>715</v>
-      </c>
-      <c r="B41" s="19" t="s">
-        <v>716</v>
-      </c>
-      <c r="C41" s="19" t="s">
-        <v>717</v>
       </c>
       <c r="D41" s="21"/>
       <c r="E41" s="21"/>
@@ -11414,13 +11420,13 @@
     </row>
     <row r="42" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="19" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="B42" s="19" t="s">
         <v>199</v>
       </c>
       <c r="C42" s="19" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="D42" s="21"/>
       <c r="E42" s="21"/>
@@ -11457,13 +11463,13 @@
     </row>
     <row r="43" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="19" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="B43" s="19" t="s">
         <v>176</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="D43" s="21"/>
       <c r="E43" s="21"/>
@@ -11500,13 +11506,13 @@
     </row>
     <row r="44" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="19" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="B44" s="19" t="s">
         <v>268</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="D44" s="21"/>
       <c r="E44" s="21"/>
@@ -11543,13 +11549,13 @@
     </row>
     <row r="45" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="19" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="B45" s="19" t="s">
         <v>48</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="D45" s="21"/>
       <c r="E45" s="21"/>
@@ -11586,13 +11592,13 @@
     </row>
     <row r="46" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="19" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="B46" s="19" t="s">
         <v>243</v>
       </c>
       <c r="C46" s="19" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="D46" s="21"/>
       <c r="E46" s="21"/>
@@ -11629,13 +11635,13 @@
     </row>
     <row r="47" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="19" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="B47" s="19" t="s">
         <v>136</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="D47" s="21">
         <v>-5.4055679999999997</v>
@@ -11720,13 +11726,13 @@
     </row>
     <row r="48" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="19" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="B48" s="19" t="s">
         <v>176</v>
       </c>
       <c r="C48" s="19" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="D48" s="21"/>
       <c r="E48" s="21"/>
@@ -11763,13 +11769,13 @@
     </row>
     <row r="49" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="19" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="B49" s="19" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C49" s="19" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="D49" s="21"/>
       <c r="E49" s="21"/>
@@ -11806,13 +11812,13 @@
     </row>
     <row r="50" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="19" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="B50" s="19" t="s">
         <v>48</v>
       </c>
       <c r="C50" s="19" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D50" s="21">
         <v>-3.697114</v>
@@ -11897,13 +11903,13 @@
     </row>
     <row r="51" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="19" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B51" s="19" t="s">
         <v>58</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="D51" s="21">
         <v>-3.7188409999999998</v>
@@ -11988,13 +11994,13 @@
     </row>
     <row r="52" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="19" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="B52" s="19" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="C52" s="19" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="D52" s="21"/>
       <c r="E52" s="21"/>
@@ -12031,13 +12037,13 @@
     </row>
     <row r="53" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="19" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="B53" s="19" t="s">
         <v>210</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="D53" s="21"/>
       <c r="E53" s="21"/>
@@ -12074,13 +12080,13 @@
     </row>
     <row r="54" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="19" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="B54" s="19" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="C54" s="19" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="D54" s="21">
         <v>-4.5583349999999996</v>
@@ -12165,13 +12171,13 @@
     </row>
     <row r="55" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="19" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B55" s="19" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="D55" s="21">
         <v>-5.1463979999999996</v>
@@ -12256,13 +12262,13 @@
     </row>
     <row r="56" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="19" t="s">
+        <v>786</v>
+      </c>
+      <c r="B56" s="19" t="s">
+        <v>787</v>
+      </c>
+      <c r="C56" s="19" t="s">
         <v>788</v>
-      </c>
-      <c r="B56" s="19" t="s">
-        <v>789</v>
-      </c>
-      <c r="C56" s="19" t="s">
-        <v>790</v>
       </c>
       <c r="D56" s="21"/>
       <c r="E56" s="21"/>
@@ -12299,13 +12305,13 @@
     </row>
     <row r="57" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="19" t="s">
+        <v>792</v>
+      </c>
+      <c r="B57" s="19" t="s">
+        <v>793</v>
+      </c>
+      <c r="C57" s="19" t="s">
         <v>794</v>
-      </c>
-      <c r="B57" s="19" t="s">
-        <v>795</v>
-      </c>
-      <c r="C57" s="19" t="s">
-        <v>796</v>
       </c>
       <c r="D57" s="21"/>
       <c r="E57" s="21"/>
@@ -12342,13 +12348,13 @@
     </row>
     <row r="58" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="19" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="B58" s="19" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="C58" s="19" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="D58" s="21"/>
       <c r="E58" s="21"/>
@@ -12385,13 +12391,13 @@
     </row>
     <row r="59" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="19" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="B59" s="19" t="s">
         <v>48</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="D59" s="21"/>
       <c r="E59" s="21"/>
@@ -14049,13 +14055,13 @@
     </row>
     <row r="91" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="19" t="s">
+        <v>477</v>
+      </c>
+      <c r="B91" s="19" t="s">
+        <v>478</v>
+      </c>
+      <c r="C91" s="19" t="s">
         <v>479</v>
-      </c>
-      <c r="B91" s="19" t="s">
-        <v>480</v>
-      </c>
-      <c r="C91" s="19" t="s">
-        <v>481</v>
       </c>
       <c r="D91" s="21"/>
       <c r="E91" s="21"/>
@@ -14092,13 +14098,13 @@
     </row>
     <row r="92" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="19" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B92" s="19" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C92" s="19" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D92" s="21"/>
       <c r="E92" s="21"/>
@@ -14135,13 +14141,13 @@
     </row>
     <row r="93" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="19" t="s">
+        <v>487</v>
+      </c>
+      <c r="B93" s="19" t="s">
+        <v>488</v>
+      </c>
+      <c r="C93" s="19" t="s">
         <v>489</v>
-      </c>
-      <c r="B93" s="19" t="s">
-        <v>490</v>
-      </c>
-      <c r="C93" s="19" t="s">
-        <v>491</v>
       </c>
       <c r="D93" s="21"/>
       <c r="E93" s="21"/>
@@ -14181,10 +14187,10 @@
         <v>153</v>
       </c>
       <c r="B94" s="19" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="C94" s="19" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="D94" s="21">
         <v>-5.0822029999999998</v>
@@ -14269,13 +14275,13 @@
     </row>
     <row r="95" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="19" t="s">
+        <v>493</v>
+      </c>
+      <c r="B95" s="19" t="s">
+        <v>494</v>
+      </c>
+      <c r="C95" s="19" t="s">
         <v>495</v>
-      </c>
-      <c r="B95" s="19" t="s">
-        <v>496</v>
-      </c>
-      <c r="C95" s="19" t="s">
-        <v>497</v>
       </c>
       <c r="D95" s="21"/>
       <c r="E95" s="21"/>
@@ -14312,13 +14318,13 @@
     </row>
     <row r="96" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="19" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B96" s="19" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C96" s="19" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D96" s="21"/>
       <c r="E96" s="21"/>
@@ -14355,13 +14361,13 @@
     </row>
     <row r="97" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="19" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B97" s="19" t="s">
         <v>136</v>
       </c>
       <c r="C97" s="19" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D97" s="21"/>
       <c r="E97" s="21"/>
@@ -14398,13 +14404,13 @@
     </row>
     <row r="98" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="19" t="s">
+        <v>509</v>
+      </c>
+      <c r="B98" s="19" t="s">
+        <v>510</v>
+      </c>
+      <c r="C98" s="19" t="s">
         <v>511</v>
-      </c>
-      <c r="B98" s="19" t="s">
-        <v>512</v>
-      </c>
-      <c r="C98" s="19" t="s">
-        <v>513</v>
       </c>
       <c r="D98" s="21"/>
       <c r="E98" s="21"/>
@@ -14441,13 +14447,13 @@
     </row>
     <row r="99" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="19" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B99" s="19" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C99" s="19" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D99" s="21"/>
       <c r="E99" s="21"/>
@@ -14484,13 +14490,13 @@
     </row>
     <row r="100" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="19" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B100" s="19" t="s">
         <v>383</v>
       </c>
       <c r="C100" s="19" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="D100" s="21"/>
       <c r="E100" s="21"/>
@@ -14527,13 +14533,13 @@
     </row>
     <row r="101" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="19" t="s">
+        <v>525</v>
+      </c>
+      <c r="B101" s="19" t="s">
+        <v>526</v>
+      </c>
+      <c r="C101" s="19" t="s">
         <v>527</v>
-      </c>
-      <c r="B101" s="19" t="s">
-        <v>528</v>
-      </c>
-      <c r="C101" s="19" t="s">
-        <v>529</v>
       </c>
       <c r="D101" s="21"/>
       <c r="E101" s="21"/>
@@ -14570,13 +14576,13 @@
     </row>
     <row r="102" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="19" t="s">
+        <v>531</v>
+      </c>
+      <c r="B102" s="19" t="s">
+        <v>532</v>
+      </c>
+      <c r="C102" s="19" t="s">
         <v>533</v>
-      </c>
-      <c r="B102" s="19" t="s">
-        <v>534</v>
-      </c>
-      <c r="C102" s="19" t="s">
-        <v>535</v>
       </c>
       <c r="D102" s="21"/>
       <c r="E102" s="21"/>
@@ -14619,7 +14625,7 @@
         <v>165</v>
       </c>
       <c r="C103" s="19" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="D103" s="21">
         <v>-4.8596729999999999</v>
@@ -14704,13 +14710,13 @@
     </row>
     <row r="104" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="19" t="s">
+        <v>537</v>
+      </c>
+      <c r="B104" s="19" t="s">
+        <v>538</v>
+      </c>
+      <c r="C104" s="19" t="s">
         <v>539</v>
-      </c>
-      <c r="B104" s="19" t="s">
-        <v>540</v>
-      </c>
-      <c r="C104" s="19" t="s">
-        <v>541</v>
       </c>
       <c r="D104" s="21">
         <v>-4.4447369999999999</v>
@@ -14795,13 +14801,13 @@
     </row>
     <row r="105" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="19" t="s">
+        <v>543</v>
+      </c>
+      <c r="B105" s="19" t="s">
+        <v>544</v>
+      </c>
+      <c r="C105" s="19" t="s">
         <v>545</v>
-      </c>
-      <c r="B105" s="19" t="s">
-        <v>546</v>
-      </c>
-      <c r="C105" s="19" t="s">
-        <v>547</v>
       </c>
       <c r="D105" s="21">
         <v>-5.1705110000000003</v>
@@ -14886,13 +14892,13 @@
     </row>
     <row r="106" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="19" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B106" s="19" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C106" s="19" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="D106" s="21"/>
       <c r="E106" s="21"/>
@@ -14929,13 +14935,13 @@
     </row>
     <row r="107" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="19" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="B107" s="19" t="s">
         <v>360</v>
       </c>
       <c r="C107" s="19" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="D107" s="21"/>
       <c r="E107" s="21"/>
@@ -15015,13 +15021,13 @@
     </row>
     <row r="109" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="19" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B109" s="19" t="s">
         <v>42</v>
       </c>
       <c r="C109" s="19" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="D109" s="21"/>
       <c r="E109" s="21"/>
@@ -15058,13 +15064,13 @@
     </row>
     <row r="110" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="19" t="s">
+        <v>563</v>
+      </c>
+      <c r="B110" s="19" t="s">
+        <v>564</v>
+      </c>
+      <c r="C110" s="19" t="s">
         <v>565</v>
-      </c>
-      <c r="B110" s="19" t="s">
-        <v>566</v>
-      </c>
-      <c r="C110" s="19" t="s">
-        <v>567</v>
       </c>
       <c r="D110" s="21">
         <v>-3.6978119999999999</v>
@@ -15149,13 +15155,13 @@
     </row>
     <row r="111" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="19" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="B111" s="19" t="s">
         <v>210</v>
       </c>
       <c r="C111" s="19" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="D111" s="21">
         <v>-5.2113269999999998</v>
@@ -15240,13 +15246,13 @@
     </row>
     <row r="112" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="19" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B112" s="19" t="s">
         <v>210</v>
       </c>
       <c r="C112" s="19" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="D112" s="21">
         <v>-4.3822749999999999</v>
@@ -15331,13 +15337,13 @@
     </row>
     <row r="113" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="19" t="s">
+        <v>579</v>
+      </c>
+      <c r="B113" s="19" t="s">
+        <v>580</v>
+      </c>
+      <c r="C113" s="19" t="s">
         <v>581</v>
-      </c>
-      <c r="B113" s="19" t="s">
-        <v>582</v>
-      </c>
-      <c r="C113" s="19" t="s">
-        <v>583</v>
       </c>
       <c r="D113" s="21"/>
       <c r="E113" s="21"/>
@@ -15374,13 +15380,13 @@
     </row>
     <row r="114" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="19" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B114" s="19" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C114" s="19" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D114" s="21"/>
       <c r="E114" s="21"/>
@@ -15417,13 +15423,13 @@
     </row>
     <row r="115" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="19" t="s">
+        <v>590</v>
+      </c>
+      <c r="B115" s="19" t="s">
+        <v>591</v>
+      </c>
+      <c r="C115" s="19" t="s">
         <v>592</v>
-      </c>
-      <c r="B115" s="19" t="s">
-        <v>593</v>
-      </c>
-      <c r="C115" s="19" t="s">
-        <v>594</v>
       </c>
       <c r="D115" s="21"/>
       <c r="E115" s="21"/>
@@ -15460,13 +15466,13 @@
     </row>
     <row r="116" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="19" t="s">
+        <v>596</v>
+      </c>
+      <c r="B116" s="19" t="s">
+        <v>597</v>
+      </c>
+      <c r="C116" s="19" t="s">
         <v>598</v>
-      </c>
-      <c r="B116" s="19" t="s">
-        <v>599</v>
-      </c>
-      <c r="C116" s="19" t="s">
-        <v>600</v>
       </c>
       <c r="D116" s="21"/>
       <c r="E116" s="21"/>
@@ -15503,13 +15509,13 @@
     </row>
     <row r="117" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="19" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B117" s="19" t="s">
         <v>142</v>
       </c>
       <c r="C117" s="19" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="D117" s="21"/>
       <c r="E117" s="21"/>
@@ -15546,13 +15552,13 @@
     </row>
     <row r="118" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="19" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="B118" s="19" t="s">
         <v>104</v>
       </c>
       <c r="C118" s="19" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="D118" s="21"/>
       <c r="E118" s="21"/>

--- a/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
+++ b/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12245B61-4064-46BD-931F-B14F7CD6273A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAB8F87B-FC15-4FB6-83A4-06C86005B746}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1833" uniqueCount="846">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1833" uniqueCount="845">
   <si>
     <t>WKT</t>
   </si>
@@ -2579,9 +2579,6 @@
   </si>
   <si>
     <t>ENGº. JOSÉ LOPES</t>
-  </si>
-  <si>
-    <t>PAVIMENTADA</t>
   </si>
 </sst>
 </file>
@@ -6819,7 +6816,7 @@
         <v>841</v>
       </c>
       <c r="K76" s="6" t="s">
-        <v>845</v>
+        <v>18</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">

--- a/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
+++ b/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAB8F87B-FC15-4FB6-83A4-06C86005B746}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{815823D5-1A64-4472-891D-A782F3CFAA4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
   </bookViews>
   <sheets>
     <sheet name="LISTA DE PONTOS" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1833" uniqueCount="845">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1843" uniqueCount="855">
   <si>
     <t>WKT</t>
   </si>
@@ -2579,14 +2579,45 @@
   </si>
   <si>
     <t>ENGº. JOSÉ LOPES</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -5,528114°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -39,517208°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -5,811800°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -39,429194°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -5,678148°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -39,430067°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -5,735844°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -39,026054°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -5,684576°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -39,195397°</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000000"/>
+    <numFmt numFmtId="165" formatCode="0.00000"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -2705,7 +2736,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2786,6 +2817,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -7002,10 +7036,10 @@
         <v>499</v>
       </c>
       <c r="C82" s="5">
-        <v>-5.7368329999999998</v>
+        <v>-5.7358440000000002</v>
       </c>
       <c r="D82" s="5">
-        <v>-39.028033000000001</v>
+        <v>-39.026054000000002</v>
       </c>
       <c r="E82" s="4" t="s">
         <v>494</v>
@@ -7037,10 +7071,10 @@
         <v>504</v>
       </c>
       <c r="C83" s="5">
-        <v>-5.6816329999999997</v>
+        <v>-5.6845759999999999</v>
       </c>
       <c r="D83" s="5">
-        <v>-39.201065999999997</v>
+        <v>-39.195397</v>
       </c>
       <c r="E83" s="4" t="s">
         <v>136</v>
@@ -8787,10 +8821,10 @@
         <v>719</v>
       </c>
       <c r="C133" s="5">
-        <v>-5.8101659999999997</v>
+        <v>-5.8117999999999999</v>
       </c>
       <c r="D133" s="5">
-        <v>-39.426600000000001</v>
+        <v>-39.429194000000003</v>
       </c>
       <c r="E133" s="4" t="s">
         <v>199</v>
@@ -10818,8 +10852,12 @@
       <c r="C29" s="19" t="s">
         <v>655</v>
       </c>
-      <c r="D29" s="21"/>
-      <c r="E29" s="21"/>
+      <c r="D29" s="31" t="s">
+        <v>845</v>
+      </c>
+      <c r="E29" s="31" t="s">
+        <v>846</v>
+      </c>
       <c r="F29" s="20"/>
       <c r="G29" s="20">
         <f t="shared" si="0"/>
@@ -11425,8 +11463,12 @@
       <c r="C42" s="19" t="s">
         <v>720</v>
       </c>
-      <c r="D42" s="21"/>
-      <c r="E42" s="21"/>
+      <c r="D42" s="31" t="s">
+        <v>847</v>
+      </c>
+      <c r="E42" s="31" t="s">
+        <v>848</v>
+      </c>
       <c r="F42" s="20"/>
       <c r="G42" s="20">
         <f t="shared" si="0"/>
@@ -14017,8 +14059,12 @@
       <c r="C90" s="19" t="s">
         <v>475</v>
       </c>
-      <c r="D90" s="21"/>
-      <c r="E90" s="21"/>
+      <c r="D90" s="31" t="s">
+        <v>849</v>
+      </c>
+      <c r="E90" s="31" t="s">
+        <v>850</v>
+      </c>
       <c r="F90" s="20"/>
       <c r="G90" s="20">
         <f t="shared" si="3"/>
@@ -14323,8 +14369,12 @@
       <c r="C96" s="19" t="s">
         <v>500</v>
       </c>
-      <c r="D96" s="21"/>
-      <c r="E96" s="21"/>
+      <c r="D96" s="31" t="s">
+        <v>851</v>
+      </c>
+      <c r="E96" s="31" t="s">
+        <v>852</v>
+      </c>
       <c r="F96" s="20"/>
       <c r="G96" s="20">
         <f t="shared" si="3"/>
@@ -14366,8 +14416,12 @@
       <c r="C97" s="19" t="s">
         <v>505</v>
       </c>
-      <c r="D97" s="21"/>
-      <c r="E97" s="21"/>
+      <c r="D97" s="31" t="s">
+        <v>853</v>
+      </c>
+      <c r="E97" s="31" t="s">
+        <v>854</v>
+      </c>
       <c r="F97" s="20"/>
       <c r="G97" s="20">
         <f t="shared" si="3"/>

--- a/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
+++ b/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{815823D5-1A64-4472-891D-A782F3CFAA4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7E65608-F8F6-4901-A848-AE2EDE7C1858}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
   </bookViews>
   <sheets>
     <sheet name="LISTA DE PONTOS" sheetId="1" r:id="rId1"/>
@@ -1563,12 +1563,6 @@
     <t>226BCE0550S3</t>
   </si>
   <si>
-    <t>ENTR CE-371 (C) /473 (MILHÃ)</t>
-  </si>
-  <si>
-    <t>ENTR CE-166/363 (SENADOR POMPEU)</t>
-  </si>
-  <si>
     <t>POINT (-38.955967 -6.944367)</t>
   </si>
   <si>
@@ -2609,6 +2603,12 @@
   </si>
   <si>
     <t xml:space="preserve"> -39,195397°</t>
+  </si>
+  <si>
+    <t>226BCE0550S1</t>
+  </si>
+  <si>
+    <t>ENTR. CE-371(B)/473(B)</t>
   </si>
 </sst>
 </file>
@@ -2797,6 +2797,9 @@
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2817,9 +2820,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4222,7 +4222,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>9</v>
@@ -4257,7 +4257,7 @@
         <v>16</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="K2" s="6" t="s">
         <v>18</v>
@@ -4292,7 +4292,7 @@
         <v>16</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="K3" s="6" t="s">
         <v>18</v>
@@ -4362,7 +4362,7 @@
         <v>16</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="K5" s="6" t="s">
         <v>18</v>
@@ -4642,7 +4642,7 @@
         <v>16</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="K13" s="6" t="s">
         <v>18</v>
@@ -4677,7 +4677,7 @@
         <v>16</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="K14" s="6" t="s">
         <v>18</v>
@@ -4747,7 +4747,7 @@
         <v>16</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="K16" s="6" t="s">
         <v>18</v>
@@ -4817,7 +4817,7 @@
         <v>16</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="K18" s="6" t="s">
         <v>18</v>
@@ -5132,7 +5132,7 @@
         <v>16</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="K27" s="6" t="s">
         <v>18</v>
@@ -5167,7 +5167,7 @@
         <v>16</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="K28" s="6" t="s">
         <v>18</v>
@@ -5202,7 +5202,7 @@
         <v>16</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="K29" s="6" t="s">
         <v>18</v>
@@ -5237,7 +5237,7 @@
         <v>16</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="K30" s="6" t="s">
         <v>18</v>
@@ -5272,7 +5272,7 @@
         <v>16</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="K31" s="6" t="s">
         <v>18</v>
@@ -5412,7 +5412,7 @@
         <v>16</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="K35" s="6" t="s">
         <v>310</v>
@@ -5692,7 +5692,7 @@
         <v>151</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="K43" s="6" t="s">
         <v>18</v>
@@ -5797,7 +5797,7 @@
         <v>101</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="K46" s="6" t="s">
         <v>18</v>
@@ -5902,7 +5902,7 @@
         <v>101</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="K49" s="6" t="s">
         <v>18</v>
@@ -5937,7 +5937,7 @@
         <v>101</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="K50" s="6" t="s">
         <v>18</v>
@@ -5972,7 +5972,7 @@
         <v>151</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="K51" s="6" t="s">
         <v>18</v>
@@ -6602,7 +6602,7 @@
         <v>101</v>
       </c>
       <c r="J69" s="6" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="K69" s="6" t="s">
         <v>18</v>
@@ -6777,7 +6777,7 @@
         <v>101</v>
       </c>
       <c r="J74" s="6" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="K74" s="6" t="s">
         <v>18</v>
@@ -6835,19 +6835,19 @@
         <v>199</v>
       </c>
       <c r="F76" s="4" t="s">
+        <v>840</v>
+      </c>
+      <c r="G76" s="4" t="s">
+        <v>841</v>
+      </c>
+      <c r="H76" s="4" t="s">
         <v>842</v>
-      </c>
-      <c r="G76" s="4" t="s">
-        <v>843</v>
-      </c>
-      <c r="H76" s="4" t="s">
-        <v>844</v>
       </c>
       <c r="I76" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J76" s="6" t="s">
-        <v>841</v>
+        <v>806</v>
       </c>
       <c r="K76" s="6" t="s">
         <v>18</v>
@@ -6952,7 +6952,7 @@
         <v>101</v>
       </c>
       <c r="J79" s="6" t="s">
-        <v>17</v>
+        <v>839</v>
       </c>
       <c r="K79" s="6" t="s">
         <v>18</v>
@@ -6987,7 +6987,7 @@
         <v>101</v>
       </c>
       <c r="J80" s="6" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="K80" s="6" t="s">
         <v>18</v>
@@ -7042,10 +7042,10 @@
         <v>-39.026054000000002</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>494</v>
+        <v>136</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>500</v>
+        <v>853</v>
       </c>
       <c r="G82" s="4" t="s">
         <v>501</v>
@@ -7057,7 +7057,7 @@
         <v>101</v>
       </c>
       <c r="J82" s="6" t="s">
-        <v>841</v>
+        <v>806</v>
       </c>
       <c r="K82" s="6" t="s">
         <v>18</v>
@@ -7083,16 +7083,16 @@
         <v>505</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>507</v>
+        <v>854</v>
       </c>
       <c r="I83" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J83" s="6" t="s">
-        <v>841</v>
+        <v>806</v>
       </c>
       <c r="K83" s="6" t="s">
         <v>18</v>
@@ -7100,10 +7100,10 @@
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C84" s="5">
         <v>-5.0811999999999999</v>
@@ -7112,16 +7112,16 @@
         <v>-38.004565999999997</v>
       </c>
       <c r="E84" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="G84" s="4" t="s">
         <v>510</v>
       </c>
-      <c r="F84" s="4" t="s">
+      <c r="H84" s="4" t="s">
         <v>511</v>
-      </c>
-      <c r="G84" s="4" t="s">
-        <v>512</v>
-      </c>
-      <c r="H84" s="4" t="s">
-        <v>513</v>
       </c>
       <c r="I84" s="4" t="s">
         <v>101</v>
@@ -7135,10 +7135,10 @@
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C85" s="5">
         <v>-5.2329999999999997</v>
@@ -7147,16 +7147,16 @@
         <v>-38.194850000000002</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="F85" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="G85" s="4" t="s">
+        <v>515</v>
+      </c>
+      <c r="H85" s="4" t="s">
         <v>516</v>
-      </c>
-      <c r="G85" s="4" t="s">
-        <v>517</v>
-      </c>
-      <c r="H85" s="4" t="s">
-        <v>518</v>
       </c>
       <c r="I85" s="4" t="s">
         <v>101</v>
@@ -7197,7 +7197,7 @@
         <v>151</v>
       </c>
       <c r="J86" s="6" t="s">
-        <v>17</v>
+        <v>839</v>
       </c>
       <c r="K86" s="6" t="s">
         <v>18</v>
@@ -7205,10 +7205,10 @@
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C87" s="5">
         <v>-3.9741499999999998</v>
@@ -7220,13 +7220,13 @@
         <v>383</v>
       </c>
       <c r="F87" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="G87" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="H87" s="4" t="s">
         <v>521</v>
-      </c>
-      <c r="G87" s="4" t="s">
-        <v>522</v>
-      </c>
-      <c r="H87" s="4" t="s">
-        <v>523</v>
       </c>
       <c r="I87" s="4" t="s">
         <v>151</v>
@@ -7240,10 +7240,10 @@
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="C88" s="5">
         <v>-3.962866</v>
@@ -7252,16 +7252,16 @@
         <v>-38.357016000000002</v>
       </c>
       <c r="E88" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>525</v>
+      </c>
+      <c r="G88" s="4" t="s">
         <v>526</v>
       </c>
-      <c r="F88" s="4" t="s">
+      <c r="H88" s="4" t="s">
         <v>527</v>
-      </c>
-      <c r="G88" s="4" t="s">
-        <v>528</v>
-      </c>
-      <c r="H88" s="4" t="s">
-        <v>529</v>
       </c>
       <c r="I88" s="4" t="s">
         <v>101</v>
@@ -7275,10 +7275,10 @@
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C89" s="5">
         <v>-4.0425329999999997</v>
@@ -7287,16 +7287,16 @@
         <v>-38.206499999999998</v>
       </c>
       <c r="E89" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="G89" s="4" t="s">
         <v>532</v>
       </c>
-      <c r="F89" s="4" t="s">
+      <c r="H89" s="4" t="s">
         <v>533</v>
-      </c>
-      <c r="G89" s="4" t="s">
-        <v>534</v>
-      </c>
-      <c r="H89" s="4" t="s">
-        <v>535</v>
       </c>
       <c r="I89" s="4" t="s">
         <v>151</v>
@@ -7337,7 +7337,7 @@
         <v>151</v>
       </c>
       <c r="J90" s="6" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="K90" s="6" t="s">
         <v>18</v>
@@ -7345,10 +7345,10 @@
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C91" s="5">
         <v>-4.4447369999999999</v>
@@ -7357,22 +7357,22 @@
         <v>-38.662745999999999</v>
       </c>
       <c r="E91" s="4" t="s">
+        <v>536</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>537</v>
+      </c>
+      <c r="G91" s="4" t="s">
         <v>538</v>
       </c>
-      <c r="F91" s="4" t="s">
+      <c r="H91" s="4" t="s">
         <v>539</v>
-      </c>
-      <c r="G91" s="4" t="s">
-        <v>540</v>
-      </c>
-      <c r="H91" s="4" t="s">
-        <v>541</v>
       </c>
       <c r="I91" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J91" s="6" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="K91" s="6" t="s">
         <v>18</v>
@@ -7380,10 +7380,10 @@
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C92" s="5">
         <v>-5.1705110000000003</v>
@@ -7392,22 +7392,22 @@
         <v>-40.708150000000003</v>
       </c>
       <c r="E92" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="F92" s="4" t="s">
+        <v>543</v>
+      </c>
+      <c r="G92" s="4" t="s">
         <v>544</v>
       </c>
-      <c r="F92" s="4" t="s">
+      <c r="H92" s="4" t="s">
         <v>545</v>
-      </c>
-      <c r="G92" s="4" t="s">
-        <v>546</v>
-      </c>
-      <c r="H92" s="4" t="s">
-        <v>547</v>
       </c>
       <c r="I92" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J92" s="6" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="K92" s="6" t="s">
         <v>18</v>
@@ -7415,10 +7415,10 @@
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C93" s="5">
         <v>-4.5725499999999997</v>
@@ -7430,13 +7430,13 @@
         <v>494</v>
       </c>
       <c r="F93" s="4" t="s">
+        <v>548</v>
+      </c>
+      <c r="G93" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="H93" s="4" t="s">
         <v>550</v>
-      </c>
-      <c r="G93" s="4" t="s">
-        <v>551</v>
-      </c>
-      <c r="H93" s="4" t="s">
-        <v>552</v>
       </c>
       <c r="I93" s="4" t="s">
         <v>101</v>
@@ -7450,10 +7450,10 @@
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="C94" s="5">
         <v>-5.1207330000000004</v>
@@ -7465,13 +7465,13 @@
         <v>360</v>
       </c>
       <c r="F94" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="G94" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="H94" s="4" t="s">
         <v>555</v>
-      </c>
-      <c r="G94" s="4" t="s">
-        <v>556</v>
-      </c>
-      <c r="H94" s="4" t="s">
-        <v>557</v>
       </c>
       <c r="I94" s="4" t="s">
         <v>101</v>
@@ -7512,7 +7512,7 @@
         <v>151</v>
       </c>
       <c r="J95" s="6" t="s">
-        <v>17</v>
+        <v>839</v>
       </c>
       <c r="K95" s="6" t="s">
         <v>18</v>
@@ -7520,10 +7520,10 @@
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C96" s="5">
         <v>-3.6957</v>
@@ -7535,13 +7535,13 @@
         <v>42</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="G96" s="4" t="s">
         <v>303</v>
       </c>
       <c r="H96" s="4" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I96" s="4" t="s">
         <v>101</v>
@@ -7555,10 +7555,10 @@
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C97" s="5">
         <v>-3.6978119999999999</v>
@@ -7567,22 +7567,22 @@
         <v>-40.307443999999997</v>
       </c>
       <c r="E97" s="4" t="s">
+        <v>562</v>
+      </c>
+      <c r="F97" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="G97" s="4" t="s">
         <v>564</v>
       </c>
-      <c r="F97" s="4" t="s">
+      <c r="H97" s="4" t="s">
         <v>565</v>
-      </c>
-      <c r="G97" s="4" t="s">
-        <v>566</v>
-      </c>
-      <c r="H97" s="4" t="s">
-        <v>567</v>
       </c>
       <c r="I97" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J97" s="6" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="K97" s="6" t="s">
         <v>18</v>
@@ -7590,10 +7590,10 @@
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C98" s="5">
         <v>-5.2113269999999998</v>
@@ -7605,19 +7605,19 @@
         <v>210</v>
       </c>
       <c r="F98" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="G98" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="H98" s="4" t="s">
         <v>570</v>
-      </c>
-      <c r="G98" s="4" t="s">
-        <v>571</v>
-      </c>
-      <c r="H98" s="4" t="s">
-        <v>572</v>
       </c>
       <c r="I98" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J98" s="6" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="K98" s="6" t="s">
         <v>18</v>
@@ -7625,10 +7625,10 @@
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C99" s="5">
         <v>-4.3822749999999999</v>
@@ -7640,19 +7640,19 @@
         <v>210</v>
       </c>
       <c r="F99" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="G99" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="H99" s="4" t="s">
         <v>575</v>
-      </c>
-      <c r="G99" s="4" t="s">
-        <v>576</v>
-      </c>
-      <c r="H99" s="4" t="s">
-        <v>577</v>
       </c>
       <c r="I99" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J99" s="6" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="K99" s="6" t="s">
         <v>18</v>
@@ -7660,10 +7660,10 @@
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C100" s="5">
         <v>-6.0296659999999997</v>
@@ -7672,16 +7672,16 @@
         <v>-38.340949999999999</v>
       </c>
       <c r="E100" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="G100" s="4" t="s">
         <v>580</v>
       </c>
-      <c r="F100" s="4" t="s">
+      <c r="H100" s="4" t="s">
         <v>581</v>
-      </c>
-      <c r="G100" s="4" t="s">
-        <v>582</v>
-      </c>
-      <c r="H100" s="4" t="s">
-        <v>583</v>
       </c>
       <c r="I100" s="4" t="s">
         <v>101</v>
@@ -7695,10 +7695,10 @@
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C101" s="5">
         <v>-5.2479829999999996</v>
@@ -7710,13 +7710,13 @@
         <v>494</v>
       </c>
       <c r="F101" s="4" t="s">
+        <v>584</v>
+      </c>
+      <c r="G101" s="4" t="s">
+        <v>585</v>
+      </c>
+      <c r="H101" s="4" t="s">
         <v>586</v>
-      </c>
-      <c r="G101" s="4" t="s">
-        <v>587</v>
-      </c>
-      <c r="H101" s="4" t="s">
-        <v>588</v>
       </c>
       <c r="I101" s="4" t="s">
         <v>151</v>
@@ -7730,10 +7730,10 @@
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C102" s="5">
         <v>-4.2260499999999999</v>
@@ -7742,16 +7742,16 @@
         <v>-38.112082999999998</v>
       </c>
       <c r="E102" s="4" t="s">
+        <v>589</v>
+      </c>
+      <c r="F102" s="4" t="s">
+        <v>590</v>
+      </c>
+      <c r="G102" s="4" t="s">
         <v>591</v>
       </c>
-      <c r="F102" s="4" t="s">
+      <c r="H102" s="4" t="s">
         <v>592</v>
-      </c>
-      <c r="G102" s="4" t="s">
-        <v>593</v>
-      </c>
-      <c r="H102" s="4" t="s">
-        <v>594</v>
       </c>
       <c r="I102" s="4" t="s">
         <v>151</v>
@@ -7765,10 +7765,10 @@
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="C103" s="5">
         <v>-4.2283499999999998</v>
@@ -7777,16 +7777,16 @@
         <v>-38.112932999999998</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="G103" s="4" t="s">
         <v>73</v>
       </c>
       <c r="H103" s="4" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="I103" s="4" t="s">
         <v>101</v>
@@ -7800,10 +7800,10 @@
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C104" s="5">
         <v>-4.5906500000000001</v>
@@ -7815,13 +7815,13 @@
         <v>142</v>
       </c>
       <c r="F104" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="G104" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="H104" s="4" t="s">
         <v>602</v>
-      </c>
-      <c r="G104" s="4" t="s">
-        <v>603</v>
-      </c>
-      <c r="H104" s="4" t="s">
-        <v>604</v>
       </c>
       <c r="I104" s="4" t="s">
         <v>101</v>
@@ -7835,10 +7835,10 @@
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="C105" s="5">
         <v>-3.9187500000000002</v>
@@ -7850,13 +7850,13 @@
         <v>104</v>
       </c>
       <c r="F105" s="4" t="s">
+        <v>605</v>
+      </c>
+      <c r="G105" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="H105" s="4" t="s">
         <v>607</v>
-      </c>
-      <c r="G105" s="4" t="s">
-        <v>608</v>
-      </c>
-      <c r="H105" s="4" t="s">
-        <v>609</v>
       </c>
       <c r="I105" s="4" t="s">
         <v>101</v>
@@ -8037,7 +8037,7 @@
         <v>151</v>
       </c>
       <c r="J110" s="6" t="s">
-        <v>17</v>
+        <v>839</v>
       </c>
       <c r="K110" s="6" t="s">
         <v>18</v>
@@ -8045,10 +8045,10 @@
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="C111" s="5">
         <v>-3.7752400000000002</v>
@@ -8057,22 +8057,22 @@
         <v>-40.496578999999997</v>
       </c>
       <c r="E111" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="F111" s="4" t="s">
+        <v>611</v>
+      </c>
+      <c r="G111" s="4" t="s">
         <v>612</v>
       </c>
-      <c r="F111" s="4" t="s">
+      <c r="H111" s="4" t="s">
         <v>613</v>
-      </c>
-      <c r="G111" s="4" t="s">
-        <v>614</v>
-      </c>
-      <c r="H111" s="4" t="s">
-        <v>615</v>
       </c>
       <c r="I111" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J111" s="6" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="K111" s="6" t="s">
         <v>18</v>
@@ -8080,10 +8080,10 @@
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="C112" s="5">
         <v>-3.9438659999999999</v>
@@ -8095,13 +8095,13 @@
         <v>210</v>
       </c>
       <c r="F112" s="4" t="s">
+        <v>616</v>
+      </c>
+      <c r="G112" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="H112" s="4" t="s">
         <v>618</v>
-      </c>
-      <c r="G112" s="4" t="s">
-        <v>619</v>
-      </c>
-      <c r="H112" s="4" t="s">
-        <v>620</v>
       </c>
       <c r="I112" s="4" t="s">
         <v>101</v>
@@ -8115,10 +8115,10 @@
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C113" s="5">
         <v>-4.7911549999999998</v>
@@ -8127,22 +8127,22 @@
         <v>-40.827958000000002</v>
       </c>
       <c r="E113" s="4" t="s">
+        <v>621</v>
+      </c>
+      <c r="F113" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="G113" s="4" t="s">
         <v>623</v>
       </c>
-      <c r="F113" s="4" t="s">
+      <c r="H113" s="4" t="s">
         <v>624</v>
-      </c>
-      <c r="G113" s="4" t="s">
-        <v>625</v>
-      </c>
-      <c r="H113" s="4" t="s">
-        <v>626</v>
       </c>
       <c r="I113" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J113" s="6" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="K113" s="6" t="s">
         <v>18</v>
@@ -8150,10 +8150,10 @@
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="C114" s="5">
         <v>-3.4767329999999999</v>
@@ -8165,13 +8165,13 @@
         <v>417</v>
       </c>
       <c r="F114" s="4" t="s">
+        <v>627</v>
+      </c>
+      <c r="G114" s="4" t="s">
+        <v>628</v>
+      </c>
+      <c r="H114" s="4" t="s">
         <v>629</v>
-      </c>
-      <c r="G114" s="4" t="s">
-        <v>630</v>
-      </c>
-      <c r="H114" s="4" t="s">
-        <v>631</v>
       </c>
       <c r="I114" s="4" t="s">
         <v>101</v>
@@ -8185,10 +8185,10 @@
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C115" s="5">
         <v>-4.5871829999999996</v>
@@ -8197,16 +8197,16 @@
         <v>-38.620182999999997</v>
       </c>
       <c r="E115" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="F115" s="4" t="s">
+        <v>633</v>
+      </c>
+      <c r="G115" s="4" t="s">
         <v>634</v>
       </c>
-      <c r="F115" s="4" t="s">
+      <c r="H115" s="4" t="s">
         <v>635</v>
-      </c>
-      <c r="G115" s="4" t="s">
-        <v>636</v>
-      </c>
-      <c r="H115" s="4" t="s">
-        <v>637</v>
       </c>
       <c r="I115" s="4" t="s">
         <v>101</v>
@@ -8220,10 +8220,10 @@
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="C116" s="5">
         <v>-3.4662999999999999</v>
@@ -8235,13 +8235,13 @@
         <v>237</v>
       </c>
       <c r="F116" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="G116" s="4" t="s">
+        <v>639</v>
+      </c>
+      <c r="H116" s="4" t="s">
         <v>640</v>
-      </c>
-      <c r="G116" s="4" t="s">
-        <v>641</v>
-      </c>
-      <c r="H116" s="4" t="s">
-        <v>642</v>
       </c>
       <c r="I116" s="4" t="s">
         <v>151</v>
@@ -8255,10 +8255,10 @@
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="C117" s="5">
         <v>-3.2141000000000002</v>
@@ -8270,13 +8270,13 @@
         <v>478</v>
       </c>
       <c r="F117" s="4" t="s">
+        <v>643</v>
+      </c>
+      <c r="G117" s="4" t="s">
+        <v>644</v>
+      </c>
+      <c r="H117" s="4" t="s">
         <v>645</v>
-      </c>
-      <c r="G117" s="4" t="s">
-        <v>646</v>
-      </c>
-      <c r="H117" s="4" t="s">
-        <v>647</v>
       </c>
       <c r="I117" s="4" t="s">
         <v>101</v>
@@ -8290,10 +8290,10 @@
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="C118" s="5">
         <v>-5.0508829999999998</v>
@@ -8302,16 +8302,16 @@
         <v>-37.779632999999997</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="F118" s="4" t="s">
+        <v>648</v>
+      </c>
+      <c r="G118" s="4" t="s">
+        <v>649</v>
+      </c>
+      <c r="H118" s="4" t="s">
         <v>650</v>
-      </c>
-      <c r="G118" s="4" t="s">
-        <v>651</v>
-      </c>
-      <c r="H118" s="4" t="s">
-        <v>652</v>
       </c>
       <c r="I118" s="4" t="s">
         <v>151</v>
@@ -8352,7 +8352,7 @@
         <v>151</v>
       </c>
       <c r="J119" s="6" t="s">
-        <v>17</v>
+        <v>839</v>
       </c>
       <c r="K119" s="6" t="s">
         <v>18</v>
@@ -8360,10 +8360,10 @@
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C120" s="5">
         <v>-5.5281140000000004</v>
@@ -8375,19 +8375,19 @@
         <v>76</v>
       </c>
       <c r="F120" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="G120" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="H120" s="4" t="s">
         <v>655</v>
-      </c>
-      <c r="G120" s="4" t="s">
-        <v>656</v>
-      </c>
-      <c r="H120" s="4" t="s">
-        <v>657</v>
       </c>
       <c r="I120" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J120" s="6" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="K120" s="6" t="s">
         <v>18</v>
@@ -8395,10 +8395,10 @@
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="C121" s="5">
         <v>-4.338266</v>
@@ -8410,13 +8410,13 @@
         <v>104</v>
       </c>
       <c r="F121" s="4" t="s">
+        <v>658</v>
+      </c>
+      <c r="G121" s="4" t="s">
+        <v>659</v>
+      </c>
+      <c r="H121" s="4" t="s">
         <v>660</v>
-      </c>
-      <c r="G121" s="4" t="s">
-        <v>661</v>
-      </c>
-      <c r="H121" s="4" t="s">
-        <v>662</v>
       </c>
       <c r="I121" s="4" t="s">
         <v>101</v>
@@ -8430,10 +8430,10 @@
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="C122" s="5">
         <v>-4.2869089999999996</v>
@@ -8445,10 +8445,10 @@
         <v>36</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="H122" s="4" t="s">
         <v>83</v>
@@ -8457,7 +8457,7 @@
         <v>151</v>
       </c>
       <c r="J122" s="6" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="K122" s="6" t="s">
         <v>18</v>
@@ -8465,10 +8465,10 @@
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C123" s="5">
         <v>-3.372366</v>
@@ -8480,13 +8480,13 @@
         <v>176</v>
       </c>
       <c r="F123" s="4" t="s">
+        <v>667</v>
+      </c>
+      <c r="G123" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="H123" s="4" t="s">
         <v>669</v>
-      </c>
-      <c r="G123" s="4" t="s">
-        <v>670</v>
-      </c>
-      <c r="H123" s="4" t="s">
-        <v>671</v>
       </c>
       <c r="I123" s="4" t="s">
         <v>151</v>
@@ -8500,10 +8500,10 @@
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="C124" s="5">
         <v>-2.8939659999999998</v>
@@ -8515,13 +8515,13 @@
         <v>176</v>
       </c>
       <c r="F124" s="4" t="s">
+        <v>672</v>
+      </c>
+      <c r="G124" s="4" t="s">
+        <v>673</v>
+      </c>
+      <c r="H124" s="4" t="s">
         <v>674</v>
-      </c>
-      <c r="G124" s="4" t="s">
-        <v>675</v>
-      </c>
-      <c r="H124" s="4" t="s">
-        <v>676</v>
       </c>
       <c r="I124" s="4" t="s">
         <v>101</v>
@@ -8535,10 +8535,10 @@
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C125" s="5">
         <v>-4.7071329999999998</v>
@@ -8550,10 +8550,10 @@
         <v>25</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="H125" s="4" t="s">
         <v>27</v>
@@ -8570,10 +8570,10 @@
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="C126" s="5">
         <v>-4.0460330000000004</v>
@@ -8585,13 +8585,13 @@
         <v>193</v>
       </c>
       <c r="F126" s="4" t="s">
+        <v>681</v>
+      </c>
+      <c r="G126" s="4" t="s">
+        <v>682</v>
+      </c>
+      <c r="H126" s="4" t="s">
         <v>683</v>
-      </c>
-      <c r="G126" s="4" t="s">
-        <v>684</v>
-      </c>
-      <c r="H126" s="4" t="s">
-        <v>685</v>
       </c>
       <c r="I126" s="4" t="s">
         <v>101</v>
@@ -8605,10 +8605,10 @@
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="C127" s="5">
         <v>-5.5796159999999997</v>
@@ -8620,13 +8620,13 @@
         <v>193</v>
       </c>
       <c r="F127" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="G127" s="4" t="s">
+        <v>687</v>
+      </c>
+      <c r="H127" s="4" t="s">
         <v>688</v>
-      </c>
-      <c r="G127" s="4" t="s">
-        <v>689</v>
-      </c>
-      <c r="H127" s="4" t="s">
-        <v>690</v>
       </c>
       <c r="I127" s="4" t="s">
         <v>151</v>
@@ -8640,10 +8640,10 @@
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="C128" s="5">
         <v>-5.3889829999999996</v>
@@ -8652,16 +8652,16 @@
         <v>-38.911766</v>
       </c>
       <c r="E128" s="4" t="s">
+        <v>691</v>
+      </c>
+      <c r="F128" s="4" t="s">
+        <v>692</v>
+      </c>
+      <c r="G128" s="4" t="s">
         <v>693</v>
       </c>
-      <c r="F128" s="4" t="s">
+      <c r="H128" s="4" t="s">
         <v>694</v>
-      </c>
-      <c r="G128" s="4" t="s">
-        <v>695</v>
-      </c>
-      <c r="H128" s="4" t="s">
-        <v>696</v>
       </c>
       <c r="I128" s="4" t="s">
         <v>101</v>
@@ -8675,10 +8675,10 @@
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="C129" s="5">
         <v>-5.9808000000000003</v>
@@ -8687,16 +8687,16 @@
         <v>-38.884349999999998</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="F129" s="4" t="s">
+        <v>697</v>
+      </c>
+      <c r="G129" s="4" t="s">
+        <v>698</v>
+      </c>
+      <c r="H129" s="4" t="s">
         <v>699</v>
-      </c>
-      <c r="G129" s="4" t="s">
-        <v>700</v>
-      </c>
-      <c r="H129" s="4" t="s">
-        <v>701</v>
       </c>
       <c r="I129" s="4" t="s">
         <v>101</v>
@@ -8710,10 +8710,10 @@
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="C130" s="5">
         <v>-3.5994000000000002</v>
@@ -8722,16 +8722,16 @@
         <v>-38.898966000000001</v>
       </c>
       <c r="E130" s="4" t="s">
+        <v>702</v>
+      </c>
+      <c r="F130" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="G130" s="4" t="s">
         <v>704</v>
       </c>
-      <c r="F130" s="4" t="s">
+      <c r="H130" s="4" t="s">
         <v>705</v>
-      </c>
-      <c r="G130" s="4" t="s">
-        <v>706</v>
-      </c>
-      <c r="H130" s="4" t="s">
-        <v>707</v>
       </c>
       <c r="I130" s="4" t="s">
         <v>101</v>
@@ -8745,10 +8745,10 @@
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C131" s="5">
         <v>-4.1112159999999998</v>
@@ -8757,10 +8757,10 @@
         <v>-39.226599999999998</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="G131" s="4" t="s">
         <v>286</v>
@@ -8780,10 +8780,10 @@
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="C132" s="5">
         <v>-3.3707829999999999</v>
@@ -8792,16 +8792,16 @@
         <v>-39.293933000000003</v>
       </c>
       <c r="E132" s="4" t="s">
+        <v>712</v>
+      </c>
+      <c r="F132" s="4" t="s">
+        <v>713</v>
+      </c>
+      <c r="G132" s="4" t="s">
         <v>714</v>
       </c>
-      <c r="F132" s="4" t="s">
+      <c r="H132" s="4" t="s">
         <v>715</v>
-      </c>
-      <c r="G132" s="4" t="s">
-        <v>716</v>
-      </c>
-      <c r="H132" s="4" t="s">
-        <v>717</v>
       </c>
       <c r="I132" s="4" t="s">
         <v>101</v>
@@ -8815,10 +8815,10 @@
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="C133" s="5">
         <v>-5.8117999999999999</v>
@@ -8830,19 +8830,19 @@
         <v>199</v>
       </c>
       <c r="F133" s="4" t="s">
+        <v>718</v>
+      </c>
+      <c r="G133" s="4" t="s">
+        <v>719</v>
+      </c>
+      <c r="H133" s="4" t="s">
         <v>720</v>
-      </c>
-      <c r="G133" s="4" t="s">
-        <v>721</v>
-      </c>
-      <c r="H133" s="4" t="s">
-        <v>722</v>
       </c>
       <c r="I133" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J133" s="6" t="s">
-        <v>841</v>
+        <v>806</v>
       </c>
       <c r="K133" s="6" t="s">
         <v>18</v>
@@ -8850,10 +8850,10 @@
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="C134" s="5">
         <v>-3.304783</v>
@@ -8865,13 +8865,13 @@
         <v>176</v>
       </c>
       <c r="F134" s="4" t="s">
+        <v>723</v>
+      </c>
+      <c r="G134" s="4" t="s">
+        <v>724</v>
+      </c>
+      <c r="H134" s="4" t="s">
         <v>725</v>
-      </c>
-      <c r="G134" s="4" t="s">
-        <v>726</v>
-      </c>
-      <c r="H134" s="4" t="s">
-        <v>727</v>
       </c>
       <c r="I134" s="4" t="s">
         <v>101</v>
@@ -8885,10 +8885,10 @@
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="C135" s="5">
         <v>-5.1408160000000001</v>
@@ -8900,13 +8900,13 @@
         <v>268</v>
       </c>
       <c r="F135" s="4" t="s">
+        <v>728</v>
+      </c>
+      <c r="G135" s="4" t="s">
+        <v>729</v>
+      </c>
+      <c r="H135" s="4" t="s">
         <v>730</v>
-      </c>
-      <c r="G135" s="4" t="s">
-        <v>731</v>
-      </c>
-      <c r="H135" s="4" t="s">
-        <v>732</v>
       </c>
       <c r="I135" s="4" t="s">
         <v>101</v>
@@ -8920,10 +8920,10 @@
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="C136" s="5">
         <v>-3.4787659999999998</v>
@@ -8935,13 +8935,13 @@
         <v>48</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="G136" s="4" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="H136" s="4" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="I136" s="4" t="s">
         <v>101</v>
@@ -8955,10 +8955,10 @@
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="C137" s="5">
         <v>-3.5617000000000001</v>
@@ -8970,13 +8970,13 @@
         <v>243</v>
       </c>
       <c r="F137" s="4" t="s">
+        <v>737</v>
+      </c>
+      <c r="G137" s="4" t="s">
+        <v>738</v>
+      </c>
+      <c r="H137" s="4" t="s">
         <v>739</v>
-      </c>
-      <c r="G137" s="4" t="s">
-        <v>740</v>
-      </c>
-      <c r="H137" s="4" t="s">
-        <v>741</v>
       </c>
       <c r="I137" s="4" t="s">
         <v>151</v>
@@ -8990,10 +8990,10 @@
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="C138" s="5">
         <v>-5.4055679999999997</v>
@@ -9005,19 +9005,19 @@
         <v>136</v>
       </c>
       <c r="F138" s="4" t="s">
+        <v>742</v>
+      </c>
+      <c r="G138" s="4" t="s">
+        <v>743</v>
+      </c>
+      <c r="H138" s="4" t="s">
         <v>744</v>
-      </c>
-      <c r="G138" s="4" t="s">
-        <v>745</v>
-      </c>
-      <c r="H138" s="4" t="s">
-        <v>746</v>
       </c>
       <c r="I138" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J138" s="6" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="K138" s="6" t="s">
         <v>18</v>
@@ -9025,10 +9025,10 @@
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C139" s="5">
         <v>-2.9782660000000001</v>
@@ -9040,13 +9040,13 @@
         <v>176</v>
       </c>
       <c r="F139" s="4" t="s">
+        <v>747</v>
+      </c>
+      <c r="G139" s="4" t="s">
+        <v>748</v>
+      </c>
+      <c r="H139" s="4" t="s">
         <v>749</v>
-      </c>
-      <c r="G139" s="4" t="s">
-        <v>750</v>
-      </c>
-      <c r="H139" s="4" t="s">
-        <v>751</v>
       </c>
       <c r="I139" s="4" t="s">
         <v>151</v>
@@ -9060,10 +9060,10 @@
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="C140" s="5">
         <v>-2.9087830000000001</v>
@@ -9072,16 +9072,16 @@
         <v>-40.118616000000003</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="F140" s="4" t="s">
+        <v>752</v>
+      </c>
+      <c r="G140" s="4" t="s">
+        <v>753</v>
+      </c>
+      <c r="H140" s="4" t="s">
         <v>754</v>
-      </c>
-      <c r="G140" s="4" t="s">
-        <v>755</v>
-      </c>
-      <c r="H140" s="4" t="s">
-        <v>756</v>
       </c>
       <c r="I140" s="4" t="s">
         <v>101</v>
@@ -9095,10 +9095,10 @@
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="C141" s="5">
         <v>-3.697114</v>
@@ -9110,19 +9110,19 @@
         <v>48</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="G141" s="4" t="s">
         <v>51</v>
       </c>
       <c r="H141" s="4" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="I141" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J141" s="6" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="K141" s="6" t="s">
         <v>18</v>
@@ -9130,10 +9130,10 @@
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="C142" s="5">
         <v>-3.7188409999999998</v>
@@ -9145,19 +9145,19 @@
         <v>58</v>
       </c>
       <c r="F142" s="4" t="s">
+        <v>761</v>
+      </c>
+      <c r="G142" s="4" t="s">
+        <v>762</v>
+      </c>
+      <c r="H142" s="4" t="s">
         <v>763</v>
-      </c>
-      <c r="G142" s="4" t="s">
-        <v>764</v>
-      </c>
-      <c r="H142" s="4" t="s">
-        <v>765</v>
       </c>
       <c r="I142" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J142" s="6" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="K142" s="6" t="s">
         <v>18</v>
@@ -9165,10 +9165,10 @@
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="C143" s="5">
         <v>-4.0392330000000003</v>
@@ -9177,16 +9177,16 @@
         <v>-40.474150000000002</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="G143" s="4" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="H143" s="4" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="I143" s="4" t="s">
         <v>151</v>
@@ -9200,10 +9200,10 @@
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C144" s="5">
         <v>-4.1177159999999997</v>
@@ -9215,13 +9215,13 @@
         <v>210</v>
       </c>
       <c r="F144" s="4" t="s">
+        <v>770</v>
+      </c>
+      <c r="G144" s="4" t="s">
+        <v>771</v>
+      </c>
+      <c r="H144" s="4" t="s">
         <v>772</v>
-      </c>
-      <c r="G144" s="4" t="s">
-        <v>773</v>
-      </c>
-      <c r="H144" s="4" t="s">
-        <v>774</v>
       </c>
       <c r="I144" s="4" t="s">
         <v>101</v>
@@ -9235,10 +9235,10 @@
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C145" s="5">
         <v>-4.5583349999999996</v>
@@ -9247,22 +9247,22 @@
         <v>-40.729585999999998</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="F145" s="4" t="s">
+        <v>775</v>
+      </c>
+      <c r="G145" s="4" t="s">
+        <v>776</v>
+      </c>
+      <c r="H145" s="4" t="s">
         <v>777</v>
-      </c>
-      <c r="G145" s="4" t="s">
-        <v>778</v>
-      </c>
-      <c r="H145" s="4" t="s">
-        <v>779</v>
       </c>
       <c r="I145" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J145" s="6" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="K145" s="6" t="s">
         <v>18</v>
@@ -9270,10 +9270,10 @@
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="C146" s="5">
         <v>-5.1463979999999996</v>
@@ -9282,22 +9282,22 @@
         <v>-40.670636000000002</v>
       </c>
       <c r="E146" s="4" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="F146" s="4" t="s">
+        <v>780</v>
+      </c>
+      <c r="G146" s="4" t="s">
+        <v>781</v>
+      </c>
+      <c r="H146" s="4" t="s">
         <v>782</v>
-      </c>
-      <c r="G146" s="4" t="s">
-        <v>783</v>
-      </c>
-      <c r="H146" s="4" t="s">
-        <v>784</v>
       </c>
       <c r="I146" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J146" s="6" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="K146" s="6" t="s">
         <v>18</v>
@@ -9305,10 +9305,10 @@
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="C147" s="5">
         <v>-4.0631500000000003</v>
@@ -9317,16 +9317,16 @@
         <v>-40.957650000000001</v>
       </c>
       <c r="E147" s="4" t="s">
+        <v>785</v>
+      </c>
+      <c r="F147" s="4" t="s">
+        <v>786</v>
+      </c>
+      <c r="G147" s="4" t="s">
         <v>787</v>
       </c>
-      <c r="F147" s="4" t="s">
+      <c r="H147" s="4" t="s">
         <v>788</v>
-      </c>
-      <c r="G147" s="4" t="s">
-        <v>789</v>
-      </c>
-      <c r="H147" s="4" t="s">
-        <v>790</v>
       </c>
       <c r="I147" s="4" t="s">
         <v>101</v>
@@ -9340,10 +9340,10 @@
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="C148" s="5">
         <v>-3.4559829999999998</v>
@@ -9352,16 +9352,16 @@
         <v>-40.210115999999999</v>
       </c>
       <c r="E148" s="4" t="s">
+        <v>791</v>
+      </c>
+      <c r="F148" s="4" t="s">
+        <v>792</v>
+      </c>
+      <c r="G148" s="4" t="s">
         <v>793</v>
       </c>
-      <c r="F148" s="4" t="s">
+      <c r="H148" s="4" t="s">
         <v>794</v>
-      </c>
-      <c r="G148" s="4" t="s">
-        <v>795</v>
-      </c>
-      <c r="H148" s="4" t="s">
-        <v>796</v>
       </c>
       <c r="I148" s="4" t="s">
         <v>151</v>
@@ -9375,10 +9375,10 @@
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="C149" s="5">
         <v>-3.5106660000000001</v>
@@ -9387,16 +9387,16 @@
         <v>-40.385066000000002</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="F149" s="4" t="s">
+        <v>797</v>
+      </c>
+      <c r="G149" s="4" t="s">
+        <v>798</v>
+      </c>
+      <c r="H149" s="4" t="s">
         <v>799</v>
-      </c>
-      <c r="G149" s="4" t="s">
-        <v>800</v>
-      </c>
-      <c r="H149" s="4" t="s">
-        <v>801</v>
       </c>
       <c r="I149" s="4" t="s">
         <v>101</v>
@@ -9410,10 +9410,10 @@
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="C150" s="5">
         <v>-3.5546000000000002</v>
@@ -9425,13 +9425,13 @@
         <v>48</v>
       </c>
       <c r="F150" s="4" t="s">
+        <v>802</v>
+      </c>
+      <c r="G150" s="4" t="s">
+        <v>803</v>
+      </c>
+      <c r="H150" s="4" t="s">
         <v>804</v>
-      </c>
-      <c r="G150" s="4" t="s">
-        <v>805</v>
-      </c>
-      <c r="H150" s="4" t="s">
-        <v>806</v>
       </c>
       <c r="I150" s="4" t="s">
         <v>151</v>
@@ -9455,6 +9455,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D18A476-0271-4A84-BE9E-901865A86FD3}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AC157"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -9475,174 +9476,174 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="30" t="s">
+        <v>807</v>
+      </c>
+      <c r="E1" s="30"/>
+      <c r="F1" s="31" t="s">
+        <v>808</v>
+      </c>
+      <c r="G1" s="31"/>
+      <c r="H1" s="27" t="s">
         <v>809</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="30" t="s">
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
+      <c r="P1" s="27"/>
+      <c r="Q1" s="27"/>
+      <c r="R1" s="27"/>
+      <c r="S1" s="27"/>
+      <c r="T1" s="27"/>
+      <c r="U1" s="27"/>
+      <c r="V1" s="27"/>
+      <c r="W1" s="27"/>
+      <c r="X1" s="27"/>
+      <c r="Y1" s="27"/>
+      <c r="Z1" s="27"/>
+      <c r="AA1" s="27"/>
+      <c r="AB1" s="27"/>
+      <c r="AC1" s="25" t="s">
         <v>810</v>
       </c>
-      <c r="G1" s="30"/>
-      <c r="H1" s="26" t="s">
+    </row>
+    <row r="2" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="28"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="26" t="s">
         <v>811</v>
       </c>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="26"/>
-      <c r="R1" s="26"/>
-      <c r="S1" s="26"/>
-      <c r="T1" s="26"/>
-      <c r="U1" s="26"/>
-      <c r="V1" s="26"/>
-      <c r="W1" s="26"/>
-      <c r="X1" s="26"/>
-      <c r="Y1" s="26"/>
-      <c r="Z1" s="26"/>
-      <c r="AA1" s="26"/>
-      <c r="AB1" s="26"/>
-      <c r="AC1" s="24" t="s">
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="9" t="s">
         <v>812</v>
       </c>
-    </row>
-    <row r="2" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="27"/>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="25" t="s">
+      <c r="L2" s="9" t="s">
+        <v>812</v>
+      </c>
+      <c r="M2" s="27" t="s">
         <v>813</v>
       </c>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="9" t="s">
+      <c r="N2" s="27"/>
+      <c r="O2" s="27"/>
+      <c r="P2" s="27"/>
+      <c r="Q2" s="27"/>
+      <c r="R2" s="27"/>
+      <c r="S2" s="27"/>
+      <c r="T2" s="27"/>
+      <c r="U2" s="27"/>
+      <c r="V2" s="27"/>
+      <c r="W2" s="27"/>
+      <c r="X2" s="27"/>
+      <c r="Y2" s="27"/>
+      <c r="Z2" s="27"/>
+      <c r="AA2" s="27"/>
+      <c r="AB2" s="27"/>
+      <c r="AC2" s="25"/>
+    </row>
+    <row r="3" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="28"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="8" t="s">
         <v>814</v>
       </c>
-      <c r="L2" s="9" t="s">
-        <v>814</v>
-      </c>
-      <c r="M2" s="26" t="s">
+      <c r="I3" s="8" t="s">
         <v>815</v>
       </c>
-      <c r="N2" s="26"/>
-      <c r="O2" s="26"/>
-      <c r="P2" s="26"/>
-      <c r="Q2" s="26"/>
-      <c r="R2" s="26"/>
-      <c r="S2" s="26"/>
-      <c r="T2" s="26"/>
-      <c r="U2" s="26"/>
-      <c r="V2" s="26"/>
-      <c r="W2" s="26"/>
-      <c r="X2" s="26"/>
-      <c r="Y2" s="26"/>
-      <c r="Z2" s="26"/>
-      <c r="AA2" s="26"/>
-      <c r="AB2" s="26"/>
-      <c r="AC2" s="24"/>
-    </row>
-    <row r="3" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="27"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="8" t="s">
+      <c r="J3" s="8" t="s">
         <v>816</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="K3" s="7" t="s">
         <v>817</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="L3" s="7" t="s">
         <v>818</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="M3" s="7" t="s">
         <v>819</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="N3" s="7" t="s">
         <v>820</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="O3" s="7" t="s">
         <v>821</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="P3" s="7" t="s">
         <v>822</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="Q3" s="7" t="s">
         <v>823</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="R3" s="7" t="s">
         <v>824</v>
       </c>
-      <c r="Q3" s="7" t="s">
+      <c r="S3" s="7" t="s">
         <v>825</v>
       </c>
-      <c r="R3" s="7" t="s">
+      <c r="T3" s="7" t="s">
         <v>826</v>
       </c>
-      <c r="S3" s="7" t="s">
+      <c r="U3" s="7" t="s">
         <v>827</v>
       </c>
-      <c r="T3" s="7" t="s">
+      <c r="V3" s="7" t="s">
         <v>828</v>
       </c>
-      <c r="U3" s="7" t="s">
+      <c r="W3" s="7" t="s">
         <v>829</v>
       </c>
-      <c r="V3" s="7" t="s">
+      <c r="X3" s="7" t="s">
         <v>830</v>
       </c>
-      <c r="W3" s="7" t="s">
+      <c r="Y3" s="7" t="s">
         <v>831</v>
       </c>
-      <c r="X3" s="7" t="s">
+      <c r="Z3" s="7" t="s">
         <v>832</v>
       </c>
-      <c r="Y3" s="7" t="s">
+      <c r="AA3" s="7" t="s">
         <v>833</v>
       </c>
-      <c r="Z3" s="7" t="s">
+      <c r="AB3" s="7" t="s">
         <v>834</v>
       </c>
-      <c r="AA3" s="7" t="s">
-        <v>835</v>
-      </c>
-      <c r="AB3" s="7" t="s">
-        <v>836</v>
-      </c>
-      <c r="AC3" s="24"/>
+      <c r="AC3" s="25"/>
     </row>
     <row r="4" spans="1:29" ht="104.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="27"/>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
+      <c r="A4" s="28"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
       <c r="D4" s="22" t="s">
         <v>2</v>
       </c>
       <c r="E4" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
       <c r="H4" s="10"/>
       <c r="I4" s="10"/>
       <c r="J4" s="10"/>
@@ -9664,9 +9665,9 @@
       <c r="Z4" s="11"/>
       <c r="AA4" s="11"/>
       <c r="AB4" s="11"/>
-      <c r="AC4" s="24"/>
-    </row>
-    <row r="5" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AC4" s="25"/>
+    </row>
+    <row r="5" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="19" t="s">
         <v>96</v>
       </c>
@@ -9709,7 +9710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
         <v>103</v>
       </c>
@@ -9752,7 +9753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="19" t="s">
         <v>109</v>
       </c>
@@ -9795,7 +9796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="19" t="s">
         <v>114</v>
       </c>
@@ -9838,7 +9839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
         <v>120</v>
       </c>
@@ -9881,7 +9882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="19" t="s">
         <v>125</v>
       </c>
@@ -9924,7 +9925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="19" t="s">
         <v>135</v>
       </c>
@@ -10015,7 +10016,7 @@
         <v>5682</v>
       </c>
     </row>
-    <row r="12" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="19" t="s">
         <v>141</v>
       </c>
@@ -10058,15 +10059,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
         <v>147</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="D13" s="21"/>
       <c r="E13" s="21"/>
@@ -10101,7 +10102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="19" t="s">
         <v>159</v>
       </c>
@@ -10144,7 +10145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="19" t="s">
         <v>175</v>
       </c>
@@ -10187,7 +10188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="19" t="s">
         <v>182</v>
       </c>
@@ -10230,7 +10231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="19" t="s">
         <v>187</v>
       </c>
@@ -10273,7 +10274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="19" t="s">
         <v>192</v>
       </c>
@@ -10316,7 +10317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="19" t="s">
         <v>198</v>
       </c>
@@ -10359,15 +10360,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="19" t="s">
+        <v>609</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>610</v>
+      </c>
+      <c r="C20" s="19" t="s">
         <v>611</v>
-      </c>
-      <c r="B20" s="19" t="s">
-        <v>612</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>613</v>
       </c>
       <c r="D20" s="21">
         <v>-3.7752400000000002</v>
@@ -10450,15 +10451,15 @@
         <v>4245</v>
       </c>
     </row>
-    <row r="21" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="19" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B21" s="19" t="s">
         <v>210</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="D21" s="21"/>
       <c r="E21" s="21"/>
@@ -10493,15 +10494,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="19" t="s">
+        <v>620</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>621</v>
+      </c>
+      <c r="C22" s="19" t="s">
         <v>622</v>
-      </c>
-      <c r="B22" s="19" t="s">
-        <v>623</v>
-      </c>
-      <c r="C22" s="19" t="s">
-        <v>624</v>
       </c>
       <c r="D22" s="21">
         <v>-4.7911549999999998</v>
@@ -10584,15 +10585,15 @@
         <v>2038</v>
       </c>
     </row>
-    <row r="23" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="19" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B23" s="19" t="s">
         <v>417</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="D23" s="21"/>
       <c r="E23" s="21"/>
@@ -10627,15 +10628,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="19" t="s">
+        <v>631</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>632</v>
+      </c>
+      <c r="C24" s="19" t="s">
         <v>633</v>
-      </c>
-      <c r="B24" s="19" t="s">
-        <v>634</v>
-      </c>
-      <c r="C24" s="19" t="s">
-        <v>635</v>
       </c>
       <c r="D24" s="21"/>
       <c r="E24" s="21"/>
@@ -10670,15 +10671,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="19" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B25" s="19" t="s">
         <v>237</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="D25" s="21"/>
       <c r="E25" s="21"/>
@@ -10713,15 +10714,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="19" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B26" s="19" t="s">
         <v>478</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="D26" s="21"/>
       <c r="E26" s="21"/>
@@ -10756,15 +10757,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="19" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="D27" s="21"/>
       <c r="E27" s="21"/>
@@ -10799,7 +10800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="19" t="s">
         <v>204</v>
       </c>
@@ -10844,24 +10845,26 @@
     </row>
     <row r="29" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B29" s="19" t="s">
         <v>76</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>655</v>
-      </c>
-      <c r="D29" s="31" t="s">
-        <v>845</v>
-      </c>
-      <c r="E29" s="31" t="s">
-        <v>846</v>
-      </c>
-      <c r="F29" s="20"/>
+        <v>653</v>
+      </c>
+      <c r="D29" s="24" t="s">
+        <v>843</v>
+      </c>
+      <c r="E29" s="24" t="s">
+        <v>844</v>
+      </c>
+      <c r="F29" s="20">
+        <v>46139</v>
+      </c>
       <c r="G29" s="20">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>46141</v>
       </c>
       <c r="H29" s="12"/>
       <c r="I29" s="12"/>
@@ -10889,15 +10892,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B30" s="19" t="s">
         <v>104</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="D30" s="21"/>
       <c r="E30" s="21"/>
@@ -10932,15 +10935,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B31" s="19" t="s">
         <v>36</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="D31" s="21">
         <v>-4.2869089999999996</v>
@@ -11023,15 +11026,15 @@
         <v>1584</v>
       </c>
     </row>
-    <row r="32" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="B32" s="19" t="s">
         <v>176</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="D32" s="21"/>
       <c r="E32" s="21"/>
@@ -11066,15 +11069,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="B33" s="19" t="s">
         <v>176</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="D33" s="21"/>
       <c r="E33" s="21"/>
@@ -11109,15 +11112,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="19" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="B34" s="19" t="s">
         <v>25</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="D34" s="21"/>
       <c r="E34" s="21"/>
@@ -11152,15 +11155,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B35" s="19" t="s">
         <v>193</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="D35" s="21"/>
       <c r="E35" s="21"/>
@@ -11195,15 +11198,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="B36" s="19" t="s">
         <v>193</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="D36" s="21"/>
       <c r="E36" s="21"/>
@@ -11238,15 +11241,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
+        <v>690</v>
+      </c>
+      <c r="B37" s="19" t="s">
+        <v>691</v>
+      </c>
+      <c r="C37" s="19" t="s">
         <v>692</v>
-      </c>
-      <c r="B37" s="19" t="s">
-        <v>693</v>
-      </c>
-      <c r="C37" s="19" t="s">
-        <v>694</v>
       </c>
       <c r="D37" s="21"/>
       <c r="E37" s="21"/>
@@ -11281,15 +11284,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="19" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="D38" s="21"/>
       <c r="E38" s="21"/>
@@ -11324,15 +11327,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="19" t="s">
+        <v>701</v>
+      </c>
+      <c r="B39" s="19" t="s">
+        <v>702</v>
+      </c>
+      <c r="C39" s="19" t="s">
         <v>703</v>
-      </c>
-      <c r="B39" s="19" t="s">
-        <v>704</v>
-      </c>
-      <c r="C39" s="19" t="s">
-        <v>705</v>
       </c>
       <c r="D39" s="21"/>
       <c r="E39" s="21"/>
@@ -11367,15 +11370,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="19" t="s">
+        <v>707</v>
+      </c>
+      <c r="B40" s="19" t="s">
+        <v>708</v>
+      </c>
+      <c r="C40" s="19" t="s">
         <v>709</v>
-      </c>
-      <c r="B40" s="19" t="s">
-        <v>710</v>
-      </c>
-      <c r="C40" s="19" t="s">
-        <v>711</v>
       </c>
       <c r="D40" s="21"/>
       <c r="E40" s="21"/>
@@ -11410,15 +11413,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="19" t="s">
+        <v>711</v>
+      </c>
+      <c r="B41" s="19" t="s">
+        <v>712</v>
+      </c>
+      <c r="C41" s="19" t="s">
         <v>713</v>
-      </c>
-      <c r="B41" s="19" t="s">
-        <v>714</v>
-      </c>
-      <c r="C41" s="19" t="s">
-        <v>715</v>
       </c>
       <c r="D41" s="21"/>
       <c r="E41" s="21"/>
@@ -11455,60 +11458,104 @@
     </row>
     <row r="42" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="19" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="B42" s="19" t="s">
         <v>199</v>
       </c>
       <c r="C42" s="19" t="s">
-        <v>720</v>
-      </c>
-      <c r="D42" s="31" t="s">
-        <v>847</v>
-      </c>
-      <c r="E42" s="31" t="s">
-        <v>848</v>
-      </c>
-      <c r="F42" s="20"/>
+        <v>718</v>
+      </c>
+      <c r="D42" s="24" t="s">
+        <v>845</v>
+      </c>
+      <c r="E42" s="24" t="s">
+        <v>846</v>
+      </c>
+      <c r="F42" s="20">
+        <v>46139</v>
+      </c>
       <c r="G42" s="20">
         <f t="shared" si="0"/>
+        <v>46141</v>
+      </c>
+      <c r="H42" s="12">
+        <v>1221</v>
+      </c>
+      <c r="I42" s="12">
+        <v>751</v>
+      </c>
+      <c r="J42" s="12">
+        <v>15</v>
+      </c>
+      <c r="K42" s="12">
+        <v>162</v>
+      </c>
+      <c r="L42" s="12">
+        <v>50</v>
+      </c>
+      <c r="M42" s="12">
+        <v>8</v>
+      </c>
+      <c r="N42" s="12">
+        <v>3</v>
+      </c>
+      <c r="O42" s="12">
+        <v>0</v>
+      </c>
+      <c r="P42" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="12">
         <v>2</v>
       </c>
-      <c r="H42" s="12"/>
-      <c r="I42" s="12"/>
-      <c r="J42" s="12"/>
-      <c r="K42" s="12"/>
-      <c r="L42" s="12"/>
-      <c r="M42" s="12"/>
-      <c r="N42" s="12"/>
-      <c r="O42" s="12"/>
-      <c r="P42" s="12"/>
-      <c r="Q42" s="12"/>
-      <c r="R42" s="12"/>
-      <c r="S42" s="12"/>
-      <c r="T42" s="12"/>
-      <c r="U42" s="12"/>
-      <c r="V42" s="12"/>
-      <c r="W42" s="12"/>
-      <c r="X42" s="12"/>
-      <c r="Y42" s="12"/>
-      <c r="Z42" s="12"/>
-      <c r="AA42" s="12"/>
-      <c r="AB42" s="12"/>
+      <c r="R42" s="12">
+        <v>0</v>
+      </c>
+      <c r="S42" s="12">
+        <v>0</v>
+      </c>
+      <c r="T42" s="12">
+        <v>29</v>
+      </c>
+      <c r="U42" s="12">
+        <v>0</v>
+      </c>
+      <c r="V42" s="12">
+        <v>0</v>
+      </c>
+      <c r="W42" s="12">
+        <v>1</v>
+      </c>
+      <c r="X42" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="12">
+        <v>2</v>
+      </c>
+      <c r="AA42" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="12">
+        <v>0</v>
+      </c>
       <c r="AC42" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>2244</v>
+      </c>
+    </row>
+    <row r="43" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="19" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="B43" s="19" t="s">
         <v>176</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D43" s="21"/>
       <c r="E43" s="21"/>
@@ -11543,15 +11590,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="19" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="B44" s="19" t="s">
         <v>268</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="D44" s="21"/>
       <c r="E44" s="21"/>
@@ -11586,15 +11633,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="19" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="B45" s="19" t="s">
         <v>48</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="D45" s="21"/>
       <c r="E45" s="21"/>
@@ -11629,15 +11676,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="19" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="B46" s="19" t="s">
         <v>243</v>
       </c>
       <c r="C46" s="19" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="D46" s="21"/>
       <c r="E46" s="21"/>
@@ -11672,15 +11719,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="19" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="B47" s="19" t="s">
         <v>136</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="D47" s="21">
         <v>-5.4055679999999997</v>
@@ -11763,15 +11810,15 @@
         <v>2429</v>
       </c>
     </row>
-    <row r="48" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="19" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="B48" s="19" t="s">
         <v>176</v>
       </c>
       <c r="C48" s="19" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="D48" s="21"/>
       <c r="E48" s="21"/>
@@ -11806,15 +11853,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="19" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="B49" s="19" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="C49" s="19" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="D49" s="21"/>
       <c r="E49" s="21"/>
@@ -11849,15 +11896,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="19" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="B50" s="19" t="s">
         <v>48</v>
       </c>
       <c r="C50" s="19" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="D50" s="21">
         <v>-3.697114</v>
@@ -11940,15 +11987,15 @@
         <v>2483</v>
       </c>
     </row>
-    <row r="51" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="19" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="B51" s="19" t="s">
         <v>58</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="D51" s="21">
         <v>-3.7188409999999998</v>
@@ -12031,15 +12078,15 @@
         <v>4263</v>
       </c>
     </row>
-    <row r="52" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="19" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="B52" s="19" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="C52" s="19" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D52" s="21"/>
       <c r="E52" s="21"/>
@@ -12074,15 +12121,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="19" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="B53" s="19" t="s">
         <v>210</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="D53" s="21"/>
       <c r="E53" s="21"/>
@@ -12117,15 +12164,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="19" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="B54" s="19" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="C54" s="19" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="D54" s="21">
         <v>-4.5583349999999996</v>
@@ -12208,15 +12255,15 @@
         <v>1560</v>
       </c>
     </row>
-    <row r="55" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="19" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="B55" s="19" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="D55" s="21">
         <v>-5.1463979999999996</v>
@@ -12299,15 +12346,15 @@
         <v>1864</v>
       </c>
     </row>
-    <row r="56" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="19" t="s">
+        <v>784</v>
+      </c>
+      <c r="B56" s="19" t="s">
+        <v>785</v>
+      </c>
+      <c r="C56" s="19" t="s">
         <v>786</v>
-      </c>
-      <c r="B56" s="19" t="s">
-        <v>787</v>
-      </c>
-      <c r="C56" s="19" t="s">
-        <v>788</v>
       </c>
       <c r="D56" s="21"/>
       <c r="E56" s="21"/>
@@ -12342,15 +12389,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="19" t="s">
+        <v>790</v>
+      </c>
+      <c r="B57" s="19" t="s">
+        <v>791</v>
+      </c>
+      <c r="C57" s="19" t="s">
         <v>792</v>
-      </c>
-      <c r="B57" s="19" t="s">
-        <v>793</v>
-      </c>
-      <c r="C57" s="19" t="s">
-        <v>794</v>
       </c>
       <c r="D57" s="21"/>
       <c r="E57" s="21"/>
@@ -12385,15 +12432,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="19" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="B58" s="19" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="C58" s="19" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="D58" s="21"/>
       <c r="E58" s="21"/>
@@ -12428,15 +12475,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="19" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="B59" s="19" t="s">
         <v>48</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="D59" s="21"/>
       <c r="E59" s="21"/>
@@ -12471,7 +12518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="19" t="s">
         <v>317</v>
       </c>
@@ -12562,7 +12609,7 @@
         <v>2567</v>
       </c>
     </row>
-    <row r="61" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="19" t="s">
         <v>322</v>
       </c>
@@ -12605,7 +12652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="19" t="s">
         <v>327</v>
       </c>
@@ -12648,7 +12695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="19" t="s">
         <v>332</v>
       </c>
@@ -12739,7 +12786,7 @@
         <v>2906</v>
       </c>
     </row>
-    <row r="64" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="19" t="s">
         <v>337</v>
       </c>
@@ -12782,7 +12829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="19" t="s">
         <v>343</v>
       </c>
@@ -12825,7 +12872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="19" t="s">
         <v>130</v>
       </c>
@@ -12916,7 +12963,7 @@
         <v>5492</v>
       </c>
     </row>
-    <row r="67" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="19" t="s">
         <v>349</v>
       </c>
@@ -13007,7 +13054,7 @@
         <v>3330</v>
       </c>
     </row>
-    <row r="68" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="19" t="s">
         <v>353</v>
       </c>
@@ -13050,7 +13097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="19" t="s">
         <v>359</v>
       </c>
@@ -13093,7 +13140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="19" t="s">
         <v>364</v>
       </c>
@@ -13136,7 +13183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="19" t="s">
         <v>370</v>
       </c>
@@ -13179,7 +13226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="19" t="s">
         <v>376</v>
       </c>
@@ -13222,7 +13269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="19" t="s">
         <v>382</v>
       </c>
@@ -13265,7 +13312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="19" t="s">
         <v>388</v>
       </c>
@@ -13308,7 +13355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="19" t="s">
         <v>393</v>
       </c>
@@ -13351,7 +13398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="19" t="s">
         <v>399</v>
       </c>
@@ -13394,7 +13441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="19" t="s">
         <v>405</v>
       </c>
@@ -13437,7 +13484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="19" t="s">
         <v>410</v>
       </c>
@@ -13480,7 +13527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="19" t="s">
         <v>416</v>
       </c>
@@ -13523,7 +13570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="19" t="s">
         <v>422</v>
       </c>
@@ -13566,7 +13613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="19" t="s">
         <v>427</v>
       </c>
@@ -13609,7 +13656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="19" t="s">
         <v>433</v>
       </c>
@@ -13652,7 +13699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="19" t="s">
         <v>438</v>
       </c>
@@ -13743,7 +13790,7 @@
         <v>6031</v>
       </c>
     </row>
-    <row r="84" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="19" t="s">
         <v>442</v>
       </c>
@@ -13786,7 +13833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="19" t="s">
         <v>447</v>
       </c>
@@ -13829,7 +13876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="19" t="s">
         <v>453</v>
       </c>
@@ -13872,7 +13919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="19" t="s">
         <v>458</v>
       </c>
@@ -13915,7 +13962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="19" t="s">
         <v>463</v>
       </c>
@@ -14006,7 +14053,7 @@
         <v>6697</v>
       </c>
     </row>
-    <row r="89" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="19" t="s">
         <v>468</v>
       </c>
@@ -14059,44 +14106,88 @@
       <c r="C90" s="19" t="s">
         <v>475</v>
       </c>
-      <c r="D90" s="31" t="s">
-        <v>849</v>
-      </c>
-      <c r="E90" s="31" t="s">
-        <v>850</v>
-      </c>
-      <c r="F90" s="20"/>
+      <c r="D90" s="24" t="s">
+        <v>847</v>
+      </c>
+      <c r="E90" s="24" t="s">
+        <v>848</v>
+      </c>
+      <c r="F90" s="20">
+        <v>46139</v>
+      </c>
       <c r="G90" s="20">
         <f t="shared" si="3"/>
+        <v>46141</v>
+      </c>
+      <c r="H90" s="12">
+        <v>504</v>
+      </c>
+      <c r="I90" s="12">
+        <v>503</v>
+      </c>
+      <c r="J90" s="12">
+        <v>9</v>
+      </c>
+      <c r="K90" s="12">
+        <v>104</v>
+      </c>
+      <c r="L90" s="12">
+        <v>99</v>
+      </c>
+      <c r="M90" s="12">
+        <v>1</v>
+      </c>
+      <c r="N90" s="12">
+        <v>1</v>
+      </c>
+      <c r="O90" s="12">
+        <v>0</v>
+      </c>
+      <c r="P90" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q90" s="12">
         <v>2</v>
       </c>
-      <c r="H90" s="12"/>
-      <c r="I90" s="12"/>
-      <c r="J90" s="12"/>
-      <c r="K90" s="12"/>
-      <c r="L90" s="12"/>
-      <c r="M90" s="12"/>
-      <c r="N90" s="12"/>
-      <c r="O90" s="12"/>
-      <c r="P90" s="12"/>
-      <c r="Q90" s="12"/>
-      <c r="R90" s="12"/>
-      <c r="S90" s="12"/>
-      <c r="T90" s="12"/>
-      <c r="U90" s="12"/>
-      <c r="V90" s="12"/>
-      <c r="W90" s="12"/>
-      <c r="X90" s="12"/>
-      <c r="Y90" s="12"/>
-      <c r="Z90" s="12"/>
-      <c r="AA90" s="12"/>
-      <c r="AB90" s="12"/>
+      <c r="R90" s="12">
+        <v>0</v>
+      </c>
+      <c r="S90" s="12">
+        <v>2</v>
+      </c>
+      <c r="T90" s="12">
+        <v>8</v>
+      </c>
+      <c r="U90" s="12">
+        <v>0</v>
+      </c>
+      <c r="V90" s="12">
+        <v>0</v>
+      </c>
+      <c r="W90" s="12">
+        <v>0</v>
+      </c>
+      <c r="X90" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y90" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z90" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA90" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB90" s="12">
+        <v>0</v>
+      </c>
       <c r="AC90" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="91" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="19" t="s">
         <v>477</v>
       </c>
@@ -14139,7 +14230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="19" t="s">
         <v>483</v>
       </c>
@@ -14182,7 +14273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="19" t="s">
         <v>487</v>
       </c>
@@ -14225,15 +14316,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="19" t="s">
         <v>153</v>
       </c>
       <c r="B94" s="19" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C94" s="19" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="D94" s="21">
         <v>-5.0822029999999998</v>
@@ -14316,7 +14407,7 @@
         <v>2883</v>
       </c>
     </row>
-    <row r="95" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="19" t="s">
         <v>493</v>
       </c>
@@ -14369,41 +14460,85 @@
       <c r="C96" s="19" t="s">
         <v>500</v>
       </c>
-      <c r="D96" s="31" t="s">
-        <v>851</v>
-      </c>
-      <c r="E96" s="31" t="s">
-        <v>852</v>
-      </c>
-      <c r="F96" s="20"/>
+      <c r="D96" s="24" t="s">
+        <v>849</v>
+      </c>
+      <c r="E96" s="24" t="s">
+        <v>850</v>
+      </c>
+      <c r="F96" s="20">
+        <v>46139</v>
+      </c>
       <c r="G96" s="20">
         <f t="shared" si="3"/>
+        <v>46141</v>
+      </c>
+      <c r="H96" s="12">
+        <v>1483</v>
+      </c>
+      <c r="I96" s="12">
+        <v>1233</v>
+      </c>
+      <c r="J96" s="12">
+        <v>25</v>
+      </c>
+      <c r="K96" s="12">
+        <v>312</v>
+      </c>
+      <c r="L96" s="12">
+        <v>119</v>
+      </c>
+      <c r="M96" s="12">
+        <v>16</v>
+      </c>
+      <c r="N96" s="12">
+        <v>21</v>
+      </c>
+      <c r="O96" s="12">
+        <v>5</v>
+      </c>
+      <c r="P96" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="12">
+        <v>8</v>
+      </c>
+      <c r="R96" s="12">
+        <v>10</v>
+      </c>
+      <c r="S96" s="12">
         <v>2</v>
       </c>
-      <c r="H96" s="12"/>
-      <c r="I96" s="12"/>
-      <c r="J96" s="12"/>
-      <c r="K96" s="12"/>
-      <c r="L96" s="12"/>
-      <c r="M96" s="12"/>
-      <c r="N96" s="12"/>
-      <c r="O96" s="12"/>
-      <c r="P96" s="12"/>
-      <c r="Q96" s="12"/>
-      <c r="R96" s="12"/>
-      <c r="S96" s="12"/>
-      <c r="T96" s="12"/>
-      <c r="U96" s="12"/>
-      <c r="V96" s="12"/>
-      <c r="W96" s="12"/>
-      <c r="X96" s="12"/>
-      <c r="Y96" s="12"/>
-      <c r="Z96" s="12"/>
-      <c r="AA96" s="12"/>
-      <c r="AB96" s="12"/>
+      <c r="T96" s="12">
+        <v>53</v>
+      </c>
+      <c r="U96" s="12">
+        <v>2</v>
+      </c>
+      <c r="V96" s="12">
+        <v>0</v>
+      </c>
+      <c r="W96" s="12">
+        <v>2</v>
+      </c>
+      <c r="X96" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="12">
+        <v>7</v>
+      </c>
+      <c r="AA96" s="12">
+        <v>4</v>
+      </c>
+      <c r="AB96" s="12">
+        <v>5</v>
+      </c>
       <c r="AC96" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3307</v>
       </c>
     </row>
     <row r="97" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -14416,52 +14551,96 @@
       <c r="C97" s="19" t="s">
         <v>505</v>
       </c>
-      <c r="D97" s="31" t="s">
-        <v>853</v>
-      </c>
-      <c r="E97" s="31" t="s">
-        <v>854</v>
-      </c>
-      <c r="F97" s="20"/>
+      <c r="D97" s="24" t="s">
+        <v>851</v>
+      </c>
+      <c r="E97" s="24" t="s">
+        <v>852</v>
+      </c>
+      <c r="F97" s="20">
+        <v>46139</v>
+      </c>
       <c r="G97" s="20">
         <f t="shared" si="3"/>
+        <v>46141</v>
+      </c>
+      <c r="H97" s="12">
+        <v>4013</v>
+      </c>
+      <c r="I97" s="12">
+        <v>2481</v>
+      </c>
+      <c r="J97" s="12">
+        <v>36</v>
+      </c>
+      <c r="K97" s="12">
+        <v>287</v>
+      </c>
+      <c r="L97" s="12">
+        <v>93</v>
+      </c>
+      <c r="M97" s="12">
+        <v>11</v>
+      </c>
+      <c r="N97" s="12">
+        <v>34</v>
+      </c>
+      <c r="O97" s="12">
+        <v>1</v>
+      </c>
+      <c r="P97" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="12">
+        <v>7</v>
+      </c>
+      <c r="R97" s="12">
+        <v>4</v>
+      </c>
+      <c r="S97" s="12">
         <v>2</v>
       </c>
-      <c r="H97" s="12"/>
-      <c r="I97" s="12"/>
-      <c r="J97" s="12"/>
-      <c r="K97" s="12"/>
-      <c r="L97" s="12"/>
-      <c r="M97" s="12"/>
-      <c r="N97" s="12"/>
-      <c r="O97" s="12"/>
-      <c r="P97" s="12"/>
-      <c r="Q97" s="12"/>
-      <c r="R97" s="12"/>
-      <c r="S97" s="12"/>
-      <c r="T97" s="12"/>
-      <c r="U97" s="12"/>
-      <c r="V97" s="12"/>
-      <c r="W97" s="12"/>
-      <c r="X97" s="12"/>
-      <c r="Y97" s="12"/>
-      <c r="Z97" s="12"/>
-      <c r="AA97" s="12"/>
-      <c r="AB97" s="12"/>
+      <c r="T97" s="12">
+        <v>85</v>
+      </c>
+      <c r="U97" s="12">
+        <v>0</v>
+      </c>
+      <c r="V97" s="12">
+        <v>0</v>
+      </c>
+      <c r="W97" s="12">
+        <v>1</v>
+      </c>
+      <c r="X97" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z97" s="12">
+        <v>4</v>
+      </c>
+      <c r="AA97" s="12">
+        <v>2</v>
+      </c>
+      <c r="AB97" s="12">
+        <v>2</v>
+      </c>
       <c r="AC97" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>7063</v>
+      </c>
+    </row>
+    <row r="98" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="19" t="s">
+        <v>507</v>
+      </c>
+      <c r="B98" s="19" t="s">
+        <v>508</v>
+      </c>
+      <c r="C98" s="19" t="s">
         <v>509</v>
-      </c>
-      <c r="B98" s="19" t="s">
-        <v>510</v>
-      </c>
-      <c r="C98" s="19" t="s">
-        <v>511</v>
       </c>
       <c r="D98" s="21"/>
       <c r="E98" s="21"/>
@@ -14496,15 +14675,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="19" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B99" s="19" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C99" s="19" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="D99" s="21"/>
       <c r="E99" s="21"/>
@@ -14539,15 +14718,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="19" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B100" s="19" t="s">
         <v>383</v>
       </c>
       <c r="C100" s="19" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="D100" s="21"/>
       <c r="E100" s="21"/>
@@ -14582,15 +14761,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="19" t="s">
+        <v>523</v>
+      </c>
+      <c r="B101" s="19" t="s">
+        <v>524</v>
+      </c>
+      <c r="C101" s="19" t="s">
         <v>525</v>
-      </c>
-      <c r="B101" s="19" t="s">
-        <v>526</v>
-      </c>
-      <c r="C101" s="19" t="s">
-        <v>527</v>
       </c>
       <c r="D101" s="21"/>
       <c r="E101" s="21"/>
@@ -14625,15 +14804,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="19" t="s">
+        <v>529</v>
+      </c>
+      <c r="B102" s="19" t="s">
+        <v>530</v>
+      </c>
+      <c r="C102" s="19" t="s">
         <v>531</v>
-      </c>
-      <c r="B102" s="19" t="s">
-        <v>532</v>
-      </c>
-      <c r="C102" s="19" t="s">
-        <v>533</v>
       </c>
       <c r="D102" s="21"/>
       <c r="E102" s="21"/>
@@ -14668,7 +14847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="19" t="s">
         <v>164</v>
       </c>
@@ -14676,7 +14855,7 @@
         <v>165</v>
       </c>
       <c r="C103" s="19" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="D103" s="21">
         <v>-4.8596729999999999</v>
@@ -14759,15 +14938,15 @@
         <v>2499</v>
       </c>
     </row>
-    <row r="104" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="19" t="s">
+        <v>535</v>
+      </c>
+      <c r="B104" s="19" t="s">
+        <v>536</v>
+      </c>
+      <c r="C104" s="19" t="s">
         <v>537</v>
-      </c>
-      <c r="B104" s="19" t="s">
-        <v>538</v>
-      </c>
-      <c r="C104" s="19" t="s">
-        <v>539</v>
       </c>
       <c r="D104" s="21">
         <v>-4.4447369999999999</v>
@@ -14850,15 +15029,15 @@
         <v>2533</v>
       </c>
     </row>
-    <row r="105" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="19" t="s">
+        <v>541</v>
+      </c>
+      <c r="B105" s="19" t="s">
+        <v>542</v>
+      </c>
+      <c r="C105" s="19" t="s">
         <v>543</v>
-      </c>
-      <c r="B105" s="19" t="s">
-        <v>544</v>
-      </c>
-      <c r="C105" s="19" t="s">
-        <v>545</v>
       </c>
       <c r="D105" s="21">
         <v>-5.1705110000000003</v>
@@ -14941,15 +15120,15 @@
         <v>2124</v>
       </c>
     </row>
-    <row r="106" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="19" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B106" s="19" t="s">
         <v>494</v>
       </c>
       <c r="C106" s="19" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="D106" s="21"/>
       <c r="E106" s="21"/>
@@ -14984,15 +15163,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="19" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B107" s="19" t="s">
         <v>360</v>
       </c>
       <c r="C107" s="19" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="D107" s="21"/>
       <c r="E107" s="21"/>
@@ -15027,7 +15206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="19" t="s">
         <v>170</v>
       </c>
@@ -15070,15 +15249,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="19" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B109" s="19" t="s">
         <v>42</v>
       </c>
       <c r="C109" s="19" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="D109" s="21"/>
       <c r="E109" s="21"/>
@@ -15113,15 +15292,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="19" t="s">
+        <v>561</v>
+      </c>
+      <c r="B110" s="19" t="s">
+        <v>562</v>
+      </c>
+      <c r="C110" s="19" t="s">
         <v>563</v>
-      </c>
-      <c r="B110" s="19" t="s">
-        <v>564</v>
-      </c>
-      <c r="C110" s="19" t="s">
-        <v>565</v>
       </c>
       <c r="D110" s="21">
         <v>-3.6978119999999999</v>
@@ -15204,15 +15383,15 @@
         <v>5171</v>
       </c>
     </row>
-    <row r="111" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="19" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B111" s="19" t="s">
         <v>210</v>
       </c>
       <c r="C111" s="19" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="D111" s="21">
         <v>-5.2113269999999998</v>
@@ -15295,15 +15474,15 @@
         <v>5543</v>
       </c>
     </row>
-    <row r="112" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="19" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B112" s="19" t="s">
         <v>210</v>
       </c>
       <c r="C112" s="19" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="D112" s="21">
         <v>-4.3822749999999999</v>
@@ -15386,15 +15565,15 @@
         <v>4135</v>
       </c>
     </row>
-    <row r="113" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="19" t="s">
+        <v>577</v>
+      </c>
+      <c r="B113" s="19" t="s">
+        <v>578</v>
+      </c>
+      <c r="C113" s="19" t="s">
         <v>579</v>
-      </c>
-      <c r="B113" s="19" t="s">
-        <v>580</v>
-      </c>
-      <c r="C113" s="19" t="s">
-        <v>581</v>
       </c>
       <c r="D113" s="21"/>
       <c r="E113" s="21"/>
@@ -15429,15 +15608,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="19" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B114" s="19" t="s">
         <v>494</v>
       </c>
       <c r="C114" s="19" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="D114" s="21"/>
       <c r="E114" s="21"/>
@@ -15472,15 +15651,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="19" t="s">
+        <v>588</v>
+      </c>
+      <c r="B115" s="19" t="s">
+        <v>589</v>
+      </c>
+      <c r="C115" s="19" t="s">
         <v>590</v>
-      </c>
-      <c r="B115" s="19" t="s">
-        <v>591</v>
-      </c>
-      <c r="C115" s="19" t="s">
-        <v>592</v>
       </c>
       <c r="D115" s="21"/>
       <c r="E115" s="21"/>
@@ -15515,15 +15694,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="19" t="s">
+        <v>594</v>
+      </c>
+      <c r="B116" s="19" t="s">
+        <v>595</v>
+      </c>
+      <c r="C116" s="19" t="s">
         <v>596</v>
-      </c>
-      <c r="B116" s="19" t="s">
-        <v>597</v>
-      </c>
-      <c r="C116" s="19" t="s">
-        <v>598</v>
       </c>
       <c r="D116" s="21"/>
       <c r="E116" s="21"/>
@@ -15558,15 +15737,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="19" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B117" s="19" t="s">
         <v>142</v>
       </c>
       <c r="C117" s="19" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="D117" s="21"/>
       <c r="E117" s="21"/>
@@ -15601,15 +15780,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="19" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B118" s="19" t="s">
         <v>104</v>
       </c>
       <c r="C118" s="19" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="D118" s="21"/>
       <c r="E118" s="21"/>
@@ -15644,7 +15823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="19" t="s">
         <v>11</v>
       </c>
@@ -15735,7 +15914,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="120" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="19" t="s">
         <v>20</v>
       </c>
@@ -15826,7 +16005,7 @@
         <v>1773</v>
       </c>
     </row>
-    <row r="121" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="19" t="s">
         <v>24</v>
       </c>
@@ -15869,7 +16048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="19" t="s">
         <v>30</v>
       </c>
@@ -15960,7 +16139,7 @@
         <v>4915</v>
       </c>
     </row>
-    <row r="123" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="19" t="s">
         <v>35</v>
       </c>
@@ -16003,7 +16182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="19" t="s">
         <v>41</v>
       </c>
@@ -16046,7 +16225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="19" t="s">
         <v>63</v>
       </c>
@@ -16089,7 +16268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="19" t="s">
         <v>69</v>
       </c>
@@ -16132,7 +16311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="19" t="s">
         <v>215</v>
       </c>
@@ -16175,7 +16354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="19" t="s">
         <v>267</v>
       </c>
@@ -16218,7 +16397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="19" t="s">
         <v>273</v>
       </c>
@@ -16261,7 +16440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="19" t="s">
         <v>279</v>
       </c>
@@ -16352,7 +16531,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="131" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="19" t="s">
         <v>284</v>
       </c>
@@ -16443,7 +16622,7 @@
         <v>1984</v>
       </c>
     </row>
-    <row r="132" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="19" t="s">
         <v>81</v>
       </c>
@@ -16534,7 +16713,7 @@
         <v>2597</v>
       </c>
     </row>
-    <row r="133" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="19" t="s">
         <v>86</v>
       </c>
@@ -16625,7 +16804,7 @@
         <v>1733</v>
       </c>
     </row>
-    <row r="134" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="19" t="s">
         <v>92</v>
       </c>
@@ -16716,7 +16895,7 @@
         <v>1724</v>
       </c>
     </row>
-    <row r="135" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="19" t="s">
         <v>289</v>
       </c>
@@ -16759,7 +16938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="19" t="s">
         <v>294</v>
       </c>
@@ -16802,7 +16981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="19" t="s">
         <v>47</v>
       </c>
@@ -16845,7 +17024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="19" t="s">
         <v>53</v>
       </c>
@@ -16888,7 +17067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="19" t="s">
         <v>57</v>
       </c>
@@ -16931,7 +17110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="19" t="s">
         <v>75</v>
       </c>
@@ -17022,7 +17201,7 @@
         <v>1839</v>
       </c>
     </row>
-    <row r="141" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="19" t="s">
         <v>209</v>
       </c>
@@ -17113,7 +17292,7 @@
         <v>2840</v>
       </c>
     </row>
-    <row r="142" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="19" t="s">
         <v>220</v>
       </c>
@@ -17204,7 +17383,7 @@
         <v>1451</v>
       </c>
     </row>
-    <row r="143" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="19" t="s">
         <v>225</v>
       </c>
@@ -17247,7 +17426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="19" t="s">
         <v>230</v>
       </c>
@@ -17338,7 +17517,7 @@
         <v>2854</v>
       </c>
     </row>
-    <row r="145" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="19" t="s">
         <v>236</v>
       </c>
@@ -17381,7 +17560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="19" t="s">
         <v>242</v>
       </c>
@@ -17424,7 +17603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="19" t="s">
         <v>248</v>
       </c>
@@ -17467,7 +17646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="19" t="s">
         <v>253</v>
       </c>
@@ -17510,7 +17689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="19" t="s">
         <v>258</v>
       </c>
@@ -17553,7 +17732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="19" t="s">
         <v>263</v>
       </c>
@@ -17596,7 +17775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="19" t="s">
         <v>300</v>
       </c>
@@ -17639,7 +17818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="19" t="s">
         <v>305</v>
       </c>
@@ -17730,7 +17909,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="153" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="19" t="s">
         <v>312</v>
       </c>
@@ -17793,6 +17972,15 @@
     </row>
   </sheetData>
   <autoFilter ref="A4:AC153" xr:uid="{1D18A476-0271-4A84-BE9E-901865A86FD3}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="P 149"/>
+        <filter val="P 156"/>
+        <filter val="P 157"/>
+        <filter val="P 42"/>
+        <filter val="P 71"/>
+      </filters>
+    </filterColumn>
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="9">

--- a/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
+++ b/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7E65608-F8F6-4901-A848-AE2EDE7C1858}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EB81150-4FD5-40E4-B7D6-BE2E137210E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
   </bookViews>
   <sheets>
     <sheet name="LISTA DE PONTOS" sheetId="1" r:id="rId1"/>
@@ -4173,7 +4173,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DA12617-6B17-4A0E-9E79-EBA6E19B3138}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K150"/>
@@ -4228,7 +4228,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -4263,7 +4263,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>19</v>
       </c>
@@ -4298,7 +4298,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>23</v>
       </c>
@@ -4333,7 +4333,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>29</v>
       </c>
@@ -4368,7 +4368,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>34</v>
       </c>
@@ -4403,7 +4403,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>40</v>
       </c>
@@ -4438,7 +4438,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>46</v>
       </c>
@@ -4473,7 +4473,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>52</v>
       </c>
@@ -4508,7 +4508,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>56</v>
       </c>
@@ -4543,7 +4543,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>62</v>
       </c>
@@ -4578,7 +4578,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>68</v>
       </c>
@@ -4613,7 +4613,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>74</v>
       </c>
@@ -4648,7 +4648,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>208</v>
       </c>
@@ -4683,7 +4683,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>214</v>
       </c>
@@ -4718,7 +4718,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>219</v>
       </c>
@@ -4753,7 +4753,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>224</v>
       </c>
@@ -4788,7 +4788,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>229</v>
       </c>
@@ -4823,7 +4823,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>235</v>
       </c>
@@ -4858,7 +4858,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>241</v>
       </c>
@@ -4893,7 +4893,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>247</v>
       </c>
@@ -4928,7 +4928,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>252</v>
       </c>
@@ -4963,7 +4963,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>257</v>
       </c>
@@ -4998,7 +4998,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>262</v>
       </c>
@@ -5033,7 +5033,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>266</v>
       </c>
@@ -5068,7 +5068,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>272</v>
       </c>
@@ -5103,7 +5103,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>278</v>
       </c>
@@ -5138,7 +5138,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>283</v>
       </c>
@@ -5173,7 +5173,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>80</v>
       </c>
@@ -5208,7 +5208,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>85</v>
       </c>
@@ -5243,7 +5243,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>91</v>
       </c>
@@ -5278,7 +5278,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>288</v>
       </c>
@@ -5313,7 +5313,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>293</v>
       </c>
@@ -5348,7 +5348,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>299</v>
       </c>
@@ -5383,7 +5383,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>304</v>
       </c>
@@ -5418,7 +5418,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>311</v>
       </c>
@@ -5453,7 +5453,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>95</v>
       </c>
@@ -5488,7 +5488,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>102</v>
       </c>
@@ -5523,7 +5523,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>108</v>
       </c>
@@ -5558,7 +5558,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>113</v>
       </c>
@@ -5593,7 +5593,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>119</v>
       </c>
@@ -5628,7 +5628,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>124</v>
       </c>
@@ -5663,7 +5663,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>316</v>
       </c>
@@ -5698,7 +5698,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>321</v>
       </c>
@@ -5733,7 +5733,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>326</v>
       </c>
@@ -5768,7 +5768,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>331</v>
       </c>
@@ -5803,7 +5803,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>336</v>
       </c>
@@ -5838,7 +5838,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>342</v>
       </c>
@@ -5873,7 +5873,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>129</v>
       </c>
@@ -5908,7 +5908,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>134</v>
       </c>
@@ -5943,7 +5943,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>348</v>
       </c>
@@ -5978,7 +5978,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>352</v>
       </c>
@@ -6013,7 +6013,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>358</v>
       </c>
@@ -6048,7 +6048,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>363</v>
       </c>
@@ -6083,7 +6083,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>369</v>
       </c>
@@ -6118,7 +6118,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>140</v>
       </c>
@@ -6153,7 +6153,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>375</v>
       </c>
@@ -6188,7 +6188,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>381</v>
       </c>
@@ -6223,7 +6223,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>146</v>
       </c>
@@ -6258,7 +6258,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>387</v>
       </c>
@@ -6293,7 +6293,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>392</v>
       </c>
@@ -6328,7 +6328,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>398</v>
       </c>
@@ -6363,7 +6363,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>404</v>
       </c>
@@ -6398,7 +6398,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>409</v>
       </c>
@@ -6433,7 +6433,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>415</v>
       </c>
@@ -6468,7 +6468,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>421</v>
       </c>
@@ -6503,7 +6503,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>426</v>
       </c>
@@ -6538,7 +6538,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>432</v>
       </c>
@@ -6573,7 +6573,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>437</v>
       </c>
@@ -6608,7 +6608,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>441</v>
       </c>
@@ -6643,7 +6643,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>446</v>
       </c>
@@ -6678,7 +6678,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>452</v>
       </c>
@@ -6713,7 +6713,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>457</v>
       </c>
@@ -6748,7 +6748,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>462</v>
       </c>
@@ -6783,7 +6783,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>467</v>
       </c>
@@ -6818,7 +6818,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>472</v>
       </c>
@@ -6853,7 +6853,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>476</v>
       </c>
@@ -6888,7 +6888,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>482</v>
       </c>
@@ -6931,10 +6931,10 @@
         <v>487</v>
       </c>
       <c r="C79" s="5">
-        <v>-4.761266</v>
+        <v>-4.7611049999999997</v>
       </c>
       <c r="D79" s="5">
-        <v>-39.490850000000002</v>
+        <v>-39.487011000000003</v>
       </c>
       <c r="E79" s="4" t="s">
         <v>488</v>
@@ -6958,7 +6958,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>152</v>
       </c>
@@ -6993,7 +6993,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>492</v>
       </c>
@@ -7028,7 +7028,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>498</v>
       </c>
@@ -7063,7 +7063,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>503</v>
       </c>
@@ -7098,7 +7098,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>506</v>
       </c>
@@ -7133,7 +7133,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>512</v>
       </c>
@@ -7176,10 +7176,10 @@
         <v>159</v>
       </c>
       <c r="C86" s="5">
-        <v>-5.215166</v>
+        <v>-5.2102599999999999</v>
       </c>
       <c r="D86" s="5">
-        <v>-39.319133000000001</v>
+        <v>-39.316634000000001</v>
       </c>
       <c r="E86" s="4" t="s">
         <v>76</v>
@@ -7203,7 +7203,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>517</v>
       </c>
@@ -7238,7 +7238,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>522</v>
       </c>
@@ -7273,7 +7273,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>528</v>
       </c>
@@ -7308,7 +7308,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>163</v>
       </c>
@@ -7343,7 +7343,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>534</v>
       </c>
@@ -7378,7 +7378,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>540</v>
       </c>
@@ -7413,7 +7413,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>546</v>
       </c>
@@ -7448,7 +7448,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>551</v>
       </c>
@@ -7491,10 +7491,10 @@
         <v>170</v>
       </c>
       <c r="C95" s="5">
-        <v>-5.172466</v>
+        <v>-5.1756060000000002</v>
       </c>
       <c r="D95" s="5">
-        <v>-39.305799999999998</v>
+        <v>-39.305515999999997</v>
       </c>
       <c r="E95" s="4" t="s">
         <v>12</v>
@@ -7518,7 +7518,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>556</v>
       </c>
@@ -7553,7 +7553,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>560</v>
       </c>
@@ -7588,7 +7588,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>566</v>
       </c>
@@ -7623,7 +7623,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>571</v>
       </c>
@@ -7658,7 +7658,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>576</v>
       </c>
@@ -7693,7 +7693,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>582</v>
       </c>
@@ -7728,7 +7728,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>587</v>
       </c>
@@ -7763,7 +7763,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>593</v>
       </c>
@@ -7798,7 +7798,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>598</v>
       </c>
@@ -7833,7 +7833,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>603</v>
       </c>
@@ -7868,7 +7868,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>174</v>
       </c>
@@ -7903,7 +7903,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>181</v>
       </c>
@@ -7938,7 +7938,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>186</v>
       </c>
@@ -7973,7 +7973,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>191</v>
       </c>
@@ -8016,10 +8016,10 @@
         <v>198</v>
       </c>
       <c r="C110" s="5">
-        <v>-5.214283</v>
+        <v>-5.2116600000000002</v>
       </c>
       <c r="D110" s="5">
-        <v>-39.311549999999997</v>
+        <v>-39.312789000000002</v>
       </c>
       <c r="E110" s="4" t="s">
         <v>199</v>
@@ -8043,7 +8043,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>608</v>
       </c>
@@ -8078,7 +8078,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>614</v>
       </c>
@@ -8113,7 +8113,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>619</v>
       </c>
@@ -8148,7 +8148,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>625</v>
       </c>
@@ -8183,7 +8183,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>630</v>
       </c>
@@ -8218,7 +8218,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>636</v>
       </c>
@@ -8253,7 +8253,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>641</v>
       </c>
@@ -8288,7 +8288,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>646</v>
       </c>
@@ -8331,10 +8331,10 @@
         <v>204</v>
       </c>
       <c r="C119" s="5">
-        <v>-5.1908500000000002</v>
+        <v>-5.1876949999999997</v>
       </c>
       <c r="D119" s="5">
-        <v>-39.270350000000001</v>
+        <v>-39.270508</v>
       </c>
       <c r="E119" s="4" t="s">
         <v>76</v>
@@ -8358,7 +8358,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>651</v>
       </c>
@@ -8387,13 +8387,13 @@
         <v>101</v>
       </c>
       <c r="J120" s="6" t="s">
-        <v>839</v>
+        <v>806</v>
       </c>
       <c r="K120" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>656</v>
       </c>
@@ -8428,7 +8428,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>661</v>
       </c>
@@ -8463,7 +8463,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>665</v>
       </c>
@@ -8498,7 +8498,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>670</v>
       </c>
@@ -8533,7 +8533,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>675</v>
       </c>
@@ -8568,7 +8568,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>679</v>
       </c>
@@ -8603,7 +8603,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>684</v>
       </c>
@@ -8638,7 +8638,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>689</v>
       </c>
@@ -8673,7 +8673,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>695</v>
       </c>
@@ -8708,7 +8708,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>700</v>
       </c>
@@ -8743,7 +8743,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>706</v>
       </c>
@@ -8778,7 +8778,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>710</v>
       </c>
@@ -8813,7 +8813,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>716</v>
       </c>
@@ -8848,7 +8848,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>721</v>
       </c>
@@ -8883,7 +8883,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>726</v>
       </c>
@@ -8918,7 +8918,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>731</v>
       </c>
@@ -8953,7 +8953,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>735</v>
       </c>
@@ -8988,7 +8988,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>740</v>
       </c>
@@ -9023,7 +9023,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>745</v>
       </c>
@@ -9058,7 +9058,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>750</v>
       </c>
@@ -9093,7 +9093,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>755</v>
       </c>
@@ -9128,7 +9128,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>759</v>
       </c>
@@ -9163,7 +9163,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>764</v>
       </c>
@@ -9198,7 +9198,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>768</v>
       </c>
@@ -9233,7 +9233,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>773</v>
       </c>
@@ -9268,7 +9268,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>778</v>
       </c>
@@ -9303,7 +9303,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>783</v>
       </c>
@@ -9338,7 +9338,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>789</v>
       </c>
@@ -9373,7 +9373,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>795</v>
       </c>
@@ -9408,7 +9408,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>800</v>
       </c>
@@ -9444,18 +9444,27 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K150" xr:uid="{4DA12617-6B17-4A0E-9E79-EBA6E19B3138}"/>
+  <autoFilter ref="A1:K150" xr:uid="{4DA12617-6B17-4A0E-9E79-EBA6E19B3138}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="-4,761105°"/>
+        <filter val="-5,175606°"/>
+        <filter val="-5,187695°"/>
+        <filter val="-5,210260°"/>
+        <filter val="-5,211660°"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K150">
     <sortCondition ref="B1:B150"/>
   </sortState>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="20" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="65" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D18A476-0271-4A84-BE9E-901865A86FD3}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AC157"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -9667,7 +9676,7 @@
       <c r="AB4" s="11"/>
       <c r="AC4" s="25"/>
     </row>
-    <row r="5" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="19" t="s">
         <v>96</v>
       </c>
@@ -9710,7 +9719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
         <v>103</v>
       </c>
@@ -9753,7 +9762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="19" t="s">
         <v>109</v>
       </c>
@@ -9796,7 +9805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="19" t="s">
         <v>114</v>
       </c>
@@ -9839,7 +9848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
         <v>120</v>
       </c>
@@ -9882,7 +9891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="19" t="s">
         <v>125</v>
       </c>
@@ -9925,7 +9934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="19" t="s">
         <v>135</v>
       </c>
@@ -10016,7 +10025,7 @@
         <v>5682</v>
       </c>
     </row>
-    <row r="12" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="19" t="s">
         <v>141</v>
       </c>
@@ -10059,7 +10068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
         <v>147</v>
       </c>
@@ -10102,7 +10111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="19" t="s">
         <v>159</v>
       </c>
@@ -10145,7 +10154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="19" t="s">
         <v>175</v>
       </c>
@@ -10188,7 +10197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="19" t="s">
         <v>182</v>
       </c>
@@ -10231,7 +10240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="19" t="s">
         <v>187</v>
       </c>
@@ -10274,7 +10283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="19" t="s">
         <v>192</v>
       </c>
@@ -10317,7 +10326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="19" t="s">
         <v>198</v>
       </c>
@@ -10360,7 +10369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="19" t="s">
         <v>609</v>
       </c>
@@ -10451,7 +10460,7 @@
         <v>4245</v>
       </c>
     </row>
-    <row r="21" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="19" t="s">
         <v>615</v>
       </c>
@@ -10494,7 +10503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="19" t="s">
         <v>620</v>
       </c>
@@ -10585,7 +10594,7 @@
         <v>2038</v>
       </c>
     </row>
-    <row r="23" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="19" t="s">
         <v>626</v>
       </c>
@@ -10628,7 +10637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="19" t="s">
         <v>631</v>
       </c>
@@ -10671,7 +10680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="19" t="s">
         <v>637</v>
       </c>
@@ -10714,7 +10723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="19" t="s">
         <v>642</v>
       </c>
@@ -10757,7 +10766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="19" t="s">
         <v>647</v>
       </c>
@@ -10800,7 +10809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="19" t="s">
         <v>204</v>
       </c>
@@ -10866,33 +10875,75 @@
         <f t="shared" si="0"/>
         <v>46141</v>
       </c>
-      <c r="H29" s="12"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="12"/>
-      <c r="M29" s="12"/>
-      <c r="N29" s="12"/>
-      <c r="O29" s="12"/>
-      <c r="P29" s="12"/>
-      <c r="Q29" s="12"/>
-      <c r="R29" s="12"/>
-      <c r="S29" s="12"/>
-      <c r="T29" s="12"/>
-      <c r="U29" s="12"/>
-      <c r="V29" s="12"/>
-      <c r="W29" s="12"/>
-      <c r="X29" s="12"/>
-      <c r="Y29" s="12"/>
-      <c r="Z29" s="12"/>
-      <c r="AA29" s="12"/>
-      <c r="AB29" s="12"/>
+      <c r="H29" s="12">
+        <v>323</v>
+      </c>
+      <c r="I29" s="12">
+        <v>1612</v>
+      </c>
+      <c r="J29" s="12">
+        <v>32</v>
+      </c>
+      <c r="K29" s="12">
+        <v>227</v>
+      </c>
+      <c r="L29" s="12">
+        <v>77</v>
+      </c>
+      <c r="M29" s="12">
+        <v>11</v>
+      </c>
+      <c r="N29" s="12">
+        <v>10</v>
+      </c>
+      <c r="O29" s="12">
+        <v>3</v>
+      </c>
+      <c r="P29" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="12">
+        <v>4</v>
+      </c>
+      <c r="R29" s="12">
+        <v>1</v>
+      </c>
+      <c r="S29" s="12">
+        <v>1</v>
+      </c>
+      <c r="T29" s="12">
+        <v>14</v>
+      </c>
+      <c r="U29" s="12">
+        <v>1</v>
+      </c>
+      <c r="V29" s="12">
+        <v>0</v>
+      </c>
+      <c r="W29" s="12">
+        <v>0</v>
+      </c>
+      <c r="X29" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="12">
+        <v>0</v>
+      </c>
       <c r="AC29" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>2316</v>
+      </c>
+    </row>
+    <row r="30" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
         <v>657</v>
       </c>
@@ -10935,7 +10986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
         <v>662</v>
       </c>
@@ -11026,7 +11077,7 @@
         <v>1584</v>
       </c>
     </row>
-    <row r="32" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
         <v>666</v>
       </c>
@@ -11069,7 +11120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
         <v>671</v>
       </c>
@@ -11112,7 +11163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="19" t="s">
         <v>676</v>
       </c>
@@ -11155,7 +11206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
         <v>680</v>
       </c>
@@ -11198,7 +11249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
         <v>685</v>
       </c>
@@ -11241,7 +11292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
         <v>690</v>
       </c>
@@ -11284,7 +11335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="19" t="s">
         <v>696</v>
       </c>
@@ -11327,7 +11378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="19" t="s">
         <v>701</v>
       </c>
@@ -11370,7 +11421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="19" t="s">
         <v>707</v>
       </c>
@@ -11413,7 +11464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="19" t="s">
         <v>711</v>
       </c>
@@ -11547,7 +11598,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="43" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="19" t="s">
         <v>722</v>
       </c>
@@ -11590,7 +11641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="19" t="s">
         <v>727</v>
       </c>
@@ -11633,7 +11684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="19" t="s">
         <v>732</v>
       </c>
@@ -11676,7 +11727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="19" t="s">
         <v>736</v>
       </c>
@@ -11719,7 +11770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="19" t="s">
         <v>741</v>
       </c>
@@ -11810,7 +11861,7 @@
         <v>2429</v>
       </c>
     </row>
-    <row r="48" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="19" t="s">
         <v>746</v>
       </c>
@@ -11853,7 +11904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="19" t="s">
         <v>751</v>
       </c>
@@ -11896,7 +11947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="19" t="s">
         <v>756</v>
       </c>
@@ -11987,7 +12038,7 @@
         <v>2483</v>
       </c>
     </row>
-    <row r="51" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="19" t="s">
         <v>760</v>
       </c>
@@ -12078,7 +12129,7 @@
         <v>4263</v>
       </c>
     </row>
-    <row r="52" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="19" t="s">
         <v>765</v>
       </c>
@@ -12121,7 +12172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="19" t="s">
         <v>769</v>
       </c>
@@ -12164,7 +12215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="19" t="s">
         <v>774</v>
       </c>
@@ -12255,7 +12306,7 @@
         <v>1560</v>
       </c>
     </row>
-    <row r="55" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="19" t="s">
         <v>779</v>
       </c>
@@ -12346,7 +12397,7 @@
         <v>1864</v>
       </c>
     </row>
-    <row r="56" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="19" t="s">
         <v>784</v>
       </c>
@@ -12389,7 +12440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="19" t="s">
         <v>790</v>
       </c>
@@ -12432,7 +12483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="19" t="s">
         <v>796</v>
       </c>
@@ -12475,7 +12526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="19" t="s">
         <v>801</v>
       </c>
@@ -12518,7 +12569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="19" t="s">
         <v>317</v>
       </c>
@@ -12609,7 +12660,7 @@
         <v>2567</v>
       </c>
     </row>
-    <row r="61" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="19" t="s">
         <v>322</v>
       </c>
@@ -12652,7 +12703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="19" t="s">
         <v>327</v>
       </c>
@@ -12695,7 +12746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="19" t="s">
         <v>332</v>
       </c>
@@ -12786,7 +12837,7 @@
         <v>2906</v>
       </c>
     </row>
-    <row r="64" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="19" t="s">
         <v>337</v>
       </c>
@@ -12829,7 +12880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="19" t="s">
         <v>343</v>
       </c>
@@ -12872,7 +12923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="19" t="s">
         <v>130</v>
       </c>
@@ -12963,7 +13014,7 @@
         <v>5492</v>
       </c>
     </row>
-    <row r="67" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="19" t="s">
         <v>349</v>
       </c>
@@ -13054,7 +13105,7 @@
         <v>3330</v>
       </c>
     </row>
-    <row r="68" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="19" t="s">
         <v>353</v>
       </c>
@@ -13097,7 +13148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="19" t="s">
         <v>359</v>
       </c>
@@ -13140,7 +13191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="19" t="s">
         <v>364</v>
       </c>
@@ -13183,7 +13234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="19" t="s">
         <v>370</v>
       </c>
@@ -13226,7 +13277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="19" t="s">
         <v>376</v>
       </c>
@@ -13269,7 +13320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="19" t="s">
         <v>382</v>
       </c>
@@ -13312,7 +13363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="19" t="s">
         <v>388</v>
       </c>
@@ -13355,7 +13406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="19" t="s">
         <v>393</v>
       </c>
@@ -13398,7 +13449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="19" t="s">
         <v>399</v>
       </c>
@@ -13441,7 +13492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="19" t="s">
         <v>405</v>
       </c>
@@ -13484,7 +13535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="19" t="s">
         <v>410</v>
       </c>
@@ -13527,7 +13578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="19" t="s">
         <v>416</v>
       </c>
@@ -13570,7 +13621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="19" t="s">
         <v>422</v>
       </c>
@@ -13613,7 +13664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="19" t="s">
         <v>427</v>
       </c>
@@ -13656,7 +13707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="19" t="s">
         <v>433</v>
       </c>
@@ -13699,7 +13750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="19" t="s">
         <v>438</v>
       </c>
@@ -13790,7 +13841,7 @@
         <v>6031</v>
       </c>
     </row>
-    <row r="84" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="19" t="s">
         <v>442</v>
       </c>
@@ -13833,7 +13884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="19" t="s">
         <v>447</v>
       </c>
@@ -13876,7 +13927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="19" t="s">
         <v>453</v>
       </c>
@@ -13919,7 +13970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="19" t="s">
         <v>458</v>
       </c>
@@ -13962,7 +14013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="19" t="s">
         <v>463</v>
       </c>
@@ -14053,7 +14104,7 @@
         <v>6697</v>
       </c>
     </row>
-    <row r="89" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="19" t="s">
         <v>468</v>
       </c>
@@ -14187,7 +14238,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="91" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="19" t="s">
         <v>477</v>
       </c>
@@ -14230,7 +14281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="19" t="s">
         <v>483</v>
       </c>
@@ -14273,7 +14324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="19" t="s">
         <v>487</v>
       </c>
@@ -14316,7 +14367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="19" t="s">
         <v>153</v>
       </c>
@@ -14407,7 +14458,7 @@
         <v>2883</v>
       </c>
     </row>
-    <row r="95" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="19" t="s">
         <v>493</v>
       </c>
@@ -14632,7 +14683,7 @@
         <v>7063</v>
       </c>
     </row>
-    <row r="98" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="19" t="s">
         <v>507</v>
       </c>
@@ -14675,7 +14726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="19" t="s">
         <v>513</v>
       </c>
@@ -14718,7 +14769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="19" t="s">
         <v>518</v>
       </c>
@@ -14761,7 +14812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="19" t="s">
         <v>523</v>
       </c>
@@ -14804,7 +14855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="19" t="s">
         <v>529</v>
       </c>
@@ -14847,7 +14898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="19" t="s">
         <v>164</v>
       </c>
@@ -14938,7 +14989,7 @@
         <v>2499</v>
       </c>
     </row>
-    <row r="104" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="19" t="s">
         <v>535</v>
       </c>
@@ -15029,7 +15080,7 @@
         <v>2533</v>
       </c>
     </row>
-    <row r="105" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="19" t="s">
         <v>541</v>
       </c>
@@ -15120,7 +15171,7 @@
         <v>2124</v>
       </c>
     </row>
-    <row r="106" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="19" t="s">
         <v>547</v>
       </c>
@@ -15163,7 +15214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="19" t="s">
         <v>552</v>
       </c>
@@ -15206,7 +15257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="19" t="s">
         <v>170</v>
       </c>
@@ -15249,7 +15300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="19" t="s">
         <v>557</v>
       </c>
@@ -15292,7 +15343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="19" t="s">
         <v>561</v>
       </c>
@@ -15383,7 +15434,7 @@
         <v>5171</v>
       </c>
     </row>
-    <row r="111" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="19" t="s">
         <v>567</v>
       </c>
@@ -15474,7 +15525,7 @@
         <v>5543</v>
       </c>
     </row>
-    <row r="112" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="19" t="s">
         <v>572</v>
       </c>
@@ -15565,7 +15616,7 @@
         <v>4135</v>
       </c>
     </row>
-    <row r="113" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="19" t="s">
         <v>577</v>
       </c>
@@ -15608,7 +15659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="19" t="s">
         <v>583</v>
       </c>
@@ -15651,7 +15702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="19" t="s">
         <v>588</v>
       </c>
@@ -15694,7 +15745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="19" t="s">
         <v>594</v>
       </c>
@@ -15737,7 +15788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="19" t="s">
         <v>599</v>
       </c>
@@ -15780,7 +15831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="19" t="s">
         <v>604</v>
       </c>
@@ -15823,7 +15874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="19" t="s">
         <v>11</v>
       </c>
@@ -15914,7 +15965,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="120" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="19" t="s">
         <v>20</v>
       </c>
@@ -16005,7 +16056,7 @@
         <v>1773</v>
       </c>
     </row>
-    <row r="121" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="19" t="s">
         <v>24</v>
       </c>
@@ -16048,7 +16099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="19" t="s">
         <v>30</v>
       </c>
@@ -16139,7 +16190,7 @@
         <v>4915</v>
       </c>
     </row>
-    <row r="123" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="19" t="s">
         <v>35</v>
       </c>
@@ -16182,7 +16233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="19" t="s">
         <v>41</v>
       </c>
@@ -16225,7 +16276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="19" t="s">
         <v>63</v>
       </c>
@@ -16268,7 +16319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="19" t="s">
         <v>69</v>
       </c>
@@ -16311,7 +16362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="19" t="s">
         <v>215</v>
       </c>
@@ -16354,7 +16405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="19" t="s">
         <v>267</v>
       </c>
@@ -16397,7 +16448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="19" t="s">
         <v>273</v>
       </c>
@@ -16440,7 +16491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="19" t="s">
         <v>279</v>
       </c>
@@ -16531,7 +16582,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="131" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="19" t="s">
         <v>284</v>
       </c>
@@ -16622,7 +16673,7 @@
         <v>1984</v>
       </c>
     </row>
-    <row r="132" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="19" t="s">
         <v>81</v>
       </c>
@@ -16713,7 +16764,7 @@
         <v>2597</v>
       </c>
     </row>
-    <row r="133" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="19" t="s">
         <v>86</v>
       </c>
@@ -16804,7 +16855,7 @@
         <v>1733</v>
       </c>
     </row>
-    <row r="134" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="19" t="s">
         <v>92</v>
       </c>
@@ -16895,7 +16946,7 @@
         <v>1724</v>
       </c>
     </row>
-    <row r="135" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="19" t="s">
         <v>289</v>
       </c>
@@ -16938,7 +16989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="19" t="s">
         <v>294</v>
       </c>
@@ -16981,7 +17032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="19" t="s">
         <v>47</v>
       </c>
@@ -17024,7 +17075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="19" t="s">
         <v>53</v>
       </c>
@@ -17067,7 +17118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="19" t="s">
         <v>57</v>
       </c>
@@ -17110,7 +17161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="19" t="s">
         <v>75</v>
       </c>
@@ -17201,7 +17252,7 @@
         <v>1839</v>
       </c>
     </row>
-    <row r="141" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="19" t="s">
         <v>209</v>
       </c>
@@ -17292,7 +17343,7 @@
         <v>2840</v>
       </c>
     </row>
-    <row r="142" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="19" t="s">
         <v>220</v>
       </c>
@@ -17383,7 +17434,7 @@
         <v>1451</v>
       </c>
     </row>
-    <row r="143" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="19" t="s">
         <v>225</v>
       </c>
@@ -17426,7 +17477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="19" t="s">
         <v>230</v>
       </c>
@@ -17517,7 +17568,7 @@
         <v>2854</v>
       </c>
     </row>
-    <row r="145" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="19" t="s">
         <v>236</v>
       </c>
@@ -17560,7 +17611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="19" t="s">
         <v>242</v>
       </c>
@@ -17603,7 +17654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="19" t="s">
         <v>248</v>
       </c>
@@ -17646,7 +17697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="19" t="s">
         <v>253</v>
       </c>
@@ -17689,7 +17740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="19" t="s">
         <v>258</v>
       </c>
@@ -17732,7 +17783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="19" t="s">
         <v>263</v>
       </c>
@@ -17775,7 +17826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="19" t="s">
         <v>300</v>
       </c>
@@ -17818,7 +17869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="19" t="s">
         <v>305</v>
       </c>
@@ -17909,7 +17960,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="153" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="19" t="s">
         <v>312</v>
       </c>
@@ -17972,15 +18023,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A4:AC153" xr:uid="{1D18A476-0271-4A84-BE9E-901865A86FD3}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="P 149"/>
-        <filter val="P 156"/>
-        <filter val="P 157"/>
-        <filter val="P 42"/>
-        <filter val="P 71"/>
-      </filters>
-    </filterColumn>
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="9">

--- a/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
+++ b/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EB81150-4FD5-40E4-B7D6-BE2E137210E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CEAA1F1-A981-4E83-AF3F-18EC4805C717}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
   </bookViews>
   <sheets>
     <sheet name="LISTA DE PONTOS" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1843" uniqueCount="855">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1853" uniqueCount="865">
   <si>
     <t>WKT</t>
   </si>
@@ -559,12 +559,6 @@
   </si>
   <si>
     <t>265ECE0250S0</t>
-  </si>
-  <si>
-    <t>ENTR. CE-166 (CANAFÍSTULA)</t>
-  </si>
-  <si>
-    <t>ENTR. BR-020 (MADALENA)</t>
   </si>
   <si>
     <t>POINT (-40.638383 -5.192050)</t>
@@ -2609,6 +2603,42 @@
   </si>
   <si>
     <t>ENTR. CE-371(B)/473(B)</t>
+  </si>
+  <si>
+    <t>166ECE0015S0</t>
+  </si>
+  <si>
+    <t>ENTR. CE-060(A)/266(A)/473 (QUIXERAMOBIM)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -5,210260°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -39,316634°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -5,211660°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -39,312789°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -5,187695°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -39,270508°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -4,761105°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -39,487011°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -5,175606°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -39,305516°</t>
   </si>
 </sst>
 </file>
@@ -4181,7 +4211,7 @@
   <cols>
     <col min="1" max="1" width="27" style="1" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16" style="1" bestFit="1" customWidth="1"/>
@@ -4222,7 +4252,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>9</v>
@@ -4257,7 +4287,7 @@
         <v>16</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="K2" s="6" t="s">
         <v>18</v>
@@ -4292,7 +4322,7 @@
         <v>16</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="K3" s="6" t="s">
         <v>18</v>
@@ -4362,7 +4392,7 @@
         <v>16</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="K5" s="6" t="s">
         <v>18</v>
@@ -4642,7 +4672,7 @@
         <v>16</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="K13" s="6" t="s">
         <v>18</v>
@@ -4650,10 +4680,10 @@
     </row>
     <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C14" s="5">
         <v>-4.9313539999999998</v>
@@ -4662,22 +4692,22 @@
         <v>-40.527043999999997</v>
       </c>
       <c r="E14" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="G14" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="H14" s="4" t="s">
         <v>211</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>213</v>
       </c>
       <c r="I14" s="4" t="s">
         <v>16</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="K14" s="6" t="s">
         <v>18</v>
@@ -4685,10 +4715,10 @@
     </row>
     <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C15" s="5">
         <v>-3.7677</v>
@@ -4697,16 +4727,16 @@
         <v>-40.979550000000003</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F15" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="H15" s="4" t="s">
         <v>216</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>218</v>
       </c>
       <c r="I15" s="4" t="s">
         <v>16</v>
@@ -4720,10 +4750,10 @@
     </row>
     <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C16" s="5">
         <v>-4.3993669999999998</v>
@@ -4735,19 +4765,19 @@
         <v>87</v>
       </c>
       <c r="F16" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="H16" s="4" t="s">
         <v>221</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>223</v>
       </c>
       <c r="I16" s="4" t="s">
         <v>16</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="K16" s="6" t="s">
         <v>18</v>
@@ -4755,10 +4785,10 @@
     </row>
     <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C17" s="5">
         <v>-3.8491379999999999</v>
@@ -4770,13 +4800,13 @@
         <v>148</v>
       </c>
       <c r="F17" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="H17" s="4" t="s">
         <v>226</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>228</v>
       </c>
       <c r="I17" s="4" t="s">
         <v>16</v>
@@ -4790,10 +4820,10 @@
     </row>
     <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C18" s="5">
         <v>-4.2870549999999996</v>
@@ -4802,22 +4832,22 @@
         <v>-38.933565000000002</v>
       </c>
       <c r="E18" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="G18" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="H18" s="4" t="s">
         <v>232</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>234</v>
       </c>
       <c r="I18" s="4" t="s">
         <v>16</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="K18" s="6" t="s">
         <v>18</v>
@@ -4825,10 +4855,10 @@
     </row>
     <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C19" s="5">
         <v>-3.992772</v>
@@ -4837,16 +4867,16 @@
         <v>-40.073487999999998</v>
       </c>
       <c r="E19" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="G19" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="H19" s="4" t="s">
         <v>238</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>240</v>
       </c>
       <c r="I19" s="4" t="s">
         <v>16</v>
@@ -4860,10 +4890,10 @@
     </row>
     <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C20" s="5">
         <v>-3.9917050000000001</v>
@@ -4872,16 +4902,16 @@
         <v>-40.079726999999998</v>
       </c>
       <c r="E20" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="G20" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="H20" s="4" t="s">
         <v>244</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>246</v>
       </c>
       <c r="I20" s="4" t="s">
         <v>16</v>
@@ -4895,10 +4925,10 @@
     </row>
     <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C21" s="5">
         <v>-3.4485109999999999</v>
@@ -4910,13 +4940,13 @@
         <v>48</v>
       </c>
       <c r="F21" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="H21" s="4" t="s">
         <v>249</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>251</v>
       </c>
       <c r="I21" s="4" t="s">
         <v>16</v>
@@ -4930,10 +4960,10 @@
     </row>
     <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C22" s="5">
         <v>-4.5111470000000002</v>
@@ -4942,16 +4972,16 @@
         <v>-38.359068999999998</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F22" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="H22" s="4" t="s">
         <v>254</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>256</v>
       </c>
       <c r="I22" s="4" t="s">
         <v>16</v>
@@ -4965,10 +4995,10 @@
     </row>
     <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C23" s="5">
         <v>-4.1670020000000001</v>
@@ -4980,13 +5010,13 @@
         <v>42</v>
       </c>
       <c r="F23" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="H23" s="4" t="s">
         <v>259</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>261</v>
       </c>
       <c r="I23" s="4" t="s">
         <v>16</v>
@@ -5000,10 +5030,10 @@
     </row>
     <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C24" s="5">
         <v>-4.1670970000000001</v>
@@ -5015,13 +5045,13 @@
         <v>76</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G24" s="4" t="s">
         <v>66</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="I24" s="4" t="s">
         <v>16</v>
@@ -5030,15 +5060,15 @@
         <v>17</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C25" s="5">
         <v>-3.97668</v>
@@ -5047,16 +5077,16 @@
         <v>-39.578536</v>
       </c>
       <c r="E25" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="G25" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="F25" s="4" t="s">
+      <c r="H25" s="4" t="s">
         <v>269</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>271</v>
       </c>
       <c r="I25" s="4" t="s">
         <v>16</v>
@@ -5070,10 +5100,10 @@
     </row>
     <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C26" s="5">
         <v>-4.0340299999999996</v>
@@ -5082,16 +5112,16 @@
         <v>-39.451304999999998</v>
       </c>
       <c r="E26" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="G26" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="H26" s="4" t="s">
         <v>275</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="H26" s="4" t="s">
-        <v>277</v>
       </c>
       <c r="I26" s="4" t="s">
         <v>16</v>
@@ -5105,10 +5135,10 @@
     </row>
     <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C27" s="5">
         <v>-4.1980709999999997</v>
@@ -5120,19 +5150,19 @@
         <v>36</v>
       </c>
       <c r="F27" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="H27" s="4" t="s">
         <v>280</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>282</v>
       </c>
       <c r="I27" s="4" t="s">
         <v>16</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="K27" s="6" t="s">
         <v>18</v>
@@ -5140,10 +5170,10 @@
     </row>
     <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C28" s="5">
         <v>-4.2305849999999996</v>
@@ -5155,19 +5185,19 @@
         <v>36</v>
       </c>
       <c r="F28" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="H28" s="4" t="s">
         <v>285</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="H28" s="4" t="s">
-        <v>287</v>
       </c>
       <c r="I28" s="4" t="s">
         <v>16</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="K28" s="6" t="s">
         <v>18</v>
@@ -5202,7 +5232,7 @@
         <v>16</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="K29" s="6" t="s">
         <v>18</v>
@@ -5237,7 +5267,7 @@
         <v>16</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="K30" s="6" t="s">
         <v>18</v>
@@ -5272,7 +5302,7 @@
         <v>16</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="K31" s="6" t="s">
         <v>18</v>
@@ -5280,10 +5310,10 @@
     </row>
     <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C32" s="5">
         <v>-3.9746800000000002</v>
@@ -5292,16 +5322,16 @@
         <v>-38.710697000000003</v>
       </c>
       <c r="E32" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="G32" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="F32" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>292</v>
-      </c>
       <c r="H32" s="4" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="I32" s="4" t="s">
         <v>16</v>
@@ -5315,10 +5345,10 @@
     </row>
     <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C33" s="5">
         <v>-3.2165300000000001</v>
@@ -5327,16 +5357,16 @@
         <v>-40.866968999999997</v>
       </c>
       <c r="E33" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="G33" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="F33" s="4" t="s">
+      <c r="H33" s="4" t="s">
         <v>296</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="H33" s="4" t="s">
-        <v>298</v>
       </c>
       <c r="I33" s="4" t="s">
         <v>16</v>
@@ -5350,10 +5380,10 @@
     </row>
     <row r="34" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C34" s="5">
         <v>-3.6606179999999999</v>
@@ -5365,13 +5395,13 @@
         <v>42</v>
       </c>
       <c r="F34" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="H34" s="4" t="s">
         <v>301</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="H34" s="4" t="s">
-        <v>303</v>
       </c>
       <c r="I34" s="4" t="s">
         <v>16</v>
@@ -5380,15 +5410,15 @@
         <v>17</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="35" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C35" s="5">
         <v>-4.5677839999999996</v>
@@ -5397,33 +5427,33 @@
         <v>-41.220272999999999</v>
       </c>
       <c r="E35" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="G35" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="F35" s="4" t="s">
+      <c r="H35" s="4" t="s">
         <v>307</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="H35" s="4" t="s">
-        <v>309</v>
       </c>
       <c r="I35" s="4" t="s">
         <v>16</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="K35" s="6" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C36" s="5">
         <v>-5.9926050000000002</v>
@@ -5435,13 +5465,13 @@
         <v>136</v>
       </c>
       <c r="F36" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="H36" s="4" t="s">
         <v>313</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="H36" s="4" t="s">
-        <v>315</v>
       </c>
       <c r="I36" s="4" t="s">
         <v>16</v>
@@ -5665,10 +5695,10 @@
     </row>
     <row r="43" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C43" s="5">
         <v>-4.228675</v>
@@ -5680,19 +5710,19 @@
         <v>148</v>
       </c>
       <c r="F43" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="H43" s="4" t="s">
         <v>318</v>
-      </c>
-      <c r="G43" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="H43" s="4" t="s">
-        <v>320</v>
       </c>
       <c r="I43" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="K43" s="6" t="s">
         <v>18</v>
@@ -5700,10 +5730,10 @@
     </row>
     <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C44" s="5">
         <v>-3.9083830000000002</v>
@@ -5715,13 +5745,13 @@
         <v>148</v>
       </c>
       <c r="F44" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="H44" s="4" t="s">
         <v>323</v>
-      </c>
-      <c r="G44" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="H44" s="4" t="s">
-        <v>325</v>
       </c>
       <c r="I44" s="4" t="s">
         <v>101</v>
@@ -5735,10 +5765,10 @@
     </row>
     <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C45" s="5">
         <v>-3.907816</v>
@@ -5750,13 +5780,13 @@
         <v>148</v>
       </c>
       <c r="F45" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="H45" s="4" t="s">
         <v>328</v>
-      </c>
-      <c r="G45" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="H45" s="4" t="s">
-        <v>330</v>
       </c>
       <c r="I45" s="4" t="s">
         <v>151</v>
@@ -5770,10 +5800,10 @@
     </row>
     <row r="46" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C46" s="5">
         <v>-4.5644640000000001</v>
@@ -5785,19 +5815,19 @@
         <v>87</v>
       </c>
       <c r="F46" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="H46" s="4" t="s">
         <v>333</v>
-      </c>
-      <c r="G46" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="H46" s="4" t="s">
-        <v>335</v>
       </c>
       <c r="I46" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="K46" s="6" t="s">
         <v>18</v>
@@ -5805,10 +5835,10 @@
     </row>
     <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C47" s="5">
         <v>-4.7033829999999996</v>
@@ -5817,16 +5847,16 @@
         <v>-37.482100000000003</v>
       </c>
       <c r="E47" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="G47" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="F47" s="4" t="s">
+      <c r="H47" s="4" t="s">
         <v>339</v>
-      </c>
-      <c r="G47" s="4" t="s">
-        <v>340</v>
-      </c>
-      <c r="H47" s="4" t="s">
-        <v>341</v>
       </c>
       <c r="I47" s="4" t="s">
         <v>151</v>
@@ -5840,10 +5870,10 @@
     </row>
     <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C48" s="5">
         <v>-4.8203329999999998</v>
@@ -5852,16 +5882,16 @@
         <v>-37.881216000000002</v>
       </c>
       <c r="E48" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="G48" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="F48" s="4" t="s">
+      <c r="H48" s="4" t="s">
         <v>345</v>
-      </c>
-      <c r="G48" s="4" t="s">
-        <v>346</v>
-      </c>
-      <c r="H48" s="4" t="s">
-        <v>347</v>
       </c>
       <c r="I48" s="4" t="s">
         <v>101</v>
@@ -5902,7 +5932,7 @@
         <v>101</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="K49" s="6" t="s">
         <v>18</v>
@@ -5937,7 +5967,7 @@
         <v>101</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="K50" s="6" t="s">
         <v>18</v>
@@ -5945,10 +5975,10 @@
     </row>
     <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C51" s="5">
         <v>-4.702947</v>
@@ -5960,10 +5990,10 @@
         <v>12</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="H51" s="4" t="s">
         <v>22</v>
@@ -5972,7 +6002,7 @@
         <v>151</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="K51" s="6" t="s">
         <v>18</v>
@@ -5980,10 +6010,10 @@
     </row>
     <row r="52" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C52" s="5">
         <v>-5.2227160000000001</v>
@@ -5992,16 +6022,16 @@
         <v>-37.964933000000002</v>
       </c>
       <c r="E52" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="G52" s="4" t="s">
         <v>354</v>
       </c>
-      <c r="F52" s="4" t="s">
+      <c r="H52" s="4" t="s">
         <v>355</v>
-      </c>
-      <c r="G52" s="4" t="s">
-        <v>356</v>
-      </c>
-      <c r="H52" s="4" t="s">
-        <v>357</v>
       </c>
       <c r="I52" s="4" t="s">
         <v>101</v>
@@ -6010,74 +6040,74 @@
         <v>17</v>
       </c>
       <c r="K52" s="6" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="C53" s="5">
+        <v>-5.2506180000000002</v>
+      </c>
+      <c r="D53" s="5">
+        <v>-38.494636999999997</v>
+      </c>
+      <c r="E53" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="B53" s="4" t="s">
+      <c r="F53" s="4" t="s">
         <v>359</v>
-      </c>
-      <c r="C53" s="5">
-        <v>-5.2497160000000003</v>
-      </c>
-      <c r="D53" s="5">
-        <v>-38.499932999999999</v>
-      </c>
-      <c r="E53" s="4" t="s">
-        <v>360</v>
-      </c>
-      <c r="F53" s="4" t="s">
-        <v>361</v>
       </c>
       <c r="G53" s="4" t="s">
         <v>27</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="I53" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>17</v>
+        <v>837</v>
       </c>
       <c r="K53" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="C54" s="5">
+        <v>-5.4016780000000004</v>
+      </c>
+      <c r="D54" s="5">
+        <v>-38.569516999999998</v>
+      </c>
+      <c r="E54" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="F54" s="4" t="s">
         <v>364</v>
       </c>
-      <c r="C54" s="5">
-        <v>-5.4021499999999998</v>
-      </c>
-      <c r="D54" s="5">
-        <v>-38.569200000000002</v>
-      </c>
-      <c r="E54" s="4" t="s">
+      <c r="G54" s="4" t="s">
         <v>365</v>
       </c>
-      <c r="F54" s="4" t="s">
+      <c r="H54" s="4" t="s">
         <v>366</v>
-      </c>
-      <c r="G54" s="4" t="s">
-        <v>367</v>
-      </c>
-      <c r="H54" s="4" t="s">
-        <v>368</v>
       </c>
       <c r="I54" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>17</v>
+        <v>837</v>
       </c>
       <c r="K54" s="6" t="s">
         <v>18</v>
@@ -6085,10 +6115,10 @@
     </row>
     <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C55" s="5">
         <v>-5.9727329999999998</v>
@@ -6097,16 +6127,16 @@
         <v>-38.8797</v>
       </c>
       <c r="E55" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="G55" s="4" t="s">
         <v>371</v>
       </c>
-      <c r="F55" s="4" t="s">
+      <c r="H55" s="4" t="s">
         <v>372</v>
-      </c>
-      <c r="G55" s="4" t="s">
-        <v>373</v>
-      </c>
-      <c r="H55" s="4" t="s">
-        <v>374</v>
       </c>
       <c r="I55" s="4" t="s">
         <v>151</v>
@@ -6155,10 +6185,10 @@
     </row>
     <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C57" s="5">
         <v>-3.5660500000000002</v>
@@ -6167,16 +6197,16 @@
         <v>-41.143765999999999</v>
       </c>
       <c r="E57" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="G57" s="4" t="s">
         <v>377</v>
       </c>
-      <c r="F57" s="4" t="s">
+      <c r="H57" s="4" t="s">
         <v>378</v>
-      </c>
-      <c r="G57" s="4" t="s">
-        <v>379</v>
-      </c>
-      <c r="H57" s="4" t="s">
-        <v>380</v>
       </c>
       <c r="I57" s="4" t="s">
         <v>151</v>
@@ -6185,15 +6215,15 @@
         <v>17</v>
       </c>
       <c r="K57" s="6" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C58" s="5">
         <v>-3.8470499999999999</v>
@@ -6202,16 +6232,16 @@
         <v>-40.655116</v>
       </c>
       <c r="E58" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="G58" s="4" t="s">
         <v>383</v>
       </c>
-      <c r="F58" s="4" t="s">
+      <c r="H58" s="4" t="s">
         <v>384</v>
-      </c>
-      <c r="G58" s="4" t="s">
-        <v>385</v>
-      </c>
-      <c r="H58" s="4" t="s">
-        <v>386</v>
       </c>
       <c r="I58" s="4" t="s">
         <v>151</v>
@@ -6260,10 +6290,10 @@
     </row>
     <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C60" s="5">
         <v>-3.9773499999999999</v>
@@ -6272,16 +6302,16 @@
         <v>-40.707566</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="F60" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="G60" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="H60" s="4" t="s">
         <v>389</v>
-      </c>
-      <c r="G60" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="H60" s="4" t="s">
-        <v>391</v>
       </c>
       <c r="I60" s="4" t="s">
         <v>151</v>
@@ -6295,10 +6325,10 @@
     </row>
     <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C61" s="5">
         <v>-4.1677330000000001</v>
@@ -6307,16 +6337,16 @@
         <v>-40.952933000000002</v>
       </c>
       <c r="E61" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="G61" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="F61" s="4" t="s">
+      <c r="H61" s="4" t="s">
         <v>395</v>
-      </c>
-      <c r="G61" s="4" t="s">
-        <v>396</v>
-      </c>
-      <c r="H61" s="4" t="s">
-        <v>397</v>
       </c>
       <c r="I61" s="4" t="s">
         <v>101</v>
@@ -6330,10 +6360,10 @@
     </row>
     <row r="62" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C62" s="5">
         <v>-4.040883</v>
@@ -6342,16 +6372,16 @@
         <v>-40.474516000000001</v>
       </c>
       <c r="E62" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="G62" s="4" t="s">
         <v>400</v>
       </c>
-      <c r="F62" s="4" t="s">
+      <c r="H62" s="4" t="s">
         <v>401</v>
-      </c>
-      <c r="G62" s="4" t="s">
-        <v>402</v>
-      </c>
-      <c r="H62" s="4" t="s">
-        <v>403</v>
       </c>
       <c r="I62" s="4" t="s">
         <v>151</v>
@@ -6365,10 +6395,10 @@
     </row>
     <row r="63" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C63" s="5">
         <v>-3.5272999999999999</v>
@@ -6377,16 +6407,16 @@
         <v>-39.073349999999998</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F63" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="G63" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="H63" s="4" t="s">
         <v>406</v>
-      </c>
-      <c r="G63" s="4" t="s">
-        <v>407</v>
-      </c>
-      <c r="H63" s="4" t="s">
-        <v>408</v>
       </c>
       <c r="I63" s="4" t="s">
         <v>101</v>
@@ -6400,10 +6430,10 @@
     </row>
     <row r="64" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C64" s="5">
         <v>-3.553566</v>
@@ -6412,16 +6442,16 @@
         <v>-38.885983000000003</v>
       </c>
       <c r="E64" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="G64" s="4" t="s">
         <v>411</v>
       </c>
-      <c r="F64" s="4" t="s">
+      <c r="H64" s="4" t="s">
         <v>412</v>
-      </c>
-      <c r="G64" s="4" t="s">
-        <v>413</v>
-      </c>
-      <c r="H64" s="4" t="s">
-        <v>414</v>
       </c>
       <c r="I64" s="4" t="s">
         <v>151</v>
@@ -6435,10 +6465,10 @@
     </row>
     <row r="65" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C65" s="5">
         <v>-3.2338659999999999</v>
@@ -6447,16 +6477,16 @@
         <v>-40.011833000000003</v>
       </c>
       <c r="E65" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="G65" s="4" t="s">
         <v>417</v>
       </c>
-      <c r="F65" s="4" t="s">
+      <c r="H65" s="4" t="s">
         <v>418</v>
-      </c>
-      <c r="G65" s="4" t="s">
-        <v>419</v>
-      </c>
-      <c r="H65" s="4" t="s">
-        <v>420</v>
       </c>
       <c r="I65" s="4" t="s">
         <v>101</v>
@@ -6470,10 +6500,10 @@
     </row>
     <row r="66" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C66" s="5">
         <v>-3.5168159999999999</v>
@@ -6482,16 +6512,16 @@
         <v>-39.583283000000002</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="F66" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="G66" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="H66" s="4" t="s">
         <v>423</v>
-      </c>
-      <c r="G66" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="H66" s="4" t="s">
-        <v>425</v>
       </c>
       <c r="I66" s="4" t="s">
         <v>101</v>
@@ -6505,10 +6535,10 @@
     </row>
     <row r="67" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C67" s="5">
         <v>-3.6586500000000002</v>
@@ -6517,16 +6547,16 @@
         <v>-39.420050000000003</v>
       </c>
       <c r="E67" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="G67" s="4" t="s">
         <v>428</v>
       </c>
-      <c r="F67" s="4" t="s">
+      <c r="H67" s="4" t="s">
         <v>429</v>
-      </c>
-      <c r="G67" s="4" t="s">
-        <v>430</v>
-      </c>
-      <c r="H67" s="4" t="s">
-        <v>431</v>
       </c>
       <c r="I67" s="4" t="s">
         <v>101</v>
@@ -6540,10 +6570,10 @@
     </row>
     <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C68" s="5">
         <v>-4.2901499999999997</v>
@@ -6552,16 +6582,16 @@
         <v>-38.625466000000003</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="F68" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="G68" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="H68" s="4" t="s">
         <v>434</v>
-      </c>
-      <c r="G68" s="4" t="s">
-        <v>435</v>
-      </c>
-      <c r="H68" s="4" t="s">
-        <v>436</v>
       </c>
       <c r="I68" s="4" t="s">
         <v>16</v>
@@ -6575,10 +6605,10 @@
     </row>
     <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C69" s="5">
         <v>-4.3755519999999999</v>
@@ -6587,22 +6617,22 @@
         <v>-38.834249999999997</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="I69" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J69" s="6" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="K69" s="6" t="s">
         <v>18</v>
@@ -6610,10 +6640,10 @@
     </row>
     <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C70" s="5">
         <v>-5.0380159999999998</v>
@@ -6622,16 +6652,16 @@
         <v>-37.783000000000001</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F70" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="G70" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="H70" s="4" t="s">
         <v>443</v>
-      </c>
-      <c r="G70" s="4" t="s">
-        <v>444</v>
-      </c>
-      <c r="H70" s="4" t="s">
-        <v>445</v>
       </c>
       <c r="I70" s="4" t="s">
         <v>151</v>
@@ -6645,10 +6675,10 @@
     </row>
     <row r="71" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C71" s="5">
         <v>-5.2755999999999998</v>
@@ -6657,16 +6687,16 @@
         <v>-38.108716000000001</v>
       </c>
       <c r="E71" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="G71" s="4" t="s">
         <v>448</v>
       </c>
-      <c r="F71" s="4" t="s">
+      <c r="H71" s="4" t="s">
         <v>449</v>
-      </c>
-      <c r="G71" s="4" t="s">
-        <v>450</v>
-      </c>
-      <c r="H71" s="4" t="s">
-        <v>451</v>
       </c>
       <c r="I71" s="4" t="s">
         <v>101</v>
@@ -6680,10 +6710,10 @@
     </row>
     <row r="72" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C72" s="5">
         <v>-3.7728000000000002</v>
@@ -6695,13 +6725,13 @@
         <v>97</v>
       </c>
       <c r="F72" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="G72" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="H72" s="4" t="s">
         <v>454</v>
-      </c>
-      <c r="G72" s="4" t="s">
-        <v>455</v>
-      </c>
-      <c r="H72" s="4" t="s">
-        <v>456</v>
       </c>
       <c r="I72" s="4" t="s">
         <v>101</v>
@@ -6715,10 +6745,10 @@
     </row>
     <row r="73" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C73" s="5">
         <v>-3.1334659999999999</v>
@@ -6727,16 +6757,16 @@
         <v>-40.815800000000003</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F73" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="G73" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="H73" s="4" t="s">
         <v>459</v>
-      </c>
-      <c r="G73" s="4" t="s">
-        <v>460</v>
-      </c>
-      <c r="H73" s="4" t="s">
-        <v>461</v>
       </c>
       <c r="I73" s="4" t="s">
         <v>101</v>
@@ -6750,10 +6780,10 @@
     </row>
     <row r="74" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C74" s="5">
         <v>-3.6184599999999998</v>
@@ -6762,22 +6792,22 @@
         <v>-40.352547000000001</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F74" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="G74" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="H74" s="4" t="s">
         <v>464</v>
-      </c>
-      <c r="G74" s="4" t="s">
-        <v>465</v>
-      </c>
-      <c r="H74" s="4" t="s">
-        <v>466</v>
       </c>
       <c r="I74" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J74" s="6" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="K74" s="6" t="s">
         <v>18</v>
@@ -6785,10 +6815,10 @@
     </row>
     <row r="75" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C75" s="5">
         <v>-3.9911660000000002</v>
@@ -6797,16 +6827,16 @@
         <v>-40.085766</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F75" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="G75" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="H75" s="4" t="s">
         <v>469</v>
-      </c>
-      <c r="G75" s="4" t="s">
-        <v>470</v>
-      </c>
-      <c r="H75" s="4" t="s">
-        <v>471</v>
       </c>
       <c r="I75" s="4" t="s">
         <v>151</v>
@@ -6820,10 +6850,10 @@
     </row>
     <row r="76" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C76" s="5">
         <v>-5.6781480000000002</v>
@@ -6832,22 +6862,22 @@
         <v>-39.430067000000001</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F76" s="4" t="s">
+        <v>838</v>
+      </c>
+      <c r="G76" s="4" t="s">
+        <v>839</v>
+      </c>
+      <c r="H76" s="4" t="s">
         <v>840</v>
-      </c>
-      <c r="G76" s="4" t="s">
-        <v>841</v>
-      </c>
-      <c r="H76" s="4" t="s">
-        <v>842</v>
       </c>
       <c r="I76" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J76" s="6" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="K76" s="6" t="s">
         <v>18</v>
@@ -6855,10 +6885,10 @@
     </row>
     <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C77" s="5">
         <v>-3.4014500000000001</v>
@@ -6867,16 +6897,16 @@
         <v>-40.686549999999997</v>
       </c>
       <c r="E77" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="G77" s="4" t="s">
         <v>478</v>
       </c>
-      <c r="F77" s="4" t="s">
+      <c r="H77" s="4" t="s">
         <v>479</v>
-      </c>
-      <c r="G77" s="4" t="s">
-        <v>480</v>
-      </c>
-      <c r="H77" s="4" t="s">
-        <v>481</v>
       </c>
       <c r="I77" s="4" t="s">
         <v>101</v>
@@ -6890,10 +6920,10 @@
     </row>
     <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C78" s="5">
         <v>-3.5714160000000001</v>
@@ -6902,16 +6932,16 @@
         <v>-40.6374</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I78" s="4" t="s">
         <v>101</v>
@@ -6923,12 +6953,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C79" s="5">
         <v>-4.7611049999999997</v>
@@ -6937,22 +6967,22 @@
         <v>-39.487011000000003</v>
       </c>
       <c r="E79" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="G79" s="4" t="s">
         <v>488</v>
       </c>
-      <c r="F79" s="4" t="s">
+      <c r="H79" s="4" t="s">
         <v>489</v>
-      </c>
-      <c r="G79" s="4" t="s">
-        <v>490</v>
-      </c>
-      <c r="H79" s="4" t="s">
-        <v>491</v>
       </c>
       <c r="I79" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J79" s="6" t="s">
-        <v>839</v>
+        <v>804</v>
       </c>
       <c r="K79" s="6" t="s">
         <v>18</v>
@@ -6987,42 +7017,42 @@
         <v>101</v>
       </c>
       <c r="J80" s="6" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="K80" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="81" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="C81" s="5">
+        <v>-5.4022300000000003</v>
+      </c>
+      <c r="D81" s="5">
+        <v>-38.571371999999997</v>
+      </c>
+      <c r="E81" s="4" t="s">
         <v>492</v>
       </c>
-      <c r="B81" s="4" t="s">
+      <c r="F81" s="4" t="s">
         <v>493</v>
       </c>
-      <c r="C81" s="5">
-        <v>-5.4021499999999998</v>
-      </c>
-      <c r="D81" s="5">
-        <v>-38.571483000000001</v>
-      </c>
-      <c r="E81" s="4" t="s">
+      <c r="G81" s="4" t="s">
         <v>494</v>
       </c>
-      <c r="F81" s="4" t="s">
+      <c r="H81" s="4" t="s">
         <v>495</v>
-      </c>
-      <c r="G81" s="4" t="s">
-        <v>496</v>
-      </c>
-      <c r="H81" s="4" t="s">
-        <v>497</v>
       </c>
       <c r="I81" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J81" s="6" t="s">
-        <v>17</v>
+        <v>837</v>
       </c>
       <c r="K81" s="6" t="s">
         <v>18</v>
@@ -7030,10 +7060,10 @@
     </row>
     <row r="82" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C82" s="5">
         <v>-5.7358440000000002</v>
@@ -7045,19 +7075,19 @@
         <v>136</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I82" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J82" s="6" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="K82" s="6" t="s">
         <v>18</v>
@@ -7065,10 +7095,10 @@
     </row>
     <row r="83" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C83" s="5">
         <v>-5.6845759999999999</v>
@@ -7080,19 +7110,19 @@
         <v>136</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="I83" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J83" s="6" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="K83" s="6" t="s">
         <v>18</v>
@@ -7100,10 +7130,10 @@
     </row>
     <row r="84" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C84" s="5">
         <v>-5.0811999999999999</v>
@@ -7112,16 +7142,16 @@
         <v>-38.004565999999997</v>
       </c>
       <c r="E84" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="G84" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="F84" s="4" t="s">
+      <c r="H84" s="4" t="s">
         <v>509</v>
-      </c>
-      <c r="G84" s="4" t="s">
-        <v>510</v>
-      </c>
-      <c r="H84" s="4" t="s">
-        <v>511</v>
       </c>
       <c r="I84" s="4" t="s">
         <v>101</v>
@@ -7135,10 +7165,10 @@
     </row>
     <row r="85" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C85" s="5">
         <v>-5.2329999999999997</v>
@@ -7147,16 +7177,16 @@
         <v>-38.194850000000002</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="F85" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="G85" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="H85" s="4" t="s">
         <v>514</v>
-      </c>
-      <c r="G85" s="4" t="s">
-        <v>515</v>
-      </c>
-      <c r="H85" s="4" t="s">
-        <v>516</v>
       </c>
       <c r="I85" s="4" t="s">
         <v>101</v>
@@ -7168,7 +7198,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>158</v>
       </c>
@@ -7197,7 +7227,7 @@
         <v>151</v>
       </c>
       <c r="J86" s="6" t="s">
-        <v>839</v>
+        <v>804</v>
       </c>
       <c r="K86" s="6" t="s">
         <v>18</v>
@@ -7205,10 +7235,10 @@
     </row>
     <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C87" s="5">
         <v>-3.9741499999999998</v>
@@ -7217,16 +7247,16 @@
         <v>-40.704782999999999</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="F87" s="4" t="s">
+        <v>517</v>
+      </c>
+      <c r="G87" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="H87" s="4" t="s">
         <v>519</v>
-      </c>
-      <c r="G87" s="4" t="s">
-        <v>520</v>
-      </c>
-      <c r="H87" s="4" t="s">
-        <v>521</v>
       </c>
       <c r="I87" s="4" t="s">
         <v>151</v>
@@ -7240,10 +7270,10 @@
     </row>
     <row r="88" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C88" s="5">
         <v>-3.962866</v>
@@ -7252,16 +7282,16 @@
         <v>-38.357016000000002</v>
       </c>
       <c r="E88" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>523</v>
+      </c>
+      <c r="G88" s="4" t="s">
         <v>524</v>
       </c>
-      <c r="F88" s="4" t="s">
+      <c r="H88" s="4" t="s">
         <v>525</v>
-      </c>
-      <c r="G88" s="4" t="s">
-        <v>526</v>
-      </c>
-      <c r="H88" s="4" t="s">
-        <v>527</v>
       </c>
       <c r="I88" s="4" t="s">
         <v>101</v>
@@ -7275,10 +7305,10 @@
     </row>
     <row r="89" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C89" s="5">
         <v>-4.0425329999999997</v>
@@ -7287,16 +7317,16 @@
         <v>-38.206499999999998</v>
       </c>
       <c r="E89" s="4" t="s">
+        <v>528</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="G89" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="F89" s="4" t="s">
+      <c r="H89" s="4" t="s">
         <v>531</v>
-      </c>
-      <c r="G89" s="4" t="s">
-        <v>532</v>
-      </c>
-      <c r="H89" s="4" t="s">
-        <v>533</v>
       </c>
       <c r="I89" s="4" t="s">
         <v>151</v>
@@ -7337,7 +7367,7 @@
         <v>151</v>
       </c>
       <c r="J90" s="6" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="K90" s="6" t="s">
         <v>18</v>
@@ -7345,10 +7375,10 @@
     </row>
     <row r="91" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C91" s="5">
         <v>-4.4447369999999999</v>
@@ -7357,22 +7387,22 @@
         <v>-38.662745999999999</v>
       </c>
       <c r="E91" s="4" t="s">
+        <v>534</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>535</v>
+      </c>
+      <c r="G91" s="4" t="s">
         <v>536</v>
       </c>
-      <c r="F91" s="4" t="s">
+      <c r="H91" s="4" t="s">
         <v>537</v>
-      </c>
-      <c r="G91" s="4" t="s">
-        <v>538</v>
-      </c>
-      <c r="H91" s="4" t="s">
-        <v>539</v>
       </c>
       <c r="I91" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J91" s="6" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="K91" s="6" t="s">
         <v>18</v>
@@ -7380,10 +7410,10 @@
     </row>
     <row r="92" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C92" s="5">
         <v>-5.1705110000000003</v>
@@ -7392,22 +7422,22 @@
         <v>-40.708150000000003</v>
       </c>
       <c r="E92" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="F92" s="4" t="s">
+        <v>541</v>
+      </c>
+      <c r="G92" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="F92" s="4" t="s">
+      <c r="H92" s="4" t="s">
         <v>543</v>
-      </c>
-      <c r="G92" s="4" t="s">
-        <v>544</v>
-      </c>
-      <c r="H92" s="4" t="s">
-        <v>545</v>
       </c>
       <c r="I92" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J92" s="6" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="K92" s="6" t="s">
         <v>18</v>
@@ -7415,10 +7445,10 @@
     </row>
     <row r="93" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C93" s="5">
         <v>-4.5725499999999997</v>
@@ -7427,16 +7457,16 @@
         <v>-37.736899999999999</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="F93" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="G93" s="4" t="s">
+        <v>547</v>
+      </c>
+      <c r="H93" s="4" t="s">
         <v>548</v>
-      </c>
-      <c r="G93" s="4" t="s">
-        <v>549</v>
-      </c>
-      <c r="H93" s="4" t="s">
-        <v>550</v>
       </c>
       <c r="I93" s="4" t="s">
         <v>101</v>
@@ -7450,10 +7480,10 @@
     </row>
     <row r="94" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C94" s="5">
         <v>-5.1207330000000004</v>
@@ -7462,16 +7492,16 @@
         <v>-39.752000000000002</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="F94" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="G94" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="H94" s="4" t="s">
         <v>553</v>
-      </c>
-      <c r="G94" s="4" t="s">
-        <v>554</v>
-      </c>
-      <c r="H94" s="4" t="s">
-        <v>555</v>
       </c>
       <c r="I94" s="4" t="s">
         <v>101</v>
@@ -7483,7 +7513,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>169</v>
       </c>
@@ -7497,22 +7527,22 @@
         <v>-39.305515999999997</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>12</v>
+        <v>197</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>171</v>
+        <v>853</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>172</v>
+        <v>132</v>
       </c>
       <c r="H95" s="4" t="s">
-        <v>173</v>
+        <v>854</v>
       </c>
       <c r="I95" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J95" s="6" t="s">
-        <v>839</v>
+        <v>804</v>
       </c>
       <c r="K95" s="6" t="s">
         <v>18</v>
@@ -7520,10 +7550,10 @@
     </row>
     <row r="96" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C96" s="5">
         <v>-3.6957</v>
@@ -7535,13 +7565,13 @@
         <v>42</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="H96" s="4" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="I96" s="4" t="s">
         <v>101</v>
@@ -7550,15 +7580,15 @@
         <v>17</v>
       </c>
       <c r="K96" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="97" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C97" s="5">
         <v>-3.6978119999999999</v>
@@ -7567,22 +7597,22 @@
         <v>-40.307443999999997</v>
       </c>
       <c r="E97" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="F97" s="4" t="s">
+        <v>561</v>
+      </c>
+      <c r="G97" s="4" t="s">
         <v>562</v>
       </c>
-      <c r="F97" s="4" t="s">
+      <c r="H97" s="4" t="s">
         <v>563</v>
-      </c>
-      <c r="G97" s="4" t="s">
-        <v>564</v>
-      </c>
-      <c r="H97" s="4" t="s">
-        <v>565</v>
       </c>
       <c r="I97" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J97" s="6" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="K97" s="6" t="s">
         <v>18</v>
@@ -7590,10 +7620,10 @@
     </row>
     <row r="98" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C98" s="5">
         <v>-5.2113269999999998</v>
@@ -7602,22 +7632,22 @@
         <v>-40.696823000000002</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F98" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="G98" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="H98" s="4" t="s">
         <v>568</v>
-      </c>
-      <c r="G98" s="4" t="s">
-        <v>569</v>
-      </c>
-      <c r="H98" s="4" t="s">
-        <v>570</v>
       </c>
       <c r="I98" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J98" s="6" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="K98" s="6" t="s">
         <v>18</v>
@@ -7625,10 +7655,10 @@
     </row>
     <row r="99" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C99" s="5">
         <v>-4.3822749999999999</v>
@@ -7637,22 +7667,22 @@
         <v>-40.712611000000003</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F99" s="4" t="s">
+        <v>571</v>
+      </c>
+      <c r="G99" s="4" t="s">
+        <v>572</v>
+      </c>
+      <c r="H99" s="4" t="s">
         <v>573</v>
-      </c>
-      <c r="G99" s="4" t="s">
-        <v>574</v>
-      </c>
-      <c r="H99" s="4" t="s">
-        <v>575</v>
       </c>
       <c r="I99" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J99" s="6" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="K99" s="6" t="s">
         <v>18</v>
@@ -7660,10 +7690,10 @@
     </row>
     <row r="100" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C100" s="5">
         <v>-6.0296659999999997</v>
@@ -7672,16 +7702,16 @@
         <v>-38.340949999999999</v>
       </c>
       <c r="E100" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>577</v>
+      </c>
+      <c r="G100" s="4" t="s">
         <v>578</v>
       </c>
-      <c r="F100" s="4" t="s">
+      <c r="H100" s="4" t="s">
         <v>579</v>
-      </c>
-      <c r="G100" s="4" t="s">
-        <v>580</v>
-      </c>
-      <c r="H100" s="4" t="s">
-        <v>581</v>
       </c>
       <c r="I100" s="4" t="s">
         <v>101</v>
@@ -7693,36 +7723,36 @@
         <v>18</v>
       </c>
     </row>
-    <row r="101" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>581</v>
+      </c>
+      <c r="C101" s="5">
+        <v>-5.2495240000000001</v>
+      </c>
+      <c r="D101" s="5">
+        <v>-38.492610999999997</v>
+      </c>
+      <c r="E101" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="F101" s="4" t="s">
         <v>582</v>
       </c>
-      <c r="B101" s="4" t="s">
+      <c r="G101" s="4" t="s">
         <v>583</v>
       </c>
-      <c r="C101" s="5">
-        <v>-5.2479829999999996</v>
-      </c>
-      <c r="D101" s="5">
-        <v>-38.491466000000003</v>
-      </c>
-      <c r="E101" s="4" t="s">
-        <v>494</v>
-      </c>
-      <c r="F101" s="4" t="s">
+      <c r="H101" s="4" t="s">
         <v>584</v>
-      </c>
-      <c r="G101" s="4" t="s">
-        <v>585</v>
-      </c>
-      <c r="H101" s="4" t="s">
-        <v>586</v>
       </c>
       <c r="I101" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J101" s="6" t="s">
-        <v>17</v>
+        <v>837</v>
       </c>
       <c r="K101" s="6" t="s">
         <v>18</v>
@@ -7730,10 +7760,10 @@
     </row>
     <row r="102" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="C102" s="5">
         <v>-4.2260499999999999</v>
@@ -7742,16 +7772,16 @@
         <v>-38.112082999999998</v>
       </c>
       <c r="E102" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="F102" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="G102" s="4" t="s">
         <v>589</v>
       </c>
-      <c r="F102" s="4" t="s">
+      <c r="H102" s="4" t="s">
         <v>590</v>
-      </c>
-      <c r="G102" s="4" t="s">
-        <v>591</v>
-      </c>
-      <c r="H102" s="4" t="s">
-        <v>592</v>
       </c>
       <c r="I102" s="4" t="s">
         <v>151</v>
@@ -7760,15 +7790,15 @@
         <v>17</v>
       </c>
       <c r="K102" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="103" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="C103" s="5">
         <v>-4.2283499999999998</v>
@@ -7777,16 +7807,16 @@
         <v>-38.112932999999998</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="G103" s="4" t="s">
         <v>73</v>
       </c>
       <c r="H103" s="4" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="I103" s="4" t="s">
         <v>101</v>
@@ -7800,10 +7830,10 @@
     </row>
     <row r="104" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="C104" s="5">
         <v>-4.5906500000000001</v>
@@ -7815,13 +7845,13 @@
         <v>142</v>
       </c>
       <c r="F104" s="4" t="s">
+        <v>598</v>
+      </c>
+      <c r="G104" s="4" t="s">
+        <v>599</v>
+      </c>
+      <c r="H104" s="4" t="s">
         <v>600</v>
-      </c>
-      <c r="G104" s="4" t="s">
-        <v>601</v>
-      </c>
-      <c r="H104" s="4" t="s">
-        <v>602</v>
       </c>
       <c r="I104" s="4" t="s">
         <v>101</v>
@@ -7835,10 +7865,10 @@
     </row>
     <row r="105" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="C105" s="5">
         <v>-3.9187500000000002</v>
@@ -7850,13 +7880,13 @@
         <v>104</v>
       </c>
       <c r="F105" s="4" t="s">
+        <v>603</v>
+      </c>
+      <c r="G105" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="H105" s="4" t="s">
         <v>605</v>
-      </c>
-      <c r="G105" s="4" t="s">
-        <v>606</v>
-      </c>
-      <c r="H105" s="4" t="s">
-        <v>607</v>
       </c>
       <c r="I105" s="4" t="s">
         <v>101</v>
@@ -7865,15 +7895,15 @@
         <v>17</v>
       </c>
       <c r="K105" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="106" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C106" s="5">
         <v>-3.4879829999999998</v>
@@ -7882,16 +7912,16 @@
         <v>-39.140065999999997</v>
       </c>
       <c r="E106" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="F106" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="G106" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="F106" s="4" t="s">
+      <c r="H106" s="4" t="s">
         <v>177</v>
-      </c>
-      <c r="G106" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="H106" s="4" t="s">
-        <v>179</v>
       </c>
       <c r="I106" s="4" t="s">
         <v>101</v>
@@ -7900,15 +7930,15 @@
         <v>17</v>
       </c>
       <c r="K106" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="107" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C107" s="5">
         <v>-2.9157660000000001</v>
@@ -7917,16 +7947,16 @@
         <v>-40.170183000000002</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F107" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="G107" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="H107" s="4" t="s">
         <v>183</v>
-      </c>
-      <c r="G107" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="H107" s="4" t="s">
-        <v>185</v>
       </c>
       <c r="I107" s="4" t="s">
         <v>101</v>
@@ -7940,10 +7970,10 @@
     </row>
     <row r="108" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C108" s="5">
         <v>-3.0767500000000001</v>
@@ -7952,16 +7982,16 @@
         <v>-41.252065999999999</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F108" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="G108" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="H108" s="4" t="s">
         <v>188</v>
-      </c>
-      <c r="G108" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="H108" s="4" t="s">
-        <v>190</v>
       </c>
       <c r="I108" s="4" t="s">
         <v>151</v>
@@ -7973,47 +8003,47 @@
         <v>18</v>
       </c>
     </row>
-    <row r="109" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C109" s="5">
+        <v>-5.0728489999999997</v>
+      </c>
+      <c r="D109" s="5">
+        <v>-38.384563</v>
+      </c>
+      <c r="E109" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B109" s="4" t="s">
+      <c r="F109" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="C109" s="5">
-        <v>-5.0715500000000002</v>
-      </c>
-      <c r="D109" s="5">
-        <v>-38.404465999999999</v>
-      </c>
-      <c r="E109" s="4" t="s">
+      <c r="G109" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="F109" s="4" t="s">
+      <c r="H109" s="4" t="s">
         <v>194</v>
-      </c>
-      <c r="G109" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="H109" s="4" t="s">
-        <v>196</v>
       </c>
       <c r="I109" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J109" s="6" t="s">
-        <v>17</v>
+        <v>837</v>
       </c>
       <c r="K109" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C110" s="5">
         <v>-5.2116600000000002</v>
@@ -8022,22 +8052,22 @@
         <v>-39.312789000000002</v>
       </c>
       <c r="E110" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="F110" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="G110" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="F110" s="4" t="s">
+      <c r="H110" s="4" t="s">
         <v>200</v>
-      </c>
-      <c r="G110" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="H110" s="4" t="s">
-        <v>202</v>
       </c>
       <c r="I110" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J110" s="6" t="s">
-        <v>839</v>
+        <v>804</v>
       </c>
       <c r="K110" s="6" t="s">
         <v>18</v>
@@ -8045,10 +8075,10 @@
     </row>
     <row r="111" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C111" s="5">
         <v>-3.7752400000000002</v>
@@ -8057,22 +8087,22 @@
         <v>-40.496578999999997</v>
       </c>
       <c r="E111" s="4" t="s">
+        <v>608</v>
+      </c>
+      <c r="F111" s="4" t="s">
+        <v>609</v>
+      </c>
+      <c r="G111" s="4" t="s">
         <v>610</v>
       </c>
-      <c r="F111" s="4" t="s">
+      <c r="H111" s="4" t="s">
         <v>611</v>
-      </c>
-      <c r="G111" s="4" t="s">
-        <v>612</v>
-      </c>
-      <c r="H111" s="4" t="s">
-        <v>613</v>
       </c>
       <c r="I111" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J111" s="6" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="K111" s="6" t="s">
         <v>18</v>
@@ -8080,10 +8110,10 @@
     </row>
     <row r="112" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="C112" s="5">
         <v>-3.9438659999999999</v>
@@ -8092,16 +8122,16 @@
         <v>-40.889215999999998</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F112" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="G112" s="4" t="s">
+        <v>615</v>
+      </c>
+      <c r="H112" s="4" t="s">
         <v>616</v>
-      </c>
-      <c r="G112" s="4" t="s">
-        <v>617</v>
-      </c>
-      <c r="H112" s="4" t="s">
-        <v>618</v>
       </c>
       <c r="I112" s="4" t="s">
         <v>101</v>
@@ -8115,10 +8145,10 @@
     </row>
     <row r="113" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="C113" s="5">
         <v>-4.7911549999999998</v>
@@ -8127,22 +8157,22 @@
         <v>-40.827958000000002</v>
       </c>
       <c r="E113" s="4" t="s">
+        <v>619</v>
+      </c>
+      <c r="F113" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="G113" s="4" t="s">
         <v>621</v>
       </c>
-      <c r="F113" s="4" t="s">
+      <c r="H113" s="4" t="s">
         <v>622</v>
-      </c>
-      <c r="G113" s="4" t="s">
-        <v>623</v>
-      </c>
-      <c r="H113" s="4" t="s">
-        <v>624</v>
       </c>
       <c r="I113" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J113" s="6" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="K113" s="6" t="s">
         <v>18</v>
@@ -8150,10 +8180,10 @@
     </row>
     <row r="114" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C114" s="5">
         <v>-3.4767329999999999</v>
@@ -8162,16 +8192,16 @@
         <v>-39.541499999999999</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="F114" s="4" t="s">
+        <v>625</v>
+      </c>
+      <c r="G114" s="4" t="s">
+        <v>626</v>
+      </c>
+      <c r="H114" s="4" t="s">
         <v>627</v>
-      </c>
-      <c r="G114" s="4" t="s">
-        <v>628</v>
-      </c>
-      <c r="H114" s="4" t="s">
-        <v>629</v>
       </c>
       <c r="I114" s="4" t="s">
         <v>101</v>
@@ -8185,10 +8215,10 @@
     </row>
     <row r="115" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="C115" s="5">
         <v>-4.5871829999999996</v>
@@ -8197,16 +8227,16 @@
         <v>-38.620182999999997</v>
       </c>
       <c r="E115" s="4" t="s">
+        <v>630</v>
+      </c>
+      <c r="F115" s="4" t="s">
+        <v>631</v>
+      </c>
+      <c r="G115" s="4" t="s">
         <v>632</v>
       </c>
-      <c r="F115" s="4" t="s">
+      <c r="H115" s="4" t="s">
         <v>633</v>
-      </c>
-      <c r="G115" s="4" t="s">
-        <v>634</v>
-      </c>
-      <c r="H115" s="4" t="s">
-        <v>635</v>
       </c>
       <c r="I115" s="4" t="s">
         <v>101</v>
@@ -8220,10 +8250,10 @@
     </row>
     <row r="116" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C116" s="5">
         <v>-3.4662999999999999</v>
@@ -8232,16 +8262,16 @@
         <v>-40.395716</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F116" s="4" t="s">
+        <v>636</v>
+      </c>
+      <c r="G116" s="4" t="s">
+        <v>637</v>
+      </c>
+      <c r="H116" s="4" t="s">
         <v>638</v>
-      </c>
-      <c r="G116" s="4" t="s">
-        <v>639</v>
-      </c>
-      <c r="H116" s="4" t="s">
-        <v>640</v>
       </c>
       <c r="I116" s="4" t="s">
         <v>151</v>
@@ -8255,10 +8285,10 @@
     </row>
     <row r="117" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="C117" s="5">
         <v>-3.2141000000000002</v>
@@ -8267,16 +8297,16 @@
         <v>-40.864533000000002</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F117" s="4" t="s">
+        <v>641</v>
+      </c>
+      <c r="G117" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="H117" s="4" t="s">
         <v>643</v>
-      </c>
-      <c r="G117" s="4" t="s">
-        <v>644</v>
-      </c>
-      <c r="H117" s="4" t="s">
-        <v>645</v>
       </c>
       <c r="I117" s="4" t="s">
         <v>101</v>
@@ -8290,10 +8320,10 @@
     </row>
     <row r="118" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="C118" s="5">
         <v>-5.0508829999999998</v>
@@ -8302,16 +8332,16 @@
         <v>-37.779632999999997</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="F118" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="G118" s="4" t="s">
+        <v>647</v>
+      </c>
+      <c r="H118" s="4" t="s">
         <v>648</v>
-      </c>
-      <c r="G118" s="4" t="s">
-        <v>649</v>
-      </c>
-      <c r="H118" s="4" t="s">
-        <v>650</v>
       </c>
       <c r="I118" s="4" t="s">
         <v>151</v>
@@ -8323,12 +8353,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C119" s="5">
         <v>-5.1876949999999997</v>
@@ -8340,19 +8370,19 @@
         <v>76</v>
       </c>
       <c r="F119" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="G119" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="H119" s="4" t="s">
         <v>205</v>
-      </c>
-      <c r="G119" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="H119" s="4" t="s">
-        <v>207</v>
       </c>
       <c r="I119" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J119" s="6" t="s">
-        <v>839</v>
+        <v>804</v>
       </c>
       <c r="K119" s="6" t="s">
         <v>18</v>
@@ -8360,10 +8390,10 @@
     </row>
     <row r="120" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C120" s="5">
         <v>-5.5281140000000004</v>
@@ -8375,19 +8405,19 @@
         <v>76</v>
       </c>
       <c r="F120" s="4" t="s">
+        <v>651</v>
+      </c>
+      <c r="G120" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="H120" s="4" t="s">
         <v>653</v>
-      </c>
-      <c r="G120" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="H120" s="4" t="s">
-        <v>655</v>
       </c>
       <c r="I120" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J120" s="6" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="K120" s="6" t="s">
         <v>18</v>
@@ -8395,10 +8425,10 @@
     </row>
     <row r="121" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C121" s="5">
         <v>-4.338266</v>
@@ -8410,13 +8440,13 @@
         <v>104</v>
       </c>
       <c r="F121" s="4" t="s">
+        <v>656</v>
+      </c>
+      <c r="G121" s="4" t="s">
+        <v>657</v>
+      </c>
+      <c r="H121" s="4" t="s">
         <v>658</v>
-      </c>
-      <c r="G121" s="4" t="s">
-        <v>659</v>
-      </c>
-      <c r="H121" s="4" t="s">
-        <v>660</v>
       </c>
       <c r="I121" s="4" t="s">
         <v>101</v>
@@ -8430,10 +8460,10 @@
     </row>
     <row r="122" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C122" s="5">
         <v>-4.2869089999999996</v>
@@ -8445,10 +8475,10 @@
         <v>36</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="H122" s="4" t="s">
         <v>83</v>
@@ -8457,7 +8487,7 @@
         <v>151</v>
       </c>
       <c r="J122" s="6" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="K122" s="6" t="s">
         <v>18</v>
@@ -8465,10 +8495,10 @@
     </row>
     <row r="123" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C123" s="5">
         <v>-3.372366</v>
@@ -8477,16 +8507,16 @@
         <v>-39.299633</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F123" s="4" t="s">
+        <v>665</v>
+      </c>
+      <c r="G123" s="4" t="s">
+        <v>666</v>
+      </c>
+      <c r="H123" s="4" t="s">
         <v>667</v>
-      </c>
-      <c r="G123" s="4" t="s">
-        <v>668</v>
-      </c>
-      <c r="H123" s="4" t="s">
-        <v>669</v>
       </c>
       <c r="I123" s="4" t="s">
         <v>151</v>
@@ -8495,15 +8525,15 @@
         <v>17</v>
       </c>
       <c r="K123" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="124" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C124" s="5">
         <v>-2.8939659999999998</v>
@@ -8512,16 +8542,16 @@
         <v>-40.223399999999998</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F124" s="4" t="s">
+        <v>670</v>
+      </c>
+      <c r="G124" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="H124" s="4" t="s">
         <v>672</v>
-      </c>
-      <c r="G124" s="4" t="s">
-        <v>673</v>
-      </c>
-      <c r="H124" s="4" t="s">
-        <v>674</v>
       </c>
       <c r="I124" s="4" t="s">
         <v>101</v>
@@ -8535,10 +8565,10 @@
     </row>
     <row r="125" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="C125" s="5">
         <v>-4.7071329999999998</v>
@@ -8550,10 +8580,10 @@
         <v>25</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="H125" s="4" t="s">
         <v>27</v>
@@ -8570,10 +8600,10 @@
     </row>
     <row r="126" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="C126" s="5">
         <v>-4.0460330000000004</v>
@@ -8582,16 +8612,16 @@
         <v>-38.206032999999998</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F126" s="4" t="s">
+        <v>679</v>
+      </c>
+      <c r="G126" s="4" t="s">
+        <v>680</v>
+      </c>
+      <c r="H126" s="4" t="s">
         <v>681</v>
-      </c>
-      <c r="G126" s="4" t="s">
-        <v>682</v>
-      </c>
-      <c r="H126" s="4" t="s">
-        <v>683</v>
       </c>
       <c r="I126" s="4" t="s">
         <v>101</v>
@@ -8605,10 +8635,10 @@
     </row>
     <row r="127" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="C127" s="5">
         <v>-5.5796159999999997</v>
@@ -8617,16 +8647,16 @@
         <v>-38.288649999999997</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F127" s="4" t="s">
+        <v>684</v>
+      </c>
+      <c r="G127" s="4" t="s">
+        <v>685</v>
+      </c>
+      <c r="H127" s="4" t="s">
         <v>686</v>
-      </c>
-      <c r="G127" s="4" t="s">
-        <v>687</v>
-      </c>
-      <c r="H127" s="4" t="s">
-        <v>688</v>
       </c>
       <c r="I127" s="4" t="s">
         <v>151</v>
@@ -8640,10 +8670,10 @@
     </row>
     <row r="128" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="C128" s="5">
         <v>-5.3889829999999996</v>
@@ -8652,16 +8682,16 @@
         <v>-38.911766</v>
       </c>
       <c r="E128" s="4" t="s">
+        <v>689</v>
+      </c>
+      <c r="F128" s="4" t="s">
+        <v>690</v>
+      </c>
+      <c r="G128" s="4" t="s">
         <v>691</v>
       </c>
-      <c r="F128" s="4" t="s">
+      <c r="H128" s="4" t="s">
         <v>692</v>
-      </c>
-      <c r="G128" s="4" t="s">
-        <v>693</v>
-      </c>
-      <c r="H128" s="4" t="s">
-        <v>694</v>
       </c>
       <c r="I128" s="4" t="s">
         <v>101</v>
@@ -8675,10 +8705,10 @@
     </row>
     <row r="129" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="C129" s="5">
         <v>-5.9808000000000003</v>
@@ -8687,16 +8717,16 @@
         <v>-38.884349999999998</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="F129" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="G129" s="4" t="s">
+        <v>696</v>
+      </c>
+      <c r="H129" s="4" t="s">
         <v>697</v>
-      </c>
-      <c r="G129" s="4" t="s">
-        <v>698</v>
-      </c>
-      <c r="H129" s="4" t="s">
-        <v>699</v>
       </c>
       <c r="I129" s="4" t="s">
         <v>101</v>
@@ -8710,10 +8740,10 @@
     </row>
     <row r="130" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="C130" s="5">
         <v>-3.5994000000000002</v>
@@ -8722,16 +8752,16 @@
         <v>-38.898966000000001</v>
       </c>
       <c r="E130" s="4" t="s">
+        <v>700</v>
+      </c>
+      <c r="F130" s="4" t="s">
+        <v>701</v>
+      </c>
+      <c r="G130" s="4" t="s">
         <v>702</v>
       </c>
-      <c r="F130" s="4" t="s">
+      <c r="H130" s="4" t="s">
         <v>703</v>
-      </c>
-      <c r="G130" s="4" t="s">
-        <v>704</v>
-      </c>
-      <c r="H130" s="4" t="s">
-        <v>705</v>
       </c>
       <c r="I130" s="4" t="s">
         <v>101</v>
@@ -8745,10 +8775,10 @@
     </row>
     <row r="131" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="C131" s="5">
         <v>-4.1112159999999998</v>
@@ -8757,13 +8787,13 @@
         <v>-39.226599999999998</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="G131" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="H131" s="4" t="s">
         <v>167</v>
@@ -8780,10 +8810,10 @@
     </row>
     <row r="132" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="C132" s="5">
         <v>-3.3707829999999999</v>
@@ -8792,16 +8822,16 @@
         <v>-39.293933000000003</v>
       </c>
       <c r="E132" s="4" t="s">
+        <v>710</v>
+      </c>
+      <c r="F132" s="4" t="s">
+        <v>711</v>
+      </c>
+      <c r="G132" s="4" t="s">
         <v>712</v>
       </c>
-      <c r="F132" s="4" t="s">
+      <c r="H132" s="4" t="s">
         <v>713</v>
-      </c>
-      <c r="G132" s="4" t="s">
-        <v>714</v>
-      </c>
-      <c r="H132" s="4" t="s">
-        <v>715</v>
       </c>
       <c r="I132" s="4" t="s">
         <v>101</v>
@@ -8815,10 +8845,10 @@
     </row>
     <row r="133" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="C133" s="5">
         <v>-5.8117999999999999</v>
@@ -8827,22 +8857,22 @@
         <v>-39.429194000000003</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F133" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="G133" s="4" t="s">
+        <v>717</v>
+      </c>
+      <c r="H133" s="4" t="s">
         <v>718</v>
-      </c>
-      <c r="G133" s="4" t="s">
-        <v>719</v>
-      </c>
-      <c r="H133" s="4" t="s">
-        <v>720</v>
       </c>
       <c r="I133" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J133" s="6" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="K133" s="6" t="s">
         <v>18</v>
@@ -8850,10 +8880,10 @@
     </row>
     <row r="134" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C134" s="5">
         <v>-3.304783</v>
@@ -8862,16 +8892,16 @@
         <v>-39.515383</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F134" s="4" t="s">
+        <v>721</v>
+      </c>
+      <c r="G134" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="H134" s="4" t="s">
         <v>723</v>
-      </c>
-      <c r="G134" s="4" t="s">
-        <v>724</v>
-      </c>
-      <c r="H134" s="4" t="s">
-        <v>725</v>
       </c>
       <c r="I134" s="4" t="s">
         <v>101</v>
@@ -8885,10 +8915,10 @@
     </row>
     <row r="135" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C135" s="5">
         <v>-5.1408160000000001</v>
@@ -8897,16 +8927,16 @@
         <v>-39.719665999999997</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="F135" s="4" t="s">
+        <v>726</v>
+      </c>
+      <c r="G135" s="4" t="s">
+        <v>727</v>
+      </c>
+      <c r="H135" s="4" t="s">
         <v>728</v>
-      </c>
-      <c r="G135" s="4" t="s">
-        <v>729</v>
-      </c>
-      <c r="H135" s="4" t="s">
-        <v>730</v>
       </c>
       <c r="I135" s="4" t="s">
         <v>101</v>
@@ -8920,10 +8950,10 @@
     </row>
     <row r="136" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="C136" s="5">
         <v>-3.4787659999999998</v>
@@ -8935,13 +8965,13 @@
         <v>48</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="G136" s="4" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="H136" s="4" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="I136" s="4" t="s">
         <v>101</v>
@@ -8955,10 +8985,10 @@
     </row>
     <row r="137" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="C137" s="5">
         <v>-3.5617000000000001</v>
@@ -8967,16 +8997,16 @@
         <v>-39.970649999999999</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F137" s="4" t="s">
+        <v>735</v>
+      </c>
+      <c r="G137" s="4" t="s">
+        <v>736</v>
+      </c>
+      <c r="H137" s="4" t="s">
         <v>737</v>
-      </c>
-      <c r="G137" s="4" t="s">
-        <v>738</v>
-      </c>
-      <c r="H137" s="4" t="s">
-        <v>739</v>
       </c>
       <c r="I137" s="4" t="s">
         <v>151</v>
@@ -8990,10 +9020,10 @@
     </row>
     <row r="138" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C138" s="5">
         <v>-5.4055679999999997</v>
@@ -9005,19 +9035,19 @@
         <v>136</v>
       </c>
       <c r="F138" s="4" t="s">
+        <v>740</v>
+      </c>
+      <c r="G138" s="4" t="s">
+        <v>741</v>
+      </c>
+      <c r="H138" s="4" t="s">
         <v>742</v>
-      </c>
-      <c r="G138" s="4" t="s">
-        <v>743</v>
-      </c>
-      <c r="H138" s="4" t="s">
-        <v>744</v>
       </c>
       <c r="I138" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J138" s="6" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="K138" s="6" t="s">
         <v>18</v>
@@ -9025,10 +9055,10 @@
     </row>
     <row r="139" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="C139" s="5">
         <v>-2.9782660000000001</v>
@@ -9037,16 +9067,16 @@
         <v>-39.890166000000001</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F139" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="G139" s="4" t="s">
+        <v>746</v>
+      </c>
+      <c r="H139" s="4" t="s">
         <v>747</v>
-      </c>
-      <c r="G139" s="4" t="s">
-        <v>748</v>
-      </c>
-      <c r="H139" s="4" t="s">
-        <v>749</v>
       </c>
       <c r="I139" s="4" t="s">
         <v>151</v>
@@ -9060,10 +9090,10 @@
     </row>
     <row r="140" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="C140" s="5">
         <v>-2.9087830000000001</v>
@@ -9072,16 +9102,16 @@
         <v>-40.118616000000003</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="F140" s="4" t="s">
+        <v>750</v>
+      </c>
+      <c r="G140" s="4" t="s">
+        <v>751</v>
+      </c>
+      <c r="H140" s="4" t="s">
         <v>752</v>
-      </c>
-      <c r="G140" s="4" t="s">
-        <v>753</v>
-      </c>
-      <c r="H140" s="4" t="s">
-        <v>754</v>
       </c>
       <c r="I140" s="4" t="s">
         <v>101</v>
@@ -9095,10 +9125,10 @@
     </row>
     <row r="141" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="C141" s="5">
         <v>-3.697114</v>
@@ -9110,19 +9140,19 @@
         <v>48</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="G141" s="4" t="s">
         <v>51</v>
       </c>
       <c r="H141" s="4" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="I141" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J141" s="6" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="K141" s="6" t="s">
         <v>18</v>
@@ -9130,10 +9160,10 @@
     </row>
     <row r="142" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="C142" s="5">
         <v>-3.7188409999999998</v>
@@ -9145,19 +9175,19 @@
         <v>58</v>
       </c>
       <c r="F142" s="4" t="s">
+        <v>759</v>
+      </c>
+      <c r="G142" s="4" t="s">
+        <v>760</v>
+      </c>
+      <c r="H142" s="4" t="s">
         <v>761</v>
-      </c>
-      <c r="G142" s="4" t="s">
-        <v>762</v>
-      </c>
-      <c r="H142" s="4" t="s">
-        <v>763</v>
       </c>
       <c r="I142" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J142" s="6" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="K142" s="6" t="s">
         <v>18</v>
@@ -9165,10 +9195,10 @@
     </row>
     <row r="143" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="C143" s="5">
         <v>-4.0392330000000003</v>
@@ -9177,16 +9207,16 @@
         <v>-40.474150000000002</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="G143" s="4" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="H143" s="4" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="I143" s="4" t="s">
         <v>151</v>
@@ -9200,10 +9230,10 @@
     </row>
     <row r="144" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="C144" s="5">
         <v>-4.1177159999999997</v>
@@ -9212,16 +9242,16 @@
         <v>-40.854500000000002</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F144" s="4" t="s">
+        <v>768</v>
+      </c>
+      <c r="G144" s="4" t="s">
+        <v>769</v>
+      </c>
+      <c r="H144" s="4" t="s">
         <v>770</v>
-      </c>
-      <c r="G144" s="4" t="s">
-        <v>771</v>
-      </c>
-      <c r="H144" s="4" t="s">
-        <v>772</v>
       </c>
       <c r="I144" s="4" t="s">
         <v>101</v>
@@ -9235,10 +9265,10 @@
     </row>
     <row r="145" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="C145" s="5">
         <v>-4.5583349999999996</v>
@@ -9247,22 +9277,22 @@
         <v>-40.729585999999998</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="F145" s="4" t="s">
+        <v>773</v>
+      </c>
+      <c r="G145" s="4" t="s">
+        <v>774</v>
+      </c>
+      <c r="H145" s="4" t="s">
         <v>775</v>
-      </c>
-      <c r="G145" s="4" t="s">
-        <v>776</v>
-      </c>
-      <c r="H145" s="4" t="s">
-        <v>777</v>
       </c>
       <c r="I145" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J145" s="6" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="K145" s="6" t="s">
         <v>18</v>
@@ -9270,10 +9300,10 @@
     </row>
     <row r="146" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="C146" s="5">
         <v>-5.1463979999999996</v>
@@ -9282,22 +9312,22 @@
         <v>-40.670636000000002</v>
       </c>
       <c r="E146" s="4" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="F146" s="4" t="s">
+        <v>778</v>
+      </c>
+      <c r="G146" s="4" t="s">
+        <v>779</v>
+      </c>
+      <c r="H146" s="4" t="s">
         <v>780</v>
-      </c>
-      <c r="G146" s="4" t="s">
-        <v>781</v>
-      </c>
-      <c r="H146" s="4" t="s">
-        <v>782</v>
       </c>
       <c r="I146" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J146" s="6" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="K146" s="6" t="s">
         <v>18</v>
@@ -9305,10 +9335,10 @@
     </row>
     <row r="147" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C147" s="5">
         <v>-4.0631500000000003</v>
@@ -9317,16 +9347,16 @@
         <v>-40.957650000000001</v>
       </c>
       <c r="E147" s="4" t="s">
+        <v>783</v>
+      </c>
+      <c r="F147" s="4" t="s">
+        <v>784</v>
+      </c>
+      <c r="G147" s="4" t="s">
         <v>785</v>
       </c>
-      <c r="F147" s="4" t="s">
+      <c r="H147" s="4" t="s">
         <v>786</v>
-      </c>
-      <c r="G147" s="4" t="s">
-        <v>787</v>
-      </c>
-      <c r="H147" s="4" t="s">
-        <v>788</v>
       </c>
       <c r="I147" s="4" t="s">
         <v>101</v>
@@ -9335,15 +9365,15 @@
         <v>17</v>
       </c>
       <c r="K147" s="6" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="148" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="C148" s="5">
         <v>-3.4559829999999998</v>
@@ -9352,16 +9382,16 @@
         <v>-40.210115999999999</v>
       </c>
       <c r="E148" s="4" t="s">
+        <v>789</v>
+      </c>
+      <c r="F148" s="4" t="s">
+        <v>790</v>
+      </c>
+      <c r="G148" s="4" t="s">
         <v>791</v>
       </c>
-      <c r="F148" s="4" t="s">
+      <c r="H148" s="4" t="s">
         <v>792</v>
-      </c>
-      <c r="G148" s="4" t="s">
-        <v>793</v>
-      </c>
-      <c r="H148" s="4" t="s">
-        <v>794</v>
       </c>
       <c r="I148" s="4" t="s">
         <v>151</v>
@@ -9375,10 +9405,10 @@
     </row>
     <row r="149" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="C149" s="5">
         <v>-3.5106660000000001</v>
@@ -9387,16 +9417,16 @@
         <v>-40.385066000000002</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="F149" s="4" t="s">
+        <v>795</v>
+      </c>
+      <c r="G149" s="4" t="s">
+        <v>796</v>
+      </c>
+      <c r="H149" s="4" t="s">
         <v>797</v>
-      </c>
-      <c r="G149" s="4" t="s">
-        <v>798</v>
-      </c>
-      <c r="H149" s="4" t="s">
-        <v>799</v>
       </c>
       <c r="I149" s="4" t="s">
         <v>101</v>
@@ -9410,10 +9440,10 @@
     </row>
     <row r="150" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="C150" s="5">
         <v>-3.5546000000000002</v>
@@ -9425,13 +9455,13 @@
         <v>48</v>
       </c>
       <c r="F150" s="4" t="s">
+        <v>800</v>
+      </c>
+      <c r="G150" s="4" t="s">
+        <v>801</v>
+      </c>
+      <c r="H150" s="4" t="s">
         <v>802</v>
-      </c>
-      <c r="G150" s="4" t="s">
-        <v>803</v>
-      </c>
-      <c r="H150" s="4" t="s">
-        <v>804</v>
       </c>
       <c r="I150" s="4" t="s">
         <v>151</v>
@@ -9445,13 +9475,13 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:K150" xr:uid="{4DA12617-6B17-4A0E-9E79-EBA6E19B3138}">
-    <filterColumn colId="2">
+    <filterColumn colId="1">
       <filters>
-        <filter val="-4,761105°"/>
-        <filter val="-5,175606°"/>
-        <filter val="-5,187695°"/>
-        <filter val="-5,210260°"/>
-        <filter val="-5,211660°"/>
+        <filter val="P 113"/>
+        <filter val="P 115"/>
+        <filter val="P 155"/>
+        <filter val="P 195"/>
+        <filter val="P 24"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -9459,12 +9489,13 @@
     <sortCondition ref="B1:B150"/>
   </sortState>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="65" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="63" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D18A476-0271-4A84-BE9E-901865A86FD3}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AC157"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -9495,15 +9526,15 @@
         <v>5</v>
       </c>
       <c r="D1" s="30" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="E1" s="30"/>
       <c r="F1" s="31" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="G1" s="31"/>
       <c r="H1" s="27" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="I1" s="27"/>
       <c r="J1" s="27"/>
@@ -9526,7 +9557,7 @@
       <c r="AA1" s="27"/>
       <c r="AB1" s="27"/>
       <c r="AC1" s="25" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
     </row>
     <row r="2" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9538,18 +9569,18 @@
       <c r="F2" s="31"/>
       <c r="G2" s="31"/>
       <c r="H2" s="26" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="I2" s="26"/>
       <c r="J2" s="26"/>
       <c r="K2" s="9" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="M2" s="27" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="N2" s="27"/>
       <c r="O2" s="27"/>
@@ -9577,67 +9608,67 @@
       <c r="F3" s="31"/>
       <c r="G3" s="31"/>
       <c r="H3" s="8" t="s">
+        <v>812</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>813</v>
+      </c>
+      <c r="J3" s="8" t="s">
         <v>814</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="K3" s="7" t="s">
         <v>815</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="L3" s="7" t="s">
         <v>816</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="M3" s="7" t="s">
         <v>817</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="N3" s="7" t="s">
         <v>818</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="O3" s="7" t="s">
         <v>819</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="P3" s="7" t="s">
         <v>820</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="Q3" s="7" t="s">
         <v>821</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="R3" s="7" t="s">
         <v>822</v>
       </c>
-      <c r="Q3" s="7" t="s">
+      <c r="S3" s="7" t="s">
         <v>823</v>
       </c>
-      <c r="R3" s="7" t="s">
+      <c r="T3" s="7" t="s">
         <v>824</v>
       </c>
-      <c r="S3" s="7" t="s">
+      <c r="U3" s="7" t="s">
         <v>825</v>
       </c>
-      <c r="T3" s="7" t="s">
+      <c r="V3" s="7" t="s">
         <v>826</v>
       </c>
-      <c r="U3" s="7" t="s">
+      <c r="W3" s="7" t="s">
         <v>827</v>
       </c>
-      <c r="V3" s="7" t="s">
+      <c r="X3" s="7" t="s">
         <v>828</v>
       </c>
-      <c r="W3" s="7" t="s">
+      <c r="Y3" s="7" t="s">
         <v>829</v>
       </c>
-      <c r="X3" s="7" t="s">
+      <c r="Z3" s="7" t="s">
         <v>830</v>
       </c>
-      <c r="Y3" s="7" t="s">
+      <c r="AA3" s="7" t="s">
         <v>831</v>
       </c>
-      <c r="Z3" s="7" t="s">
+      <c r="AB3" s="7" t="s">
         <v>832</v>
-      </c>
-      <c r="AA3" s="7" t="s">
-        <v>833</v>
-      </c>
-      <c r="AB3" s="7" t="s">
-        <v>834</v>
       </c>
       <c r="AC3" s="25"/>
     </row>
@@ -9676,7 +9707,7 @@
       <c r="AB4" s="11"/>
       <c r="AC4" s="25"/>
     </row>
-    <row r="5" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="19" t="s">
         <v>96</v>
       </c>
@@ -9719,7 +9750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
         <v>103</v>
       </c>
@@ -9762,7 +9793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="19" t="s">
         <v>109</v>
       </c>
@@ -9805,7 +9836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="19" t="s">
         <v>114</v>
       </c>
@@ -9848,7 +9879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
         <v>120</v>
       </c>
@@ -9891,7 +9922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="19" t="s">
         <v>125</v>
       </c>
@@ -9934,7 +9965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="19" t="s">
         <v>135</v>
       </c>
@@ -10025,7 +10056,7 @@
         <v>5682</v>
       </c>
     </row>
-    <row r="12" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="19" t="s">
         <v>141</v>
       </c>
@@ -10068,15 +10099,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
         <v>147</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="D13" s="21"/>
       <c r="E13" s="21"/>
@@ -10111,7 +10142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="19" t="s">
         <v>159</v>
       </c>
@@ -10121,48 +10152,96 @@
       <c r="C14" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="20"/>
+      <c r="D14" s="24" t="s">
+        <v>855</v>
+      </c>
+      <c r="E14" s="24" t="s">
+        <v>856</v>
+      </c>
+      <c r="F14" s="20">
+        <v>46142</v>
+      </c>
       <c r="G14" s="20">
         <f t="shared" si="0"/>
+        <v>46144</v>
+      </c>
+      <c r="H14" s="12">
+        <v>1977</v>
+      </c>
+      <c r="I14" s="12">
+        <v>2574</v>
+      </c>
+      <c r="J14" s="12">
+        <v>46</v>
+      </c>
+      <c r="K14" s="12">
+        <v>307</v>
+      </c>
+      <c r="L14" s="12">
+        <v>133</v>
+      </c>
+      <c r="M14" s="12">
+        <v>20</v>
+      </c>
+      <c r="N14" s="12">
+        <v>39</v>
+      </c>
+      <c r="O14" s="12">
+        <v>1</v>
+      </c>
+      <c r="P14" s="12">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="12">
+        <v>6</v>
+      </c>
+      <c r="R14" s="12">
+        <v>6</v>
+      </c>
+      <c r="S14" s="12">
+        <v>4</v>
+      </c>
+      <c r="T14" s="12">
+        <v>69</v>
+      </c>
+      <c r="U14" s="12">
         <v>2</v>
       </c>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="12"/>
-      <c r="M14" s="12"/>
-      <c r="N14" s="12"/>
-      <c r="O14" s="12"/>
-      <c r="P14" s="12"/>
-      <c r="Q14" s="12"/>
-      <c r="R14" s="12"/>
-      <c r="S14" s="12"/>
-      <c r="T14" s="12"/>
-      <c r="U14" s="12"/>
-      <c r="V14" s="12"/>
-      <c r="W14" s="12"/>
-      <c r="X14" s="12"/>
-      <c r="Y14" s="12"/>
-      <c r="Z14" s="12"/>
-      <c r="AA14" s="12"/>
-      <c r="AB14" s="12"/>
+      <c r="V14" s="12">
+        <v>0</v>
+      </c>
+      <c r="W14" s="12">
+        <v>1</v>
+      </c>
+      <c r="X14" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="12">
+        <v>2</v>
+      </c>
+      <c r="AA14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="12">
+        <v>2</v>
+      </c>
       <c r="AC14" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>5190</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="C15" s="19" t="s">
         <v>175</v>
-      </c>
-      <c r="B15" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>177</v>
       </c>
       <c r="D15" s="21"/>
       <c r="E15" s="21"/>
@@ -10197,15 +10276,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="19" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D16" s="21"/>
       <c r="E16" s="21"/>
@@ -10240,15 +10319,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="19" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D17" s="21"/>
       <c r="E17" s="21"/>
@@ -10285,13 +10364,13 @@
     </row>
     <row r="18" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="C18" s="19" t="s">
         <v>192</v>
-      </c>
-      <c r="B18" s="19" t="s">
-        <v>193</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>194</v>
       </c>
       <c r="D18" s="21"/>
       <c r="E18" s="21"/>
@@ -10326,58 +10405,106 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="C19" s="19" t="s">
         <v>198</v>
       </c>
-      <c r="B19" s="19" t="s">
-        <v>199</v>
-      </c>
-      <c r="C19" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="20"/>
+      <c r="D19" s="24" t="s">
+        <v>857</v>
+      </c>
+      <c r="E19" s="24" t="s">
+        <v>858</v>
+      </c>
+      <c r="F19" s="20">
+        <v>46142</v>
+      </c>
       <c r="G19" s="20">
         <f t="shared" si="0"/>
+        <v>46144</v>
+      </c>
+      <c r="H19" s="12">
+        <v>397</v>
+      </c>
+      <c r="I19" s="12">
+        <v>888</v>
+      </c>
+      <c r="J19" s="12">
+        <v>21</v>
+      </c>
+      <c r="K19" s="12">
+        <v>93</v>
+      </c>
+      <c r="L19" s="12">
+        <v>46</v>
+      </c>
+      <c r="M19" s="12">
+        <v>8</v>
+      </c>
+      <c r="N19" s="12">
+        <v>7</v>
+      </c>
+      <c r="O19" s="12">
+        <v>0</v>
+      </c>
+      <c r="P19" s="12">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="12">
         <v>2</v>
       </c>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12"/>
-      <c r="K19" s="12"/>
-      <c r="L19" s="12"/>
-      <c r="M19" s="12"/>
-      <c r="N19" s="12"/>
-      <c r="O19" s="12"/>
-      <c r="P19" s="12"/>
-      <c r="Q19" s="12"/>
-      <c r="R19" s="12"/>
-      <c r="S19" s="12"/>
-      <c r="T19" s="12"/>
-      <c r="U19" s="12"/>
-      <c r="V19" s="12"/>
-      <c r="W19" s="12"/>
-      <c r="X19" s="12"/>
-      <c r="Y19" s="12"/>
-      <c r="Z19" s="12"/>
-      <c r="AA19" s="12"/>
-      <c r="AB19" s="12"/>
+      <c r="R19" s="12">
+        <v>2</v>
+      </c>
+      <c r="S19" s="12">
+        <v>6</v>
+      </c>
+      <c r="T19" s="12">
+        <v>15</v>
+      </c>
+      <c r="U19" s="12">
+        <v>0</v>
+      </c>
+      <c r="V19" s="12">
+        <v>0</v>
+      </c>
+      <c r="W19" s="12">
+        <v>0</v>
+      </c>
+      <c r="X19" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB19" s="12">
+        <v>0</v>
+      </c>
       <c r="AC19" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1486</v>
+      </c>
+    </row>
+    <row r="20" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="19" t="s">
+        <v>607</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>608</v>
+      </c>
+      <c r="C20" s="19" t="s">
         <v>609</v>
-      </c>
-      <c r="B20" s="19" t="s">
-        <v>610</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>611</v>
       </c>
       <c r="D20" s="21">
         <v>-3.7752400000000002</v>
@@ -10460,15 +10587,15 @@
         <v>4245</v>
       </c>
     </row>
-    <row r="21" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="19" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="D21" s="21"/>
       <c r="E21" s="21"/>
@@ -10503,15 +10630,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="19" t="s">
+        <v>618</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>619</v>
+      </c>
+      <c r="C22" s="19" t="s">
         <v>620</v>
-      </c>
-      <c r="B22" s="19" t="s">
-        <v>621</v>
-      </c>
-      <c r="C22" s="19" t="s">
-        <v>622</v>
       </c>
       <c r="D22" s="21">
         <v>-4.7911549999999998</v>
@@ -10594,15 +10721,15 @@
         <v>2038</v>
       </c>
     </row>
-    <row r="23" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="19" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="D23" s="21"/>
       <c r="E23" s="21"/>
@@ -10637,15 +10764,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="19" t="s">
+        <v>629</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>630</v>
+      </c>
+      <c r="C24" s="19" t="s">
         <v>631</v>
-      </c>
-      <c r="B24" s="19" t="s">
-        <v>632</v>
-      </c>
-      <c r="C24" s="19" t="s">
-        <v>633</v>
       </c>
       <c r="D24" s="21"/>
       <c r="E24" s="21"/>
@@ -10680,15 +10807,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="19" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="D25" s="21"/>
       <c r="E25" s="21"/>
@@ -10723,15 +10850,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="19" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="D26" s="21"/>
       <c r="E26" s="21"/>
@@ -10766,15 +10893,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="19" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="D27" s="21"/>
       <c r="E27" s="21"/>
@@ -10809,64 +10936,112 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="19" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B28" s="19" t="s">
         <v>76</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>205</v>
-      </c>
-      <c r="D28" s="21"/>
-      <c r="E28" s="21"/>
-      <c r="F28" s="20"/>
+        <v>203</v>
+      </c>
+      <c r="D28" s="24" t="s">
+        <v>859</v>
+      </c>
+      <c r="E28" s="24" t="s">
+        <v>860</v>
+      </c>
+      <c r="F28" s="20">
+        <v>46142</v>
+      </c>
       <c r="G28" s="20">
         <f t="shared" si="0"/>
+        <v>46144</v>
+      </c>
+      <c r="H28" s="12">
+        <v>3309</v>
+      </c>
+      <c r="I28" s="12">
+        <v>4718</v>
+      </c>
+      <c r="J28" s="12">
+        <v>73</v>
+      </c>
+      <c r="K28" s="12">
+        <v>467</v>
+      </c>
+      <c r="L28" s="12">
+        <v>214</v>
+      </c>
+      <c r="M28" s="12">
+        <v>31</v>
+      </c>
+      <c r="N28" s="12">
+        <v>70</v>
+      </c>
+      <c r="O28" s="12">
+        <v>5</v>
+      </c>
+      <c r="P28" s="12">
+        <v>8</v>
+      </c>
+      <c r="Q28" s="12">
+        <v>12</v>
+      </c>
+      <c r="R28" s="12">
+        <v>19</v>
+      </c>
+      <c r="S28" s="12">
+        <v>11</v>
+      </c>
+      <c r="T28" s="12">
+        <v>135</v>
+      </c>
+      <c r="U28" s="12">
         <v>2</v>
       </c>
-      <c r="H28" s="12"/>
-      <c r="I28" s="12"/>
-      <c r="J28" s="12"/>
-      <c r="K28" s="12"/>
-      <c r="L28" s="12"/>
-      <c r="M28" s="12"/>
-      <c r="N28" s="12"/>
-      <c r="O28" s="12"/>
-      <c r="P28" s="12"/>
-      <c r="Q28" s="12"/>
-      <c r="R28" s="12"/>
-      <c r="S28" s="12"/>
-      <c r="T28" s="12"/>
-      <c r="U28" s="12"/>
-      <c r="V28" s="12"/>
-      <c r="W28" s="12"/>
-      <c r="X28" s="12"/>
-      <c r="Y28" s="12"/>
-      <c r="Z28" s="12"/>
-      <c r="AA28" s="12"/>
-      <c r="AB28" s="12"/>
+      <c r="V28" s="12">
+        <v>2</v>
+      </c>
+      <c r="W28" s="12">
+        <v>3</v>
+      </c>
+      <c r="X28" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z28" s="12">
+        <v>4</v>
+      </c>
+      <c r="AA28" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB28" s="12">
+        <v>16</v>
+      </c>
       <c r="AC28" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>9101</v>
+      </c>
+    </row>
+    <row r="29" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B29" s="19" t="s">
         <v>76</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="D29" s="24" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="E29" s="24" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="F29" s="20">
         <v>46139</v>
@@ -10943,15 +11118,15 @@
         <v>2316</v>
       </c>
     </row>
-    <row r="30" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="B30" s="19" t="s">
         <v>104</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="D30" s="21"/>
       <c r="E30" s="21"/>
@@ -10986,15 +11161,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="B31" s="19" t="s">
         <v>36</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="D31" s="21">
         <v>-4.2869089999999996</v>
@@ -11077,15 +11252,15 @@
         <v>1584</v>
       </c>
     </row>
-    <row r="32" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="D32" s="21"/>
       <c r="E32" s="21"/>
@@ -11120,15 +11295,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="D33" s="21"/>
       <c r="E33" s="21"/>
@@ -11163,15 +11338,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="19" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="B34" s="19" t="s">
         <v>25</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="D34" s="21"/>
       <c r="E34" s="21"/>
@@ -11206,15 +11381,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="D35" s="21"/>
       <c r="E35" s="21"/>
@@ -11249,15 +11424,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="D36" s="21"/>
       <c r="E36" s="21"/>
@@ -11292,15 +11467,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
+        <v>688</v>
+      </c>
+      <c r="B37" s="19" t="s">
+        <v>689</v>
+      </c>
+      <c r="C37" s="19" t="s">
         <v>690</v>
-      </c>
-      <c r="B37" s="19" t="s">
-        <v>691</v>
-      </c>
-      <c r="C37" s="19" t="s">
-        <v>692</v>
       </c>
       <c r="D37" s="21"/>
       <c r="E37" s="21"/>
@@ -11335,15 +11510,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="19" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="D38" s="21"/>
       <c r="E38" s="21"/>
@@ -11378,15 +11553,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="19" t="s">
+        <v>699</v>
+      </c>
+      <c r="B39" s="19" t="s">
+        <v>700</v>
+      </c>
+      <c r="C39" s="19" t="s">
         <v>701</v>
-      </c>
-      <c r="B39" s="19" t="s">
-        <v>702</v>
-      </c>
-      <c r="C39" s="19" t="s">
-        <v>703</v>
       </c>
       <c r="D39" s="21"/>
       <c r="E39" s="21"/>
@@ -11421,15 +11596,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="19" t="s">
+        <v>705</v>
+      </c>
+      <c r="B40" s="19" t="s">
+        <v>706</v>
+      </c>
+      <c r="C40" s="19" t="s">
         <v>707</v>
-      </c>
-      <c r="B40" s="19" t="s">
-        <v>708</v>
-      </c>
-      <c r="C40" s="19" t="s">
-        <v>709</v>
       </c>
       <c r="D40" s="21"/>
       <c r="E40" s="21"/>
@@ -11464,15 +11639,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="19" t="s">
+        <v>709</v>
+      </c>
+      <c r="B41" s="19" t="s">
+        <v>710</v>
+      </c>
+      <c r="C41" s="19" t="s">
         <v>711</v>
-      </c>
-      <c r="B41" s="19" t="s">
-        <v>712</v>
-      </c>
-      <c r="C41" s="19" t="s">
-        <v>713</v>
       </c>
       <c r="D41" s="21"/>
       <c r="E41" s="21"/>
@@ -11507,21 +11682,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="19" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="B42" s="19" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C42" s="19" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="D42" s="24" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="E42" s="24" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="F42" s="20">
         <v>46139</v>
@@ -11598,15 +11773,15 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="43" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="19" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="B43" s="19" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="D43" s="21"/>
       <c r="E43" s="21"/>
@@ -11641,15 +11816,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="19" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="B44" s="19" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="D44" s="21"/>
       <c r="E44" s="21"/>
@@ -11684,15 +11859,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="19" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="B45" s="19" t="s">
         <v>48</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="D45" s="21"/>
       <c r="E45" s="21"/>
@@ -11727,15 +11902,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="19" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="B46" s="19" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C46" s="19" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="D46" s="21"/>
       <c r="E46" s="21"/>
@@ -11770,15 +11945,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="19" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="B47" s="19" t="s">
         <v>136</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="D47" s="21">
         <v>-5.4055679999999997</v>
@@ -11861,15 +12036,15 @@
         <v>2429</v>
       </c>
     </row>
-    <row r="48" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="19" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="B48" s="19" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C48" s="19" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="D48" s="21"/>
       <c r="E48" s="21"/>
@@ -11904,15 +12079,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="19" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="B49" s="19" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C49" s="19" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="D49" s="21"/>
       <c r="E49" s="21"/>
@@ -11947,15 +12122,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="19" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="B50" s="19" t="s">
         <v>48</v>
       </c>
       <c r="C50" s="19" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="D50" s="21">
         <v>-3.697114</v>
@@ -12038,15 +12213,15 @@
         <v>2483</v>
       </c>
     </row>
-    <row r="51" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="19" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="B51" s="19" t="s">
         <v>58</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D51" s="21">
         <v>-3.7188409999999998</v>
@@ -12129,15 +12304,15 @@
         <v>4263</v>
       </c>
     </row>
-    <row r="52" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="19" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="B52" s="19" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="C52" s="19" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="D52" s="21"/>
       <c r="E52" s="21"/>
@@ -12172,15 +12347,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="19" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="B53" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="D53" s="21"/>
       <c r="E53" s="21"/>
@@ -12215,15 +12390,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="19" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="B54" s="19" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="C54" s="19" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="D54" s="21">
         <v>-4.5583349999999996</v>
@@ -12306,15 +12481,15 @@
         <v>1560</v>
       </c>
     </row>
-    <row r="55" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="19" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="B55" s="19" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="D55" s="21">
         <v>-5.1463979999999996</v>
@@ -12397,15 +12572,15 @@
         <v>1864</v>
       </c>
     </row>
-    <row r="56" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="19" t="s">
+        <v>782</v>
+      </c>
+      <c r="B56" s="19" t="s">
+        <v>783</v>
+      </c>
+      <c r="C56" s="19" t="s">
         <v>784</v>
-      </c>
-      <c r="B56" s="19" t="s">
-        <v>785</v>
-      </c>
-      <c r="C56" s="19" t="s">
-        <v>786</v>
       </c>
       <c r="D56" s="21"/>
       <c r="E56" s="21"/>
@@ -12440,15 +12615,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="19" t="s">
+        <v>788</v>
+      </c>
+      <c r="B57" s="19" t="s">
+        <v>789</v>
+      </c>
+      <c r="C57" s="19" t="s">
         <v>790</v>
-      </c>
-      <c r="B57" s="19" t="s">
-        <v>791</v>
-      </c>
-      <c r="C57" s="19" t="s">
-        <v>792</v>
       </c>
       <c r="D57" s="21"/>
       <c r="E57" s="21"/>
@@ -12483,15 +12658,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="19" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="B58" s="19" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="C58" s="19" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="D58" s="21"/>
       <c r="E58" s="21"/>
@@ -12526,15 +12701,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="19" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="B59" s="19" t="s">
         <v>48</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="D59" s="21"/>
       <c r="E59" s="21"/>
@@ -12569,15 +12744,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="19" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B60" s="19" t="s">
         <v>148</v>
       </c>
       <c r="C60" s="19" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D60" s="21">
         <v>-4.228675</v>
@@ -12660,15 +12835,15 @@
         <v>2567</v>
       </c>
     </row>
-    <row r="61" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="19" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B61" s="19" t="s">
         <v>148</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D61" s="21"/>
       <c r="E61" s="21"/>
@@ -12703,15 +12878,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="19" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B62" s="19" t="s">
         <v>148</v>
       </c>
       <c r="C62" s="19" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D62" s="21"/>
       <c r="E62" s="21"/>
@@ -12746,15 +12921,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="19" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B63" s="19" t="s">
         <v>87</v>
       </c>
       <c r="C63" s="19" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D63" s="21">
         <v>-4.5644640000000001</v>
@@ -12837,15 +13012,15 @@
         <v>2906</v>
       </c>
     </row>
-    <row r="64" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="19" t="s">
+        <v>335</v>
+      </c>
+      <c r="B64" s="19" t="s">
+        <v>336</v>
+      </c>
+      <c r="C64" s="19" t="s">
         <v>337</v>
-      </c>
-      <c r="B64" s="19" t="s">
-        <v>338</v>
-      </c>
-      <c r="C64" s="19" t="s">
-        <v>339</v>
       </c>
       <c r="D64" s="21"/>
       <c r="E64" s="21"/>
@@ -12880,15 +13055,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="19" t="s">
+        <v>341</v>
+      </c>
+      <c r="B65" s="19" t="s">
+        <v>342</v>
+      </c>
+      <c r="C65" s="19" t="s">
         <v>343</v>
-      </c>
-      <c r="B65" s="19" t="s">
-        <v>344</v>
-      </c>
-      <c r="C65" s="19" t="s">
-        <v>345</v>
       </c>
       <c r="D65" s="21"/>
       <c r="E65" s="21"/>
@@ -12923,7 +13098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="19" t="s">
         <v>130</v>
       </c>
@@ -13014,15 +13189,15 @@
         <v>5492</v>
       </c>
     </row>
-    <row r="67" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="19" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B67" s="19" t="s">
         <v>12</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D67" s="21">
         <v>-4.702947</v>
@@ -13105,15 +13280,15 @@
         <v>3330</v>
       </c>
     </row>
-    <row r="68" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="19" t="s">
+        <v>351</v>
+      </c>
+      <c r="B68" s="19" t="s">
+        <v>352</v>
+      </c>
+      <c r="C68" s="19" t="s">
         <v>353</v>
-      </c>
-      <c r="B68" s="19" t="s">
-        <v>354</v>
-      </c>
-      <c r="C68" s="19" t="s">
-        <v>355</v>
       </c>
       <c r="D68" s="21"/>
       <c r="E68" s="21"/>
@@ -13150,13 +13325,13 @@
     </row>
     <row r="69" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="19" t="s">
+        <v>357</v>
+      </c>
+      <c r="B69" s="19" t="s">
+        <v>358</v>
+      </c>
+      <c r="C69" s="19" t="s">
         <v>359</v>
-      </c>
-      <c r="B69" s="19" t="s">
-        <v>360</v>
-      </c>
-      <c r="C69" s="19" t="s">
-        <v>361</v>
       </c>
       <c r="D69" s="21"/>
       <c r="E69" s="21"/>
@@ -13193,13 +13368,13 @@
     </row>
     <row r="70" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="19" t="s">
+        <v>362</v>
+      </c>
+      <c r="B70" s="19" t="s">
+        <v>363</v>
+      </c>
+      <c r="C70" s="19" t="s">
         <v>364</v>
-      </c>
-      <c r="B70" s="19" t="s">
-        <v>365</v>
-      </c>
-      <c r="C70" s="19" t="s">
-        <v>366</v>
       </c>
       <c r="D70" s="21"/>
       <c r="E70" s="21"/>
@@ -13234,15 +13409,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="19" t="s">
+        <v>368</v>
+      </c>
+      <c r="B71" s="19" t="s">
+        <v>369</v>
+      </c>
+      <c r="C71" s="19" t="s">
         <v>370</v>
-      </c>
-      <c r="B71" s="19" t="s">
-        <v>371</v>
-      </c>
-      <c r="C71" s="19" t="s">
-        <v>372</v>
       </c>
       <c r="D71" s="21"/>
       <c r="E71" s="21"/>
@@ -13277,15 +13452,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="19" t="s">
+        <v>374</v>
+      </c>
+      <c r="B72" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="C72" s="19" t="s">
         <v>376</v>
-      </c>
-      <c r="B72" s="19" t="s">
-        <v>377</v>
-      </c>
-      <c r="C72" s="19" t="s">
-        <v>378</v>
       </c>
       <c r="D72" s="21"/>
       <c r="E72" s="21"/>
@@ -13320,15 +13495,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="19" t="s">
+        <v>380</v>
+      </c>
+      <c r="B73" s="19" t="s">
+        <v>381</v>
+      </c>
+      <c r="C73" s="19" t="s">
         <v>382</v>
-      </c>
-      <c r="B73" s="19" t="s">
-        <v>383</v>
-      </c>
-      <c r="C73" s="19" t="s">
-        <v>384</v>
       </c>
       <c r="D73" s="21"/>
       <c r="E73" s="21"/>
@@ -13363,15 +13538,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="19" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B74" s="19" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C74" s="19" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D74" s="21"/>
       <c r="E74" s="21"/>
@@ -13406,15 +13581,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="19" t="s">
+        <v>391</v>
+      </c>
+      <c r="B75" s="19" t="s">
+        <v>392</v>
+      </c>
+      <c r="C75" s="19" t="s">
         <v>393</v>
-      </c>
-      <c r="B75" s="19" t="s">
-        <v>394</v>
-      </c>
-      <c r="C75" s="19" t="s">
-        <v>395</v>
       </c>
       <c r="D75" s="21"/>
       <c r="E75" s="21"/>
@@ -13449,15 +13624,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="19" t="s">
+        <v>397</v>
+      </c>
+      <c r="B76" s="19" t="s">
+        <v>398</v>
+      </c>
+      <c r="C76" s="19" t="s">
         <v>399</v>
-      </c>
-      <c r="B76" s="19" t="s">
-        <v>400</v>
-      </c>
-      <c r="C76" s="19" t="s">
-        <v>401</v>
       </c>
       <c r="D76" s="21"/>
       <c r="E76" s="21"/>
@@ -13492,15 +13667,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="19" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B77" s="19" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C77" s="19" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D77" s="21"/>
       <c r="E77" s="21"/>
@@ -13535,15 +13710,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="19" t="s">
+        <v>408</v>
+      </c>
+      <c r="B78" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="C78" s="19" t="s">
         <v>410</v>
-      </c>
-      <c r="B78" s="19" t="s">
-        <v>411</v>
-      </c>
-      <c r="C78" s="19" t="s">
-        <v>412</v>
       </c>
       <c r="D78" s="21"/>
       <c r="E78" s="21"/>
@@ -13578,15 +13753,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="B79" s="19" t="s">
+        <v>415</v>
+      </c>
+      <c r="C79" s="19" t="s">
         <v>416</v>
-      </c>
-      <c r="B79" s="19" t="s">
-        <v>417</v>
-      </c>
-      <c r="C79" s="19" t="s">
-        <v>418</v>
       </c>
       <c r="D79" s="21"/>
       <c r="E79" s="21"/>
@@ -13621,15 +13796,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="19" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B80" s="19" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C80" s="19" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D80" s="21"/>
       <c r="E80" s="21"/>
@@ -13664,15 +13839,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="19" t="s">
+        <v>425</v>
+      </c>
+      <c r="B81" s="19" t="s">
+        <v>426</v>
+      </c>
+      <c r="C81" s="19" t="s">
         <v>427</v>
-      </c>
-      <c r="B81" s="19" t="s">
-        <v>428</v>
-      </c>
-      <c r="C81" s="19" t="s">
-        <v>429</v>
       </c>
       <c r="D81" s="21"/>
       <c r="E81" s="21"/>
@@ -13707,15 +13882,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="19" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B82" s="19" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C82" s="19" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D82" s="21"/>
       <c r="E82" s="21"/>
@@ -13750,15 +13925,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="19" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B83" s="19" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C83" s="19" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D83" s="21">
         <v>-4.3755519999999999</v>
@@ -13841,15 +14016,15 @@
         <v>6031</v>
       </c>
     </row>
-    <row r="84" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="19" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B84" s="19" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C84" s="19" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D84" s="21"/>
       <c r="E84" s="21"/>
@@ -13884,15 +14059,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="19" t="s">
+        <v>445</v>
+      </c>
+      <c r="B85" s="19" t="s">
+        <v>446</v>
+      </c>
+      <c r="C85" s="19" t="s">
         <v>447</v>
-      </c>
-      <c r="B85" s="19" t="s">
-        <v>448</v>
-      </c>
-      <c r="C85" s="19" t="s">
-        <v>449</v>
       </c>
       <c r="D85" s="21"/>
       <c r="E85" s="21"/>
@@ -13927,15 +14102,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="19" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B86" s="19" t="s">
         <v>97</v>
       </c>
       <c r="C86" s="19" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D86" s="21"/>
       <c r="E86" s="21"/>
@@ -13970,15 +14145,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B87" s="19" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C87" s="19" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="D87" s="21"/>
       <c r="E87" s="21"/>
@@ -14013,15 +14188,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="19" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B88" s="19" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C88" s="19" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="D88" s="21">
         <v>-3.6184599999999998</v>
@@ -14104,15 +14279,15 @@
         <v>6697</v>
       </c>
     </row>
-    <row r="89" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="19" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B89" s="19" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C89" s="19" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D89" s="21"/>
       <c r="E89" s="21"/>
@@ -14147,21 +14322,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="19" t="s">
+        <v>471</v>
+      </c>
+      <c r="B90" s="19" t="s">
+        <v>472</v>
+      </c>
+      <c r="C90" s="19" t="s">
         <v>473</v>
       </c>
-      <c r="B90" s="19" t="s">
-        <v>474</v>
-      </c>
-      <c r="C90" s="19" t="s">
-        <v>475</v>
-      </c>
       <c r="D90" s="24" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="E90" s="24" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="F90" s="20">
         <v>46139</v>
@@ -14238,15 +14413,15 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="91" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="19" t="s">
+        <v>475</v>
+      </c>
+      <c r="B91" s="19" t="s">
+        <v>476</v>
+      </c>
+      <c r="C91" s="19" t="s">
         <v>477</v>
-      </c>
-      <c r="B91" s="19" t="s">
-        <v>478</v>
-      </c>
-      <c r="C91" s="19" t="s">
-        <v>479</v>
       </c>
       <c r="D91" s="21"/>
       <c r="E91" s="21"/>
@@ -14281,15 +14456,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="19" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B92" s="19" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C92" s="19" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="D92" s="21"/>
       <c r="E92" s="21"/>
@@ -14324,58 +14499,106 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="19" t="s">
+        <v>485</v>
+      </c>
+      <c r="B93" s="19" t="s">
+        <v>486</v>
+      </c>
+      <c r="C93" s="19" t="s">
         <v>487</v>
       </c>
-      <c r="B93" s="19" t="s">
-        <v>488</v>
-      </c>
-      <c r="C93" s="19" t="s">
-        <v>489</v>
-      </c>
-      <c r="D93" s="21"/>
-      <c r="E93" s="21"/>
-      <c r="F93" s="20"/>
+      <c r="D93" s="24" t="s">
+        <v>861</v>
+      </c>
+      <c r="E93" s="24" t="s">
+        <v>862</v>
+      </c>
+      <c r="F93" s="20">
+        <v>46142</v>
+      </c>
       <c r="G93" s="20">
         <f t="shared" si="3"/>
+        <v>46144</v>
+      </c>
+      <c r="H93" s="12">
+        <v>279</v>
+      </c>
+      <c r="I93" s="12">
+        <v>558</v>
+      </c>
+      <c r="J93" s="12">
+        <v>48</v>
+      </c>
+      <c r="K93" s="12">
+        <v>68</v>
+      </c>
+      <c r="L93" s="12">
+        <v>25</v>
+      </c>
+      <c r="M93" s="12">
+        <v>4</v>
+      </c>
+      <c r="N93" s="12">
         <v>2</v>
       </c>
-      <c r="H93" s="12"/>
-      <c r="I93" s="12"/>
-      <c r="J93" s="12"/>
-      <c r="K93" s="12"/>
-      <c r="L93" s="12"/>
-      <c r="M93" s="12"/>
-      <c r="N93" s="12"/>
-      <c r="O93" s="12"/>
-      <c r="P93" s="12"/>
-      <c r="Q93" s="12"/>
-      <c r="R93" s="12"/>
-      <c r="S93" s="12"/>
-      <c r="T93" s="12"/>
-      <c r="U93" s="12"/>
-      <c r="V93" s="12"/>
-      <c r="W93" s="12"/>
-      <c r="X93" s="12"/>
-      <c r="Y93" s="12"/>
-      <c r="Z93" s="12"/>
-      <c r="AA93" s="12"/>
-      <c r="AB93" s="12"/>
+      <c r="O93" s="12">
+        <v>0</v>
+      </c>
+      <c r="P93" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="12">
+        <v>0</v>
+      </c>
+      <c r="R93" s="12">
+        <v>1</v>
+      </c>
+      <c r="S93" s="12">
+        <v>1</v>
+      </c>
+      <c r="T93" s="12">
+        <v>2</v>
+      </c>
+      <c r="U93" s="12">
+        <v>0</v>
+      </c>
+      <c r="V93" s="12">
+        <v>0</v>
+      </c>
+      <c r="W93" s="12">
+        <v>0</v>
+      </c>
+      <c r="X93" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y93" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z93" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA93" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB93" s="12">
+        <v>0</v>
+      </c>
       <c r="AC93" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="94" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="19" t="s">
         <v>153</v>
       </c>
       <c r="B94" s="19" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C94" s="19" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="D94" s="21">
         <v>-5.0822029999999998</v>
@@ -14460,13 +14683,13 @@
     </row>
     <row r="95" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="19" t="s">
+        <v>491</v>
+      </c>
+      <c r="B95" s="19" t="s">
+        <v>492</v>
+      </c>
+      <c r="C95" s="19" t="s">
         <v>493</v>
-      </c>
-      <c r="B95" s="19" t="s">
-        <v>494</v>
-      </c>
-      <c r="C95" s="19" t="s">
-        <v>495</v>
       </c>
       <c r="D95" s="21"/>
       <c r="E95" s="21"/>
@@ -14501,21 +14724,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="19" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B96" s="19" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C96" s="19" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="D96" s="24" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="E96" s="24" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="F96" s="20">
         <v>46139</v>
@@ -14592,21 +14815,21 @@
         <v>3307</v>
       </c>
     </row>
-    <row r="97" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="19" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B97" s="19" t="s">
         <v>136</v>
       </c>
       <c r="C97" s="19" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D97" s="24" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="E97" s="24" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="F97" s="20">
         <v>46139</v>
@@ -14683,15 +14906,15 @@
         <v>7063</v>
       </c>
     </row>
-    <row r="98" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="19" t="s">
+        <v>505</v>
+      </c>
+      <c r="B98" s="19" t="s">
+        <v>506</v>
+      </c>
+      <c r="C98" s="19" t="s">
         <v>507</v>
-      </c>
-      <c r="B98" s="19" t="s">
-        <v>508</v>
-      </c>
-      <c r="C98" s="19" t="s">
-        <v>509</v>
       </c>
       <c r="D98" s="21"/>
       <c r="E98" s="21"/>
@@ -14726,15 +14949,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="19" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B99" s="19" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C99" s="19" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="D99" s="21"/>
       <c r="E99" s="21"/>
@@ -14769,15 +14992,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="19" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B100" s="19" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C100" s="19" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D100" s="21"/>
       <c r="E100" s="21"/>
@@ -14812,15 +15035,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="19" t="s">
+        <v>521</v>
+      </c>
+      <c r="B101" s="19" t="s">
+        <v>522</v>
+      </c>
+      <c r="C101" s="19" t="s">
         <v>523</v>
-      </c>
-      <c r="B101" s="19" t="s">
-        <v>524</v>
-      </c>
-      <c r="C101" s="19" t="s">
-        <v>525</v>
       </c>
       <c r="D101" s="21"/>
       <c r="E101" s="21"/>
@@ -14855,15 +15078,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="19" t="s">
+        <v>527</v>
+      </c>
+      <c r="B102" s="19" t="s">
+        <v>528</v>
+      </c>
+      <c r="C102" s="19" t="s">
         <v>529</v>
-      </c>
-      <c r="B102" s="19" t="s">
-        <v>530</v>
-      </c>
-      <c r="C102" s="19" t="s">
-        <v>531</v>
       </c>
       <c r="D102" s="21"/>
       <c r="E102" s="21"/>
@@ -14898,7 +15121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="19" t="s">
         <v>164</v>
       </c>
@@ -14906,7 +15129,7 @@
         <v>165</v>
       </c>
       <c r="C103" s="19" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="D103" s="21">
         <v>-4.8596729999999999</v>
@@ -14989,15 +15212,15 @@
         <v>2499</v>
       </c>
     </row>
-    <row r="104" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="19" t="s">
+        <v>533</v>
+      </c>
+      <c r="B104" s="19" t="s">
+        <v>534</v>
+      </c>
+      <c r="C104" s="19" t="s">
         <v>535</v>
-      </c>
-      <c r="B104" s="19" t="s">
-        <v>536</v>
-      </c>
-      <c r="C104" s="19" t="s">
-        <v>537</v>
       </c>
       <c r="D104" s="21">
         <v>-4.4447369999999999</v>
@@ -15080,15 +15303,15 @@
         <v>2533</v>
       </c>
     </row>
-    <row r="105" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="19" t="s">
+        <v>539</v>
+      </c>
+      <c r="B105" s="19" t="s">
+        <v>540</v>
+      </c>
+      <c r="C105" s="19" t="s">
         <v>541</v>
-      </c>
-      <c r="B105" s="19" t="s">
-        <v>542</v>
-      </c>
-      <c r="C105" s="19" t="s">
-        <v>543</v>
       </c>
       <c r="D105" s="21">
         <v>-5.1705110000000003</v>
@@ -15171,15 +15394,15 @@
         <v>2124</v>
       </c>
     </row>
-    <row r="106" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="19" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B106" s="19" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C106" s="19" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="D106" s="21"/>
       <c r="E106" s="21"/>
@@ -15214,15 +15437,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="19" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B107" s="19" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C107" s="19" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="D107" s="21"/>
       <c r="E107" s="21"/>
@@ -15257,7 +15480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="19" t="s">
         <v>170</v>
       </c>
@@ -15267,48 +15490,96 @@
       <c r="C108" s="19" t="s">
         <v>171</v>
       </c>
-      <c r="D108" s="21"/>
-      <c r="E108" s="21"/>
-      <c r="F108" s="20"/>
+      <c r="D108" s="24" t="s">
+        <v>863</v>
+      </c>
+      <c r="E108" s="24" t="s">
+        <v>864</v>
+      </c>
+      <c r="F108" s="20">
+        <v>46142</v>
+      </c>
       <c r="G108" s="20">
         <f t="shared" si="3"/>
+        <v>46144</v>
+      </c>
+      <c r="H108" s="12">
+        <v>755</v>
+      </c>
+      <c r="I108" s="12">
+        <v>836</v>
+      </c>
+      <c r="J108" s="12">
+        <v>30</v>
+      </c>
+      <c r="K108" s="12">
+        <v>175</v>
+      </c>
+      <c r="L108" s="12">
+        <v>60</v>
+      </c>
+      <c r="M108" s="12">
+        <v>7</v>
+      </c>
+      <c r="N108" s="12">
+        <v>15</v>
+      </c>
+      <c r="O108" s="12">
+        <v>4</v>
+      </c>
+      <c r="P108" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q108" s="12">
+        <v>4</v>
+      </c>
+      <c r="R108" s="12">
+        <v>11</v>
+      </c>
+      <c r="S108" s="12">
         <v>2</v>
       </c>
-      <c r="H108" s="12"/>
-      <c r="I108" s="12"/>
-      <c r="J108" s="12"/>
-      <c r="K108" s="12"/>
-      <c r="L108" s="12"/>
-      <c r="M108" s="12"/>
-      <c r="N108" s="12"/>
-      <c r="O108" s="12"/>
-      <c r="P108" s="12"/>
-      <c r="Q108" s="12"/>
-      <c r="R108" s="12"/>
-      <c r="S108" s="12"/>
-      <c r="T108" s="12"/>
-      <c r="U108" s="12"/>
-      <c r="V108" s="12"/>
-      <c r="W108" s="12"/>
-      <c r="X108" s="12"/>
-      <c r="Y108" s="12"/>
-      <c r="Z108" s="12"/>
-      <c r="AA108" s="12"/>
-      <c r="AB108" s="12"/>
+      <c r="T108" s="12">
+        <v>41</v>
+      </c>
+      <c r="U108" s="12">
+        <v>0</v>
+      </c>
+      <c r="V108" s="12">
+        <v>0</v>
+      </c>
+      <c r="W108" s="12">
+        <v>1</v>
+      </c>
+      <c r="X108" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y108" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z108" s="12">
+        <v>13</v>
+      </c>
+      <c r="AA108" s="12">
+        <v>2</v>
+      </c>
+      <c r="AB108" s="12">
+        <v>17</v>
+      </c>
       <c r="AC108" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1973</v>
+      </c>
+    </row>
+    <row r="109" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="19" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B109" s="19" t="s">
         <v>42</v>
       </c>
       <c r="C109" s="19" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="D109" s="21"/>
       <c r="E109" s="21"/>
@@ -15343,15 +15614,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="19" t="s">
+        <v>559</v>
+      </c>
+      <c r="B110" s="19" t="s">
+        <v>560</v>
+      </c>
+      <c r="C110" s="19" t="s">
         <v>561</v>
-      </c>
-      <c r="B110" s="19" t="s">
-        <v>562</v>
-      </c>
-      <c r="C110" s="19" t="s">
-        <v>563</v>
       </c>
       <c r="D110" s="21">
         <v>-3.6978119999999999</v>
@@ -15434,15 +15705,15 @@
         <v>5171</v>
       </c>
     </row>
-    <row r="111" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="19" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="B111" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C111" s="19" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="D111" s="21">
         <v>-5.2113269999999998</v>
@@ -15525,15 +15796,15 @@
         <v>5543</v>
       </c>
     </row>
-    <row r="112" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="19" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="B112" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C112" s="19" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="D112" s="21">
         <v>-4.3822749999999999</v>
@@ -15616,15 +15887,15 @@
         <v>4135</v>
       </c>
     </row>
-    <row r="113" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="19" t="s">
+        <v>575</v>
+      </c>
+      <c r="B113" s="19" t="s">
+        <v>576</v>
+      </c>
+      <c r="C113" s="19" t="s">
         <v>577</v>
-      </c>
-      <c r="B113" s="19" t="s">
-        <v>578</v>
-      </c>
-      <c r="C113" s="19" t="s">
-        <v>579</v>
       </c>
       <c r="D113" s="21"/>
       <c r="E113" s="21"/>
@@ -15661,13 +15932,13 @@
     </row>
     <row r="114" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="19" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B114" s="19" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C114" s="19" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="D114" s="21"/>
       <c r="E114" s="21"/>
@@ -15702,15 +15973,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="19" t="s">
+        <v>586</v>
+      </c>
+      <c r="B115" s="19" t="s">
+        <v>587</v>
+      </c>
+      <c r="C115" s="19" t="s">
         <v>588</v>
-      </c>
-      <c r="B115" s="19" t="s">
-        <v>589</v>
-      </c>
-      <c r="C115" s="19" t="s">
-        <v>590</v>
       </c>
       <c r="D115" s="21"/>
       <c r="E115" s="21"/>
@@ -15745,15 +16016,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="19" t="s">
+        <v>592</v>
+      </c>
+      <c r="B116" s="19" t="s">
+        <v>593</v>
+      </c>
+      <c r="C116" s="19" t="s">
         <v>594</v>
-      </c>
-      <c r="B116" s="19" t="s">
-        <v>595</v>
-      </c>
-      <c r="C116" s="19" t="s">
-        <v>596</v>
       </c>
       <c r="D116" s="21"/>
       <c r="E116" s="21"/>
@@ -15788,15 +16059,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="19" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B117" s="19" t="s">
         <v>142</v>
       </c>
       <c r="C117" s="19" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="D117" s="21"/>
       <c r="E117" s="21"/>
@@ -15831,15 +16102,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="19" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="B118" s="19" t="s">
         <v>104</v>
       </c>
       <c r="C118" s="19" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="D118" s="21"/>
       <c r="E118" s="21"/>
@@ -15874,7 +16145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="19" t="s">
         <v>11</v>
       </c>
@@ -15965,7 +16236,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="120" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="19" t="s">
         <v>20</v>
       </c>
@@ -16056,7 +16327,7 @@
         <v>1773</v>
       </c>
     </row>
-    <row r="121" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="19" t="s">
         <v>24</v>
       </c>
@@ -16099,7 +16370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="19" t="s">
         <v>30</v>
       </c>
@@ -16190,7 +16461,7 @@
         <v>4915</v>
       </c>
     </row>
-    <row r="123" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="19" t="s">
         <v>35</v>
       </c>
@@ -16233,7 +16504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="19" t="s">
         <v>41</v>
       </c>
@@ -16276,7 +16547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="19" t="s">
         <v>63</v>
       </c>
@@ -16319,7 +16590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="19" t="s">
         <v>69</v>
       </c>
@@ -16362,15 +16633,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="19" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B127" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C127" s="19" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D127" s="21"/>
       <c r="E127" s="21"/>
@@ -16405,15 +16676,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="19" t="s">
+        <v>265</v>
+      </c>
+      <c r="B128" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="C128" s="19" t="s">
         <v>267</v>
-      </c>
-      <c r="B128" s="19" t="s">
-        <v>268</v>
-      </c>
-      <c r="C128" s="19" t="s">
-        <v>269</v>
       </c>
       <c r="D128" s="21"/>
       <c r="E128" s="21"/>
@@ -16448,15 +16719,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="19" t="s">
+        <v>271</v>
+      </c>
+      <c r="B129" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="C129" s="19" t="s">
         <v>273</v>
-      </c>
-      <c r="B129" s="19" t="s">
-        <v>274</v>
-      </c>
-      <c r="C129" s="19" t="s">
-        <v>275</v>
       </c>
       <c r="D129" s="21"/>
       <c r="E129" s="21"/>
@@ -16491,15 +16762,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="19" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B130" s="19" t="s">
         <v>36</v>
       </c>
       <c r="C130" s="19" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D130" s="21">
         <v>-4.1980709999999997</v>
@@ -16582,15 +16853,15 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="131" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="19" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B131" s="19" t="s">
         <v>36</v>
       </c>
       <c r="C131" s="19" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D131" s="21">
         <v>-4.2305849999999996</v>
@@ -16673,7 +16944,7 @@
         <v>1984</v>
       </c>
     </row>
-    <row r="132" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="19" t="s">
         <v>81</v>
       </c>
@@ -16764,7 +17035,7 @@
         <v>2597</v>
       </c>
     </row>
-    <row r="133" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="19" t="s">
         <v>86</v>
       </c>
@@ -16855,7 +17126,7 @@
         <v>1733</v>
       </c>
     </row>
-    <row r="134" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="19" t="s">
         <v>92</v>
       </c>
@@ -16946,15 +17217,15 @@
         <v>1724</v>
       </c>
     </row>
-    <row r="135" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="19" t="s">
+        <v>287</v>
+      </c>
+      <c r="B135" s="19" t="s">
+        <v>288</v>
+      </c>
+      <c r="C135" s="19" t="s">
         <v>289</v>
-      </c>
-      <c r="B135" s="19" t="s">
-        <v>290</v>
-      </c>
-      <c r="C135" s="19" t="s">
-        <v>291</v>
       </c>
       <c r="D135" s="21"/>
       <c r="E135" s="21"/>
@@ -16989,15 +17260,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="19" t="s">
+        <v>292</v>
+      </c>
+      <c r="B136" s="19" t="s">
+        <v>293</v>
+      </c>
+      <c r="C136" s="19" t="s">
         <v>294</v>
-      </c>
-      <c r="B136" s="19" t="s">
-        <v>295</v>
-      </c>
-      <c r="C136" s="19" t="s">
-        <v>296</v>
       </c>
       <c r="D136" s="21"/>
       <c r="E136" s="21"/>
@@ -17032,7 +17303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="19" t="s">
         <v>47</v>
       </c>
@@ -17075,7 +17346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="19" t="s">
         <v>53</v>
       </c>
@@ -17118,7 +17389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="19" t="s">
         <v>57</v>
       </c>
@@ -17161,7 +17432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="19" t="s">
         <v>75</v>
       </c>
@@ -17252,15 +17523,15 @@
         <v>1839</v>
       </c>
     </row>
-    <row r="141" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="B141" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="C141" s="19" t="s">
         <v>209</v>
-      </c>
-      <c r="B141" s="19" t="s">
-        <v>210</v>
-      </c>
-      <c r="C141" s="19" t="s">
-        <v>211</v>
       </c>
       <c r="D141" s="21">
         <v>-4.9313539999999998</v>
@@ -17343,15 +17614,15 @@
         <v>2840</v>
       </c>
     </row>
-    <row r="142" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="19" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B142" s="19" t="s">
         <v>87</v>
       </c>
       <c r="C142" s="19" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D142" s="21">
         <v>-4.3993669999999998</v>
@@ -17434,15 +17705,15 @@
         <v>1451</v>
       </c>
     </row>
-    <row r="143" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="19" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B143" s="19" t="s">
         <v>148</v>
       </c>
       <c r="C143" s="19" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D143" s="21"/>
       <c r="E143" s="21"/>
@@ -17477,15 +17748,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="B144" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="C144" s="19" t="s">
         <v>230</v>
-      </c>
-      <c r="B144" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="C144" s="19" t="s">
-        <v>232</v>
       </c>
       <c r="D144" s="21">
         <v>-4.2870549999999996</v>
@@ -17568,15 +17839,15 @@
         <v>2854</v>
       </c>
     </row>
-    <row r="145" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="B145" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="C145" s="19" t="s">
         <v>236</v>
-      </c>
-      <c r="B145" s="19" t="s">
-        <v>237</v>
-      </c>
-      <c r="C145" s="19" t="s">
-        <v>238</v>
       </c>
       <c r="D145" s="21"/>
       <c r="E145" s="21"/>
@@ -17611,15 +17882,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="19" t="s">
+        <v>240</v>
+      </c>
+      <c r="B146" s="19" t="s">
+        <v>241</v>
+      </c>
+      <c r="C146" s="19" t="s">
         <v>242</v>
-      </c>
-      <c r="B146" s="19" t="s">
-        <v>243</v>
-      </c>
-      <c r="C146" s="19" t="s">
-        <v>244</v>
       </c>
       <c r="D146" s="21"/>
       <c r="E146" s="21"/>
@@ -17654,15 +17925,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="19" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B147" s="19" t="s">
         <v>48</v>
       </c>
       <c r="C147" s="19" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D147" s="21"/>
       <c r="E147" s="21"/>
@@ -17697,15 +17968,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="19" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B148" s="19" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C148" s="19" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D148" s="21"/>
       <c r="E148" s="21"/>
@@ -17740,15 +18011,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="19" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B149" s="19" t="s">
         <v>42</v>
       </c>
       <c r="C149" s="19" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D149" s="21"/>
       <c r="E149" s="21"/>
@@ -17783,15 +18054,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="19" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B150" s="19" t="s">
         <v>76</v>
       </c>
       <c r="C150" s="19" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D150" s="21"/>
       <c r="E150" s="21"/>
@@ -17826,15 +18097,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="19" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B151" s="19" t="s">
         <v>42</v>
       </c>
       <c r="C151" s="19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D151" s="21"/>
       <c r="E151" s="21"/>
@@ -17869,15 +18140,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="19" t="s">
+        <v>303</v>
+      </c>
+      <c r="B152" s="19" t="s">
+        <v>304</v>
+      </c>
+      <c r="C152" s="19" t="s">
         <v>305</v>
-      </c>
-      <c r="B152" s="19" t="s">
-        <v>306</v>
-      </c>
-      <c r="C152" s="19" t="s">
-        <v>307</v>
       </c>
       <c r="D152" s="21">
         <v>-4.5677839999999996</v>
@@ -17960,15 +18231,15 @@
         <v>184</v>
       </c>
     </row>
-    <row r="153" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="19" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B153" s="19" t="s">
         <v>136</v>
       </c>
       <c r="C153" s="19" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D153" s="21"/>
       <c r="E153" s="21"/>
@@ -18023,6 +18294,15 @@
     </row>
   </sheetData>
   <autoFilter ref="A4:AC153" xr:uid="{1D18A476-0271-4A84-BE9E-901865A86FD3}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="P 113"/>
+        <filter val="P 115"/>
+        <filter val="P 155"/>
+        <filter val="P 195"/>
+        <filter val="P 24"/>
+      </filters>
+    </filterColumn>
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="9">

--- a/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
+++ b/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CEAA1F1-A981-4E83-AF3F-18EC4805C717}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06D683C8-75EB-4FFB-8B7E-CA9640978DA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
   </bookViews>
@@ -4203,7 +4203,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DA12617-6B17-4A0E-9E79-EBA6E19B3138}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K150"/>
@@ -4258,7 +4258,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -4293,7 +4293,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>19</v>
       </c>
@@ -4328,7 +4328,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>23</v>
       </c>
@@ -4363,7 +4363,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>29</v>
       </c>
@@ -4398,7 +4398,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>34</v>
       </c>
@@ -4433,7 +4433,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>40</v>
       </c>
@@ -4468,7 +4468,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>46</v>
       </c>
@@ -4503,7 +4503,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>52</v>
       </c>
@@ -4538,7 +4538,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>56</v>
       </c>
@@ -4573,7 +4573,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>62</v>
       </c>
@@ -4608,7 +4608,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>68</v>
       </c>
@@ -4643,7 +4643,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>74</v>
       </c>
@@ -4678,7 +4678,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>206</v>
       </c>
@@ -4713,7 +4713,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>212</v>
       </c>
@@ -4748,7 +4748,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>217</v>
       </c>
@@ -4783,7 +4783,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>222</v>
       </c>
@@ -4818,7 +4818,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>227</v>
       </c>
@@ -4853,7 +4853,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>233</v>
       </c>
@@ -4888,7 +4888,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>239</v>
       </c>
@@ -4923,7 +4923,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>245</v>
       </c>
@@ -4952,13 +4952,13 @@
         <v>16</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>17</v>
+        <v>837</v>
       </c>
       <c r="K21" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>250</v>
       </c>
@@ -4993,7 +4993,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>255</v>
       </c>
@@ -5028,7 +5028,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>260</v>
       </c>
@@ -5063,7 +5063,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>264</v>
       </c>
@@ -5098,7 +5098,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>270</v>
       </c>
@@ -5133,7 +5133,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>276</v>
       </c>
@@ -5168,7 +5168,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>281</v>
       </c>
@@ -5203,7 +5203,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>80</v>
       </c>
@@ -5238,7 +5238,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>85</v>
       </c>
@@ -5273,7 +5273,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>91</v>
       </c>
@@ -5308,7 +5308,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>286</v>
       </c>
@@ -5343,7 +5343,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>291</v>
       </c>
@@ -5378,7 +5378,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="34" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>297</v>
       </c>
@@ -5413,7 +5413,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="35" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>302</v>
       </c>
@@ -5448,7 +5448,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>309</v>
       </c>
@@ -5483,7 +5483,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>95</v>
       </c>
@@ -5518,7 +5518,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>102</v>
       </c>
@@ -5553,7 +5553,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>108</v>
       </c>
@@ -5588,7 +5588,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>113</v>
       </c>
@@ -5623,7 +5623,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>119</v>
       </c>
@@ -5658,7 +5658,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>124</v>
       </c>
@@ -5693,7 +5693,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="43" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>314</v>
       </c>
@@ -5728,7 +5728,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>319</v>
       </c>
@@ -5763,7 +5763,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>324</v>
       </c>
@@ -5798,7 +5798,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="46" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>329</v>
       </c>
@@ -5833,7 +5833,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>334</v>
       </c>
@@ -5868,7 +5868,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>340</v>
       </c>
@@ -5903,7 +5903,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>129</v>
       </c>
@@ -5938,7 +5938,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>134</v>
       </c>
@@ -5973,7 +5973,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>346</v>
       </c>
@@ -6008,7 +6008,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="52" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>350</v>
       </c>
@@ -6072,7 +6072,7 @@
         <v>101</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>837</v>
+        <v>804</v>
       </c>
       <c r="K53" s="6" t="s">
         <v>18</v>
@@ -6107,13 +6107,13 @@
         <v>151</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>837</v>
+        <v>804</v>
       </c>
       <c r="K54" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>367</v>
       </c>
@@ -6148,7 +6148,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="56" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>140</v>
       </c>
@@ -6183,7 +6183,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>373</v>
       </c>
@@ -6218,7 +6218,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>379</v>
       </c>
@@ -6253,7 +6253,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>146</v>
       </c>
@@ -6288,7 +6288,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>385</v>
       </c>
@@ -6323,7 +6323,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>390</v>
       </c>
@@ -6358,7 +6358,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="62" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>396</v>
       </c>
@@ -6393,7 +6393,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="63" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>402</v>
       </c>
@@ -6428,7 +6428,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="64" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>407</v>
       </c>
@@ -6463,7 +6463,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="65" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>413</v>
       </c>
@@ -6498,7 +6498,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="66" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>419</v>
       </c>
@@ -6527,13 +6527,13 @@
         <v>101</v>
       </c>
       <c r="J66" s="6" t="s">
-        <v>17</v>
+        <v>837</v>
       </c>
       <c r="K66" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="67" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>424</v>
       </c>
@@ -6562,13 +6562,13 @@
         <v>101</v>
       </c>
       <c r="J67" s="6" t="s">
-        <v>17</v>
+        <v>837</v>
       </c>
       <c r="K67" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>430</v>
       </c>
@@ -6603,7 +6603,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>435</v>
       </c>
@@ -6638,7 +6638,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>439</v>
       </c>
@@ -6673,7 +6673,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="71" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>444</v>
       </c>
@@ -6708,7 +6708,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="72" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>450</v>
       </c>
@@ -6743,7 +6743,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="73" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>455</v>
       </c>
@@ -6778,7 +6778,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="74" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>460</v>
       </c>
@@ -6813,7 +6813,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="75" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>465</v>
       </c>
@@ -6848,7 +6848,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="76" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>470</v>
       </c>
@@ -6883,7 +6883,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>474</v>
       </c>
@@ -6918,7 +6918,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>480</v>
       </c>
@@ -6953,7 +6953,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>484</v>
       </c>
@@ -6988,7 +6988,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="80" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>152</v>
       </c>
@@ -7052,13 +7052,13 @@
         <v>101</v>
       </c>
       <c r="J81" s="6" t="s">
-        <v>837</v>
+        <v>804</v>
       </c>
       <c r="K81" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="82" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>496</v>
       </c>
@@ -7093,7 +7093,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="83" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>501</v>
       </c>
@@ -7128,7 +7128,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="84" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>504</v>
       </c>
@@ -7163,7 +7163,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="85" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>510</v>
       </c>
@@ -7198,7 +7198,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="86" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>158</v>
       </c>
@@ -7233,7 +7233,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>515</v>
       </c>
@@ -7268,7 +7268,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="88" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>520</v>
       </c>
@@ -7303,7 +7303,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="89" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>526</v>
       </c>
@@ -7338,7 +7338,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="90" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>163</v>
       </c>
@@ -7373,7 +7373,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="91" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>532</v>
       </c>
@@ -7408,7 +7408,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="92" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>538</v>
       </c>
@@ -7443,7 +7443,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="93" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>544</v>
       </c>
@@ -7478,7 +7478,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="94" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>549</v>
       </c>
@@ -7513,7 +7513,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="95" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>169</v>
       </c>
@@ -7548,7 +7548,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="96" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>554</v>
       </c>
@@ -7583,7 +7583,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="97" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>558</v>
       </c>
@@ -7618,7 +7618,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="98" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>564</v>
       </c>
@@ -7653,7 +7653,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="99" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>569</v>
       </c>
@@ -7688,7 +7688,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="100" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>574</v>
       </c>
@@ -7752,13 +7752,13 @@
         <v>151</v>
       </c>
       <c r="J101" s="6" t="s">
-        <v>837</v>
+        <v>804</v>
       </c>
       <c r="K101" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="102" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>585</v>
       </c>
@@ -7793,7 +7793,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="103" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>591</v>
       </c>
@@ -7828,7 +7828,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="104" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>596</v>
       </c>
@@ -7863,7 +7863,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="105" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>601</v>
       </c>
@@ -7898,7 +7898,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="106" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>172</v>
       </c>
@@ -7933,7 +7933,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="107" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>179</v>
       </c>
@@ -7968,7 +7968,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="108" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>184</v>
       </c>
@@ -8032,13 +8032,13 @@
         <v>151</v>
       </c>
       <c r="J109" s="6" t="s">
-        <v>837</v>
+        <v>804</v>
       </c>
       <c r="K109" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="110" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>195</v>
       </c>
@@ -8073,7 +8073,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="111" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>606</v>
       </c>
@@ -8108,7 +8108,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="112" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>612</v>
       </c>
@@ -8143,7 +8143,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="113" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>617</v>
       </c>
@@ -8178,7 +8178,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="114" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>623</v>
       </c>
@@ -8207,13 +8207,13 @@
         <v>101</v>
       </c>
       <c r="J114" s="6" t="s">
-        <v>17</v>
+        <v>837</v>
       </c>
       <c r="K114" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="115" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>628</v>
       </c>
@@ -8248,7 +8248,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="116" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>634</v>
       </c>
@@ -8283,7 +8283,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="117" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>639</v>
       </c>
@@ -8318,7 +8318,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="118" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>644</v>
       </c>
@@ -8353,7 +8353,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="119" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>201</v>
       </c>
@@ -8388,7 +8388,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="120" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>649</v>
       </c>
@@ -8423,7 +8423,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="121" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>654</v>
       </c>
@@ -8458,7 +8458,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="122" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>659</v>
       </c>
@@ -8493,7 +8493,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="123" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>663</v>
       </c>
@@ -8528,7 +8528,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="124" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>668</v>
       </c>
@@ -8563,7 +8563,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="125" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>673</v>
       </c>
@@ -8598,7 +8598,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="126" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>677</v>
       </c>
@@ -8633,7 +8633,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="127" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>682</v>
       </c>
@@ -8668,7 +8668,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="128" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>687</v>
       </c>
@@ -8703,7 +8703,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="129" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>693</v>
       </c>
@@ -8738,7 +8738,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="130" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>698</v>
       </c>
@@ -8773,7 +8773,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="131" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>704</v>
       </c>
@@ -8808,7 +8808,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="132" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>708</v>
       </c>
@@ -8843,7 +8843,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="133" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>714</v>
       </c>
@@ -8878,7 +8878,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="134" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>719</v>
       </c>
@@ -8913,7 +8913,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="135" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>724</v>
       </c>
@@ -8948,7 +8948,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="136" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>729</v>
       </c>
@@ -8977,13 +8977,13 @@
         <v>101</v>
       </c>
       <c r="J136" s="6" t="s">
-        <v>17</v>
+        <v>837</v>
       </c>
       <c r="K136" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="137" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>733</v>
       </c>
@@ -9018,7 +9018,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="138" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>738</v>
       </c>
@@ -9053,7 +9053,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="139" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>743</v>
       </c>
@@ -9088,7 +9088,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="140" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>748</v>
       </c>
@@ -9123,7 +9123,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="141" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>753</v>
       </c>
@@ -9158,7 +9158,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="142" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>757</v>
       </c>
@@ -9193,7 +9193,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="143" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>762</v>
       </c>
@@ -9228,7 +9228,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="144" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>766</v>
       </c>
@@ -9263,7 +9263,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="145" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>771</v>
       </c>
@@ -9298,7 +9298,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="146" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>776</v>
       </c>
@@ -9333,7 +9333,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="147" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>781</v>
       </c>
@@ -9368,7 +9368,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="148" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>787</v>
       </c>
@@ -9403,7 +9403,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="149" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>793</v>
       </c>
@@ -9438,7 +9438,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="150" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>798</v>
       </c>
@@ -9474,22 +9474,12 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K150" xr:uid="{4DA12617-6B17-4A0E-9E79-EBA6E19B3138}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="P 113"/>
-        <filter val="P 115"/>
-        <filter val="P 155"/>
-        <filter val="P 195"/>
-        <filter val="P 24"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:K150" xr:uid="{4DA12617-6B17-4A0E-9E79-EBA6E19B3138}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K150">
     <sortCondition ref="B1:B150"/>
   </sortState>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="63" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="20" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -10372,37 +10362,85 @@
       <c r="C18" s="19" t="s">
         <v>192</v>
       </c>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="20"/>
+      <c r="D18" s="24">
+        <v>-5.0728489999999997</v>
+      </c>
+      <c r="E18" s="24">
+        <v>-38.384563</v>
+      </c>
+      <c r="F18" s="20">
+        <v>46145</v>
+      </c>
       <c r="G18" s="20">
         <f t="shared" si="0"/>
+        <v>46147</v>
+      </c>
+      <c r="H18" s="12">
+        <v>1139</v>
+      </c>
+      <c r="I18" s="12">
+        <v>2306</v>
+      </c>
+      <c r="J18" s="12">
+        <v>21</v>
+      </c>
+      <c r="K18" s="12">
+        <v>219</v>
+      </c>
+      <c r="L18" s="12">
+        <v>88</v>
+      </c>
+      <c r="M18" s="12">
+        <v>24</v>
+      </c>
+      <c r="N18" s="12">
+        <v>30</v>
+      </c>
+      <c r="O18" s="12">
+        <v>4</v>
+      </c>
+      <c r="P18" s="12">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="12">
+        <v>6</v>
+      </c>
+      <c r="R18" s="12">
+        <v>14</v>
+      </c>
+      <c r="S18" s="12">
+        <v>1</v>
+      </c>
+      <c r="T18" s="12">
+        <v>63</v>
+      </c>
+      <c r="U18" s="12">
+        <v>0</v>
+      </c>
+      <c r="V18" s="12">
+        <v>0</v>
+      </c>
+      <c r="W18" s="12">
+        <v>1</v>
+      </c>
+      <c r="X18" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="12">
+        <v>7</v>
+      </c>
+      <c r="AA18" s="12">
         <v>2</v>
       </c>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="12"/>
-      <c r="K18" s="12"/>
-      <c r="L18" s="12"/>
-      <c r="M18" s="12"/>
-      <c r="N18" s="12"/>
-      <c r="O18" s="12"/>
-      <c r="P18" s="12"/>
-      <c r="Q18" s="12"/>
-      <c r="R18" s="12"/>
-      <c r="S18" s="12"/>
-      <c r="T18" s="12"/>
-      <c r="U18" s="12"/>
-      <c r="V18" s="12"/>
-      <c r="W18" s="12"/>
-      <c r="X18" s="12"/>
-      <c r="Y18" s="12"/>
-      <c r="Z18" s="12"/>
-      <c r="AA18" s="12"/>
-      <c r="AB18" s="12"/>
+      <c r="AB18" s="12">
+        <v>6</v>
+      </c>
       <c r="AC18" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3934</v>
       </c>
     </row>
     <row r="19" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -13333,37 +13371,85 @@
       <c r="C69" s="19" t="s">
         <v>359</v>
       </c>
-      <c r="D69" s="21"/>
-      <c r="E69" s="21"/>
-      <c r="F69" s="20"/>
+      <c r="D69" s="24">
+        <v>-5.2506180000000002</v>
+      </c>
+      <c r="E69" s="24">
+        <v>-38.494636999999997</v>
+      </c>
+      <c r="F69" s="20">
+        <v>46145</v>
+      </c>
       <c r="G69" s="20">
         <f t="shared" si="0"/>
+        <v>46147</v>
+      </c>
+      <c r="H69" s="12">
+        <v>342</v>
+      </c>
+      <c r="I69" s="12">
+        <v>520</v>
+      </c>
+      <c r="J69" s="12">
+        <v>9</v>
+      </c>
+      <c r="K69" s="12">
+        <v>69</v>
+      </c>
+      <c r="L69" s="12">
+        <v>13</v>
+      </c>
+      <c r="M69" s="12">
+        <v>5</v>
+      </c>
+      <c r="N69" s="12">
+        <v>6</v>
+      </c>
+      <c r="O69" s="12">
+        <v>0</v>
+      </c>
+      <c r="P69" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="12">
         <v>2</v>
       </c>
-      <c r="H69" s="12"/>
-      <c r="I69" s="12"/>
-      <c r="J69" s="12"/>
-      <c r="K69" s="12"/>
-      <c r="L69" s="12"/>
-      <c r="M69" s="12"/>
-      <c r="N69" s="12"/>
-      <c r="O69" s="12"/>
-      <c r="P69" s="12"/>
-      <c r="Q69" s="12"/>
-      <c r="R69" s="12"/>
-      <c r="S69" s="12"/>
-      <c r="T69" s="12"/>
-      <c r="U69" s="12"/>
-      <c r="V69" s="12"/>
-      <c r="W69" s="12"/>
-      <c r="X69" s="12"/>
-      <c r="Y69" s="12"/>
-      <c r="Z69" s="12"/>
-      <c r="AA69" s="12"/>
-      <c r="AB69" s="12"/>
+      <c r="R69" s="12">
+        <v>0</v>
+      </c>
+      <c r="S69" s="12">
+        <v>1</v>
+      </c>
+      <c r="T69" s="12">
+        <v>7</v>
+      </c>
+      <c r="U69" s="12">
+        <v>1</v>
+      </c>
+      <c r="V69" s="12">
+        <v>0</v>
+      </c>
+      <c r="W69" s="12">
+        <v>2</v>
+      </c>
+      <c r="X69" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z69" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA69" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB69" s="12">
+        <v>1</v>
+      </c>
       <c r="AC69" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>978</v>
       </c>
     </row>
     <row r="70" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -13376,37 +13462,85 @@
       <c r="C70" s="19" t="s">
         <v>364</v>
       </c>
-      <c r="D70" s="21"/>
-      <c r="E70" s="21"/>
-      <c r="F70" s="20"/>
+      <c r="D70" s="24">
+        <v>-5.4016780000000004</v>
+      </c>
+      <c r="E70" s="24">
+        <v>-38.569516999999998</v>
+      </c>
+      <c r="F70" s="20">
+        <v>46145</v>
+      </c>
       <c r="G70" s="20">
-        <f t="shared" ref="G70:G133" si="3">F70+2</f>
+        <f t="shared" ref="G70" si="3">F70+2</f>
+        <v>46147</v>
+      </c>
+      <c r="H70" s="12">
+        <v>300</v>
+      </c>
+      <c r="I70" s="12">
+        <v>747</v>
+      </c>
+      <c r="J70" s="12">
+        <v>13</v>
+      </c>
+      <c r="K70" s="12">
+        <v>105</v>
+      </c>
+      <c r="L70" s="12">
+        <v>47</v>
+      </c>
+      <c r="M70" s="12">
+        <v>7</v>
+      </c>
+      <c r="N70" s="12">
+        <v>6</v>
+      </c>
+      <c r="O70" s="12">
+        <v>1</v>
+      </c>
+      <c r="P70" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="12">
         <v>2</v>
       </c>
-      <c r="H70" s="12"/>
-      <c r="I70" s="12"/>
-      <c r="J70" s="12"/>
-      <c r="K70" s="12"/>
-      <c r="L70" s="12"/>
-      <c r="M70" s="12"/>
-      <c r="N70" s="12"/>
-      <c r="O70" s="12"/>
-      <c r="P70" s="12"/>
-      <c r="Q70" s="12"/>
-      <c r="R70" s="12"/>
-      <c r="S70" s="12"/>
-      <c r="T70" s="12"/>
-      <c r="U70" s="12"/>
-      <c r="V70" s="12"/>
-      <c r="W70" s="12"/>
-      <c r="X70" s="12"/>
-      <c r="Y70" s="12"/>
-      <c r="Z70" s="12"/>
-      <c r="AA70" s="12"/>
-      <c r="AB70" s="12"/>
+      <c r="R70" s="12">
+        <v>0</v>
+      </c>
+      <c r="S70" s="12">
+        <v>1</v>
+      </c>
+      <c r="T70" s="12">
+        <v>28</v>
+      </c>
+      <c r="U70" s="12">
+        <v>0</v>
+      </c>
+      <c r="V70" s="12">
+        <v>0</v>
+      </c>
+      <c r="W70" s="12">
+        <v>0</v>
+      </c>
+      <c r="X70" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="12">
+        <v>2</v>
+      </c>
+      <c r="AA70" s="12">
+        <v>2</v>
+      </c>
+      <c r="AB70" s="12">
+        <v>0</v>
+      </c>
       <c r="AC70" s="13">
         <f t="shared" ref="AC70:AC133" si="4">SUM(H70:AB70)</f>
-        <v>0</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="71" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -13423,7 +13557,7 @@
       <c r="E71" s="21"/>
       <c r="F71" s="20"/>
       <c r="G71" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="G70:G133" si="5">F71+2</f>
         <v>2</v>
       </c>
       <c r="H71" s="12"/>
@@ -13466,7 +13600,7 @@
       <c r="E72" s="21"/>
       <c r="F72" s="20"/>
       <c r="G72" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="H72" s="12"/>
@@ -13509,7 +13643,7 @@
       <c r="E73" s="21"/>
       <c r="F73" s="20"/>
       <c r="G73" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="H73" s="12"/>
@@ -13552,7 +13686,7 @@
       <c r="E74" s="21"/>
       <c r="F74" s="20"/>
       <c r="G74" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="H74" s="12"/>
@@ -13595,7 +13729,7 @@
       <c r="E75" s="21"/>
       <c r="F75" s="20"/>
       <c r="G75" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="H75" s="12"/>
@@ -13638,7 +13772,7 @@
       <c r="E76" s="21"/>
       <c r="F76" s="20"/>
       <c r="G76" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="H76" s="12"/>
@@ -13681,7 +13815,7 @@
       <c r="E77" s="21"/>
       <c r="F77" s="20"/>
       <c r="G77" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="H77" s="12"/>
@@ -13724,7 +13858,7 @@
       <c r="E78" s="21"/>
       <c r="F78" s="20"/>
       <c r="G78" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="H78" s="12"/>
@@ -13767,7 +13901,7 @@
       <c r="E79" s="21"/>
       <c r="F79" s="20"/>
       <c r="G79" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="H79" s="12"/>
@@ -13810,7 +13944,7 @@
       <c r="E80" s="21"/>
       <c r="F80" s="20"/>
       <c r="G80" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="H80" s="12"/>
@@ -13853,7 +13987,7 @@
       <c r="E81" s="21"/>
       <c r="F81" s="20"/>
       <c r="G81" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="H81" s="12"/>
@@ -13896,7 +14030,7 @@
       <c r="E82" s="21"/>
       <c r="F82" s="20"/>
       <c r="G82" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="H82" s="12"/>
@@ -13945,7 +14079,7 @@
         <v>46107</v>
       </c>
       <c r="G83" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>46109</v>
       </c>
       <c r="H83" s="12">
@@ -14030,7 +14164,7 @@
       <c r="E84" s="21"/>
       <c r="F84" s="20"/>
       <c r="G84" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="H84" s="12"/>
@@ -14073,7 +14207,7 @@
       <c r="E85" s="21"/>
       <c r="F85" s="20"/>
       <c r="G85" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="H85" s="12"/>
@@ -14116,7 +14250,7 @@
       <c r="E86" s="21"/>
       <c r="F86" s="20"/>
       <c r="G86" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="H86" s="12"/>
@@ -14159,7 +14293,7 @@
       <c r="E87" s="21"/>
       <c r="F87" s="20"/>
       <c r="G87" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="H87" s="12"/>
@@ -14208,7 +14342,7 @@
         <v>46119</v>
       </c>
       <c r="G88" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>46121</v>
       </c>
       <c r="H88" s="12">
@@ -14293,7 +14427,7 @@
       <c r="E89" s="21"/>
       <c r="F89" s="20"/>
       <c r="G89" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="H89" s="12"/>
@@ -14342,7 +14476,7 @@
         <v>46139</v>
       </c>
       <c r="G90" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>46141</v>
       </c>
       <c r="H90" s="12">
@@ -14427,7 +14561,7 @@
       <c r="E91" s="21"/>
       <c r="F91" s="20"/>
       <c r="G91" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="H91" s="12"/>
@@ -14470,7 +14604,7 @@
       <c r="E92" s="21"/>
       <c r="F92" s="20"/>
       <c r="G92" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="H92" s="12"/>
@@ -14519,7 +14653,7 @@
         <v>46142</v>
       </c>
       <c r="G93" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>46144</v>
       </c>
       <c r="H93" s="12">
@@ -14610,7 +14744,7 @@
         <v>46111</v>
       </c>
       <c r="G94" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>46113</v>
       </c>
       <c r="H94" s="12">
@@ -14691,37 +14825,85 @@
       <c r="C95" s="19" t="s">
         <v>493</v>
       </c>
-      <c r="D95" s="21"/>
-      <c r="E95" s="21"/>
-      <c r="F95" s="20"/>
+      <c r="D95" s="24">
+        <v>-5.4022300000000003</v>
+      </c>
+      <c r="E95" s="24">
+        <v>-38.571371999999997</v>
+      </c>
+      <c r="F95" s="20">
+        <v>46145</v>
+      </c>
       <c r="G95" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
+        <v>46147</v>
+      </c>
+      <c r="H95" s="12">
+        <v>318</v>
+      </c>
+      <c r="I95" s="12">
+        <v>940</v>
+      </c>
+      <c r="J95" s="12">
+        <v>83</v>
+      </c>
+      <c r="K95" s="12">
+        <v>141</v>
+      </c>
+      <c r="L95" s="12">
+        <v>67</v>
+      </c>
+      <c r="M95" s="12">
+        <v>10</v>
+      </c>
+      <c r="N95" s="12">
+        <v>8</v>
+      </c>
+      <c r="O95" s="12">
+        <v>0</v>
+      </c>
+      <c r="P95" s="12">
         <v>2</v>
       </c>
-      <c r="H95" s="12"/>
-      <c r="I95" s="12"/>
-      <c r="J95" s="12"/>
-      <c r="K95" s="12"/>
-      <c r="L95" s="12"/>
-      <c r="M95" s="12"/>
-      <c r="N95" s="12"/>
-      <c r="O95" s="12"/>
-      <c r="P95" s="12"/>
-      <c r="Q95" s="12"/>
-      <c r="R95" s="12"/>
-      <c r="S95" s="12"/>
-      <c r="T95" s="12"/>
-      <c r="U95" s="12"/>
-      <c r="V95" s="12"/>
-      <c r="W95" s="12"/>
-      <c r="X95" s="12"/>
-      <c r="Y95" s="12"/>
-      <c r="Z95" s="12"/>
-      <c r="AA95" s="12"/>
-      <c r="AB95" s="12"/>
+      <c r="Q95" s="12">
+        <v>4</v>
+      </c>
+      <c r="R95" s="12">
+        <v>6</v>
+      </c>
+      <c r="S95" s="12">
+        <v>1</v>
+      </c>
+      <c r="T95" s="12">
+        <v>33</v>
+      </c>
+      <c r="U95" s="12">
+        <v>0</v>
+      </c>
+      <c r="V95" s="12">
+        <v>0</v>
+      </c>
+      <c r="W95" s="12">
+        <v>0</v>
+      </c>
+      <c r="X95" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y95" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z95" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA95" s="12">
+        <v>3</v>
+      </c>
+      <c r="AB95" s="12">
+        <v>1</v>
+      </c>
       <c r="AC95" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="96" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -14744,7 +14926,7 @@
         <v>46139</v>
       </c>
       <c r="G96" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>46141</v>
       </c>
       <c r="H96" s="12">
@@ -14835,7 +15017,7 @@
         <v>46139</v>
       </c>
       <c r="G97" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>46141</v>
       </c>
       <c r="H97" s="12">
@@ -14920,7 +15102,7 @@
       <c r="E98" s="21"/>
       <c r="F98" s="20"/>
       <c r="G98" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="H98" s="12"/>
@@ -14963,7 +15145,7 @@
       <c r="E99" s="21"/>
       <c r="F99" s="20"/>
       <c r="G99" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="H99" s="12"/>
@@ -15006,7 +15188,7 @@
       <c r="E100" s="21"/>
       <c r="F100" s="20"/>
       <c r="G100" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="H100" s="12"/>
@@ -15049,7 +15231,7 @@
       <c r="E101" s="21"/>
       <c r="F101" s="20"/>
       <c r="G101" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="H101" s="12"/>
@@ -15092,7 +15274,7 @@
       <c r="E102" s="21"/>
       <c r="F102" s="20"/>
       <c r="G102" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="H102" s="12"/>
@@ -15141,7 +15323,7 @@
         <v>46111</v>
       </c>
       <c r="G103" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>46113</v>
       </c>
       <c r="H103" s="12">
@@ -15232,7 +15414,7 @@
         <v>46107</v>
       </c>
       <c r="G104" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>46109</v>
       </c>
       <c r="H104" s="12">
@@ -15323,7 +15505,7 @@
         <v>46125</v>
       </c>
       <c r="G105" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>46127</v>
       </c>
       <c r="H105" s="12">
@@ -15408,7 +15590,7 @@
       <c r="E106" s="21"/>
       <c r="F106" s="20"/>
       <c r="G106" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="H106" s="12"/>
@@ -15451,7 +15633,7 @@
       <c r="E107" s="21"/>
       <c r="F107" s="20"/>
       <c r="G107" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="H107" s="12"/>
@@ -15500,7 +15682,7 @@
         <v>46142</v>
       </c>
       <c r="G108" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>46144</v>
       </c>
       <c r="H108" s="12">
@@ -15585,7 +15767,7 @@
       <c r="E109" s="21"/>
       <c r="F109" s="20"/>
       <c r="G109" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="H109" s="12"/>
@@ -15634,7 +15816,7 @@
         <v>46119</v>
       </c>
       <c r="G110" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>46121</v>
       </c>
       <c r="H110" s="12">
@@ -15725,7 +15907,7 @@
         <v>46125</v>
       </c>
       <c r="G111" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>46127</v>
       </c>
       <c r="H111" s="12">
@@ -15816,7 +15998,7 @@
         <v>46131</v>
       </c>
       <c r="G112" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>46133</v>
       </c>
       <c r="H112" s="12">
@@ -15901,7 +16083,7 @@
       <c r="E113" s="21"/>
       <c r="F113" s="20"/>
       <c r="G113" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="H113" s="12"/>
@@ -15940,37 +16122,85 @@
       <c r="C114" s="19" t="s">
         <v>582</v>
       </c>
-      <c r="D114" s="21"/>
-      <c r="E114" s="21"/>
-      <c r="F114" s="20"/>
+      <c r="D114" s="24">
+        <v>-5.2495240000000001</v>
+      </c>
+      <c r="E114" s="24">
+        <v>-38.492610999999997</v>
+      </c>
+      <c r="F114" s="20">
+        <v>46145</v>
+      </c>
       <c r="G114" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
+        <v>46147</v>
+      </c>
+      <c r="H114" s="12">
+        <v>501</v>
+      </c>
+      <c r="I114" s="12">
+        <v>2131</v>
+      </c>
+      <c r="J114" s="12">
+        <v>74</v>
+      </c>
+      <c r="K114" s="12">
+        <v>126</v>
+      </c>
+      <c r="L114" s="12">
+        <v>45</v>
+      </c>
+      <c r="M114" s="12">
+        <v>5</v>
+      </c>
+      <c r="N114" s="12">
+        <v>13</v>
+      </c>
+      <c r="O114" s="12">
         <v>2</v>
       </c>
-      <c r="H114" s="12"/>
-      <c r="I114" s="12"/>
-      <c r="J114" s="12"/>
-      <c r="K114" s="12"/>
-      <c r="L114" s="12"/>
-      <c r="M114" s="12"/>
-      <c r="N114" s="12"/>
-      <c r="O114" s="12"/>
-      <c r="P114" s="12"/>
-      <c r="Q114" s="12"/>
-      <c r="R114" s="12"/>
-      <c r="S114" s="12"/>
-      <c r="T114" s="12"/>
-      <c r="U114" s="12"/>
-      <c r="V114" s="12"/>
-      <c r="W114" s="12"/>
-      <c r="X114" s="12"/>
-      <c r="Y114" s="12"/>
-      <c r="Z114" s="12"/>
-      <c r="AA114" s="12"/>
-      <c r="AB114" s="12"/>
+      <c r="P114" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q114" s="12">
+        <v>4</v>
+      </c>
+      <c r="R114" s="12">
+        <v>3</v>
+      </c>
+      <c r="S114" s="12">
+        <v>1</v>
+      </c>
+      <c r="T114" s="12">
+        <v>34</v>
+      </c>
+      <c r="U114" s="12">
+        <v>3</v>
+      </c>
+      <c r="V114" s="12">
+        <v>0</v>
+      </c>
+      <c r="W114" s="12">
+        <v>1</v>
+      </c>
+      <c r="X114" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y114" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z114" s="12">
+        <v>4</v>
+      </c>
+      <c r="AA114" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB114" s="12">
+        <v>0</v>
+      </c>
       <c r="AC114" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2947</v>
       </c>
     </row>
     <row r="115" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -15987,7 +16217,7 @@
       <c r="E115" s="21"/>
       <c r="F115" s="20"/>
       <c r="G115" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="H115" s="12"/>
@@ -16030,7 +16260,7 @@
       <c r="E116" s="21"/>
       <c r="F116" s="20"/>
       <c r="G116" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="H116" s="12"/>
@@ -16073,7 +16303,7 @@
       <c r="E117" s="21"/>
       <c r="F117" s="20"/>
       <c r="G117" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="H117" s="12"/>
@@ -16116,7 +16346,7 @@
       <c r="E118" s="21"/>
       <c r="F118" s="20"/>
       <c r="G118" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="H118" s="12"/>
@@ -16165,7 +16395,7 @@
         <v>46128</v>
       </c>
       <c r="G119" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>46130</v>
       </c>
       <c r="H119" s="12">
@@ -16256,7 +16486,7 @@
         <v>46128</v>
       </c>
       <c r="G120" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>46130</v>
       </c>
       <c r="H120" s="12">
@@ -16341,7 +16571,7 @@
       <c r="E121" s="21"/>
       <c r="F121" s="20"/>
       <c r="G121" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="H121" s="12"/>
@@ -16390,7 +16620,7 @@
         <v>46111</v>
       </c>
       <c r="G122" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>46113</v>
       </c>
       <c r="H122" s="12">
@@ -16475,7 +16705,7 @@
       <c r="E123" s="21"/>
       <c r="F123" s="20"/>
       <c r="G123" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="H123" s="12"/>
@@ -16518,7 +16748,7 @@
       <c r="E124" s="21"/>
       <c r="F124" s="20"/>
       <c r="G124" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="H124" s="12"/>
@@ -16561,7 +16791,7 @@
       <c r="E125" s="21"/>
       <c r="F125" s="20"/>
       <c r="G125" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="H125" s="12"/>
@@ -16604,7 +16834,7 @@
       <c r="E126" s="21"/>
       <c r="F126" s="20"/>
       <c r="G126" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="H126" s="12"/>
@@ -16647,7 +16877,7 @@
       <c r="E127" s="21"/>
       <c r="F127" s="20"/>
       <c r="G127" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="H127" s="12"/>
@@ -16690,7 +16920,7 @@
       <c r="E128" s="21"/>
       <c r="F128" s="20"/>
       <c r="G128" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="H128" s="12"/>
@@ -16733,7 +16963,7 @@
       <c r="E129" s="21"/>
       <c r="F129" s="20"/>
       <c r="G129" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="H129" s="12"/>
@@ -16782,7 +17012,7 @@
         <v>46104</v>
       </c>
       <c r="G130" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>46106</v>
       </c>
       <c r="H130" s="12">
@@ -16873,7 +17103,7 @@
         <v>46104</v>
       </c>
       <c r="G131" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>46106</v>
       </c>
       <c r="H131" s="12">
@@ -16964,7 +17194,7 @@
         <v>46107</v>
       </c>
       <c r="G132" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>46109</v>
       </c>
       <c r="H132" s="12">
@@ -17055,7 +17285,7 @@
         <v>46107</v>
       </c>
       <c r="G133" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>46109</v>
       </c>
       <c r="H133" s="12">
@@ -17146,7 +17376,7 @@
         <v>46107</v>
       </c>
       <c r="G134" s="20">
-        <f t="shared" ref="G134:G153" si="5">F134+2</f>
+        <f t="shared" ref="G134:G153" si="6">F134+2</f>
         <v>46109</v>
       </c>
       <c r="H134" s="12">
@@ -17213,7 +17443,7 @@
         <v>0</v>
       </c>
       <c r="AC134" s="13">
-        <f t="shared" ref="AC134:AC153" si="6">SUM(H134:AB134)</f>
+        <f t="shared" ref="AC134:AC153" si="7">SUM(H134:AB134)</f>
         <v>1724</v>
       </c>
     </row>
@@ -17231,7 +17461,7 @@
       <c r="E135" s="21"/>
       <c r="F135" s="20"/>
       <c r="G135" s="20">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="H135" s="12"/>
@@ -17256,7 +17486,7 @@
       <c r="AA135" s="12"/>
       <c r="AB135" s="12"/>
       <c r="AC135" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -17274,7 +17504,7 @@
       <c r="E136" s="21"/>
       <c r="F136" s="20"/>
       <c r="G136" s="20">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="H136" s="12"/>
@@ -17299,7 +17529,7 @@
       <c r="AA136" s="12"/>
       <c r="AB136" s="12"/>
       <c r="AC136" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -17317,7 +17547,7 @@
       <c r="E137" s="21"/>
       <c r="F137" s="20"/>
       <c r="G137" s="20">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="H137" s="12"/>
@@ -17342,7 +17572,7 @@
       <c r="AA137" s="12"/>
       <c r="AB137" s="12"/>
       <c r="AC137" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -17360,7 +17590,7 @@
       <c r="E138" s="21"/>
       <c r="F138" s="20"/>
       <c r="G138" s="20">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="H138" s="12"/>
@@ -17385,7 +17615,7 @@
       <c r="AA138" s="12"/>
       <c r="AB138" s="12"/>
       <c r="AC138" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -17403,7 +17633,7 @@
       <c r="E139" s="21"/>
       <c r="F139" s="20"/>
       <c r="G139" s="20">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="H139" s="12"/>
@@ -17428,7 +17658,7 @@
       <c r="AA139" s="12"/>
       <c r="AB139" s="12"/>
       <c r="AC139" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -17452,7 +17682,7 @@
         <v>46111</v>
       </c>
       <c r="G140" s="20">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>46113</v>
       </c>
       <c r="H140" s="12">
@@ -17519,7 +17749,7 @@
         <v>1</v>
       </c>
       <c r="AC140" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1839</v>
       </c>
     </row>
@@ -17543,7 +17773,7 @@
         <v>46128</v>
       </c>
       <c r="G141" s="20">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>46130</v>
       </c>
       <c r="H141" s="12">
@@ -17610,7 +17840,7 @@
         <v>0</v>
       </c>
       <c r="AC141" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2840</v>
       </c>
     </row>
@@ -17634,7 +17864,7 @@
         <v>46131</v>
       </c>
       <c r="G142" s="20">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>46133</v>
       </c>
       <c r="H142" s="12">
@@ -17701,7 +17931,7 @@
         <v>0</v>
       </c>
       <c r="AC142" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1451</v>
       </c>
     </row>
@@ -17719,7 +17949,7 @@
       <c r="E143" s="21"/>
       <c r="F143" s="20"/>
       <c r="G143" s="20">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="H143" s="12"/>
@@ -17744,7 +17974,7 @@
       <c r="AA143" s="12"/>
       <c r="AB143" s="12"/>
       <c r="AC143" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -17768,7 +17998,7 @@
         <v>46104</v>
       </c>
       <c r="G144" s="20">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>46106</v>
       </c>
       <c r="H144" s="12">
@@ -17835,7 +18065,7 @@
         <v>0</v>
       </c>
       <c r="AC144" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2854</v>
       </c>
     </row>
@@ -17853,7 +18083,7 @@
       <c r="E145" s="21"/>
       <c r="F145" s="20"/>
       <c r="G145" s="20">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="H145" s="12"/>
@@ -17878,7 +18108,7 @@
       <c r="AA145" s="12"/>
       <c r="AB145" s="12"/>
       <c r="AC145" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -17896,7 +18126,7 @@
       <c r="E146" s="21"/>
       <c r="F146" s="20"/>
       <c r="G146" s="20">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="H146" s="12"/>
@@ -17921,7 +18151,7 @@
       <c r="AA146" s="12"/>
       <c r="AB146" s="12"/>
       <c r="AC146" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -17939,7 +18169,7 @@
       <c r="E147" s="21"/>
       <c r="F147" s="20"/>
       <c r="G147" s="20">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="H147" s="12"/>
@@ -17964,7 +18194,7 @@
       <c r="AA147" s="12"/>
       <c r="AB147" s="12"/>
       <c r="AC147" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -17982,7 +18212,7 @@
       <c r="E148" s="21"/>
       <c r="F148" s="20"/>
       <c r="G148" s="20">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="H148" s="12"/>
@@ -18007,7 +18237,7 @@
       <c r="AA148" s="12"/>
       <c r="AB148" s="12"/>
       <c r="AC148" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -18025,7 +18255,7 @@
       <c r="E149" s="21"/>
       <c r="F149" s="20"/>
       <c r="G149" s="20">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="H149" s="12"/>
@@ -18050,7 +18280,7 @@
       <c r="AA149" s="12"/>
       <c r="AB149" s="12"/>
       <c r="AC149" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -18068,7 +18298,7 @@
       <c r="E150" s="21"/>
       <c r="F150" s="20"/>
       <c r="G150" s="20">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="H150" s="12"/>
@@ -18093,7 +18323,7 @@
       <c r="AA150" s="12"/>
       <c r="AB150" s="12"/>
       <c r="AC150" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -18111,7 +18341,7 @@
       <c r="E151" s="21"/>
       <c r="F151" s="20"/>
       <c r="G151" s="20">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="H151" s="12"/>
@@ -18136,7 +18366,7 @@
       <c r="AA151" s="12"/>
       <c r="AB151" s="12"/>
       <c r="AC151" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -18160,7 +18390,7 @@
         <v>46131</v>
       </c>
       <c r="G152" s="20">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>46133</v>
       </c>
       <c r="H152" s="12">
@@ -18227,7 +18457,7 @@
         <v>0</v>
       </c>
       <c r="AC152" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>184</v>
       </c>
     </row>
@@ -18245,7 +18475,7 @@
       <c r="E153" s="21"/>
       <c r="F153" s="20"/>
       <c r="G153" s="20">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="H153" s="12"/>
@@ -18270,7 +18500,7 @@
       <c r="AA153" s="12"/>
       <c r="AB153" s="12"/>
       <c r="AC153" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>

--- a/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
+++ b/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06D683C8-75EB-4FFB-8B7E-CA9640978DA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57C88608-6929-4D6B-B485-66BEE26151C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
   </bookViews>
   <sheets>
     <sheet name="LISTA DE PONTOS" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'DADOS COLETADOS'!$A$4:$AC$153</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'LISTA DE PONTOS'!$A$1:$K$150</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'LISTA DE PONTOS'!$A$1:$K$150</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'LISTA DE PONTOS'!$A$1:$K$148</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'LISTA DE PONTOS'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -4931,10 +4931,10 @@
         <v>246</v>
       </c>
       <c r="C21" s="5">
-        <v>-3.4485109999999999</v>
+        <v>-3.444842</v>
       </c>
       <c r="D21" s="5">
-        <v>-39.407550000000001</v>
+        <v>-39.394502000000003</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>48</v>
@@ -6506,10 +6506,10 @@
         <v>420</v>
       </c>
       <c r="C66" s="5">
-        <v>-3.5168159999999999</v>
+        <v>-3.512756</v>
       </c>
       <c r="D66" s="5">
-        <v>-39.583283000000002</v>
+        <v>-39.583770999999999</v>
       </c>
       <c r="E66" s="4" t="s">
         <v>266</v>
@@ -6541,10 +6541,10 @@
         <v>425</v>
       </c>
       <c r="C67" s="5">
-        <v>-3.6586500000000002</v>
+        <v>-3.6566749999999999</v>
       </c>
       <c r="D67" s="5">
-        <v>-39.420050000000003</v>
+        <v>-39.424249000000003</v>
       </c>
       <c r="E67" s="4" t="s">
         <v>426</v>
@@ -8186,10 +8186,10 @@
         <v>624</v>
       </c>
       <c r="C114" s="5">
-        <v>-3.4767329999999999</v>
+        <v>-3.4859019999999998</v>
       </c>
       <c r="D114" s="5">
-        <v>-39.541499999999999</v>
+        <v>-39.523645000000002</v>
       </c>
       <c r="E114" s="4" t="s">
         <v>415</v>
@@ -8956,10 +8956,10 @@
         <v>730</v>
       </c>
       <c r="C136" s="5">
-        <v>-3.4787659999999998</v>
+        <v>-3.4763199999999999</v>
       </c>
       <c r="D136" s="5">
-        <v>-39.626750000000001</v>
+        <v>-39.631295999999999</v>
       </c>
       <c r="E136" s="4" t="s">
         <v>48</v>
@@ -9474,18 +9474,16 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K150" xr:uid="{4DA12617-6B17-4A0E-9E79-EBA6E19B3138}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K150">
     <sortCondition ref="B1:B150"/>
   </sortState>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="20" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="63" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D18A476-0271-4A84-BE9E-901865A86FD3}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AC157"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -9697,7 +9695,7 @@
       <c r="AB4" s="11"/>
       <c r="AC4" s="25"/>
     </row>
-    <row r="5" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="19" t="s">
         <v>96</v>
       </c>
@@ -9740,7 +9738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
         <v>103</v>
       </c>
@@ -9783,7 +9781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="19" t="s">
         <v>109</v>
       </c>
@@ -9826,7 +9824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="19" t="s">
         <v>114</v>
       </c>
@@ -9869,7 +9867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
         <v>120</v>
       </c>
@@ -9912,7 +9910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="19" t="s">
         <v>125</v>
       </c>
@@ -9955,7 +9953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="19" t="s">
         <v>135</v>
       </c>
@@ -10046,7 +10044,7 @@
         <v>5682</v>
       </c>
     </row>
-    <row r="12" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="19" t="s">
         <v>141</v>
       </c>
@@ -10089,7 +10087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
         <v>147</v>
       </c>
@@ -10132,7 +10130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="19" t="s">
         <v>159</v>
       </c>
@@ -10223,7 +10221,7 @@
         <v>5190</v>
       </c>
     </row>
-    <row r="15" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="19" t="s">
         <v>173</v>
       </c>
@@ -10266,7 +10264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="19" t="s">
         <v>180</v>
       </c>
@@ -10309,7 +10307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="19" t="s">
         <v>185</v>
       </c>
@@ -10443,7 +10441,7 @@
         <v>3934</v>
       </c>
     </row>
-    <row r="19" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="19" t="s">
         <v>196</v>
       </c>
@@ -10534,7 +10532,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="20" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="19" t="s">
         <v>607</v>
       </c>
@@ -10625,7 +10623,7 @@
         <v>4245</v>
       </c>
     </row>
-    <row r="21" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="19" t="s">
         <v>613</v>
       </c>
@@ -10668,7 +10666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="19" t="s">
         <v>618</v>
       </c>
@@ -10759,7 +10757,7 @@
         <v>2038</v>
       </c>
     </row>
-    <row r="23" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="19" t="s">
         <v>624</v>
       </c>
@@ -10802,7 +10800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="19" t="s">
         <v>629</v>
       </c>
@@ -10845,7 +10843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="19" t="s">
         <v>635</v>
       </c>
@@ -10888,7 +10886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="19" t="s">
         <v>640</v>
       </c>
@@ -10931,7 +10929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="19" t="s">
         <v>645</v>
       </c>
@@ -10974,7 +10972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="19" t="s">
         <v>202</v>
       </c>
@@ -11065,7 +11063,7 @@
         <v>9101</v>
       </c>
     </row>
-    <row r="29" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
         <v>650</v>
       </c>
@@ -11156,7 +11154,7 @@
         <v>2316</v>
       </c>
     </row>
-    <row r="30" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
         <v>655</v>
       </c>
@@ -11199,7 +11197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
         <v>660</v>
       </c>
@@ -11290,7 +11288,7 @@
         <v>1584</v>
       </c>
     </row>
-    <row r="32" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
         <v>664</v>
       </c>
@@ -11333,7 +11331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
         <v>669</v>
       </c>
@@ -11376,7 +11374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="19" t="s">
         <v>674</v>
       </c>
@@ -11419,7 +11417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
         <v>678</v>
       </c>
@@ -11462,7 +11460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
         <v>683</v>
       </c>
@@ -11505,7 +11503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
         <v>688</v>
       </c>
@@ -11548,7 +11546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="19" t="s">
         <v>694</v>
       </c>
@@ -11591,7 +11589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="19" t="s">
         <v>699</v>
       </c>
@@ -11634,7 +11632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="19" t="s">
         <v>705</v>
       </c>
@@ -11677,7 +11675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="19" t="s">
         <v>709</v>
       </c>
@@ -11720,7 +11718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="19" t="s">
         <v>715</v>
       </c>
@@ -11811,7 +11809,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="43" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="19" t="s">
         <v>720</v>
       </c>
@@ -11854,7 +11852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="19" t="s">
         <v>725</v>
       </c>
@@ -11897,7 +11895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="19" t="s">
         <v>730</v>
       </c>
@@ -11940,7 +11938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="19" t="s">
         <v>734</v>
       </c>
@@ -11983,7 +11981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="19" t="s">
         <v>739</v>
       </c>
@@ -12074,7 +12072,7 @@
         <v>2429</v>
       </c>
     </row>
-    <row r="48" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="19" t="s">
         <v>744</v>
       </c>
@@ -12117,7 +12115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="19" t="s">
         <v>749</v>
       </c>
@@ -12160,7 +12158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="19" t="s">
         <v>754</v>
       </c>
@@ -12251,7 +12249,7 @@
         <v>2483</v>
       </c>
     </row>
-    <row r="51" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="19" t="s">
         <v>758</v>
       </c>
@@ -12342,7 +12340,7 @@
         <v>4263</v>
       </c>
     </row>
-    <row r="52" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="19" t="s">
         <v>763</v>
       </c>
@@ -12385,7 +12383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="19" t="s">
         <v>767</v>
       </c>
@@ -12428,7 +12426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="19" t="s">
         <v>772</v>
       </c>
@@ -12519,7 +12517,7 @@
         <v>1560</v>
       </c>
     </row>
-    <row r="55" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="19" t="s">
         <v>777</v>
       </c>
@@ -12610,7 +12608,7 @@
         <v>1864</v>
       </c>
     </row>
-    <row r="56" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="19" t="s">
         <v>782</v>
       </c>
@@ -12653,7 +12651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="19" t="s">
         <v>788</v>
       </c>
@@ -12696,7 +12694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="19" t="s">
         <v>794</v>
       </c>
@@ -12739,7 +12737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="19" t="s">
         <v>799</v>
       </c>
@@ -12782,7 +12780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="19" t="s">
         <v>315</v>
       </c>
@@ -12873,7 +12871,7 @@
         <v>2567</v>
       </c>
     </row>
-    <row r="61" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="19" t="s">
         <v>320</v>
       </c>
@@ -12916,7 +12914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="19" t="s">
         <v>325</v>
       </c>
@@ -12959,7 +12957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="19" t="s">
         <v>330</v>
       </c>
@@ -13050,7 +13048,7 @@
         <v>2906</v>
       </c>
     </row>
-    <row r="64" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="19" t="s">
         <v>335</v>
       </c>
@@ -13093,7 +13091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="19" t="s">
         <v>341</v>
       </c>
@@ -13136,7 +13134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="19" t="s">
         <v>130</v>
       </c>
@@ -13227,7 +13225,7 @@
         <v>5492</v>
       </c>
     </row>
-    <row r="67" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="19" t="s">
         <v>347</v>
       </c>
@@ -13318,7 +13316,7 @@
         <v>3330</v>
       </c>
     </row>
-    <row r="68" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="19" t="s">
         <v>351</v>
       </c>
@@ -13543,7 +13541,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="71" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="19" t="s">
         <v>368</v>
       </c>
@@ -13557,7 +13555,7 @@
       <c r="E71" s="21"/>
       <c r="F71" s="20"/>
       <c r="G71" s="20">
-        <f t="shared" ref="G70:G133" si="5">F71+2</f>
+        <f t="shared" ref="G71:G133" si="5">F71+2</f>
         <v>2</v>
       </c>
       <c r="H71" s="12"/>
@@ -13586,7 +13584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="19" t="s">
         <v>374</v>
       </c>
@@ -13629,7 +13627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="19" t="s">
         <v>380</v>
       </c>
@@ -13672,7 +13670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="19" t="s">
         <v>386</v>
       </c>
@@ -13715,7 +13713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="19" t="s">
         <v>391</v>
       </c>
@@ -13758,7 +13756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="19" t="s">
         <v>397</v>
       </c>
@@ -13801,7 +13799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="19" t="s">
         <v>403</v>
       </c>
@@ -13844,7 +13842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="19" t="s">
         <v>408</v>
       </c>
@@ -13887,7 +13885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="19" t="s">
         <v>414</v>
       </c>
@@ -13930,7 +13928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="19" t="s">
         <v>420</v>
       </c>
@@ -13973,7 +13971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="19" t="s">
         <v>425</v>
       </c>
@@ -14016,7 +14014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="19" t="s">
         <v>431</v>
       </c>
@@ -14059,7 +14057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="19" t="s">
         <v>436</v>
       </c>
@@ -14150,7 +14148,7 @@
         <v>6031</v>
       </c>
     </row>
-    <row r="84" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="19" t="s">
         <v>440</v>
       </c>
@@ -14193,7 +14191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="19" t="s">
         <v>445</v>
       </c>
@@ -14236,7 +14234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="19" t="s">
         <v>451</v>
       </c>
@@ -14279,7 +14277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="19" t="s">
         <v>456</v>
       </c>
@@ -14322,7 +14320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="19" t="s">
         <v>461</v>
       </c>
@@ -14413,7 +14411,7 @@
         <v>6697</v>
       </c>
     </row>
-    <row r="89" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="19" t="s">
         <v>466</v>
       </c>
@@ -14456,7 +14454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="19" t="s">
         <v>471</v>
       </c>
@@ -14547,7 +14545,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="91" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="19" t="s">
         <v>475</v>
       </c>
@@ -14590,7 +14588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="19" t="s">
         <v>481</v>
       </c>
@@ -14633,7 +14631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="19" t="s">
         <v>485</v>
       </c>
@@ -14724,7 +14722,7 @@
         <v>988</v>
       </c>
     </row>
-    <row r="94" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="19" t="s">
         <v>153</v>
       </c>
@@ -14906,7 +14904,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="96" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="19" t="s">
         <v>497</v>
       </c>
@@ -14997,7 +14995,7 @@
         <v>3307</v>
       </c>
     </row>
-    <row r="97" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="19" t="s">
         <v>502</v>
       </c>
@@ -15088,7 +15086,7 @@
         <v>7063</v>
       </c>
     </row>
-    <row r="98" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="19" t="s">
         <v>505</v>
       </c>
@@ -15131,7 +15129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="19" t="s">
         <v>511</v>
       </c>
@@ -15174,7 +15172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="19" t="s">
         <v>516</v>
       </c>
@@ -15217,7 +15215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="19" t="s">
         <v>521</v>
       </c>
@@ -15260,7 +15258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="19" t="s">
         <v>527</v>
       </c>
@@ -15303,7 +15301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="19" t="s">
         <v>164</v>
       </c>
@@ -15394,7 +15392,7 @@
         <v>2499</v>
       </c>
     </row>
-    <row r="104" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="19" t="s">
         <v>533</v>
       </c>
@@ -15485,7 +15483,7 @@
         <v>2533</v>
       </c>
     </row>
-    <row r="105" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="19" t="s">
         <v>539</v>
       </c>
@@ -15576,7 +15574,7 @@
         <v>2124</v>
       </c>
     </row>
-    <row r="106" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="19" t="s">
         <v>545</v>
       </c>
@@ -15619,7 +15617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="19" t="s">
         <v>550</v>
       </c>
@@ -15662,7 +15660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="19" t="s">
         <v>170</v>
       </c>
@@ -15753,7 +15751,7 @@
         <v>1973</v>
       </c>
     </row>
-    <row r="109" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="19" t="s">
         <v>555</v>
       </c>
@@ -15796,7 +15794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="19" t="s">
         <v>559</v>
       </c>
@@ -15887,7 +15885,7 @@
         <v>5171</v>
       </c>
     </row>
-    <row r="111" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="19" t="s">
         <v>565</v>
       </c>
@@ -15978,7 +15976,7 @@
         <v>5543</v>
       </c>
     </row>
-    <row r="112" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="19" t="s">
         <v>570</v>
       </c>
@@ -16069,7 +16067,7 @@
         <v>4135</v>
       </c>
     </row>
-    <row r="113" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="19" t="s">
         <v>575</v>
       </c>
@@ -16203,7 +16201,7 @@
         <v>2947</v>
       </c>
     </row>
-    <row r="115" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="19" t="s">
         <v>586</v>
       </c>
@@ -16246,7 +16244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="19" t="s">
         <v>592</v>
       </c>
@@ -16289,7 +16287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="19" t="s">
         <v>597</v>
       </c>
@@ -16332,7 +16330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="19" t="s">
         <v>602</v>
       </c>
@@ -16375,7 +16373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="19" t="s">
         <v>11</v>
       </c>
@@ -16466,7 +16464,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="120" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="19" t="s">
         <v>20</v>
       </c>
@@ -16557,7 +16555,7 @@
         <v>1773</v>
       </c>
     </row>
-    <row r="121" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="19" t="s">
         <v>24</v>
       </c>
@@ -16600,7 +16598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="19" t="s">
         <v>30</v>
       </c>
@@ -16691,7 +16689,7 @@
         <v>4915</v>
       </c>
     </row>
-    <row r="123" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="19" t="s">
         <v>35</v>
       </c>
@@ -16734,7 +16732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="19" t="s">
         <v>41</v>
       </c>
@@ -16777,7 +16775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="19" t="s">
         <v>63</v>
       </c>
@@ -16820,7 +16818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="19" t="s">
         <v>69</v>
       </c>
@@ -16863,7 +16861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="19" t="s">
         <v>213</v>
       </c>
@@ -16906,7 +16904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="19" t="s">
         <v>265</v>
       </c>
@@ -16949,7 +16947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="19" t="s">
         <v>271</v>
       </c>
@@ -16992,7 +16990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="19" t="s">
         <v>277</v>
       </c>
@@ -17083,7 +17081,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="131" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="19" t="s">
         <v>282</v>
       </c>
@@ -17174,7 +17172,7 @@
         <v>1984</v>
       </c>
     </row>
-    <row r="132" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="19" t="s">
         <v>81</v>
       </c>
@@ -17265,7 +17263,7 @@
         <v>2597</v>
       </c>
     </row>
-    <row r="133" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="19" t="s">
         <v>86</v>
       </c>
@@ -17356,7 +17354,7 @@
         <v>1733</v>
       </c>
     </row>
-    <row r="134" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="19" t="s">
         <v>92</v>
       </c>
@@ -17447,7 +17445,7 @@
         <v>1724</v>
       </c>
     </row>
-    <row r="135" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="19" t="s">
         <v>287</v>
       </c>
@@ -17490,7 +17488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="19" t="s">
         <v>292</v>
       </c>
@@ -17533,7 +17531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="19" t="s">
         <v>47</v>
       </c>
@@ -17576,7 +17574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="19" t="s">
         <v>53</v>
       </c>
@@ -17619,7 +17617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="19" t="s">
         <v>57</v>
       </c>
@@ -17662,7 +17660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="19" t="s">
         <v>75</v>
       </c>
@@ -17753,7 +17751,7 @@
         <v>1839</v>
       </c>
     </row>
-    <row r="141" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="19" t="s">
         <v>207</v>
       </c>
@@ -17844,7 +17842,7 @@
         <v>2840</v>
       </c>
     </row>
-    <row r="142" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="19" t="s">
         <v>218</v>
       </c>
@@ -17935,7 +17933,7 @@
         <v>1451</v>
       </c>
     </row>
-    <row r="143" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="19" t="s">
         <v>223</v>
       </c>
@@ -17978,7 +17976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="19" t="s">
         <v>228</v>
       </c>
@@ -18069,7 +18067,7 @@
         <v>2854</v>
       </c>
     </row>
-    <row r="145" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="19" t="s">
         <v>234</v>
       </c>
@@ -18112,7 +18110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="19" t="s">
         <v>240</v>
       </c>
@@ -18155,7 +18153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="19" t="s">
         <v>246</v>
       </c>
@@ -18198,7 +18196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="19" t="s">
         <v>251</v>
       </c>
@@ -18241,7 +18239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="19" t="s">
         <v>256</v>
       </c>
@@ -18284,7 +18282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="19" t="s">
         <v>261</v>
       </c>
@@ -18327,7 +18325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="19" t="s">
         <v>298</v>
       </c>
@@ -18370,7 +18368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="19" t="s">
         <v>303</v>
       </c>
@@ -18461,7 +18459,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="153" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="19" t="s">
         <v>310</v>
       </c>
@@ -18524,15 +18522,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A4:AC153" xr:uid="{1D18A476-0271-4A84-BE9E-901865A86FD3}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="P 113"/>
-        <filter val="P 115"/>
-        <filter val="P 155"/>
-        <filter val="P 195"/>
-        <filter val="P 24"/>
-      </filters>
-    </filterColumn>
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="9">

--- a/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
+++ b/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57C88608-6929-4D6B-B485-66BEE26151C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06BA95FA-0016-49FF-BD0B-520DB7E379B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
   </bookViews>
   <sheets>
     <sheet name="LISTA DE PONTOS" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'DADOS COLETADOS'!$A$4:$AC$153</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'LISTA DE PONTOS'!$A$1:$K$150</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'LISTA DE PONTOS'!$A$1:$K$148</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'LISTA DE PONTOS'!$A$1:$K$150</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'LISTA DE PONTOS'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1853" uniqueCount="865">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1861" uniqueCount="873">
   <si>
     <t>WKT</t>
   </si>
@@ -2639,6 +2639,30 @@
   </si>
   <si>
     <t xml:space="preserve"> -39,305516°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -3.485902°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -39.523645°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -3.476320°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -39.631296°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -3.512756° </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -39.583771°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -3.444842°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -39.394502°</t>
   </si>
 </sst>
 </file>
@@ -4203,7 +4227,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DA12617-6B17-4A0E-9E79-EBA6E19B3138}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K150"/>
@@ -4211,7 +4235,7 @@
   <cols>
     <col min="1" max="1" width="27" style="1" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16" style="1" bestFit="1" customWidth="1"/>
@@ -4258,7 +4282,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -4293,7 +4317,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>19</v>
       </c>
@@ -4328,7 +4352,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>23</v>
       </c>
@@ -4363,7 +4387,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>29</v>
       </c>
@@ -4398,7 +4422,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>34</v>
       </c>
@@ -4433,7 +4457,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>40</v>
       </c>
@@ -4468,7 +4492,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>46</v>
       </c>
@@ -4503,7 +4527,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>52</v>
       </c>
@@ -4546,10 +4570,10 @@
         <v>57</v>
       </c>
       <c r="C10" s="5">
-        <v>-2.9375879999999999</v>
+        <v>-2.9383110000000001</v>
       </c>
       <c r="D10" s="5">
-        <v>-40.181438</v>
+        <v>-40.181694</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>58</v>
@@ -4567,13 +4591,13 @@
         <v>16</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>17</v>
+        <v>837</v>
       </c>
       <c r="K10" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>62</v>
       </c>
@@ -4608,7 +4632,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>68</v>
       </c>
@@ -4643,7 +4667,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>74</v>
       </c>
@@ -4678,7 +4702,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>206</v>
       </c>
@@ -4713,7 +4737,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>212</v>
       </c>
@@ -4748,7 +4772,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>217</v>
       </c>
@@ -4783,7 +4807,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>222</v>
       </c>
@@ -4818,7 +4842,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>227</v>
       </c>
@@ -4853,7 +4877,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>233</v>
       </c>
@@ -4888,7 +4912,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>239</v>
       </c>
@@ -4952,13 +4976,13 @@
         <v>16</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>837</v>
+        <v>804</v>
       </c>
       <c r="K21" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>250</v>
       </c>
@@ -4993,7 +5017,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>255</v>
       </c>
@@ -5028,7 +5052,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>260</v>
       </c>
@@ -5063,7 +5087,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>264</v>
       </c>
@@ -5098,7 +5122,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>270</v>
       </c>
@@ -5133,7 +5157,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>276</v>
       </c>
@@ -5168,7 +5192,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>281</v>
       </c>
@@ -5203,7 +5227,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>80</v>
       </c>
@@ -5238,7 +5262,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>85</v>
       </c>
@@ -5273,7 +5297,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>91</v>
       </c>
@@ -5308,7 +5332,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>286</v>
       </c>
@@ -5343,7 +5367,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>291</v>
       </c>
@@ -5378,7 +5402,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>297</v>
       </c>
@@ -5413,7 +5437,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>302</v>
       </c>
@@ -5448,7 +5472,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>309</v>
       </c>
@@ -5483,7 +5507,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>95</v>
       </c>
@@ -5518,7 +5542,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>102</v>
       </c>
@@ -5553,7 +5577,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>108</v>
       </c>
@@ -5588,7 +5612,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>113</v>
       </c>
@@ -5623,7 +5647,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>119</v>
       </c>
@@ -5658,7 +5682,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>124</v>
       </c>
@@ -5693,7 +5717,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>314</v>
       </c>
@@ -5728,7 +5752,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>319</v>
       </c>
@@ -5763,7 +5787,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>324</v>
       </c>
@@ -5798,7 +5822,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>329</v>
       </c>
@@ -5833,7 +5857,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>334</v>
       </c>
@@ -5868,7 +5892,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>340</v>
       </c>
@@ -5903,7 +5927,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>129</v>
       </c>
@@ -5938,7 +5962,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>134</v>
       </c>
@@ -5973,7 +5997,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>346</v>
       </c>
@@ -6008,7 +6032,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>350</v>
       </c>
@@ -6043,7 +6067,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>356</v>
       </c>
@@ -6078,7 +6102,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>361</v>
       </c>
@@ -6113,7 +6137,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>367</v>
       </c>
@@ -6148,7 +6172,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>140</v>
       </c>
@@ -6183,7 +6207,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>373</v>
       </c>
@@ -6218,7 +6242,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>379</v>
       </c>
@@ -6253,7 +6277,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>146</v>
       </c>
@@ -6288,7 +6312,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>385</v>
       </c>
@@ -6323,7 +6347,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>390</v>
       </c>
@@ -6358,7 +6382,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>396</v>
       </c>
@@ -6393,7 +6417,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>402</v>
       </c>
@@ -6428,7 +6452,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>407</v>
       </c>
@@ -6463,7 +6487,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>413</v>
       </c>
@@ -6527,7 +6551,7 @@
         <v>101</v>
       </c>
       <c r="J66" s="6" t="s">
-        <v>837</v>
+        <v>804</v>
       </c>
       <c r="K66" s="6" t="s">
         <v>18</v>
@@ -6568,7 +6592,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>430</v>
       </c>
@@ -6603,7 +6627,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>435</v>
       </c>
@@ -6638,7 +6662,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>439</v>
       </c>
@@ -6673,7 +6697,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>444</v>
       </c>
@@ -6708,7 +6732,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>450</v>
       </c>
@@ -6743,7 +6767,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>455</v>
       </c>
@@ -6778,7 +6802,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>460</v>
       </c>
@@ -6813,7 +6837,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>465</v>
       </c>
@@ -6848,7 +6872,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>470</v>
       </c>
@@ -6883,7 +6907,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>474</v>
       </c>
@@ -6918,7 +6942,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>480</v>
       </c>
@@ -6953,7 +6977,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>484</v>
       </c>
@@ -6988,7 +7012,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>152</v>
       </c>
@@ -7023,7 +7047,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>490</v>
       </c>
@@ -7058,7 +7082,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>496</v>
       </c>
@@ -7093,7 +7117,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>501</v>
       </c>
@@ -7128,7 +7152,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>504</v>
       </c>
@@ -7163,7 +7187,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>510</v>
       </c>
@@ -7198,7 +7222,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>158</v>
       </c>
@@ -7233,7 +7257,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>515</v>
       </c>
@@ -7268,7 +7292,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>520</v>
       </c>
@@ -7303,7 +7327,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>526</v>
       </c>
@@ -7338,7 +7362,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>163</v>
       </c>
@@ -7373,7 +7397,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>532</v>
       </c>
@@ -7408,7 +7432,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>538</v>
       </c>
@@ -7443,7 +7467,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>544</v>
       </c>
@@ -7478,7 +7502,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>549</v>
       </c>
@@ -7513,7 +7537,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>169</v>
       </c>
@@ -7548,7 +7572,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>554</v>
       </c>
@@ -7583,7 +7607,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>558</v>
       </c>
@@ -7618,7 +7642,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>564</v>
       </c>
@@ -7653,7 +7677,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>569</v>
       </c>
@@ -7688,7 +7712,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>574</v>
       </c>
@@ -7723,7 +7747,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>580</v>
       </c>
@@ -7758,7 +7782,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>585</v>
       </c>
@@ -7793,7 +7817,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>591</v>
       </c>
@@ -7828,7 +7852,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>596</v>
       </c>
@@ -7863,7 +7887,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>601</v>
       </c>
@@ -7898,7 +7922,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>172</v>
       </c>
@@ -7941,10 +7965,10 @@
         <v>180</v>
       </c>
       <c r="C107" s="5">
-        <v>-2.9157660000000001</v>
+        <v>-2.9143889999999999</v>
       </c>
       <c r="D107" s="5">
-        <v>-40.170183000000002</v>
+        <v>-40.170302</v>
       </c>
       <c r="E107" s="4" t="s">
         <v>174</v>
@@ -7962,13 +7986,13 @@
         <v>101</v>
       </c>
       <c r="J107" s="6" t="s">
-        <v>17</v>
+        <v>837</v>
       </c>
       <c r="K107" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>184</v>
       </c>
@@ -8003,7 +8027,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>189</v>
       </c>
@@ -8038,7 +8062,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>195</v>
       </c>
@@ -8073,7 +8097,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>606</v>
       </c>
@@ -8108,7 +8132,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>612</v>
       </c>
@@ -8143,7 +8167,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>617</v>
       </c>
@@ -8207,13 +8231,13 @@
         <v>101</v>
       </c>
       <c r="J114" s="6" t="s">
-        <v>837</v>
+        <v>804</v>
       </c>
       <c r="K114" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>628</v>
       </c>
@@ -8248,7 +8272,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>634</v>
       </c>
@@ -8283,7 +8307,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>639</v>
       </c>
@@ -8318,7 +8342,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>644</v>
       </c>
@@ -8353,7 +8377,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>201</v>
       </c>
@@ -8388,7 +8412,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>649</v>
       </c>
@@ -8423,7 +8447,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>654</v>
       </c>
@@ -8458,7 +8482,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>659</v>
       </c>
@@ -8493,7 +8517,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>663</v>
       </c>
@@ -8536,10 +8560,10 @@
         <v>669</v>
       </c>
       <c r="C124" s="5">
-        <v>-2.8939659999999998</v>
+        <v>-2.8945319999999999</v>
       </c>
       <c r="D124" s="5">
-        <v>-40.223399999999998</v>
+        <v>-40.225693999999997</v>
       </c>
       <c r="E124" s="4" t="s">
         <v>174</v>
@@ -8557,13 +8581,13 @@
         <v>101</v>
       </c>
       <c r="J124" s="6" t="s">
-        <v>17</v>
+        <v>837</v>
       </c>
       <c r="K124" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>673</v>
       </c>
@@ -8598,7 +8622,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>677</v>
       </c>
@@ -8633,7 +8657,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>682</v>
       </c>
@@ -8668,7 +8692,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>687</v>
       </c>
@@ -8703,7 +8727,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>693</v>
       </c>
@@ -8738,7 +8762,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>698</v>
       </c>
@@ -8773,7 +8797,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>704</v>
       </c>
@@ -8808,7 +8832,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>708</v>
       </c>
@@ -8843,7 +8867,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>714</v>
       </c>
@@ -8878,7 +8902,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>719</v>
       </c>
@@ -8913,7 +8937,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>724</v>
       </c>
@@ -8977,13 +9001,13 @@
         <v>101</v>
       </c>
       <c r="J136" s="6" t="s">
-        <v>837</v>
+        <v>804</v>
       </c>
       <c r="K136" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>733</v>
       </c>
@@ -9018,7 +9042,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>738</v>
       </c>
@@ -9082,7 +9106,7 @@
         <v>151</v>
       </c>
       <c r="J139" s="6" t="s">
-        <v>17</v>
+        <v>837</v>
       </c>
       <c r="K139" s="6" t="s">
         <v>18</v>
@@ -9096,10 +9120,10 @@
         <v>749</v>
       </c>
       <c r="C140" s="5">
-        <v>-2.9087830000000001</v>
+        <v>-2.92225</v>
       </c>
       <c r="D140" s="5">
-        <v>-40.118616000000003</v>
+        <v>-40.120244</v>
       </c>
       <c r="E140" s="4" t="s">
         <v>560</v>
@@ -9117,13 +9141,13 @@
         <v>101</v>
       </c>
       <c r="J140" s="6" t="s">
-        <v>17</v>
+        <v>837</v>
       </c>
       <c r="K140" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>753</v>
       </c>
@@ -9158,7 +9182,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>757</v>
       </c>
@@ -9193,7 +9217,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>762</v>
       </c>
@@ -9228,7 +9252,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>766</v>
       </c>
@@ -9263,7 +9287,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>771</v>
       </c>
@@ -9298,7 +9322,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>776</v>
       </c>
@@ -9333,7 +9357,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>781</v>
       </c>
@@ -9368,7 +9392,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>787</v>
       </c>
@@ -9403,7 +9427,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>793</v>
       </c>
@@ -9438,7 +9462,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>798</v>
       </c>
@@ -9474,6 +9498,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K150" xr:uid="{4DA12617-6B17-4A0E-9E79-EBA6E19B3138}">
+    <filterColumn colId="9">
+      <filters>
+        <filter val="EM ANDAMENTO"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K150">
     <sortCondition ref="B1:B150"/>
   </sortState>
@@ -9484,6 +9515,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D18A476-0271-4A84-BE9E-901865A86FD3}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AC157"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -9695,7 +9727,7 @@
       <c r="AB4" s="11"/>
       <c r="AC4" s="25"/>
     </row>
-    <row r="5" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="19" t="s">
         <v>96</v>
       </c>
@@ -9738,7 +9770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
         <v>103</v>
       </c>
@@ -9781,7 +9813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="19" t="s">
         <v>109</v>
       </c>
@@ -9824,7 +9856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="19" t="s">
         <v>114</v>
       </c>
@@ -9867,7 +9899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
         <v>120</v>
       </c>
@@ -9910,7 +9942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="19" t="s">
         <v>125</v>
       </c>
@@ -9953,7 +9985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="19" t="s">
         <v>135</v>
       </c>
@@ -10044,7 +10076,7 @@
         <v>5682</v>
       </c>
     </row>
-    <row r="12" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="19" t="s">
         <v>141</v>
       </c>
@@ -10087,7 +10119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
         <v>147</v>
       </c>
@@ -10130,7 +10162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="19" t="s">
         <v>159</v>
       </c>
@@ -10221,7 +10253,7 @@
         <v>5190</v>
       </c>
     </row>
-    <row r="15" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="19" t="s">
         <v>173</v>
       </c>
@@ -10264,7 +10296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="19" t="s">
         <v>180</v>
       </c>
@@ -10307,7 +10339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="19" t="s">
         <v>185</v>
       </c>
@@ -10350,7 +10382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="19" t="s">
         <v>190</v>
       </c>
@@ -10441,7 +10473,7 @@
         <v>3934</v>
       </c>
     </row>
-    <row r="19" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="19" t="s">
         <v>196</v>
       </c>
@@ -10532,7 +10564,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="20" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="19" t="s">
         <v>607</v>
       </c>
@@ -10623,7 +10655,7 @@
         <v>4245</v>
       </c>
     </row>
-    <row r="21" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="19" t="s">
         <v>613</v>
       </c>
@@ -10666,7 +10698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="19" t="s">
         <v>618</v>
       </c>
@@ -10686,7 +10718,7 @@
         <v>46128</v>
       </c>
       <c r="G22" s="20">
-        <f t="shared" ref="G22" si="2">F22+2</f>
+        <f t="shared" ref="G22:G23" si="2">F22+2</f>
         <v>46130</v>
       </c>
       <c r="H22" s="12">
@@ -10767,40 +10799,88 @@
       <c r="C23" s="19" t="s">
         <v>625</v>
       </c>
-      <c r="D23" s="21"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="20"/>
+      <c r="D23" s="24" t="s">
+        <v>865</v>
+      </c>
+      <c r="E23" s="24" t="s">
+        <v>866</v>
+      </c>
+      <c r="F23" s="20">
+        <v>46153</v>
+      </c>
       <c r="G23" s="20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
+        <v>46155</v>
+      </c>
+      <c r="H23" s="12">
+        <v>1241</v>
+      </c>
+      <c r="I23" s="12">
+        <v>5192</v>
+      </c>
+      <c r="J23" s="12">
+        <v>53</v>
+      </c>
+      <c r="K23" s="12">
+        <v>350</v>
+      </c>
+      <c r="L23" s="12">
+        <v>93</v>
+      </c>
+      <c r="M23" s="12">
+        <v>29</v>
+      </c>
+      <c r="N23" s="12">
+        <v>37</v>
+      </c>
+      <c r="O23" s="12">
+        <v>9</v>
+      </c>
+      <c r="P23" s="12">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="12">
+        <v>7</v>
+      </c>
+      <c r="R23" s="12">
+        <v>12</v>
+      </c>
+      <c r="S23" s="12">
+        <v>18</v>
+      </c>
+      <c r="T23" s="12">
+        <v>40</v>
+      </c>
+      <c r="U23" s="12">
+        <v>3</v>
+      </c>
+      <c r="V23" s="12">
+        <v>0</v>
+      </c>
+      <c r="W23" s="12">
+        <v>6</v>
+      </c>
+      <c r="X23" s="12">
         <v>2</v>
       </c>
-      <c r="H23" s="12"/>
-      <c r="I23" s="12"/>
-      <c r="J23" s="12"/>
-      <c r="K23" s="12"/>
-      <c r="L23" s="12"/>
-      <c r="M23" s="12"/>
-      <c r="N23" s="12"/>
-      <c r="O23" s="12"/>
-      <c r="P23" s="12"/>
-      <c r="Q23" s="12"/>
-      <c r="R23" s="12"/>
-      <c r="S23" s="12"/>
-      <c r="T23" s="12"/>
-      <c r="U23" s="12"/>
-      <c r="V23" s="12"/>
-      <c r="W23" s="12"/>
-      <c r="X23" s="12"/>
-      <c r="Y23" s="12"/>
-      <c r="Z23" s="12"/>
-      <c r="AA23" s="12"/>
-      <c r="AB23" s="12"/>
+      <c r="Y23" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="12">
+        <v>9</v>
+      </c>
+      <c r="AA23" s="12">
+        <v>2</v>
+      </c>
+      <c r="AB23" s="12">
+        <v>2</v>
+      </c>
       <c r="AC23" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>7108</v>
+      </c>
+    </row>
+    <row r="24" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="19" t="s">
         <v>629</v>
       </c>
@@ -10843,7 +10923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="19" t="s">
         <v>635</v>
       </c>
@@ -10886,7 +10966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="19" t="s">
         <v>640</v>
       </c>
@@ -10929,7 +11009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="19" t="s">
         <v>645</v>
       </c>
@@ -10972,7 +11052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="19" t="s">
         <v>202</v>
       </c>
@@ -11063,7 +11143,7 @@
         <v>9101</v>
       </c>
     </row>
-    <row r="29" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
         <v>650</v>
       </c>
@@ -11154,7 +11234,7 @@
         <v>2316</v>
       </c>
     </row>
-    <row r="30" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
         <v>655</v>
       </c>
@@ -11197,7 +11277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
         <v>660</v>
       </c>
@@ -11288,7 +11368,7 @@
         <v>1584</v>
       </c>
     </row>
-    <row r="32" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
         <v>664</v>
       </c>
@@ -11331,7 +11411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
         <v>669</v>
       </c>
@@ -11374,7 +11454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="19" t="s">
         <v>674</v>
       </c>
@@ -11417,7 +11497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
         <v>678</v>
       </c>
@@ -11460,7 +11540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
         <v>683</v>
       </c>
@@ -11503,7 +11583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
         <v>688</v>
       </c>
@@ -11546,7 +11626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="19" t="s">
         <v>694</v>
       </c>
@@ -11589,7 +11669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="19" t="s">
         <v>699</v>
       </c>
@@ -11632,7 +11712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="19" t="s">
         <v>705</v>
       </c>
@@ -11675,7 +11755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="19" t="s">
         <v>709</v>
       </c>
@@ -11718,7 +11798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="19" t="s">
         <v>715</v>
       </c>
@@ -11809,7 +11889,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="43" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="19" t="s">
         <v>720</v>
       </c>
@@ -11852,7 +11932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="19" t="s">
         <v>725</v>
       </c>
@@ -11905,40 +11985,88 @@
       <c r="C45" s="19" t="s">
         <v>731</v>
       </c>
-      <c r="D45" s="21"/>
-      <c r="E45" s="21"/>
-      <c r="F45" s="20"/>
+      <c r="D45" s="24" t="s">
+        <v>867</v>
+      </c>
+      <c r="E45" s="24" t="s">
+        <v>868</v>
+      </c>
+      <c r="F45" s="20">
+        <v>46153</v>
+      </c>
       <c r="G45" s="20">
         <f t="shared" si="0"/>
+        <v>46155</v>
+      </c>
+      <c r="H45" s="12">
+        <v>2395</v>
+      </c>
+      <c r="I45" s="12">
+        <v>4219</v>
+      </c>
+      <c r="J45" s="12">
+        <v>318</v>
+      </c>
+      <c r="K45" s="12">
+        <v>551</v>
+      </c>
+      <c r="L45" s="12">
+        <v>193</v>
+      </c>
+      <c r="M45" s="12">
+        <v>38</v>
+      </c>
+      <c r="N45" s="12">
+        <v>55</v>
+      </c>
+      <c r="O45" s="12">
+        <v>6</v>
+      </c>
+      <c r="P45" s="12">
+        <v>9</v>
+      </c>
+      <c r="Q45" s="12">
+        <v>19</v>
+      </c>
+      <c r="R45" s="12">
+        <v>26</v>
+      </c>
+      <c r="S45" s="12">
+        <v>5</v>
+      </c>
+      <c r="T45" s="12">
+        <v>94</v>
+      </c>
+      <c r="U45" s="12">
+        <v>1</v>
+      </c>
+      <c r="V45" s="12">
+        <v>1</v>
+      </c>
+      <c r="W45" s="12">
+        <v>6</v>
+      </c>
+      <c r="X45" s="12">
+        <v>3</v>
+      </c>
+      <c r="Y45" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="12">
+        <v>14</v>
+      </c>
+      <c r="AA45" s="12">
         <v>2</v>
       </c>
-      <c r="H45" s="12"/>
-      <c r="I45" s="12"/>
-      <c r="J45" s="12"/>
-      <c r="K45" s="12"/>
-      <c r="L45" s="12"/>
-      <c r="M45" s="12"/>
-      <c r="N45" s="12"/>
-      <c r="O45" s="12"/>
-      <c r="P45" s="12"/>
-      <c r="Q45" s="12"/>
-      <c r="R45" s="12"/>
-      <c r="S45" s="12"/>
-      <c r="T45" s="12"/>
-      <c r="U45" s="12"/>
-      <c r="V45" s="12"/>
-      <c r="W45" s="12"/>
-      <c r="X45" s="12"/>
-      <c r="Y45" s="12"/>
-      <c r="Z45" s="12"/>
-      <c r="AA45" s="12"/>
-      <c r="AB45" s="12"/>
+      <c r="AB45" s="12">
+        <v>4</v>
+      </c>
       <c r="AC45" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>7959</v>
+      </c>
+    </row>
+    <row r="46" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="19" t="s">
         <v>734</v>
       </c>
@@ -11981,7 +12109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="19" t="s">
         <v>739</v>
       </c>
@@ -12072,7 +12200,7 @@
         <v>2429</v>
       </c>
     </row>
-    <row r="48" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="19" t="s">
         <v>744</v>
       </c>
@@ -12115,7 +12243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="19" t="s">
         <v>749</v>
       </c>
@@ -12158,7 +12286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="19" t="s">
         <v>754</v>
       </c>
@@ -12249,7 +12377,7 @@
         <v>2483</v>
       </c>
     </row>
-    <row r="51" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="19" t="s">
         <v>758</v>
       </c>
@@ -12340,7 +12468,7 @@
         <v>4263</v>
       </c>
     </row>
-    <row r="52" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="19" t="s">
         <v>763</v>
       </c>
@@ -12383,7 +12511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="19" t="s">
         <v>767</v>
       </c>
@@ -12426,7 +12554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="19" t="s">
         <v>772</v>
       </c>
@@ -12517,7 +12645,7 @@
         <v>1560</v>
       </c>
     </row>
-    <row r="55" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="19" t="s">
         <v>777</v>
       </c>
@@ -12608,7 +12736,7 @@
         <v>1864</v>
       </c>
     </row>
-    <row r="56" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="19" t="s">
         <v>782</v>
       </c>
@@ -12651,7 +12779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="19" t="s">
         <v>788</v>
       </c>
@@ -12694,7 +12822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="19" t="s">
         <v>794</v>
       </c>
@@ -12737,7 +12865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="19" t="s">
         <v>799</v>
       </c>
@@ -12780,7 +12908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="19" t="s">
         <v>315</v>
       </c>
@@ -12871,7 +12999,7 @@
         <v>2567</v>
       </c>
     </row>
-    <row r="61" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="19" t="s">
         <v>320</v>
       </c>
@@ -12914,7 +13042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="19" t="s">
         <v>325</v>
       </c>
@@ -12957,7 +13085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="19" t="s">
         <v>330</v>
       </c>
@@ -13048,7 +13176,7 @@
         <v>2906</v>
       </c>
     </row>
-    <row r="64" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="19" t="s">
         <v>335</v>
       </c>
@@ -13091,7 +13219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="19" t="s">
         <v>341</v>
       </c>
@@ -13134,7 +13262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="19" t="s">
         <v>130</v>
       </c>
@@ -13225,7 +13353,7 @@
         <v>5492</v>
       </c>
     </row>
-    <row r="67" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="19" t="s">
         <v>347</v>
       </c>
@@ -13316,7 +13444,7 @@
         <v>3330</v>
       </c>
     </row>
-    <row r="68" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="19" t="s">
         <v>351</v>
       </c>
@@ -13359,7 +13487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="19" t="s">
         <v>357</v>
       </c>
@@ -13450,7 +13578,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="70" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="19" t="s">
         <v>362</v>
       </c>
@@ -13541,7 +13669,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="71" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="19" t="s">
         <v>368</v>
       </c>
@@ -13584,7 +13712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="19" t="s">
         <v>374</v>
       </c>
@@ -13627,7 +13755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="19" t="s">
         <v>380</v>
       </c>
@@ -13670,7 +13798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="19" t="s">
         <v>386</v>
       </c>
@@ -13713,7 +13841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="19" t="s">
         <v>391</v>
       </c>
@@ -13756,7 +13884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="19" t="s">
         <v>397</v>
       </c>
@@ -13799,7 +13927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="19" t="s">
         <v>403</v>
       </c>
@@ -13842,7 +13970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="19" t="s">
         <v>408</v>
       </c>
@@ -13885,7 +14013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="19" t="s">
         <v>414</v>
       </c>
@@ -13938,40 +14066,88 @@
       <c r="C80" s="19" t="s">
         <v>421</v>
       </c>
-      <c r="D80" s="21"/>
-      <c r="E80" s="21"/>
-      <c r="F80" s="20"/>
+      <c r="D80" s="24" t="s">
+        <v>869</v>
+      </c>
+      <c r="E80" s="24" t="s">
+        <v>870</v>
+      </c>
+      <c r="F80" s="20">
+        <v>46153</v>
+      </c>
       <c r="G80" s="20">
         <f t="shared" si="5"/>
+        <v>46155</v>
+      </c>
+      <c r="H80" s="12">
+        <v>2987</v>
+      </c>
+      <c r="I80" s="12">
+        <v>942</v>
+      </c>
+      <c r="J80" s="12">
+        <v>18</v>
+      </c>
+      <c r="K80" s="12">
+        <v>128</v>
+      </c>
+      <c r="L80" s="12">
+        <v>7</v>
+      </c>
+      <c r="M80" s="12">
+        <v>0</v>
+      </c>
+      <c r="N80" s="12">
+        <v>52</v>
+      </c>
+      <c r="O80" s="12">
+        <v>0</v>
+      </c>
+      <c r="P80" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="12">
         <v>2</v>
       </c>
-      <c r="H80" s="12"/>
-      <c r="I80" s="12"/>
-      <c r="J80" s="12"/>
-      <c r="K80" s="12"/>
-      <c r="L80" s="12"/>
-      <c r="M80" s="12"/>
-      <c r="N80" s="12"/>
-      <c r="O80" s="12"/>
-      <c r="P80" s="12"/>
-      <c r="Q80" s="12"/>
-      <c r="R80" s="12"/>
-      <c r="S80" s="12"/>
-      <c r="T80" s="12"/>
-      <c r="U80" s="12"/>
-      <c r="V80" s="12"/>
-      <c r="W80" s="12"/>
-      <c r="X80" s="12"/>
-      <c r="Y80" s="12"/>
-      <c r="Z80" s="12"/>
-      <c r="AA80" s="12"/>
-      <c r="AB80" s="12"/>
+      <c r="R80" s="12">
+        <v>0</v>
+      </c>
+      <c r="S80" s="12">
+        <v>0</v>
+      </c>
+      <c r="T80" s="12">
+        <v>108</v>
+      </c>
+      <c r="U80" s="12">
+        <v>0</v>
+      </c>
+      <c r="V80" s="12">
+        <v>0</v>
+      </c>
+      <c r="W80" s="12">
+        <v>0</v>
+      </c>
+      <c r="X80" s="12">
+        <v>1</v>
+      </c>
+      <c r="Y80" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z80" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA80" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB80" s="12">
+        <v>1</v>
+      </c>
       <c r="AC80" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4247</v>
+      </c>
+    </row>
+    <row r="81" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="19" t="s">
         <v>425</v>
       </c>
@@ -14014,7 +14190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="19" t="s">
         <v>431</v>
       </c>
@@ -14057,7 +14233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="19" t="s">
         <v>436</v>
       </c>
@@ -14148,7 +14324,7 @@
         <v>6031</v>
       </c>
     </row>
-    <row r="84" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="19" t="s">
         <v>440</v>
       </c>
@@ -14191,7 +14367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="19" t="s">
         <v>445</v>
       </c>
@@ -14234,7 +14410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="19" t="s">
         <v>451</v>
       </c>
@@ -14277,7 +14453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="19" t="s">
         <v>456</v>
       </c>
@@ -14320,7 +14496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="19" t="s">
         <v>461</v>
       </c>
@@ -14411,7 +14587,7 @@
         <v>6697</v>
       </c>
     </row>
-    <row r="89" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="19" t="s">
         <v>466</v>
       </c>
@@ -14454,7 +14630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="19" t="s">
         <v>471</v>
       </c>
@@ -14545,7 +14721,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="91" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="19" t="s">
         <v>475</v>
       </c>
@@ -14588,7 +14764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="19" t="s">
         <v>481</v>
       </c>
@@ -14631,7 +14807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="19" t="s">
         <v>485</v>
       </c>
@@ -14722,7 +14898,7 @@
         <v>988</v>
       </c>
     </row>
-    <row r="94" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="19" t="s">
         <v>153</v>
       </c>
@@ -14813,7 +14989,7 @@
         <v>2883</v>
       </c>
     </row>
-    <row r="95" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="19" t="s">
         <v>491</v>
       </c>
@@ -14904,7 +15080,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="96" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="19" t="s">
         <v>497</v>
       </c>
@@ -14995,7 +15171,7 @@
         <v>3307</v>
       </c>
     </row>
-    <row r="97" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="19" t="s">
         <v>502</v>
       </c>
@@ -15086,7 +15262,7 @@
         <v>7063</v>
       </c>
     </row>
-    <row r="98" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="19" t="s">
         <v>505</v>
       </c>
@@ -15129,7 +15305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="19" t="s">
         <v>511</v>
       </c>
@@ -15172,7 +15348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="19" t="s">
         <v>516</v>
       </c>
@@ -15215,7 +15391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="19" t="s">
         <v>521</v>
       </c>
@@ -15258,7 +15434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="19" t="s">
         <v>527</v>
       </c>
@@ -15301,7 +15477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="19" t="s">
         <v>164</v>
       </c>
@@ -15392,7 +15568,7 @@
         <v>2499</v>
       </c>
     </row>
-    <row r="104" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="19" t="s">
         <v>533</v>
       </c>
@@ -15483,7 +15659,7 @@
         <v>2533</v>
       </c>
     </row>
-    <row r="105" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="19" t="s">
         <v>539</v>
       </c>
@@ -15574,7 +15750,7 @@
         <v>2124</v>
       </c>
     </row>
-    <row r="106" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="19" t="s">
         <v>545</v>
       </c>
@@ -15617,7 +15793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="19" t="s">
         <v>550</v>
       </c>
@@ -15660,7 +15836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="19" t="s">
         <v>170</v>
       </c>
@@ -15751,7 +15927,7 @@
         <v>1973</v>
       </c>
     </row>
-    <row r="109" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="19" t="s">
         <v>555</v>
       </c>
@@ -15794,7 +15970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="19" t="s">
         <v>559</v>
       </c>
@@ -15885,7 +16061,7 @@
         <v>5171</v>
       </c>
     </row>
-    <row r="111" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="19" t="s">
         <v>565</v>
       </c>
@@ -15976,7 +16152,7 @@
         <v>5543</v>
       </c>
     </row>
-    <row r="112" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="19" t="s">
         <v>570</v>
       </c>
@@ -16067,7 +16243,7 @@
         <v>4135</v>
       </c>
     </row>
-    <row r="113" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="19" t="s">
         <v>575</v>
       </c>
@@ -16110,7 +16286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="19" t="s">
         <v>581</v>
       </c>
@@ -16201,7 +16377,7 @@
         <v>2947</v>
       </c>
     </row>
-    <row r="115" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="19" t="s">
         <v>586</v>
       </c>
@@ -16244,7 +16420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="19" t="s">
         <v>592</v>
       </c>
@@ -16287,7 +16463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="19" t="s">
         <v>597</v>
       </c>
@@ -16330,7 +16506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="19" t="s">
         <v>602</v>
       </c>
@@ -16373,7 +16549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="19" t="s">
         <v>11</v>
       </c>
@@ -16464,7 +16640,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="120" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="19" t="s">
         <v>20</v>
       </c>
@@ -16555,7 +16731,7 @@
         <v>1773</v>
       </c>
     </row>
-    <row r="121" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="19" t="s">
         <v>24</v>
       </c>
@@ -16598,7 +16774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="19" t="s">
         <v>30</v>
       </c>
@@ -16689,7 +16865,7 @@
         <v>4915</v>
       </c>
     </row>
-    <row r="123" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="19" t="s">
         <v>35</v>
       </c>
@@ -16732,7 +16908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="19" t="s">
         <v>41</v>
       </c>
@@ -16775,7 +16951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="19" t="s">
         <v>63</v>
       </c>
@@ -16818,7 +16994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="19" t="s">
         <v>69</v>
       </c>
@@ -16861,7 +17037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="19" t="s">
         <v>213</v>
       </c>
@@ -16904,7 +17080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="19" t="s">
         <v>265</v>
       </c>
@@ -16947,7 +17123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="19" t="s">
         <v>271</v>
       </c>
@@ -16990,7 +17166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="19" t="s">
         <v>277</v>
       </c>
@@ -17081,7 +17257,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="131" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="19" t="s">
         <v>282</v>
       </c>
@@ -17172,7 +17348,7 @@
         <v>1984</v>
       </c>
     </row>
-    <row r="132" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="19" t="s">
         <v>81</v>
       </c>
@@ -17263,7 +17439,7 @@
         <v>2597</v>
       </c>
     </row>
-    <row r="133" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="19" t="s">
         <v>86</v>
       </c>
@@ -17354,7 +17530,7 @@
         <v>1733</v>
       </c>
     </row>
-    <row r="134" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="19" t="s">
         <v>92</v>
       </c>
@@ -17445,7 +17621,7 @@
         <v>1724</v>
       </c>
     </row>
-    <row r="135" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="19" t="s">
         <v>287</v>
       </c>
@@ -17488,7 +17664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="19" t="s">
         <v>292</v>
       </c>
@@ -17531,7 +17707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="19" t="s">
         <v>47</v>
       </c>
@@ -17574,7 +17750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="19" t="s">
         <v>53</v>
       </c>
@@ -17617,7 +17793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="19" t="s">
         <v>57</v>
       </c>
@@ -17660,7 +17836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="19" t="s">
         <v>75</v>
       </c>
@@ -17751,7 +17927,7 @@
         <v>1839</v>
       </c>
     </row>
-    <row r="141" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="19" t="s">
         <v>207</v>
       </c>
@@ -17842,7 +18018,7 @@
         <v>2840</v>
       </c>
     </row>
-    <row r="142" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="19" t="s">
         <v>218</v>
       </c>
@@ -17933,7 +18109,7 @@
         <v>1451</v>
       </c>
     </row>
-    <row r="143" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="19" t="s">
         <v>223</v>
       </c>
@@ -17976,7 +18152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="19" t="s">
         <v>228</v>
       </c>
@@ -18067,7 +18243,7 @@
         <v>2854</v>
       </c>
     </row>
-    <row r="145" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="19" t="s">
         <v>234</v>
       </c>
@@ -18110,7 +18286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="19" t="s">
         <v>240</v>
       </c>
@@ -18163,40 +18339,88 @@
       <c r="C147" s="19" t="s">
         <v>247</v>
       </c>
-      <c r="D147" s="21"/>
-      <c r="E147" s="21"/>
-      <c r="F147" s="20"/>
+      <c r="D147" s="24" t="s">
+        <v>871</v>
+      </c>
+      <c r="E147" s="24" t="s">
+        <v>872</v>
+      </c>
+      <c r="F147" s="20">
+        <v>46153</v>
+      </c>
       <c r="G147" s="20">
         <f t="shared" si="6"/>
+        <v>46155</v>
+      </c>
+      <c r="H147" s="12">
+        <v>433</v>
+      </c>
+      <c r="I147" s="12">
+        <v>2118</v>
+      </c>
+      <c r="J147" s="12">
+        <v>71</v>
+      </c>
+      <c r="K147" s="12">
+        <v>191</v>
+      </c>
+      <c r="L147" s="12">
+        <v>62</v>
+      </c>
+      <c r="M147" s="12">
+        <v>21</v>
+      </c>
+      <c r="N147" s="12">
+        <v>7</v>
+      </c>
+      <c r="O147" s="12">
+        <v>1</v>
+      </c>
+      <c r="P147" s="12">
+        <v>1</v>
+      </c>
+      <c r="Q147" s="12">
+        <v>7</v>
+      </c>
+      <c r="R147" s="12">
+        <v>7</v>
+      </c>
+      <c r="S147" s="12">
         <v>2</v>
       </c>
-      <c r="H147" s="12"/>
-      <c r="I147" s="12"/>
-      <c r="J147" s="12"/>
-      <c r="K147" s="12"/>
-      <c r="L147" s="12"/>
-      <c r="M147" s="12"/>
-      <c r="N147" s="12"/>
-      <c r="O147" s="12"/>
-      <c r="P147" s="12"/>
-      <c r="Q147" s="12"/>
-      <c r="R147" s="12"/>
-      <c r="S147" s="12"/>
-      <c r="T147" s="12"/>
-      <c r="U147" s="12"/>
-      <c r="V147" s="12"/>
-      <c r="W147" s="12"/>
-      <c r="X147" s="12"/>
-      <c r="Y147" s="12"/>
-      <c r="Z147" s="12"/>
-      <c r="AA147" s="12"/>
-      <c r="AB147" s="12"/>
+      <c r="T147" s="12">
+        <v>8</v>
+      </c>
+      <c r="U147" s="12">
+        <v>0</v>
+      </c>
+      <c r="V147" s="12">
+        <v>0</v>
+      </c>
+      <c r="W147" s="12">
+        <v>1</v>
+      </c>
+      <c r="X147" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y147" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z147" s="12">
+        <v>3</v>
+      </c>
+      <c r="AA147" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB147" s="12">
+        <v>3</v>
+      </c>
       <c r="AC147" s="13">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>2936</v>
+      </c>
+    </row>
+    <row r="148" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="19" t="s">
         <v>251</v>
       </c>
@@ -18239,7 +18463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="19" t="s">
         <v>256</v>
       </c>
@@ -18282,7 +18506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="19" t="s">
         <v>261</v>
       </c>
@@ -18325,7 +18549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="19" t="s">
         <v>298</v>
       </c>
@@ -18368,7 +18592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="19" t="s">
         <v>303</v>
       </c>
@@ -18459,7 +18683,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="153" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="19" t="s">
         <v>310</v>
       </c>
@@ -18522,6 +18746,14 @@
     </row>
   </sheetData>
   <autoFilter ref="A4:AC153" xr:uid="{1D18A476-0271-4A84-BE9E-901865A86FD3}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="E 153"/>
+        <filter val="P 137"/>
+        <filter val="P 33"/>
+        <filter val="P 77"/>
+      </filters>
+    </filterColumn>
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="9">

--- a/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
+++ b/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06BA95FA-0016-49FF-BD0B-520DB7E379B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8875C376-4238-4F73-A018-BFCC7B691975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
   </bookViews>
@@ -4947,7 +4947,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>245</v>
       </c>
@@ -6522,7 +6522,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>419</v>
       </c>
@@ -8202,7 +8202,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>623</v>
       </c>
@@ -8972,7 +8972,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>729</v>
       </c>
@@ -9085,10 +9085,10 @@
         <v>744</v>
       </c>
       <c r="C139" s="5">
-        <v>-2.9782660000000001</v>
+        <v>-2.9586229999999998</v>
       </c>
       <c r="D139" s="5">
-        <v>-39.890166000000001</v>
+        <v>-39.903604000000001</v>
       </c>
       <c r="E139" s="4" t="s">
         <v>174</v>

--- a/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
+++ b/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\MAPA CONTAGEM PDR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\5- MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8875C376-4238-4F73-A018-BFCC7B691975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D78174B-AC9F-4DD2-9855-FC214EB626F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
   </bookViews>
@@ -4562,7 +4562,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>56</v>
       </c>
@@ -4591,7 +4591,7 @@
         <v>16</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>837</v>
+        <v>804</v>
       </c>
       <c r="K10" s="6" t="s">
         <v>18</v>
@@ -6942,7 +6942,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>480</v>
       </c>
@@ -6971,7 +6971,7 @@
         <v>101</v>
       </c>
       <c r="J78" s="6" t="s">
-        <v>17</v>
+        <v>837</v>
       </c>
       <c r="K78" s="6" t="s">
         <v>18</v>
@@ -7957,7 +7957,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>179</v>
       </c>
@@ -7986,7 +7986,7 @@
         <v>101</v>
       </c>
       <c r="J107" s="6" t="s">
-        <v>837</v>
+        <v>804</v>
       </c>
       <c r="K107" s="6" t="s">
         <v>18</v>
@@ -8272,7 +8272,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="116" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>634</v>
       </c>
@@ -8301,7 +8301,7 @@
         <v>151</v>
       </c>
       <c r="J116" s="6" t="s">
-        <v>17</v>
+        <v>837</v>
       </c>
       <c r="K116" s="6" t="s">
         <v>18</v>
@@ -8552,7 +8552,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>668</v>
       </c>
@@ -8581,7 +8581,7 @@
         <v>101</v>
       </c>
       <c r="J124" s="6" t="s">
-        <v>837</v>
+        <v>804</v>
       </c>
       <c r="K124" s="6" t="s">
         <v>18</v>
@@ -9077,7 +9077,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>743</v>
       </c>
@@ -9106,13 +9106,13 @@
         <v>151</v>
       </c>
       <c r="J139" s="6" t="s">
-        <v>837</v>
+        <v>804</v>
       </c>
       <c r="K139" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>748</v>
       </c>
@@ -9141,7 +9141,7 @@
         <v>101</v>
       </c>
       <c r="J140" s="6" t="s">
-        <v>837</v>
+        <v>804</v>
       </c>
       <c r="K140" s="6" t="s">
         <v>18</v>
@@ -9392,7 +9392,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="148" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>787</v>
       </c>
@@ -9421,13 +9421,13 @@
         <v>151</v>
       </c>
       <c r="J148" s="6" t="s">
-        <v>17</v>
+        <v>837</v>
       </c>
       <c r="K148" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="149" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>793</v>
       </c>
@@ -9456,13 +9456,13 @@
         <v>101</v>
       </c>
       <c r="J149" s="6" t="s">
-        <v>17</v>
+        <v>837</v>
       </c>
       <c r="K149" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="150" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>798</v>
       </c>
@@ -9491,7 +9491,7 @@
         <v>151</v>
       </c>
       <c r="J150" s="6" t="s">
-        <v>17</v>
+        <v>837</v>
       </c>
       <c r="K150" s="6" t="s">
         <v>18</v>
@@ -9515,7 +9515,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D18A476-0271-4A84-BE9E-901865A86FD3}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AC157"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -9727,7 +9726,7 @@
       <c r="AB4" s="11"/>
       <c r="AC4" s="25"/>
     </row>
-    <row r="5" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="19" t="s">
         <v>96</v>
       </c>
@@ -9770,7 +9769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
         <v>103</v>
       </c>
@@ -9813,7 +9812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="19" t="s">
         <v>109</v>
       </c>
@@ -9856,7 +9855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="19" t="s">
         <v>114</v>
       </c>
@@ -9899,7 +9898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
         <v>120</v>
       </c>
@@ -9942,7 +9941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="19" t="s">
         <v>125</v>
       </c>
@@ -9985,7 +9984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="19" t="s">
         <v>135</v>
       </c>
@@ -10076,7 +10075,7 @@
         <v>5682</v>
       </c>
     </row>
-    <row r="12" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="19" t="s">
         <v>141</v>
       </c>
@@ -10119,7 +10118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
         <v>147</v>
       </c>
@@ -10162,7 +10161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="19" t="s">
         <v>159</v>
       </c>
@@ -10253,7 +10252,7 @@
         <v>5190</v>
       </c>
     </row>
-    <row r="15" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="19" t="s">
         <v>173</v>
       </c>
@@ -10296,7 +10295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="19" t="s">
         <v>180</v>
       </c>
@@ -10306,40 +10305,88 @@
       <c r="C16" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="20"/>
+      <c r="D16" s="24">
+        <v>-2.9143889999999999</v>
+      </c>
+      <c r="E16" s="24">
+        <v>-40.170302</v>
+      </c>
+      <c r="F16" s="20">
+        <v>46156</v>
+      </c>
       <c r="G16" s="20">
         <f t="shared" si="0"/>
+        <v>46158</v>
+      </c>
+      <c r="H16" s="12">
+        <v>1561</v>
+      </c>
+      <c r="I16" s="12">
+        <v>3376</v>
+      </c>
+      <c r="J16" s="12">
+        <v>105</v>
+      </c>
+      <c r="K16" s="12">
+        <v>424</v>
+      </c>
+      <c r="L16" s="12">
+        <v>166</v>
+      </c>
+      <c r="M16" s="12">
+        <v>24</v>
+      </c>
+      <c r="N16" s="12">
+        <v>42</v>
+      </c>
+      <c r="O16" s="12">
+        <v>12</v>
+      </c>
+      <c r="P16" s="12">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="12">
+        <v>12</v>
+      </c>
+      <c r="R16" s="12">
+        <v>19</v>
+      </c>
+      <c r="S16" s="12">
+        <v>9</v>
+      </c>
+      <c r="T16" s="12">
+        <v>69</v>
+      </c>
+      <c r="U16" s="12">
+        <v>1</v>
+      </c>
+      <c r="V16" s="12">
         <v>2</v>
       </c>
-      <c r="H16" s="12"/>
-      <c r="I16" s="12"/>
-      <c r="J16" s="12"/>
-      <c r="K16" s="12"/>
-      <c r="L16" s="12"/>
-      <c r="M16" s="12"/>
-      <c r="N16" s="12"/>
-      <c r="O16" s="12"/>
-      <c r="P16" s="12"/>
-      <c r="Q16" s="12"/>
-      <c r="R16" s="12"/>
-      <c r="S16" s="12"/>
-      <c r="T16" s="12"/>
-      <c r="U16" s="12"/>
-      <c r="V16" s="12"/>
-      <c r="W16" s="12"/>
-      <c r="X16" s="12"/>
-      <c r="Y16" s="12"/>
-      <c r="Z16" s="12"/>
-      <c r="AA16" s="12"/>
-      <c r="AB16" s="12"/>
+      <c r="W16" s="12">
+        <v>6</v>
+      </c>
+      <c r="X16" s="12">
+        <v>1</v>
+      </c>
+      <c r="Y16" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="12">
+        <v>5</v>
+      </c>
+      <c r="AA16" s="12">
+        <v>5</v>
+      </c>
+      <c r="AB16" s="12">
+        <v>5</v>
+      </c>
       <c r="AC16" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>5845</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="19" t="s">
         <v>185</v>
       </c>
@@ -10382,7 +10429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="19" t="s">
         <v>190</v>
       </c>
@@ -10473,7 +10520,7 @@
         <v>3934</v>
       </c>
     </row>
-    <row r="19" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="19" t="s">
         <v>196</v>
       </c>
@@ -10564,7 +10611,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="20" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="19" t="s">
         <v>607</v>
       </c>
@@ -10655,7 +10702,7 @@
         <v>4245</v>
       </c>
     </row>
-    <row r="21" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="19" t="s">
         <v>613</v>
       </c>
@@ -10698,7 +10745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="19" t="s">
         <v>618</v>
       </c>
@@ -10880,7 +10927,7 @@
         <v>7108</v>
       </c>
     </row>
-    <row r="24" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="19" t="s">
         <v>629</v>
       </c>
@@ -10923,7 +10970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="19" t="s">
         <v>635</v>
       </c>
@@ -10966,7 +11013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="19" t="s">
         <v>640</v>
       </c>
@@ -11009,7 +11056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="19" t="s">
         <v>645</v>
       </c>
@@ -11052,7 +11099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="19" t="s">
         <v>202</v>
       </c>
@@ -11143,7 +11190,7 @@
         <v>9101</v>
       </c>
     </row>
-    <row r="29" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
         <v>650</v>
       </c>
@@ -11234,7 +11281,7 @@
         <v>2316</v>
       </c>
     </row>
-    <row r="30" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
         <v>655</v>
       </c>
@@ -11277,7 +11324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
         <v>660</v>
       </c>
@@ -11368,7 +11415,7 @@
         <v>1584</v>
       </c>
     </row>
-    <row r="32" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
         <v>664</v>
       </c>
@@ -11411,7 +11458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
         <v>669</v>
       </c>
@@ -11421,40 +11468,88 @@
       <c r="C33" s="19" t="s">
         <v>670</v>
       </c>
-      <c r="D33" s="21"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="20"/>
+      <c r="D33" s="24">
+        <v>-2.8945319999999999</v>
+      </c>
+      <c r="E33" s="24">
+        <v>-40.225693999999997</v>
+      </c>
+      <c r="F33" s="20">
+        <v>46156</v>
+      </c>
       <c r="G33" s="20">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="H33" s="12"/>
-      <c r="I33" s="12"/>
-      <c r="J33" s="12"/>
-      <c r="K33" s="12"/>
-      <c r="L33" s="12"/>
-      <c r="M33" s="12"/>
-      <c r="N33" s="12"/>
-      <c r="O33" s="12"/>
-      <c r="P33" s="12"/>
-      <c r="Q33" s="12"/>
-      <c r="R33" s="12"/>
-      <c r="S33" s="12"/>
-      <c r="T33" s="12"/>
-      <c r="U33" s="12"/>
-      <c r="V33" s="12"/>
-      <c r="W33" s="12"/>
-      <c r="X33" s="12"/>
-      <c r="Y33" s="12"/>
-      <c r="Z33" s="12"/>
-      <c r="AA33" s="12"/>
-      <c r="AB33" s="12"/>
+        <v>46158</v>
+      </c>
+      <c r="H33" s="12">
+        <v>924</v>
+      </c>
+      <c r="I33" s="12">
+        <v>2796</v>
+      </c>
+      <c r="J33" s="12">
+        <v>103</v>
+      </c>
+      <c r="K33" s="12">
+        <v>430</v>
+      </c>
+      <c r="L33" s="12">
+        <v>187</v>
+      </c>
+      <c r="M33" s="12">
+        <v>34</v>
+      </c>
+      <c r="N33" s="12">
+        <v>27</v>
+      </c>
+      <c r="O33" s="12">
+        <v>4</v>
+      </c>
+      <c r="P33" s="12">
+        <v>4</v>
+      </c>
+      <c r="Q33" s="12">
+        <v>8</v>
+      </c>
+      <c r="R33" s="12">
+        <v>10</v>
+      </c>
+      <c r="S33" s="12">
+        <v>5</v>
+      </c>
+      <c r="T33" s="12">
+        <v>62</v>
+      </c>
+      <c r="U33" s="12">
+        <v>3</v>
+      </c>
+      <c r="V33" s="12">
+        <v>1</v>
+      </c>
+      <c r="W33" s="12">
+        <v>9</v>
+      </c>
+      <c r="X33" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z33" s="12">
+        <v>7</v>
+      </c>
+      <c r="AA33" s="12">
+        <v>14</v>
+      </c>
+      <c r="AB33" s="12">
+        <v>7</v>
+      </c>
       <c r="AC33" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4636</v>
+      </c>
+    </row>
+    <row r="34" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="19" t="s">
         <v>674</v>
       </c>
@@ -11497,7 +11592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
         <v>678</v>
       </c>
@@ -11540,7 +11635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
         <v>683</v>
       </c>
@@ -11583,7 +11678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
         <v>688</v>
       </c>
@@ -11626,7 +11721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="19" t="s">
         <v>694</v>
       </c>
@@ -11669,7 +11764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="19" t="s">
         <v>699</v>
       </c>
@@ -11712,7 +11807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="19" t="s">
         <v>705</v>
       </c>
@@ -11755,7 +11850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="19" t="s">
         <v>709</v>
       </c>
@@ -11798,7 +11893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="19" t="s">
         <v>715</v>
       </c>
@@ -11889,7 +11984,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="43" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="19" t="s">
         <v>720</v>
       </c>
@@ -11932,7 +12027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="19" t="s">
         <v>725</v>
       </c>
@@ -12066,7 +12161,7 @@
         <v>7959</v>
       </c>
     </row>
-    <row r="46" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="19" t="s">
         <v>734</v>
       </c>
@@ -12109,7 +12204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="19" t="s">
         <v>739</v>
       </c>
@@ -12200,7 +12295,7 @@
         <v>2429</v>
       </c>
     </row>
-    <row r="48" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="19" t="s">
         <v>744</v>
       </c>
@@ -12210,40 +12305,88 @@
       <c r="C48" s="19" t="s">
         <v>745</v>
       </c>
-      <c r="D48" s="21"/>
-      <c r="E48" s="21"/>
-      <c r="F48" s="20"/>
+      <c r="D48" s="24">
+        <v>-2.9586229999999998</v>
+      </c>
+      <c r="E48" s="24">
+        <v>-39.903604000000001</v>
+      </c>
+      <c r="F48" s="20">
+        <v>46156</v>
+      </c>
       <c r="G48" s="20">
         <f t="shared" si="0"/>
+        <v>46158</v>
+      </c>
+      <c r="H48" s="12">
+        <v>1697</v>
+      </c>
+      <c r="I48" s="12">
+        <v>3111</v>
+      </c>
+      <c r="J48" s="12">
+        <v>48</v>
+      </c>
+      <c r="K48" s="12">
+        <v>445</v>
+      </c>
+      <c r="L48" s="12">
+        <v>180</v>
+      </c>
+      <c r="M48" s="12">
+        <v>15</v>
+      </c>
+      <c r="N48" s="12">
+        <v>23</v>
+      </c>
+      <c r="O48" s="12">
+        <v>6</v>
+      </c>
+      <c r="P48" s="12">
+        <v>1</v>
+      </c>
+      <c r="Q48" s="12">
+        <v>5</v>
+      </c>
+      <c r="R48" s="12">
+        <v>5</v>
+      </c>
+      <c r="S48" s="12">
+        <v>4</v>
+      </c>
+      <c r="T48" s="12">
+        <v>102</v>
+      </c>
+      <c r="U48" s="12">
+        <v>0</v>
+      </c>
+      <c r="V48" s="12">
+        <v>1</v>
+      </c>
+      <c r="W48" s="12">
+        <v>0</v>
+      </c>
+      <c r="X48" s="12">
+        <v>1</v>
+      </c>
+      <c r="Y48" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z48" s="12">
         <v>2</v>
       </c>
-      <c r="H48" s="12"/>
-      <c r="I48" s="12"/>
-      <c r="J48" s="12"/>
-      <c r="K48" s="12"/>
-      <c r="L48" s="12"/>
-      <c r="M48" s="12"/>
-      <c r="N48" s="12"/>
-      <c r="O48" s="12"/>
-      <c r="P48" s="12"/>
-      <c r="Q48" s="12"/>
-      <c r="R48" s="12"/>
-      <c r="S48" s="12"/>
-      <c r="T48" s="12"/>
-      <c r="U48" s="12"/>
-      <c r="V48" s="12"/>
-      <c r="W48" s="12"/>
-      <c r="X48" s="12"/>
-      <c r="Y48" s="12"/>
-      <c r="Z48" s="12"/>
-      <c r="AA48" s="12"/>
-      <c r="AB48" s="12"/>
+      <c r="AA48" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB48" s="12">
+        <v>1</v>
+      </c>
       <c r="AC48" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>5649</v>
+      </c>
+    </row>
+    <row r="49" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="19" t="s">
         <v>749</v>
       </c>
@@ -12253,40 +12396,88 @@
       <c r="C49" s="19" t="s">
         <v>750</v>
       </c>
-      <c r="D49" s="21"/>
-      <c r="E49" s="21"/>
-      <c r="F49" s="20"/>
+      <c r="D49" s="24">
+        <v>-2.92225</v>
+      </c>
+      <c r="E49" s="24">
+        <v>-40.120244</v>
+      </c>
+      <c r="F49" s="20">
+        <v>46156</v>
+      </c>
       <c r="G49" s="20">
         <f t="shared" si="0"/>
+        <v>46158</v>
+      </c>
+      <c r="H49" s="12">
+        <v>2788</v>
+      </c>
+      <c r="I49" s="12">
+        <v>3057</v>
+      </c>
+      <c r="J49" s="12">
+        <v>84</v>
+      </c>
+      <c r="K49" s="12">
+        <v>381</v>
+      </c>
+      <c r="L49" s="12">
+        <v>126</v>
+      </c>
+      <c r="M49" s="12">
+        <v>38</v>
+      </c>
+      <c r="N49" s="12">
+        <v>40</v>
+      </c>
+      <c r="O49" s="12">
+        <v>6</v>
+      </c>
+      <c r="P49" s="12">
+        <v>3</v>
+      </c>
+      <c r="Q49" s="12">
+        <v>13</v>
+      </c>
+      <c r="R49" s="12">
+        <v>13</v>
+      </c>
+      <c r="S49" s="12">
+        <v>1</v>
+      </c>
+      <c r="T49" s="12">
+        <v>77</v>
+      </c>
+      <c r="U49" s="12">
         <v>2</v>
       </c>
-      <c r="H49" s="12"/>
-      <c r="I49" s="12"/>
-      <c r="J49" s="12"/>
-      <c r="K49" s="12"/>
-      <c r="L49" s="12"/>
-      <c r="M49" s="12"/>
-      <c r="N49" s="12"/>
-      <c r="O49" s="12"/>
-      <c r="P49" s="12"/>
-      <c r="Q49" s="12"/>
-      <c r="R49" s="12"/>
-      <c r="S49" s="12"/>
-      <c r="T49" s="12"/>
-      <c r="U49" s="12"/>
-      <c r="V49" s="12"/>
-      <c r="W49" s="12"/>
-      <c r="X49" s="12"/>
-      <c r="Y49" s="12"/>
-      <c r="Z49" s="12"/>
-      <c r="AA49" s="12"/>
-      <c r="AB49" s="12"/>
+      <c r="V49" s="12">
+        <v>3</v>
+      </c>
+      <c r="W49" s="12">
+        <v>5</v>
+      </c>
+      <c r="X49" s="12">
+        <v>2</v>
+      </c>
+      <c r="Y49" s="12">
+        <v>2</v>
+      </c>
+      <c r="Z49" s="12">
+        <v>7</v>
+      </c>
+      <c r="AA49" s="12">
+        <v>5</v>
+      </c>
+      <c r="AB49" s="12">
+        <v>7</v>
+      </c>
       <c r="AC49" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>6660</v>
+      </c>
+    </row>
+    <row r="50" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="19" t="s">
         <v>754</v>
       </c>
@@ -12377,7 +12568,7 @@
         <v>2483</v>
       </c>
     </row>
-    <row r="51" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="19" t="s">
         <v>758</v>
       </c>
@@ -12468,7 +12659,7 @@
         <v>4263</v>
       </c>
     </row>
-    <row r="52" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="19" t="s">
         <v>763</v>
       </c>
@@ -12511,7 +12702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="19" t="s">
         <v>767</v>
       </c>
@@ -12554,7 +12745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="19" t="s">
         <v>772</v>
       </c>
@@ -12645,7 +12836,7 @@
         <v>1560</v>
       </c>
     </row>
-    <row r="55" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="19" t="s">
         <v>777</v>
       </c>
@@ -12736,7 +12927,7 @@
         <v>1864</v>
       </c>
     </row>
-    <row r="56" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="19" t="s">
         <v>782</v>
       </c>
@@ -12779,7 +12970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="19" t="s">
         <v>788</v>
       </c>
@@ -12822,7 +13013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="19" t="s">
         <v>794</v>
       </c>
@@ -12865,7 +13056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="19" t="s">
         <v>799</v>
       </c>
@@ -12908,7 +13099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="19" t="s">
         <v>315</v>
       </c>
@@ -12999,7 +13190,7 @@
         <v>2567</v>
       </c>
     </row>
-    <row r="61" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="19" t="s">
         <v>320</v>
       </c>
@@ -13042,7 +13233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="19" t="s">
         <v>325</v>
       </c>
@@ -13085,7 +13276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="19" t="s">
         <v>330</v>
       </c>
@@ -13176,7 +13367,7 @@
         <v>2906</v>
       </c>
     </row>
-    <row r="64" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="19" t="s">
         <v>335</v>
       </c>
@@ -13219,7 +13410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="19" t="s">
         <v>341</v>
       </c>
@@ -13262,7 +13453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="19" t="s">
         <v>130</v>
       </c>
@@ -13353,7 +13544,7 @@
         <v>5492</v>
       </c>
     </row>
-    <row r="67" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="19" t="s">
         <v>347</v>
       </c>
@@ -13444,7 +13635,7 @@
         <v>3330</v>
       </c>
     </row>
-    <row r="68" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="19" t="s">
         <v>351</v>
       </c>
@@ -13487,7 +13678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="19" t="s">
         <v>357</v>
       </c>
@@ -13578,7 +13769,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="70" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="19" t="s">
         <v>362</v>
       </c>
@@ -13669,7 +13860,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="71" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="19" t="s">
         <v>368</v>
       </c>
@@ -13712,7 +13903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="19" t="s">
         <v>374</v>
       </c>
@@ -13755,7 +13946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="19" t="s">
         <v>380</v>
       </c>
@@ -13798,7 +13989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="19" t="s">
         <v>386</v>
       </c>
@@ -13841,7 +14032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="19" t="s">
         <v>391</v>
       </c>
@@ -13884,7 +14075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="19" t="s">
         <v>397</v>
       </c>
@@ -13927,7 +14118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="19" t="s">
         <v>403</v>
       </c>
@@ -13970,7 +14161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="19" t="s">
         <v>408</v>
       </c>
@@ -14013,7 +14204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="19" t="s">
         <v>414</v>
       </c>
@@ -14147,7 +14338,7 @@
         <v>4247</v>
       </c>
     </row>
-    <row r="81" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="19" t="s">
         <v>425</v>
       </c>
@@ -14190,7 +14381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="19" t="s">
         <v>431</v>
       </c>
@@ -14233,7 +14424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="19" t="s">
         <v>436</v>
       </c>
@@ -14324,7 +14515,7 @@
         <v>6031</v>
       </c>
     </row>
-    <row r="84" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="19" t="s">
         <v>440</v>
       </c>
@@ -14367,7 +14558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="19" t="s">
         <v>445</v>
       </c>
@@ -14410,7 +14601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="19" t="s">
         <v>451</v>
       </c>
@@ -14453,7 +14644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="19" t="s">
         <v>456</v>
       </c>
@@ -14496,7 +14687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="19" t="s">
         <v>461</v>
       </c>
@@ -14587,7 +14778,7 @@
         <v>6697</v>
       </c>
     </row>
-    <row r="89" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="19" t="s">
         <v>466</v>
       </c>
@@ -14630,7 +14821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="19" t="s">
         <v>471</v>
       </c>
@@ -14721,7 +14912,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="91" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="19" t="s">
         <v>475</v>
       </c>
@@ -14764,7 +14955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="19" t="s">
         <v>481</v>
       </c>
@@ -14807,7 +14998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="19" t="s">
         <v>485</v>
       </c>
@@ -14898,7 +15089,7 @@
         <v>988</v>
       </c>
     </row>
-    <row r="94" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="19" t="s">
         <v>153</v>
       </c>
@@ -14989,7 +15180,7 @@
         <v>2883</v>
       </c>
     </row>
-    <row r="95" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="19" t="s">
         <v>491</v>
       </c>
@@ -15080,7 +15271,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="96" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="19" t="s">
         <v>497</v>
       </c>
@@ -15171,7 +15362,7 @@
         <v>3307</v>
       </c>
     </row>
-    <row r="97" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="19" t="s">
         <v>502</v>
       </c>
@@ -15262,7 +15453,7 @@
         <v>7063</v>
       </c>
     </row>
-    <row r="98" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="19" t="s">
         <v>505</v>
       </c>
@@ -15305,7 +15496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="19" t="s">
         <v>511</v>
       </c>
@@ -15348,7 +15539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="19" t="s">
         <v>516</v>
       </c>
@@ -15391,7 +15582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="19" t="s">
         <v>521</v>
       </c>
@@ -15434,7 +15625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="19" t="s">
         <v>527</v>
       </c>
@@ -15477,7 +15668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="19" t="s">
         <v>164</v>
       </c>
@@ -15568,7 +15759,7 @@
         <v>2499</v>
       </c>
     </row>
-    <row r="104" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="19" t="s">
         <v>533</v>
       </c>
@@ -15659,7 +15850,7 @@
         <v>2533</v>
       </c>
     </row>
-    <row r="105" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="19" t="s">
         <v>539</v>
       </c>
@@ -15750,7 +15941,7 @@
         <v>2124</v>
       </c>
     </row>
-    <row r="106" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="19" t="s">
         <v>545</v>
       </c>
@@ -15793,7 +15984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="19" t="s">
         <v>550</v>
       </c>
@@ -15836,7 +16027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="19" t="s">
         <v>170</v>
       </c>
@@ -15927,7 +16118,7 @@
         <v>1973</v>
       </c>
     </row>
-    <row r="109" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="19" t="s">
         <v>555</v>
       </c>
@@ -15970,7 +16161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="19" t="s">
         <v>559</v>
       </c>
@@ -16061,7 +16252,7 @@
         <v>5171</v>
       </c>
     </row>
-    <row r="111" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="19" t="s">
         <v>565</v>
       </c>
@@ -16152,7 +16343,7 @@
         <v>5543</v>
       </c>
     </row>
-    <row r="112" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="19" t="s">
         <v>570</v>
       </c>
@@ -16243,7 +16434,7 @@
         <v>4135</v>
       </c>
     </row>
-    <row r="113" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="19" t="s">
         <v>575</v>
       </c>
@@ -16286,7 +16477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="19" t="s">
         <v>581</v>
       </c>
@@ -16377,7 +16568,7 @@
         <v>2947</v>
       </c>
     </row>
-    <row r="115" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="19" t="s">
         <v>586</v>
       </c>
@@ -16420,7 +16611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="19" t="s">
         <v>592</v>
       </c>
@@ -16463,7 +16654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="19" t="s">
         <v>597</v>
       </c>
@@ -16506,7 +16697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="19" t="s">
         <v>602</v>
       </c>
@@ -16549,7 +16740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="19" t="s">
         <v>11</v>
       </c>
@@ -16640,7 +16831,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="120" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="19" t="s">
         <v>20</v>
       </c>
@@ -16731,7 +16922,7 @@
         <v>1773</v>
       </c>
     </row>
-    <row r="121" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="19" t="s">
         <v>24</v>
       </c>
@@ -16774,7 +16965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="19" t="s">
         <v>30</v>
       </c>
@@ -16865,7 +17056,7 @@
         <v>4915</v>
       </c>
     </row>
-    <row r="123" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="19" t="s">
         <v>35</v>
       </c>
@@ -16908,7 +17099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="19" t="s">
         <v>41</v>
       </c>
@@ -16951,7 +17142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="19" t="s">
         <v>63</v>
       </c>
@@ -16994,7 +17185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="19" t="s">
         <v>69</v>
       </c>
@@ -17037,7 +17228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="19" t="s">
         <v>213</v>
       </c>
@@ -17080,7 +17271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="19" t="s">
         <v>265</v>
       </c>
@@ -17123,7 +17314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="19" t="s">
         <v>271</v>
       </c>
@@ -17166,7 +17357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="19" t="s">
         <v>277</v>
       </c>
@@ -17257,7 +17448,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="131" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="19" t="s">
         <v>282</v>
       </c>
@@ -17348,7 +17539,7 @@
         <v>1984</v>
       </c>
     </row>
-    <row r="132" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="19" t="s">
         <v>81</v>
       </c>
@@ -17439,7 +17630,7 @@
         <v>2597</v>
       </c>
     </row>
-    <row r="133" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="19" t="s">
         <v>86</v>
       </c>
@@ -17530,7 +17721,7 @@
         <v>1733</v>
       </c>
     </row>
-    <row r="134" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="19" t="s">
         <v>92</v>
       </c>
@@ -17621,7 +17812,7 @@
         <v>1724</v>
       </c>
     </row>
-    <row r="135" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="19" t="s">
         <v>287</v>
       </c>
@@ -17664,7 +17855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="19" t="s">
         <v>292</v>
       </c>
@@ -17707,7 +17898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="19" t="s">
         <v>47</v>
       </c>
@@ -17750,7 +17941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="19" t="s">
         <v>53</v>
       </c>
@@ -17793,7 +17984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="19" t="s">
         <v>57</v>
       </c>
@@ -17803,40 +17994,88 @@
       <c r="C139" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="D139" s="21"/>
-      <c r="E139" s="21"/>
-      <c r="F139" s="20"/>
+      <c r="D139" s="24">
+        <v>-2.9383110000000001</v>
+      </c>
+      <c r="E139" s="24">
+        <v>-40.181694</v>
+      </c>
+      <c r="F139" s="20">
+        <v>46156</v>
+      </c>
       <c r="G139" s="20">
         <f t="shared" si="6"/>
+        <v>46158</v>
+      </c>
+      <c r="H139" s="12">
+        <v>2769</v>
+      </c>
+      <c r="I139" s="12">
+        <v>1973</v>
+      </c>
+      <c r="J139" s="12">
+        <v>23</v>
+      </c>
+      <c r="K139" s="12">
+        <v>231</v>
+      </c>
+      <c r="L139" s="12">
+        <v>119</v>
+      </c>
+      <c r="M139" s="12">
+        <v>24</v>
+      </c>
+      <c r="N139" s="12">
+        <v>18</v>
+      </c>
+      <c r="O139" s="12">
         <v>2</v>
       </c>
-      <c r="H139" s="12"/>
-      <c r="I139" s="12"/>
-      <c r="J139" s="12"/>
-      <c r="K139" s="12"/>
-      <c r="L139" s="12"/>
-      <c r="M139" s="12"/>
-      <c r="N139" s="12"/>
-      <c r="O139" s="12"/>
-      <c r="P139" s="12"/>
-      <c r="Q139" s="12"/>
-      <c r="R139" s="12"/>
-      <c r="S139" s="12"/>
-      <c r="T139" s="12"/>
-      <c r="U139" s="12"/>
-      <c r="V139" s="12"/>
-      <c r="W139" s="12"/>
-      <c r="X139" s="12"/>
-      <c r="Y139" s="12"/>
-      <c r="Z139" s="12"/>
-      <c r="AA139" s="12"/>
-      <c r="AB139" s="12"/>
+      <c r="P139" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q139" s="12">
+        <v>8</v>
+      </c>
+      <c r="R139" s="12">
+        <v>0</v>
+      </c>
+      <c r="S139" s="12">
+        <v>4</v>
+      </c>
+      <c r="T139" s="12">
+        <v>84</v>
+      </c>
+      <c r="U139" s="12">
+        <v>0</v>
+      </c>
+      <c r="V139" s="12">
+        <v>2</v>
+      </c>
+      <c r="W139" s="12">
+        <v>0</v>
+      </c>
+      <c r="X139" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y139" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z139" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA139" s="12">
+        <v>5</v>
+      </c>
+      <c r="AB139" s="12">
+        <v>1</v>
+      </c>
       <c r="AC139" s="13">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>5263</v>
+      </c>
+    </row>
+    <row r="140" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="19" t="s">
         <v>75</v>
       </c>
@@ -17927,7 +18166,7 @@
         <v>1839</v>
       </c>
     </row>
-    <row r="141" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="19" t="s">
         <v>207</v>
       </c>
@@ -18018,7 +18257,7 @@
         <v>2840</v>
       </c>
     </row>
-    <row r="142" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="19" t="s">
         <v>218</v>
       </c>
@@ -18109,7 +18348,7 @@
         <v>1451</v>
       </c>
     </row>
-    <row r="143" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="19" t="s">
         <v>223</v>
       </c>
@@ -18152,7 +18391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="19" t="s">
         <v>228</v>
       </c>
@@ -18243,7 +18482,7 @@
         <v>2854</v>
       </c>
     </row>
-    <row r="145" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="19" t="s">
         <v>234</v>
       </c>
@@ -18286,7 +18525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="19" t="s">
         <v>240</v>
       </c>
@@ -18420,7 +18659,7 @@
         <v>2936</v>
       </c>
     </row>
-    <row r="148" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="19" t="s">
         <v>251</v>
       </c>
@@ -18463,7 +18702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="19" t="s">
         <v>256</v>
       </c>
@@ -18506,7 +18745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="19" t="s">
         <v>261</v>
       </c>
@@ -18549,7 +18788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="19" t="s">
         <v>298</v>
       </c>
@@ -18592,7 +18831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="19" t="s">
         <v>303</v>
       </c>
@@ -18683,7 +18922,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="153" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="19" t="s">
         <v>310</v>
       </c>
@@ -18746,14 +18985,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A4:AC153" xr:uid="{1D18A476-0271-4A84-BE9E-901865A86FD3}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="E 153"/>
-        <filter val="P 137"/>
-        <filter val="P 33"/>
-        <filter val="P 77"/>
-      </filters>
-    </filterColumn>
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="9">

--- a/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
+++ b/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\5- MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D78174B-AC9F-4DD2-9855-FC214EB626F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03EE331B-1403-4C76-BF09-5A68727C8C49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
   </bookViews>
@@ -6950,10 +6950,10 @@
         <v>481</v>
       </c>
       <c r="C78" s="5">
-        <v>-3.5714160000000001</v>
+        <v>-3.5688710000000001</v>
       </c>
       <c r="D78" s="5">
-        <v>-40.6374</v>
+        <v>-40.636719999999997</v>
       </c>
       <c r="E78" s="4" t="s">
         <v>476</v>
@@ -8280,10 +8280,10 @@
         <v>635</v>
       </c>
       <c r="C116" s="5">
-        <v>-3.4662999999999999</v>
+        <v>-3.5105249999999999</v>
       </c>
       <c r="D116" s="5">
-        <v>-40.395716</v>
+        <v>-40.357357</v>
       </c>
       <c r="E116" s="4" t="s">
         <v>235</v>
@@ -9400,10 +9400,10 @@
         <v>788</v>
       </c>
       <c r="C148" s="5">
-        <v>-3.4559829999999998</v>
+        <v>-3.521487</v>
       </c>
       <c r="D148" s="5">
-        <v>-40.210115999999999</v>
+        <v>-40.330056999999996</v>
       </c>
       <c r="E148" s="4" t="s">
         <v>789</v>
@@ -9435,10 +9435,10 @@
         <v>794</v>
       </c>
       <c r="C149" s="5">
-        <v>-3.5106660000000001</v>
+        <v>-3.5194079999999999</v>
       </c>
       <c r="D149" s="5">
-        <v>-40.385066000000002</v>
+        <v>-40.361950999999998</v>
       </c>
       <c r="E149" s="4" t="s">
         <v>789</v>
@@ -9470,10 +9470,10 @@
         <v>799</v>
       </c>
       <c r="C150" s="5">
-        <v>-3.5546000000000002</v>
+        <v>-3.552886</v>
       </c>
       <c r="D150" s="5">
-        <v>-40.664700000000003</v>
+        <v>-40.663702000000001</v>
       </c>
       <c r="E150" s="4" t="s">
         <v>48</v>

--- a/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
+++ b/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\5- MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03EE331B-1403-4C76-BF09-5A68727C8C49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25889E98-B14E-4516-9EB3-9B6F1B8AAEF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1861" uniqueCount="873">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1863" uniqueCount="875">
   <si>
     <t>WKT</t>
   </si>
@@ -2663,6 +2663,12 @@
   </si>
   <si>
     <t xml:space="preserve"> -39.394502°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -3.656675°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -39.424249°</t>
   </si>
 </sst>
 </file>
@@ -6557,7 +6563,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>424</v>
       </c>
@@ -6586,7 +6592,7 @@
         <v>101</v>
       </c>
       <c r="J67" s="6" t="s">
-        <v>837</v>
+        <v>804</v>
       </c>
       <c r="K67" s="6" t="s">
         <v>18</v>
@@ -14348,37 +14354,85 @@
       <c r="C81" s="19" t="s">
         <v>427</v>
       </c>
-      <c r="D81" s="21"/>
-      <c r="E81" s="21"/>
-      <c r="F81" s="20"/>
+      <c r="D81" s="24" t="s">
+        <v>873</v>
+      </c>
+      <c r="E81" s="24" t="s">
+        <v>874</v>
+      </c>
+      <c r="F81" s="20">
+        <v>46153</v>
+      </c>
       <c r="G81" s="20">
         <f t="shared" si="5"/>
+        <v>46155</v>
+      </c>
+      <c r="H81" s="12">
+        <v>769</v>
+      </c>
+      <c r="I81" s="12">
+        <v>2867</v>
+      </c>
+      <c r="J81" s="12">
+        <v>48</v>
+      </c>
+      <c r="K81" s="12">
+        <v>280</v>
+      </c>
+      <c r="L81" s="12">
+        <v>100</v>
+      </c>
+      <c r="M81" s="12">
+        <v>22</v>
+      </c>
+      <c r="N81" s="12">
+        <v>11</v>
+      </c>
+      <c r="O81" s="12">
+        <v>5</v>
+      </c>
+      <c r="P81" s="12">
         <v>2</v>
       </c>
-      <c r="H81" s="12"/>
-      <c r="I81" s="12"/>
-      <c r="J81" s="12"/>
-      <c r="K81" s="12"/>
-      <c r="L81" s="12"/>
-      <c r="M81" s="12"/>
-      <c r="N81" s="12"/>
-      <c r="O81" s="12"/>
-      <c r="P81" s="12"/>
-      <c r="Q81" s="12"/>
-      <c r="R81" s="12"/>
-      <c r="S81" s="12"/>
-      <c r="T81" s="12"/>
-      <c r="U81" s="12"/>
-      <c r="V81" s="12"/>
-      <c r="W81" s="12"/>
-      <c r="X81" s="12"/>
-      <c r="Y81" s="12"/>
-      <c r="Z81" s="12"/>
-      <c r="AA81" s="12"/>
-      <c r="AB81" s="12"/>
+      <c r="Q81" s="12">
+        <v>8</v>
+      </c>
+      <c r="R81" s="12">
+        <v>13</v>
+      </c>
+      <c r="S81" s="12">
+        <v>4</v>
+      </c>
+      <c r="T81" s="12">
+        <v>25</v>
+      </c>
+      <c r="U81" s="12">
+        <v>0</v>
+      </c>
+      <c r="V81" s="12">
+        <v>1</v>
+      </c>
+      <c r="W81" s="12">
+        <v>1</v>
+      </c>
+      <c r="X81" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y81" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z81" s="12">
+        <v>3</v>
+      </c>
+      <c r="AA81" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB81" s="12">
+        <v>1</v>
+      </c>
       <c r="AC81" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4161</v>
       </c>
     </row>
     <row r="82" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">

--- a/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
+++ b/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\5- MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25889E98-B14E-4516-9EB3-9B6F1B8AAEF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE749E55-4798-4520-8745-6E333370DA13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
   </bookViews>
   <sheets>
     <sheet name="LISTA DE PONTOS" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1863" uniqueCount="875">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1873" uniqueCount="884">
   <si>
     <t>WKT</t>
   </si>
@@ -2557,9 +2557,6 @@
     <t>456ECE0050S0</t>
   </si>
   <si>
-    <t>EM ANDAMENTO</t>
-  </si>
-  <si>
     <t>166ECE0110S0</t>
   </si>
   <si>
@@ -2669,6 +2666,36 @@
   </si>
   <si>
     <t xml:space="preserve"> -39.424249°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -3,510525°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -40,357357°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -3,521487°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -40,330057°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -3,519408°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -40,361951°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -3,552886°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -40,663702°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -3,568871°</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -40,636720°</t>
   </si>
 </sst>
 </file>
@@ -6895,13 +6922,13 @@
         <v>197</v>
       </c>
       <c r="F76" s="4" t="s">
+        <v>837</v>
+      </c>
+      <c r="G76" s="4" t="s">
         <v>838</v>
       </c>
-      <c r="G76" s="4" t="s">
+      <c r="H76" s="4" t="s">
         <v>839</v>
-      </c>
-      <c r="H76" s="4" t="s">
-        <v>840</v>
       </c>
       <c r="I76" s="4" t="s">
         <v>101</v>
@@ -6977,7 +7004,7 @@
         <v>101</v>
       </c>
       <c r="J78" s="6" t="s">
-        <v>837</v>
+        <v>804</v>
       </c>
       <c r="K78" s="6" t="s">
         <v>18</v>
@@ -7105,7 +7132,7 @@
         <v>136</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="G82" s="4" t="s">
         <v>499</v>
@@ -7146,7 +7173,7 @@
         <v>500</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="I83" s="4" t="s">
         <v>101</v>
@@ -7560,13 +7587,13 @@
         <v>197</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="G95" s="4" t="s">
         <v>132</v>
       </c>
       <c r="H95" s="4" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="I95" s="4" t="s">
         <v>151</v>
@@ -8307,7 +8334,7 @@
         <v>151</v>
       </c>
       <c r="J116" s="6" t="s">
-        <v>837</v>
+        <v>804</v>
       </c>
       <c r="K116" s="6" t="s">
         <v>18</v>
@@ -9427,7 +9454,7 @@
         <v>151</v>
       </c>
       <c r="J148" s="6" t="s">
-        <v>837</v>
+        <v>804</v>
       </c>
       <c r="K148" s="6" t="s">
         <v>18</v>
@@ -9462,7 +9489,7 @@
         <v>101</v>
       </c>
       <c r="J149" s="6" t="s">
-        <v>837</v>
+        <v>804</v>
       </c>
       <c r="K149" s="6" t="s">
         <v>18</v>
@@ -9497,7 +9524,7 @@
         <v>151</v>
       </c>
       <c r="J150" s="6" t="s">
-        <v>837</v>
+        <v>804</v>
       </c>
       <c r="K150" s="6" t="s">
         <v>18</v>
@@ -9521,6 +9548,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D18A476-0271-4A84-BE9E-901865A86FD3}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AC157"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -9732,7 +9760,7 @@
       <c r="AB4" s="11"/>
       <c r="AC4" s="25"/>
     </row>
-    <row r="5" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="19" t="s">
         <v>96</v>
       </c>
@@ -9775,7 +9803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
         <v>103</v>
       </c>
@@ -9818,7 +9846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="19" t="s">
         <v>109</v>
       </c>
@@ -9861,7 +9889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="19" t="s">
         <v>114</v>
       </c>
@@ -9904,7 +9932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
         <v>120</v>
       </c>
@@ -9947,7 +9975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="19" t="s">
         <v>125</v>
       </c>
@@ -9990,7 +10018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="19" t="s">
         <v>135</v>
       </c>
@@ -10081,7 +10109,7 @@
         <v>5682</v>
       </c>
     </row>
-    <row r="12" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="19" t="s">
         <v>141</v>
       </c>
@@ -10124,7 +10152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
         <v>147</v>
       </c>
@@ -10167,7 +10195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="19" t="s">
         <v>159</v>
       </c>
@@ -10178,10 +10206,10 @@
         <v>160</v>
       </c>
       <c r="D14" s="24" t="s">
+        <v>854</v>
+      </c>
+      <c r="E14" s="24" t="s">
         <v>855</v>
-      </c>
-      <c r="E14" s="24" t="s">
-        <v>856</v>
       </c>
       <c r="F14" s="20">
         <v>46142</v>
@@ -10258,7 +10286,7 @@
         <v>5190</v>
       </c>
     </row>
-    <row r="15" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="19" t="s">
         <v>173</v>
       </c>
@@ -10301,7 +10329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="19" t="s">
         <v>180</v>
       </c>
@@ -10392,7 +10420,7 @@
         <v>5845</v>
       </c>
     </row>
-    <row r="17" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="19" t="s">
         <v>185</v>
       </c>
@@ -10435,7 +10463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="19" t="s">
         <v>190</v>
       </c>
@@ -10526,7 +10554,7 @@
         <v>3934</v>
       </c>
     </row>
-    <row r="19" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="19" t="s">
         <v>196</v>
       </c>
@@ -10537,10 +10565,10 @@
         <v>198</v>
       </c>
       <c r="D19" s="24" t="s">
+        <v>856</v>
+      </c>
+      <c r="E19" s="24" t="s">
         <v>857</v>
-      </c>
-      <c r="E19" s="24" t="s">
-        <v>858</v>
       </c>
       <c r="F19" s="20">
         <v>46142</v>
@@ -10617,7 +10645,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="20" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="19" t="s">
         <v>607</v>
       </c>
@@ -10708,7 +10736,7 @@
         <v>4245</v>
       </c>
     </row>
-    <row r="21" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="19" t="s">
         <v>613</v>
       </c>
@@ -10751,7 +10779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="19" t="s">
         <v>618</v>
       </c>
@@ -10842,7 +10870,7 @@
         <v>2038</v>
       </c>
     </row>
-    <row r="23" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="19" t="s">
         <v>624</v>
       </c>
@@ -10853,10 +10881,10 @@
         <v>625</v>
       </c>
       <c r="D23" s="24" t="s">
+        <v>864</v>
+      </c>
+      <c r="E23" s="24" t="s">
         <v>865</v>
-      </c>
-      <c r="E23" s="24" t="s">
-        <v>866</v>
       </c>
       <c r="F23" s="20">
         <v>46153</v>
@@ -10933,7 +10961,7 @@
         <v>7108</v>
       </c>
     </row>
-    <row r="24" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="19" t="s">
         <v>629</v>
       </c>
@@ -10986,40 +11014,88 @@
       <c r="C25" s="19" t="s">
         <v>636</v>
       </c>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="20"/>
+      <c r="D25" s="24" t="s">
+        <v>874</v>
+      </c>
+      <c r="E25" s="24" t="s">
+        <v>875</v>
+      </c>
+      <c r="F25" s="20">
+        <v>46159</v>
+      </c>
       <c r="G25" s="20">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="H25" s="12"/>
-      <c r="I25" s="12"/>
-      <c r="J25" s="12"/>
-      <c r="K25" s="12"/>
-      <c r="L25" s="12"/>
-      <c r="M25" s="12"/>
-      <c r="N25" s="12"/>
-      <c r="O25" s="12"/>
-      <c r="P25" s="12"/>
-      <c r="Q25" s="12"/>
-      <c r="R25" s="12"/>
-      <c r="S25" s="12"/>
-      <c r="T25" s="12"/>
-      <c r="U25" s="12"/>
-      <c r="V25" s="12"/>
-      <c r="W25" s="12"/>
-      <c r="X25" s="12"/>
-      <c r="Y25" s="12"/>
-      <c r="Z25" s="12"/>
-      <c r="AA25" s="12"/>
-      <c r="AB25" s="12"/>
+        <v>46161</v>
+      </c>
+      <c r="H25" s="12">
+        <v>1775</v>
+      </c>
+      <c r="I25" s="12">
+        <v>2637</v>
+      </c>
+      <c r="J25" s="12">
+        <v>6</v>
+      </c>
+      <c r="K25" s="12">
+        <v>111</v>
+      </c>
+      <c r="L25" s="12">
+        <v>16</v>
+      </c>
+      <c r="M25" s="12">
+        <v>3</v>
+      </c>
+      <c r="N25" s="12">
+        <v>4</v>
+      </c>
+      <c r="O25" s="12">
+        <v>0</v>
+      </c>
+      <c r="P25" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="12">
+        <v>0</v>
+      </c>
+      <c r="R25" s="12">
+        <v>3</v>
+      </c>
+      <c r="S25" s="12">
+        <v>1</v>
+      </c>
+      <c r="T25" s="12">
+        <v>29</v>
+      </c>
+      <c r="U25" s="12">
+        <v>0</v>
+      </c>
+      <c r="V25" s="12">
+        <v>0</v>
+      </c>
+      <c r="W25" s="12">
+        <v>0</v>
+      </c>
+      <c r="X25" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA25" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="12">
+        <v>0</v>
+      </c>
       <c r="AC25" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>4586</v>
+      </c>
+    </row>
+    <row r="26" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="19" t="s">
         <v>640</v>
       </c>
@@ -11062,7 +11138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="19" t="s">
         <v>645</v>
       </c>
@@ -11105,7 +11181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="19" t="s">
         <v>202</v>
       </c>
@@ -11116,10 +11192,10 @@
         <v>203</v>
       </c>
       <c r="D28" s="24" t="s">
+        <v>858</v>
+      </c>
+      <c r="E28" s="24" t="s">
         <v>859</v>
-      </c>
-      <c r="E28" s="24" t="s">
-        <v>860</v>
       </c>
       <c r="F28" s="20">
         <v>46142</v>
@@ -11196,7 +11272,7 @@
         <v>9101</v>
       </c>
     </row>
-    <row r="29" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
         <v>650</v>
       </c>
@@ -11207,10 +11283,10 @@
         <v>651</v>
       </c>
       <c r="D29" s="24" t="s">
+        <v>840</v>
+      </c>
+      <c r="E29" s="24" t="s">
         <v>841</v>
-      </c>
-      <c r="E29" s="24" t="s">
-        <v>842</v>
       </c>
       <c r="F29" s="20">
         <v>46139</v>
@@ -11287,7 +11363,7 @@
         <v>2316</v>
       </c>
     </row>
-    <row r="30" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
         <v>655</v>
       </c>
@@ -11330,7 +11406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
         <v>660</v>
       </c>
@@ -11421,7 +11497,7 @@
         <v>1584</v>
       </c>
     </row>
-    <row r="32" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
         <v>664</v>
       </c>
@@ -11464,7 +11540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
         <v>669</v>
       </c>
@@ -11555,7 +11631,7 @@
         <v>4636</v>
       </c>
     </row>
-    <row r="34" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="19" t="s">
         <v>674</v>
       </c>
@@ -11598,7 +11674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
         <v>678</v>
       </c>
@@ -11641,7 +11717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
         <v>683</v>
       </c>
@@ -11684,7 +11760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
         <v>688</v>
       </c>
@@ -11727,7 +11803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="19" t="s">
         <v>694</v>
       </c>
@@ -11770,7 +11846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="19" t="s">
         <v>699</v>
       </c>
@@ -11813,7 +11889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="19" t="s">
         <v>705</v>
       </c>
@@ -11856,7 +11932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="19" t="s">
         <v>709</v>
       </c>
@@ -11899,7 +11975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="19" t="s">
         <v>715</v>
       </c>
@@ -11910,10 +11986,10 @@
         <v>716</v>
       </c>
       <c r="D42" s="24" t="s">
+        <v>842</v>
+      </c>
+      <c r="E42" s="24" t="s">
         <v>843</v>
-      </c>
-      <c r="E42" s="24" t="s">
-        <v>844</v>
       </c>
       <c r="F42" s="20">
         <v>46139</v>
@@ -11990,7 +12066,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="43" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="19" t="s">
         <v>720</v>
       </c>
@@ -12033,7 +12109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="19" t="s">
         <v>725</v>
       </c>
@@ -12076,7 +12152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="19" t="s">
         <v>730</v>
       </c>
@@ -12087,10 +12163,10 @@
         <v>731</v>
       </c>
       <c r="D45" s="24" t="s">
+        <v>866</v>
+      </c>
+      <c r="E45" s="24" t="s">
         <v>867</v>
-      </c>
-      <c r="E45" s="24" t="s">
-        <v>868</v>
       </c>
       <c r="F45" s="20">
         <v>46153</v>
@@ -12167,7 +12243,7 @@
         <v>7959</v>
       </c>
     </row>
-    <row r="46" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="19" t="s">
         <v>734</v>
       </c>
@@ -12210,7 +12286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="19" t="s">
         <v>739</v>
       </c>
@@ -12301,7 +12377,7 @@
         <v>2429</v>
       </c>
     </row>
-    <row r="48" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="19" t="s">
         <v>744</v>
       </c>
@@ -12392,7 +12468,7 @@
         <v>5649</v>
       </c>
     </row>
-    <row r="49" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="19" t="s">
         <v>749</v>
       </c>
@@ -12483,7 +12559,7 @@
         <v>6660</v>
       </c>
     </row>
-    <row r="50" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="19" t="s">
         <v>754</v>
       </c>
@@ -12574,7 +12650,7 @@
         <v>2483</v>
       </c>
     </row>
-    <row r="51" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="19" t="s">
         <v>758</v>
       </c>
@@ -12665,7 +12741,7 @@
         <v>4263</v>
       </c>
     </row>
-    <row r="52" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="19" t="s">
         <v>763</v>
       </c>
@@ -12708,7 +12784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="19" t="s">
         <v>767</v>
       </c>
@@ -12751,7 +12827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="19" t="s">
         <v>772</v>
       </c>
@@ -12842,7 +12918,7 @@
         <v>1560</v>
       </c>
     </row>
-    <row r="55" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="19" t="s">
         <v>777</v>
       </c>
@@ -12933,7 +13009,7 @@
         <v>1864</v>
       </c>
     </row>
-    <row r="56" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="19" t="s">
         <v>782</v>
       </c>
@@ -12986,37 +13062,85 @@
       <c r="C57" s="19" t="s">
         <v>790</v>
       </c>
-      <c r="D57" s="21"/>
-      <c r="E57" s="21"/>
-      <c r="F57" s="20"/>
+      <c r="D57" s="24" t="s">
+        <v>876</v>
+      </c>
+      <c r="E57" s="24" t="s">
+        <v>877</v>
+      </c>
+      <c r="F57" s="20">
+        <v>46159</v>
+      </c>
       <c r="G57" s="20">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="H57" s="12"/>
-      <c r="I57" s="12"/>
-      <c r="J57" s="12"/>
-      <c r="K57" s="12"/>
-      <c r="L57" s="12"/>
-      <c r="M57" s="12"/>
-      <c r="N57" s="12"/>
-      <c r="O57" s="12"/>
-      <c r="P57" s="12"/>
-      <c r="Q57" s="12"/>
-      <c r="R57" s="12"/>
-      <c r="S57" s="12"/>
-      <c r="T57" s="12"/>
-      <c r="U57" s="12"/>
-      <c r="V57" s="12"/>
-      <c r="W57" s="12"/>
-      <c r="X57" s="12"/>
-      <c r="Y57" s="12"/>
-      <c r="Z57" s="12"/>
-      <c r="AA57" s="12"/>
-      <c r="AB57" s="12"/>
+        <v>46161</v>
+      </c>
+      <c r="H57" s="12">
+        <v>1852</v>
+      </c>
+      <c r="I57" s="12">
+        <v>963</v>
+      </c>
+      <c r="J57" s="12">
+        <v>7</v>
+      </c>
+      <c r="K57" s="12">
+        <v>72</v>
+      </c>
+      <c r="L57" s="12">
+        <v>6</v>
+      </c>
+      <c r="M57" s="12">
+        <v>7</v>
+      </c>
+      <c r="N57" s="12">
+        <v>5</v>
+      </c>
+      <c r="O57" s="12">
+        <v>0</v>
+      </c>
+      <c r="P57" s="12">
+        <v>1</v>
+      </c>
+      <c r="Q57" s="12">
+        <v>0</v>
+      </c>
+      <c r="R57" s="12">
+        <v>0</v>
+      </c>
+      <c r="S57" s="12">
+        <v>1</v>
+      </c>
+      <c r="T57" s="12">
+        <v>38</v>
+      </c>
+      <c r="U57" s="12">
+        <v>0</v>
+      </c>
+      <c r="V57" s="12">
+        <v>0</v>
+      </c>
+      <c r="W57" s="12">
+        <v>0</v>
+      </c>
+      <c r="X57" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y57" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z57" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA57" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB57" s="12">
+        <v>0</v>
+      </c>
       <c r="AC57" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2952</v>
       </c>
     </row>
     <row r="58" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -13029,37 +13153,85 @@
       <c r="C58" s="19" t="s">
         <v>795</v>
       </c>
-      <c r="D58" s="21"/>
-      <c r="E58" s="21"/>
-      <c r="F58" s="20"/>
+      <c r="D58" s="24" t="s">
+        <v>878</v>
+      </c>
+      <c r="E58" s="24" t="s">
+        <v>879</v>
+      </c>
+      <c r="F58" s="20">
+        <v>46159</v>
+      </c>
       <c r="G58" s="20">
         <f t="shared" si="0"/>
+        <v>46161</v>
+      </c>
+      <c r="H58" s="12">
+        <v>881</v>
+      </c>
+      <c r="I58" s="12">
+        <v>486</v>
+      </c>
+      <c r="J58" s="12">
+        <v>1</v>
+      </c>
+      <c r="K58" s="12">
+        <v>28</v>
+      </c>
+      <c r="L58" s="12">
         <v>2</v>
       </c>
-      <c r="H58" s="12"/>
-      <c r="I58" s="12"/>
-      <c r="J58" s="12"/>
-      <c r="K58" s="12"/>
-      <c r="L58" s="12"/>
-      <c r="M58" s="12"/>
-      <c r="N58" s="12"/>
-      <c r="O58" s="12"/>
-      <c r="P58" s="12"/>
-      <c r="Q58" s="12"/>
-      <c r="R58" s="12"/>
-      <c r="S58" s="12"/>
-      <c r="T58" s="12"/>
-      <c r="U58" s="12"/>
-      <c r="V58" s="12"/>
-      <c r="W58" s="12"/>
-      <c r="X58" s="12"/>
-      <c r="Y58" s="12"/>
-      <c r="Z58" s="12"/>
-      <c r="AA58" s="12"/>
-      <c r="AB58" s="12"/>
+      <c r="M58" s="12">
+        <v>0</v>
+      </c>
+      <c r="N58" s="12">
+        <v>0</v>
+      </c>
+      <c r="O58" s="12">
+        <v>0</v>
+      </c>
+      <c r="P58" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="12">
+        <v>0</v>
+      </c>
+      <c r="R58" s="12">
+        <v>0</v>
+      </c>
+      <c r="S58" s="12">
+        <v>0</v>
+      </c>
+      <c r="T58" s="12">
+        <v>16</v>
+      </c>
+      <c r="U58" s="12">
+        <v>0</v>
+      </c>
+      <c r="V58" s="12">
+        <v>0</v>
+      </c>
+      <c r="W58" s="12">
+        <v>0</v>
+      </c>
+      <c r="X58" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="12">
+        <v>0</v>
+      </c>
       <c r="AC58" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="59" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -13072,40 +13244,88 @@
       <c r="C59" s="19" t="s">
         <v>800</v>
       </c>
-      <c r="D59" s="21"/>
-      <c r="E59" s="21"/>
-      <c r="F59" s="20"/>
+      <c r="D59" s="24" t="s">
+        <v>880</v>
+      </c>
+      <c r="E59" s="24" t="s">
+        <v>881</v>
+      </c>
+      <c r="F59" s="20">
+        <v>46159</v>
+      </c>
       <c r="G59" s="20">
         <f t="shared" si="0"/>
+        <v>46161</v>
+      </c>
+      <c r="H59" s="12">
+        <v>2639</v>
+      </c>
+      <c r="I59" s="12">
+        <v>1245</v>
+      </c>
+      <c r="J59" s="12">
+        <v>5</v>
+      </c>
+      <c r="K59" s="12">
+        <v>47</v>
+      </c>
+      <c r="L59" s="12">
+        <v>3</v>
+      </c>
+      <c r="M59" s="12">
+        <v>8</v>
+      </c>
+      <c r="N59" s="12">
         <v>2</v>
       </c>
-      <c r="H59" s="12"/>
-      <c r="I59" s="12"/>
-      <c r="J59" s="12"/>
-      <c r="K59" s="12"/>
-      <c r="L59" s="12"/>
-      <c r="M59" s="12"/>
-      <c r="N59" s="12"/>
-      <c r="O59" s="12"/>
-      <c r="P59" s="12"/>
-      <c r="Q59" s="12"/>
-      <c r="R59" s="12"/>
-      <c r="S59" s="12"/>
-      <c r="T59" s="12"/>
-      <c r="U59" s="12"/>
-      <c r="V59" s="12"/>
-      <c r="W59" s="12"/>
-      <c r="X59" s="12"/>
-      <c r="Y59" s="12"/>
-      <c r="Z59" s="12"/>
-      <c r="AA59" s="12"/>
-      <c r="AB59" s="12"/>
+      <c r="O59" s="12">
+        <v>0</v>
+      </c>
+      <c r="P59" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="12">
+        <v>0</v>
+      </c>
+      <c r="R59" s="12">
+        <v>0</v>
+      </c>
+      <c r="S59" s="12">
+        <v>0</v>
+      </c>
+      <c r="T59" s="12">
+        <v>49</v>
+      </c>
+      <c r="U59" s="12">
+        <v>0</v>
+      </c>
+      <c r="V59" s="12">
+        <v>1</v>
+      </c>
+      <c r="W59" s="12">
+        <v>0</v>
+      </c>
+      <c r="X59" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y59" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z59" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA59" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB59" s="12">
+        <v>0</v>
+      </c>
       <c r="AC59" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>3999</v>
+      </c>
+    </row>
+    <row r="60" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="19" t="s">
         <v>315</v>
       </c>
@@ -13196,7 +13416,7 @@
         <v>2567</v>
       </c>
     </row>
-    <row r="61" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="19" t="s">
         <v>320</v>
       </c>
@@ -13239,7 +13459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="19" t="s">
         <v>325</v>
       </c>
@@ -13282,7 +13502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="19" t="s">
         <v>330</v>
       </c>
@@ -13373,7 +13593,7 @@
         <v>2906</v>
       </c>
     </row>
-    <row r="64" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="19" t="s">
         <v>335</v>
       </c>
@@ -13416,7 +13636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="19" t="s">
         <v>341</v>
       </c>
@@ -13459,7 +13679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="19" t="s">
         <v>130</v>
       </c>
@@ -13550,7 +13770,7 @@
         <v>5492</v>
       </c>
     </row>
-    <row r="67" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="19" t="s">
         <v>347</v>
       </c>
@@ -13641,7 +13861,7 @@
         <v>3330</v>
       </c>
     </row>
-    <row r="68" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="19" t="s">
         <v>351</v>
       </c>
@@ -13684,7 +13904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="19" t="s">
         <v>357</v>
       </c>
@@ -13775,7 +13995,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="70" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="19" t="s">
         <v>362</v>
       </c>
@@ -13866,7 +14086,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="71" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="19" t="s">
         <v>368</v>
       </c>
@@ -13909,7 +14129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="19" t="s">
         <v>374</v>
       </c>
@@ -13952,7 +14172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="19" t="s">
         <v>380</v>
       </c>
@@ -13995,7 +14215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="19" t="s">
         <v>386</v>
       </c>
@@ -14038,7 +14258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="19" t="s">
         <v>391</v>
       </c>
@@ -14081,7 +14301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="19" t="s">
         <v>397</v>
       </c>
@@ -14124,7 +14344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="19" t="s">
         <v>403</v>
       </c>
@@ -14167,7 +14387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="19" t="s">
         <v>408</v>
       </c>
@@ -14210,7 +14430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="19" t="s">
         <v>414</v>
       </c>
@@ -14253,7 +14473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="19" t="s">
         <v>420</v>
       </c>
@@ -14264,10 +14484,10 @@
         <v>421</v>
       </c>
       <c r="D80" s="24" t="s">
+        <v>868</v>
+      </c>
+      <c r="E80" s="24" t="s">
         <v>869</v>
-      </c>
-      <c r="E80" s="24" t="s">
-        <v>870</v>
       </c>
       <c r="F80" s="20">
         <v>46153</v>
@@ -14344,7 +14564,7 @@
         <v>4247</v>
       </c>
     </row>
-    <row r="81" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="19" t="s">
         <v>425</v>
       </c>
@@ -14355,10 +14575,10 @@
         <v>427</v>
       </c>
       <c r="D81" s="24" t="s">
+        <v>872</v>
+      </c>
+      <c r="E81" s="24" t="s">
         <v>873</v>
-      </c>
-      <c r="E81" s="24" t="s">
-        <v>874</v>
       </c>
       <c r="F81" s="20">
         <v>46153</v>
@@ -14435,7 +14655,7 @@
         <v>4161</v>
       </c>
     </row>
-    <row r="82" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="19" t="s">
         <v>431</v>
       </c>
@@ -14478,7 +14698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="19" t="s">
         <v>436</v>
       </c>
@@ -14569,7 +14789,7 @@
         <v>6031</v>
       </c>
     </row>
-    <row r="84" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="19" t="s">
         <v>440</v>
       </c>
@@ -14612,7 +14832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="19" t="s">
         <v>445</v>
       </c>
@@ -14655,7 +14875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="19" t="s">
         <v>451</v>
       </c>
@@ -14698,7 +14918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="19" t="s">
         <v>456</v>
       </c>
@@ -14741,7 +14961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="19" t="s">
         <v>461</v>
       </c>
@@ -14832,7 +15052,7 @@
         <v>6697</v>
       </c>
     </row>
-    <row r="89" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="19" t="s">
         <v>466</v>
       </c>
@@ -14875,7 +15095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="19" t="s">
         <v>471</v>
       </c>
@@ -14886,10 +15106,10 @@
         <v>473</v>
       </c>
       <c r="D90" s="24" t="s">
+        <v>844</v>
+      </c>
+      <c r="E90" s="24" t="s">
         <v>845</v>
-      </c>
-      <c r="E90" s="24" t="s">
-        <v>846</v>
       </c>
       <c r="F90" s="20">
         <v>46139</v>
@@ -14966,7 +15186,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="91" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="19" t="s">
         <v>475</v>
       </c>
@@ -15019,40 +15239,88 @@
       <c r="C92" s="19" t="s">
         <v>482</v>
       </c>
-      <c r="D92" s="21"/>
-      <c r="E92" s="21"/>
-      <c r="F92" s="20"/>
+      <c r="D92" s="24" t="s">
+        <v>882</v>
+      </c>
+      <c r="E92" s="24" t="s">
+        <v>883</v>
+      </c>
+      <c r="F92" s="20">
+        <v>46159</v>
+      </c>
       <c r="G92" s="20">
         <f t="shared" si="5"/>
+        <v>46161</v>
+      </c>
+      <c r="H92" s="12">
+        <v>889</v>
+      </c>
+      <c r="I92" s="12">
+        <v>1762</v>
+      </c>
+      <c r="J92" s="12">
+        <v>26</v>
+      </c>
+      <c r="K92" s="12">
+        <v>116</v>
+      </c>
+      <c r="L92" s="12">
+        <v>15</v>
+      </c>
+      <c r="M92" s="12">
+        <v>1</v>
+      </c>
+      <c r="N92" s="12">
+        <v>3</v>
+      </c>
+      <c r="O92" s="12">
+        <v>1</v>
+      </c>
+      <c r="P92" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="12">
+        <v>0</v>
+      </c>
+      <c r="R92" s="12">
         <v>2</v>
       </c>
-      <c r="H92" s="12"/>
-      <c r="I92" s="12"/>
-      <c r="J92" s="12"/>
-      <c r="K92" s="12"/>
-      <c r="L92" s="12"/>
-      <c r="M92" s="12"/>
-      <c r="N92" s="12"/>
-      <c r="O92" s="12"/>
-      <c r="P92" s="12"/>
-      <c r="Q92" s="12"/>
-      <c r="R92" s="12"/>
-      <c r="S92" s="12"/>
-      <c r="T92" s="12"/>
-      <c r="U92" s="12"/>
-      <c r="V92" s="12"/>
-      <c r="W92" s="12"/>
-      <c r="X92" s="12"/>
-      <c r="Y92" s="12"/>
-      <c r="Z92" s="12"/>
-      <c r="AA92" s="12"/>
-      <c r="AB92" s="12"/>
+      <c r="S92" s="12">
+        <v>0</v>
+      </c>
+      <c r="T92" s="12">
+        <v>21</v>
+      </c>
+      <c r="U92" s="12">
+        <v>3</v>
+      </c>
+      <c r="V92" s="12">
+        <v>0</v>
+      </c>
+      <c r="W92" s="12">
+        <v>0</v>
+      </c>
+      <c r="X92" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y92" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z92" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA92" s="12">
+        <v>2</v>
+      </c>
+      <c r="AB92" s="12">
+        <v>0</v>
+      </c>
       <c r="AC92" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>2842</v>
+      </c>
+    </row>
+    <row r="93" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="19" t="s">
         <v>485</v>
       </c>
@@ -15063,10 +15331,10 @@
         <v>487</v>
       </c>
       <c r="D93" s="24" t="s">
+        <v>860</v>
+      </c>
+      <c r="E93" s="24" t="s">
         <v>861</v>
-      </c>
-      <c r="E93" s="24" t="s">
-        <v>862</v>
       </c>
       <c r="F93" s="20">
         <v>46142</v>
@@ -15143,7 +15411,7 @@
         <v>988</v>
       </c>
     </row>
-    <row r="94" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="19" t="s">
         <v>153</v>
       </c>
@@ -15234,7 +15502,7 @@
         <v>2883</v>
       </c>
     </row>
-    <row r="95" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="19" t="s">
         <v>491</v>
       </c>
@@ -15325,7 +15593,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="96" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="19" t="s">
         <v>497</v>
       </c>
@@ -15336,10 +15604,10 @@
         <v>498</v>
       </c>
       <c r="D96" s="24" t="s">
+        <v>846</v>
+      </c>
+      <c r="E96" s="24" t="s">
         <v>847</v>
-      </c>
-      <c r="E96" s="24" t="s">
-        <v>848</v>
       </c>
       <c r="F96" s="20">
         <v>46139</v>
@@ -15416,7 +15684,7 @@
         <v>3307</v>
       </c>
     </row>
-    <row r="97" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="19" t="s">
         <v>502</v>
       </c>
@@ -15427,10 +15695,10 @@
         <v>503</v>
       </c>
       <c r="D97" s="24" t="s">
+        <v>848</v>
+      </c>
+      <c r="E97" s="24" t="s">
         <v>849</v>
-      </c>
-      <c r="E97" s="24" t="s">
-        <v>850</v>
       </c>
       <c r="F97" s="20">
         <v>46139</v>
@@ -15507,7 +15775,7 @@
         <v>7063</v>
       </c>
     </row>
-    <row r="98" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="19" t="s">
         <v>505</v>
       </c>
@@ -15550,7 +15818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="19" t="s">
         <v>511</v>
       </c>
@@ -15593,7 +15861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="19" t="s">
         <v>516</v>
       </c>
@@ -15636,7 +15904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="19" t="s">
         <v>521</v>
       </c>
@@ -15679,7 +15947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="19" t="s">
         <v>527</v>
       </c>
@@ -15722,7 +15990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="19" t="s">
         <v>164</v>
       </c>
@@ -15813,7 +16081,7 @@
         <v>2499</v>
       </c>
     </row>
-    <row r="104" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="19" t="s">
         <v>533</v>
       </c>
@@ -15904,7 +16172,7 @@
         <v>2533</v>
       </c>
     </row>
-    <row r="105" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="19" t="s">
         <v>539</v>
       </c>
@@ -15995,7 +16263,7 @@
         <v>2124</v>
       </c>
     </row>
-    <row r="106" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="19" t="s">
         <v>545</v>
       </c>
@@ -16038,7 +16306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="19" t="s">
         <v>550</v>
       </c>
@@ -16081,7 +16349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="19" t="s">
         <v>170</v>
       </c>
@@ -16092,10 +16360,10 @@
         <v>171</v>
       </c>
       <c r="D108" s="24" t="s">
+        <v>862</v>
+      </c>
+      <c r="E108" s="24" t="s">
         <v>863</v>
-      </c>
-      <c r="E108" s="24" t="s">
-        <v>864</v>
       </c>
       <c r="F108" s="20">
         <v>46142</v>
@@ -16172,7 +16440,7 @@
         <v>1973</v>
       </c>
     </row>
-    <row r="109" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="19" t="s">
         <v>555</v>
       </c>
@@ -16215,7 +16483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="19" t="s">
         <v>559</v>
       </c>
@@ -16306,7 +16574,7 @@
         <v>5171</v>
       </c>
     </row>
-    <row r="111" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="19" t="s">
         <v>565</v>
       </c>
@@ -16397,7 +16665,7 @@
         <v>5543</v>
       </c>
     </row>
-    <row r="112" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="19" t="s">
         <v>570</v>
       </c>
@@ -16488,7 +16756,7 @@
         <v>4135</v>
       </c>
     </row>
-    <row r="113" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="19" t="s">
         <v>575</v>
       </c>
@@ -16531,7 +16799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="19" t="s">
         <v>581</v>
       </c>
@@ -16622,7 +16890,7 @@
         <v>2947</v>
       </c>
     </row>
-    <row r="115" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="19" t="s">
         <v>586</v>
       </c>
@@ -16665,7 +16933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="19" t="s">
         <v>592</v>
       </c>
@@ -16708,7 +16976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="19" t="s">
         <v>597</v>
       </c>
@@ -16751,7 +17019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="19" t="s">
         <v>602</v>
       </c>
@@ -16794,7 +17062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="19" t="s">
         <v>11</v>
       </c>
@@ -16885,7 +17153,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="120" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="19" t="s">
         <v>20</v>
       </c>
@@ -16976,7 +17244,7 @@
         <v>1773</v>
       </c>
     </row>
-    <row r="121" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="19" t="s">
         <v>24</v>
       </c>
@@ -17019,7 +17287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="19" t="s">
         <v>30</v>
       </c>
@@ -17110,7 +17378,7 @@
         <v>4915</v>
       </c>
     </row>
-    <row r="123" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="19" t="s">
         <v>35</v>
       </c>
@@ -17153,7 +17421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="19" t="s">
         <v>41</v>
       </c>
@@ -17196,7 +17464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="19" t="s">
         <v>63</v>
       </c>
@@ -17239,7 +17507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="19" t="s">
         <v>69</v>
       </c>
@@ -17282,7 +17550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="19" t="s">
         <v>213</v>
       </c>
@@ -17325,7 +17593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="19" t="s">
         <v>265</v>
       </c>
@@ -17368,7 +17636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="19" t="s">
         <v>271</v>
       </c>
@@ -17411,7 +17679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="19" t="s">
         <v>277</v>
       </c>
@@ -17502,7 +17770,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="131" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="19" t="s">
         <v>282</v>
       </c>
@@ -17593,7 +17861,7 @@
         <v>1984</v>
       </c>
     </row>
-    <row r="132" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="19" t="s">
         <v>81</v>
       </c>
@@ -17684,7 +17952,7 @@
         <v>2597</v>
       </c>
     </row>
-    <row r="133" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="19" t="s">
         <v>86</v>
       </c>
@@ -17775,7 +18043,7 @@
         <v>1733</v>
       </c>
     </row>
-    <row r="134" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="19" t="s">
         <v>92</v>
       </c>
@@ -17866,7 +18134,7 @@
         <v>1724</v>
       </c>
     </row>
-    <row r="135" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="19" t="s">
         <v>287</v>
       </c>
@@ -17909,7 +18177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="19" t="s">
         <v>292</v>
       </c>
@@ -17952,7 +18220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="19" t="s">
         <v>47</v>
       </c>
@@ -17995,7 +18263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="19" t="s">
         <v>53</v>
       </c>
@@ -18038,7 +18306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="19" t="s">
         <v>57</v>
       </c>
@@ -18129,7 +18397,7 @@
         <v>5263</v>
       </c>
     </row>
-    <row r="140" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="19" t="s">
         <v>75</v>
       </c>
@@ -18220,7 +18488,7 @@
         <v>1839</v>
       </c>
     </row>
-    <row r="141" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="19" t="s">
         <v>207</v>
       </c>
@@ -18311,7 +18579,7 @@
         <v>2840</v>
       </c>
     </row>
-    <row r="142" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="19" t="s">
         <v>218</v>
       </c>
@@ -18402,7 +18670,7 @@
         <v>1451</v>
       </c>
     </row>
-    <row r="143" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="19" t="s">
         <v>223</v>
       </c>
@@ -18445,7 +18713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="19" t="s">
         <v>228</v>
       </c>
@@ -18536,7 +18804,7 @@
         <v>2854</v>
       </c>
     </row>
-    <row r="145" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="19" t="s">
         <v>234</v>
       </c>
@@ -18579,7 +18847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="19" t="s">
         <v>240</v>
       </c>
@@ -18622,7 +18890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="19" t="s">
         <v>246</v>
       </c>
@@ -18633,10 +18901,10 @@
         <v>247</v>
       </c>
       <c r="D147" s="24" t="s">
+        <v>870</v>
+      </c>
+      <c r="E147" s="24" t="s">
         <v>871</v>
-      </c>
-      <c r="E147" s="24" t="s">
-        <v>872</v>
       </c>
       <c r="F147" s="20">
         <v>46153</v>
@@ -18713,7 +18981,7 @@
         <v>2936</v>
       </c>
     </row>
-    <row r="148" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="19" t="s">
         <v>251</v>
       </c>
@@ -18756,7 +19024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="19" t="s">
         <v>256</v>
       </c>
@@ -18799,7 +19067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="19" t="s">
         <v>261</v>
       </c>
@@ -18842,7 +19110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="19" t="s">
         <v>298</v>
       </c>
@@ -18885,7 +19153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="19" t="s">
         <v>303</v>
       </c>
@@ -18976,7 +19244,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="153" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="19" t="s">
         <v>310</v>
       </c>
@@ -19039,6 +19307,15 @@
     </row>
   </sheetData>
   <autoFilter ref="A4:AC153" xr:uid="{1D18A476-0271-4A84-BE9E-901865A86FD3}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="P 151"/>
+        <filter val="P 35"/>
+        <filter val="P 96"/>
+        <filter val="P 97"/>
+        <filter val="P 99"/>
+      </filters>
+    </filterColumn>
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="9">

--- a/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
+++ b/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\5- MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE749E55-4798-4520-8745-6E333370DA13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA25D04F-6318-45A8-B22F-E9CEB618E802}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
   </bookViews>
   <sheets>
     <sheet name="LISTA DE PONTOS" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1873" uniqueCount="884">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1873" uniqueCount="883">
   <si>
     <t>WKT</t>
   </si>
@@ -1168,18 +1168,6 @@
   </si>
   <si>
     <t>P 128</t>
-  </si>
-  <si>
-    <t>CE-313</t>
-  </si>
-  <si>
-    <t>313ECE0110N0</t>
-  </si>
-  <si>
-    <t>ENTR. CE-232(B) (TABAINHA)</t>
-  </si>
-  <si>
-    <t>ENTR. CE-240 (ARAPÁ)</t>
   </si>
   <si>
     <t>POINT (-40.474150 -4.039233)</t>
@@ -2696,6 +2684,15 @@
   </si>
   <si>
     <t xml:space="preserve"> -40,636720°</t>
+  </si>
+  <si>
+    <t>232ECE0210S0</t>
+  </si>
+  <si>
+    <t>ENTR. CE-187/311 (VIÇOSA DO CEARÁ)</t>
+  </si>
+  <si>
+    <t>ENTR. CE-515</t>
   </si>
 </sst>
 </file>
@@ -4309,7 +4306,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>9</v>
@@ -4344,7 +4341,7 @@
         <v>16</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K2" s="6" t="s">
         <v>18</v>
@@ -4379,13 +4376,13 @@
         <v>16</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K3" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>23</v>
       </c>
@@ -4449,13 +4446,13 @@
         <v>16</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K5" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>34</v>
       </c>
@@ -4490,7 +4487,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>40</v>
       </c>
@@ -4525,7 +4522,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>46</v>
       </c>
@@ -4560,7 +4557,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>52</v>
       </c>
@@ -4624,13 +4621,13 @@
         <v>16</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K10" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>62</v>
       </c>
@@ -4665,7 +4662,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>68</v>
       </c>
@@ -4729,7 +4726,7 @@
         <v>16</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K13" s="6" t="s">
         <v>18</v>
@@ -4764,13 +4761,13 @@
         <v>16</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K14" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>212</v>
       </c>
@@ -4834,13 +4831,13 @@
         <v>16</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K16" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>222</v>
       </c>
@@ -4904,13 +4901,13 @@
         <v>16</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K18" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>233</v>
       </c>
@@ -4945,7 +4942,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>239</v>
       </c>
@@ -5009,13 +5006,13 @@
         <v>16</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K21" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>250</v>
       </c>
@@ -5050,7 +5047,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>255</v>
       </c>
@@ -5085,7 +5082,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>260</v>
       </c>
@@ -5120,7 +5117,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>264</v>
       </c>
@@ -5155,7 +5152,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>270</v>
       </c>
@@ -5219,7 +5216,7 @@
         <v>16</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K27" s="6" t="s">
         <v>18</v>
@@ -5254,7 +5251,7 @@
         <v>16</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K28" s="6" t="s">
         <v>18</v>
@@ -5289,7 +5286,7 @@
         <v>16</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K29" s="6" t="s">
         <v>18</v>
@@ -5324,7 +5321,7 @@
         <v>16</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K30" s="6" t="s">
         <v>18</v>
@@ -5359,13 +5356,13 @@
         <v>16</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K31" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>286</v>
       </c>
@@ -5400,7 +5397,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>291</v>
       </c>
@@ -5435,7 +5432,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="34" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>297</v>
       </c>
@@ -5499,13 +5496,13 @@
         <v>16</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K35" s="6" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>309</v>
       </c>
@@ -5540,7 +5537,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>95</v>
       </c>
@@ -5575,7 +5572,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>102</v>
       </c>
@@ -5610,7 +5607,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>108</v>
       </c>
@@ -5645,7 +5642,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>113</v>
       </c>
@@ -5680,7 +5677,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>119</v>
       </c>
@@ -5715,7 +5712,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>124</v>
       </c>
@@ -5779,13 +5776,13 @@
         <v>151</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K43" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>319</v>
       </c>
@@ -5820,7 +5817,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>324</v>
       </c>
@@ -5884,13 +5881,13 @@
         <v>101</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K46" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>334</v>
       </c>
@@ -5925,7 +5922,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>340</v>
       </c>
@@ -5989,7 +5986,7 @@
         <v>101</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K49" s="6" t="s">
         <v>18</v>
@@ -6024,7 +6021,7 @@
         <v>101</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K50" s="6" t="s">
         <v>18</v>
@@ -6059,13 +6056,13 @@
         <v>151</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K51" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="52" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>350</v>
       </c>
@@ -6129,7 +6126,7 @@
         <v>101</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K53" s="6" t="s">
         <v>18</v>
@@ -6164,13 +6161,13 @@
         <v>151</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K54" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>367</v>
       </c>
@@ -6205,7 +6202,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="56" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>140</v>
       </c>
@@ -6240,7 +6237,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>373</v>
       </c>
@@ -6254,16 +6251,16 @@
         <v>-41.143765999999999</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>375</v>
+        <v>785</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>376</v>
+        <v>880</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>377</v>
+        <v>881</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>378</v>
+        <v>882</v>
       </c>
       <c r="I57" s="4" t="s">
         <v>151</v>
@@ -6272,15 +6269,15 @@
         <v>17</v>
       </c>
       <c r="K57" s="6" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="C58" s="5">
         <v>-3.8470499999999999</v>
@@ -6289,16 +6286,16 @@
         <v>-40.655116</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="I58" s="4" t="s">
         <v>151</v>
@@ -6310,7 +6307,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>146</v>
       </c>
@@ -6345,12 +6342,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C60" s="5">
         <v>-3.9773499999999999</v>
@@ -6359,16 +6356,16 @@
         <v>-40.707566</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="I60" s="4" t="s">
         <v>151</v>
@@ -6380,12 +6377,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="C61" s="5">
         <v>-4.1677330000000001</v>
@@ -6394,16 +6391,16 @@
         <v>-40.952933000000002</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="I61" s="4" t="s">
         <v>101</v>
@@ -6415,12 +6412,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="62" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="C62" s="5">
         <v>-4.040883</v>
@@ -6429,16 +6426,16 @@
         <v>-40.474516000000001</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="I62" s="4" t="s">
         <v>151</v>
@@ -6450,12 +6447,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="63" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="C63" s="5">
         <v>-3.5272999999999999</v>
@@ -6467,13 +6464,13 @@
         <v>272</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="I63" s="4" t="s">
         <v>101</v>
@@ -6485,12 +6482,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="64" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="C64" s="5">
         <v>-3.553566</v>
@@ -6499,16 +6496,16 @@
         <v>-38.885983000000003</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="I64" s="4" t="s">
         <v>151</v>
@@ -6520,12 +6517,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="65" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="C65" s="5">
         <v>-3.2338659999999999</v>
@@ -6534,16 +6531,16 @@
         <v>-40.011833000000003</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="I65" s="4" t="s">
         <v>101</v>
@@ -6557,10 +6554,10 @@
     </row>
     <row r="66" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="C66" s="5">
         <v>-3.512756</v>
@@ -6572,19 +6569,19 @@
         <v>266</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="I66" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J66" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K66" s="6" t="s">
         <v>18</v>
@@ -6592,10 +6589,10 @@
     </row>
     <row r="67" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="C67" s="5">
         <v>-3.6566749999999999</v>
@@ -6604,33 +6601,33 @@
         <v>-39.424249000000003</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="I67" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J67" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K67" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C68" s="5">
         <v>-4.2901499999999997</v>
@@ -6639,16 +6636,16 @@
         <v>-38.625466000000003</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="I68" s="4" t="s">
         <v>16</v>
@@ -6662,10 +6659,10 @@
     </row>
     <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="C69" s="5">
         <v>-4.3755519999999999</v>
@@ -6677,30 +6674,30 @@
         <v>229</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="G69" s="4" t="s">
         <v>232</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="I69" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J69" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K69" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="C70" s="5">
         <v>-5.0380159999999998</v>
@@ -6712,13 +6709,13 @@
         <v>229</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="I70" s="4" t="s">
         <v>151</v>
@@ -6730,12 +6727,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="71" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="C71" s="5">
         <v>-5.2755999999999998</v>
@@ -6744,16 +6741,16 @@
         <v>-38.108716000000001</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="I71" s="4" t="s">
         <v>101</v>
@@ -6765,12 +6762,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="72" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="C72" s="5">
         <v>-3.7728000000000002</v>
@@ -6782,13 +6779,13 @@
         <v>97</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="I72" s="4" t="s">
         <v>101</v>
@@ -6800,12 +6797,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="73" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="C73" s="5">
         <v>-3.1334659999999999</v>
@@ -6817,13 +6814,13 @@
         <v>235</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="I73" s="4" t="s">
         <v>101</v>
@@ -6837,10 +6834,10 @@
     </row>
     <row r="74" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="C74" s="5">
         <v>-3.6184599999999998</v>
@@ -6852,30 +6849,30 @@
         <v>235</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="I74" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J74" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K74" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="75" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="C75" s="5">
         <v>-3.9911660000000002</v>
@@ -6887,13 +6884,13 @@
         <v>235</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="I75" s="4" t="s">
         <v>151</v>
@@ -6907,10 +6904,10 @@
     </row>
     <row r="76" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="C76" s="5">
         <v>-5.6781480000000002</v>
@@ -6922,30 +6919,30 @@
         <v>197</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="I76" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J76" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K76" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="C77" s="5">
         <v>-3.4014500000000001</v>
@@ -6954,16 +6951,16 @@
         <v>-40.686549999999997</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="I77" s="4" t="s">
         <v>101</v>
@@ -6975,12 +6972,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="C78" s="5">
         <v>-3.5688710000000001</v>
@@ -6989,22 +6986,22 @@
         <v>-40.636719999999997</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="I78" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J78" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K78" s="6" t="s">
         <v>18</v>
@@ -7012,10 +7009,10 @@
     </row>
     <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="C79" s="5">
         <v>-4.7611049999999997</v>
@@ -7024,22 +7021,22 @@
         <v>-39.487011000000003</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="I79" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J79" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K79" s="6" t="s">
         <v>18</v>
@@ -7074,7 +7071,7 @@
         <v>101</v>
       </c>
       <c r="J80" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K80" s="6" t="s">
         <v>18</v>
@@ -7082,10 +7079,10 @@
     </row>
     <row r="81" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="C81" s="5">
         <v>-5.4022300000000003</v>
@@ -7094,22 +7091,22 @@
         <v>-38.571371999999997</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="I81" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J81" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K81" s="6" t="s">
         <v>18</v>
@@ -7117,10 +7114,10 @@
     </row>
     <row r="82" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C82" s="5">
         <v>-5.7358440000000002</v>
@@ -7132,19 +7129,19 @@
         <v>136</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="I82" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J82" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K82" s="6" t="s">
         <v>18</v>
@@ -7152,10 +7149,10 @@
     </row>
     <row r="83" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="C83" s="5">
         <v>-5.6845759999999999</v>
@@ -7167,30 +7164,30 @@
         <v>136</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="I83" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J83" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K83" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="84" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="C84" s="5">
         <v>-5.0811999999999999</v>
@@ -7199,16 +7196,16 @@
         <v>-38.004565999999997</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="I84" s="4" t="s">
         <v>101</v>
@@ -7220,12 +7217,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="85" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="C85" s="5">
         <v>-5.2329999999999997</v>
@@ -7234,16 +7231,16 @@
         <v>-38.194850000000002</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="H85" s="4" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="I85" s="4" t="s">
         <v>101</v>
@@ -7284,18 +7281,18 @@
         <v>151</v>
       </c>
       <c r="J86" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K86" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="C87" s="5">
         <v>-3.9741499999999998</v>
@@ -7304,16 +7301,16 @@
         <v>-40.704782999999999</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="I87" s="4" t="s">
         <v>151</v>
@@ -7325,12 +7322,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="88" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="C88" s="5">
         <v>-3.962866</v>
@@ -7339,16 +7336,16 @@
         <v>-38.357016000000002</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="H88" s="4" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="I88" s="4" t="s">
         <v>101</v>
@@ -7360,12 +7357,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="89" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="C89" s="5">
         <v>-4.0425329999999997</v>
@@ -7374,16 +7371,16 @@
         <v>-38.206499999999998</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="I89" s="4" t="s">
         <v>151</v>
@@ -7424,7 +7421,7 @@
         <v>151</v>
       </c>
       <c r="J90" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K90" s="6" t="s">
         <v>18</v>
@@ -7432,10 +7429,10 @@
     </row>
     <row r="91" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="C91" s="5">
         <v>-4.4447369999999999</v>
@@ -7444,22 +7441,22 @@
         <v>-38.662745999999999</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="I91" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J91" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K91" s="6" t="s">
         <v>18</v>
@@ -7467,10 +7464,10 @@
     </row>
     <row r="92" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="C92" s="5">
         <v>-5.1705110000000003</v>
@@ -7479,33 +7476,33 @@
         <v>-40.708150000000003</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="H92" s="4" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="I92" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J92" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K92" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="93" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="C93" s="5">
         <v>-4.5725499999999997</v>
@@ -7514,16 +7511,16 @@
         <v>-37.736899999999999</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="I93" s="4" t="s">
         <v>101</v>
@@ -7535,12 +7532,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="94" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="C94" s="5">
         <v>-5.1207330000000004</v>
@@ -7552,13 +7549,13 @@
         <v>358</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="H94" s="4" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="I94" s="4" t="s">
         <v>101</v>
@@ -7587,30 +7584,30 @@
         <v>197</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="G95" s="4" t="s">
         <v>132</v>
       </c>
       <c r="H95" s="4" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="I95" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J95" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K95" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="96" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="C96" s="5">
         <v>-3.6957</v>
@@ -7622,13 +7619,13 @@
         <v>42</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="G96" s="4" t="s">
         <v>301</v>
       </c>
       <c r="H96" s="4" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="I96" s="4" t="s">
         <v>101</v>
@@ -7642,10 +7639,10 @@
     </row>
     <row r="97" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="C97" s="5">
         <v>-3.6978119999999999</v>
@@ -7654,22 +7651,22 @@
         <v>-40.307443999999997</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="H97" s="4" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="I97" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J97" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K97" s="6" t="s">
         <v>18</v>
@@ -7677,10 +7674,10 @@
     </row>
     <row r="98" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="C98" s="5">
         <v>-5.2113269999999998</v>
@@ -7692,19 +7689,19 @@
         <v>208</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="H98" s="4" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="I98" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J98" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K98" s="6" t="s">
         <v>18</v>
@@ -7712,10 +7709,10 @@
     </row>
     <row r="99" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="C99" s="5">
         <v>-4.3822749999999999</v>
@@ -7727,30 +7724,30 @@
         <v>208</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="H99" s="4" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="I99" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J99" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K99" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="100" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="C100" s="5">
         <v>-6.0296659999999997</v>
@@ -7759,16 +7756,16 @@
         <v>-38.340949999999999</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="H100" s="4" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="I100" s="4" t="s">
         <v>101</v>
@@ -7782,10 +7779,10 @@
     </row>
     <row r="101" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="C101" s="5">
         <v>-5.2495240000000001</v>
@@ -7794,33 +7791,33 @@
         <v>-38.492610999999997</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="H101" s="4" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="I101" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J101" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K101" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="102" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="C102" s="5">
         <v>-4.2260499999999999</v>
@@ -7829,16 +7826,16 @@
         <v>-38.112082999999998</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="H102" s="4" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="I102" s="4" t="s">
         <v>151</v>
@@ -7850,12 +7847,12 @@
         <v>178</v>
       </c>
     </row>
-    <row r="103" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="C103" s="5">
         <v>-4.2283499999999998</v>
@@ -7864,16 +7861,16 @@
         <v>-38.112932999999998</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="G103" s="4" t="s">
         <v>73</v>
       </c>
       <c r="H103" s="4" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="I103" s="4" t="s">
         <v>101</v>
@@ -7885,12 +7882,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="104" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="C104" s="5">
         <v>-4.5906500000000001</v>
@@ -7902,13 +7899,13 @@
         <v>142</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="H104" s="4" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="I104" s="4" t="s">
         <v>101</v>
@@ -7920,12 +7917,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="105" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="C105" s="5">
         <v>-3.9187500000000002</v>
@@ -7937,13 +7934,13 @@
         <v>104</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="H105" s="4" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="I105" s="4" t="s">
         <v>101</v>
@@ -7955,7 +7952,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="106" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>172</v>
       </c>
@@ -8019,13 +8016,13 @@
         <v>101</v>
       </c>
       <c r="J107" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K107" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="108" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>184</v>
       </c>
@@ -8089,7 +8086,7 @@
         <v>151</v>
       </c>
       <c r="J109" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K109" s="6" t="s">
         <v>18</v>
@@ -8124,7 +8121,7 @@
         <v>151</v>
       </c>
       <c r="J110" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K110" s="6" t="s">
         <v>18</v>
@@ -8132,10 +8129,10 @@
     </row>
     <row r="111" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="C111" s="5">
         <v>-3.7752400000000002</v>
@@ -8144,33 +8141,33 @@
         <v>-40.496578999999997</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="H111" s="4" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="I111" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J111" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K111" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="112" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="C112" s="5">
         <v>-3.9438659999999999</v>
@@ -8182,13 +8179,13 @@
         <v>208</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="H112" s="4" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="I112" s="4" t="s">
         <v>101</v>
@@ -8202,10 +8199,10 @@
     </row>
     <row r="113" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="C113" s="5">
         <v>-4.7911549999999998</v>
@@ -8214,22 +8211,22 @@
         <v>-40.827958000000002</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="H113" s="4" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="I113" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J113" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K113" s="6" t="s">
         <v>18</v>
@@ -8237,10 +8234,10 @@
     </row>
     <row r="114" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="C114" s="5">
         <v>-3.4859019999999998</v>
@@ -8249,33 +8246,33 @@
         <v>-39.523645000000002</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="H114" s="4" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="I114" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J114" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K114" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="115" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="C115" s="5">
         <v>-4.5871829999999996</v>
@@ -8284,16 +8281,16 @@
         <v>-38.620182999999997</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="H115" s="4" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="I115" s="4" t="s">
         <v>101</v>
@@ -8305,12 +8302,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="C116" s="5">
         <v>-3.5105249999999999</v>
@@ -8322,30 +8319,30 @@
         <v>235</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="H116" s="4" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="I116" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J116" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K116" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="117" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="C117" s="5">
         <v>-3.2141000000000002</v>
@@ -8354,16 +8351,16 @@
         <v>-40.864533000000002</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="H117" s="4" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="I117" s="4" t="s">
         <v>101</v>
@@ -8375,12 +8372,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="118" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="C118" s="5">
         <v>-5.0508829999999998</v>
@@ -8389,16 +8386,16 @@
         <v>-37.779632999999997</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="H118" s="4" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="I118" s="4" t="s">
         <v>151</v>
@@ -8439,7 +8436,7 @@
         <v>151</v>
       </c>
       <c r="J119" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K119" s="6" t="s">
         <v>18</v>
@@ -8447,10 +8444,10 @@
     </row>
     <row r="120" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="C120" s="5">
         <v>-5.5281140000000004</v>
@@ -8462,30 +8459,30 @@
         <v>76</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="H120" s="4" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="I120" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J120" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K120" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="121" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="C121" s="5">
         <v>-4.338266</v>
@@ -8497,13 +8494,13 @@
         <v>104</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="H121" s="4" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="I121" s="4" t="s">
         <v>101</v>
@@ -8517,10 +8514,10 @@
     </row>
     <row r="122" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="C122" s="5">
         <v>-4.2869089999999996</v>
@@ -8532,10 +8529,10 @@
         <v>36</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="H122" s="4" t="s">
         <v>83</v>
@@ -8544,18 +8541,18 @@
         <v>151</v>
       </c>
       <c r="J122" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K122" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="123" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="C123" s="5">
         <v>-3.372366</v>
@@ -8567,13 +8564,13 @@
         <v>174</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="H123" s="4" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="I123" s="4" t="s">
         <v>151</v>
@@ -8587,10 +8584,10 @@
     </row>
     <row r="124" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="C124" s="5">
         <v>-2.8945319999999999</v>
@@ -8602,30 +8599,30 @@
         <v>174</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="H124" s="4" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="I124" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J124" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K124" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="125" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="C125" s="5">
         <v>-4.7071329999999998</v>
@@ -8637,10 +8634,10 @@
         <v>25</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="H125" s="4" t="s">
         <v>27</v>
@@ -8655,12 +8652,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="126" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="C126" s="5">
         <v>-4.0460330000000004</v>
@@ -8672,13 +8669,13 @@
         <v>191</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="H126" s="4" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="I126" s="4" t="s">
         <v>101</v>
@@ -8690,12 +8687,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="127" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="C127" s="5">
         <v>-5.5796159999999997</v>
@@ -8707,13 +8704,13 @@
         <v>191</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="H127" s="4" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="I127" s="4" t="s">
         <v>151</v>
@@ -8725,12 +8722,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="128" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="C128" s="5">
         <v>-5.3889829999999996</v>
@@ -8739,16 +8736,16 @@
         <v>-38.911766</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="H128" s="4" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="I128" s="4" t="s">
         <v>101</v>
@@ -8760,12 +8757,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="129" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="C129" s="5">
         <v>-5.9808000000000003</v>
@@ -8774,16 +8771,16 @@
         <v>-38.884349999999998</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="G129" s="4" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="H129" s="4" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="I129" s="4" t="s">
         <v>101</v>
@@ -8795,12 +8792,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="130" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="C130" s="5">
         <v>-3.5994000000000002</v>
@@ -8809,16 +8806,16 @@
         <v>-38.898966000000001</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="G130" s="4" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="H130" s="4" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="I130" s="4" t="s">
         <v>101</v>
@@ -8830,12 +8827,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="131" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="C131" s="5">
         <v>-4.1112159999999998</v>
@@ -8844,10 +8841,10 @@
         <v>-39.226599999999998</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="G131" s="4" t="s">
         <v>284</v>
@@ -8865,12 +8862,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="132" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="C132" s="5">
         <v>-3.3707829999999999</v>
@@ -8879,16 +8876,16 @@
         <v>-39.293933000000003</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="G132" s="4" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="H132" s="4" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="I132" s="4" t="s">
         <v>101</v>
@@ -8902,10 +8899,10 @@
     </row>
     <row r="133" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="C133" s="5">
         <v>-5.8117999999999999</v>
@@ -8917,30 +8914,30 @@
         <v>197</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="G133" s="4" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H133" s="4" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="I133" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J133" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K133" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="134" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="C134" s="5">
         <v>-3.304783</v>
@@ -8952,13 +8949,13 @@
         <v>174</v>
       </c>
       <c r="F134" s="4" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="H134" s="4" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="I134" s="4" t="s">
         <v>101</v>
@@ -8970,12 +8967,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="135" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="C135" s="5">
         <v>-5.1408160000000001</v>
@@ -8987,13 +8984,13 @@
         <v>266</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="H135" s="4" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="I135" s="4" t="s">
         <v>101</v>
@@ -9007,10 +9004,10 @@
     </row>
     <row r="136" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="C136" s="5">
         <v>-3.4763199999999999</v>
@@ -9022,30 +9019,30 @@
         <v>48</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="G136" s="4" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="H136" s="4" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="I136" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J136" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K136" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="137" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="C137" s="5">
         <v>-3.5617000000000001</v>
@@ -9057,13 +9054,13 @@
         <v>241</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="H137" s="4" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="I137" s="4" t="s">
         <v>151</v>
@@ -9077,10 +9074,10 @@
     </row>
     <row r="138" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="C138" s="5">
         <v>-5.4055679999999997</v>
@@ -9092,19 +9089,19 @@
         <v>136</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="G138" s="4" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="H138" s="4" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="I138" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J138" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K138" s="6" t="s">
         <v>18</v>
@@ -9112,10 +9109,10 @@
     </row>
     <row r="139" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="C139" s="5">
         <v>-2.9586229999999998</v>
@@ -9127,19 +9124,19 @@
         <v>174</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="H139" s="4" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="I139" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J139" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K139" s="6" t="s">
         <v>18</v>
@@ -9147,10 +9144,10 @@
     </row>
     <row r="140" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="C140" s="5">
         <v>-2.92225</v>
@@ -9159,22 +9156,22 @@
         <v>-40.120244</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="G140" s="4" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="H140" s="4" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="I140" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J140" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K140" s="6" t="s">
         <v>18</v>
@@ -9182,10 +9179,10 @@
     </row>
     <row r="141" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="C141" s="5">
         <v>-3.697114</v>
@@ -9197,19 +9194,19 @@
         <v>48</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="G141" s="4" t="s">
         <v>51</v>
       </c>
       <c r="H141" s="4" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="I141" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J141" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K141" s="6" t="s">
         <v>18</v>
@@ -9217,10 +9214,10 @@
     </row>
     <row r="142" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="C142" s="5">
         <v>-3.7188409999999998</v>
@@ -9232,30 +9229,30 @@
         <v>58</v>
       </c>
       <c r="F142" s="4" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="G142" s="4" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="H142" s="4" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="I142" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J142" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K142" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="143" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="C143" s="5">
         <v>-4.0392330000000003</v>
@@ -9264,16 +9261,16 @@
         <v>-40.474150000000002</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="G143" s="4" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="H143" s="4" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="I143" s="4" t="s">
         <v>151</v>
@@ -9285,12 +9282,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="144" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="C144" s="5">
         <v>-4.1177159999999997</v>
@@ -9302,13 +9299,13 @@
         <v>208</v>
       </c>
       <c r="F144" s="4" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="G144" s="4" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="H144" s="4" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="I144" s="4" t="s">
         <v>101</v>
@@ -9322,10 +9319,10 @@
     </row>
     <row r="145" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="C145" s="5">
         <v>-4.5583349999999996</v>
@@ -9334,22 +9331,22 @@
         <v>-40.729585999999998</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="F145" s="4" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="G145" s="4" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="H145" s="4" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="I145" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J145" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K145" s="6" t="s">
         <v>18</v>
@@ -9357,10 +9354,10 @@
     </row>
     <row r="146" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="C146" s="5">
         <v>-5.1463979999999996</v>
@@ -9369,33 +9366,33 @@
         <v>-40.670636000000002</v>
       </c>
       <c r="E146" s="4" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="F146" s="4" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="G146" s="4" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="H146" s="4" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="I146" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J146" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K146" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="147" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="C147" s="5">
         <v>-4.0631500000000003</v>
@@ -9404,16 +9401,16 @@
         <v>-40.957650000000001</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="F147" s="4" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="G147" s="4" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="H147" s="4" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="I147" s="4" t="s">
         <v>101</v>
@@ -9425,12 +9422,12 @@
         <v>308</v>
       </c>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="C148" s="5">
         <v>-3.521487</v>
@@ -9439,33 +9436,33 @@
         <v>-40.330056999999996</v>
       </c>
       <c r="E148" s="4" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="F148" s="4" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="G148" s="4" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="H148" s="4" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="I148" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J148" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K148" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="C149" s="5">
         <v>-3.5194079999999999</v>
@@ -9474,33 +9471,33 @@
         <v>-40.361950999999998</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="F149" s="4" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="H149" s="4" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
       <c r="I149" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J149" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K149" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="C150" s="5">
         <v>-3.552886</v>
@@ -9512,19 +9509,19 @@
         <v>48</v>
       </c>
       <c r="F150" s="4" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="G150" s="4" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="H150" s="4" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="I150" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J150" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="K150" s="6" t="s">
         <v>18</v>
@@ -9534,7 +9531,7 @@
   <autoFilter ref="A1:K150" xr:uid="{4DA12617-6B17-4A0E-9E79-EBA6E19B3138}">
     <filterColumn colId="9">
       <filters>
-        <filter val="EM ANDAMENTO"/>
+        <filter val="NÃO"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -9542,13 +9539,12 @@
     <sortCondition ref="B1:B150"/>
   </sortState>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="63" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="36" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D18A476-0271-4A84-BE9E-901865A86FD3}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AC157"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -9579,15 +9575,15 @@
         <v>5</v>
       </c>
       <c r="D1" s="30" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="E1" s="30"/>
       <c r="F1" s="31" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="G1" s="31"/>
       <c r="H1" s="27" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="I1" s="27"/>
       <c r="J1" s="27"/>
@@ -9610,7 +9606,7 @@
       <c r="AA1" s="27"/>
       <c r="AB1" s="27"/>
       <c r="AC1" s="25" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
     </row>
     <row r="2" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9622,18 +9618,18 @@
       <c r="F2" s="31"/>
       <c r="G2" s="31"/>
       <c r="H2" s="26" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="I2" s="26"/>
       <c r="J2" s="26"/>
       <c r="K2" s="9" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="M2" s="27" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="N2" s="27"/>
       <c r="O2" s="27"/>
@@ -9661,67 +9657,67 @@
       <c r="F3" s="31"/>
       <c r="G3" s="31"/>
       <c r="H3" s="8" t="s">
+        <v>808</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>809</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>810</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>811</v>
+      </c>
+      <c r="L3" s="7" t="s">
         <v>812</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="M3" s="7" t="s">
         <v>813</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="N3" s="7" t="s">
         <v>814</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="O3" s="7" t="s">
         <v>815</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="P3" s="7" t="s">
         <v>816</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="Q3" s="7" t="s">
         <v>817</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="R3" s="7" t="s">
         <v>818</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="S3" s="7" t="s">
         <v>819</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="T3" s="7" t="s">
         <v>820</v>
       </c>
-      <c r="Q3" s="7" t="s">
+      <c r="U3" s="7" t="s">
         <v>821</v>
       </c>
-      <c r="R3" s="7" t="s">
+      <c r="V3" s="7" t="s">
         <v>822</v>
       </c>
-      <c r="S3" s="7" t="s">
+      <c r="W3" s="7" t="s">
         <v>823</v>
       </c>
-      <c r="T3" s="7" t="s">
+      <c r="X3" s="7" t="s">
         <v>824</v>
       </c>
-      <c r="U3" s="7" t="s">
+      <c r="Y3" s="7" t="s">
         <v>825</v>
       </c>
-      <c r="V3" s="7" t="s">
+      <c r="Z3" s="7" t="s">
         <v>826</v>
       </c>
-      <c r="W3" s="7" t="s">
+      <c r="AA3" s="7" t="s">
         <v>827</v>
       </c>
-      <c r="X3" s="7" t="s">
+      <c r="AB3" s="7" t="s">
         <v>828</v>
-      </c>
-      <c r="Y3" s="7" t="s">
-        <v>829</v>
-      </c>
-      <c r="Z3" s="7" t="s">
-        <v>830</v>
-      </c>
-      <c r="AA3" s="7" t="s">
-        <v>831</v>
-      </c>
-      <c r="AB3" s="7" t="s">
-        <v>832</v>
       </c>
       <c r="AC3" s="25"/>
     </row>
@@ -9760,7 +9756,7 @@
       <c r="AB4" s="11"/>
       <c r="AC4" s="25"/>
     </row>
-    <row r="5" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="19" t="s">
         <v>96</v>
       </c>
@@ -9803,7 +9799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
         <v>103</v>
       </c>
@@ -9846,7 +9842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="19" t="s">
         <v>109</v>
       </c>
@@ -9889,7 +9885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="19" t="s">
         <v>114</v>
       </c>
@@ -9932,7 +9928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
         <v>120</v>
       </c>
@@ -9975,7 +9971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="19" t="s">
         <v>125</v>
       </c>
@@ -10018,7 +10014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="19" t="s">
         <v>135</v>
       </c>
@@ -10109,7 +10105,7 @@
         <v>5682</v>
       </c>
     </row>
-    <row r="12" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="19" t="s">
         <v>141</v>
       </c>
@@ -10152,15 +10148,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
         <v>147</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="D13" s="21"/>
       <c r="E13" s="21"/>
@@ -10195,7 +10191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="19" t="s">
         <v>159</v>
       </c>
@@ -10206,10 +10202,10 @@
         <v>160</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="E14" s="24" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="F14" s="20">
         <v>46142</v>
@@ -10286,7 +10282,7 @@
         <v>5190</v>
       </c>
     </row>
-    <row r="15" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="19" t="s">
         <v>173</v>
       </c>
@@ -10329,7 +10325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="19" t="s">
         <v>180</v>
       </c>
@@ -10420,7 +10416,7 @@
         <v>5845</v>
       </c>
     </row>
-    <row r="17" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="19" t="s">
         <v>185</v>
       </c>
@@ -10463,7 +10459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="19" t="s">
         <v>190</v>
       </c>
@@ -10554,7 +10550,7 @@
         <v>3934</v>
       </c>
     </row>
-    <row r="19" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="19" t="s">
         <v>196</v>
       </c>
@@ -10565,10 +10561,10 @@
         <v>198</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="E19" s="24" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="F19" s="20">
         <v>46142</v>
@@ -10645,15 +10641,15 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="20" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="19" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="D20" s="21">
         <v>-3.7752400000000002</v>
@@ -10736,15 +10732,15 @@
         <v>4245</v>
       </c>
     </row>
-    <row r="21" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="19" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="B21" s="19" t="s">
         <v>208</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="D21" s="21"/>
       <c r="E21" s="21"/>
@@ -10779,15 +10775,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="19" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="D22" s="21">
         <v>-4.7911549999999998</v>
@@ -10870,21 +10866,21 @@
         <v>2038</v>
       </c>
     </row>
-    <row r="23" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="19" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="D23" s="24" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="E23" s="24" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="F23" s="20">
         <v>46153</v>
@@ -10961,15 +10957,15 @@
         <v>7108</v>
       </c>
     </row>
-    <row r="24" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="19" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="D24" s="21"/>
       <c r="E24" s="21"/>
@@ -11006,19 +11002,19 @@
     </row>
     <row r="25" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="19" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="B25" s="19" t="s">
         <v>235</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="D25" s="24" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="E25" s="24" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="F25" s="20">
         <v>46159</v>
@@ -11095,15 +11091,15 @@
         <v>4586</v>
       </c>
     </row>
-    <row r="26" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="19" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="D26" s="21"/>
       <c r="E26" s="21"/>
@@ -11138,15 +11134,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="19" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="D27" s="21"/>
       <c r="E27" s="21"/>
@@ -11181,7 +11177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="19" t="s">
         <v>202</v>
       </c>
@@ -11192,10 +11188,10 @@
         <v>203</v>
       </c>
       <c r="D28" s="24" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="E28" s="24" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="F28" s="20">
         <v>46142</v>
@@ -11272,21 +11268,21 @@
         <v>9101</v>
       </c>
     </row>
-    <row r="29" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="B29" s="19" t="s">
         <v>76</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="D29" s="24" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="E29" s="24" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="F29" s="20">
         <v>46139</v>
@@ -11363,15 +11359,15 @@
         <v>2316</v>
       </c>
     </row>
-    <row r="30" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="B30" s="19" t="s">
         <v>104</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="D30" s="21"/>
       <c r="E30" s="21"/>
@@ -11406,15 +11402,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="B31" s="19" t="s">
         <v>36</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="D31" s="21">
         <v>-4.2869089999999996</v>
@@ -11497,15 +11493,15 @@
         <v>1584</v>
       </c>
     </row>
-    <row r="32" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="B32" s="19" t="s">
         <v>174</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="D32" s="21"/>
       <c r="E32" s="21"/>
@@ -11540,15 +11536,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="B33" s="19" t="s">
         <v>174</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="D33" s="24">
         <v>-2.8945319999999999</v>
@@ -11631,15 +11627,15 @@
         <v>4636</v>
       </c>
     </row>
-    <row r="34" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="19" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="B34" s="19" t="s">
         <v>25</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="D34" s="21"/>
       <c r="E34" s="21"/>
@@ -11674,15 +11670,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="B35" s="19" t="s">
         <v>191</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="D35" s="21"/>
       <c r="E35" s="21"/>
@@ -11717,15 +11713,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="B36" s="19" t="s">
         <v>191</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="D36" s="21"/>
       <c r="E36" s="21"/>
@@ -11760,15 +11756,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="D37" s="21"/>
       <c r="E37" s="21"/>
@@ -11803,15 +11799,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="19" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="D38" s="21"/>
       <c r="E38" s="21"/>
@@ -11846,15 +11842,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="19" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="D39" s="21"/>
       <c r="E39" s="21"/>
@@ -11889,15 +11885,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="19" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="D40" s="21"/>
       <c r="E40" s="21"/>
@@ -11932,15 +11928,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="19" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="D41" s="21"/>
       <c r="E41" s="21"/>
@@ -11975,21 +11971,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="19" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="B42" s="19" t="s">
         <v>197</v>
       </c>
       <c r="C42" s="19" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="D42" s="24" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="E42" s="24" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="F42" s="20">
         <v>46139</v>
@@ -12066,15 +12062,15 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="43" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="19" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="B43" s="19" t="s">
         <v>174</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="D43" s="21"/>
       <c r="E43" s="21"/>
@@ -12109,15 +12105,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="19" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="B44" s="19" t="s">
         <v>266</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="D44" s="21"/>
       <c r="E44" s="21"/>
@@ -12152,21 +12148,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="19" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="B45" s="19" t="s">
         <v>48</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="D45" s="24" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="E45" s="24" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="F45" s="20">
         <v>46153</v>
@@ -12243,15 +12239,15 @@
         <v>7959</v>
       </c>
     </row>
-    <row r="46" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="19" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="B46" s="19" t="s">
         <v>241</v>
       </c>
       <c r="C46" s="19" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="D46" s="21"/>
       <c r="E46" s="21"/>
@@ -12286,15 +12282,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="19" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="B47" s="19" t="s">
         <v>136</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="D47" s="21">
         <v>-5.4055679999999997</v>
@@ -12377,15 +12373,15 @@
         <v>2429</v>
       </c>
     </row>
-    <row r="48" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="19" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="B48" s="19" t="s">
         <v>174</v>
       </c>
       <c r="C48" s="19" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="D48" s="24">
         <v>-2.9586229999999998</v>
@@ -12468,15 +12464,15 @@
         <v>5649</v>
       </c>
     </row>
-    <row r="49" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="19" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="B49" s="19" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="C49" s="19" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="D49" s="24">
         <v>-2.92225</v>
@@ -12559,15 +12555,15 @@
         <v>6660</v>
       </c>
     </row>
-    <row r="50" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="19" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="B50" s="19" t="s">
         <v>48</v>
       </c>
       <c r="C50" s="19" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="D50" s="21">
         <v>-3.697114</v>
@@ -12650,15 +12646,15 @@
         <v>2483</v>
       </c>
     </row>
-    <row r="51" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="19" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="B51" s="19" t="s">
         <v>58</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="D51" s="21">
         <v>-3.7188409999999998</v>
@@ -12741,15 +12737,15 @@
         <v>4263</v>
       </c>
     </row>
-    <row r="52" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="19" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="B52" s="19" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="C52" s="19" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="D52" s="21"/>
       <c r="E52" s="21"/>
@@ -12784,15 +12780,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="19" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="B53" s="19" t="s">
         <v>208</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="D53" s="21"/>
       <c r="E53" s="21"/>
@@ -12827,15 +12823,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="19" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="B54" s="19" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="C54" s="19" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="D54" s="21">
         <v>-4.5583349999999996</v>
@@ -12918,15 +12914,15 @@
         <v>1560</v>
       </c>
     </row>
-    <row r="55" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="19" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="B55" s="19" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="D55" s="21">
         <v>-5.1463979999999996</v>
@@ -13009,15 +13005,15 @@
         <v>1864</v>
       </c>
     </row>
-    <row r="56" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="19" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="B56" s="19" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="C56" s="19" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="D56" s="21"/>
       <c r="E56" s="21"/>
@@ -13054,19 +13050,19 @@
     </row>
     <row r="57" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="19" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="B57" s="19" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="D57" s="24" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="E57" s="24" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="F57" s="20">
         <v>46159</v>
@@ -13145,19 +13141,19 @@
     </row>
     <row r="58" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="19" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="B58" s="19" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="C58" s="19" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="D58" s="24" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="E58" s="24" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
       <c r="F58" s="20">
         <v>46159</v>
@@ -13236,19 +13232,19 @@
     </row>
     <row r="59" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="19" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="B59" s="19" t="s">
         <v>48</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="D59" s="24" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="E59" s="24" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
       <c r="F59" s="20">
         <v>46159</v>
@@ -13325,7 +13321,7 @@
         <v>3999</v>
       </c>
     </row>
-    <row r="60" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="19" t="s">
         <v>315</v>
       </c>
@@ -13416,7 +13412,7 @@
         <v>2567</v>
       </c>
     </row>
-    <row r="61" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="19" t="s">
         <v>320</v>
       </c>
@@ -13459,7 +13455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="19" t="s">
         <v>325</v>
       </c>
@@ -13502,7 +13498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="19" t="s">
         <v>330</v>
       </c>
@@ -13593,7 +13589,7 @@
         <v>2906</v>
       </c>
     </row>
-    <row r="64" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="19" t="s">
         <v>335</v>
       </c>
@@ -13636,7 +13632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="19" t="s">
         <v>341</v>
       </c>
@@ -13679,7 +13675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="19" t="s">
         <v>130</v>
       </c>
@@ -13770,7 +13766,7 @@
         <v>5492</v>
       </c>
     </row>
-    <row r="67" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="19" t="s">
         <v>347</v>
       </c>
@@ -13861,7 +13857,7 @@
         <v>3330</v>
       </c>
     </row>
-    <row r="68" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="19" t="s">
         <v>351</v>
       </c>
@@ -13904,7 +13900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="19" t="s">
         <v>357</v>
       </c>
@@ -13995,7 +13991,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="70" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="19" t="s">
         <v>362</v>
       </c>
@@ -14086,7 +14082,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="71" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="19" t="s">
         <v>368</v>
       </c>
@@ -14129,15 +14125,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="19" t="s">
         <v>374</v>
       </c>
       <c r="B72" s="19" t="s">
-        <v>375</v>
+        <v>785</v>
       </c>
       <c r="C72" s="19" t="s">
-        <v>376</v>
+        <v>880</v>
       </c>
       <c r="D72" s="21"/>
       <c r="E72" s="21"/>
@@ -14172,15 +14168,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="19" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="B73" s="19" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="C73" s="19" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="D73" s="21"/>
       <c r="E73" s="21"/>
@@ -14215,15 +14211,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="19" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="B74" s="19" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="C74" s="19" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="D74" s="21"/>
       <c r="E74" s="21"/>
@@ -14258,15 +14254,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="19" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="B75" s="19" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="C75" s="19" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="D75" s="21"/>
       <c r="E75" s="21"/>
@@ -14301,15 +14297,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="19" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="B76" s="19" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="C76" s="19" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="D76" s="21"/>
       <c r="E76" s="21"/>
@@ -14344,15 +14340,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="19" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="B77" s="19" t="s">
         <v>272</v>
       </c>
       <c r="C77" s="19" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="D77" s="21"/>
       <c r="E77" s="21"/>
@@ -14387,15 +14383,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="19" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="B78" s="19" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="C78" s="19" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="D78" s="21"/>
       <c r="E78" s="21"/>
@@ -14430,15 +14426,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="19" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="B79" s="19" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="C79" s="19" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="D79" s="21"/>
       <c r="E79" s="21"/>
@@ -14473,21 +14469,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="19" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="B80" s="19" t="s">
         <v>266</v>
       </c>
       <c r="C80" s="19" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="D80" s="24" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="E80" s="24" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="F80" s="20">
         <v>46153</v>
@@ -14564,21 +14560,21 @@
         <v>4247</v>
       </c>
     </row>
-    <row r="81" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="19" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="B81" s="19" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="C81" s="19" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="D81" s="24" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="E81" s="24" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
       <c r="F81" s="20">
         <v>46153</v>
@@ -14655,15 +14651,15 @@
         <v>4161</v>
       </c>
     </row>
-    <row r="82" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="19" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="B82" s="19" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="C82" s="19" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D82" s="21"/>
       <c r="E82" s="21"/>
@@ -14698,15 +14694,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="19" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="B83" s="19" t="s">
         <v>229</v>
       </c>
       <c r="C83" s="19" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="D83" s="21">
         <v>-4.3755519999999999</v>
@@ -14789,15 +14785,15 @@
         <v>6031</v>
       </c>
     </row>
-    <row r="84" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="19" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="B84" s="19" t="s">
         <v>229</v>
       </c>
       <c r="C84" s="19" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="D84" s="21"/>
       <c r="E84" s="21"/>
@@ -14832,15 +14828,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="19" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="B85" s="19" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="C85" s="19" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="D85" s="21"/>
       <c r="E85" s="21"/>
@@ -14875,15 +14871,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="19" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="B86" s="19" t="s">
         <v>97</v>
       </c>
       <c r="C86" s="19" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="D86" s="21"/>
       <c r="E86" s="21"/>
@@ -14918,15 +14914,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="19" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="B87" s="19" t="s">
         <v>235</v>
       </c>
       <c r="C87" s="19" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="D87" s="21"/>
       <c r="E87" s="21"/>
@@ -14961,15 +14957,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="19" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="B88" s="19" t="s">
         <v>235</v>
       </c>
       <c r="C88" s="19" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="D88" s="21">
         <v>-3.6184599999999998</v>
@@ -15052,15 +15048,15 @@
         <v>6697</v>
       </c>
     </row>
-    <row r="89" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="19" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="B89" s="19" t="s">
         <v>235</v>
       </c>
       <c r="C89" s="19" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="D89" s="21"/>
       <c r="E89" s="21"/>
@@ -15095,21 +15091,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="19" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="B90" s="19" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="C90" s="19" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="D90" s="24" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="E90" s="24" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="F90" s="20">
         <v>46139</v>
@@ -15186,15 +15182,15 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="91" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="19" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="B91" s="19" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="C91" s="19" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="D91" s="21"/>
       <c r="E91" s="21"/>
@@ -15231,19 +15227,19 @@
     </row>
     <row r="92" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="19" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="B92" s="19" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="C92" s="19" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="D92" s="24" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
       <c r="E92" s="24" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="F92" s="20">
         <v>46159</v>
@@ -15320,21 +15316,21 @@
         <v>2842</v>
       </c>
     </row>
-    <row r="93" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="19" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="B93" s="19" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="C93" s="19" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="D93" s="24" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="E93" s="24" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
       <c r="F93" s="20">
         <v>46142</v>
@@ -15411,15 +15407,15 @@
         <v>988</v>
       </c>
     </row>
-    <row r="94" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="19" t="s">
         <v>153</v>
       </c>
       <c r="B94" s="19" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="C94" s="19" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="D94" s="21">
         <v>-5.0822029999999998</v>
@@ -15502,15 +15498,15 @@
         <v>2883</v>
       </c>
     </row>
-    <row r="95" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="19" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="B95" s="19" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="C95" s="19" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D95" s="24">
         <v>-5.4022300000000003</v>
@@ -15593,21 +15589,21 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="96" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="19" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="B96" s="19" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="C96" s="19" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="D96" s="24" t="s">
-        <v>846</v>
+        <v>842</v>
       </c>
       <c r="E96" s="24" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="F96" s="20">
         <v>46139</v>
@@ -15684,21 +15680,21 @@
         <v>3307</v>
       </c>
     </row>
-    <row r="97" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="19" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="B97" s="19" t="s">
         <v>136</v>
       </c>
       <c r="C97" s="19" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="D97" s="24" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="E97" s="24" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="F97" s="20">
         <v>46139</v>
@@ -15775,15 +15771,15 @@
         <v>7063</v>
       </c>
     </row>
-    <row r="98" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="19" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="B98" s="19" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="C98" s="19" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="D98" s="21"/>
       <c r="E98" s="21"/>
@@ -15818,15 +15814,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="19" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="B99" s="19" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="C99" s="19" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="D99" s="21"/>
       <c r="E99" s="21"/>
@@ -15861,15 +15857,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="19" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B100" s="19" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="C100" s="19" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="D100" s="21"/>
       <c r="E100" s="21"/>
@@ -15904,15 +15900,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="19" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="B101" s="19" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="C101" s="19" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="D101" s="21"/>
       <c r="E101" s="21"/>
@@ -15947,15 +15943,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="19" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="B102" s="19" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="C102" s="19" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="D102" s="21"/>
       <c r="E102" s="21"/>
@@ -15990,7 +15986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="19" t="s">
         <v>164</v>
       </c>
@@ -15998,7 +15994,7 @@
         <v>165</v>
       </c>
       <c r="C103" s="19" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="D103" s="21">
         <v>-4.8596729999999999</v>
@@ -16081,15 +16077,15 @@
         <v>2499</v>
       </c>
     </row>
-    <row r="104" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="19" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="B104" s="19" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="C104" s="19" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="D104" s="21">
         <v>-4.4447369999999999</v>
@@ -16172,15 +16168,15 @@
         <v>2533</v>
       </c>
     </row>
-    <row r="105" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="19" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="B105" s="19" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="C105" s="19" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="D105" s="21">
         <v>-5.1705110000000003</v>
@@ -16263,15 +16259,15 @@
         <v>2124</v>
       </c>
     </row>
-    <row r="106" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="19" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="B106" s="19" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="C106" s="19" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="D106" s="21"/>
       <c r="E106" s="21"/>
@@ -16306,15 +16302,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="19" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="B107" s="19" t="s">
         <v>358</v>
       </c>
       <c r="C107" s="19" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="D107" s="21"/>
       <c r="E107" s="21"/>
@@ -16349,7 +16345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="19" t="s">
         <v>170</v>
       </c>
@@ -16360,10 +16356,10 @@
         <v>171</v>
       </c>
       <c r="D108" s="24" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="E108" s="24" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="F108" s="20">
         <v>46142</v>
@@ -16440,15 +16436,15 @@
         <v>1973</v>
       </c>
     </row>
-    <row r="109" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="19" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="B109" s="19" t="s">
         <v>42</v>
       </c>
       <c r="C109" s="19" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="D109" s="21"/>
       <c r="E109" s="21"/>
@@ -16483,15 +16479,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="19" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="B110" s="19" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="C110" s="19" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="D110" s="21">
         <v>-3.6978119999999999</v>
@@ -16574,15 +16570,15 @@
         <v>5171</v>
       </c>
     </row>
-    <row r="111" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="19" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="B111" s="19" t="s">
         <v>208</v>
       </c>
       <c r="C111" s="19" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="D111" s="21">
         <v>-5.2113269999999998</v>
@@ -16665,15 +16661,15 @@
         <v>5543</v>
       </c>
     </row>
-    <row r="112" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="19" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="B112" s="19" t="s">
         <v>208</v>
       </c>
       <c r="C112" s="19" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="D112" s="21">
         <v>-4.3822749999999999</v>
@@ -16756,15 +16752,15 @@
         <v>4135</v>
       </c>
     </row>
-    <row r="113" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="19" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="B113" s="19" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="C113" s="19" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="D113" s="21"/>
       <c r="E113" s="21"/>
@@ -16799,15 +16795,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="19" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="B114" s="19" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="C114" s="19" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="D114" s="24">
         <v>-5.2495240000000001</v>
@@ -16890,15 +16886,15 @@
         <v>2947</v>
       </c>
     </row>
-    <row r="115" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="19" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="B115" s="19" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="C115" s="19" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="D115" s="21"/>
       <c r="E115" s="21"/>
@@ -16933,15 +16929,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="19" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="B116" s="19" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="C116" s="19" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="D116" s="21"/>
       <c r="E116" s="21"/>
@@ -16976,15 +16972,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="19" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="B117" s="19" t="s">
         <v>142</v>
       </c>
       <c r="C117" s="19" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="D117" s="21"/>
       <c r="E117" s="21"/>
@@ -17019,15 +17015,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="19" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="B118" s="19" t="s">
         <v>104</v>
       </c>
       <c r="C118" s="19" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="D118" s="21"/>
       <c r="E118" s="21"/>
@@ -17062,7 +17058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="19" t="s">
         <v>11</v>
       </c>
@@ -17153,7 +17149,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="120" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="19" t="s">
         <v>20</v>
       </c>
@@ -17244,7 +17240,7 @@
         <v>1773</v>
       </c>
     </row>
-    <row r="121" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="19" t="s">
         <v>24</v>
       </c>
@@ -17287,7 +17283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="19" t="s">
         <v>30</v>
       </c>
@@ -17378,7 +17374,7 @@
         <v>4915</v>
       </c>
     </row>
-    <row r="123" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="19" t="s">
         <v>35</v>
       </c>
@@ -17421,7 +17417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="19" t="s">
         <v>41</v>
       </c>
@@ -17464,7 +17460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="19" t="s">
         <v>63</v>
       </c>
@@ -17507,7 +17503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="19" t="s">
         <v>69</v>
       </c>
@@ -17550,7 +17546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="19" t="s">
         <v>213</v>
       </c>
@@ -17593,7 +17589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="19" t="s">
         <v>265</v>
       </c>
@@ -17636,7 +17632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="19" t="s">
         <v>271</v>
       </c>
@@ -17679,7 +17675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="19" t="s">
         <v>277</v>
       </c>
@@ -17770,7 +17766,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="131" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="19" t="s">
         <v>282</v>
       </c>
@@ -17861,7 +17857,7 @@
         <v>1984</v>
       </c>
     </row>
-    <row r="132" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="19" t="s">
         <v>81</v>
       </c>
@@ -17952,7 +17948,7 @@
         <v>2597</v>
       </c>
     </row>
-    <row r="133" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="19" t="s">
         <v>86</v>
       </c>
@@ -18043,7 +18039,7 @@
         <v>1733</v>
       </c>
     </row>
-    <row r="134" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="19" t="s">
         <v>92</v>
       </c>
@@ -18134,7 +18130,7 @@
         <v>1724</v>
       </c>
     </row>
-    <row r="135" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="19" t="s">
         <v>287</v>
       </c>
@@ -18177,7 +18173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="19" t="s">
         <v>292</v>
       </c>
@@ -18220,7 +18216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="19" t="s">
         <v>47</v>
       </c>
@@ -18263,7 +18259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="19" t="s">
         <v>53</v>
       </c>
@@ -18306,7 +18302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="19" t="s">
         <v>57</v>
       </c>
@@ -18397,7 +18393,7 @@
         <v>5263</v>
       </c>
     </row>
-    <row r="140" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="19" t="s">
         <v>75</v>
       </c>
@@ -18488,7 +18484,7 @@
         <v>1839</v>
       </c>
     </row>
-    <row r="141" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="19" t="s">
         <v>207</v>
       </c>
@@ -18579,7 +18575,7 @@
         <v>2840</v>
       </c>
     </row>
-    <row r="142" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="19" t="s">
         <v>218</v>
       </c>
@@ -18670,7 +18666,7 @@
         <v>1451</v>
       </c>
     </row>
-    <row r="143" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="19" t="s">
         <v>223</v>
       </c>
@@ -18713,7 +18709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="19" t="s">
         <v>228</v>
       </c>
@@ -18804,7 +18800,7 @@
         <v>2854</v>
       </c>
     </row>
-    <row r="145" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="19" t="s">
         <v>234</v>
       </c>
@@ -18847,7 +18843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="19" t="s">
         <v>240</v>
       </c>
@@ -18890,7 +18886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="19" t="s">
         <v>246</v>
       </c>
@@ -18901,10 +18897,10 @@
         <v>247</v>
       </c>
       <c r="D147" s="24" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="E147" s="24" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="F147" s="20">
         <v>46153</v>
@@ -18981,7 +18977,7 @@
         <v>2936</v>
       </c>
     </row>
-    <row r="148" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="19" t="s">
         <v>251</v>
       </c>
@@ -19024,7 +19020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="19" t="s">
         <v>256</v>
       </c>
@@ -19067,7 +19063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="19" t="s">
         <v>261</v>
       </c>
@@ -19110,7 +19106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="19" t="s">
         <v>298</v>
       </c>
@@ -19153,7 +19149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="19" t="s">
         <v>303</v>
       </c>
@@ -19244,7 +19240,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="153" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="19" t="s">
         <v>310</v>
       </c>
@@ -19307,15 +19303,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A4:AC153" xr:uid="{1D18A476-0271-4A84-BE9E-901865A86FD3}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="P 151"/>
-        <filter val="P 35"/>
-        <filter val="P 96"/>
-        <filter val="P 97"/>
-        <filter val="P 99"/>
-      </filters>
-    </filterColumn>
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="9">

--- a/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
+++ b/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\5- MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA25D04F-6318-45A8-B22F-E9CEB618E802}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ACA8DA5-34F2-48AC-9149-84B08ABFFB79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
   </bookViews>
   <sheets>
     <sheet name="LISTA DE PONTOS" sheetId="1" r:id="rId1"/>
@@ -5895,10 +5895,10 @@
         <v>335</v>
       </c>
       <c r="C47" s="5">
-        <v>-4.7033829999999996</v>
+        <v>-4.7222119999999999</v>
       </c>
       <c r="D47" s="5">
-        <v>-37.482100000000003</v>
+        <v>-37.556274999999999</v>
       </c>
       <c r="E47" s="4" t="s">
         <v>336</v>
@@ -6210,10 +6210,10 @@
         <v>141</v>
       </c>
       <c r="C56" s="5">
-        <v>-4.6214500000000003</v>
+        <v>-4.5752660000000001</v>
       </c>
       <c r="D56" s="5">
-        <v>-37.649166000000001</v>
+        <v>-37.733165999999997</v>
       </c>
       <c r="E56" s="4" t="s">
         <v>142</v>
@@ -7890,10 +7890,10 @@
         <v>593</v>
       </c>
       <c r="C104" s="5">
-        <v>-4.5906500000000001</v>
+        <v>-4.5797999999999996</v>
       </c>
       <c r="D104" s="5">
-        <v>-38.206983000000001</v>
+        <v>-37.851931</v>
       </c>
       <c r="E104" s="4" t="s">
         <v>142</v>
@@ -8625,10 +8625,10 @@
         <v>670</v>
       </c>
       <c r="C125" s="5">
-        <v>-4.7071329999999998</v>
+        <v>-4.5807399999999996</v>
       </c>
       <c r="D125" s="5">
-        <v>-37.839233</v>
+        <v>-37.849532000000004</v>
       </c>
       <c r="E125" s="4" t="s">
         <v>25</v>
@@ -8695,10 +8695,10 @@
         <v>679</v>
       </c>
       <c r="C127" s="5">
-        <v>-5.5796159999999997</v>
+        <v>-5.395251</v>
       </c>
       <c r="D127" s="5">
-        <v>-38.288649999999997</v>
+        <v>-38.230089999999997</v>
       </c>
       <c r="E127" s="4" t="s">
         <v>191</v>

--- a/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
+++ b/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\5- MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ACA8DA5-34F2-48AC-9149-84B08ABFFB79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1635329E-D06D-4643-9122-922D65107A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1873" uniqueCount="883">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1873" uniqueCount="884">
   <si>
     <t>WKT</t>
   </si>
@@ -2693,6 +2693,9 @@
   </si>
   <si>
     <t>ENTR. CE-515</t>
+  </si>
+  <si>
+    <t>EM ANDAMENTO</t>
   </si>
 </sst>
 </file>
@@ -6091,7 +6094,7 @@
         <v>101</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>17</v>
+        <v>883</v>
       </c>
       <c r="K52" s="6" t="s">
         <v>308</v>
@@ -6756,7 +6759,7 @@
         <v>101</v>
       </c>
       <c r="J71" s="6" t="s">
-        <v>17</v>
+        <v>883</v>
       </c>
       <c r="K71" s="6" t="s">
         <v>18</v>
@@ -7211,7 +7214,7 @@
         <v>101</v>
       </c>
       <c r="J84" s="6" t="s">
-        <v>17</v>
+        <v>883</v>
       </c>
       <c r="K84" s="6" t="s">
         <v>18</v>
@@ -7246,7 +7249,7 @@
         <v>101</v>
       </c>
       <c r="J85" s="6" t="s">
-        <v>17</v>
+        <v>883</v>
       </c>
       <c r="K85" s="6" t="s">
         <v>18</v>
@@ -8716,7 +8719,7 @@
         <v>151</v>
       </c>
       <c r="J127" s="6" t="s">
-        <v>17</v>
+        <v>883</v>
       </c>
       <c r="K127" s="6" t="s">
         <v>18</v>

--- a/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
+++ b/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\5- MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1635329E-D06D-4643-9122-922D65107A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76E002DF-A6BB-452D-A823-DB434D440F81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
   </bookViews>
@@ -8383,10 +8383,10 @@
         <v>641</v>
       </c>
       <c r="C118" s="5">
-        <v>-5.0508829999999998</v>
+        <v>-5.0261940000000003</v>
       </c>
       <c r="D118" s="5">
-        <v>-37.779632999999997</v>
+        <v>-37.710459</v>
       </c>
       <c r="E118" s="4" t="s">
         <v>502</v>

--- a/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
+++ b/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\5- MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76E002DF-A6BB-452D-A823-DB434D440F81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAF69C08-7F70-484D-A1A2-FE2406C76A17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
   </bookViews>
   <sheets>
     <sheet name="LISTA DE PONTOS" sheetId="1" r:id="rId1"/>
@@ -4385,7 +4385,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>23</v>
       </c>
@@ -4455,7 +4455,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>34</v>
       </c>
@@ -4490,7 +4490,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>40</v>
       </c>
@@ -4525,7 +4525,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>46</v>
       </c>
@@ -4560,7 +4560,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>52</v>
       </c>
@@ -4630,7 +4630,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>62</v>
       </c>
@@ -4665,7 +4665,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>68</v>
       </c>
@@ -4770,7 +4770,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>212</v>
       </c>
@@ -4840,7 +4840,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>222</v>
       </c>
@@ -4910,7 +4910,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>233</v>
       </c>
@@ -4945,7 +4945,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>239</v>
       </c>
@@ -5015,7 +5015,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>250</v>
       </c>
@@ -5050,7 +5050,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>255</v>
       </c>
@@ -5085,7 +5085,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>260</v>
       </c>
@@ -5120,7 +5120,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>264</v>
       </c>
@@ -5155,7 +5155,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>270</v>
       </c>
@@ -5365,7 +5365,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>286</v>
       </c>
@@ -5400,7 +5400,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>291</v>
       </c>
@@ -5435,7 +5435,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>297</v>
       </c>
@@ -5505,7 +5505,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>309</v>
       </c>
@@ -5540,7 +5540,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>95</v>
       </c>
@@ -5575,7 +5575,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>102</v>
       </c>
@@ -5610,7 +5610,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>108</v>
       </c>
@@ -5645,7 +5645,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>113</v>
       </c>
@@ -5680,7 +5680,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>119</v>
       </c>
@@ -5715,7 +5715,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>124</v>
       </c>
@@ -5785,7 +5785,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>319</v>
       </c>
@@ -5820,7 +5820,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>324</v>
       </c>
@@ -5890,7 +5890,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>334</v>
       </c>
@@ -5925,7 +5925,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>340</v>
       </c>
@@ -6073,10 +6073,10 @@
         <v>351</v>
       </c>
       <c r="C52" s="5">
-        <v>-5.2227160000000001</v>
+        <v>-5.2215020000000001</v>
       </c>
       <c r="D52" s="5">
-        <v>-37.964933000000002</v>
+        <v>-37.892071000000001</v>
       </c>
       <c r="E52" s="4" t="s">
         <v>352</v>
@@ -6170,7 +6170,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>367</v>
       </c>
@@ -6205,7 +6205,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>140</v>
       </c>
@@ -6240,7 +6240,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>373</v>
       </c>
@@ -6275,7 +6275,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>375</v>
       </c>
@@ -6310,7 +6310,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>146</v>
       </c>
@@ -6345,7 +6345,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>381</v>
       </c>
@@ -6380,7 +6380,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>386</v>
       </c>
@@ -6415,7 +6415,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>392</v>
       </c>
@@ -6450,7 +6450,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>398</v>
       </c>
@@ -6485,7 +6485,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>403</v>
       </c>
@@ -6520,7 +6520,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>409</v>
       </c>
@@ -6625,7 +6625,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>426</v>
       </c>
@@ -6695,7 +6695,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>435</v>
       </c>
@@ -6738,10 +6738,10 @@
         <v>441</v>
       </c>
       <c r="C71" s="5">
-        <v>-5.2755999999999998</v>
+        <v>-5.2738310000000004</v>
       </c>
       <c r="D71" s="5">
-        <v>-38.108716000000001</v>
+        <v>-38.108522000000001</v>
       </c>
       <c r="E71" s="4" t="s">
         <v>442</v>
@@ -6765,7 +6765,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>446</v>
       </c>
@@ -6800,7 +6800,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>451</v>
       </c>
@@ -6870,7 +6870,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>461</v>
       </c>
@@ -6940,7 +6940,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>470</v>
       </c>
@@ -7193,10 +7193,10 @@
         <v>501</v>
       </c>
       <c r="C84" s="5">
-        <v>-5.0811999999999999</v>
+        <v>-5.0848469999999999</v>
       </c>
       <c r="D84" s="5">
-        <v>-38.004565999999997</v>
+        <v>-38.009757</v>
       </c>
       <c r="E84" s="4" t="s">
         <v>502</v>
@@ -7228,10 +7228,10 @@
         <v>507</v>
       </c>
       <c r="C85" s="5">
-        <v>-5.2329999999999997</v>
+        <v>-5.2461500000000001</v>
       </c>
       <c r="D85" s="5">
-        <v>-38.194850000000002</v>
+        <v>-38.214409000000003</v>
       </c>
       <c r="E85" s="4" t="s">
         <v>502</v>
@@ -7290,7 +7290,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>511</v>
       </c>
@@ -7325,7 +7325,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>516</v>
       </c>
@@ -7360,7 +7360,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>522</v>
       </c>
@@ -7500,7 +7500,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>540</v>
       </c>
@@ -7535,7 +7535,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>545</v>
       </c>
@@ -7605,7 +7605,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>550</v>
       </c>
@@ -7745,7 +7745,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>570</v>
       </c>
@@ -7815,7 +7815,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>581</v>
       </c>
@@ -7850,7 +7850,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>587</v>
       </c>
@@ -7885,7 +7885,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>592</v>
       </c>
@@ -7920,7 +7920,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>597</v>
       </c>
@@ -7955,7 +7955,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>172</v>
       </c>
@@ -8025,7 +8025,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>184</v>
       </c>
@@ -8165,7 +8165,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>608</v>
       </c>
@@ -8270,7 +8270,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>624</v>
       </c>
@@ -8340,7 +8340,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>635</v>
       </c>
@@ -8375,7 +8375,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>640</v>
       </c>
@@ -8480,7 +8480,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>650</v>
       </c>
@@ -8550,7 +8550,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>659</v>
       </c>
@@ -8620,7 +8620,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>669</v>
       </c>
@@ -8655,7 +8655,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>673</v>
       </c>
@@ -8725,7 +8725,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>683</v>
       </c>
@@ -8760,7 +8760,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>689</v>
       </c>
@@ -8795,7 +8795,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>694</v>
       </c>
@@ -8830,7 +8830,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>700</v>
       </c>
@@ -8865,7 +8865,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>704</v>
       </c>
@@ -8935,7 +8935,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>715</v>
       </c>
@@ -8970,7 +8970,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>720</v>
       </c>
@@ -9040,7 +9040,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>729</v>
       </c>
@@ -9250,7 +9250,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>758</v>
       </c>
@@ -9285,7 +9285,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>762</v>
       </c>
@@ -9390,7 +9390,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>777</v>
       </c>
@@ -9534,7 +9534,7 @@
   <autoFilter ref="A1:K150" xr:uid="{4DA12617-6B17-4A0E-9E79-EBA6E19B3138}">
     <filterColumn colId="9">
       <filters>
-        <filter val="NÃO"/>
+        <filter val="EM ANDAMENTO"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -9542,7 +9542,7 @@
     <sortCondition ref="B1:B150"/>
   </sortState>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="36" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="63" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
+++ b/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\5- MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAF69C08-7F70-484D-A1A2-FE2406C76A17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5FEB6C8-8D1D-43E8-824D-F69294CF4252}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
   </bookViews>
   <sheets>
     <sheet name="LISTA DE PONTOS" sheetId="1" r:id="rId1"/>
@@ -8698,10 +8698,10 @@
         <v>679</v>
       </c>
       <c r="C127" s="5">
-        <v>-5.395251</v>
+        <v>-5.4253080000000002</v>
       </c>
       <c r="D127" s="5">
-        <v>-38.230089999999997</v>
+        <v>-38.218938999999999</v>
       </c>
       <c r="E127" s="4" t="s">
         <v>191</v>

--- a/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
+++ b/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\5- MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5FEB6C8-8D1D-43E8-824D-F69294CF4252}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AB12EB1-B672-48D6-B870-D7046200A045}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
   </bookViews>
   <sheets>
     <sheet name="LISTA DE PONTOS" sheetId="1" r:id="rId1"/>
@@ -4260,7 +4260,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DA12617-6B17-4A0E-9E79-EBA6E19B3138}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K150"/>
@@ -4315,7 +4315,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -4350,7 +4350,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>19</v>
       </c>
@@ -4385,7 +4385,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>23</v>
       </c>
@@ -4393,10 +4393,10 @@
         <v>24</v>
       </c>
       <c r="C4" s="5">
-        <v>-4.818416</v>
+        <v>-4.8189970000000004</v>
       </c>
       <c r="D4" s="5">
-        <v>-37.871932999999999</v>
+        <v>-37.872013000000003</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>25</v>
@@ -4420,7 +4420,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>29</v>
       </c>
@@ -4455,7 +4455,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>34</v>
       </c>
@@ -4490,7 +4490,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>40</v>
       </c>
@@ -4525,7 +4525,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>46</v>
       </c>
@@ -4560,7 +4560,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>52</v>
       </c>
@@ -4595,7 +4595,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>56</v>
       </c>
@@ -4630,7 +4630,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>62</v>
       </c>
@@ -4665,7 +4665,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>68</v>
       </c>
@@ -4700,7 +4700,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>74</v>
       </c>
@@ -4735,7 +4735,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>206</v>
       </c>
@@ -4770,7 +4770,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>212</v>
       </c>
@@ -4805,7 +4805,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>217</v>
       </c>
@@ -4840,7 +4840,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>222</v>
       </c>
@@ -4875,7 +4875,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>227</v>
       </c>
@@ -4910,7 +4910,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>233</v>
       </c>
@@ -4945,7 +4945,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>239</v>
       </c>
@@ -4980,7 +4980,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>245</v>
       </c>
@@ -5015,7 +5015,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>250</v>
       </c>
@@ -5050,7 +5050,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>255</v>
       </c>
@@ -5085,7 +5085,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>260</v>
       </c>
@@ -5120,7 +5120,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>264</v>
       </c>
@@ -5155,7 +5155,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>270</v>
       </c>
@@ -5190,7 +5190,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>276</v>
       </c>
@@ -5225,7 +5225,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>281</v>
       </c>
@@ -5260,7 +5260,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>80</v>
       </c>
@@ -5295,7 +5295,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>85</v>
       </c>
@@ -5330,7 +5330,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>91</v>
       </c>
@@ -5365,7 +5365,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>286</v>
       </c>
@@ -5400,7 +5400,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>291</v>
       </c>
@@ -5435,7 +5435,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="34" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>297</v>
       </c>
@@ -5470,7 +5470,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="35" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>302</v>
       </c>
@@ -5505,7 +5505,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>309</v>
       </c>
@@ -5540,7 +5540,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>95</v>
       </c>
@@ -5575,7 +5575,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>102</v>
       </c>
@@ -5610,7 +5610,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>108</v>
       </c>
@@ -5618,10 +5618,10 @@
         <v>109</v>
       </c>
       <c r="C39" s="5">
-        <v>-4.8713660000000001</v>
+        <v>-4.9123150000000004</v>
       </c>
       <c r="D39" s="5">
-        <v>-38.027166000000001</v>
+        <v>-38.000574</v>
       </c>
       <c r="E39" s="4" t="s">
         <v>104</v>
@@ -5645,7 +5645,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>113</v>
       </c>
@@ -5680,7 +5680,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>119</v>
       </c>
@@ -5715,7 +5715,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>124</v>
       </c>
@@ -5750,7 +5750,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="43" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>314</v>
       </c>
@@ -5785,7 +5785,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>319</v>
       </c>
@@ -5820,7 +5820,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>324</v>
       </c>
@@ -5855,7 +5855,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="46" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>329</v>
       </c>
@@ -5890,7 +5890,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>334</v>
       </c>
@@ -5925,7 +5925,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>340</v>
       </c>
@@ -5933,10 +5933,10 @@
         <v>341</v>
       </c>
       <c r="C48" s="5">
-        <v>-4.8203329999999998</v>
+        <v>-4.8210379999999997</v>
       </c>
       <c r="D48" s="5">
-        <v>-37.881216000000002</v>
+        <v>-37.875945000000002</v>
       </c>
       <c r="E48" s="4" t="s">
         <v>342</v>
@@ -5960,7 +5960,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>129</v>
       </c>
@@ -5995,7 +5995,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>134</v>
       </c>
@@ -6030,7 +6030,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>346</v>
       </c>
@@ -6100,7 +6100,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>356</v>
       </c>
@@ -6135,7 +6135,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>361</v>
       </c>
@@ -6170,7 +6170,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>367</v>
       </c>
@@ -6205,7 +6205,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="56" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>140</v>
       </c>
@@ -6240,7 +6240,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>373</v>
       </c>
@@ -6275,7 +6275,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>375</v>
       </c>
@@ -6310,7 +6310,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>146</v>
       </c>
@@ -6345,7 +6345,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>381</v>
       </c>
@@ -6380,7 +6380,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>386</v>
       </c>
@@ -6415,7 +6415,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="62" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>392</v>
       </c>
@@ -6450,7 +6450,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="63" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>398</v>
       </c>
@@ -6485,7 +6485,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="64" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>403</v>
       </c>
@@ -6520,7 +6520,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="65" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>409</v>
       </c>
@@ -6555,7 +6555,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="66" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>415</v>
       </c>
@@ -6590,7 +6590,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="67" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>420</v>
       </c>
@@ -6625,7 +6625,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>426</v>
       </c>
@@ -6660,7 +6660,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>431</v>
       </c>
@@ -6695,7 +6695,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>435</v>
       </c>
@@ -6703,10 +6703,10 @@
         <v>436</v>
       </c>
       <c r="C70" s="5">
-        <v>-5.0380159999999998</v>
+        <v>-5.041658</v>
       </c>
       <c r="D70" s="5">
-        <v>-37.783000000000001</v>
+        <v>-37.779488000000001</v>
       </c>
       <c r="E70" s="4" t="s">
         <v>229</v>
@@ -6765,7 +6765,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="72" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>446</v>
       </c>
@@ -6800,7 +6800,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="73" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>451</v>
       </c>
@@ -6835,7 +6835,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="74" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>456</v>
       </c>
@@ -6870,7 +6870,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="75" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>461</v>
       </c>
@@ -6905,7 +6905,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="76" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>466</v>
       </c>
@@ -6940,7 +6940,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>470</v>
       </c>
@@ -6975,7 +6975,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>476</v>
       </c>
@@ -7010,7 +7010,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>480</v>
       </c>
@@ -7045,7 +7045,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="80" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>152</v>
       </c>
@@ -7080,7 +7080,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="81" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>486</v>
       </c>
@@ -7115,7 +7115,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="82" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>492</v>
       </c>
@@ -7150,7 +7150,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="83" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>497</v>
       </c>
@@ -7255,7 +7255,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="86" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>158</v>
       </c>
@@ -7290,7 +7290,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>511</v>
       </c>
@@ -7325,7 +7325,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="88" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>516</v>
       </c>
@@ -7360,7 +7360,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="89" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>522</v>
       </c>
@@ -7395,7 +7395,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="90" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>163</v>
       </c>
@@ -7430,7 +7430,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="91" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>528</v>
       </c>
@@ -7465,7 +7465,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="92" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>534</v>
       </c>
@@ -7500,7 +7500,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="93" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>540</v>
       </c>
@@ -7535,7 +7535,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="94" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>545</v>
       </c>
@@ -7570,7 +7570,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="95" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>169</v>
       </c>
@@ -7605,7 +7605,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="96" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>550</v>
       </c>
@@ -7640,7 +7640,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="97" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>554</v>
       </c>
@@ -7675,7 +7675,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="98" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>560</v>
       </c>
@@ -7710,7 +7710,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="99" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>565</v>
       </c>
@@ -7745,7 +7745,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="100" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>570</v>
       </c>
@@ -7780,7 +7780,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="101" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>576</v>
       </c>
@@ -7815,7 +7815,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="102" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>581</v>
       </c>
@@ -7850,7 +7850,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="103" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>587</v>
       </c>
@@ -7885,7 +7885,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="104" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>592</v>
       </c>
@@ -7920,7 +7920,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="105" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>597</v>
       </c>
@@ -7955,7 +7955,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="106" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>172</v>
       </c>
@@ -7990,7 +7990,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="107" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>179</v>
       </c>
@@ -8025,7 +8025,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="108" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>184</v>
       </c>
@@ -8060,7 +8060,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="109" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>189</v>
       </c>
@@ -8095,7 +8095,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="110" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>195</v>
       </c>
@@ -8130,7 +8130,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="111" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>602</v>
       </c>
@@ -8165,7 +8165,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="112" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>608</v>
       </c>
@@ -8200,7 +8200,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="113" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>613</v>
       </c>
@@ -8235,7 +8235,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="114" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>619</v>
       </c>
@@ -8270,7 +8270,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="115" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>624</v>
       </c>
@@ -8305,7 +8305,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="116" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>630</v>
       </c>
@@ -8340,7 +8340,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="117" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>635</v>
       </c>
@@ -8375,7 +8375,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="118" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>640</v>
       </c>
@@ -8383,10 +8383,10 @@
         <v>641</v>
       </c>
       <c r="C118" s="5">
-        <v>-5.0261940000000003</v>
+        <v>-5.0453950000000001</v>
       </c>
       <c r="D118" s="5">
-        <v>-37.710459</v>
+        <v>-37.773105999999999</v>
       </c>
       <c r="E118" s="4" t="s">
         <v>502</v>
@@ -8410,7 +8410,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="119" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>201</v>
       </c>
@@ -8445,7 +8445,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="120" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>645</v>
       </c>
@@ -8480,7 +8480,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="121" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>650</v>
       </c>
@@ -8515,7 +8515,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="122" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>655</v>
       </c>
@@ -8550,7 +8550,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="123" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>659</v>
       </c>
@@ -8585,7 +8585,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="124" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>664</v>
       </c>
@@ -8620,7 +8620,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="125" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>669</v>
       </c>
@@ -8655,7 +8655,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="126" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>673</v>
       </c>
@@ -8725,7 +8725,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="128" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>683</v>
       </c>
@@ -8760,7 +8760,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="129" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>689</v>
       </c>
@@ -8795,7 +8795,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="130" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>694</v>
       </c>
@@ -8830,7 +8830,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="131" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>700</v>
       </c>
@@ -8865,7 +8865,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="132" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>704</v>
       </c>
@@ -8900,7 +8900,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="133" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>710</v>
       </c>
@@ -8935,7 +8935,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="134" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>715</v>
       </c>
@@ -8970,7 +8970,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="135" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>720</v>
       </c>
@@ -9005,7 +9005,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="136" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>725</v>
       </c>
@@ -9040,7 +9040,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="137" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>729</v>
       </c>
@@ -9075,7 +9075,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="138" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>734</v>
       </c>
@@ -9110,7 +9110,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="139" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>739</v>
       </c>
@@ -9145,7 +9145,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="140" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>744</v>
       </c>
@@ -9180,7 +9180,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="141" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>749</v>
       </c>
@@ -9215,7 +9215,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="142" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>753</v>
       </c>
@@ -9250,7 +9250,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="143" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>758</v>
       </c>
@@ -9285,7 +9285,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="144" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>762</v>
       </c>
@@ -9320,7 +9320,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="145" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>767</v>
       </c>
@@ -9355,7 +9355,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="146" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>772</v>
       </c>
@@ -9390,7 +9390,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="147" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>777</v>
       </c>
@@ -9425,7 +9425,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="148" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>783</v>
       </c>
@@ -9460,7 +9460,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="149" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>789</v>
       </c>
@@ -9495,7 +9495,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="150" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>794</v>
       </c>
@@ -9531,18 +9531,12 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K150" xr:uid="{4DA12617-6B17-4A0E-9E79-EBA6E19B3138}">
-    <filterColumn colId="9">
-      <filters>
-        <filter val="EM ANDAMENTO"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:K150" xr:uid="{4DA12617-6B17-4A0E-9E79-EBA6E19B3138}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K150">
     <sortCondition ref="B1:B150"/>
   </sortState>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="63" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="20" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
+++ b/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\5- MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AB12EB1-B672-48D6-B870-D7046200A045}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA75CBF8-AC0F-40CA-905F-C203435C699A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
   </bookViews>
@@ -4260,7 +4260,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DA12617-6B17-4A0E-9E79-EBA6E19B3138}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K150"/>
@@ -4315,7 +4315,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -4350,7 +4350,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>19</v>
       </c>
@@ -4414,13 +4414,13 @@
         <v>16</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>17</v>
+        <v>883</v>
       </c>
       <c r="K4" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>29</v>
       </c>
@@ -4455,7 +4455,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>34</v>
       </c>
@@ -4490,7 +4490,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>40</v>
       </c>
@@ -4525,7 +4525,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>46</v>
       </c>
@@ -4560,7 +4560,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>52</v>
       </c>
@@ -4595,7 +4595,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>56</v>
       </c>
@@ -4630,7 +4630,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>62</v>
       </c>
@@ -4665,7 +4665,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>68</v>
       </c>
@@ -4700,7 +4700,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>74</v>
       </c>
@@ -4735,7 +4735,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>206</v>
       </c>
@@ -4770,7 +4770,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>212</v>
       </c>
@@ -4805,7 +4805,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>217</v>
       </c>
@@ -4840,7 +4840,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>222</v>
       </c>
@@ -4875,7 +4875,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>227</v>
       </c>
@@ -4910,7 +4910,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>233</v>
       </c>
@@ -4945,7 +4945,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>239</v>
       </c>
@@ -4980,7 +4980,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>245</v>
       </c>
@@ -5015,7 +5015,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>250</v>
       </c>
@@ -5050,7 +5050,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>255</v>
       </c>
@@ -5085,7 +5085,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>260</v>
       </c>
@@ -5120,7 +5120,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>264</v>
       </c>
@@ -5155,7 +5155,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>270</v>
       </c>
@@ -5190,7 +5190,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>276</v>
       </c>
@@ -5225,7 +5225,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>281</v>
       </c>
@@ -5260,7 +5260,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>80</v>
       </c>
@@ -5295,7 +5295,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>85</v>
       </c>
@@ -5330,7 +5330,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>91</v>
       </c>
@@ -5365,7 +5365,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>286</v>
       </c>
@@ -5400,7 +5400,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>291</v>
       </c>
@@ -5435,7 +5435,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>297</v>
       </c>
@@ -5470,7 +5470,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>302</v>
       </c>
@@ -5505,7 +5505,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>309</v>
       </c>
@@ -5540,7 +5540,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>95</v>
       </c>
@@ -5575,7 +5575,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>102</v>
       </c>
@@ -5639,13 +5639,13 @@
         <v>101</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>17</v>
+        <v>883</v>
       </c>
       <c r="K39" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>113</v>
       </c>
@@ -5680,7 +5680,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>119</v>
       </c>
@@ -5715,7 +5715,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>124</v>
       </c>
@@ -5750,7 +5750,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>314</v>
       </c>
@@ -5785,7 +5785,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>319</v>
       </c>
@@ -5820,7 +5820,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>324</v>
       </c>
@@ -5855,7 +5855,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>329</v>
       </c>
@@ -5890,7 +5890,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>334</v>
       </c>
@@ -5954,13 +5954,13 @@
         <v>101</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>17</v>
+        <v>883</v>
       </c>
       <c r="K48" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>129</v>
       </c>
@@ -5995,7 +5995,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>134</v>
       </c>
@@ -6030,7 +6030,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>346</v>
       </c>
@@ -6065,7 +6065,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>350</v>
       </c>
@@ -6094,13 +6094,13 @@
         <v>101</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>883</v>
+        <v>800</v>
       </c>
       <c r="K52" s="6" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>356</v>
       </c>
@@ -6135,7 +6135,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>361</v>
       </c>
@@ -6170,7 +6170,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>367</v>
       </c>
@@ -6205,7 +6205,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>140</v>
       </c>
@@ -6240,7 +6240,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>373</v>
       </c>
@@ -6275,7 +6275,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>375</v>
       </c>
@@ -6310,7 +6310,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>146</v>
       </c>
@@ -6345,7 +6345,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>381</v>
       </c>
@@ -6380,7 +6380,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>386</v>
       </c>
@@ -6415,7 +6415,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>392</v>
       </c>
@@ -6450,7 +6450,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>398</v>
       </c>
@@ -6485,7 +6485,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>403</v>
       </c>
@@ -6520,7 +6520,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>409</v>
       </c>
@@ -6555,7 +6555,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>415</v>
       </c>
@@ -6590,7 +6590,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>420</v>
       </c>
@@ -6625,7 +6625,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>426</v>
       </c>
@@ -6660,7 +6660,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>431</v>
       </c>
@@ -6724,13 +6724,13 @@
         <v>151</v>
       </c>
       <c r="J70" s="6" t="s">
-        <v>17</v>
+        <v>883</v>
       </c>
       <c r="K70" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>440</v>
       </c>
@@ -6759,13 +6759,13 @@
         <v>101</v>
       </c>
       <c r="J71" s="6" t="s">
-        <v>883</v>
+        <v>800</v>
       </c>
       <c r="K71" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>446</v>
       </c>
@@ -6800,7 +6800,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>451</v>
       </c>
@@ -6835,7 +6835,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>456</v>
       </c>
@@ -6870,7 +6870,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>461</v>
       </c>
@@ -6905,7 +6905,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>466</v>
       </c>
@@ -6940,7 +6940,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>470</v>
       </c>
@@ -6975,7 +6975,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>476</v>
       </c>
@@ -7010,7 +7010,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>480</v>
       </c>
@@ -7045,7 +7045,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>152</v>
       </c>
@@ -7080,7 +7080,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>486</v>
       </c>
@@ -7115,7 +7115,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>492</v>
       </c>
@@ -7150,7 +7150,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>497</v>
       </c>
@@ -7185,7 +7185,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>500</v>
       </c>
@@ -7214,13 +7214,13 @@
         <v>101</v>
       </c>
       <c r="J84" s="6" t="s">
-        <v>883</v>
+        <v>800</v>
       </c>
       <c r="K84" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>506</v>
       </c>
@@ -7249,13 +7249,13 @@
         <v>101</v>
       </c>
       <c r="J85" s="6" t="s">
-        <v>883</v>
+        <v>800</v>
       </c>
       <c r="K85" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>158</v>
       </c>
@@ -7290,7 +7290,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>511</v>
       </c>
@@ -7325,7 +7325,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>516</v>
       </c>
@@ -7360,7 +7360,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>522</v>
       </c>
@@ -7395,7 +7395,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>163</v>
       </c>
@@ -7430,7 +7430,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>528</v>
       </c>
@@ -7465,7 +7465,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>534</v>
       </c>
@@ -7500,7 +7500,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>540</v>
       </c>
@@ -7535,7 +7535,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>545</v>
       </c>
@@ -7570,7 +7570,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>169</v>
       </c>
@@ -7605,7 +7605,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>550</v>
       </c>
@@ -7640,7 +7640,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>554</v>
       </c>
@@ -7675,7 +7675,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>560</v>
       </c>
@@ -7710,7 +7710,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>565</v>
       </c>
@@ -7745,7 +7745,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>570</v>
       </c>
@@ -7780,7 +7780,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>576</v>
       </c>
@@ -7815,7 +7815,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>581</v>
       </c>
@@ -7850,7 +7850,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>587</v>
       </c>
@@ -7885,7 +7885,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>592</v>
       </c>
@@ -7920,7 +7920,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>597</v>
       </c>
@@ -7955,7 +7955,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>172</v>
       </c>
@@ -7990,7 +7990,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>179</v>
       </c>
@@ -8025,7 +8025,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>184</v>
       </c>
@@ -8060,7 +8060,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>189</v>
       </c>
@@ -8095,7 +8095,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>195</v>
       </c>
@@ -8130,7 +8130,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>602</v>
       </c>
@@ -8165,7 +8165,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>608</v>
       </c>
@@ -8200,7 +8200,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>613</v>
       </c>
@@ -8235,7 +8235,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>619</v>
       </c>
@@ -8270,7 +8270,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>624</v>
       </c>
@@ -8305,7 +8305,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>630</v>
       </c>
@@ -8340,7 +8340,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>635</v>
       </c>
@@ -8404,13 +8404,13 @@
         <v>151</v>
       </c>
       <c r="J118" s="6" t="s">
-        <v>17</v>
+        <v>883</v>
       </c>
       <c r="K118" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>201</v>
       </c>
@@ -8445,7 +8445,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>645</v>
       </c>
@@ -8480,7 +8480,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>650</v>
       </c>
@@ -8515,7 +8515,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>655</v>
       </c>
@@ -8550,7 +8550,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>659</v>
       </c>
@@ -8585,7 +8585,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>664</v>
       </c>
@@ -8620,7 +8620,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>669</v>
       </c>
@@ -8655,7 +8655,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>673</v>
       </c>
@@ -8690,7 +8690,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>678</v>
       </c>
@@ -8719,13 +8719,13 @@
         <v>151</v>
       </c>
       <c r="J127" s="6" t="s">
-        <v>883</v>
+        <v>800</v>
       </c>
       <c r="K127" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>683</v>
       </c>
@@ -8760,7 +8760,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>689</v>
       </c>
@@ -8795,7 +8795,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>694</v>
       </c>
@@ -8830,7 +8830,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>700</v>
       </c>
@@ -8865,7 +8865,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>704</v>
       </c>
@@ -8900,7 +8900,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>710</v>
       </c>
@@ -8935,7 +8935,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>715</v>
       </c>
@@ -8970,7 +8970,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>720</v>
       </c>
@@ -9005,7 +9005,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>725</v>
       </c>
@@ -9040,7 +9040,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>729</v>
       </c>
@@ -9075,7 +9075,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>734</v>
       </c>
@@ -9110,7 +9110,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>739</v>
       </c>
@@ -9145,7 +9145,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>744</v>
       </c>
@@ -9180,7 +9180,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>749</v>
       </c>
@@ -9215,7 +9215,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>753</v>
       </c>
@@ -9250,7 +9250,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>758</v>
       </c>
@@ -9285,7 +9285,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>762</v>
       </c>
@@ -9320,7 +9320,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>767</v>
       </c>
@@ -9355,7 +9355,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>772</v>
       </c>
@@ -9390,7 +9390,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>777</v>
       </c>
@@ -9425,7 +9425,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>783</v>
       </c>
@@ -9460,7 +9460,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>789</v>
       </c>
@@ -9495,7 +9495,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>794</v>
       </c>
@@ -9531,17 +9531,33 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K150" xr:uid="{4DA12617-6B17-4A0E-9E79-EBA6E19B3138}"/>
+  <autoFilter ref="A1:K150" xr:uid="{4DA12617-6B17-4A0E-9E79-EBA6E19B3138}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="E 04"/>
+        <filter val="P 05"/>
+        <filter val="P 107"/>
+        <filter val="P 143"/>
+        <filter val="P 39"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="9">
+      <filters>
+        <filter val="NÃO"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K150">
     <sortCondition ref="B1:B150"/>
   </sortState>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="20" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="63" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D18A476-0271-4A84-BE9E-901865A86FD3}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AC157"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -9753,7 +9769,7 @@
       <c r="AB4" s="11"/>
       <c r="AC4" s="25"/>
     </row>
-    <row r="5" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="19" t="s">
         <v>96</v>
       </c>
@@ -9796,7 +9812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
         <v>103</v>
       </c>
@@ -9839,7 +9855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="19" t="s">
         <v>109</v>
       </c>
@@ -9882,7 +9898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="19" t="s">
         <v>114</v>
       </c>
@@ -9925,7 +9941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
         <v>120</v>
       </c>
@@ -9968,7 +9984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="19" t="s">
         <v>125</v>
       </c>
@@ -10011,7 +10027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="19" t="s">
         <v>135</v>
       </c>
@@ -10102,7 +10118,7 @@
         <v>5682</v>
       </c>
     </row>
-    <row r="12" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="19" t="s">
         <v>141</v>
       </c>
@@ -10145,7 +10161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
         <v>147</v>
       </c>
@@ -10188,7 +10204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="19" t="s">
         <v>159</v>
       </c>
@@ -10279,7 +10295,7 @@
         <v>5190</v>
       </c>
     </row>
-    <row r="15" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="19" t="s">
         <v>173</v>
       </c>
@@ -10322,7 +10338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="19" t="s">
         <v>180</v>
       </c>
@@ -10413,7 +10429,7 @@
         <v>5845</v>
       </c>
     </row>
-    <row r="17" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="19" t="s">
         <v>185</v>
       </c>
@@ -10456,7 +10472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="19" t="s">
         <v>190</v>
       </c>
@@ -10547,7 +10563,7 @@
         <v>3934</v>
       </c>
     </row>
-    <row r="19" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="19" t="s">
         <v>196</v>
       </c>
@@ -10638,7 +10654,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="20" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="19" t="s">
         <v>603</v>
       </c>
@@ -10729,7 +10745,7 @@
         <v>4245</v>
       </c>
     </row>
-    <row r="21" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="19" t="s">
         <v>609</v>
       </c>
@@ -10772,7 +10788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="19" t="s">
         <v>614</v>
       </c>
@@ -10863,7 +10879,7 @@
         <v>2038</v>
       </c>
     </row>
-    <row r="23" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="19" t="s">
         <v>620</v>
       </c>
@@ -10954,7 +10970,7 @@
         <v>7108</v>
       </c>
     </row>
-    <row r="24" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="19" t="s">
         <v>625</v>
       </c>
@@ -10997,7 +11013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="19" t="s">
         <v>631</v>
       </c>
@@ -11088,7 +11104,7 @@
         <v>4586</v>
       </c>
     </row>
-    <row r="26" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="19" t="s">
         <v>636</v>
       </c>
@@ -11131,7 +11147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="19" t="s">
         <v>641</v>
       </c>
@@ -11174,7 +11190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="19" t="s">
         <v>202</v>
       </c>
@@ -11265,7 +11281,7 @@
         <v>9101</v>
       </c>
     </row>
-    <row r="29" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
         <v>646</v>
       </c>
@@ -11356,7 +11372,7 @@
         <v>2316</v>
       </c>
     </row>
-    <row r="30" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
         <v>651</v>
       </c>
@@ -11399,7 +11415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
         <v>656</v>
       </c>
@@ -11490,7 +11506,7 @@
         <v>1584</v>
       </c>
     </row>
-    <row r="32" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
         <v>660</v>
       </c>
@@ -11533,7 +11549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
         <v>665</v>
       </c>
@@ -11624,7 +11640,7 @@
         <v>4636</v>
       </c>
     </row>
-    <row r="34" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="19" t="s">
         <v>670</v>
       </c>
@@ -11667,7 +11683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
         <v>674</v>
       </c>
@@ -11720,40 +11736,88 @@
       <c r="C36" s="19" t="s">
         <v>680</v>
       </c>
-      <c r="D36" s="21"/>
-      <c r="E36" s="21"/>
-      <c r="F36" s="20"/>
+      <c r="D36" s="24">
+        <v>-5.4253080000000002</v>
+      </c>
+      <c r="E36" s="24">
+        <v>-38.218938999999999</v>
+      </c>
+      <c r="F36" s="20">
+        <v>46167</v>
+      </c>
       <c r="G36" s="20">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="H36" s="12"/>
-      <c r="I36" s="12"/>
-      <c r="J36" s="12"/>
-      <c r="K36" s="12"/>
-      <c r="L36" s="12"/>
-      <c r="M36" s="12"/>
-      <c r="N36" s="12"/>
-      <c r="O36" s="12"/>
-      <c r="P36" s="12"/>
-      <c r="Q36" s="12"/>
-      <c r="R36" s="12"/>
-      <c r="S36" s="12"/>
-      <c r="T36" s="12"/>
-      <c r="U36" s="12"/>
-      <c r="V36" s="12"/>
-      <c r="W36" s="12"/>
-      <c r="X36" s="12"/>
-      <c r="Y36" s="12"/>
-      <c r="Z36" s="12"/>
-      <c r="AA36" s="12"/>
-      <c r="AB36" s="12"/>
+        <v>46169</v>
+      </c>
+      <c r="H36" s="12">
+        <v>138</v>
+      </c>
+      <c r="I36" s="12">
+        <v>1469</v>
+      </c>
+      <c r="J36" s="12">
+        <v>42</v>
+      </c>
+      <c r="K36" s="12">
+        <v>235</v>
+      </c>
+      <c r="L36" s="12">
+        <v>26</v>
+      </c>
+      <c r="M36" s="12">
+        <v>23</v>
+      </c>
+      <c r="N36" s="12">
+        <v>0</v>
+      </c>
+      <c r="O36" s="12">
+        <v>0</v>
+      </c>
+      <c r="P36" s="12">
+        <v>3</v>
+      </c>
+      <c r="Q36" s="12">
+        <v>4</v>
+      </c>
+      <c r="R36" s="12">
+        <v>0</v>
+      </c>
+      <c r="S36" s="12">
+        <v>0</v>
+      </c>
+      <c r="T36" s="12">
+        <v>9</v>
+      </c>
+      <c r="U36" s="12">
+        <v>0</v>
+      </c>
+      <c r="V36" s="12">
+        <v>0</v>
+      </c>
+      <c r="W36" s="12">
+        <v>0</v>
+      </c>
+      <c r="X36" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="12">
+        <v>4</v>
+      </c>
+      <c r="AA36" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB36" s="12">
+        <v>0</v>
+      </c>
       <c r="AC36" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1953</v>
+      </c>
+    </row>
+    <row r="37" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
         <v>684</v>
       </c>
@@ -11796,7 +11860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="19" t="s">
         <v>690</v>
       </c>
@@ -11839,7 +11903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="19" t="s">
         <v>695</v>
       </c>
@@ -11882,7 +11946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="19" t="s">
         <v>701</v>
       </c>
@@ -11925,7 +11989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="19" t="s">
         <v>705</v>
       </c>
@@ -11968,7 +12032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="19" t="s">
         <v>711</v>
       </c>
@@ -12059,7 +12123,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="43" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="19" t="s">
         <v>716</v>
       </c>
@@ -12102,7 +12166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="19" t="s">
         <v>721</v>
       </c>
@@ -12145,7 +12209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="19" t="s">
         <v>726</v>
       </c>
@@ -12236,7 +12300,7 @@
         <v>7959</v>
       </c>
     </row>
-    <row r="46" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="19" t="s">
         <v>730</v>
       </c>
@@ -12279,7 +12343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="19" t="s">
         <v>735</v>
       </c>
@@ -12370,7 +12434,7 @@
         <v>2429</v>
       </c>
     </row>
-    <row r="48" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="19" t="s">
         <v>740</v>
       </c>
@@ -12461,7 +12525,7 @@
         <v>5649</v>
       </c>
     </row>
-    <row r="49" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="19" t="s">
         <v>745</v>
       </c>
@@ -12552,7 +12616,7 @@
         <v>6660</v>
       </c>
     </row>
-    <row r="50" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="19" t="s">
         <v>750</v>
       </c>
@@ -12643,7 +12707,7 @@
         <v>2483</v>
       </c>
     </row>
-    <row r="51" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="19" t="s">
         <v>754</v>
       </c>
@@ -12734,7 +12798,7 @@
         <v>4263</v>
       </c>
     </row>
-    <row r="52" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="19" t="s">
         <v>759</v>
       </c>
@@ -12777,7 +12841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="19" t="s">
         <v>763</v>
       </c>
@@ -12820,7 +12884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="19" t="s">
         <v>768</v>
       </c>
@@ -12911,7 +12975,7 @@
         <v>1560</v>
       </c>
     </row>
-    <row r="55" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="19" t="s">
         <v>773</v>
       </c>
@@ -13002,7 +13066,7 @@
         <v>1864</v>
       </c>
     </row>
-    <row r="56" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="19" t="s">
         <v>778</v>
       </c>
@@ -13045,7 +13109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="19" t="s">
         <v>784</v>
       </c>
@@ -13136,7 +13200,7 @@
         <v>2952</v>
       </c>
     </row>
-    <row r="58" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="19" t="s">
         <v>790</v>
       </c>
@@ -13227,7 +13291,7 @@
         <v>1414</v>
       </c>
     </row>
-    <row r="59" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="19" t="s">
         <v>795</v>
       </c>
@@ -13318,7 +13382,7 @@
         <v>3999</v>
       </c>
     </row>
-    <row r="60" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="19" t="s">
         <v>315</v>
       </c>
@@ -13409,7 +13473,7 @@
         <v>2567</v>
       </c>
     </row>
-    <row r="61" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="19" t="s">
         <v>320</v>
       </c>
@@ -13452,7 +13516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="19" t="s">
         <v>325</v>
       </c>
@@ -13495,7 +13559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="19" t="s">
         <v>330</v>
       </c>
@@ -13586,7 +13650,7 @@
         <v>2906</v>
       </c>
     </row>
-    <row r="64" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="19" t="s">
         <v>335</v>
       </c>
@@ -13629,7 +13693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="19" t="s">
         <v>341</v>
       </c>
@@ -13672,7 +13736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="19" t="s">
         <v>130</v>
       </c>
@@ -13763,7 +13827,7 @@
         <v>5492</v>
       </c>
     </row>
-    <row r="67" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="19" t="s">
         <v>347</v>
       </c>
@@ -13864,40 +13928,88 @@
       <c r="C68" s="19" t="s">
         <v>353</v>
       </c>
-      <c r="D68" s="21"/>
-      <c r="E68" s="21"/>
-      <c r="F68" s="20"/>
+      <c r="D68" s="24">
+        <v>-5.2215020000000001</v>
+      </c>
+      <c r="E68" s="24">
+        <v>-37.892071000000001</v>
+      </c>
+      <c r="F68" s="20">
+        <v>46167</v>
+      </c>
       <c r="G68" s="20">
         <f t="shared" si="0"/>
+        <v>46169</v>
+      </c>
+      <c r="H68" s="12">
+        <v>333</v>
+      </c>
+      <c r="I68" s="12">
+        <v>493</v>
+      </c>
+      <c r="J68" s="12">
+        <v>8</v>
+      </c>
+      <c r="K68" s="12">
+        <v>49</v>
+      </c>
+      <c r="L68" s="12">
+        <v>31</v>
+      </c>
+      <c r="M68" s="12">
         <v>2</v>
       </c>
-      <c r="H68" s="12"/>
-      <c r="I68" s="12"/>
-      <c r="J68" s="12"/>
-      <c r="K68" s="12"/>
-      <c r="L68" s="12"/>
-      <c r="M68" s="12"/>
-      <c r="N68" s="12"/>
-      <c r="O68" s="12"/>
-      <c r="P68" s="12"/>
-      <c r="Q68" s="12"/>
-      <c r="R68" s="12"/>
-      <c r="S68" s="12"/>
-      <c r="T68" s="12"/>
-      <c r="U68" s="12"/>
-      <c r="V68" s="12"/>
-      <c r="W68" s="12"/>
-      <c r="X68" s="12"/>
-      <c r="Y68" s="12"/>
-      <c r="Z68" s="12"/>
-      <c r="AA68" s="12"/>
-      <c r="AB68" s="12"/>
+      <c r="N68" s="12">
+        <v>4</v>
+      </c>
+      <c r="O68" s="12">
+        <v>1</v>
+      </c>
+      <c r="P68" s="12">
+        <v>2</v>
+      </c>
+      <c r="Q68" s="12">
+        <v>3</v>
+      </c>
+      <c r="R68" s="12">
+        <v>4</v>
+      </c>
+      <c r="S68" s="12">
+        <v>0</v>
+      </c>
+      <c r="T68" s="12">
+        <v>14</v>
+      </c>
+      <c r="U68" s="12">
+        <v>0</v>
+      </c>
+      <c r="V68" s="12">
+        <v>0</v>
+      </c>
+      <c r="W68" s="12">
+        <v>0</v>
+      </c>
+      <c r="X68" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z68" s="12">
+        <v>3</v>
+      </c>
+      <c r="AA68" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB68" s="12">
+        <v>4</v>
+      </c>
       <c r="AC68" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="69" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="19" t="s">
         <v>357</v>
       </c>
@@ -13988,7 +14100,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="70" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="19" t="s">
         <v>362</v>
       </c>
@@ -14079,7 +14191,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="71" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="19" t="s">
         <v>368</v>
       </c>
@@ -14122,7 +14234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="19" t="s">
         <v>374</v>
       </c>
@@ -14165,7 +14277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="19" t="s">
         <v>376</v>
       </c>
@@ -14208,7 +14320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="19" t="s">
         <v>382</v>
       </c>
@@ -14251,7 +14363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="19" t="s">
         <v>387</v>
       </c>
@@ -14294,7 +14406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="19" t="s">
         <v>393</v>
       </c>
@@ -14337,7 +14449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="19" t="s">
         <v>399</v>
       </c>
@@ -14380,7 +14492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="19" t="s">
         <v>404</v>
       </c>
@@ -14423,7 +14535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="19" t="s">
         <v>410</v>
       </c>
@@ -14466,7 +14578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="19" t="s">
         <v>416</v>
       </c>
@@ -14557,7 +14669,7 @@
         <v>4247</v>
       </c>
     </row>
-    <row r="81" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="19" t="s">
         <v>421</v>
       </c>
@@ -14648,7 +14760,7 @@
         <v>4161</v>
       </c>
     </row>
-    <row r="82" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="19" t="s">
         <v>427</v>
       </c>
@@ -14691,7 +14803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="19" t="s">
         <v>432</v>
       </c>
@@ -14782,7 +14894,7 @@
         <v>6031</v>
       </c>
     </row>
-    <row r="84" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="19" t="s">
         <v>436</v>
       </c>
@@ -14835,40 +14947,88 @@
       <c r="C85" s="19" t="s">
         <v>443</v>
       </c>
-      <c r="D85" s="21"/>
-      <c r="E85" s="21"/>
-      <c r="F85" s="20"/>
+      <c r="D85" s="24">
+        <v>-5.2738310000000004</v>
+      </c>
+      <c r="E85" s="24">
+        <v>-38.108522000000001</v>
+      </c>
+      <c r="F85" s="20">
+        <v>46167</v>
+      </c>
       <c r="G85" s="20">
         <f t="shared" si="5"/>
-        <v>2</v>
-      </c>
-      <c r="H85" s="12"/>
-      <c r="I85" s="12"/>
-      <c r="J85" s="12"/>
-      <c r="K85" s="12"/>
-      <c r="L85" s="12"/>
-      <c r="M85" s="12"/>
-      <c r="N85" s="12"/>
-      <c r="O85" s="12"/>
-      <c r="P85" s="12"/>
-      <c r="Q85" s="12"/>
-      <c r="R85" s="12"/>
-      <c r="S85" s="12"/>
-      <c r="T85" s="12"/>
-      <c r="U85" s="12"/>
-      <c r="V85" s="12"/>
-      <c r="W85" s="12"/>
-      <c r="X85" s="12"/>
-      <c r="Y85" s="12"/>
-      <c r="Z85" s="12"/>
-      <c r="AA85" s="12"/>
-      <c r="AB85" s="12"/>
+        <v>46169</v>
+      </c>
+      <c r="H85" s="12">
+        <v>1830</v>
+      </c>
+      <c r="I85" s="12">
+        <v>839</v>
+      </c>
+      <c r="J85" s="12">
+        <v>24</v>
+      </c>
+      <c r="K85" s="12">
+        <v>111</v>
+      </c>
+      <c r="L85" s="12">
+        <v>43</v>
+      </c>
+      <c r="M85" s="12">
+        <v>13</v>
+      </c>
+      <c r="N85" s="12">
+        <v>4</v>
+      </c>
+      <c r="O85" s="12">
+        <v>1</v>
+      </c>
+      <c r="P85" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="12">
+        <v>1</v>
+      </c>
+      <c r="R85" s="12">
+        <v>0</v>
+      </c>
+      <c r="S85" s="12">
+        <v>1</v>
+      </c>
+      <c r="T85" s="12">
+        <v>31</v>
+      </c>
+      <c r="U85" s="12">
+        <v>0</v>
+      </c>
+      <c r="V85" s="12">
+        <v>0</v>
+      </c>
+      <c r="W85" s="12">
+        <v>0</v>
+      </c>
+      <c r="X85" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y85" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z85" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA85" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB85" s="12">
+        <v>0</v>
+      </c>
       <c r="AC85" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>2898</v>
+      </c>
+    </row>
+    <row r="86" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="19" t="s">
         <v>447</v>
       </c>
@@ -14911,7 +15071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="19" t="s">
         <v>452</v>
       </c>
@@ -14954,7 +15114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="19" t="s">
         <v>457</v>
       </c>
@@ -15045,7 +15205,7 @@
         <v>6697</v>
       </c>
     </row>
-    <row r="89" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="19" t="s">
         <v>462</v>
       </c>
@@ -15088,7 +15248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="19" t="s">
         <v>467</v>
       </c>
@@ -15179,7 +15339,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="91" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="19" t="s">
         <v>471</v>
       </c>
@@ -15222,7 +15382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="19" t="s">
         <v>477</v>
       </c>
@@ -15313,7 +15473,7 @@
         <v>2842</v>
       </c>
     </row>
-    <row r="93" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="19" t="s">
         <v>481</v>
       </c>
@@ -15404,7 +15564,7 @@
         <v>988</v>
       </c>
     </row>
-    <row r="94" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="19" t="s">
         <v>153</v>
       </c>
@@ -15495,7 +15655,7 @@
         <v>2883</v>
       </c>
     </row>
-    <row r="95" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="19" t="s">
         <v>487</v>
       </c>
@@ -15586,7 +15746,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="96" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="19" t="s">
         <v>493</v>
       </c>
@@ -15677,7 +15837,7 @@
         <v>3307</v>
       </c>
     </row>
-    <row r="97" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="19" t="s">
         <v>498</v>
       </c>
@@ -15778,37 +15938,85 @@
       <c r="C98" s="19" t="s">
         <v>503</v>
       </c>
-      <c r="D98" s="21"/>
-      <c r="E98" s="21"/>
-      <c r="F98" s="20"/>
+      <c r="D98" s="24">
+        <v>-5.0848469999999999</v>
+      </c>
+      <c r="E98" s="24">
+        <v>-38.009757</v>
+      </c>
+      <c r="F98" s="20">
+        <v>46167</v>
+      </c>
       <c r="G98" s="20">
         <f t="shared" si="5"/>
+        <v>46169</v>
+      </c>
+      <c r="H98" s="12">
+        <v>1367</v>
+      </c>
+      <c r="I98" s="12">
+        <v>1757</v>
+      </c>
+      <c r="J98" s="12">
+        <v>69</v>
+      </c>
+      <c r="K98" s="12">
+        <v>232</v>
+      </c>
+      <c r="L98" s="12">
+        <v>50</v>
+      </c>
+      <c r="M98" s="12">
+        <v>15</v>
+      </c>
+      <c r="N98" s="12">
+        <v>23</v>
+      </c>
+      <c r="O98" s="12">
+        <v>5</v>
+      </c>
+      <c r="P98" s="12">
         <v>2</v>
       </c>
-      <c r="H98" s="12"/>
-      <c r="I98" s="12"/>
-      <c r="J98" s="12"/>
-      <c r="K98" s="12"/>
-      <c r="L98" s="12"/>
-      <c r="M98" s="12"/>
-      <c r="N98" s="12"/>
-      <c r="O98" s="12"/>
-      <c r="P98" s="12"/>
-      <c r="Q98" s="12"/>
-      <c r="R98" s="12"/>
-      <c r="S98" s="12"/>
-      <c r="T98" s="12"/>
-      <c r="U98" s="12"/>
-      <c r="V98" s="12"/>
-      <c r="W98" s="12"/>
-      <c r="X98" s="12"/>
-      <c r="Y98" s="12"/>
-      <c r="Z98" s="12"/>
-      <c r="AA98" s="12"/>
-      <c r="AB98" s="12"/>
+      <c r="Q98" s="12">
+        <v>8</v>
+      </c>
+      <c r="R98" s="12">
+        <v>5</v>
+      </c>
+      <c r="S98" s="12">
+        <v>2</v>
+      </c>
+      <c r="T98" s="12">
+        <v>39</v>
+      </c>
+      <c r="U98" s="12">
+        <v>0</v>
+      </c>
+      <c r="V98" s="12">
+        <v>1</v>
+      </c>
+      <c r="W98" s="12">
+        <v>6</v>
+      </c>
+      <c r="X98" s="12">
+        <v>1</v>
+      </c>
+      <c r="Y98" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z98" s="12">
+        <v>3</v>
+      </c>
+      <c r="AA98" s="12">
+        <v>5</v>
+      </c>
+      <c r="AB98" s="12">
+        <v>0</v>
+      </c>
       <c r="AC98" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3590</v>
       </c>
     </row>
     <row r="99" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -15821,40 +16029,88 @@
       <c r="C99" s="19" t="s">
         <v>508</v>
       </c>
-      <c r="D99" s="21"/>
-      <c r="E99" s="21"/>
-      <c r="F99" s="20"/>
+      <c r="D99" s="24">
+        <v>-5.2461500000000001</v>
+      </c>
+      <c r="E99" s="24">
+        <v>-38.214409000000003</v>
+      </c>
+      <c r="F99" s="20">
+        <v>46167</v>
+      </c>
       <c r="G99" s="20">
         <f t="shared" si="5"/>
-        <v>2</v>
-      </c>
-      <c r="H99" s="12"/>
-      <c r="I99" s="12"/>
-      <c r="J99" s="12"/>
-      <c r="K99" s="12"/>
-      <c r="L99" s="12"/>
-      <c r="M99" s="12"/>
-      <c r="N99" s="12"/>
-      <c r="O99" s="12"/>
-      <c r="P99" s="12"/>
-      <c r="Q99" s="12"/>
-      <c r="R99" s="12"/>
-      <c r="S99" s="12"/>
-      <c r="T99" s="12"/>
-      <c r="U99" s="12"/>
-      <c r="V99" s="12"/>
-      <c r="W99" s="12"/>
-      <c r="X99" s="12"/>
-      <c r="Y99" s="12"/>
-      <c r="Z99" s="12"/>
-      <c r="AA99" s="12"/>
-      <c r="AB99" s="12"/>
+        <v>46169</v>
+      </c>
+      <c r="H99" s="12">
+        <v>1176</v>
+      </c>
+      <c r="I99" s="12">
+        <v>920</v>
+      </c>
+      <c r="J99" s="12">
+        <v>25</v>
+      </c>
+      <c r="K99" s="12">
+        <v>132</v>
+      </c>
+      <c r="L99" s="12">
+        <v>40</v>
+      </c>
+      <c r="M99" s="12">
+        <v>1</v>
+      </c>
+      <c r="N99" s="12">
+        <v>4</v>
+      </c>
+      <c r="O99" s="12">
+        <v>1</v>
+      </c>
+      <c r="P99" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="12">
+        <v>0</v>
+      </c>
+      <c r="R99" s="12">
+        <v>1</v>
+      </c>
+      <c r="S99" s="12">
+        <v>0</v>
+      </c>
+      <c r="T99" s="12">
+        <v>31</v>
+      </c>
+      <c r="U99" s="12">
+        <v>0</v>
+      </c>
+      <c r="V99" s="12">
+        <v>0</v>
+      </c>
+      <c r="W99" s="12">
+        <v>0</v>
+      </c>
+      <c r="X99" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y99" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z99" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA99" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB99" s="12">
+        <v>0</v>
+      </c>
       <c r="AC99" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>2331</v>
+      </c>
+    </row>
+    <row r="100" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="19" t="s">
         <v>512</v>
       </c>
@@ -15897,7 +16153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="19" t="s">
         <v>517</v>
       </c>
@@ -15940,7 +16196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="19" t="s">
         <v>523</v>
       </c>
@@ -15983,7 +16239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="19" t="s">
         <v>164</v>
       </c>
@@ -16074,7 +16330,7 @@
         <v>2499</v>
       </c>
     </row>
-    <row r="104" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="19" t="s">
         <v>529</v>
       </c>
@@ -16165,7 +16421,7 @@
         <v>2533</v>
       </c>
     </row>
-    <row r="105" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="19" t="s">
         <v>535</v>
       </c>
@@ -16256,7 +16512,7 @@
         <v>2124</v>
       </c>
     </row>
-    <row r="106" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="19" t="s">
         <v>541</v>
       </c>
@@ -16299,7 +16555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="19" t="s">
         <v>546</v>
       </c>
@@ -16342,7 +16598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="19" t="s">
         <v>170</v>
       </c>
@@ -16433,7 +16689,7 @@
         <v>1973</v>
       </c>
     </row>
-    <row r="109" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="19" t="s">
         <v>551</v>
       </c>
@@ -16476,7 +16732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="19" t="s">
         <v>555</v>
       </c>
@@ -16567,7 +16823,7 @@
         <v>5171</v>
       </c>
     </row>
-    <row r="111" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="19" t="s">
         <v>561</v>
       </c>
@@ -16658,7 +16914,7 @@
         <v>5543</v>
       </c>
     </row>
-    <row r="112" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="19" t="s">
         <v>566</v>
       </c>
@@ -16749,7 +17005,7 @@
         <v>4135</v>
       </c>
     </row>
-    <row r="113" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="19" t="s">
         <v>571</v>
       </c>
@@ -16792,7 +17048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="19" t="s">
         <v>577</v>
       </c>
@@ -16883,7 +17139,7 @@
         <v>2947</v>
       </c>
     </row>
-    <row r="115" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="19" t="s">
         <v>582</v>
       </c>
@@ -16926,7 +17182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="19" t="s">
         <v>588</v>
       </c>
@@ -16969,7 +17225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="19" t="s">
         <v>593</v>
       </c>
@@ -17012,7 +17268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="19" t="s">
         <v>598</v>
       </c>
@@ -17055,7 +17311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="19" t="s">
         <v>11</v>
       </c>
@@ -17146,7 +17402,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="120" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="19" t="s">
         <v>20</v>
       </c>
@@ -17237,7 +17493,7 @@
         <v>1773</v>
       </c>
     </row>
-    <row r="121" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="19" t="s">
         <v>24</v>
       </c>
@@ -17280,7 +17536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="19" t="s">
         <v>30</v>
       </c>
@@ -17371,7 +17627,7 @@
         <v>4915</v>
       </c>
     </row>
-    <row r="123" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="19" t="s">
         <v>35</v>
       </c>
@@ -17414,7 +17670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="19" t="s">
         <v>41</v>
       </c>
@@ -17457,7 +17713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="19" t="s">
         <v>63</v>
       </c>
@@ -17500,7 +17756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="19" t="s">
         <v>69</v>
       </c>
@@ -17543,7 +17799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="19" t="s">
         <v>213</v>
       </c>
@@ -17586,7 +17842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="19" t="s">
         <v>265</v>
       </c>
@@ -17629,7 +17885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="19" t="s">
         <v>271</v>
       </c>
@@ -17672,7 +17928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="19" t="s">
         <v>277</v>
       </c>
@@ -17763,7 +18019,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="131" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="19" t="s">
         <v>282</v>
       </c>
@@ -17854,7 +18110,7 @@
         <v>1984</v>
       </c>
     </row>
-    <row r="132" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="19" t="s">
         <v>81</v>
       </c>
@@ -17945,7 +18201,7 @@
         <v>2597</v>
       </c>
     </row>
-    <row r="133" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="19" t="s">
         <v>86</v>
       </c>
@@ -18036,7 +18292,7 @@
         <v>1733</v>
       </c>
     </row>
-    <row r="134" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="19" t="s">
         <v>92</v>
       </c>
@@ -18127,7 +18383,7 @@
         <v>1724</v>
       </c>
     </row>
-    <row r="135" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="19" t="s">
         <v>287</v>
       </c>
@@ -18170,7 +18426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="19" t="s">
         <v>292</v>
       </c>
@@ -18213,7 +18469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="19" t="s">
         <v>47</v>
       </c>
@@ -18256,7 +18512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="19" t="s">
         <v>53</v>
       </c>
@@ -18299,7 +18555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="19" t="s">
         <v>57</v>
       </c>
@@ -18390,7 +18646,7 @@
         <v>5263</v>
       </c>
     </row>
-    <row r="140" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="19" t="s">
         <v>75</v>
       </c>
@@ -18481,7 +18737,7 @@
         <v>1839</v>
       </c>
     </row>
-    <row r="141" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="19" t="s">
         <v>207</v>
       </c>
@@ -18572,7 +18828,7 @@
         <v>2840</v>
       </c>
     </row>
-    <row r="142" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="19" t="s">
         <v>218</v>
       </c>
@@ -18663,7 +18919,7 @@
         <v>1451</v>
       </c>
     </row>
-    <row r="143" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="19" t="s">
         <v>223</v>
       </c>
@@ -18706,7 +18962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="19" t="s">
         <v>228</v>
       </c>
@@ -18797,7 +19053,7 @@
         <v>2854</v>
       </c>
     </row>
-    <row r="145" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="19" t="s">
         <v>234</v>
       </c>
@@ -18840,7 +19096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="19" t="s">
         <v>240</v>
       </c>
@@ -18883,7 +19139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="19" t="s">
         <v>246</v>
       </c>
@@ -18974,7 +19230,7 @@
         <v>2936</v>
       </c>
     </row>
-    <row r="148" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="19" t="s">
         <v>251</v>
       </c>
@@ -19017,7 +19273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="19" t="s">
         <v>256</v>
       </c>
@@ -19060,7 +19316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="19" t="s">
         <v>261</v>
       </c>
@@ -19103,7 +19359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="19" t="s">
         <v>298</v>
       </c>
@@ -19146,7 +19402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="19" t="s">
         <v>303</v>
       </c>
@@ -19237,7 +19493,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="153" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="19" t="s">
         <v>310</v>
       </c>
@@ -19300,6 +19556,15 @@
     </row>
   </sheetData>
   <autoFilter ref="A4:AC153" xr:uid="{1D18A476-0271-4A84-BE9E-901865A86FD3}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="P 112"/>
+        <filter val="P 144"/>
+        <filter val="P 163"/>
+        <filter val="P 164"/>
+        <filter val="P 57"/>
+      </filters>
+    </filterColumn>
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="9">

--- a/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
+++ b/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\5- MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA75CBF8-AC0F-40CA-905F-C203435C699A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D4D8B84-CE14-4399-AEFA-07E302F63EA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
   </bookViews>
@@ -4385,7 +4385,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>23</v>
       </c>
@@ -5610,7 +5610,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>108</v>
       </c>
@@ -5890,7 +5890,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>334</v>
       </c>
@@ -5898,10 +5898,10 @@
         <v>335</v>
       </c>
       <c r="C47" s="5">
-        <v>-4.7222119999999999</v>
+        <v>-4.720345</v>
       </c>
       <c r="D47" s="5">
-        <v>-37.556274999999999</v>
+        <v>-37.548856999999998</v>
       </c>
       <c r="E47" s="4" t="s">
         <v>336</v>
@@ -5925,7 +5925,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>340</v>
       </c>
@@ -6205,7 +6205,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="56" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>140</v>
       </c>
@@ -6213,10 +6213,10 @@
         <v>141</v>
       </c>
       <c r="C56" s="5">
-        <v>-4.5752660000000001</v>
+        <v>-4.5740670000000003</v>
       </c>
       <c r="D56" s="5">
-        <v>-37.733165999999997</v>
+        <v>-37.736370999999998</v>
       </c>
       <c r="E56" s="4" t="s">
         <v>142</v>
@@ -6695,7 +6695,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>435</v>
       </c>
@@ -7500,7 +7500,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="93" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>540</v>
       </c>
@@ -7508,10 +7508,10 @@
         <v>541</v>
       </c>
       <c r="C93" s="5">
-        <v>-4.5725499999999997</v>
+        <v>-4.5701270000000003</v>
       </c>
       <c r="D93" s="5">
-        <v>-37.736899999999999</v>
+        <v>-37.734988999999999</v>
       </c>
       <c r="E93" s="4" t="s">
         <v>488</v>
@@ -7885,7 +7885,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="104" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>592</v>
       </c>
@@ -7893,10 +7893,10 @@
         <v>593</v>
       </c>
       <c r="C104" s="5">
-        <v>-4.5797999999999996</v>
+        <v>-4.5799000000000003</v>
       </c>
       <c r="D104" s="5">
-        <v>-37.851931</v>
+        <v>-37.851894999999999</v>
       </c>
       <c r="E104" s="4" t="s">
         <v>142</v>
@@ -8375,7 +8375,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>640</v>
       </c>
@@ -8620,7 +8620,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="125" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>669</v>
       </c>
@@ -8628,10 +8628,10 @@
         <v>670</v>
       </c>
       <c r="C125" s="5">
-        <v>-4.5807399999999996</v>
+        <v>-4.5809509999999998</v>
       </c>
       <c r="D125" s="5">
-        <v>-37.849532000000004</v>
+        <v>-37.849564000000001</v>
       </c>
       <c r="E125" s="4" t="s">
         <v>25</v>
@@ -9534,11 +9534,11 @@
   <autoFilter ref="A1:K150" xr:uid="{4DA12617-6B17-4A0E-9E79-EBA6E19B3138}">
     <filterColumn colId="1">
       <filters>
-        <filter val="E 04"/>
-        <filter val="P 05"/>
-        <filter val="P 107"/>
-        <filter val="P 143"/>
-        <filter val="P 39"/>
+        <filter val="P 106"/>
+        <filter val="P 12"/>
+        <filter val="P 181"/>
+        <filter val="P 198"/>
+        <filter val="P 55"/>
       </filters>
     </filterColumn>
     <filterColumn colId="9">

--- a/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
+++ b/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\5- MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D4D8B84-CE14-4399-AEFA-07E302F63EA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18EF208B-5E45-458E-8EF8-E415C574F9D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
   </bookViews>
   <sheets>
     <sheet name="LISTA DE PONTOS" sheetId="1" r:id="rId1"/>
@@ -4260,7 +4260,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DA12617-6B17-4A0E-9E79-EBA6E19B3138}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K150"/>
@@ -4315,7 +4315,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -4350,7 +4350,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>19</v>
       </c>
@@ -4385,7 +4385,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>23</v>
       </c>
@@ -4414,13 +4414,13 @@
         <v>16</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>883</v>
+        <v>800</v>
       </c>
       <c r="K4" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>29</v>
       </c>
@@ -4455,7 +4455,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>34</v>
       </c>
@@ -4490,7 +4490,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>40</v>
       </c>
@@ -4525,7 +4525,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>46</v>
       </c>
@@ -4560,7 +4560,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>52</v>
       </c>
@@ -4595,7 +4595,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>56</v>
       </c>
@@ -4630,7 +4630,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>62</v>
       </c>
@@ -4665,7 +4665,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>68</v>
       </c>
@@ -4700,7 +4700,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>74</v>
       </c>
@@ -4735,7 +4735,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>206</v>
       </c>
@@ -4770,7 +4770,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>212</v>
       </c>
@@ -4805,7 +4805,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>217</v>
       </c>
@@ -4840,7 +4840,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>222</v>
       </c>
@@ -4875,7 +4875,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>227</v>
       </c>
@@ -4910,7 +4910,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>233</v>
       </c>
@@ -4945,7 +4945,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>239</v>
       </c>
@@ -4980,7 +4980,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>245</v>
       </c>
@@ -5015,7 +5015,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>250</v>
       </c>
@@ -5050,7 +5050,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>255</v>
       </c>
@@ -5085,7 +5085,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>260</v>
       </c>
@@ -5120,7 +5120,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>264</v>
       </c>
@@ -5155,7 +5155,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>270</v>
       </c>
@@ -5190,7 +5190,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>276</v>
       </c>
@@ -5225,7 +5225,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>281</v>
       </c>
@@ -5260,7 +5260,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>80</v>
       </c>
@@ -5295,7 +5295,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>85</v>
       </c>
@@ -5330,7 +5330,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>91</v>
       </c>
@@ -5365,7 +5365,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>286</v>
       </c>
@@ -5400,7 +5400,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>291</v>
       </c>
@@ -5435,7 +5435,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="34" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>297</v>
       </c>
@@ -5470,7 +5470,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="35" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>302</v>
       </c>
@@ -5505,7 +5505,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>309</v>
       </c>
@@ -5540,7 +5540,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>95</v>
       </c>
@@ -5575,7 +5575,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>102</v>
       </c>
@@ -5610,7 +5610,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>108</v>
       </c>
@@ -5639,13 +5639,13 @@
         <v>101</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>883</v>
+        <v>800</v>
       </c>
       <c r="K39" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>113</v>
       </c>
@@ -5680,7 +5680,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>119</v>
       </c>
@@ -5715,7 +5715,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>124</v>
       </c>
@@ -5750,7 +5750,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="43" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>314</v>
       </c>
@@ -5785,7 +5785,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>319</v>
       </c>
@@ -5820,7 +5820,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>324</v>
       </c>
@@ -5855,7 +5855,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="46" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>329</v>
       </c>
@@ -5919,13 +5919,13 @@
         <v>151</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>17</v>
+        <v>883</v>
       </c>
       <c r="K47" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>340</v>
       </c>
@@ -5954,13 +5954,13 @@
         <v>101</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>883</v>
+        <v>800</v>
       </c>
       <c r="K48" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>129</v>
       </c>
@@ -5995,7 +5995,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>134</v>
       </c>
@@ -6030,7 +6030,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>346</v>
       </c>
@@ -6065,7 +6065,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="52" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>350</v>
       </c>
@@ -6100,7 +6100,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>356</v>
       </c>
@@ -6135,7 +6135,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>361</v>
       </c>
@@ -6170,7 +6170,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>367</v>
       </c>
@@ -6234,13 +6234,13 @@
         <v>101</v>
       </c>
       <c r="J56" s="6" t="s">
-        <v>17</v>
+        <v>883</v>
       </c>
       <c r="K56" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>373</v>
       </c>
@@ -6275,7 +6275,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>375</v>
       </c>
@@ -6310,7 +6310,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>146</v>
       </c>
@@ -6345,7 +6345,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>381</v>
       </c>
@@ -6380,7 +6380,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>386</v>
       </c>
@@ -6415,7 +6415,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="62" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>392</v>
       </c>
@@ -6450,7 +6450,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="63" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>398</v>
       </c>
@@ -6485,7 +6485,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="64" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>403</v>
       </c>
@@ -6520,7 +6520,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="65" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>409</v>
       </c>
@@ -6555,7 +6555,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="66" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>415</v>
       </c>
@@ -6590,7 +6590,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="67" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>420</v>
       </c>
@@ -6625,7 +6625,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>426</v>
       </c>
@@ -6660,7 +6660,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>431</v>
       </c>
@@ -6695,7 +6695,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>435</v>
       </c>
@@ -6724,13 +6724,13 @@
         <v>151</v>
       </c>
       <c r="J70" s="6" t="s">
-        <v>883</v>
+        <v>800</v>
       </c>
       <c r="K70" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="71" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>440</v>
       </c>
@@ -6765,7 +6765,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="72" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>446</v>
       </c>
@@ -6800,7 +6800,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="73" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>451</v>
       </c>
@@ -6835,7 +6835,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="74" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>456</v>
       </c>
@@ -6870,7 +6870,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="75" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>461</v>
       </c>
@@ -6905,7 +6905,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="76" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>466</v>
       </c>
@@ -6940,7 +6940,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>470</v>
       </c>
@@ -6975,7 +6975,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>476</v>
       </c>
@@ -7010,7 +7010,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>480</v>
       </c>
@@ -7045,7 +7045,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="80" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>152</v>
       </c>
@@ -7080,7 +7080,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="81" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>486</v>
       </c>
@@ -7115,7 +7115,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="82" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>492</v>
       </c>
@@ -7150,7 +7150,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="83" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>497</v>
       </c>
@@ -7185,7 +7185,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="84" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>500</v>
       </c>
@@ -7220,7 +7220,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="85" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>506</v>
       </c>
@@ -7255,7 +7255,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="86" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>158</v>
       </c>
@@ -7290,7 +7290,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>511</v>
       </c>
@@ -7325,7 +7325,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="88" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>516</v>
       </c>
@@ -7360,7 +7360,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="89" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>522</v>
       </c>
@@ -7395,7 +7395,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="90" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>163</v>
       </c>
@@ -7430,7 +7430,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="91" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>528</v>
       </c>
@@ -7465,7 +7465,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="92" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>534</v>
       </c>
@@ -7529,13 +7529,13 @@
         <v>101</v>
       </c>
       <c r="J93" s="6" t="s">
-        <v>17</v>
+        <v>883</v>
       </c>
       <c r="K93" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="94" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>545</v>
       </c>
@@ -7570,7 +7570,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="95" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>169</v>
       </c>
@@ -7605,7 +7605,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="96" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>550</v>
       </c>
@@ -7640,7 +7640,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="97" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>554</v>
       </c>
@@ -7675,7 +7675,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="98" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>560</v>
       </c>
@@ -7710,7 +7710,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="99" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>565</v>
       </c>
@@ -7745,7 +7745,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="100" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>570</v>
       </c>
@@ -7780,7 +7780,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="101" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>576</v>
       </c>
@@ -7815,7 +7815,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="102" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>581</v>
       </c>
@@ -7850,7 +7850,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="103" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>587</v>
       </c>
@@ -7914,13 +7914,13 @@
         <v>101</v>
       </c>
       <c r="J104" s="6" t="s">
-        <v>17</v>
+        <v>883</v>
       </c>
       <c r="K104" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="105" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>597</v>
       </c>
@@ -7955,7 +7955,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="106" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>172</v>
       </c>
@@ -7990,7 +7990,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="107" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>179</v>
       </c>
@@ -8025,7 +8025,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="108" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>184</v>
       </c>
@@ -8060,7 +8060,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="109" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>189</v>
       </c>
@@ -8095,7 +8095,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="110" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>195</v>
       </c>
@@ -8130,7 +8130,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="111" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>602</v>
       </c>
@@ -8165,7 +8165,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="112" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>608</v>
       </c>
@@ -8200,7 +8200,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="113" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>613</v>
       </c>
@@ -8235,7 +8235,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="114" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>619</v>
       </c>
@@ -8270,7 +8270,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="115" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>624</v>
       </c>
@@ -8305,7 +8305,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="116" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>630</v>
       </c>
@@ -8340,7 +8340,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="117" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>635</v>
       </c>
@@ -8375,7 +8375,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="118" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>640</v>
       </c>
@@ -8404,13 +8404,13 @@
         <v>151</v>
       </c>
       <c r="J118" s="6" t="s">
-        <v>883</v>
+        <v>800</v>
       </c>
       <c r="K118" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="119" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>201</v>
       </c>
@@ -8445,7 +8445,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="120" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>645</v>
       </c>
@@ -8480,7 +8480,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="121" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>650</v>
       </c>
@@ -8515,7 +8515,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="122" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>655</v>
       </c>
@@ -8550,7 +8550,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="123" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>659</v>
       </c>
@@ -8585,7 +8585,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="124" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>664</v>
       </c>
@@ -8649,13 +8649,13 @@
         <v>101</v>
       </c>
       <c r="J125" s="6" t="s">
-        <v>17</v>
+        <v>883</v>
       </c>
       <c r="K125" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="126" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>673</v>
       </c>
@@ -8690,7 +8690,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="127" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>678</v>
       </c>
@@ -8725,7 +8725,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="128" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>683</v>
       </c>
@@ -8760,7 +8760,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="129" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>689</v>
       </c>
@@ -8795,7 +8795,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="130" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>694</v>
       </c>
@@ -8830,7 +8830,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="131" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>700</v>
       </c>
@@ -8865,7 +8865,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="132" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>704</v>
       </c>
@@ -8900,7 +8900,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="133" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>710</v>
       </c>
@@ -8935,7 +8935,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="134" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>715</v>
       </c>
@@ -8970,7 +8970,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="135" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>720</v>
       </c>
@@ -9005,7 +9005,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="136" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>725</v>
       </c>
@@ -9040,7 +9040,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="137" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>729</v>
       </c>
@@ -9075,7 +9075,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="138" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>734</v>
       </c>
@@ -9110,7 +9110,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="139" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>739</v>
       </c>
@@ -9145,7 +9145,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="140" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>744</v>
       </c>
@@ -9180,7 +9180,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="141" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>749</v>
       </c>
@@ -9215,7 +9215,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="142" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>753</v>
       </c>
@@ -9250,7 +9250,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="143" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>758</v>
       </c>
@@ -9285,7 +9285,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="144" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>762</v>
       </c>
@@ -9320,7 +9320,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="145" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>767</v>
       </c>
@@ -9355,7 +9355,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="146" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>772</v>
       </c>
@@ -9390,7 +9390,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="147" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>777</v>
       </c>
@@ -9425,7 +9425,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="148" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>783</v>
       </c>
@@ -9460,7 +9460,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="149" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>789</v>
       </c>
@@ -9495,7 +9495,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="150" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>794</v>
       </c>
@@ -9531,27 +9531,12 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K150" xr:uid="{4DA12617-6B17-4A0E-9E79-EBA6E19B3138}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="P 106"/>
-        <filter val="P 12"/>
-        <filter val="P 181"/>
-        <filter val="P 198"/>
-        <filter val="P 55"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="9">
-      <filters>
-        <filter val="NÃO"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:K150" xr:uid="{4DA12617-6B17-4A0E-9E79-EBA6E19B3138}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K150">
     <sortCondition ref="B1:B150"/>
   </sortState>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="63" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="20" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -9855,7 +9840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="19" t="s">
         <v>109</v>
       </c>
@@ -9865,37 +9850,85 @@
       <c r="C7" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="20"/>
+      <c r="D7" s="24">
+        <v>-4.9123150000000004</v>
+      </c>
+      <c r="E7" s="24">
+        <v>-38.000574</v>
+      </c>
+      <c r="F7" s="20">
+        <v>46170</v>
+      </c>
       <c r="G7" s="20">
         <f t="shared" si="0"/>
+        <v>46172</v>
+      </c>
+      <c r="H7" s="12">
+        <v>1420</v>
+      </c>
+      <c r="I7" s="12">
+        <v>5166</v>
+      </c>
+      <c r="J7" s="12">
+        <v>223</v>
+      </c>
+      <c r="K7" s="12">
+        <v>932</v>
+      </c>
+      <c r="L7" s="12">
+        <v>443</v>
+      </c>
+      <c r="M7" s="12">
+        <v>27</v>
+      </c>
+      <c r="N7" s="12">
+        <v>223</v>
+      </c>
+      <c r="O7" s="12">
+        <v>63</v>
+      </c>
+      <c r="P7" s="12">
+        <v>9</v>
+      </c>
+      <c r="Q7" s="12">
+        <v>76</v>
+      </c>
+      <c r="R7" s="12">
+        <v>107</v>
+      </c>
+      <c r="S7" s="12">
+        <v>22</v>
+      </c>
+      <c r="T7" s="12">
+        <v>103</v>
+      </c>
+      <c r="U7" s="12">
+        <v>11</v>
+      </c>
+      <c r="V7" s="12">
         <v>2</v>
       </c>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="12"/>
-      <c r="L7" s="12"/>
-      <c r="M7" s="12"/>
-      <c r="N7" s="12"/>
-      <c r="O7" s="12"/>
-      <c r="P7" s="12"/>
-      <c r="Q7" s="12"/>
-      <c r="R7" s="12"/>
-      <c r="S7" s="12"/>
-      <c r="T7" s="12"/>
-      <c r="U7" s="12"/>
-      <c r="V7" s="12"/>
-      <c r="W7" s="12"/>
-      <c r="X7" s="12"/>
-      <c r="Y7" s="12"/>
-      <c r="Z7" s="12"/>
-      <c r="AA7" s="12"/>
-      <c r="AB7" s="12"/>
+      <c r="W7" s="12">
+        <v>27</v>
+      </c>
+      <c r="X7" s="12">
+        <v>6</v>
+      </c>
+      <c r="Y7" s="12">
+        <v>2</v>
+      </c>
+      <c r="Z7" s="12">
+        <v>47</v>
+      </c>
+      <c r="AA7" s="12">
+        <v>45</v>
+      </c>
+      <c r="AB7" s="12">
+        <v>64</v>
+      </c>
       <c r="AC7" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>9018</v>
       </c>
     </row>
     <row r="8" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -11147,7 +11180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="19" t="s">
         <v>641</v>
       </c>
@@ -11157,37 +11190,85 @@
       <c r="C27" s="19" t="s">
         <v>642</v>
       </c>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="20"/>
+      <c r="D27" s="24">
+        <v>-5.0453950000000001</v>
+      </c>
+      <c r="E27" s="24">
+        <v>-37.773105999999999</v>
+      </c>
+      <c r="F27" s="20">
+        <v>46170</v>
+      </c>
       <c r="G27" s="20">
         <f t="shared" si="0"/>
+        <v>46172</v>
+      </c>
+      <c r="H27" s="12">
+        <v>233</v>
+      </c>
+      <c r="I27" s="12">
+        <v>1352</v>
+      </c>
+      <c r="J27" s="12">
+        <v>138</v>
+      </c>
+      <c r="K27" s="12">
+        <v>316</v>
+      </c>
+      <c r="L27" s="12">
+        <v>274</v>
+      </c>
+      <c r="M27" s="12">
+        <v>21</v>
+      </c>
+      <c r="N27" s="12">
+        <v>92</v>
+      </c>
+      <c r="O27" s="12">
+        <v>11</v>
+      </c>
+      <c r="P27" s="12">
+        <v>5</v>
+      </c>
+      <c r="Q27" s="12">
+        <v>52</v>
+      </c>
+      <c r="R27" s="12">
+        <v>64</v>
+      </c>
+      <c r="S27" s="12">
+        <v>4</v>
+      </c>
+      <c r="T27" s="12">
+        <v>36</v>
+      </c>
+      <c r="U27" s="12">
+        <v>15</v>
+      </c>
+      <c r="V27" s="12">
         <v>2</v>
       </c>
-      <c r="H27" s="12"/>
-      <c r="I27" s="12"/>
-      <c r="J27" s="12"/>
-      <c r="K27" s="12"/>
-      <c r="L27" s="12"/>
-      <c r="M27" s="12"/>
-      <c r="N27" s="12"/>
-      <c r="O27" s="12"/>
-      <c r="P27" s="12"/>
-      <c r="Q27" s="12"/>
-      <c r="R27" s="12"/>
-      <c r="S27" s="12"/>
-      <c r="T27" s="12"/>
-      <c r="U27" s="12"/>
-      <c r="V27" s="12"/>
-      <c r="W27" s="12"/>
-      <c r="X27" s="12"/>
-      <c r="Y27" s="12"/>
-      <c r="Z27" s="12"/>
-      <c r="AA27" s="12"/>
-      <c r="AB27" s="12"/>
+      <c r="W27" s="12">
+        <v>27</v>
+      </c>
+      <c r="X27" s="12">
+        <v>5</v>
+      </c>
+      <c r="Y27" s="12">
+        <v>5</v>
+      </c>
+      <c r="Z27" s="12">
+        <v>71</v>
+      </c>
+      <c r="AA27" s="12">
+        <v>56</v>
+      </c>
+      <c r="AB27" s="12">
+        <v>65</v>
+      </c>
       <c r="AC27" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2844</v>
       </c>
     </row>
     <row r="28" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -11726,7 +11807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
         <v>679</v>
       </c>
@@ -13693,7 +13774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="19" t="s">
         <v>341</v>
       </c>
@@ -13703,37 +13784,85 @@
       <c r="C65" s="19" t="s">
         <v>343</v>
       </c>
-      <c r="D65" s="21"/>
-      <c r="E65" s="21"/>
-      <c r="F65" s="20"/>
+      <c r="D65" s="24">
+        <v>-4.8210379999999997</v>
+      </c>
+      <c r="E65" s="24">
+        <v>-37.875945000000002</v>
+      </c>
+      <c r="F65" s="20">
+        <v>46170</v>
+      </c>
       <c r="G65" s="20">
         <f t="shared" si="0"/>
+        <v>46172</v>
+      </c>
+      <c r="H65" s="12">
+        <v>466</v>
+      </c>
+      <c r="I65" s="12">
+        <v>1375</v>
+      </c>
+      <c r="J65" s="12">
+        <v>33</v>
+      </c>
+      <c r="K65" s="12">
+        <v>346</v>
+      </c>
+      <c r="L65" s="12">
+        <v>91</v>
+      </c>
+      <c r="M65" s="12">
+        <v>13</v>
+      </c>
+      <c r="N65" s="12">
+        <v>6</v>
+      </c>
+      <c r="O65" s="12">
+        <v>4</v>
+      </c>
+      <c r="P65" s="12">
+        <v>1</v>
+      </c>
+      <c r="Q65" s="12">
         <v>2</v>
       </c>
-      <c r="H65" s="12"/>
-      <c r="I65" s="12"/>
-      <c r="J65" s="12"/>
-      <c r="K65" s="12"/>
-      <c r="L65" s="12"/>
-      <c r="M65" s="12"/>
-      <c r="N65" s="12"/>
-      <c r="O65" s="12"/>
-      <c r="P65" s="12"/>
-      <c r="Q65" s="12"/>
-      <c r="R65" s="12"/>
-      <c r="S65" s="12"/>
-      <c r="T65" s="12"/>
-      <c r="U65" s="12"/>
-      <c r="V65" s="12"/>
-      <c r="W65" s="12"/>
-      <c r="X65" s="12"/>
-      <c r="Y65" s="12"/>
-      <c r="Z65" s="12"/>
-      <c r="AA65" s="12"/>
-      <c r="AB65" s="12"/>
+      <c r="R65" s="12">
+        <v>6</v>
+      </c>
+      <c r="S65" s="12">
+        <v>0</v>
+      </c>
+      <c r="T65" s="12">
+        <v>20</v>
+      </c>
+      <c r="U65" s="12">
+        <v>0</v>
+      </c>
+      <c r="V65" s="12">
+        <v>0</v>
+      </c>
+      <c r="W65" s="12">
+        <v>0</v>
+      </c>
+      <c r="X65" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z65" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA65" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB65" s="12">
+        <v>0</v>
+      </c>
       <c r="AC65" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2365</v>
       </c>
     </row>
     <row r="66" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -13918,7 +14047,7 @@
         <v>3330</v>
       </c>
     </row>
-    <row r="68" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="19" t="s">
         <v>351</v>
       </c>
@@ -14894,7 +15023,7 @@
         <v>6031</v>
       </c>
     </row>
-    <row r="84" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="19" t="s">
         <v>436</v>
       </c>
@@ -14904,40 +15033,88 @@
       <c r="C84" s="19" t="s">
         <v>437</v>
       </c>
-      <c r="D84" s="21"/>
-      <c r="E84" s="21"/>
-      <c r="F84" s="20"/>
+      <c r="D84" s="24">
+        <v>-5.041658</v>
+      </c>
+      <c r="E84" s="24">
+        <v>-37.779488000000001</v>
+      </c>
+      <c r="F84" s="20">
+        <v>46170</v>
+      </c>
       <c r="G84" s="20">
         <f t="shared" si="5"/>
-        <v>2</v>
-      </c>
-      <c r="H84" s="12"/>
-      <c r="I84" s="12"/>
-      <c r="J84" s="12"/>
-      <c r="K84" s="12"/>
-      <c r="L84" s="12"/>
-      <c r="M84" s="12"/>
-      <c r="N84" s="12"/>
-      <c r="O84" s="12"/>
-      <c r="P84" s="12"/>
-      <c r="Q84" s="12"/>
-      <c r="R84" s="12"/>
-      <c r="S84" s="12"/>
-      <c r="T84" s="12"/>
-      <c r="U84" s="12"/>
-      <c r="V84" s="12"/>
-      <c r="W84" s="12"/>
-      <c r="X84" s="12"/>
-      <c r="Y84" s="12"/>
-      <c r="Z84" s="12"/>
-      <c r="AA84" s="12"/>
-      <c r="AB84" s="12"/>
+        <v>46172</v>
+      </c>
+      <c r="H84" s="12">
+        <v>201</v>
+      </c>
+      <c r="I84" s="12">
+        <v>1313</v>
+      </c>
+      <c r="J84" s="12">
+        <v>39</v>
+      </c>
+      <c r="K84" s="12">
+        <v>292</v>
+      </c>
+      <c r="L84" s="12">
+        <v>225</v>
+      </c>
+      <c r="M84" s="12">
+        <v>7</v>
+      </c>
+      <c r="N84" s="12">
+        <v>70</v>
+      </c>
+      <c r="O84" s="12">
+        <v>12</v>
+      </c>
+      <c r="P84" s="12">
+        <v>6</v>
+      </c>
+      <c r="Q84" s="12">
+        <v>44</v>
+      </c>
+      <c r="R84" s="12">
+        <v>74</v>
+      </c>
+      <c r="S84" s="12">
+        <v>7</v>
+      </c>
+      <c r="T84" s="12">
+        <v>29</v>
+      </c>
+      <c r="U84" s="12">
+        <v>3</v>
+      </c>
+      <c r="V84" s="12">
+        <v>3</v>
+      </c>
+      <c r="W84" s="12">
+        <v>26</v>
+      </c>
+      <c r="X84" s="12">
+        <v>3</v>
+      </c>
+      <c r="Y84" s="12">
+        <v>4</v>
+      </c>
+      <c r="Z84" s="12">
+        <v>44</v>
+      </c>
+      <c r="AA84" s="12">
+        <v>55</v>
+      </c>
+      <c r="AB84" s="12">
+        <v>89</v>
+      </c>
       <c r="AC84" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>2546</v>
+      </c>
+    </row>
+    <row r="85" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="19" t="s">
         <v>441</v>
       </c>
@@ -15928,7 +16105,7 @@
         <v>7063</v>
       </c>
     </row>
-    <row r="98" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="19" t="s">
         <v>501</v>
       </c>
@@ -16019,7 +16196,7 @@
         <v>3590</v>
       </c>
     </row>
-    <row r="99" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="19" t="s">
         <v>507</v>
       </c>
@@ -17493,7 +17670,7 @@
         <v>1773</v>
       </c>
     </row>
-    <row r="121" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="19" t="s">
         <v>24</v>
       </c>
@@ -17503,37 +17680,85 @@
       <c r="C121" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="D121" s="21"/>
-      <c r="E121" s="21"/>
-      <c r="F121" s="20"/>
+      <c r="D121" s="24">
+        <v>-4.8189970000000004</v>
+      </c>
+      <c r="E121" s="24">
+        <v>-37.872013000000003</v>
+      </c>
+      <c r="F121" s="20">
+        <v>46170</v>
+      </c>
       <c r="G121" s="20">
         <f t="shared" si="5"/>
-        <v>2</v>
-      </c>
-      <c r="H121" s="12"/>
-      <c r="I121" s="12"/>
-      <c r="J121" s="12"/>
-      <c r="K121" s="12"/>
-      <c r="L121" s="12"/>
-      <c r="M121" s="12"/>
-      <c r="N121" s="12"/>
-      <c r="O121" s="12"/>
-      <c r="P121" s="12"/>
-      <c r="Q121" s="12"/>
-      <c r="R121" s="12"/>
-      <c r="S121" s="12"/>
-      <c r="T121" s="12"/>
-      <c r="U121" s="12"/>
-      <c r="V121" s="12"/>
-      <c r="W121" s="12"/>
-      <c r="X121" s="12"/>
-      <c r="Y121" s="12"/>
-      <c r="Z121" s="12"/>
-      <c r="AA121" s="12"/>
-      <c r="AB121" s="12"/>
+        <v>46172</v>
+      </c>
+      <c r="H121" s="12">
+        <v>368</v>
+      </c>
+      <c r="I121" s="12">
+        <v>1843</v>
+      </c>
+      <c r="J121" s="12">
+        <v>30</v>
+      </c>
+      <c r="K121" s="12">
+        <v>231</v>
+      </c>
+      <c r="L121" s="12">
+        <v>46</v>
+      </c>
+      <c r="M121" s="12">
+        <v>13</v>
+      </c>
+      <c r="N121" s="12">
+        <v>4</v>
+      </c>
+      <c r="O121" s="12">
+        <v>0</v>
+      </c>
+      <c r="P121" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q121" s="12">
+        <v>4</v>
+      </c>
+      <c r="R121" s="12">
+        <v>3</v>
+      </c>
+      <c r="S121" s="12">
+        <v>1</v>
+      </c>
+      <c r="T121" s="12">
+        <v>12</v>
+      </c>
+      <c r="U121" s="12">
+        <v>0</v>
+      </c>
+      <c r="V121" s="12">
+        <v>0</v>
+      </c>
+      <c r="W121" s="12">
+        <v>0</v>
+      </c>
+      <c r="X121" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y121" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z121" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA121" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB121" s="12">
+        <v>0</v>
+      </c>
       <c r="AC121" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2556</v>
       </c>
     </row>
     <row r="122" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -19558,11 +19783,11 @@
   <autoFilter ref="A4:AC153" xr:uid="{1D18A476-0271-4A84-BE9E-901865A86FD3}">
     <filterColumn colId="0">
       <filters>
-        <filter val="P 112"/>
-        <filter val="P 144"/>
-        <filter val="P 163"/>
-        <filter val="P 164"/>
-        <filter val="P 57"/>
+        <filter val="E 04"/>
+        <filter val="P 05"/>
+        <filter val="P 107"/>
+        <filter val="P 143"/>
+        <filter val="P 39"/>
       </filters>
     </filterColumn>
     <filterColumn colId="5" showButton="0"/>

--- a/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
+++ b/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\5- MAPA CONTAGEM PDR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gesto\OneDrive\Área de Trabalho\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18EF208B-5E45-458E-8EF8-E415C574F9D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75A7BD85-BBE4-4AF4-8D37-5B1665941792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
   </bookViews>
   <sheets>
     <sheet name="LISTA DE PONTOS" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1873" uniqueCount="884">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1873" uniqueCount="883">
   <si>
     <t>WKT</t>
   </si>
@@ -943,9 +943,6 @@
   </si>
   <si>
     <t>155ECE0030E0</t>
-  </si>
-  <si>
-    <t>CE-576</t>
   </si>
   <si>
     <t>ENTR. CE-085</t>
@@ -2823,7 +2820,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2907,6 +2904,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4260,7 +4260,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DA12617-6B17-4A0E-9E79-EBA6E19B3138}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K150"/>
@@ -4309,13 +4309,13 @@
         <v>8</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -4344,13 +4344,13 @@
         <v>16</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K2" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>19</v>
       </c>
@@ -4379,13 +4379,13 @@
         <v>16</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K3" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>23</v>
       </c>
@@ -4414,13 +4414,13 @@
         <v>16</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K4" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>29</v>
       </c>
@@ -4449,13 +4449,13 @@
         <v>16</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K5" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>34</v>
       </c>
@@ -4490,7 +4490,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>40</v>
       </c>
@@ -4525,7 +4525,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>46</v>
       </c>
@@ -4560,7 +4560,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>52</v>
       </c>
@@ -4595,7 +4595,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>56</v>
       </c>
@@ -4624,13 +4624,13 @@
         <v>16</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K10" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>62</v>
       </c>
@@ -4665,7 +4665,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>68</v>
       </c>
@@ -4700,7 +4700,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>74</v>
       </c>
@@ -4729,13 +4729,13 @@
         <v>16</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K13" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>206</v>
       </c>
@@ -4764,13 +4764,13 @@
         <v>16</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K14" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>212</v>
       </c>
@@ -4805,7 +4805,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>217</v>
       </c>
@@ -4834,13 +4834,13 @@
         <v>16</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K16" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>222</v>
       </c>
@@ -4875,7 +4875,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>227</v>
       </c>
@@ -4904,13 +4904,13 @@
         <v>16</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K18" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>233</v>
       </c>
@@ -4945,7 +4945,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>239</v>
       </c>
@@ -4980,7 +4980,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>245</v>
       </c>
@@ -5009,13 +5009,13 @@
         <v>16</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K21" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>250</v>
       </c>
@@ -5050,7 +5050,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>255</v>
       </c>
@@ -5085,7 +5085,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>260</v>
       </c>
@@ -5120,7 +5120,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>264</v>
       </c>
@@ -5155,7 +5155,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>270</v>
       </c>
@@ -5190,7 +5190,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>276</v>
       </c>
@@ -5219,13 +5219,13 @@
         <v>16</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K27" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>281</v>
       </c>
@@ -5254,13 +5254,13 @@
         <v>16</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K28" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>80</v>
       </c>
@@ -5289,13 +5289,13 @@
         <v>16</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K29" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>85</v>
       </c>
@@ -5324,13 +5324,13 @@
         <v>16</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K30" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>91</v>
       </c>
@@ -5359,13 +5359,13 @@
         <v>16</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K31" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>286</v>
       </c>
@@ -5400,7 +5400,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>291</v>
       </c>
@@ -5443,13 +5443,13 @@
         <v>298</v>
       </c>
       <c r="C34" s="5">
-        <v>-3.6606179999999999</v>
+        <v>-3.6712609999999999</v>
       </c>
       <c r="D34" s="5">
-        <v>-38.856175999999998</v>
+        <v>-38.815711</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>42</v>
+        <v>404</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>299</v>
@@ -5458,24 +5458,24 @@
         <v>300</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>301</v>
+        <v>552</v>
       </c>
       <c r="I34" s="4" t="s">
         <v>16</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>17</v>
+        <v>882</v>
       </c>
       <c r="K34" s="6" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B35" s="4" t="s">
         <v>302</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>303</v>
       </c>
       <c r="C35" s="5">
         <v>-4.5677839999999996</v>
@@ -5484,33 +5484,33 @@
         <v>-41.220272999999999</v>
       </c>
       <c r="E35" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="F35" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="F35" s="4" t="s">
+      <c r="G35" s="4" t="s">
         <v>305</v>
       </c>
-      <c r="G35" s="4" t="s">
+      <c r="H35" s="4" t="s">
         <v>306</v>
-      </c>
-      <c r="H35" s="4" t="s">
-        <v>307</v>
       </c>
       <c r="I35" s="4" t="s">
         <v>16</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K35" s="6" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
+      <c r="B36" s="4" t="s">
         <v>309</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>310</v>
       </c>
       <c r="C36" s="5">
         <v>-5.9926050000000002</v>
@@ -5522,13 +5522,13 @@
         <v>136</v>
       </c>
       <c r="F36" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="G36" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="G36" s="4" t="s">
+      <c r="H36" s="4" t="s">
         <v>312</v>
-      </c>
-      <c r="H36" s="4" t="s">
-        <v>313</v>
       </c>
       <c r="I36" s="4" t="s">
         <v>16</v>
@@ -5540,7 +5540,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>95</v>
       </c>
@@ -5575,7 +5575,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>102</v>
       </c>
@@ -5610,7 +5610,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>108</v>
       </c>
@@ -5639,13 +5639,13 @@
         <v>101</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K39" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>113</v>
       </c>
@@ -5680,7 +5680,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>119</v>
       </c>
@@ -5715,7 +5715,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>124</v>
       </c>
@@ -5750,12 +5750,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B43" s="4" t="s">
         <v>314</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>315</v>
       </c>
       <c r="C43" s="5">
         <v>-4.228675</v>
@@ -5767,30 +5767,30 @@
         <v>148</v>
       </c>
       <c r="F43" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="G43" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="G43" s="4" t="s">
+      <c r="H43" s="4" t="s">
         <v>317</v>
-      </c>
-      <c r="H43" s="4" t="s">
-        <v>318</v>
       </c>
       <c r="I43" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K43" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B44" s="4" t="s">
         <v>319</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>320</v>
       </c>
       <c r="C44" s="5">
         <v>-3.9083830000000002</v>
@@ -5802,13 +5802,13 @@
         <v>148</v>
       </c>
       <c r="F44" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="G44" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="G44" s="4" t="s">
+      <c r="H44" s="4" t="s">
         <v>322</v>
-      </c>
-      <c r="H44" s="4" t="s">
-        <v>323</v>
       </c>
       <c r="I44" s="4" t="s">
         <v>101</v>
@@ -5820,12 +5820,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B45" s="4" t="s">
         <v>324</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>325</v>
       </c>
       <c r="C45" s="5">
         <v>-3.907816</v>
@@ -5837,13 +5837,13 @@
         <v>148</v>
       </c>
       <c r="F45" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="G45" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="G45" s="4" t="s">
+      <c r="H45" s="4" t="s">
         <v>327</v>
-      </c>
-      <c r="H45" s="4" t="s">
-        <v>328</v>
       </c>
       <c r="I45" s="4" t="s">
         <v>151</v>
@@ -5855,12 +5855,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B46" s="4" t="s">
         <v>329</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>330</v>
       </c>
       <c r="C46" s="5">
         <v>-4.5644640000000001</v>
@@ -5872,30 +5872,30 @@
         <v>87</v>
       </c>
       <c r="F46" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="G46" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="G46" s="4" t="s">
+      <c r="H46" s="4" t="s">
         <v>332</v>
-      </c>
-      <c r="H46" s="4" t="s">
-        <v>333</v>
       </c>
       <c r="I46" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K46" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B47" s="4" t="s">
         <v>334</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>335</v>
       </c>
       <c r="C47" s="5">
         <v>-4.720345</v>
@@ -5904,33 +5904,33 @@
         <v>-37.548856999999998</v>
       </c>
       <c r="E47" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="F47" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="F47" s="4" t="s">
+      <c r="G47" s="4" t="s">
         <v>337</v>
       </c>
-      <c r="G47" s="4" t="s">
+      <c r="H47" s="4" t="s">
         <v>338</v>
-      </c>
-      <c r="H47" s="4" t="s">
-        <v>339</v>
       </c>
       <c r="I47" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>883</v>
+        <v>799</v>
       </c>
       <c r="K47" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B48" s="4" t="s">
         <v>340</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>341</v>
       </c>
       <c r="C48" s="5">
         <v>-4.8210379999999997</v>
@@ -5939,28 +5939,28 @@
         <v>-37.875945000000002</v>
       </c>
       <c r="E48" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="F48" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="F48" s="4" t="s">
+      <c r="G48" s="4" t="s">
         <v>343</v>
       </c>
-      <c r="G48" s="4" t="s">
+      <c r="H48" s="4" t="s">
         <v>344</v>
-      </c>
-      <c r="H48" s="4" t="s">
-        <v>345</v>
       </c>
       <c r="I48" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K48" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>129</v>
       </c>
@@ -5989,13 +5989,13 @@
         <v>101</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K49" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>134</v>
       </c>
@@ -6024,18 +6024,18 @@
         <v>101</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K50" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B51" s="4" t="s">
         <v>346</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>347</v>
       </c>
       <c r="C51" s="5">
         <v>-4.702947</v>
@@ -6047,10 +6047,10 @@
         <v>12</v>
       </c>
       <c r="F51" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="G51" s="4" t="s">
         <v>348</v>
-      </c>
-      <c r="G51" s="4" t="s">
-        <v>349</v>
       </c>
       <c r="H51" s="4" t="s">
         <v>22</v>
@@ -6059,18 +6059,18 @@
         <v>151</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K51" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B52" s="4" t="s">
         <v>350</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>351</v>
       </c>
       <c r="C52" s="5">
         <v>-5.2215020000000001</v>
@@ -6079,33 +6079,33 @@
         <v>-37.892071000000001</v>
       </c>
       <c r="E52" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="F52" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="F52" s="4" t="s">
+      <c r="G52" s="4" t="s">
         <v>353</v>
       </c>
-      <c r="G52" s="4" t="s">
+      <c r="H52" s="4" t="s">
         <v>354</v>
-      </c>
-      <c r="H52" s="4" t="s">
-        <v>355</v>
       </c>
       <c r="I52" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K52" s="6" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B53" s="4" t="s">
         <v>356</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>357</v>
       </c>
       <c r="C53" s="5">
         <v>-5.2506180000000002</v>
@@ -6114,33 +6114,33 @@
         <v>-38.494636999999997</v>
       </c>
       <c r="E53" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="F53" s="4" t="s">
         <v>358</v>
-      </c>
-      <c r="F53" s="4" t="s">
-        <v>359</v>
       </c>
       <c r="G53" s="4" t="s">
         <v>27</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="I53" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K53" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B54" s="4" t="s">
         <v>361</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>362</v>
       </c>
       <c r="C54" s="5">
         <v>-5.4016780000000004</v>
@@ -6149,33 +6149,33 @@
         <v>-38.569516999999998</v>
       </c>
       <c r="E54" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="F54" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="F54" s="4" t="s">
+      <c r="G54" s="4" t="s">
         <v>364</v>
       </c>
-      <c r="G54" s="4" t="s">
+      <c r="H54" s="4" t="s">
         <v>365</v>
-      </c>
-      <c r="H54" s="4" t="s">
-        <v>366</v>
       </c>
       <c r="I54" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K54" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="B55" s="4" t="s">
         <v>367</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>368</v>
       </c>
       <c r="C55" s="5">
         <v>-5.9727329999999998</v>
@@ -6184,16 +6184,16 @@
         <v>-38.8797</v>
       </c>
       <c r="E55" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="F55" s="4" t="s">
         <v>369</v>
       </c>
-      <c r="F55" s="4" t="s">
+      <c r="G55" s="4" t="s">
         <v>370</v>
       </c>
-      <c r="G55" s="4" t="s">
+      <c r="H55" s="4" t="s">
         <v>371</v>
-      </c>
-      <c r="H55" s="4" t="s">
-        <v>372</v>
       </c>
       <c r="I55" s="4" t="s">
         <v>151</v>
@@ -6205,7 +6205,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>140</v>
       </c>
@@ -6234,18 +6234,18 @@
         <v>101</v>
       </c>
       <c r="J56" s="6" t="s">
-        <v>883</v>
+        <v>799</v>
       </c>
       <c r="K56" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B57" s="4" t="s">
         <v>373</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>374</v>
       </c>
       <c r="C57" s="5">
         <v>-3.5660500000000002</v>
@@ -6254,16 +6254,16 @@
         <v>-41.143765999999999</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="F57" s="4" t="s">
+        <v>879</v>
+      </c>
+      <c r="G57" s="4" t="s">
         <v>880</v>
       </c>
-      <c r="G57" s="4" t="s">
+      <c r="H57" s="4" t="s">
         <v>881</v>
-      </c>
-      <c r="H57" s="4" t="s">
-        <v>882</v>
       </c>
       <c r="I57" s="4" t="s">
         <v>151</v>
@@ -6275,12 +6275,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B58" s="4" t="s">
         <v>375</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>376</v>
       </c>
       <c r="C58" s="5">
         <v>-3.8470499999999999</v>
@@ -6289,16 +6289,16 @@
         <v>-40.655116</v>
       </c>
       <c r="E58" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="F58" s="4" t="s">
         <v>377</v>
       </c>
-      <c r="F58" s="4" t="s">
+      <c r="G58" s="4" t="s">
         <v>378</v>
       </c>
-      <c r="G58" s="4" t="s">
+      <c r="H58" s="4" t="s">
         <v>379</v>
-      </c>
-      <c r="H58" s="4" t="s">
-        <v>380</v>
       </c>
       <c r="I58" s="4" t="s">
         <v>151</v>
@@ -6310,7 +6310,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>146</v>
       </c>
@@ -6345,12 +6345,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B60" s="4" t="s">
         <v>381</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>382</v>
       </c>
       <c r="C60" s="5">
         <v>-3.9773499999999999</v>
@@ -6359,16 +6359,16 @@
         <v>-40.707566</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F60" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="G60" s="4" t="s">
         <v>383</v>
       </c>
-      <c r="G60" s="4" t="s">
+      <c r="H60" s="4" t="s">
         <v>384</v>
-      </c>
-      <c r="H60" s="4" t="s">
-        <v>385</v>
       </c>
       <c r="I60" s="4" t="s">
         <v>151</v>
@@ -6380,12 +6380,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B61" s="4" t="s">
         <v>386</v>
-      </c>
-      <c r="B61" s="4" t="s">
-        <v>387</v>
       </c>
       <c r="C61" s="5">
         <v>-4.1677330000000001</v>
@@ -6394,16 +6394,16 @@
         <v>-40.952933000000002</v>
       </c>
       <c r="E61" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="F61" s="4" t="s">
         <v>388</v>
       </c>
-      <c r="F61" s="4" t="s">
+      <c r="G61" s="4" t="s">
         <v>389</v>
       </c>
-      <c r="G61" s="4" t="s">
+      <c r="H61" s="4" t="s">
         <v>390</v>
-      </c>
-      <c r="H61" s="4" t="s">
-        <v>391</v>
       </c>
       <c r="I61" s="4" t="s">
         <v>101</v>
@@ -6415,12 +6415,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B62" s="4" t="s">
         <v>392</v>
-      </c>
-      <c r="B62" s="4" t="s">
-        <v>393</v>
       </c>
       <c r="C62" s="5">
         <v>-4.040883</v>
@@ -6429,16 +6429,16 @@
         <v>-40.474516000000001</v>
       </c>
       <c r="E62" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="F62" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="F62" s="4" t="s">
+      <c r="G62" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="G62" s="4" t="s">
+      <c r="H62" s="4" t="s">
         <v>396</v>
-      </c>
-      <c r="H62" s="4" t="s">
-        <v>397</v>
       </c>
       <c r="I62" s="4" t="s">
         <v>151</v>
@@ -6450,12 +6450,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B63" s="4" t="s">
         <v>398</v>
-      </c>
-      <c r="B63" s="4" t="s">
-        <v>399</v>
       </c>
       <c r="C63" s="5">
         <v>-3.5272999999999999</v>
@@ -6467,13 +6467,13 @@
         <v>272</v>
       </c>
       <c r="F63" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="G63" s="4" t="s">
         <v>400</v>
       </c>
-      <c r="G63" s="4" t="s">
+      <c r="H63" s="4" t="s">
         <v>401</v>
-      </c>
-      <c r="H63" s="4" t="s">
-        <v>402</v>
       </c>
       <c r="I63" s="4" t="s">
         <v>101</v>
@@ -6485,12 +6485,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B64" s="4" t="s">
         <v>403</v>
-      </c>
-      <c r="B64" s="4" t="s">
-        <v>404</v>
       </c>
       <c r="C64" s="5">
         <v>-3.553566</v>
@@ -6499,16 +6499,16 @@
         <v>-38.885983000000003</v>
       </c>
       <c r="E64" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="F64" s="4" t="s">
         <v>405</v>
       </c>
-      <c r="F64" s="4" t="s">
+      <c r="G64" s="4" t="s">
         <v>406</v>
       </c>
-      <c r="G64" s="4" t="s">
+      <c r="H64" s="4" t="s">
         <v>407</v>
-      </c>
-      <c r="H64" s="4" t="s">
-        <v>408</v>
       </c>
       <c r="I64" s="4" t="s">
         <v>151</v>
@@ -6520,12 +6520,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B65" s="4" t="s">
         <v>409</v>
-      </c>
-      <c r="B65" s="4" t="s">
-        <v>410</v>
       </c>
       <c r="C65" s="5">
         <v>-3.2338659999999999</v>
@@ -6534,16 +6534,16 @@
         <v>-40.011833000000003</v>
       </c>
       <c r="E65" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="F65" s="4" t="s">
         <v>411</v>
       </c>
-      <c r="F65" s="4" t="s">
+      <c r="G65" s="4" t="s">
         <v>412</v>
       </c>
-      <c r="G65" s="4" t="s">
+      <c r="H65" s="4" t="s">
         <v>413</v>
-      </c>
-      <c r="H65" s="4" t="s">
-        <v>414</v>
       </c>
       <c r="I65" s="4" t="s">
         <v>101</v>
@@ -6555,12 +6555,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B66" s="4" t="s">
         <v>415</v>
-      </c>
-      <c r="B66" s="4" t="s">
-        <v>416</v>
       </c>
       <c r="C66" s="5">
         <v>-3.512756</v>
@@ -6572,30 +6572,30 @@
         <v>266</v>
       </c>
       <c r="F66" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="G66" s="4" t="s">
         <v>417</v>
       </c>
-      <c r="G66" s="4" t="s">
+      <c r="H66" s="4" t="s">
         <v>418</v>
-      </c>
-      <c r="H66" s="4" t="s">
-        <v>419</v>
       </c>
       <c r="I66" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J66" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K66" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="B67" s="4" t="s">
         <v>420</v>
-      </c>
-      <c r="B67" s="4" t="s">
-        <v>421</v>
       </c>
       <c r="C67" s="5">
         <v>-3.6566749999999999</v>
@@ -6604,33 +6604,33 @@
         <v>-39.424249000000003</v>
       </c>
       <c r="E67" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="F67" s="4" t="s">
         <v>422</v>
       </c>
-      <c r="F67" s="4" t="s">
+      <c r="G67" s="4" t="s">
         <v>423</v>
       </c>
-      <c r="G67" s="4" t="s">
+      <c r="H67" s="4" t="s">
         <v>424</v>
-      </c>
-      <c r="H67" s="4" t="s">
-        <v>425</v>
       </c>
       <c r="I67" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J67" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K67" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B68" s="4" t="s">
         <v>426</v>
-      </c>
-      <c r="B68" s="4" t="s">
-        <v>427</v>
       </c>
       <c r="C68" s="5">
         <v>-4.2901499999999997</v>
@@ -6639,16 +6639,16 @@
         <v>-38.625466000000003</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F68" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="G68" s="4" t="s">
         <v>428</v>
       </c>
-      <c r="G68" s="4" t="s">
+      <c r="H68" s="4" t="s">
         <v>429</v>
-      </c>
-      <c r="H68" s="4" t="s">
-        <v>430</v>
       </c>
       <c r="I68" s="4" t="s">
         <v>16</v>
@@ -6660,12 +6660,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="B69" s="4" t="s">
         <v>431</v>
-      </c>
-      <c r="B69" s="4" t="s">
-        <v>432</v>
       </c>
       <c r="C69" s="5">
         <v>-4.3755519999999999</v>
@@ -6677,30 +6677,30 @@
         <v>229</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="G69" s="4" t="s">
         <v>232</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="I69" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J69" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K69" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="B70" s="4" t="s">
         <v>435</v>
-      </c>
-      <c r="B70" s="4" t="s">
-        <v>436</v>
       </c>
       <c r="C70" s="5">
         <v>-5.041658</v>
@@ -6712,30 +6712,30 @@
         <v>229</v>
       </c>
       <c r="F70" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="G70" s="4" t="s">
         <v>437</v>
       </c>
-      <c r="G70" s="4" t="s">
+      <c r="H70" s="4" t="s">
         <v>438</v>
-      </c>
-      <c r="H70" s="4" t="s">
-        <v>439</v>
       </c>
       <c r="I70" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J70" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K70" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="B71" s="4" t="s">
         <v>440</v>
-      </c>
-      <c r="B71" s="4" t="s">
-        <v>441</v>
       </c>
       <c r="C71" s="5">
         <v>-5.2738310000000004</v>
@@ -6744,33 +6744,33 @@
         <v>-38.108522000000001</v>
       </c>
       <c r="E71" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="F71" s="4" t="s">
         <v>442</v>
       </c>
-      <c r="F71" s="4" t="s">
+      <c r="G71" s="4" t="s">
         <v>443</v>
       </c>
-      <c r="G71" s="4" t="s">
+      <c r="H71" s="4" t="s">
         <v>444</v>
-      </c>
-      <c r="H71" s="4" t="s">
-        <v>445</v>
       </c>
       <c r="I71" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J71" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K71" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="B72" s="4" t="s">
         <v>446</v>
-      </c>
-      <c r="B72" s="4" t="s">
-        <v>447</v>
       </c>
       <c r="C72" s="5">
         <v>-3.7728000000000002</v>
@@ -6782,13 +6782,13 @@
         <v>97</v>
       </c>
       <c r="F72" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="G72" s="4" t="s">
         <v>448</v>
       </c>
-      <c r="G72" s="4" t="s">
+      <c r="H72" s="4" t="s">
         <v>449</v>
-      </c>
-      <c r="H72" s="4" t="s">
-        <v>450</v>
       </c>
       <c r="I72" s="4" t="s">
         <v>101</v>
@@ -6800,12 +6800,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="B73" s="4" t="s">
         <v>451</v>
-      </c>
-      <c r="B73" s="4" t="s">
-        <v>452</v>
       </c>
       <c r="C73" s="5">
         <v>-3.1334659999999999</v>
@@ -6817,13 +6817,13 @@
         <v>235</v>
       </c>
       <c r="F73" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="G73" s="4" t="s">
         <v>453</v>
       </c>
-      <c r="G73" s="4" t="s">
+      <c r="H73" s="4" t="s">
         <v>454</v>
-      </c>
-      <c r="H73" s="4" t="s">
-        <v>455</v>
       </c>
       <c r="I73" s="4" t="s">
         <v>101</v>
@@ -6835,12 +6835,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B74" s="4" t="s">
         <v>456</v>
-      </c>
-      <c r="B74" s="4" t="s">
-        <v>457</v>
       </c>
       <c r="C74" s="5">
         <v>-3.6184599999999998</v>
@@ -6852,30 +6852,30 @@
         <v>235</v>
       </c>
       <c r="F74" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="G74" s="4" t="s">
         <v>458</v>
       </c>
-      <c r="G74" s="4" t="s">
+      <c r="H74" s="4" t="s">
         <v>459</v>
-      </c>
-      <c r="H74" s="4" t="s">
-        <v>460</v>
       </c>
       <c r="I74" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J74" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K74" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="B75" s="4" t="s">
         <v>461</v>
-      </c>
-      <c r="B75" s="4" t="s">
-        <v>462</v>
       </c>
       <c r="C75" s="5">
         <v>-3.9911660000000002</v>
@@ -6887,13 +6887,13 @@
         <v>235</v>
       </c>
       <c r="F75" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="G75" s="4" t="s">
         <v>463</v>
       </c>
-      <c r="G75" s="4" t="s">
+      <c r="H75" s="4" t="s">
         <v>464</v>
-      </c>
-      <c r="H75" s="4" t="s">
-        <v>465</v>
       </c>
       <c r="I75" s="4" t="s">
         <v>151</v>
@@ -6905,12 +6905,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="B76" s="4" t="s">
         <v>466</v>
-      </c>
-      <c r="B76" s="4" t="s">
-        <v>467</v>
       </c>
       <c r="C76" s="5">
         <v>-5.6781480000000002</v>
@@ -6922,30 +6922,30 @@
         <v>197</v>
       </c>
       <c r="F76" s="4" t="s">
+        <v>832</v>
+      </c>
+      <c r="G76" s="4" t="s">
         <v>833</v>
       </c>
-      <c r="G76" s="4" t="s">
+      <c r="H76" s="4" t="s">
         <v>834</v>
-      </c>
-      <c r="H76" s="4" t="s">
-        <v>835</v>
       </c>
       <c r="I76" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J76" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K76" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="B77" s="4" t="s">
         <v>470</v>
-      </c>
-      <c r="B77" s="4" t="s">
-        <v>471</v>
       </c>
       <c r="C77" s="5">
         <v>-3.4014500000000001</v>
@@ -6954,16 +6954,16 @@
         <v>-40.686549999999997</v>
       </c>
       <c r="E77" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="F77" s="4" t="s">
         <v>472</v>
       </c>
-      <c r="F77" s="4" t="s">
+      <c r="G77" s="4" t="s">
         <v>473</v>
       </c>
-      <c r="G77" s="4" t="s">
+      <c r="H77" s="4" t="s">
         <v>474</v>
-      </c>
-      <c r="H77" s="4" t="s">
-        <v>475</v>
       </c>
       <c r="I77" s="4" t="s">
         <v>101</v>
@@ -6975,12 +6975,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="B78" s="4" t="s">
         <v>476</v>
-      </c>
-      <c r="B78" s="4" t="s">
-        <v>477</v>
       </c>
       <c r="C78" s="5">
         <v>-3.5688710000000001</v>
@@ -6989,33 +6989,33 @@
         <v>-40.636719999999997</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F78" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="G78" s="4" t="s">
         <v>478</v>
       </c>
-      <c r="G78" s="4" t="s">
-        <v>479</v>
-      </c>
       <c r="H78" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="I78" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J78" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K78" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="B79" s="4" t="s">
         <v>480</v>
-      </c>
-      <c r="B79" s="4" t="s">
-        <v>481</v>
       </c>
       <c r="C79" s="5">
         <v>-4.7611049999999997</v>
@@ -7024,28 +7024,28 @@
         <v>-39.487011000000003</v>
       </c>
       <c r="E79" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="F79" s="4" t="s">
         <v>482</v>
       </c>
-      <c r="F79" s="4" t="s">
+      <c r="G79" s="4" t="s">
         <v>483</v>
       </c>
-      <c r="G79" s="4" t="s">
+      <c r="H79" s="4" t="s">
         <v>484</v>
-      </c>
-      <c r="H79" s="4" t="s">
-        <v>485</v>
       </c>
       <c r="I79" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J79" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K79" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>152</v>
       </c>
@@ -7074,18 +7074,18 @@
         <v>101</v>
       </c>
       <c r="J80" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K80" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="B81" s="4" t="s">
         <v>486</v>
-      </c>
-      <c r="B81" s="4" t="s">
-        <v>487</v>
       </c>
       <c r="C81" s="5">
         <v>-5.4022300000000003</v>
@@ -7094,33 +7094,33 @@
         <v>-38.571371999999997</v>
       </c>
       <c r="E81" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="F81" s="4" t="s">
         <v>488</v>
       </c>
-      <c r="F81" s="4" t="s">
+      <c r="G81" s="4" t="s">
         <v>489</v>
       </c>
-      <c r="G81" s="4" t="s">
+      <c r="H81" s="4" t="s">
         <v>490</v>
-      </c>
-      <c r="H81" s="4" t="s">
-        <v>491</v>
       </c>
       <c r="I81" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J81" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K81" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="B82" s="4" t="s">
         <v>492</v>
-      </c>
-      <c r="B82" s="4" t="s">
-        <v>493</v>
       </c>
       <c r="C82" s="5">
         <v>-5.7358440000000002</v>
@@ -7132,30 +7132,30 @@
         <v>136</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="G82" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="H82" s="4" t="s">
         <v>495</v>
-      </c>
-      <c r="H82" s="4" t="s">
-        <v>496</v>
       </c>
       <c r="I82" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J82" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K82" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="B83" s="4" t="s">
         <v>497</v>
-      </c>
-      <c r="B83" s="4" t="s">
-        <v>498</v>
       </c>
       <c r="C83" s="5">
         <v>-5.6845759999999999</v>
@@ -7167,30 +7167,30 @@
         <v>136</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="I83" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J83" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K83" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="B84" s="4" t="s">
         <v>500</v>
-      </c>
-      <c r="B84" s="4" t="s">
-        <v>501</v>
       </c>
       <c r="C84" s="5">
         <v>-5.0848469999999999</v>
@@ -7199,33 +7199,33 @@
         <v>-38.009757</v>
       </c>
       <c r="E84" s="4" t="s">
+        <v>501</v>
+      </c>
+      <c r="F84" s="4" t="s">
         <v>502</v>
       </c>
-      <c r="F84" s="4" t="s">
+      <c r="G84" s="4" t="s">
         <v>503</v>
       </c>
-      <c r="G84" s="4" t="s">
+      <c r="H84" s="4" t="s">
         <v>504</v>
-      </c>
-      <c r="H84" s="4" t="s">
-        <v>505</v>
       </c>
       <c r="I84" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J84" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K84" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="B85" s="4" t="s">
         <v>506</v>
-      </c>
-      <c r="B85" s="4" t="s">
-        <v>507</v>
       </c>
       <c r="C85" s="5">
         <v>-5.2461500000000001</v>
@@ -7234,28 +7234,28 @@
         <v>-38.214409000000003</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="F85" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="G85" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="G85" s="4" t="s">
+      <c r="H85" s="4" t="s">
         <v>509</v>
-      </c>
-      <c r="H85" s="4" t="s">
-        <v>510</v>
       </c>
       <c r="I85" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J85" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K85" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>158</v>
       </c>
@@ -7284,18 +7284,18 @@
         <v>151</v>
       </c>
       <c r="J86" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K86" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="B87" s="4" t="s">
         <v>511</v>
-      </c>
-      <c r="B87" s="4" t="s">
-        <v>512</v>
       </c>
       <c r="C87" s="5">
         <v>-3.9741499999999998</v>
@@ -7304,16 +7304,16 @@
         <v>-40.704782999999999</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F87" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="G87" s="4" t="s">
         <v>513</v>
       </c>
-      <c r="G87" s="4" t="s">
+      <c r="H87" s="4" t="s">
         <v>514</v>
-      </c>
-      <c r="H87" s="4" t="s">
-        <v>515</v>
       </c>
       <c r="I87" s="4" t="s">
         <v>151</v>
@@ -7325,12 +7325,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="B88" s="4" t="s">
         <v>516</v>
-      </c>
-      <c r="B88" s="4" t="s">
-        <v>517</v>
       </c>
       <c r="C88" s="5">
         <v>-3.962866</v>
@@ -7339,16 +7339,16 @@
         <v>-38.357016000000002</v>
       </c>
       <c r="E88" s="4" t="s">
+        <v>517</v>
+      </c>
+      <c r="F88" s="4" t="s">
         <v>518</v>
       </c>
-      <c r="F88" s="4" t="s">
+      <c r="G88" s="4" t="s">
         <v>519</v>
       </c>
-      <c r="G88" s="4" t="s">
+      <c r="H88" s="4" t="s">
         <v>520</v>
-      </c>
-      <c r="H88" s="4" t="s">
-        <v>521</v>
       </c>
       <c r="I88" s="4" t="s">
         <v>101</v>
@@ -7360,12 +7360,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="B89" s="4" t="s">
         <v>522</v>
-      </c>
-      <c r="B89" s="4" t="s">
-        <v>523</v>
       </c>
       <c r="C89" s="5">
         <v>-4.0425329999999997</v>
@@ -7374,16 +7374,16 @@
         <v>-38.206499999999998</v>
       </c>
       <c r="E89" s="4" t="s">
+        <v>523</v>
+      </c>
+      <c r="F89" s="4" t="s">
         <v>524</v>
       </c>
-      <c r="F89" s="4" t="s">
+      <c r="G89" s="4" t="s">
         <v>525</v>
       </c>
-      <c r="G89" s="4" t="s">
+      <c r="H89" s="4" t="s">
         <v>526</v>
-      </c>
-      <c r="H89" s="4" t="s">
-        <v>527</v>
       </c>
       <c r="I89" s="4" t="s">
         <v>151</v>
@@ -7395,7 +7395,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>163</v>
       </c>
@@ -7424,18 +7424,18 @@
         <v>151</v>
       </c>
       <c r="J90" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K90" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="B91" s="4" t="s">
         <v>528</v>
-      </c>
-      <c r="B91" s="4" t="s">
-        <v>529</v>
       </c>
       <c r="C91" s="5">
         <v>-4.4447369999999999</v>
@@ -7444,33 +7444,33 @@
         <v>-38.662745999999999</v>
       </c>
       <c r="E91" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="F91" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="F91" s="4" t="s">
+      <c r="G91" s="4" t="s">
         <v>531</v>
       </c>
-      <c r="G91" s="4" t="s">
+      <c r="H91" s="4" t="s">
         <v>532</v>
-      </c>
-      <c r="H91" s="4" t="s">
-        <v>533</v>
       </c>
       <c r="I91" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J91" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K91" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="B92" s="4" t="s">
         <v>534</v>
-      </c>
-      <c r="B92" s="4" t="s">
-        <v>535</v>
       </c>
       <c r="C92" s="5">
         <v>-5.1705110000000003</v>
@@ -7479,33 +7479,33 @@
         <v>-40.708150000000003</v>
       </c>
       <c r="E92" s="4" t="s">
+        <v>535</v>
+      </c>
+      <c r="F92" s="4" t="s">
         <v>536</v>
       </c>
-      <c r="F92" s="4" t="s">
+      <c r="G92" s="4" t="s">
         <v>537</v>
       </c>
-      <c r="G92" s="4" t="s">
+      <c r="H92" s="4" t="s">
         <v>538</v>
-      </c>
-      <c r="H92" s="4" t="s">
-        <v>539</v>
       </c>
       <c r="I92" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J92" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K92" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="B93" s="4" t="s">
         <v>540</v>
-      </c>
-      <c r="B93" s="4" t="s">
-        <v>541</v>
       </c>
       <c r="C93" s="5">
         <v>-4.5701270000000003</v>
@@ -7514,33 +7514,33 @@
         <v>-37.734988999999999</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F93" s="4" t="s">
+        <v>541</v>
+      </c>
+      <c r="G93" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="G93" s="4" t="s">
+      <c r="H93" s="4" t="s">
         <v>543</v>
-      </c>
-      <c r="H93" s="4" t="s">
-        <v>544</v>
       </c>
       <c r="I93" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J93" s="6" t="s">
-        <v>883</v>
+        <v>799</v>
       </c>
       <c r="K93" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="B94" s="4" t="s">
         <v>545</v>
-      </c>
-      <c r="B94" s="4" t="s">
-        <v>546</v>
       </c>
       <c r="C94" s="5">
         <v>-5.1207330000000004</v>
@@ -7549,16 +7549,16 @@
         <v>-39.752000000000002</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F94" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="G94" s="4" t="s">
         <v>547</v>
       </c>
-      <c r="G94" s="4" t="s">
+      <c r="H94" s="4" t="s">
         <v>548</v>
-      </c>
-      <c r="H94" s="4" t="s">
-        <v>549</v>
       </c>
       <c r="I94" s="4" t="s">
         <v>101</v>
@@ -7570,7 +7570,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>169</v>
       </c>
@@ -7587,19 +7587,19 @@
         <v>197</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="G95" s="4" t="s">
         <v>132</v>
       </c>
       <c r="H95" s="4" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="I95" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J95" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K95" s="6" t="s">
         <v>18</v>
@@ -7607,45 +7607,45 @@
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="B96" s="4" t="s">
         <v>550</v>
       </c>
-      <c r="B96" s="4" t="s">
-        <v>551</v>
-      </c>
       <c r="C96" s="5">
-        <v>-3.6957</v>
-      </c>
-      <c r="D96" s="5">
-        <v>-38.869149999999998</v>
+        <v>-3.6776800000000001</v>
+      </c>
+      <c r="D96" s="32">
+        <v>-38.859572</v>
       </c>
       <c r="E96" s="4" t="s">
         <v>42</v>
       </c>
       <c r="F96" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="G96" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="H96" s="4" t="s">
         <v>552</v>
-      </c>
-      <c r="G96" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="H96" s="4" t="s">
-        <v>553</v>
       </c>
       <c r="I96" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J96" s="6" t="s">
-        <v>17</v>
+        <v>882</v>
       </c>
       <c r="K96" s="6" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="B97" s="4" t="s">
         <v>554</v>
-      </c>
-      <c r="B97" s="4" t="s">
-        <v>555</v>
       </c>
       <c r="C97" s="5">
         <v>-3.6978119999999999</v>
@@ -7654,33 +7654,33 @@
         <v>-40.307443999999997</v>
       </c>
       <c r="E97" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="F97" s="4" t="s">
         <v>556</v>
       </c>
-      <c r="F97" s="4" t="s">
+      <c r="G97" s="4" t="s">
         <v>557</v>
       </c>
-      <c r="G97" s="4" t="s">
+      <c r="H97" s="4" t="s">
         <v>558</v>
-      </c>
-      <c r="H97" s="4" t="s">
-        <v>559</v>
       </c>
       <c r="I97" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J97" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K97" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="B98" s="4" t="s">
         <v>560</v>
-      </c>
-      <c r="B98" s="4" t="s">
-        <v>561</v>
       </c>
       <c r="C98" s="5">
         <v>-5.2113269999999998</v>
@@ -7692,30 +7692,30 @@
         <v>208</v>
       </c>
       <c r="F98" s="4" t="s">
+        <v>561</v>
+      </c>
+      <c r="G98" s="4" t="s">
         <v>562</v>
       </c>
-      <c r="G98" s="4" t="s">
+      <c r="H98" s="4" t="s">
         <v>563</v>
-      </c>
-      <c r="H98" s="4" t="s">
-        <v>564</v>
       </c>
       <c r="I98" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J98" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K98" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B99" s="4" t="s">
         <v>565</v>
-      </c>
-      <c r="B99" s="4" t="s">
-        <v>566</v>
       </c>
       <c r="C99" s="5">
         <v>-4.3822749999999999</v>
@@ -7727,30 +7727,30 @@
         <v>208</v>
       </c>
       <c r="F99" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="G99" s="4" t="s">
         <v>567</v>
       </c>
-      <c r="G99" s="4" t="s">
+      <c r="H99" s="4" t="s">
         <v>568</v>
-      </c>
-      <c r="H99" s="4" t="s">
-        <v>569</v>
       </c>
       <c r="I99" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J99" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K99" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="B100" s="4" t="s">
         <v>570</v>
-      </c>
-      <c r="B100" s="4" t="s">
-        <v>571</v>
       </c>
       <c r="C100" s="5">
         <v>-6.0296659999999997</v>
@@ -7759,16 +7759,16 @@
         <v>-38.340949999999999</v>
       </c>
       <c r="E100" s="4" t="s">
+        <v>571</v>
+      </c>
+      <c r="F100" s="4" t="s">
         <v>572</v>
       </c>
-      <c r="F100" s="4" t="s">
+      <c r="G100" s="4" t="s">
         <v>573</v>
       </c>
-      <c r="G100" s="4" t="s">
+      <c r="H100" s="4" t="s">
         <v>574</v>
-      </c>
-      <c r="H100" s="4" t="s">
-        <v>575</v>
       </c>
       <c r="I100" s="4" t="s">
         <v>101</v>
@@ -7780,12 +7780,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="B101" s="4" t="s">
         <v>576</v>
-      </c>
-      <c r="B101" s="4" t="s">
-        <v>577</v>
       </c>
       <c r="C101" s="5">
         <v>-5.2495240000000001</v>
@@ -7794,33 +7794,33 @@
         <v>-38.492610999999997</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F101" s="4" t="s">
+        <v>577</v>
+      </c>
+      <c r="G101" s="4" t="s">
         <v>578</v>
       </c>
-      <c r="G101" s="4" t="s">
+      <c r="H101" s="4" t="s">
         <v>579</v>
-      </c>
-      <c r="H101" s="4" t="s">
-        <v>580</v>
       </c>
       <c r="I101" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J101" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K101" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="B102" s="4" t="s">
         <v>581</v>
-      </c>
-      <c r="B102" s="4" t="s">
-        <v>582</v>
       </c>
       <c r="C102" s="5">
         <v>-4.2260499999999999</v>
@@ -7829,16 +7829,16 @@
         <v>-38.112082999999998</v>
       </c>
       <c r="E102" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="F102" s="4" t="s">
         <v>583</v>
       </c>
-      <c r="F102" s="4" t="s">
+      <c r="G102" s="4" t="s">
         <v>584</v>
       </c>
-      <c r="G102" s="4" t="s">
+      <c r="H102" s="4" t="s">
         <v>585</v>
-      </c>
-      <c r="H102" s="4" t="s">
-        <v>586</v>
       </c>
       <c r="I102" s="4" t="s">
         <v>151</v>
@@ -7850,12 +7850,12 @@
         <v>178</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="B103" s="4" t="s">
         <v>587</v>
-      </c>
-      <c r="B103" s="4" t="s">
-        <v>588</v>
       </c>
       <c r="C103" s="5">
         <v>-4.2283499999999998</v>
@@ -7864,16 +7864,16 @@
         <v>-38.112932999999998</v>
       </c>
       <c r="E103" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="F103" s="4" t="s">
         <v>589</v>
-      </c>
-      <c r="F103" s="4" t="s">
-        <v>590</v>
       </c>
       <c r="G103" s="4" t="s">
         <v>73</v>
       </c>
       <c r="H103" s="4" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="I103" s="4" t="s">
         <v>101</v>
@@ -7885,12 +7885,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="B104" s="4" t="s">
         <v>592</v>
-      </c>
-      <c r="B104" s="4" t="s">
-        <v>593</v>
       </c>
       <c r="C104" s="5">
         <v>-4.5799000000000003</v>
@@ -7902,30 +7902,30 @@
         <v>142</v>
       </c>
       <c r="F104" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="G104" s="4" t="s">
         <v>594</v>
       </c>
-      <c r="G104" s="4" t="s">
+      <c r="H104" s="4" t="s">
         <v>595</v>
-      </c>
-      <c r="H104" s="4" t="s">
-        <v>596</v>
       </c>
       <c r="I104" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J104" s="6" t="s">
-        <v>883</v>
+        <v>799</v>
       </c>
       <c r="K104" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="B105" s="4" t="s">
         <v>597</v>
-      </c>
-      <c r="B105" s="4" t="s">
-        <v>598</v>
       </c>
       <c r="C105" s="5">
         <v>-3.9187500000000002</v>
@@ -7937,13 +7937,13 @@
         <v>104</v>
       </c>
       <c r="F105" s="4" t="s">
+        <v>598</v>
+      </c>
+      <c r="G105" s="4" t="s">
         <v>599</v>
       </c>
-      <c r="G105" s="4" t="s">
+      <c r="H105" s="4" t="s">
         <v>600</v>
-      </c>
-      <c r="H105" s="4" t="s">
-        <v>601</v>
       </c>
       <c r="I105" s="4" t="s">
         <v>101</v>
@@ -7955,7 +7955,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>172</v>
       </c>
@@ -7990,7 +7990,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>179</v>
       </c>
@@ -8019,13 +8019,13 @@
         <v>101</v>
       </c>
       <c r="J107" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K107" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>184</v>
       </c>
@@ -8060,7 +8060,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>189</v>
       </c>
@@ -8089,13 +8089,13 @@
         <v>151</v>
       </c>
       <c r="J109" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K109" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>195</v>
       </c>
@@ -8124,18 +8124,18 @@
         <v>151</v>
       </c>
       <c r="J110" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K110" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="B111" s="4" t="s">
         <v>602</v>
-      </c>
-      <c r="B111" s="4" t="s">
-        <v>603</v>
       </c>
       <c r="C111" s="5">
         <v>-3.7752400000000002</v>
@@ -8144,33 +8144,33 @@
         <v>-40.496578999999997</v>
       </c>
       <c r="E111" s="4" t="s">
+        <v>603</v>
+      </c>
+      <c r="F111" s="4" t="s">
         <v>604</v>
       </c>
-      <c r="F111" s="4" t="s">
+      <c r="G111" s="4" t="s">
         <v>605</v>
       </c>
-      <c r="G111" s="4" t="s">
+      <c r="H111" s="4" t="s">
         <v>606</v>
-      </c>
-      <c r="H111" s="4" t="s">
-        <v>607</v>
       </c>
       <c r="I111" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J111" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K111" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="B112" s="4" t="s">
         <v>608</v>
-      </c>
-      <c r="B112" s="4" t="s">
-        <v>609</v>
       </c>
       <c r="C112" s="5">
         <v>-3.9438659999999999</v>
@@ -8182,13 +8182,13 @@
         <v>208</v>
       </c>
       <c r="F112" s="4" t="s">
+        <v>609</v>
+      </c>
+      <c r="G112" s="4" t="s">
         <v>610</v>
       </c>
-      <c r="G112" s="4" t="s">
+      <c r="H112" s="4" t="s">
         <v>611</v>
-      </c>
-      <c r="H112" s="4" t="s">
-        <v>612</v>
       </c>
       <c r="I112" s="4" t="s">
         <v>101</v>
@@ -8200,12 +8200,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="B113" s="4" t="s">
         <v>613</v>
-      </c>
-      <c r="B113" s="4" t="s">
-        <v>614</v>
       </c>
       <c r="C113" s="5">
         <v>-4.7911549999999998</v>
@@ -8214,33 +8214,33 @@
         <v>-40.827958000000002</v>
       </c>
       <c r="E113" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="F113" s="4" t="s">
         <v>615</v>
       </c>
-      <c r="F113" s="4" t="s">
+      <c r="G113" s="4" t="s">
         <v>616</v>
       </c>
-      <c r="G113" s="4" t="s">
+      <c r="H113" s="4" t="s">
         <v>617</v>
-      </c>
-      <c r="H113" s="4" t="s">
-        <v>618</v>
       </c>
       <c r="I113" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J113" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K113" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="B114" s="4" t="s">
         <v>619</v>
-      </c>
-      <c r="B114" s="4" t="s">
-        <v>620</v>
       </c>
       <c r="C114" s="5">
         <v>-3.4859019999999998</v>
@@ -8249,33 +8249,33 @@
         <v>-39.523645000000002</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F114" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="G114" s="4" t="s">
         <v>621</v>
       </c>
-      <c r="G114" s="4" t="s">
+      <c r="H114" s="4" t="s">
         <v>622</v>
-      </c>
-      <c r="H114" s="4" t="s">
-        <v>623</v>
       </c>
       <c r="I114" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J114" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K114" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="B115" s="4" t="s">
         <v>624</v>
-      </c>
-      <c r="B115" s="4" t="s">
-        <v>625</v>
       </c>
       <c r="C115" s="5">
         <v>-4.5871829999999996</v>
@@ -8284,16 +8284,16 @@
         <v>-38.620182999999997</v>
       </c>
       <c r="E115" s="4" t="s">
+        <v>625</v>
+      </c>
+      <c r="F115" s="4" t="s">
         <v>626</v>
       </c>
-      <c r="F115" s="4" t="s">
+      <c r="G115" s="4" t="s">
         <v>627</v>
       </c>
-      <c r="G115" s="4" t="s">
+      <c r="H115" s="4" t="s">
         <v>628</v>
-      </c>
-      <c r="H115" s="4" t="s">
-        <v>629</v>
       </c>
       <c r="I115" s="4" t="s">
         <v>101</v>
@@ -8305,12 +8305,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="B116" s="4" t="s">
         <v>630</v>
-      </c>
-      <c r="B116" s="4" t="s">
-        <v>631</v>
       </c>
       <c r="C116" s="5">
         <v>-3.5105249999999999</v>
@@ -8322,30 +8322,30 @@
         <v>235</v>
       </c>
       <c r="F116" s="4" t="s">
+        <v>631</v>
+      </c>
+      <c r="G116" s="4" t="s">
         <v>632</v>
       </c>
-      <c r="G116" s="4" t="s">
+      <c r="H116" s="4" t="s">
         <v>633</v>
-      </c>
-      <c r="H116" s="4" t="s">
-        <v>634</v>
       </c>
       <c r="I116" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J116" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K116" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="B117" s="4" t="s">
         <v>635</v>
-      </c>
-      <c r="B117" s="4" t="s">
-        <v>636</v>
       </c>
       <c r="C117" s="5">
         <v>-3.2141000000000002</v>
@@ -8354,16 +8354,16 @@
         <v>-40.864533000000002</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F117" s="4" t="s">
+        <v>636</v>
+      </c>
+      <c r="G117" s="4" t="s">
         <v>637</v>
       </c>
-      <c r="G117" s="4" t="s">
+      <c r="H117" s="4" t="s">
         <v>638</v>
-      </c>
-      <c r="H117" s="4" t="s">
-        <v>639</v>
       </c>
       <c r="I117" s="4" t="s">
         <v>101</v>
@@ -8375,12 +8375,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="B118" s="4" t="s">
         <v>640</v>
-      </c>
-      <c r="B118" s="4" t="s">
-        <v>641</v>
       </c>
       <c r="C118" s="5">
         <v>-5.0453950000000001</v>
@@ -8389,28 +8389,28 @@
         <v>-37.773105999999999</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="F118" s="4" t="s">
+        <v>641</v>
+      </c>
+      <c r="G118" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="G118" s="4" t="s">
+      <c r="H118" s="4" t="s">
         <v>643</v>
-      </c>
-      <c r="H118" s="4" t="s">
-        <v>644</v>
       </c>
       <c r="I118" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J118" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K118" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>201</v>
       </c>
@@ -8439,18 +8439,18 @@
         <v>151</v>
       </c>
       <c r="J119" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K119" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="B120" s="4" t="s">
         <v>645</v>
-      </c>
-      <c r="B120" s="4" t="s">
-        <v>646</v>
       </c>
       <c r="C120" s="5">
         <v>-5.5281140000000004</v>
@@ -8462,30 +8462,30 @@
         <v>76</v>
       </c>
       <c r="F120" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="G120" s="4" t="s">
         <v>647</v>
       </c>
-      <c r="G120" s="4" t="s">
+      <c r="H120" s="4" t="s">
         <v>648</v>
-      </c>
-      <c r="H120" s="4" t="s">
-        <v>649</v>
       </c>
       <c r="I120" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J120" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K120" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="B121" s="4" t="s">
         <v>650</v>
-      </c>
-      <c r="B121" s="4" t="s">
-        <v>651</v>
       </c>
       <c r="C121" s="5">
         <v>-4.338266</v>
@@ -8497,13 +8497,13 @@
         <v>104</v>
       </c>
       <c r="F121" s="4" t="s">
+        <v>651</v>
+      </c>
+      <c r="G121" s="4" t="s">
         <v>652</v>
       </c>
-      <c r="G121" s="4" t="s">
+      <c r="H121" s="4" t="s">
         <v>653</v>
-      </c>
-      <c r="H121" s="4" t="s">
-        <v>654</v>
       </c>
       <c r="I121" s="4" t="s">
         <v>101</v>
@@ -8515,12 +8515,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="B122" s="4" t="s">
         <v>655</v>
-      </c>
-      <c r="B122" s="4" t="s">
-        <v>656</v>
       </c>
       <c r="C122" s="5">
         <v>-4.2869089999999996</v>
@@ -8532,10 +8532,10 @@
         <v>36</v>
       </c>
       <c r="F122" s="4" t="s">
+        <v>656</v>
+      </c>
+      <c r="G122" s="4" t="s">
         <v>657</v>
-      </c>
-      <c r="G122" s="4" t="s">
-        <v>658</v>
       </c>
       <c r="H122" s="4" t="s">
         <v>83</v>
@@ -8544,18 +8544,18 @@
         <v>151</v>
       </c>
       <c r="J122" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K122" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="B123" s="4" t="s">
         <v>659</v>
-      </c>
-      <c r="B123" s="4" t="s">
-        <v>660</v>
       </c>
       <c r="C123" s="5">
         <v>-3.372366</v>
@@ -8567,13 +8567,13 @@
         <v>174</v>
       </c>
       <c r="F123" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="G123" s="4" t="s">
         <v>661</v>
       </c>
-      <c r="G123" s="4" t="s">
+      <c r="H123" s="4" t="s">
         <v>662</v>
-      </c>
-      <c r="H123" s="4" t="s">
-        <v>663</v>
       </c>
       <c r="I123" s="4" t="s">
         <v>151</v>
@@ -8585,12 +8585,12 @@
         <v>178</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="B124" s="4" t="s">
         <v>664</v>
-      </c>
-      <c r="B124" s="4" t="s">
-        <v>665</v>
       </c>
       <c r="C124" s="5">
         <v>-2.8945319999999999</v>
@@ -8602,30 +8602,30 @@
         <v>174</v>
       </c>
       <c r="F124" s="4" t="s">
+        <v>665</v>
+      </c>
+      <c r="G124" s="4" t="s">
         <v>666</v>
       </c>
-      <c r="G124" s="4" t="s">
+      <c r="H124" s="4" t="s">
         <v>667</v>
-      </c>
-      <c r="H124" s="4" t="s">
-        <v>668</v>
       </c>
       <c r="I124" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J124" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K124" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="B125" s="4" t="s">
         <v>669</v>
-      </c>
-      <c r="B125" s="4" t="s">
-        <v>670</v>
       </c>
       <c r="C125" s="5">
         <v>-4.5809509999999998</v>
@@ -8637,10 +8637,10 @@
         <v>25</v>
       </c>
       <c r="F125" s="4" t="s">
+        <v>670</v>
+      </c>
+      <c r="G125" s="4" t="s">
         <v>671</v>
-      </c>
-      <c r="G125" s="4" t="s">
-        <v>672</v>
       </c>
       <c r="H125" s="4" t="s">
         <v>27</v>
@@ -8649,18 +8649,18 @@
         <v>101</v>
       </c>
       <c r="J125" s="6" t="s">
-        <v>883</v>
+        <v>799</v>
       </c>
       <c r="K125" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="B126" s="4" t="s">
         <v>673</v>
-      </c>
-      <c r="B126" s="4" t="s">
-        <v>674</v>
       </c>
       <c r="C126" s="5">
         <v>-4.0460330000000004</v>
@@ -8672,13 +8672,13 @@
         <v>191</v>
       </c>
       <c r="F126" s="4" t="s">
+        <v>674</v>
+      </c>
+      <c r="G126" s="4" t="s">
         <v>675</v>
       </c>
-      <c r="G126" s="4" t="s">
+      <c r="H126" s="4" t="s">
         <v>676</v>
-      </c>
-      <c r="H126" s="4" t="s">
-        <v>677</v>
       </c>
       <c r="I126" s="4" t="s">
         <v>101</v>
@@ -8690,12 +8690,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="B127" s="4" t="s">
         <v>678</v>
-      </c>
-      <c r="B127" s="4" t="s">
-        <v>679</v>
       </c>
       <c r="C127" s="5">
         <v>-5.4253080000000002</v>
@@ -8707,30 +8707,30 @@
         <v>191</v>
       </c>
       <c r="F127" s="4" t="s">
+        <v>679</v>
+      </c>
+      <c r="G127" s="4" t="s">
         <v>680</v>
       </c>
-      <c r="G127" s="4" t="s">
+      <c r="H127" s="4" t="s">
         <v>681</v>
-      </c>
-      <c r="H127" s="4" t="s">
-        <v>682</v>
       </c>
       <c r="I127" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J127" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K127" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="B128" s="4" t="s">
         <v>683</v>
-      </c>
-      <c r="B128" s="4" t="s">
-        <v>684</v>
       </c>
       <c r="C128" s="5">
         <v>-5.3889829999999996</v>
@@ -8739,16 +8739,16 @@
         <v>-38.911766</v>
       </c>
       <c r="E128" s="4" t="s">
+        <v>684</v>
+      </c>
+      <c r="F128" s="4" t="s">
         <v>685</v>
       </c>
-      <c r="F128" s="4" t="s">
+      <c r="G128" s="4" t="s">
         <v>686</v>
       </c>
-      <c r="G128" s="4" t="s">
+      <c r="H128" s="4" t="s">
         <v>687</v>
-      </c>
-      <c r="H128" s="4" t="s">
-        <v>688</v>
       </c>
       <c r="I128" s="4" t="s">
         <v>101</v>
@@ -8760,12 +8760,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="B129" s="4" t="s">
         <v>689</v>
-      </c>
-      <c r="B129" s="4" t="s">
-        <v>690</v>
       </c>
       <c r="C129" s="5">
         <v>-5.9808000000000003</v>
@@ -8774,16 +8774,16 @@
         <v>-38.884349999999998</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="F129" s="4" t="s">
+        <v>690</v>
+      </c>
+      <c r="G129" s="4" t="s">
         <v>691</v>
       </c>
-      <c r="G129" s="4" t="s">
+      <c r="H129" s="4" t="s">
         <v>692</v>
-      </c>
-      <c r="H129" s="4" t="s">
-        <v>693</v>
       </c>
       <c r="I129" s="4" t="s">
         <v>101</v>
@@ -8797,45 +8797,45 @@
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="B130" s="4" t="s">
         <v>694</v>
       </c>
-      <c r="B130" s="4" t="s">
+      <c r="C130" s="5">
+        <v>-3.6789869999999998</v>
+      </c>
+      <c r="D130" s="5">
+        <v>-38.909970999999999</v>
+      </c>
+      <c r="E130" s="4" t="s">
         <v>695</v>
       </c>
-      <c r="C130" s="5">
-        <v>-3.5994000000000002</v>
-      </c>
-      <c r="D130" s="5">
-        <v>-38.898966000000001</v>
-      </c>
-      <c r="E130" s="4" t="s">
+      <c r="F130" s="4" t="s">
         <v>696</v>
       </c>
-      <c r="F130" s="4" t="s">
+      <c r="G130" s="4" t="s">
         <v>697</v>
       </c>
-      <c r="G130" s="4" t="s">
+      <c r="H130" s="4" t="s">
         <v>698</v>
-      </c>
-      <c r="H130" s="4" t="s">
-        <v>699</v>
       </c>
       <c r="I130" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J130" s="6" t="s">
-        <v>17</v>
+        <v>882</v>
       </c>
       <c r="K130" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="B131" s="4" t="s">
         <v>700</v>
-      </c>
-      <c r="B131" s="4" t="s">
-        <v>701</v>
       </c>
       <c r="C131" s="5">
         <v>-4.1112159999999998</v>
@@ -8844,10 +8844,10 @@
         <v>-39.226599999999998</v>
       </c>
       <c r="E131" s="4" t="s">
+        <v>701</v>
+      </c>
+      <c r="F131" s="4" t="s">
         <v>702</v>
-      </c>
-      <c r="F131" s="4" t="s">
-        <v>703</v>
       </c>
       <c r="G131" s="4" t="s">
         <v>284</v>
@@ -8865,12 +8865,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="B132" s="4" t="s">
         <v>704</v>
-      </c>
-      <c r="B132" s="4" t="s">
-        <v>705</v>
       </c>
       <c r="C132" s="5">
         <v>-3.3707829999999999</v>
@@ -8879,16 +8879,16 @@
         <v>-39.293933000000003</v>
       </c>
       <c r="E132" s="4" t="s">
+        <v>705</v>
+      </c>
+      <c r="F132" s="4" t="s">
         <v>706</v>
       </c>
-      <c r="F132" s="4" t="s">
+      <c r="G132" s="4" t="s">
         <v>707</v>
       </c>
-      <c r="G132" s="4" t="s">
+      <c r="H132" s="4" t="s">
         <v>708</v>
-      </c>
-      <c r="H132" s="4" t="s">
-        <v>709</v>
       </c>
       <c r="I132" s="4" t="s">
         <v>101</v>
@@ -8900,12 +8900,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="B133" s="4" t="s">
         <v>710</v>
-      </c>
-      <c r="B133" s="4" t="s">
-        <v>711</v>
       </c>
       <c r="C133" s="5">
         <v>-5.8117999999999999</v>
@@ -8917,30 +8917,30 @@
         <v>197</v>
       </c>
       <c r="F133" s="4" t="s">
+        <v>711</v>
+      </c>
+      <c r="G133" s="4" t="s">
         <v>712</v>
       </c>
-      <c r="G133" s="4" t="s">
+      <c r="H133" s="4" t="s">
         <v>713</v>
-      </c>
-      <c r="H133" s="4" t="s">
-        <v>714</v>
       </c>
       <c r="I133" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J133" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K133" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="B134" s="4" t="s">
         <v>715</v>
-      </c>
-      <c r="B134" s="4" t="s">
-        <v>716</v>
       </c>
       <c r="C134" s="5">
         <v>-3.304783</v>
@@ -8952,13 +8952,13 @@
         <v>174</v>
       </c>
       <c r="F134" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="G134" s="4" t="s">
         <v>717</v>
       </c>
-      <c r="G134" s="4" t="s">
+      <c r="H134" s="4" t="s">
         <v>718</v>
-      </c>
-      <c r="H134" s="4" t="s">
-        <v>719</v>
       </c>
       <c r="I134" s="4" t="s">
         <v>101</v>
@@ -8970,12 +8970,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="B135" s="4" t="s">
         <v>720</v>
-      </c>
-      <c r="B135" s="4" t="s">
-        <v>721</v>
       </c>
       <c r="C135" s="5">
         <v>-5.1408160000000001</v>
@@ -8987,13 +8987,13 @@
         <v>266</v>
       </c>
       <c r="F135" s="4" t="s">
+        <v>721</v>
+      </c>
+      <c r="G135" s="4" t="s">
         <v>722</v>
       </c>
-      <c r="G135" s="4" t="s">
+      <c r="H135" s="4" t="s">
         <v>723</v>
-      </c>
-      <c r="H135" s="4" t="s">
-        <v>724</v>
       </c>
       <c r="I135" s="4" t="s">
         <v>101</v>
@@ -9005,12 +9005,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="B136" s="4" t="s">
         <v>725</v>
-      </c>
-      <c r="B136" s="4" t="s">
-        <v>726</v>
       </c>
       <c r="C136" s="5">
         <v>-3.4763199999999999</v>
@@ -9022,30 +9022,30 @@
         <v>48</v>
       </c>
       <c r="F136" s="4" t="s">
+        <v>726</v>
+      </c>
+      <c r="G136" s="4" t="s">
+        <v>621</v>
+      </c>
+      <c r="H136" s="4" t="s">
         <v>727</v>
-      </c>
-      <c r="G136" s="4" t="s">
-        <v>622</v>
-      </c>
-      <c r="H136" s="4" t="s">
-        <v>728</v>
       </c>
       <c r="I136" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J136" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K136" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="B137" s="4" t="s">
         <v>729</v>
-      </c>
-      <c r="B137" s="4" t="s">
-        <v>730</v>
       </c>
       <c r="C137" s="5">
         <v>-3.5617000000000001</v>
@@ -9057,13 +9057,13 @@
         <v>241</v>
       </c>
       <c r="F137" s="4" t="s">
+        <v>730</v>
+      </c>
+      <c r="G137" s="4" t="s">
         <v>731</v>
       </c>
-      <c r="G137" s="4" t="s">
+      <c r="H137" s="4" t="s">
         <v>732</v>
-      </c>
-      <c r="H137" s="4" t="s">
-        <v>733</v>
       </c>
       <c r="I137" s="4" t="s">
         <v>151</v>
@@ -9075,12 +9075,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="B138" s="4" t="s">
         <v>734</v>
-      </c>
-      <c r="B138" s="4" t="s">
-        <v>735</v>
       </c>
       <c r="C138" s="5">
         <v>-5.4055679999999997</v>
@@ -9092,30 +9092,30 @@
         <v>136</v>
       </c>
       <c r="F138" s="4" t="s">
+        <v>735</v>
+      </c>
+      <c r="G138" s="4" t="s">
         <v>736</v>
       </c>
-      <c r="G138" s="4" t="s">
+      <c r="H138" s="4" t="s">
         <v>737</v>
-      </c>
-      <c r="H138" s="4" t="s">
-        <v>738</v>
       </c>
       <c r="I138" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J138" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K138" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>738</v>
+      </c>
+      <c r="B139" s="4" t="s">
         <v>739</v>
-      </c>
-      <c r="B139" s="4" t="s">
-        <v>740</v>
       </c>
       <c r="C139" s="5">
         <v>-2.9586229999999998</v>
@@ -9127,30 +9127,30 @@
         <v>174</v>
       </c>
       <c r="F139" s="4" t="s">
+        <v>740</v>
+      </c>
+      <c r="G139" s="4" t="s">
         <v>741</v>
       </c>
-      <c r="G139" s="4" t="s">
+      <c r="H139" s="4" t="s">
         <v>742</v>
-      </c>
-      <c r="H139" s="4" t="s">
-        <v>743</v>
       </c>
       <c r="I139" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J139" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K139" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="B140" s="4" t="s">
         <v>744</v>
-      </c>
-      <c r="B140" s="4" t="s">
-        <v>745</v>
       </c>
       <c r="C140" s="5">
         <v>-2.92225</v>
@@ -9159,33 +9159,33 @@
         <v>-40.120244</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="F140" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="G140" s="4" t="s">
         <v>746</v>
       </c>
-      <c r="G140" s="4" t="s">
+      <c r="H140" s="4" t="s">
         <v>747</v>
-      </c>
-      <c r="H140" s="4" t="s">
-        <v>748</v>
       </c>
       <c r="I140" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J140" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K140" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="B141" s="4" t="s">
         <v>749</v>
-      </c>
-      <c r="B141" s="4" t="s">
-        <v>750</v>
       </c>
       <c r="C141" s="5">
         <v>-3.697114</v>
@@ -9197,30 +9197,30 @@
         <v>48</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="G141" s="4" t="s">
         <v>51</v>
       </c>
       <c r="H141" s="4" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="I141" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J141" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K141" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="B142" s="4" t="s">
         <v>753</v>
-      </c>
-      <c r="B142" s="4" t="s">
-        <v>754</v>
       </c>
       <c r="C142" s="5">
         <v>-3.7188409999999998</v>
@@ -9232,30 +9232,30 @@
         <v>58</v>
       </c>
       <c r="F142" s="4" t="s">
+        <v>754</v>
+      </c>
+      <c r="G142" s="4" t="s">
         <v>755</v>
       </c>
-      <c r="G142" s="4" t="s">
+      <c r="H142" s="4" t="s">
         <v>756</v>
-      </c>
-      <c r="H142" s="4" t="s">
-        <v>757</v>
       </c>
       <c r="I142" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J142" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K142" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="B143" s="4" t="s">
         <v>758</v>
-      </c>
-      <c r="B143" s="4" t="s">
-        <v>759</v>
       </c>
       <c r="C143" s="5">
         <v>-4.0392330000000003</v>
@@ -9264,16 +9264,16 @@
         <v>-40.474150000000002</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="F143" s="4" t="s">
+        <v>759</v>
+      </c>
+      <c r="G143" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="H143" s="4" t="s">
         <v>760</v>
-      </c>
-      <c r="G143" s="4" t="s">
-        <v>607</v>
-      </c>
-      <c r="H143" s="4" t="s">
-        <v>761</v>
       </c>
       <c r="I143" s="4" t="s">
         <v>151</v>
@@ -9285,12 +9285,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="B144" s="4" t="s">
         <v>762</v>
-      </c>
-      <c r="B144" s="4" t="s">
-        <v>763</v>
       </c>
       <c r="C144" s="5">
         <v>-4.1177159999999997</v>
@@ -9302,13 +9302,13 @@
         <v>208</v>
       </c>
       <c r="F144" s="4" t="s">
+        <v>763</v>
+      </c>
+      <c r="G144" s="4" t="s">
         <v>764</v>
       </c>
-      <c r="G144" s="4" t="s">
+      <c r="H144" s="4" t="s">
         <v>765</v>
-      </c>
-      <c r="H144" s="4" t="s">
-        <v>766</v>
       </c>
       <c r="I144" s="4" t="s">
         <v>101</v>
@@ -9320,12 +9320,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="B145" s="4" t="s">
         <v>767</v>
-      </c>
-      <c r="B145" s="4" t="s">
-        <v>768</v>
       </c>
       <c r="C145" s="5">
         <v>-4.5583349999999996</v>
@@ -9334,33 +9334,33 @@
         <v>-40.729585999999998</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="F145" s="4" t="s">
+        <v>768</v>
+      </c>
+      <c r="G145" s="4" t="s">
         <v>769</v>
       </c>
-      <c r="G145" s="4" t="s">
+      <c r="H145" s="4" t="s">
         <v>770</v>
-      </c>
-      <c r="H145" s="4" t="s">
-        <v>771</v>
       </c>
       <c r="I145" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J145" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K145" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="B146" s="4" t="s">
         <v>772</v>
-      </c>
-      <c r="B146" s="4" t="s">
-        <v>773</v>
       </c>
       <c r="C146" s="5">
         <v>-5.1463979999999996</v>
@@ -9369,33 +9369,33 @@
         <v>-40.670636000000002</v>
       </c>
       <c r="E146" s="4" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="F146" s="4" t="s">
+        <v>773</v>
+      </c>
+      <c r="G146" s="4" t="s">
         <v>774</v>
       </c>
-      <c r="G146" s="4" t="s">
+      <c r="H146" s="4" t="s">
         <v>775</v>
-      </c>
-      <c r="H146" s="4" t="s">
-        <v>776</v>
       </c>
       <c r="I146" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J146" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K146" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>776</v>
+      </c>
+      <c r="B147" s="4" t="s">
         <v>777</v>
-      </c>
-      <c r="B147" s="4" t="s">
-        <v>778</v>
       </c>
       <c r="C147" s="5">
         <v>-4.0631500000000003</v>
@@ -9404,16 +9404,16 @@
         <v>-40.957650000000001</v>
       </c>
       <c r="E147" s="4" t="s">
+        <v>778</v>
+      </c>
+      <c r="F147" s="4" t="s">
         <v>779</v>
       </c>
-      <c r="F147" s="4" t="s">
+      <c r="G147" s="4" t="s">
         <v>780</v>
       </c>
-      <c r="G147" s="4" t="s">
+      <c r="H147" s="4" t="s">
         <v>781</v>
-      </c>
-      <c r="H147" s="4" t="s">
-        <v>782</v>
       </c>
       <c r="I147" s="4" t="s">
         <v>101</v>
@@ -9422,15 +9422,15 @@
         <v>17</v>
       </c>
       <c r="K147" s="6" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>782</v>
+      </c>
+      <c r="B148" s="4" t="s">
         <v>783</v>
-      </c>
-      <c r="B148" s="4" t="s">
-        <v>784</v>
       </c>
       <c r="C148" s="5">
         <v>-3.521487</v>
@@ -9439,33 +9439,33 @@
         <v>-40.330056999999996</v>
       </c>
       <c r="E148" s="4" t="s">
+        <v>784</v>
+      </c>
+      <c r="F148" s="4" t="s">
         <v>785</v>
       </c>
-      <c r="F148" s="4" t="s">
+      <c r="G148" s="4" t="s">
         <v>786</v>
       </c>
-      <c r="G148" s="4" t="s">
+      <c r="H148" s="4" t="s">
         <v>787</v>
-      </c>
-      <c r="H148" s="4" t="s">
-        <v>788</v>
       </c>
       <c r="I148" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J148" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K148" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="B149" s="4" t="s">
         <v>789</v>
-      </c>
-      <c r="B149" s="4" t="s">
-        <v>790</v>
       </c>
       <c r="C149" s="5">
         <v>-3.5194079999999999</v>
@@ -9474,33 +9474,33 @@
         <v>-40.361950999999998</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="F149" s="4" t="s">
+        <v>790</v>
+      </c>
+      <c r="G149" s="4" t="s">
         <v>791</v>
       </c>
-      <c r="G149" s="4" t="s">
+      <c r="H149" s="4" t="s">
         <v>792</v>
-      </c>
-      <c r="H149" s="4" t="s">
-        <v>793</v>
       </c>
       <c r="I149" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J149" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K149" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="B150" s="4" t="s">
         <v>794</v>
-      </c>
-      <c r="B150" s="4" t="s">
-        <v>795</v>
       </c>
       <c r="C150" s="5">
         <v>-3.552886</v>
@@ -9512,31 +9512,39 @@
         <v>48</v>
       </c>
       <c r="F150" s="4" t="s">
+        <v>795</v>
+      </c>
+      <c r="G150" s="4" t="s">
         <v>796</v>
       </c>
-      <c r="G150" s="4" t="s">
+      <c r="H150" s="4" t="s">
         <v>797</v>
-      </c>
-      <c r="H150" s="4" t="s">
-        <v>798</v>
       </c>
       <c r="I150" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J150" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K150" s="6" t="s">
         <v>18</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K150" xr:uid="{4DA12617-6B17-4A0E-9E79-EBA6E19B3138}"/>
+  <autoFilter ref="A1:K150" xr:uid="{4DA12617-6B17-4A0E-9E79-EBA6E19B3138}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="N 01"/>
+        <filter val="P 185"/>
+        <filter val="P 67"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K150">
     <sortCondition ref="B1:B150"/>
   </sortState>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="20" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="63" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -9573,15 +9581,15 @@
         <v>5</v>
       </c>
       <c r="D1" s="30" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="E1" s="30"/>
       <c r="F1" s="31" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="G1" s="31"/>
       <c r="H1" s="27" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="I1" s="27"/>
       <c r="J1" s="27"/>
@@ -9604,7 +9612,7 @@
       <c r="AA1" s="27"/>
       <c r="AB1" s="27"/>
       <c r="AC1" s="25" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="2" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9616,18 +9624,18 @@
       <c r="F2" s="31"/>
       <c r="G2" s="31"/>
       <c r="H2" s="26" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="I2" s="26"/>
       <c r="J2" s="26"/>
       <c r="K2" s="9" t="s">
+        <v>805</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>805</v>
+      </c>
+      <c r="M2" s="27" t="s">
         <v>806</v>
-      </c>
-      <c r="L2" s="9" t="s">
-        <v>806</v>
-      </c>
-      <c r="M2" s="27" t="s">
-        <v>807</v>
       </c>
       <c r="N2" s="27"/>
       <c r="O2" s="27"/>
@@ -9655,67 +9663,67 @@
       <c r="F3" s="31"/>
       <c r="G3" s="31"/>
       <c r="H3" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="I3" s="8" t="s">
         <v>808</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="J3" s="8" t="s">
         <v>809</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="K3" s="7" t="s">
         <v>810</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="L3" s="7" t="s">
         <v>811</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="M3" s="7" t="s">
         <v>812</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="N3" s="7" t="s">
         <v>813</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="O3" s="7" t="s">
         <v>814</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="P3" s="7" t="s">
         <v>815</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="Q3" s="7" t="s">
         <v>816</v>
       </c>
-      <c r="Q3" s="7" t="s">
+      <c r="R3" s="7" t="s">
         <v>817</v>
       </c>
-      <c r="R3" s="7" t="s">
+      <c r="S3" s="7" t="s">
         <v>818</v>
       </c>
-      <c r="S3" s="7" t="s">
+      <c r="T3" s="7" t="s">
         <v>819</v>
       </c>
-      <c r="T3" s="7" t="s">
+      <c r="U3" s="7" t="s">
         <v>820</v>
       </c>
-      <c r="U3" s="7" t="s">
+      <c r="V3" s="7" t="s">
         <v>821</v>
       </c>
-      <c r="V3" s="7" t="s">
+      <c r="W3" s="7" t="s">
         <v>822</v>
       </c>
-      <c r="W3" s="7" t="s">
+      <c r="X3" s="7" t="s">
         <v>823</v>
       </c>
-      <c r="X3" s="7" t="s">
+      <c r="Y3" s="7" t="s">
         <v>824</v>
       </c>
-      <c r="Y3" s="7" t="s">
+      <c r="Z3" s="7" t="s">
         <v>825</v>
       </c>
-      <c r="Z3" s="7" t="s">
+      <c r="AA3" s="7" t="s">
         <v>826</v>
       </c>
-      <c r="AA3" s="7" t="s">
+      <c r="AB3" s="7" t="s">
         <v>827</v>
-      </c>
-      <c r="AB3" s="7" t="s">
-        <v>828</v>
       </c>
       <c r="AC3" s="25"/>
     </row>
@@ -9840,7 +9848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="19" t="s">
         <v>109</v>
       </c>
@@ -10151,7 +10159,7 @@
         <v>5682</v>
       </c>
     </row>
-    <row r="12" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="19" t="s">
         <v>141</v>
       </c>
@@ -10161,37 +10169,84 @@
       <c r="C12" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="20"/>
+      <c r="D12" s="21">
+        <v>-4.5740699999999999</v>
+      </c>
+      <c r="E12" s="21">
+        <v>-37.736370000000001</v>
+      </c>
+      <c r="F12" s="20">
+        <v>46173</v>
+      </c>
       <c r="G12" s="20">
-        <f t="shared" si="0"/>
+        <v>46175</v>
+      </c>
+      <c r="H12" s="12">
+        <v>1118</v>
+      </c>
+      <c r="I12" s="12">
+        <v>5695</v>
+      </c>
+      <c r="J12" s="12">
+        <v>120</v>
+      </c>
+      <c r="K12" s="12">
+        <v>531</v>
+      </c>
+      <c r="L12" s="12">
+        <v>262</v>
+      </c>
+      <c r="M12" s="12">
+        <v>46</v>
+      </c>
+      <c r="N12" s="12">
+        <v>180</v>
+      </c>
+      <c r="O12" s="12">
+        <v>66</v>
+      </c>
+      <c r="P12" s="12">
+        <v>9</v>
+      </c>
+      <c r="Q12" s="12">
+        <v>58</v>
+      </c>
+      <c r="R12" s="12">
+        <v>104</v>
+      </c>
+      <c r="S12" s="12">
+        <v>8</v>
+      </c>
+      <c r="T12" s="12">
+        <v>78</v>
+      </c>
+      <c r="U12" s="12">
+        <v>3</v>
+      </c>
+      <c r="V12" s="12">
         <v>2</v>
       </c>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
-      <c r="L12" s="12"/>
-      <c r="M12" s="12"/>
-      <c r="N12" s="12"/>
-      <c r="O12" s="12"/>
-      <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
-      <c r="R12" s="12"/>
-      <c r="S12" s="12"/>
-      <c r="T12" s="12"/>
-      <c r="U12" s="12"/>
-      <c r="V12" s="12"/>
-      <c r="W12" s="12"/>
-      <c r="X12" s="12"/>
-      <c r="Y12" s="12"/>
-      <c r="Z12" s="12"/>
-      <c r="AA12" s="12"/>
-      <c r="AB12" s="12"/>
+      <c r="W12" s="12">
+        <v>11</v>
+      </c>
+      <c r="X12" s="12">
+        <v>7</v>
+      </c>
+      <c r="Y12" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="12">
+        <v>36</v>
+      </c>
+      <c r="AA12" s="12">
+        <v>51</v>
+      </c>
+      <c r="AB12" s="12">
+        <v>11</v>
+      </c>
       <c r="AC12" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>8397</v>
       </c>
     </row>
     <row r="13" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -10199,10 +10254,10 @@
         <v>147</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="D13" s="21"/>
       <c r="E13" s="21"/>
@@ -10248,10 +10303,10 @@
         <v>160</v>
       </c>
       <c r="D14" s="24" t="s">
+        <v>849</v>
+      </c>
+      <c r="E14" s="24" t="s">
         <v>850</v>
-      </c>
-      <c r="E14" s="24" t="s">
-        <v>851</v>
       </c>
       <c r="F14" s="20">
         <v>46142</v>
@@ -10607,10 +10662,10 @@
         <v>198</v>
       </c>
       <c r="D19" s="24" t="s">
+        <v>851</v>
+      </c>
+      <c r="E19" s="24" t="s">
         <v>852</v>
-      </c>
-      <c r="E19" s="24" t="s">
-        <v>853</v>
       </c>
       <c r="F19" s="20">
         <v>46142</v>
@@ -10689,13 +10744,13 @@
     </row>
     <row r="20" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="19" t="s">
+        <v>602</v>
+      </c>
+      <c r="B20" s="19" t="s">
         <v>603</v>
       </c>
-      <c r="B20" s="19" t="s">
+      <c r="C20" s="19" t="s">
         <v>604</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>605</v>
       </c>
       <c r="D20" s="21">
         <v>-3.7752400000000002</v>
@@ -10780,13 +10835,13 @@
     </row>
     <row r="21" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="19" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B21" s="19" t="s">
         <v>208</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="D21" s="21"/>
       <c r="E21" s="21"/>
@@ -10823,13 +10878,13 @@
     </row>
     <row r="22" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="19" t="s">
+        <v>613</v>
+      </c>
+      <c r="B22" s="19" t="s">
         <v>614</v>
       </c>
-      <c r="B22" s="19" t="s">
+      <c r="C22" s="19" t="s">
         <v>615</v>
-      </c>
-      <c r="C22" s="19" t="s">
-        <v>616</v>
       </c>
       <c r="D22" s="21">
         <v>-4.7911549999999998</v>
@@ -10914,19 +10969,19 @@
     </row>
     <row r="23" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="19" t="s">
+        <v>619</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="C23" s="19" t="s">
         <v>620</v>
       </c>
-      <c r="B23" s="19" t="s">
-        <v>411</v>
-      </c>
-      <c r="C23" s="19" t="s">
-        <v>621</v>
-      </c>
       <c r="D23" s="24" t="s">
+        <v>859</v>
+      </c>
+      <c r="E23" s="24" t="s">
         <v>860</v>
-      </c>
-      <c r="E23" s="24" t="s">
-        <v>861</v>
       </c>
       <c r="F23" s="20">
         <v>46153</v>
@@ -11005,13 +11060,13 @@
     </row>
     <row r="24" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="19" t="s">
+        <v>624</v>
+      </c>
+      <c r="B24" s="19" t="s">
         <v>625</v>
       </c>
-      <c r="B24" s="19" t="s">
+      <c r="C24" s="19" t="s">
         <v>626</v>
-      </c>
-      <c r="C24" s="19" t="s">
-        <v>627</v>
       </c>
       <c r="D24" s="21"/>
       <c r="E24" s="21"/>
@@ -11048,19 +11103,19 @@
     </row>
     <row r="25" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B25" s="19" t="s">
         <v>235</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D25" s="24" t="s">
+        <v>869</v>
+      </c>
+      <c r="E25" s="24" t="s">
         <v>870</v>
-      </c>
-      <c r="E25" s="24" t="s">
-        <v>871</v>
       </c>
       <c r="F25" s="20">
         <v>46159</v>
@@ -11139,13 +11194,13 @@
     </row>
     <row r="26" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="B26" s="19" t="s">
+        <v>471</v>
+      </c>
+      <c r="C26" s="19" t="s">
         <v>636</v>
-      </c>
-      <c r="B26" s="19" t="s">
-        <v>472</v>
-      </c>
-      <c r="C26" s="19" t="s">
-        <v>637</v>
       </c>
       <c r="D26" s="21"/>
       <c r="E26" s="21"/>
@@ -11180,15 +11235,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="19" t="s">
+        <v>640</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>501</v>
+      </c>
+      <c r="C27" s="19" t="s">
         <v>641</v>
-      </c>
-      <c r="B27" s="19" t="s">
-        <v>502</v>
-      </c>
-      <c r="C27" s="19" t="s">
-        <v>642</v>
       </c>
       <c r="D27" s="24">
         <v>-5.0453950000000001</v>
@@ -11282,10 +11337,10 @@
         <v>203</v>
       </c>
       <c r="D28" s="24" t="s">
+        <v>853</v>
+      </c>
+      <c r="E28" s="24" t="s">
         <v>854</v>
-      </c>
-      <c r="E28" s="24" t="s">
-        <v>855</v>
       </c>
       <c r="F28" s="20">
         <v>46142</v>
@@ -11364,19 +11419,19 @@
     </row>
     <row r="29" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B29" s="19" t="s">
         <v>76</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D29" s="24" t="s">
+        <v>835</v>
+      </c>
+      <c r="E29" s="24" t="s">
         <v>836</v>
-      </c>
-      <c r="E29" s="24" t="s">
-        <v>837</v>
       </c>
       <c r="F29" s="20">
         <v>46139</v>
@@ -11455,13 +11510,13 @@
     </row>
     <row r="30" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B30" s="19" t="s">
         <v>104</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D30" s="21"/>
       <c r="E30" s="21"/>
@@ -11498,13 +11553,13 @@
     </row>
     <row r="31" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B31" s="19" t="s">
         <v>36</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="D31" s="21">
         <v>-4.2869089999999996</v>
@@ -11589,13 +11644,13 @@
     </row>
     <row r="32" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B32" s="19" t="s">
         <v>174</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="D32" s="21"/>
       <c r="E32" s="21"/>
@@ -11632,13 +11687,13 @@
     </row>
     <row r="33" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B33" s="19" t="s">
         <v>174</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="D33" s="24">
         <v>-2.8945319999999999</v>
@@ -11721,58 +11776,105 @@
         <v>4636</v>
       </c>
     </row>
-    <row r="34" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="19" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B34" s="19" t="s">
         <v>25</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>671</v>
-      </c>
-      <c r="D34" s="21"/>
-      <c r="E34" s="21"/>
-      <c r="F34" s="20"/>
+        <v>670</v>
+      </c>
+      <c r="D34" s="21">
+        <v>-4.5809499999999996</v>
+      </c>
+      <c r="E34" s="21">
+        <v>-37.849559999999997</v>
+      </c>
+      <c r="F34" s="20">
+        <v>46173</v>
+      </c>
       <c r="G34" s="20">
-        <f t="shared" si="0"/>
+        <v>46175</v>
+      </c>
+      <c r="H34" s="12">
+        <v>422</v>
+      </c>
+      <c r="I34" s="12">
+        <v>2047</v>
+      </c>
+      <c r="J34" s="12">
+        <v>41</v>
+      </c>
+      <c r="K34" s="12">
+        <v>270</v>
+      </c>
+      <c r="L34" s="12">
+        <v>59</v>
+      </c>
+      <c r="M34" s="12">
+        <v>18</v>
+      </c>
+      <c r="N34" s="12">
+        <v>6</v>
+      </c>
+      <c r="O34" s="12">
+        <v>0</v>
+      </c>
+      <c r="P34" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="12">
+        <v>6</v>
+      </c>
+      <c r="R34" s="12">
+        <v>4</v>
+      </c>
+      <c r="S34" s="12">
         <v>2</v>
       </c>
-      <c r="H34" s="12"/>
-      <c r="I34" s="12"/>
-      <c r="J34" s="12"/>
-      <c r="K34" s="12"/>
-      <c r="L34" s="12"/>
-      <c r="M34" s="12"/>
-      <c r="N34" s="12"/>
-      <c r="O34" s="12"/>
-      <c r="P34" s="12"/>
-      <c r="Q34" s="12"/>
-      <c r="R34" s="12"/>
-      <c r="S34" s="12"/>
-      <c r="T34" s="12"/>
-      <c r="U34" s="12"/>
-      <c r="V34" s="12"/>
-      <c r="W34" s="12"/>
-      <c r="X34" s="12"/>
-      <c r="Y34" s="12"/>
-      <c r="Z34" s="12"/>
-      <c r="AA34" s="12"/>
-      <c r="AB34" s="12"/>
+      <c r="T34" s="12">
+        <v>16</v>
+      </c>
+      <c r="U34" s="12">
+        <v>0</v>
+      </c>
+      <c r="V34" s="12">
+        <v>0</v>
+      </c>
+      <c r="W34" s="12">
+        <v>0</v>
+      </c>
+      <c r="X34" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="12">
+        <v>2</v>
+      </c>
+      <c r="AB34" s="12">
+        <v>0</v>
+      </c>
       <c r="AC34" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2893</v>
       </c>
     </row>
     <row r="35" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B35" s="19" t="s">
         <v>191</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="D35" s="21"/>
       <c r="E35" s="21"/>
@@ -11809,13 +11911,13 @@
     </row>
     <row r="36" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B36" s="19" t="s">
         <v>191</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="D36" s="24">
         <v>-5.4253080000000002</v>
@@ -11900,13 +12002,13 @@
     </row>
     <row r="37" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
+        <v>683</v>
+      </c>
+      <c r="B37" s="19" t="s">
         <v>684</v>
       </c>
-      <c r="B37" s="19" t="s">
+      <c r="C37" s="19" t="s">
         <v>685</v>
-      </c>
-      <c r="C37" s="19" t="s">
-        <v>686</v>
       </c>
       <c r="D37" s="21"/>
       <c r="E37" s="21"/>
@@ -11943,13 +12045,13 @@
     </row>
     <row r="38" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="19" t="s">
+        <v>689</v>
+      </c>
+      <c r="B38" s="19" t="s">
+        <v>684</v>
+      </c>
+      <c r="C38" s="19" t="s">
         <v>690</v>
-      </c>
-      <c r="B38" s="19" t="s">
-        <v>685</v>
-      </c>
-      <c r="C38" s="19" t="s">
-        <v>691</v>
       </c>
       <c r="D38" s="21"/>
       <c r="E38" s="21"/>
@@ -11986,13 +12088,13 @@
     </row>
     <row r="39" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="19" t="s">
+        <v>694</v>
+      </c>
+      <c r="B39" s="19" t="s">
         <v>695</v>
       </c>
-      <c r="B39" s="19" t="s">
+      <c r="C39" s="19" t="s">
         <v>696</v>
-      </c>
-      <c r="C39" s="19" t="s">
-        <v>697</v>
       </c>
       <c r="D39" s="21"/>
       <c r="E39" s="21"/>
@@ -12029,13 +12131,13 @@
     </row>
     <row r="40" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="19" t="s">
+        <v>700</v>
+      </c>
+      <c r="B40" s="19" t="s">
         <v>701</v>
       </c>
-      <c r="B40" s="19" t="s">
+      <c r="C40" s="19" t="s">
         <v>702</v>
-      </c>
-      <c r="C40" s="19" t="s">
-        <v>703</v>
       </c>
       <c r="D40" s="21"/>
       <c r="E40" s="21"/>
@@ -12072,13 +12174,13 @@
     </row>
     <row r="41" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="19" t="s">
+        <v>704</v>
+      </c>
+      <c r="B41" s="19" t="s">
         <v>705</v>
       </c>
-      <c r="B41" s="19" t="s">
+      <c r="C41" s="19" t="s">
         <v>706</v>
-      </c>
-      <c r="C41" s="19" t="s">
-        <v>707</v>
       </c>
       <c r="D41" s="21"/>
       <c r="E41" s="21"/>
@@ -12115,19 +12217,19 @@
     </row>
     <row r="42" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="19" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B42" s="19" t="s">
         <v>197</v>
       </c>
       <c r="C42" s="19" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="D42" s="24" t="s">
+        <v>837</v>
+      </c>
+      <c r="E42" s="24" t="s">
         <v>838</v>
-      </c>
-      <c r="E42" s="24" t="s">
-        <v>839</v>
       </c>
       <c r="F42" s="20">
         <v>46139</v>
@@ -12206,13 +12308,13 @@
     </row>
     <row r="43" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="19" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B43" s="19" t="s">
         <v>174</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D43" s="21"/>
       <c r="E43" s="21"/>
@@ -12249,13 +12351,13 @@
     </row>
     <row r="44" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="19" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B44" s="19" t="s">
         <v>266</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D44" s="21"/>
       <c r="E44" s="21"/>
@@ -12292,19 +12394,19 @@
     </row>
     <row r="45" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="19" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B45" s="19" t="s">
         <v>48</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="D45" s="24" t="s">
+        <v>861</v>
+      </c>
+      <c r="E45" s="24" t="s">
         <v>862</v>
-      </c>
-      <c r="E45" s="24" t="s">
-        <v>863</v>
       </c>
       <c r="F45" s="20">
         <v>46153</v>
@@ -12383,13 +12485,13 @@
     </row>
     <row r="46" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="19" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B46" s="19" t="s">
         <v>241</v>
       </c>
       <c r="C46" s="19" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="D46" s="21"/>
       <c r="E46" s="21"/>
@@ -12426,13 +12528,13 @@
     </row>
     <row r="47" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="19" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B47" s="19" t="s">
         <v>136</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="D47" s="21">
         <v>-5.4055679999999997</v>
@@ -12517,13 +12619,13 @@
     </row>
     <row r="48" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="19" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B48" s="19" t="s">
         <v>174</v>
       </c>
       <c r="C48" s="19" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="D48" s="24">
         <v>-2.9586229999999998</v>
@@ -12608,13 +12710,13 @@
     </row>
     <row r="49" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="19" t="s">
+        <v>744</v>
+      </c>
+      <c r="B49" s="19" t="s">
+        <v>555</v>
+      </c>
+      <c r="C49" s="19" t="s">
         <v>745</v>
-      </c>
-      <c r="B49" s="19" t="s">
-        <v>556</v>
-      </c>
-      <c r="C49" s="19" t="s">
-        <v>746</v>
       </c>
       <c r="D49" s="24">
         <v>-2.92225</v>
@@ -12699,13 +12801,13 @@
     </row>
     <row r="50" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="19" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B50" s="19" t="s">
         <v>48</v>
       </c>
       <c r="C50" s="19" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="D50" s="21">
         <v>-3.697114</v>
@@ -12790,13 +12892,13 @@
     </row>
     <row r="51" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="19" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B51" s="19" t="s">
         <v>58</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="D51" s="21">
         <v>-3.7188409999999998</v>
@@ -12881,13 +12983,13 @@
     </row>
     <row r="52" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="19" t="s">
+        <v>758</v>
+      </c>
+      <c r="B52" s="19" t="s">
+        <v>603</v>
+      </c>
+      <c r="C52" s="19" t="s">
         <v>759</v>
-      </c>
-      <c r="B52" s="19" t="s">
-        <v>604</v>
-      </c>
-      <c r="C52" s="19" t="s">
-        <v>760</v>
       </c>
       <c r="D52" s="21"/>
       <c r="E52" s="21"/>
@@ -12924,13 +13026,13 @@
     </row>
     <row r="53" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="19" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B53" s="19" t="s">
         <v>208</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D53" s="21"/>
       <c r="E53" s="21"/>
@@ -12967,13 +13069,13 @@
     </row>
     <row r="54" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="19" t="s">
+        <v>767</v>
+      </c>
+      <c r="B54" s="19" t="s">
+        <v>614</v>
+      </c>
+      <c r="C54" s="19" t="s">
         <v>768</v>
-      </c>
-      <c r="B54" s="19" t="s">
-        <v>615</v>
-      </c>
-      <c r="C54" s="19" t="s">
-        <v>769</v>
       </c>
       <c r="D54" s="21">
         <v>-4.5583349999999996</v>
@@ -13058,13 +13160,13 @@
     </row>
     <row r="55" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="19" t="s">
+        <v>772</v>
+      </c>
+      <c r="B55" s="19" t="s">
+        <v>614</v>
+      </c>
+      <c r="C55" s="19" t="s">
         <v>773</v>
-      </c>
-      <c r="B55" s="19" t="s">
-        <v>615</v>
-      </c>
-      <c r="C55" s="19" t="s">
-        <v>774</v>
       </c>
       <c r="D55" s="21">
         <v>-5.1463979999999996</v>
@@ -13149,13 +13251,13 @@
     </row>
     <row r="56" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="19" t="s">
+        <v>777</v>
+      </c>
+      <c r="B56" s="19" t="s">
         <v>778</v>
       </c>
-      <c r="B56" s="19" t="s">
+      <c r="C56" s="19" t="s">
         <v>779</v>
-      </c>
-      <c r="C56" s="19" t="s">
-        <v>780</v>
       </c>
       <c r="D56" s="21"/>
       <c r="E56" s="21"/>
@@ -13192,19 +13294,19 @@
     </row>
     <row r="57" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="19" t="s">
+        <v>783</v>
+      </c>
+      <c r="B57" s="19" t="s">
         <v>784</v>
       </c>
-      <c r="B57" s="19" t="s">
+      <c r="C57" s="19" t="s">
         <v>785</v>
       </c>
-      <c r="C57" s="19" t="s">
-        <v>786</v>
-      </c>
       <c r="D57" s="24" t="s">
+        <v>871</v>
+      </c>
+      <c r="E57" s="24" t="s">
         <v>872</v>
-      </c>
-      <c r="E57" s="24" t="s">
-        <v>873</v>
       </c>
       <c r="F57" s="20">
         <v>46159</v>
@@ -13283,19 +13385,19 @@
     </row>
     <row r="58" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="19" t="s">
+        <v>789</v>
+      </c>
+      <c r="B58" s="19" t="s">
+        <v>784</v>
+      </c>
+      <c r="C58" s="19" t="s">
         <v>790</v>
       </c>
-      <c r="B58" s="19" t="s">
-        <v>785</v>
-      </c>
-      <c r="C58" s="19" t="s">
-        <v>791</v>
-      </c>
       <c r="D58" s="24" t="s">
+        <v>873</v>
+      </c>
+      <c r="E58" s="24" t="s">
         <v>874</v>
-      </c>
-      <c r="E58" s="24" t="s">
-        <v>875</v>
       </c>
       <c r="F58" s="20">
         <v>46159</v>
@@ -13374,19 +13476,19 @@
     </row>
     <row r="59" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="19" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B59" s="19" t="s">
         <v>48</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="D59" s="24" t="s">
+        <v>875</v>
+      </c>
+      <c r="E59" s="24" t="s">
         <v>876</v>
-      </c>
-      <c r="E59" s="24" t="s">
-        <v>877</v>
       </c>
       <c r="F59" s="20">
         <v>46159</v>
@@ -13465,13 +13567,13 @@
     </row>
     <row r="60" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="19" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B60" s="19" t="s">
         <v>148</v>
       </c>
       <c r="C60" s="19" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D60" s="21">
         <v>-4.228675</v>
@@ -13556,13 +13658,13 @@
     </row>
     <row r="61" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="19" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B61" s="19" t="s">
         <v>148</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D61" s="21"/>
       <c r="E61" s="21"/>
@@ -13599,13 +13701,13 @@
     </row>
     <row r="62" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="19" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B62" s="19" t="s">
         <v>148</v>
       </c>
       <c r="C62" s="19" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D62" s="21"/>
       <c r="E62" s="21"/>
@@ -13642,13 +13744,13 @@
     </row>
     <row r="63" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="19" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B63" s="19" t="s">
         <v>87</v>
       </c>
       <c r="C63" s="19" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D63" s="21">
         <v>-4.5644640000000001</v>
@@ -13731,58 +13833,105 @@
         <v>2906</v>
       </c>
     </row>
-    <row r="64" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="19" t="s">
+        <v>334</v>
+      </c>
+      <c r="B64" s="19" t="s">
         <v>335</v>
       </c>
-      <c r="B64" s="19" t="s">
+      <c r="C64" s="19" t="s">
         <v>336</v>
       </c>
-      <c r="C64" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="D64" s="21"/>
-      <c r="E64" s="21"/>
-      <c r="F64" s="20"/>
+      <c r="D64" s="21">
+        <v>-4.7203499999999998</v>
+      </c>
+      <c r="E64" s="21">
+        <v>-37.548859999999998</v>
+      </c>
+      <c r="F64" s="20">
+        <v>46173</v>
+      </c>
       <c r="G64" s="20">
-        <f t="shared" si="0"/>
+        <v>46175</v>
+      </c>
+      <c r="H64" s="12">
+        <v>191</v>
+      </c>
+      <c r="I64" s="12">
+        <v>2297</v>
+      </c>
+      <c r="J64" s="12">
+        <v>41</v>
+      </c>
+      <c r="K64" s="12">
+        <v>127</v>
+      </c>
+      <c r="L64" s="12">
+        <v>11</v>
+      </c>
+      <c r="M64" s="12">
+        <v>14</v>
+      </c>
+      <c r="N64" s="12">
+        <v>6</v>
+      </c>
+      <c r="O64" s="12">
+        <v>0</v>
+      </c>
+      <c r="P64" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="12">
+        <v>0</v>
+      </c>
+      <c r="R64" s="12">
+        <v>3</v>
+      </c>
+      <c r="S64" s="12">
+        <v>4</v>
+      </c>
+      <c r="T64" s="12">
+        <v>9</v>
+      </c>
+      <c r="U64" s="12">
         <v>2</v>
       </c>
-      <c r="H64" s="12"/>
-      <c r="I64" s="12"/>
-      <c r="J64" s="12"/>
-      <c r="K64" s="12"/>
-      <c r="L64" s="12"/>
-      <c r="M64" s="12"/>
-      <c r="N64" s="12"/>
-      <c r="O64" s="12"/>
-      <c r="P64" s="12"/>
-      <c r="Q64" s="12"/>
-      <c r="R64" s="12"/>
-      <c r="S64" s="12"/>
-      <c r="T64" s="12"/>
-      <c r="U64" s="12"/>
-      <c r="V64" s="12"/>
-      <c r="W64" s="12"/>
-      <c r="X64" s="12"/>
-      <c r="Y64" s="12"/>
-      <c r="Z64" s="12"/>
-      <c r="AA64" s="12"/>
-      <c r="AB64" s="12"/>
+      <c r="V64" s="12">
+        <v>0</v>
+      </c>
+      <c r="W64" s="12">
+        <v>0</v>
+      </c>
+      <c r="X64" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z64" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA64" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB64" s="12">
+        <v>0</v>
+      </c>
       <c r="AC64" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>2705</v>
+      </c>
+    </row>
+    <row r="65" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="19" t="s">
+        <v>340</v>
+      </c>
+      <c r="B65" s="19" t="s">
         <v>341</v>
       </c>
-      <c r="B65" s="19" t="s">
+      <c r="C65" s="19" t="s">
         <v>342</v>
-      </c>
-      <c r="C65" s="19" t="s">
-        <v>343</v>
       </c>
       <c r="D65" s="24">
         <v>-4.8210379999999997</v>
@@ -13958,13 +14107,13 @@
     </row>
     <row r="67" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="19" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B67" s="19" t="s">
         <v>12</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D67" s="21">
         <v>-4.702947</v>
@@ -14049,13 +14198,13 @@
     </row>
     <row r="68" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="19" t="s">
+        <v>350</v>
+      </c>
+      <c r="B68" s="19" t="s">
         <v>351</v>
       </c>
-      <c r="B68" s="19" t="s">
+      <c r="C68" s="19" t="s">
         <v>352</v>
-      </c>
-      <c r="C68" s="19" t="s">
-        <v>353</v>
       </c>
       <c r="D68" s="24">
         <v>-5.2215020000000001</v>
@@ -14140,13 +14289,13 @@
     </row>
     <row r="69" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="19" t="s">
+        <v>356</v>
+      </c>
+      <c r="B69" s="19" t="s">
         <v>357</v>
       </c>
-      <c r="B69" s="19" t="s">
+      <c r="C69" s="19" t="s">
         <v>358</v>
-      </c>
-      <c r="C69" s="19" t="s">
-        <v>359</v>
       </c>
       <c r="D69" s="24">
         <v>-5.2506180000000002</v>
@@ -14231,13 +14380,13 @@
     </row>
     <row r="70" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="19" t="s">
+        <v>361</v>
+      </c>
+      <c r="B70" s="19" t="s">
         <v>362</v>
       </c>
-      <c r="B70" s="19" t="s">
+      <c r="C70" s="19" t="s">
         <v>363</v>
-      </c>
-      <c r="C70" s="19" t="s">
-        <v>364</v>
       </c>
       <c r="D70" s="24">
         <v>-5.4016780000000004</v>
@@ -14322,13 +14471,13 @@
     </row>
     <row r="71" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="19" t="s">
+        <v>367</v>
+      </c>
+      <c r="B71" s="19" t="s">
         <v>368</v>
       </c>
-      <c r="B71" s="19" t="s">
+      <c r="C71" s="19" t="s">
         <v>369</v>
-      </c>
-      <c r="C71" s="19" t="s">
-        <v>370</v>
       </c>
       <c r="D71" s="21"/>
       <c r="E71" s="21"/>
@@ -14365,13 +14514,13 @@
     </row>
     <row r="72" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="19" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B72" s="19" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="C72" s="19" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="D72" s="21"/>
       <c r="E72" s="21"/>
@@ -14408,13 +14557,13 @@
     </row>
     <row r="73" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="B73" s="19" t="s">
         <v>376</v>
       </c>
-      <c r="B73" s="19" t="s">
+      <c r="C73" s="19" t="s">
         <v>377</v>
-      </c>
-      <c r="C73" s="19" t="s">
-        <v>378</v>
       </c>
       <c r="D73" s="21"/>
       <c r="E73" s="21"/>
@@ -14451,13 +14600,13 @@
     </row>
     <row r="74" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="19" t="s">
+        <v>381</v>
+      </c>
+      <c r="B74" s="19" t="s">
+        <v>376</v>
+      </c>
+      <c r="C74" s="19" t="s">
         <v>382</v>
-      </c>
-      <c r="B74" s="19" t="s">
-        <v>377</v>
-      </c>
-      <c r="C74" s="19" t="s">
-        <v>383</v>
       </c>
       <c r="D74" s="21"/>
       <c r="E74" s="21"/>
@@ -14494,13 +14643,13 @@
     </row>
     <row r="75" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="19" t="s">
+        <v>386</v>
+      </c>
+      <c r="B75" s="19" t="s">
         <v>387</v>
       </c>
-      <c r="B75" s="19" t="s">
+      <c r="C75" s="19" t="s">
         <v>388</v>
-      </c>
-      <c r="C75" s="19" t="s">
-        <v>389</v>
       </c>
       <c r="D75" s="21"/>
       <c r="E75" s="21"/>
@@ -14537,13 +14686,13 @@
     </row>
     <row r="76" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="19" t="s">
+        <v>392</v>
+      </c>
+      <c r="B76" s="19" t="s">
         <v>393</v>
       </c>
-      <c r="B76" s="19" t="s">
+      <c r="C76" s="19" t="s">
         <v>394</v>
-      </c>
-      <c r="C76" s="19" t="s">
-        <v>395</v>
       </c>
       <c r="D76" s="21"/>
       <c r="E76" s="21"/>
@@ -14580,13 +14729,13 @@
     </row>
     <row r="77" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="19" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B77" s="19" t="s">
         <v>272</v>
       </c>
       <c r="C77" s="19" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D77" s="21"/>
       <c r="E77" s="21"/>
@@ -14623,13 +14772,13 @@
     </row>
     <row r="78" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="19" t="s">
+        <v>403</v>
+      </c>
+      <c r="B78" s="19" t="s">
         <v>404</v>
       </c>
-      <c r="B78" s="19" t="s">
+      <c r="C78" s="19" t="s">
         <v>405</v>
-      </c>
-      <c r="C78" s="19" t="s">
-        <v>406</v>
       </c>
       <c r="D78" s="21"/>
       <c r="E78" s="21"/>
@@ -14666,13 +14815,13 @@
     </row>
     <row r="79" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="B79" s="19" t="s">
         <v>410</v>
       </c>
-      <c r="B79" s="19" t="s">
+      <c r="C79" s="19" t="s">
         <v>411</v>
-      </c>
-      <c r="C79" s="19" t="s">
-        <v>412</v>
       </c>
       <c r="D79" s="21"/>
       <c r="E79" s="21"/>
@@ -14709,19 +14858,19 @@
     </row>
     <row r="80" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="19" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B80" s="19" t="s">
         <v>266</v>
       </c>
       <c r="C80" s="19" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D80" s="24" t="s">
+        <v>863</v>
+      </c>
+      <c r="E80" s="24" t="s">
         <v>864</v>
-      </c>
-      <c r="E80" s="24" t="s">
-        <v>865</v>
       </c>
       <c r="F80" s="20">
         <v>46153</v>
@@ -14800,19 +14949,19 @@
     </row>
     <row r="81" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="19" t="s">
+        <v>420</v>
+      </c>
+      <c r="B81" s="19" t="s">
         <v>421</v>
       </c>
-      <c r="B81" s="19" t="s">
+      <c r="C81" s="19" t="s">
         <v>422</v>
       </c>
-      <c r="C81" s="19" t="s">
-        <v>423</v>
-      </c>
       <c r="D81" s="24" t="s">
+        <v>867</v>
+      </c>
+      <c r="E81" s="24" t="s">
         <v>868</v>
-      </c>
-      <c r="E81" s="24" t="s">
-        <v>869</v>
       </c>
       <c r="F81" s="20">
         <v>46153</v>
@@ -14891,13 +15040,13 @@
     </row>
     <row r="82" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="19" t="s">
+        <v>426</v>
+      </c>
+      <c r="B82" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="C82" s="19" t="s">
         <v>427</v>
-      </c>
-      <c r="B82" s="19" t="s">
-        <v>411</v>
-      </c>
-      <c r="C82" s="19" t="s">
-        <v>428</v>
       </c>
       <c r="D82" s="21"/>
       <c r="E82" s="21"/>
@@ -14934,13 +15083,13 @@
     </row>
     <row r="83" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="19" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B83" s="19" t="s">
         <v>229</v>
       </c>
       <c r="C83" s="19" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D83" s="21">
         <v>-4.3755519999999999</v>
@@ -15023,15 +15172,15 @@
         <v>6031</v>
       </c>
     </row>
-    <row r="84" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="19" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B84" s="19" t="s">
         <v>229</v>
       </c>
       <c r="C84" s="19" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D84" s="24">
         <v>-5.041658</v>
@@ -15116,13 +15265,13 @@
     </row>
     <row r="85" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="19" t="s">
+        <v>440</v>
+      </c>
+      <c r="B85" s="19" t="s">
         <v>441</v>
       </c>
-      <c r="B85" s="19" t="s">
+      <c r="C85" s="19" t="s">
         <v>442</v>
-      </c>
-      <c r="C85" s="19" t="s">
-        <v>443</v>
       </c>
       <c r="D85" s="24">
         <v>-5.2738310000000004</v>
@@ -15207,13 +15356,13 @@
     </row>
     <row r="86" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="19" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B86" s="19" t="s">
         <v>97</v>
       </c>
       <c r="C86" s="19" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D86" s="21"/>
       <c r="E86" s="21"/>
@@ -15250,13 +15399,13 @@
     </row>
     <row r="87" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="19" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B87" s="19" t="s">
         <v>235</v>
       </c>
       <c r="C87" s="19" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D87" s="21"/>
       <c r="E87" s="21"/>
@@ -15293,13 +15442,13 @@
     </row>
     <row r="88" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="19" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B88" s="19" t="s">
         <v>235</v>
       </c>
       <c r="C88" s="19" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D88" s="21">
         <v>-3.6184599999999998</v>
@@ -15384,13 +15533,13 @@
     </row>
     <row r="89" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="19" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B89" s="19" t="s">
         <v>235</v>
       </c>
       <c r="C89" s="19" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D89" s="21"/>
       <c r="E89" s="21"/>
@@ -15427,19 +15576,19 @@
     </row>
     <row r="90" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="19" t="s">
+        <v>466</v>
+      </c>
+      <c r="B90" s="19" t="s">
         <v>467</v>
       </c>
-      <c r="B90" s="19" t="s">
+      <c r="C90" s="19" t="s">
         <v>468</v>
       </c>
-      <c r="C90" s="19" t="s">
-        <v>469</v>
-      </c>
       <c r="D90" s="24" t="s">
+        <v>839</v>
+      </c>
+      <c r="E90" s="24" t="s">
         <v>840</v>
-      </c>
-      <c r="E90" s="24" t="s">
-        <v>841</v>
       </c>
       <c r="F90" s="20">
         <v>46139</v>
@@ -15518,13 +15667,13 @@
     </row>
     <row r="91" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="19" t="s">
+        <v>470</v>
+      </c>
+      <c r="B91" s="19" t="s">
         <v>471</v>
       </c>
-      <c r="B91" s="19" t="s">
+      <c r="C91" s="19" t="s">
         <v>472</v>
-      </c>
-      <c r="C91" s="19" t="s">
-        <v>473</v>
       </c>
       <c r="D91" s="21"/>
       <c r="E91" s="21"/>
@@ -15561,19 +15710,19 @@
     </row>
     <row r="92" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="19" t="s">
+        <v>476</v>
+      </c>
+      <c r="B92" s="19" t="s">
+        <v>471</v>
+      </c>
+      <c r="C92" s="19" t="s">
         <v>477</v>
       </c>
-      <c r="B92" s="19" t="s">
-        <v>472</v>
-      </c>
-      <c r="C92" s="19" t="s">
-        <v>478</v>
-      </c>
       <c r="D92" s="24" t="s">
+        <v>877</v>
+      </c>
+      <c r="E92" s="24" t="s">
         <v>878</v>
-      </c>
-      <c r="E92" s="24" t="s">
-        <v>879</v>
       </c>
       <c r="F92" s="20">
         <v>46159</v>
@@ -15652,19 +15801,19 @@
     </row>
     <row r="93" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="19" t="s">
+        <v>480</v>
+      </c>
+      <c r="B93" s="19" t="s">
         <v>481</v>
       </c>
-      <c r="B93" s="19" t="s">
+      <c r="C93" s="19" t="s">
         <v>482</v>
       </c>
-      <c r="C93" s="19" t="s">
-        <v>483</v>
-      </c>
       <c r="D93" s="24" t="s">
+        <v>855</v>
+      </c>
+      <c r="E93" s="24" t="s">
         <v>856</v>
-      </c>
-      <c r="E93" s="24" t="s">
-        <v>857</v>
       </c>
       <c r="F93" s="20">
         <v>46142</v>
@@ -15746,10 +15895,10 @@
         <v>153</v>
       </c>
       <c r="B94" s="19" t="s">
+        <v>829</v>
+      </c>
+      <c r="C94" s="19" t="s">
         <v>830</v>
-      </c>
-      <c r="C94" s="19" t="s">
-        <v>831</v>
       </c>
       <c r="D94" s="21">
         <v>-5.0822029999999998</v>
@@ -15834,13 +15983,13 @@
     </row>
     <row r="95" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="19" t="s">
+        <v>486</v>
+      </c>
+      <c r="B95" s="19" t="s">
         <v>487</v>
       </c>
-      <c r="B95" s="19" t="s">
+      <c r="C95" s="19" t="s">
         <v>488</v>
-      </c>
-      <c r="C95" s="19" t="s">
-        <v>489</v>
       </c>
       <c r="D95" s="24">
         <v>-5.4022300000000003</v>
@@ -15925,19 +16074,19 @@
     </row>
     <row r="96" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="19" t="s">
+        <v>492</v>
+      </c>
+      <c r="B96" s="19" t="s">
+        <v>487</v>
+      </c>
+      <c r="C96" s="19" t="s">
         <v>493</v>
       </c>
-      <c r="B96" s="19" t="s">
-        <v>488</v>
-      </c>
-      <c r="C96" s="19" t="s">
-        <v>494</v>
-      </c>
       <c r="D96" s="24" t="s">
+        <v>841</v>
+      </c>
+      <c r="E96" s="24" t="s">
         <v>842</v>
-      </c>
-      <c r="E96" s="24" t="s">
-        <v>843</v>
       </c>
       <c r="F96" s="20">
         <v>46139</v>
@@ -16016,19 +16165,19 @@
     </row>
     <row r="97" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="19" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B97" s="19" t="s">
         <v>136</v>
       </c>
       <c r="C97" s="19" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D97" s="24" t="s">
+        <v>843</v>
+      </c>
+      <c r="E97" s="24" t="s">
         <v>844</v>
-      </c>
-      <c r="E97" s="24" t="s">
-        <v>845</v>
       </c>
       <c r="F97" s="20">
         <v>46139</v>
@@ -16107,13 +16256,13 @@
     </row>
     <row r="98" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="19" t="s">
+        <v>500</v>
+      </c>
+      <c r="B98" s="19" t="s">
         <v>501</v>
       </c>
-      <c r="B98" s="19" t="s">
+      <c r="C98" s="19" t="s">
         <v>502</v>
-      </c>
-      <c r="C98" s="19" t="s">
-        <v>503</v>
       </c>
       <c r="D98" s="24">
         <v>-5.0848469999999999</v>
@@ -16198,13 +16347,13 @@
     </row>
     <row r="99" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="19" t="s">
+        <v>506</v>
+      </c>
+      <c r="B99" s="19" t="s">
+        <v>501</v>
+      </c>
+      <c r="C99" s="19" t="s">
         <v>507</v>
-      </c>
-      <c r="B99" s="19" t="s">
-        <v>502</v>
-      </c>
-      <c r="C99" s="19" t="s">
-        <v>508</v>
       </c>
       <c r="D99" s="24">
         <v>-5.2461500000000001</v>
@@ -16289,13 +16438,13 @@
     </row>
     <row r="100" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="19" t="s">
+        <v>511</v>
+      </c>
+      <c r="B100" s="19" t="s">
+        <v>376</v>
+      </c>
+      <c r="C100" s="19" t="s">
         <v>512</v>
-      </c>
-      <c r="B100" s="19" t="s">
-        <v>377</v>
-      </c>
-      <c r="C100" s="19" t="s">
-        <v>513</v>
       </c>
       <c r="D100" s="21"/>
       <c r="E100" s="21"/>
@@ -16332,13 +16481,13 @@
     </row>
     <row r="101" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="19" t="s">
+        <v>516</v>
+      </c>
+      <c r="B101" s="19" t="s">
         <v>517</v>
       </c>
-      <c r="B101" s="19" t="s">
+      <c r="C101" s="19" t="s">
         <v>518</v>
-      </c>
-      <c r="C101" s="19" t="s">
-        <v>519</v>
       </c>
       <c r="D101" s="21"/>
       <c r="E101" s="21"/>
@@ -16375,13 +16524,13 @@
     </row>
     <row r="102" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="19" t="s">
+        <v>522</v>
+      </c>
+      <c r="B102" s="19" t="s">
         <v>523</v>
       </c>
-      <c r="B102" s="19" t="s">
+      <c r="C102" s="19" t="s">
         <v>524</v>
-      </c>
-      <c r="C102" s="19" t="s">
-        <v>525</v>
       </c>
       <c r="D102" s="21"/>
       <c r="E102" s="21"/>
@@ -16424,7 +16573,7 @@
         <v>165</v>
       </c>
       <c r="C103" s="19" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="D103" s="21">
         <v>-4.8596729999999999</v>
@@ -16509,13 +16658,13 @@
     </row>
     <row r="104" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="19" t="s">
+        <v>528</v>
+      </c>
+      <c r="B104" s="19" t="s">
         <v>529</v>
       </c>
-      <c r="B104" s="19" t="s">
+      <c r="C104" s="19" t="s">
         <v>530</v>
-      </c>
-      <c r="C104" s="19" t="s">
-        <v>531</v>
       </c>
       <c r="D104" s="21">
         <v>-4.4447369999999999</v>
@@ -16600,13 +16749,13 @@
     </row>
     <row r="105" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="19" t="s">
+        <v>534</v>
+      </c>
+      <c r="B105" s="19" t="s">
         <v>535</v>
       </c>
-      <c r="B105" s="19" t="s">
+      <c r="C105" s="19" t="s">
         <v>536</v>
-      </c>
-      <c r="C105" s="19" t="s">
-        <v>537</v>
       </c>
       <c r="D105" s="21">
         <v>-5.1705110000000003</v>
@@ -16689,58 +16838,105 @@
         <v>2124</v>
       </c>
     </row>
-    <row r="106" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="19" t="s">
+        <v>540</v>
+      </c>
+      <c r="B106" s="19" t="s">
+        <v>487</v>
+      </c>
+      <c r="C106" s="19" t="s">
         <v>541</v>
       </c>
-      <c r="B106" s="19" t="s">
-        <v>488</v>
-      </c>
-      <c r="C106" s="19" t="s">
-        <v>542</v>
-      </c>
-      <c r="D106" s="21"/>
-      <c r="E106" s="21"/>
-      <c r="F106" s="20"/>
+      <c r="D106" s="21">
+        <v>-4.5701299999999998</v>
+      </c>
+      <c r="E106" s="21">
+        <v>-37.734990000000003</v>
+      </c>
+      <c r="F106" s="20">
+        <v>46173</v>
+      </c>
       <c r="G106" s="20">
-        <f t="shared" si="5"/>
+        <v>46175</v>
+      </c>
+      <c r="H106" s="12">
+        <v>1508</v>
+      </c>
+      <c r="I106" s="12">
+        <v>4085</v>
+      </c>
+      <c r="J106" s="12">
+        <v>115</v>
+      </c>
+      <c r="K106" s="12">
+        <v>302</v>
+      </c>
+      <c r="L106" s="12">
+        <v>40</v>
+      </c>
+      <c r="M106" s="12">
+        <v>10</v>
+      </c>
+      <c r="N106" s="12">
+        <v>47</v>
+      </c>
+      <c r="O106" s="12">
+        <v>1</v>
+      </c>
+      <c r="P106" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q106" s="12">
+        <v>0</v>
+      </c>
+      <c r="R106" s="12">
         <v>2</v>
       </c>
-      <c r="H106" s="12"/>
-      <c r="I106" s="12"/>
-      <c r="J106" s="12"/>
-      <c r="K106" s="12"/>
-      <c r="L106" s="12"/>
-      <c r="M106" s="12"/>
-      <c r="N106" s="12"/>
-      <c r="O106" s="12"/>
-      <c r="P106" s="12"/>
-      <c r="Q106" s="12"/>
-      <c r="R106" s="12"/>
-      <c r="S106" s="12"/>
-      <c r="T106" s="12"/>
-      <c r="U106" s="12"/>
-      <c r="V106" s="12"/>
-      <c r="W106" s="12"/>
-      <c r="X106" s="12"/>
-      <c r="Y106" s="12"/>
-      <c r="Z106" s="12"/>
-      <c r="AA106" s="12"/>
-      <c r="AB106" s="12"/>
+      <c r="S106" s="12">
+        <v>1</v>
+      </c>
+      <c r="T106" s="12">
+        <v>53</v>
+      </c>
+      <c r="U106" s="12">
+        <v>1</v>
+      </c>
+      <c r="V106" s="12">
+        <v>1</v>
+      </c>
+      <c r="W106" s="12">
+        <v>0</v>
+      </c>
+      <c r="X106" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y106" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z106" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA106" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB106" s="12">
+        <v>0</v>
+      </c>
       <c r="AC106" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6166</v>
       </c>
     </row>
     <row r="107" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="19" t="s">
+        <v>545</v>
+      </c>
+      <c r="B107" s="19" t="s">
+        <v>357</v>
+      </c>
+      <c r="C107" s="19" t="s">
         <v>546</v>
-      </c>
-      <c r="B107" s="19" t="s">
-        <v>358</v>
-      </c>
-      <c r="C107" s="19" t="s">
-        <v>547</v>
       </c>
       <c r="D107" s="21"/>
       <c r="E107" s="21"/>
@@ -16786,10 +16982,10 @@
         <v>171</v>
       </c>
       <c r="D108" s="24" t="s">
+        <v>857</v>
+      </c>
+      <c r="E108" s="24" t="s">
         <v>858</v>
-      </c>
-      <c r="E108" s="24" t="s">
-        <v>859</v>
       </c>
       <c r="F108" s="20">
         <v>46142</v>
@@ -16868,13 +17064,13 @@
     </row>
     <row r="109" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="19" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B109" s="19" t="s">
         <v>42</v>
       </c>
       <c r="C109" s="19" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D109" s="21"/>
       <c r="E109" s="21"/>
@@ -16911,13 +17107,13 @@
     </row>
     <row r="110" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="19" t="s">
+        <v>554</v>
+      </c>
+      <c r="B110" s="19" t="s">
         <v>555</v>
       </c>
-      <c r="B110" s="19" t="s">
+      <c r="C110" s="19" t="s">
         <v>556</v>
-      </c>
-      <c r="C110" s="19" t="s">
-        <v>557</v>
       </c>
       <c r="D110" s="21">
         <v>-3.6978119999999999</v>
@@ -17002,13 +17198,13 @@
     </row>
     <row r="111" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="19" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B111" s="19" t="s">
         <v>208</v>
       </c>
       <c r="C111" s="19" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D111" s="21">
         <v>-5.2113269999999998</v>
@@ -17093,13 +17289,13 @@
     </row>
     <row r="112" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="19" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B112" s="19" t="s">
         <v>208</v>
       </c>
       <c r="C112" s="19" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="D112" s="21">
         <v>-4.3822749999999999</v>
@@ -17184,13 +17380,13 @@
     </row>
     <row r="113" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="19" t="s">
+        <v>570</v>
+      </c>
+      <c r="B113" s="19" t="s">
         <v>571</v>
       </c>
-      <c r="B113" s="19" t="s">
+      <c r="C113" s="19" t="s">
         <v>572</v>
-      </c>
-      <c r="C113" s="19" t="s">
-        <v>573</v>
       </c>
       <c r="D113" s="21"/>
       <c r="E113" s="21"/>
@@ -17227,13 +17423,13 @@
     </row>
     <row r="114" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="19" t="s">
+        <v>576</v>
+      </c>
+      <c r="B114" s="19" t="s">
+        <v>487</v>
+      </c>
+      <c r="C114" s="19" t="s">
         <v>577</v>
-      </c>
-      <c r="B114" s="19" t="s">
-        <v>488</v>
-      </c>
-      <c r="C114" s="19" t="s">
-        <v>578</v>
       </c>
       <c r="D114" s="24">
         <v>-5.2495240000000001</v>
@@ -17318,13 +17514,13 @@
     </row>
     <row r="115" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="19" t="s">
+        <v>581</v>
+      </c>
+      <c r="B115" s="19" t="s">
         <v>582</v>
       </c>
-      <c r="B115" s="19" t="s">
+      <c r="C115" s="19" t="s">
         <v>583</v>
-      </c>
-      <c r="C115" s="19" t="s">
-        <v>584</v>
       </c>
       <c r="D115" s="21"/>
       <c r="E115" s="21"/>
@@ -17361,13 +17557,13 @@
     </row>
     <row r="116" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="19" t="s">
+        <v>587</v>
+      </c>
+      <c r="B116" s="19" t="s">
         <v>588</v>
       </c>
-      <c r="B116" s="19" t="s">
+      <c r="C116" s="19" t="s">
         <v>589</v>
-      </c>
-      <c r="C116" s="19" t="s">
-        <v>590</v>
       </c>
       <c r="D116" s="21"/>
       <c r="E116" s="21"/>
@@ -17402,58 +17598,105 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="19" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B117" s="19" t="s">
         <v>142</v>
       </c>
       <c r="C117" s="19" t="s">
-        <v>594</v>
-      </c>
-      <c r="D117" s="21"/>
-      <c r="E117" s="21"/>
-      <c r="F117" s="20"/>
+        <v>593</v>
+      </c>
+      <c r="D117" s="21">
+        <v>-4.5799000000000003</v>
+      </c>
+      <c r="E117" s="21">
+        <v>-37.851900000000001</v>
+      </c>
+      <c r="F117" s="20">
+        <v>46173</v>
+      </c>
       <c r="G117" s="20">
-        <f t="shared" si="5"/>
+        <v>46175</v>
+      </c>
+      <c r="H117" s="12">
+        <v>648</v>
+      </c>
+      <c r="I117" s="12">
+        <v>1856</v>
+      </c>
+      <c r="J117" s="12">
+        <v>44</v>
+      </c>
+      <c r="K117" s="12">
+        <v>242</v>
+      </c>
+      <c r="L117" s="12">
+        <v>109</v>
+      </c>
+      <c r="M117" s="12">
+        <v>17</v>
+      </c>
+      <c r="N117" s="12">
+        <v>132</v>
+      </c>
+      <c r="O117" s="12">
+        <v>53</v>
+      </c>
+      <c r="P117" s="12">
+        <v>13</v>
+      </c>
+      <c r="Q117" s="12">
+        <v>50</v>
+      </c>
+      <c r="R117" s="12">
+        <v>101</v>
+      </c>
+      <c r="S117" s="12">
+        <v>3</v>
+      </c>
+      <c r="T117" s="12">
+        <v>49</v>
+      </c>
+      <c r="U117" s="12">
+        <v>5</v>
+      </c>
+      <c r="V117" s="12">
         <v>2</v>
       </c>
-      <c r="H117" s="12"/>
-      <c r="I117" s="12"/>
-      <c r="J117" s="12"/>
-      <c r="K117" s="12"/>
-      <c r="L117" s="12"/>
-      <c r="M117" s="12"/>
-      <c r="N117" s="12"/>
-      <c r="O117" s="12"/>
-      <c r="P117" s="12"/>
-      <c r="Q117" s="12"/>
-      <c r="R117" s="12"/>
-      <c r="S117" s="12"/>
-      <c r="T117" s="12"/>
-      <c r="U117" s="12"/>
-      <c r="V117" s="12"/>
-      <c r="W117" s="12"/>
-      <c r="X117" s="12"/>
-      <c r="Y117" s="12"/>
-      <c r="Z117" s="12"/>
-      <c r="AA117" s="12"/>
-      <c r="AB117" s="12"/>
+      <c r="W117" s="12">
+        <v>16</v>
+      </c>
+      <c r="X117" s="12">
+        <v>11</v>
+      </c>
+      <c r="Y117" s="12">
+        <v>2</v>
+      </c>
+      <c r="Z117" s="12">
+        <v>37</v>
+      </c>
+      <c r="AA117" s="12">
+        <v>61</v>
+      </c>
+      <c r="AB117" s="12">
+        <v>19</v>
+      </c>
       <c r="AC117" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3470</v>
       </c>
     </row>
     <row r="118" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="19" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B118" s="19" t="s">
         <v>104</v>
       </c>
       <c r="C118" s="19" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="D118" s="21"/>
       <c r="E118" s="21"/>
@@ -17670,7 +17913,7 @@
         <v>1773</v>
       </c>
     </row>
-    <row r="121" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="19" t="s">
         <v>24</v>
       </c>
@@ -19375,10 +19618,10 @@
         <v>247</v>
       </c>
       <c r="D147" s="24" t="s">
+        <v>865</v>
+      </c>
+      <c r="E147" s="24" t="s">
         <v>866</v>
-      </c>
-      <c r="E147" s="24" t="s">
-        <v>867</v>
       </c>
       <c r="F147" s="20">
         <v>46153</v>
@@ -19629,13 +19872,13 @@
     </row>
     <row r="152" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="19" t="s">
+        <v>302</v>
+      </c>
+      <c r="B152" s="19" t="s">
         <v>303</v>
       </c>
-      <c r="B152" s="19" t="s">
+      <c r="C152" s="19" t="s">
         <v>304</v>
-      </c>
-      <c r="C152" s="19" t="s">
-        <v>305</v>
       </c>
       <c r="D152" s="21">
         <v>-4.5677839999999996</v>
@@ -19720,13 +19963,13 @@
     </row>
     <row r="153" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B153" s="19" t="s">
         <v>136</v>
       </c>
       <c r="C153" s="19" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D153" s="21"/>
       <c r="E153" s="21"/>
@@ -19783,11 +20026,11 @@
   <autoFilter ref="A4:AC153" xr:uid="{1D18A476-0271-4A84-BE9E-901865A86FD3}">
     <filterColumn colId="0">
       <filters>
-        <filter val="E 04"/>
-        <filter val="P 05"/>
-        <filter val="P 107"/>
-        <filter val="P 143"/>
-        <filter val="P 39"/>
+        <filter val="P 106"/>
+        <filter val="P 12"/>
+        <filter val="P 181"/>
+        <filter val="P 198"/>
+        <filter val="P 55"/>
       </filters>
     </filterColumn>
     <filterColumn colId="5" showButton="0"/>

--- a/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
+++ b/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gesto\OneDrive\Área de Trabalho\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\5- MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75A7BD85-BBE4-4AF4-8D37-5B1665941792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39CFD38C-5068-436E-A17C-ED316E88C009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
   </bookViews>
   <sheets>
     <sheet name="LISTA DE PONTOS" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1873" uniqueCount="883">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1873" uniqueCount="882">
   <si>
     <t>WKT</t>
   </si>
@@ -940,9 +940,6 @@
   </si>
   <si>
     <t>N 01</t>
-  </si>
-  <si>
-    <t>155ECE0030E0</t>
   </si>
   <si>
     <t>ENTR. CE-085</t>
@@ -2692,7 +2689,7 @@
     <t>ENTR. CE-515</t>
   </si>
   <si>
-    <t>EM ANDAMENTO</t>
+    <t>348ECE0170S0</t>
   </si>
 </sst>
 </file>
@@ -2820,7 +2817,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2884,6 +2881,9 @@
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2905,8 +2905,8 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4309,7 +4309,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>9</v>
@@ -4344,7 +4344,7 @@
         <v>16</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K2" s="6" t="s">
         <v>18</v>
@@ -4379,7 +4379,7 @@
         <v>16</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K3" s="6" t="s">
         <v>18</v>
@@ -4414,7 +4414,7 @@
         <v>16</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K4" s="6" t="s">
         <v>18</v>
@@ -4449,7 +4449,7 @@
         <v>16</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K5" s="6" t="s">
         <v>18</v>
@@ -4624,7 +4624,7 @@
         <v>16</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K10" s="6" t="s">
         <v>18</v>
@@ -4729,7 +4729,7 @@
         <v>16</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K13" s="6" t="s">
         <v>18</v>
@@ -4764,7 +4764,7 @@
         <v>16</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K14" s="6" t="s">
         <v>18</v>
@@ -4834,7 +4834,7 @@
         <v>16</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K16" s="6" t="s">
         <v>18</v>
@@ -4904,7 +4904,7 @@
         <v>16</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K18" s="6" t="s">
         <v>18</v>
@@ -5009,7 +5009,7 @@
         <v>16</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K21" s="6" t="s">
         <v>18</v>
@@ -5219,7 +5219,7 @@
         <v>16</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K27" s="6" t="s">
         <v>18</v>
@@ -5254,7 +5254,7 @@
         <v>16</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K28" s="6" t="s">
         <v>18</v>
@@ -5289,7 +5289,7 @@
         <v>16</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K29" s="6" t="s">
         <v>18</v>
@@ -5324,7 +5324,7 @@
         <v>16</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K30" s="6" t="s">
         <v>18</v>
@@ -5359,7 +5359,7 @@
         <v>16</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K31" s="6" t="s">
         <v>18</v>
@@ -5449,22 +5449,22 @@
         <v>-38.815711</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="F34" s="4" t="s">
+        <v>881</v>
+      </c>
+      <c r="G34" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="G34" s="4" t="s">
-        <v>300</v>
-      </c>
       <c r="H34" s="4" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="I34" s="4" t="s">
         <v>16</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>882</v>
+        <v>798</v>
       </c>
       <c r="K34" s="6" t="s">
         <v>178</v>
@@ -5472,10 +5472,10 @@
     </row>
     <row r="35" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B35" s="4" t="s">
         <v>301</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>302</v>
       </c>
       <c r="C35" s="5">
         <v>-4.5677839999999996</v>
@@ -5484,33 +5484,33 @@
         <v>-41.220272999999999</v>
       </c>
       <c r="E35" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="F35" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="F35" s="4" t="s">
+      <c r="G35" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="G35" s="4" t="s">
+      <c r="H35" s="4" t="s">
         <v>305</v>
-      </c>
-      <c r="H35" s="4" t="s">
-        <v>306</v>
       </c>
       <c r="I35" s="4" t="s">
         <v>16</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K35" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B36" s="4" t="s">
         <v>308</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>309</v>
       </c>
       <c r="C36" s="5">
         <v>-5.9926050000000002</v>
@@ -5522,13 +5522,13 @@
         <v>136</v>
       </c>
       <c r="F36" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="G36" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="G36" s="4" t="s">
+      <c r="H36" s="4" t="s">
         <v>311</v>
-      </c>
-      <c r="H36" s="4" t="s">
-        <v>312</v>
       </c>
       <c r="I36" s="4" t="s">
         <v>16</v>
@@ -5639,7 +5639,7 @@
         <v>101</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K39" s="6" t="s">
         <v>18</v>
@@ -5752,10 +5752,10 @@
     </row>
     <row r="43" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B43" s="4" t="s">
         <v>313</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>314</v>
       </c>
       <c r="C43" s="5">
         <v>-4.228675</v>
@@ -5767,19 +5767,19 @@
         <v>148</v>
       </c>
       <c r="F43" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="G43" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="G43" s="4" t="s">
+      <c r="H43" s="4" t="s">
         <v>316</v>
-      </c>
-      <c r="H43" s="4" t="s">
-        <v>317</v>
       </c>
       <c r="I43" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K43" s="6" t="s">
         <v>18</v>
@@ -5787,10 +5787,10 @@
     </row>
     <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B44" s="4" t="s">
         <v>318</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>319</v>
       </c>
       <c r="C44" s="5">
         <v>-3.9083830000000002</v>
@@ -5802,13 +5802,13 @@
         <v>148</v>
       </c>
       <c r="F44" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="G44" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="G44" s="4" t="s">
+      <c r="H44" s="4" t="s">
         <v>321</v>
-      </c>
-      <c r="H44" s="4" t="s">
-        <v>322</v>
       </c>
       <c r="I44" s="4" t="s">
         <v>101</v>
@@ -5822,10 +5822,10 @@
     </row>
     <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B45" s="4" t="s">
         <v>323</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>324</v>
       </c>
       <c r="C45" s="5">
         <v>-3.907816</v>
@@ -5837,13 +5837,13 @@
         <v>148</v>
       </c>
       <c r="F45" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="G45" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="G45" s="4" t="s">
+      <c r="H45" s="4" t="s">
         <v>326</v>
-      </c>
-      <c r="H45" s="4" t="s">
-        <v>327</v>
       </c>
       <c r="I45" s="4" t="s">
         <v>151</v>
@@ -5857,10 +5857,10 @@
     </row>
     <row r="46" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B46" s="4" t="s">
         <v>328</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>329</v>
       </c>
       <c r="C46" s="5">
         <v>-4.5644640000000001</v>
@@ -5872,19 +5872,19 @@
         <v>87</v>
       </c>
       <c r="F46" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="G46" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="G46" s="4" t="s">
+      <c r="H46" s="4" t="s">
         <v>331</v>
-      </c>
-      <c r="H46" s="4" t="s">
-        <v>332</v>
       </c>
       <c r="I46" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K46" s="6" t="s">
         <v>18</v>
@@ -5892,10 +5892,10 @@
     </row>
     <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B47" s="4" t="s">
         <v>333</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>334</v>
       </c>
       <c r="C47" s="5">
         <v>-4.720345</v>
@@ -5904,22 +5904,22 @@
         <v>-37.548856999999998</v>
       </c>
       <c r="E47" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="F47" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="F47" s="4" t="s">
+      <c r="G47" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="G47" s="4" t="s">
+      <c r="H47" s="4" t="s">
         <v>337</v>
-      </c>
-      <c r="H47" s="4" t="s">
-        <v>338</v>
       </c>
       <c r="I47" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K47" s="6" t="s">
         <v>18</v>
@@ -5927,10 +5927,10 @@
     </row>
     <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B48" s="4" t="s">
         <v>339</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>340</v>
       </c>
       <c r="C48" s="5">
         <v>-4.8210379999999997</v>
@@ -5939,22 +5939,22 @@
         <v>-37.875945000000002</v>
       </c>
       <c r="E48" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="F48" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="F48" s="4" t="s">
+      <c r="G48" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="G48" s="4" t="s">
+      <c r="H48" s="4" t="s">
         <v>343</v>
-      </c>
-      <c r="H48" s="4" t="s">
-        <v>344</v>
       </c>
       <c r="I48" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K48" s="6" t="s">
         <v>18</v>
@@ -5989,7 +5989,7 @@
         <v>101</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K49" s="6" t="s">
         <v>18</v>
@@ -6024,7 +6024,7 @@
         <v>101</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K50" s="6" t="s">
         <v>18</v>
@@ -6032,10 +6032,10 @@
     </row>
     <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B51" s="4" t="s">
         <v>345</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>346</v>
       </c>
       <c r="C51" s="5">
         <v>-4.702947</v>
@@ -6047,10 +6047,10 @@
         <v>12</v>
       </c>
       <c r="F51" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="G51" s="4" t="s">
         <v>347</v>
-      </c>
-      <c r="G51" s="4" t="s">
-        <v>348</v>
       </c>
       <c r="H51" s="4" t="s">
         <v>22</v>
@@ -6059,7 +6059,7 @@
         <v>151</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K51" s="6" t="s">
         <v>18</v>
@@ -6067,10 +6067,10 @@
     </row>
     <row r="52" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B52" s="4" t="s">
         <v>349</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>350</v>
       </c>
       <c r="C52" s="5">
         <v>-5.2215020000000001</v>
@@ -6079,33 +6079,33 @@
         <v>-37.892071000000001</v>
       </c>
       <c r="E52" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="F52" s="4" t="s">
         <v>351</v>
       </c>
-      <c r="F52" s="4" t="s">
+      <c r="G52" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="G52" s="4" t="s">
+      <c r="H52" s="4" t="s">
         <v>353</v>
-      </c>
-      <c r="H52" s="4" t="s">
-        <v>354</v>
       </c>
       <c r="I52" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K52" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B53" s="4" t="s">
         <v>355</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>356</v>
       </c>
       <c r="C53" s="5">
         <v>-5.2506180000000002</v>
@@ -6114,22 +6114,22 @@
         <v>-38.494636999999997</v>
       </c>
       <c r="E53" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="F53" s="4" t="s">
         <v>357</v>
-      </c>
-      <c r="F53" s="4" t="s">
-        <v>358</v>
       </c>
       <c r="G53" s="4" t="s">
         <v>27</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="I53" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K53" s="6" t="s">
         <v>18</v>
@@ -6137,10 +6137,10 @@
     </row>
     <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B54" s="4" t="s">
         <v>360</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>361</v>
       </c>
       <c r="C54" s="5">
         <v>-5.4016780000000004</v>
@@ -6149,22 +6149,22 @@
         <v>-38.569516999999998</v>
       </c>
       <c r="E54" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="F54" s="4" t="s">
         <v>362</v>
       </c>
-      <c r="F54" s="4" t="s">
+      <c r="G54" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="G54" s="4" t="s">
+      <c r="H54" s="4" t="s">
         <v>364</v>
-      </c>
-      <c r="H54" s="4" t="s">
-        <v>365</v>
       </c>
       <c r="I54" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K54" s="6" t="s">
         <v>18</v>
@@ -6172,10 +6172,10 @@
     </row>
     <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B55" s="4" t="s">
         <v>366</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>367</v>
       </c>
       <c r="C55" s="5">
         <v>-5.9727329999999998</v>
@@ -6184,16 +6184,16 @@
         <v>-38.8797</v>
       </c>
       <c r="E55" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="F55" s="4" t="s">
         <v>368</v>
       </c>
-      <c r="F55" s="4" t="s">
+      <c r="G55" s="4" t="s">
         <v>369</v>
       </c>
-      <c r="G55" s="4" t="s">
+      <c r="H55" s="4" t="s">
         <v>370</v>
-      </c>
-      <c r="H55" s="4" t="s">
-        <v>371</v>
       </c>
       <c r="I55" s="4" t="s">
         <v>151</v>
@@ -6234,7 +6234,7 @@
         <v>101</v>
       </c>
       <c r="J56" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K56" s="6" t="s">
         <v>18</v>
@@ -6242,10 +6242,10 @@
     </row>
     <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B57" s="4" t="s">
         <v>372</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>373</v>
       </c>
       <c r="C57" s="5">
         <v>-3.5660500000000002</v>
@@ -6254,16 +6254,16 @@
         <v>-41.143765999999999</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="F57" s="4" t="s">
+        <v>878</v>
+      </c>
+      <c r="G57" s="4" t="s">
         <v>879</v>
       </c>
-      <c r="G57" s="4" t="s">
+      <c r="H57" s="4" t="s">
         <v>880</v>
-      </c>
-      <c r="H57" s="4" t="s">
-        <v>881</v>
       </c>
       <c r="I57" s="4" t="s">
         <v>151</v>
@@ -6277,10 +6277,10 @@
     </row>
     <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B58" s="4" t="s">
         <v>374</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>375</v>
       </c>
       <c r="C58" s="5">
         <v>-3.8470499999999999</v>
@@ -6289,16 +6289,16 @@
         <v>-40.655116</v>
       </c>
       <c r="E58" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="F58" s="4" t="s">
         <v>376</v>
       </c>
-      <c r="F58" s="4" t="s">
+      <c r="G58" s="4" t="s">
         <v>377</v>
       </c>
-      <c r="G58" s="4" t="s">
+      <c r="H58" s="4" t="s">
         <v>378</v>
-      </c>
-      <c r="H58" s="4" t="s">
-        <v>379</v>
       </c>
       <c r="I58" s="4" t="s">
         <v>151</v>
@@ -6347,10 +6347,10 @@
     </row>
     <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="B60" s="4" t="s">
         <v>380</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>381</v>
       </c>
       <c r="C60" s="5">
         <v>-3.9773499999999999</v>
@@ -6359,16 +6359,16 @@
         <v>-40.707566</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F60" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="G60" s="4" t="s">
         <v>382</v>
       </c>
-      <c r="G60" s="4" t="s">
+      <c r="H60" s="4" t="s">
         <v>383</v>
-      </c>
-      <c r="H60" s="4" t="s">
-        <v>384</v>
       </c>
       <c r="I60" s="4" t="s">
         <v>151</v>
@@ -6382,10 +6382,10 @@
     </row>
     <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B61" s="4" t="s">
         <v>385</v>
-      </c>
-      <c r="B61" s="4" t="s">
-        <v>386</v>
       </c>
       <c r="C61" s="5">
         <v>-4.1677330000000001</v>
@@ -6394,16 +6394,16 @@
         <v>-40.952933000000002</v>
       </c>
       <c r="E61" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="F61" s="4" t="s">
         <v>387</v>
       </c>
-      <c r="F61" s="4" t="s">
+      <c r="G61" s="4" t="s">
         <v>388</v>
       </c>
-      <c r="G61" s="4" t="s">
+      <c r="H61" s="4" t="s">
         <v>389</v>
-      </c>
-      <c r="H61" s="4" t="s">
-        <v>390</v>
       </c>
       <c r="I61" s="4" t="s">
         <v>101</v>
@@ -6417,10 +6417,10 @@
     </row>
     <row r="62" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="B62" s="4" t="s">
         <v>391</v>
-      </c>
-      <c r="B62" s="4" t="s">
-        <v>392</v>
       </c>
       <c r="C62" s="5">
         <v>-4.040883</v>
@@ -6429,16 +6429,16 @@
         <v>-40.474516000000001</v>
       </c>
       <c r="E62" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="F62" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="F62" s="4" t="s">
+      <c r="G62" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="G62" s="4" t="s">
+      <c r="H62" s="4" t="s">
         <v>395</v>
-      </c>
-      <c r="H62" s="4" t="s">
-        <v>396</v>
       </c>
       <c r="I62" s="4" t="s">
         <v>151</v>
@@ -6452,10 +6452,10 @@
     </row>
     <row r="63" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B63" s="4" t="s">
         <v>397</v>
-      </c>
-      <c r="B63" s="4" t="s">
-        <v>398</v>
       </c>
       <c r="C63" s="5">
         <v>-3.5272999999999999</v>
@@ -6467,13 +6467,13 @@
         <v>272</v>
       </c>
       <c r="F63" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="G63" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="G63" s="4" t="s">
+      <c r="H63" s="4" t="s">
         <v>400</v>
-      </c>
-      <c r="H63" s="4" t="s">
-        <v>401</v>
       </c>
       <c r="I63" s="4" t="s">
         <v>101</v>
@@ -6487,10 +6487,10 @@
     </row>
     <row r="64" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="B64" s="4" t="s">
         <v>402</v>
-      </c>
-      <c r="B64" s="4" t="s">
-        <v>403</v>
       </c>
       <c r="C64" s="5">
         <v>-3.553566</v>
@@ -6499,16 +6499,16 @@
         <v>-38.885983000000003</v>
       </c>
       <c r="E64" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="F64" s="4" t="s">
         <v>404</v>
       </c>
-      <c r="F64" s="4" t="s">
+      <c r="G64" s="4" t="s">
         <v>405</v>
       </c>
-      <c r="G64" s="4" t="s">
+      <c r="H64" s="4" t="s">
         <v>406</v>
-      </c>
-      <c r="H64" s="4" t="s">
-        <v>407</v>
       </c>
       <c r="I64" s="4" t="s">
         <v>151</v>
@@ -6522,10 +6522,10 @@
     </row>
     <row r="65" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="B65" s="4" t="s">
         <v>408</v>
-      </c>
-      <c r="B65" s="4" t="s">
-        <v>409</v>
       </c>
       <c r="C65" s="5">
         <v>-3.2338659999999999</v>
@@ -6534,16 +6534,16 @@
         <v>-40.011833000000003</v>
       </c>
       <c r="E65" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="F65" s="4" t="s">
         <v>410</v>
       </c>
-      <c r="F65" s="4" t="s">
+      <c r="G65" s="4" t="s">
         <v>411</v>
       </c>
-      <c r="G65" s="4" t="s">
+      <c r="H65" s="4" t="s">
         <v>412</v>
-      </c>
-      <c r="H65" s="4" t="s">
-        <v>413</v>
       </c>
       <c r="I65" s="4" t="s">
         <v>101</v>
@@ -6557,10 +6557,10 @@
     </row>
     <row r="66" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="B66" s="4" t="s">
         <v>414</v>
-      </c>
-      <c r="B66" s="4" t="s">
-        <v>415</v>
       </c>
       <c r="C66" s="5">
         <v>-3.512756</v>
@@ -6572,19 +6572,19 @@
         <v>266</v>
       </c>
       <c r="F66" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="G66" s="4" t="s">
         <v>416</v>
       </c>
-      <c r="G66" s="4" t="s">
+      <c r="H66" s="4" t="s">
         <v>417</v>
-      </c>
-      <c r="H66" s="4" t="s">
-        <v>418</v>
       </c>
       <c r="I66" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J66" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K66" s="6" t="s">
         <v>18</v>
@@ -6592,10 +6592,10 @@
     </row>
     <row r="67" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B67" s="4" t="s">
         <v>419</v>
-      </c>
-      <c r="B67" s="4" t="s">
-        <v>420</v>
       </c>
       <c r="C67" s="5">
         <v>-3.6566749999999999</v>
@@ -6604,22 +6604,22 @@
         <v>-39.424249000000003</v>
       </c>
       <c r="E67" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="F67" s="4" t="s">
         <v>421</v>
       </c>
-      <c r="F67" s="4" t="s">
+      <c r="G67" s="4" t="s">
         <v>422</v>
       </c>
-      <c r="G67" s="4" t="s">
+      <c r="H67" s="4" t="s">
         <v>423</v>
-      </c>
-      <c r="H67" s="4" t="s">
-        <v>424</v>
       </c>
       <c r="I67" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J67" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K67" s="6" t="s">
         <v>18</v>
@@ -6627,10 +6627,10 @@
     </row>
     <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="B68" s="4" t="s">
         <v>425</v>
-      </c>
-      <c r="B68" s="4" t="s">
-        <v>426</v>
       </c>
       <c r="C68" s="5">
         <v>-4.2901499999999997</v>
@@ -6639,16 +6639,16 @@
         <v>-38.625466000000003</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F68" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="G68" s="4" t="s">
         <v>427</v>
       </c>
-      <c r="G68" s="4" t="s">
+      <c r="H68" s="4" t="s">
         <v>428</v>
-      </c>
-      <c r="H68" s="4" t="s">
-        <v>429</v>
       </c>
       <c r="I68" s="4" t="s">
         <v>16</v>
@@ -6662,10 +6662,10 @@
     </row>
     <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B69" s="4" t="s">
         <v>430</v>
-      </c>
-      <c r="B69" s="4" t="s">
-        <v>431</v>
       </c>
       <c r="C69" s="5">
         <v>-4.3755519999999999</v>
@@ -6677,19 +6677,19 @@
         <v>229</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G69" s="4" t="s">
         <v>232</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I69" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J69" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K69" s="6" t="s">
         <v>18</v>
@@ -6697,10 +6697,10 @@
     </row>
     <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B70" s="4" t="s">
         <v>434</v>
-      </c>
-      <c r="B70" s="4" t="s">
-        <v>435</v>
       </c>
       <c r="C70" s="5">
         <v>-5.041658</v>
@@ -6712,19 +6712,19 @@
         <v>229</v>
       </c>
       <c r="F70" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="G70" s="4" t="s">
         <v>436</v>
       </c>
-      <c r="G70" s="4" t="s">
+      <c r="H70" s="4" t="s">
         <v>437</v>
-      </c>
-      <c r="H70" s="4" t="s">
-        <v>438</v>
       </c>
       <c r="I70" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J70" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K70" s="6" t="s">
         <v>18</v>
@@ -6732,10 +6732,10 @@
     </row>
     <row r="71" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B71" s="4" t="s">
         <v>439</v>
-      </c>
-      <c r="B71" s="4" t="s">
-        <v>440</v>
       </c>
       <c r="C71" s="5">
         <v>-5.2738310000000004</v>
@@ -6744,22 +6744,22 @@
         <v>-38.108522000000001</v>
       </c>
       <c r="E71" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="F71" s="4" t="s">
         <v>441</v>
       </c>
-      <c r="F71" s="4" t="s">
+      <c r="G71" s="4" t="s">
         <v>442</v>
       </c>
-      <c r="G71" s="4" t="s">
+      <c r="H71" s="4" t="s">
         <v>443</v>
-      </c>
-      <c r="H71" s="4" t="s">
-        <v>444</v>
       </c>
       <c r="I71" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J71" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K71" s="6" t="s">
         <v>18</v>
@@ -6767,10 +6767,10 @@
     </row>
     <row r="72" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B72" s="4" t="s">
         <v>445</v>
-      </c>
-      <c r="B72" s="4" t="s">
-        <v>446</v>
       </c>
       <c r="C72" s="5">
         <v>-3.7728000000000002</v>
@@ -6782,13 +6782,13 @@
         <v>97</v>
       </c>
       <c r="F72" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="G72" s="4" t="s">
         <v>447</v>
       </c>
-      <c r="G72" s="4" t="s">
+      <c r="H72" s="4" t="s">
         <v>448</v>
-      </c>
-      <c r="H72" s="4" t="s">
-        <v>449</v>
       </c>
       <c r="I72" s="4" t="s">
         <v>101</v>
@@ -6802,10 +6802,10 @@
     </row>
     <row r="73" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="B73" s="4" t="s">
         <v>450</v>
-      </c>
-      <c r="B73" s="4" t="s">
-        <v>451</v>
       </c>
       <c r="C73" s="5">
         <v>-3.1334659999999999</v>
@@ -6817,13 +6817,13 @@
         <v>235</v>
       </c>
       <c r="F73" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="G73" s="4" t="s">
         <v>452</v>
       </c>
-      <c r="G73" s="4" t="s">
+      <c r="H73" s="4" t="s">
         <v>453</v>
-      </c>
-      <c r="H73" s="4" t="s">
-        <v>454</v>
       </c>
       <c r="I73" s="4" t="s">
         <v>101</v>
@@ -6837,10 +6837,10 @@
     </row>
     <row r="74" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="B74" s="4" t="s">
         <v>455</v>
-      </c>
-      <c r="B74" s="4" t="s">
-        <v>456</v>
       </c>
       <c r="C74" s="5">
         <v>-3.6184599999999998</v>
@@ -6852,19 +6852,19 @@
         <v>235</v>
       </c>
       <c r="F74" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="G74" s="4" t="s">
         <v>457</v>
       </c>
-      <c r="G74" s="4" t="s">
+      <c r="H74" s="4" t="s">
         <v>458</v>
-      </c>
-      <c r="H74" s="4" t="s">
-        <v>459</v>
       </c>
       <c r="I74" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J74" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K74" s="6" t="s">
         <v>18</v>
@@ -6872,10 +6872,10 @@
     </row>
     <row r="75" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="B75" s="4" t="s">
         <v>460</v>
-      </c>
-      <c r="B75" s="4" t="s">
-        <v>461</v>
       </c>
       <c r="C75" s="5">
         <v>-3.9911660000000002</v>
@@ -6887,13 +6887,13 @@
         <v>235</v>
       </c>
       <c r="F75" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="G75" s="4" t="s">
         <v>462</v>
       </c>
-      <c r="G75" s="4" t="s">
+      <c r="H75" s="4" t="s">
         <v>463</v>
-      </c>
-      <c r="H75" s="4" t="s">
-        <v>464</v>
       </c>
       <c r="I75" s="4" t="s">
         <v>151</v>
@@ -6907,10 +6907,10 @@
     </row>
     <row r="76" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B76" s="4" t="s">
         <v>465</v>
-      </c>
-      <c r="B76" s="4" t="s">
-        <v>466</v>
       </c>
       <c r="C76" s="5">
         <v>-5.6781480000000002</v>
@@ -6922,19 +6922,19 @@
         <v>197</v>
       </c>
       <c r="F76" s="4" t="s">
+        <v>831</v>
+      </c>
+      <c r="G76" s="4" t="s">
         <v>832</v>
       </c>
-      <c r="G76" s="4" t="s">
+      <c r="H76" s="4" t="s">
         <v>833</v>
-      </c>
-      <c r="H76" s="4" t="s">
-        <v>834</v>
       </c>
       <c r="I76" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J76" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K76" s="6" t="s">
         <v>18</v>
@@ -6942,10 +6942,10 @@
     </row>
     <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="B77" s="4" t="s">
         <v>469</v>
-      </c>
-      <c r="B77" s="4" t="s">
-        <v>470</v>
       </c>
       <c r="C77" s="5">
         <v>-3.4014500000000001</v>
@@ -6954,16 +6954,16 @@
         <v>-40.686549999999997</v>
       </c>
       <c r="E77" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="F77" s="4" t="s">
         <v>471</v>
       </c>
-      <c r="F77" s="4" t="s">
+      <c r="G77" s="4" t="s">
         <v>472</v>
       </c>
-      <c r="G77" s="4" t="s">
+      <c r="H77" s="4" t="s">
         <v>473</v>
-      </c>
-      <c r="H77" s="4" t="s">
-        <v>474</v>
       </c>
       <c r="I77" s="4" t="s">
         <v>101</v>
@@ -6977,10 +6977,10 @@
     </row>
     <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="B78" s="4" t="s">
         <v>475</v>
-      </c>
-      <c r="B78" s="4" t="s">
-        <v>476</v>
       </c>
       <c r="C78" s="5">
         <v>-3.5688710000000001</v>
@@ -6989,22 +6989,22 @@
         <v>-40.636719999999997</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F78" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="G78" s="4" t="s">
         <v>477</v>
       </c>
-      <c r="G78" s="4" t="s">
-        <v>478</v>
-      </c>
       <c r="H78" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="I78" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J78" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K78" s="6" t="s">
         <v>18</v>
@@ -7012,10 +7012,10 @@
     </row>
     <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="B79" s="4" t="s">
         <v>479</v>
-      </c>
-      <c r="B79" s="4" t="s">
-        <v>480</v>
       </c>
       <c r="C79" s="5">
         <v>-4.7611049999999997</v>
@@ -7024,22 +7024,22 @@
         <v>-39.487011000000003</v>
       </c>
       <c r="E79" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="F79" s="4" t="s">
         <v>481</v>
       </c>
-      <c r="F79" s="4" t="s">
+      <c r="G79" s="4" t="s">
         <v>482</v>
       </c>
-      <c r="G79" s="4" t="s">
+      <c r="H79" s="4" t="s">
         <v>483</v>
-      </c>
-      <c r="H79" s="4" t="s">
-        <v>484</v>
       </c>
       <c r="I79" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J79" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K79" s="6" t="s">
         <v>18</v>
@@ -7074,7 +7074,7 @@
         <v>101</v>
       </c>
       <c r="J80" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K80" s="6" t="s">
         <v>18</v>
@@ -7082,10 +7082,10 @@
     </row>
     <row r="81" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="B81" s="4" t="s">
         <v>485</v>
-      </c>
-      <c r="B81" s="4" t="s">
-        <v>486</v>
       </c>
       <c r="C81" s="5">
         <v>-5.4022300000000003</v>
@@ -7094,22 +7094,22 @@
         <v>-38.571371999999997</v>
       </c>
       <c r="E81" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="F81" s="4" t="s">
         <v>487</v>
       </c>
-      <c r="F81" s="4" t="s">
+      <c r="G81" s="4" t="s">
         <v>488</v>
       </c>
-      <c r="G81" s="4" t="s">
+      <c r="H81" s="4" t="s">
         <v>489</v>
-      </c>
-      <c r="H81" s="4" t="s">
-        <v>490</v>
       </c>
       <c r="I81" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J81" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K81" s="6" t="s">
         <v>18</v>
@@ -7117,10 +7117,10 @@
     </row>
     <row r="82" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="B82" s="4" t="s">
         <v>491</v>
-      </c>
-      <c r="B82" s="4" t="s">
-        <v>492</v>
       </c>
       <c r="C82" s="5">
         <v>-5.7358440000000002</v>
@@ -7132,19 +7132,19 @@
         <v>136</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="G82" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="H82" s="4" t="s">
         <v>494</v>
-      </c>
-      <c r="H82" s="4" t="s">
-        <v>495</v>
       </c>
       <c r="I82" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J82" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K82" s="6" t="s">
         <v>18</v>
@@ -7152,10 +7152,10 @@
     </row>
     <row r="83" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="B83" s="4" t="s">
         <v>496</v>
-      </c>
-      <c r="B83" s="4" t="s">
-        <v>497</v>
       </c>
       <c r="C83" s="5">
         <v>-5.6845759999999999</v>
@@ -7167,19 +7167,19 @@
         <v>136</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="I83" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J83" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K83" s="6" t="s">
         <v>18</v>
@@ -7187,10 +7187,10 @@
     </row>
     <row r="84" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="B84" s="4" t="s">
         <v>499</v>
-      </c>
-      <c r="B84" s="4" t="s">
-        <v>500</v>
       </c>
       <c r="C84" s="5">
         <v>-5.0848469999999999</v>
@@ -7199,22 +7199,22 @@
         <v>-38.009757</v>
       </c>
       <c r="E84" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="F84" s="4" t="s">
         <v>501</v>
       </c>
-      <c r="F84" s="4" t="s">
+      <c r="G84" s="4" t="s">
         <v>502</v>
       </c>
-      <c r="G84" s="4" t="s">
+      <c r="H84" s="4" t="s">
         <v>503</v>
-      </c>
-      <c r="H84" s="4" t="s">
-        <v>504</v>
       </c>
       <c r="I84" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J84" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K84" s="6" t="s">
         <v>18</v>
@@ -7222,10 +7222,10 @@
     </row>
     <row r="85" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="B85" s="4" t="s">
         <v>505</v>
-      </c>
-      <c r="B85" s="4" t="s">
-        <v>506</v>
       </c>
       <c r="C85" s="5">
         <v>-5.2461500000000001</v>
@@ -7234,22 +7234,22 @@
         <v>-38.214409000000003</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="F85" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="G85" s="4" t="s">
         <v>507</v>
       </c>
-      <c r="G85" s="4" t="s">
+      <c r="H85" s="4" t="s">
         <v>508</v>
-      </c>
-      <c r="H85" s="4" t="s">
-        <v>509</v>
       </c>
       <c r="I85" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J85" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K85" s="6" t="s">
         <v>18</v>
@@ -7284,7 +7284,7 @@
         <v>151</v>
       </c>
       <c r="J86" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K86" s="6" t="s">
         <v>18</v>
@@ -7292,10 +7292,10 @@
     </row>
     <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="B87" s="4" t="s">
         <v>510</v>
-      </c>
-      <c r="B87" s="4" t="s">
-        <v>511</v>
       </c>
       <c r="C87" s="5">
         <v>-3.9741499999999998</v>
@@ -7304,16 +7304,16 @@
         <v>-40.704782999999999</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F87" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="G87" s="4" t="s">
         <v>512</v>
       </c>
-      <c r="G87" s="4" t="s">
+      <c r="H87" s="4" t="s">
         <v>513</v>
-      </c>
-      <c r="H87" s="4" t="s">
-        <v>514</v>
       </c>
       <c r="I87" s="4" t="s">
         <v>151</v>
@@ -7327,10 +7327,10 @@
     </row>
     <row r="88" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="B88" s="4" t="s">
         <v>515</v>
-      </c>
-      <c r="B88" s="4" t="s">
-        <v>516</v>
       </c>
       <c r="C88" s="5">
         <v>-3.962866</v>
@@ -7339,16 +7339,16 @@
         <v>-38.357016000000002</v>
       </c>
       <c r="E88" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="F88" s="4" t="s">
         <v>517</v>
       </c>
-      <c r="F88" s="4" t="s">
+      <c r="G88" s="4" t="s">
         <v>518</v>
       </c>
-      <c r="G88" s="4" t="s">
+      <c r="H88" s="4" t="s">
         <v>519</v>
-      </c>
-      <c r="H88" s="4" t="s">
-        <v>520</v>
       </c>
       <c r="I88" s="4" t="s">
         <v>101</v>
@@ -7362,10 +7362,10 @@
     </row>
     <row r="89" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="B89" s="4" t="s">
         <v>521</v>
-      </c>
-      <c r="B89" s="4" t="s">
-        <v>522</v>
       </c>
       <c r="C89" s="5">
         <v>-4.0425329999999997</v>
@@ -7374,16 +7374,16 @@
         <v>-38.206499999999998</v>
       </c>
       <c r="E89" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="F89" s="4" t="s">
         <v>523</v>
       </c>
-      <c r="F89" s="4" t="s">
+      <c r="G89" s="4" t="s">
         <v>524</v>
       </c>
-      <c r="G89" s="4" t="s">
+      <c r="H89" s="4" t="s">
         <v>525</v>
-      </c>
-      <c r="H89" s="4" t="s">
-        <v>526</v>
       </c>
       <c r="I89" s="4" t="s">
         <v>151</v>
@@ -7424,7 +7424,7 @@
         <v>151</v>
       </c>
       <c r="J90" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K90" s="6" t="s">
         <v>18</v>
@@ -7432,10 +7432,10 @@
     </row>
     <row r="91" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="B91" s="4" t="s">
         <v>527</v>
-      </c>
-      <c r="B91" s="4" t="s">
-        <v>528</v>
       </c>
       <c r="C91" s="5">
         <v>-4.4447369999999999</v>
@@ -7444,22 +7444,22 @@
         <v>-38.662745999999999</v>
       </c>
       <c r="E91" s="4" t="s">
+        <v>528</v>
+      </c>
+      <c r="F91" s="4" t="s">
         <v>529</v>
       </c>
-      <c r="F91" s="4" t="s">
+      <c r="G91" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="G91" s="4" t="s">
+      <c r="H91" s="4" t="s">
         <v>531</v>
-      </c>
-      <c r="H91" s="4" t="s">
-        <v>532</v>
       </c>
       <c r="I91" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J91" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K91" s="6" t="s">
         <v>18</v>
@@ -7467,10 +7467,10 @@
     </row>
     <row r="92" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="B92" s="4" t="s">
         <v>533</v>
-      </c>
-      <c r="B92" s="4" t="s">
-        <v>534</v>
       </c>
       <c r="C92" s="5">
         <v>-5.1705110000000003</v>
@@ -7479,22 +7479,22 @@
         <v>-40.708150000000003</v>
       </c>
       <c r="E92" s="4" t="s">
+        <v>534</v>
+      </c>
+      <c r="F92" s="4" t="s">
         <v>535</v>
       </c>
-      <c r="F92" s="4" t="s">
+      <c r="G92" s="4" t="s">
         <v>536</v>
       </c>
-      <c r="G92" s="4" t="s">
+      <c r="H92" s="4" t="s">
         <v>537</v>
-      </c>
-      <c r="H92" s="4" t="s">
-        <v>538</v>
       </c>
       <c r="I92" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J92" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K92" s="6" t="s">
         <v>18</v>
@@ -7502,10 +7502,10 @@
     </row>
     <row r="93" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="B93" s="4" t="s">
         <v>539</v>
-      </c>
-      <c r="B93" s="4" t="s">
-        <v>540</v>
       </c>
       <c r="C93" s="5">
         <v>-4.5701270000000003</v>
@@ -7514,22 +7514,22 @@
         <v>-37.734988999999999</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="F93" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="G93" s="4" t="s">
         <v>541</v>
       </c>
-      <c r="G93" s="4" t="s">
+      <c r="H93" s="4" t="s">
         <v>542</v>
-      </c>
-      <c r="H93" s="4" t="s">
-        <v>543</v>
       </c>
       <c r="I93" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J93" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K93" s="6" t="s">
         <v>18</v>
@@ -7537,10 +7537,10 @@
     </row>
     <row r="94" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="B94" s="4" t="s">
         <v>544</v>
-      </c>
-      <c r="B94" s="4" t="s">
-        <v>545</v>
       </c>
       <c r="C94" s="5">
         <v>-5.1207330000000004</v>
@@ -7549,16 +7549,16 @@
         <v>-39.752000000000002</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F94" s="4" t="s">
+        <v>545</v>
+      </c>
+      <c r="G94" s="4" t="s">
         <v>546</v>
       </c>
-      <c r="G94" s="4" t="s">
+      <c r="H94" s="4" t="s">
         <v>547</v>
-      </c>
-      <c r="H94" s="4" t="s">
-        <v>548</v>
       </c>
       <c r="I94" s="4" t="s">
         <v>101</v>
@@ -7587,19 +7587,19 @@
         <v>197</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="G95" s="4" t="s">
         <v>132</v>
       </c>
       <c r="H95" s="4" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="I95" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J95" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K95" s="6" t="s">
         <v>18</v>
@@ -7607,34 +7607,34 @@
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="B96" s="4" t="s">
         <v>549</v>
-      </c>
-      <c r="B96" s="4" t="s">
-        <v>550</v>
       </c>
       <c r="C96" s="5">
         <v>-3.6776800000000001</v>
       </c>
-      <c r="D96" s="32">
+      <c r="D96" s="25">
         <v>-38.859572</v>
       </c>
       <c r="E96" s="4" t="s">
         <v>42</v>
       </c>
       <c r="F96" s="4" t="s">
+        <v>550</v>
+      </c>
+      <c r="G96" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="H96" s="4" t="s">
         <v>551</v>
-      </c>
-      <c r="G96" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="H96" s="4" t="s">
-        <v>552</v>
       </c>
       <c r="I96" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J96" s="6" t="s">
-        <v>882</v>
+        <v>798</v>
       </c>
       <c r="K96" s="6" t="s">
         <v>178</v>
@@ -7642,10 +7642,10 @@
     </row>
     <row r="97" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="B97" s="4" t="s">
         <v>553</v>
-      </c>
-      <c r="B97" s="4" t="s">
-        <v>554</v>
       </c>
       <c r="C97" s="5">
         <v>-3.6978119999999999</v>
@@ -7654,22 +7654,22 @@
         <v>-40.307443999999997</v>
       </c>
       <c r="E97" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="F97" s="4" t="s">
         <v>555</v>
       </c>
-      <c r="F97" s="4" t="s">
+      <c r="G97" s="4" t="s">
         <v>556</v>
       </c>
-      <c r="G97" s="4" t="s">
+      <c r="H97" s="4" t="s">
         <v>557</v>
-      </c>
-      <c r="H97" s="4" t="s">
-        <v>558</v>
       </c>
       <c r="I97" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J97" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K97" s="6" t="s">
         <v>18</v>
@@ -7677,10 +7677,10 @@
     </row>
     <row r="98" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="B98" s="4" t="s">
         <v>559</v>
-      </c>
-      <c r="B98" s="4" t="s">
-        <v>560</v>
       </c>
       <c r="C98" s="5">
         <v>-5.2113269999999998</v>
@@ -7692,19 +7692,19 @@
         <v>208</v>
       </c>
       <c r="F98" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="G98" s="4" t="s">
         <v>561</v>
       </c>
-      <c r="G98" s="4" t="s">
+      <c r="H98" s="4" t="s">
         <v>562</v>
-      </c>
-      <c r="H98" s="4" t="s">
-        <v>563</v>
       </c>
       <c r="I98" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J98" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K98" s="6" t="s">
         <v>18</v>
@@ -7712,10 +7712,10 @@
     </row>
     <row r="99" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="B99" s="4" t="s">
         <v>564</v>
-      </c>
-      <c r="B99" s="4" t="s">
-        <v>565</v>
       </c>
       <c r="C99" s="5">
         <v>-4.3822749999999999</v>
@@ -7727,19 +7727,19 @@
         <v>208</v>
       </c>
       <c r="F99" s="4" t="s">
+        <v>565</v>
+      </c>
+      <c r="G99" s="4" t="s">
         <v>566</v>
       </c>
-      <c r="G99" s="4" t="s">
+      <c r="H99" s="4" t="s">
         <v>567</v>
-      </c>
-      <c r="H99" s="4" t="s">
-        <v>568</v>
       </c>
       <c r="I99" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J99" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K99" s="6" t="s">
         <v>18</v>
@@ -7747,10 +7747,10 @@
     </row>
     <row r="100" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="B100" s="4" t="s">
         <v>569</v>
-      </c>
-      <c r="B100" s="4" t="s">
-        <v>570</v>
       </c>
       <c r="C100" s="5">
         <v>-6.0296659999999997</v>
@@ -7759,16 +7759,16 @@
         <v>-38.340949999999999</v>
       </c>
       <c r="E100" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="F100" s="4" t="s">
         <v>571</v>
       </c>
-      <c r="F100" s="4" t="s">
+      <c r="G100" s="4" t="s">
         <v>572</v>
       </c>
-      <c r="G100" s="4" t="s">
+      <c r="H100" s="4" t="s">
         <v>573</v>
-      </c>
-      <c r="H100" s="4" t="s">
-        <v>574</v>
       </c>
       <c r="I100" s="4" t="s">
         <v>101</v>
@@ -7782,10 +7782,10 @@
     </row>
     <row r="101" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="B101" s="4" t="s">
         <v>575</v>
-      </c>
-      <c r="B101" s="4" t="s">
-        <v>576</v>
       </c>
       <c r="C101" s="5">
         <v>-5.2495240000000001</v>
@@ -7794,22 +7794,22 @@
         <v>-38.492610999999997</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="F101" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="G101" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="G101" s="4" t="s">
+      <c r="H101" s="4" t="s">
         <v>578</v>
-      </c>
-      <c r="H101" s="4" t="s">
-        <v>579</v>
       </c>
       <c r="I101" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J101" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K101" s="6" t="s">
         <v>18</v>
@@ -7817,10 +7817,10 @@
     </row>
     <row r="102" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="B102" s="4" t="s">
         <v>580</v>
-      </c>
-      <c r="B102" s="4" t="s">
-        <v>581</v>
       </c>
       <c r="C102" s="5">
         <v>-4.2260499999999999</v>
@@ -7829,16 +7829,16 @@
         <v>-38.112082999999998</v>
       </c>
       <c r="E102" s="4" t="s">
+        <v>581</v>
+      </c>
+      <c r="F102" s="4" t="s">
         <v>582</v>
       </c>
-      <c r="F102" s="4" t="s">
+      <c r="G102" s="4" t="s">
         <v>583</v>
       </c>
-      <c r="G102" s="4" t="s">
+      <c r="H102" s="4" t="s">
         <v>584</v>
-      </c>
-      <c r="H102" s="4" t="s">
-        <v>585</v>
       </c>
       <c r="I102" s="4" t="s">
         <v>151</v>
@@ -7852,10 +7852,10 @@
     </row>
     <row r="103" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="B103" s="4" t="s">
         <v>586</v>
-      </c>
-      <c r="B103" s="4" t="s">
-        <v>587</v>
       </c>
       <c r="C103" s="5">
         <v>-4.2283499999999998</v>
@@ -7864,16 +7864,16 @@
         <v>-38.112932999999998</v>
       </c>
       <c r="E103" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="F103" s="4" t="s">
         <v>588</v>
-      </c>
-      <c r="F103" s="4" t="s">
-        <v>589</v>
       </c>
       <c r="G103" s="4" t="s">
         <v>73</v>
       </c>
       <c r="H103" s="4" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="I103" s="4" t="s">
         <v>101</v>
@@ -7887,10 +7887,10 @@
     </row>
     <row r="104" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="B104" s="4" t="s">
         <v>591</v>
-      </c>
-      <c r="B104" s="4" t="s">
-        <v>592</v>
       </c>
       <c r="C104" s="5">
         <v>-4.5799000000000003</v>
@@ -7902,19 +7902,19 @@
         <v>142</v>
       </c>
       <c r="F104" s="4" t="s">
+        <v>592</v>
+      </c>
+      <c r="G104" s="4" t="s">
         <v>593</v>
       </c>
-      <c r="G104" s="4" t="s">
+      <c r="H104" s="4" t="s">
         <v>594</v>
-      </c>
-      <c r="H104" s="4" t="s">
-        <v>595</v>
       </c>
       <c r="I104" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J104" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K104" s="6" t="s">
         <v>18</v>
@@ -7922,10 +7922,10 @@
     </row>
     <row r="105" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="B105" s="4" t="s">
         <v>596</v>
-      </c>
-      <c r="B105" s="4" t="s">
-        <v>597</v>
       </c>
       <c r="C105" s="5">
         <v>-3.9187500000000002</v>
@@ -7937,13 +7937,13 @@
         <v>104</v>
       </c>
       <c r="F105" s="4" t="s">
+        <v>597</v>
+      </c>
+      <c r="G105" s="4" t="s">
         <v>598</v>
       </c>
-      <c r="G105" s="4" t="s">
+      <c r="H105" s="4" t="s">
         <v>599</v>
-      </c>
-      <c r="H105" s="4" t="s">
-        <v>600</v>
       </c>
       <c r="I105" s="4" t="s">
         <v>101</v>
@@ -8019,7 +8019,7 @@
         <v>101</v>
       </c>
       <c r="J107" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K107" s="6" t="s">
         <v>18</v>
@@ -8089,7 +8089,7 @@
         <v>151</v>
       </c>
       <c r="J109" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K109" s="6" t="s">
         <v>18</v>
@@ -8124,7 +8124,7 @@
         <v>151</v>
       </c>
       <c r="J110" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K110" s="6" t="s">
         <v>18</v>
@@ -8132,10 +8132,10 @@
     </row>
     <row r="111" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="B111" s="4" t="s">
         <v>601</v>
-      </c>
-      <c r="B111" s="4" t="s">
-        <v>602</v>
       </c>
       <c r="C111" s="5">
         <v>-3.7752400000000002</v>
@@ -8144,22 +8144,22 @@
         <v>-40.496578999999997</v>
       </c>
       <c r="E111" s="4" t="s">
+        <v>602</v>
+      </c>
+      <c r="F111" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="F111" s="4" t="s">
+      <c r="G111" s="4" t="s">
         <v>604</v>
       </c>
-      <c r="G111" s="4" t="s">
+      <c r="H111" s="4" t="s">
         <v>605</v>
-      </c>
-      <c r="H111" s="4" t="s">
-        <v>606</v>
       </c>
       <c r="I111" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J111" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K111" s="6" t="s">
         <v>18</v>
@@ -8167,10 +8167,10 @@
     </row>
     <row r="112" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="B112" s="4" t="s">
         <v>607</v>
-      </c>
-      <c r="B112" s="4" t="s">
-        <v>608</v>
       </c>
       <c r="C112" s="5">
         <v>-3.9438659999999999</v>
@@ -8182,13 +8182,13 @@
         <v>208</v>
       </c>
       <c r="F112" s="4" t="s">
+        <v>608</v>
+      </c>
+      <c r="G112" s="4" t="s">
         <v>609</v>
       </c>
-      <c r="G112" s="4" t="s">
+      <c r="H112" s="4" t="s">
         <v>610</v>
-      </c>
-      <c r="H112" s="4" t="s">
-        <v>611</v>
       </c>
       <c r="I112" s="4" t="s">
         <v>101</v>
@@ -8202,10 +8202,10 @@
     </row>
     <row r="113" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="B113" s="4" t="s">
         <v>612</v>
-      </c>
-      <c r="B113" s="4" t="s">
-        <v>613</v>
       </c>
       <c r="C113" s="5">
         <v>-4.7911549999999998</v>
@@ -8214,22 +8214,22 @@
         <v>-40.827958000000002</v>
       </c>
       <c r="E113" s="4" t="s">
+        <v>613</v>
+      </c>
+      <c r="F113" s="4" t="s">
         <v>614</v>
       </c>
-      <c r="F113" s="4" t="s">
+      <c r="G113" s="4" t="s">
         <v>615</v>
       </c>
-      <c r="G113" s="4" t="s">
+      <c r="H113" s="4" t="s">
         <v>616</v>
-      </c>
-      <c r="H113" s="4" t="s">
-        <v>617</v>
       </c>
       <c r="I113" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J113" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K113" s="6" t="s">
         <v>18</v>
@@ -8237,10 +8237,10 @@
     </row>
     <row r="114" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="B114" s="4" t="s">
         <v>618</v>
-      </c>
-      <c r="B114" s="4" t="s">
-        <v>619</v>
       </c>
       <c r="C114" s="5">
         <v>-3.4859019999999998</v>
@@ -8249,22 +8249,22 @@
         <v>-39.523645000000002</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F114" s="4" t="s">
+        <v>619</v>
+      </c>
+      <c r="G114" s="4" t="s">
         <v>620</v>
       </c>
-      <c r="G114" s="4" t="s">
+      <c r="H114" s="4" t="s">
         <v>621</v>
-      </c>
-      <c r="H114" s="4" t="s">
-        <v>622</v>
       </c>
       <c r="I114" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J114" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K114" s="6" t="s">
         <v>18</v>
@@ -8272,10 +8272,10 @@
     </row>
     <row r="115" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="B115" s="4" t="s">
         <v>623</v>
-      </c>
-      <c r="B115" s="4" t="s">
-        <v>624</v>
       </c>
       <c r="C115" s="5">
         <v>-4.5871829999999996</v>
@@ -8284,16 +8284,16 @@
         <v>-38.620182999999997</v>
       </c>
       <c r="E115" s="4" t="s">
+        <v>624</v>
+      </c>
+      <c r="F115" s="4" t="s">
         <v>625</v>
       </c>
-      <c r="F115" s="4" t="s">
+      <c r="G115" s="4" t="s">
         <v>626</v>
       </c>
-      <c r="G115" s="4" t="s">
+      <c r="H115" s="4" t="s">
         <v>627</v>
-      </c>
-      <c r="H115" s="4" t="s">
-        <v>628</v>
       </c>
       <c r="I115" s="4" t="s">
         <v>101</v>
@@ -8307,10 +8307,10 @@
     </row>
     <row r="116" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="B116" s="4" t="s">
         <v>629</v>
-      </c>
-      <c r="B116" s="4" t="s">
-        <v>630</v>
       </c>
       <c r="C116" s="5">
         <v>-3.5105249999999999</v>
@@ -8322,19 +8322,19 @@
         <v>235</v>
       </c>
       <c r="F116" s="4" t="s">
+        <v>630</v>
+      </c>
+      <c r="G116" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="G116" s="4" t="s">
+      <c r="H116" s="4" t="s">
         <v>632</v>
-      </c>
-      <c r="H116" s="4" t="s">
-        <v>633</v>
       </c>
       <c r="I116" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J116" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K116" s="6" t="s">
         <v>18</v>
@@ -8342,10 +8342,10 @@
     </row>
     <row r="117" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="B117" s="4" t="s">
         <v>634</v>
-      </c>
-      <c r="B117" s="4" t="s">
-        <v>635</v>
       </c>
       <c r="C117" s="5">
         <v>-3.2141000000000002</v>
@@ -8354,16 +8354,16 @@
         <v>-40.864533000000002</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F117" s="4" t="s">
+        <v>635</v>
+      </c>
+      <c r="G117" s="4" t="s">
         <v>636</v>
       </c>
-      <c r="G117" s="4" t="s">
+      <c r="H117" s="4" t="s">
         <v>637</v>
-      </c>
-      <c r="H117" s="4" t="s">
-        <v>638</v>
       </c>
       <c r="I117" s="4" t="s">
         <v>101</v>
@@ -8377,10 +8377,10 @@
     </row>
     <row r="118" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="B118" s="4" t="s">
         <v>639</v>
-      </c>
-      <c r="B118" s="4" t="s">
-        <v>640</v>
       </c>
       <c r="C118" s="5">
         <v>-5.0453950000000001</v>
@@ -8389,22 +8389,22 @@
         <v>-37.773105999999999</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="F118" s="4" t="s">
+        <v>640</v>
+      </c>
+      <c r="G118" s="4" t="s">
         <v>641</v>
       </c>
-      <c r="G118" s="4" t="s">
+      <c r="H118" s="4" t="s">
         <v>642</v>
-      </c>
-      <c r="H118" s="4" t="s">
-        <v>643</v>
       </c>
       <c r="I118" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J118" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K118" s="6" t="s">
         <v>18</v>
@@ -8439,7 +8439,7 @@
         <v>151</v>
       </c>
       <c r="J119" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K119" s="6" t="s">
         <v>18</v>
@@ -8447,10 +8447,10 @@
     </row>
     <row r="120" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="B120" s="4" t="s">
         <v>644</v>
-      </c>
-      <c r="B120" s="4" t="s">
-        <v>645</v>
       </c>
       <c r="C120" s="5">
         <v>-5.5281140000000004</v>
@@ -8462,19 +8462,19 @@
         <v>76</v>
       </c>
       <c r="F120" s="4" t="s">
+        <v>645</v>
+      </c>
+      <c r="G120" s="4" t="s">
         <v>646</v>
       </c>
-      <c r="G120" s="4" t="s">
+      <c r="H120" s="4" t="s">
         <v>647</v>
-      </c>
-      <c r="H120" s="4" t="s">
-        <v>648</v>
       </c>
       <c r="I120" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J120" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K120" s="6" t="s">
         <v>18</v>
@@ -8482,10 +8482,10 @@
     </row>
     <row r="121" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="B121" s="4" t="s">
         <v>649</v>
-      </c>
-      <c r="B121" s="4" t="s">
-        <v>650</v>
       </c>
       <c r="C121" s="5">
         <v>-4.338266</v>
@@ -8497,13 +8497,13 @@
         <v>104</v>
       </c>
       <c r="F121" s="4" t="s">
+        <v>650</v>
+      </c>
+      <c r="G121" s="4" t="s">
         <v>651</v>
       </c>
-      <c r="G121" s="4" t="s">
+      <c r="H121" s="4" t="s">
         <v>652</v>
-      </c>
-      <c r="H121" s="4" t="s">
-        <v>653</v>
       </c>
       <c r="I121" s="4" t="s">
         <v>101</v>
@@ -8517,10 +8517,10 @@
     </row>
     <row r="122" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="B122" s="4" t="s">
         <v>654</v>
-      </c>
-      <c r="B122" s="4" t="s">
-        <v>655</v>
       </c>
       <c r="C122" s="5">
         <v>-4.2869089999999996</v>
@@ -8532,10 +8532,10 @@
         <v>36</v>
       </c>
       <c r="F122" s="4" t="s">
+        <v>655</v>
+      </c>
+      <c r="G122" s="4" t="s">
         <v>656</v>
-      </c>
-      <c r="G122" s="4" t="s">
-        <v>657</v>
       </c>
       <c r="H122" s="4" t="s">
         <v>83</v>
@@ -8544,7 +8544,7 @@
         <v>151</v>
       </c>
       <c r="J122" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K122" s="6" t="s">
         <v>18</v>
@@ -8552,10 +8552,10 @@
     </row>
     <row r="123" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="B123" s="4" t="s">
         <v>658</v>
-      </c>
-      <c r="B123" s="4" t="s">
-        <v>659</v>
       </c>
       <c r="C123" s="5">
         <v>-3.372366</v>
@@ -8567,13 +8567,13 @@
         <v>174</v>
       </c>
       <c r="F123" s="4" t="s">
+        <v>659</v>
+      </c>
+      <c r="G123" s="4" t="s">
         <v>660</v>
       </c>
-      <c r="G123" s="4" t="s">
+      <c r="H123" s="4" t="s">
         <v>661</v>
-      </c>
-      <c r="H123" s="4" t="s">
-        <v>662</v>
       </c>
       <c r="I123" s="4" t="s">
         <v>151</v>
@@ -8587,10 +8587,10 @@
     </row>
     <row r="124" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="B124" s="4" t="s">
         <v>663</v>
-      </c>
-      <c r="B124" s="4" t="s">
-        <v>664</v>
       </c>
       <c r="C124" s="5">
         <v>-2.8945319999999999</v>
@@ -8602,19 +8602,19 @@
         <v>174</v>
       </c>
       <c r="F124" s="4" t="s">
+        <v>664</v>
+      </c>
+      <c r="G124" s="4" t="s">
         <v>665</v>
       </c>
-      <c r="G124" s="4" t="s">
+      <c r="H124" s="4" t="s">
         <v>666</v>
-      </c>
-      <c r="H124" s="4" t="s">
-        <v>667</v>
       </c>
       <c r="I124" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J124" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K124" s="6" t="s">
         <v>18</v>
@@ -8622,10 +8622,10 @@
     </row>
     <row r="125" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="B125" s="4" t="s">
         <v>668</v>
-      </c>
-      <c r="B125" s="4" t="s">
-        <v>669</v>
       </c>
       <c r="C125" s="5">
         <v>-4.5809509999999998</v>
@@ -8637,10 +8637,10 @@
         <v>25</v>
       </c>
       <c r="F125" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="G125" s="4" t="s">
         <v>670</v>
-      </c>
-      <c r="G125" s="4" t="s">
-        <v>671</v>
       </c>
       <c r="H125" s="4" t="s">
         <v>27</v>
@@ -8649,7 +8649,7 @@
         <v>101</v>
       </c>
       <c r="J125" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K125" s="6" t="s">
         <v>18</v>
@@ -8657,10 +8657,10 @@
     </row>
     <row r="126" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="B126" s="4" t="s">
         <v>672</v>
-      </c>
-      <c r="B126" s="4" t="s">
-        <v>673</v>
       </c>
       <c r="C126" s="5">
         <v>-4.0460330000000004</v>
@@ -8672,13 +8672,13 @@
         <v>191</v>
       </c>
       <c r="F126" s="4" t="s">
+        <v>673</v>
+      </c>
+      <c r="G126" s="4" t="s">
         <v>674</v>
       </c>
-      <c r="G126" s="4" t="s">
+      <c r="H126" s="4" t="s">
         <v>675</v>
-      </c>
-      <c r="H126" s="4" t="s">
-        <v>676</v>
       </c>
       <c r="I126" s="4" t="s">
         <v>101</v>
@@ -8692,10 +8692,10 @@
     </row>
     <row r="127" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="B127" s="4" t="s">
         <v>677</v>
-      </c>
-      <c r="B127" s="4" t="s">
-        <v>678</v>
       </c>
       <c r="C127" s="5">
         <v>-5.4253080000000002</v>
@@ -8707,19 +8707,19 @@
         <v>191</v>
       </c>
       <c r="F127" s="4" t="s">
+        <v>678</v>
+      </c>
+      <c r="G127" s="4" t="s">
         <v>679</v>
       </c>
-      <c r="G127" s="4" t="s">
+      <c r="H127" s="4" t="s">
         <v>680</v>
-      </c>
-      <c r="H127" s="4" t="s">
-        <v>681</v>
       </c>
       <c r="I127" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J127" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K127" s="6" t="s">
         <v>18</v>
@@ -8727,10 +8727,10 @@
     </row>
     <row r="128" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="B128" s="4" t="s">
         <v>682</v>
-      </c>
-      <c r="B128" s="4" t="s">
-        <v>683</v>
       </c>
       <c r="C128" s="5">
         <v>-5.3889829999999996</v>
@@ -8739,16 +8739,16 @@
         <v>-38.911766</v>
       </c>
       <c r="E128" s="4" t="s">
+        <v>683</v>
+      </c>
+      <c r="F128" s="4" t="s">
         <v>684</v>
       </c>
-      <c r="F128" s="4" t="s">
+      <c r="G128" s="4" t="s">
         <v>685</v>
       </c>
-      <c r="G128" s="4" t="s">
+      <c r="H128" s="4" t="s">
         <v>686</v>
-      </c>
-      <c r="H128" s="4" t="s">
-        <v>687</v>
       </c>
       <c r="I128" s="4" t="s">
         <v>101</v>
@@ -8762,10 +8762,10 @@
     </row>
     <row r="129" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="B129" s="4" t="s">
         <v>688</v>
-      </c>
-      <c r="B129" s="4" t="s">
-        <v>689</v>
       </c>
       <c r="C129" s="5">
         <v>-5.9808000000000003</v>
@@ -8774,16 +8774,16 @@
         <v>-38.884349999999998</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="F129" s="4" t="s">
+        <v>689</v>
+      </c>
+      <c r="G129" s="4" t="s">
         <v>690</v>
       </c>
-      <c r="G129" s="4" t="s">
+      <c r="H129" s="4" t="s">
         <v>691</v>
-      </c>
-      <c r="H129" s="4" t="s">
-        <v>692</v>
       </c>
       <c r="I129" s="4" t="s">
         <v>101</v>
@@ -8797,10 +8797,10 @@
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="B130" s="4" t="s">
         <v>693</v>
-      </c>
-      <c r="B130" s="4" t="s">
-        <v>694</v>
       </c>
       <c r="C130" s="5">
         <v>-3.6789869999999998</v>
@@ -8809,22 +8809,22 @@
         <v>-38.909970999999999</v>
       </c>
       <c r="E130" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="F130" s="4" t="s">
         <v>695</v>
       </c>
-      <c r="F130" s="4" t="s">
+      <c r="G130" s="4" t="s">
         <v>696</v>
       </c>
-      <c r="G130" s="4" t="s">
+      <c r="H130" s="4" t="s">
         <v>697</v>
-      </c>
-      <c r="H130" s="4" t="s">
-        <v>698</v>
       </c>
       <c r="I130" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J130" s="6" t="s">
-        <v>882</v>
+        <v>798</v>
       </c>
       <c r="K130" s="6" t="s">
         <v>18</v>
@@ -8832,10 +8832,10 @@
     </row>
     <row r="131" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="B131" s="4" t="s">
         <v>699</v>
-      </c>
-      <c r="B131" s="4" t="s">
-        <v>700</v>
       </c>
       <c r="C131" s="5">
         <v>-4.1112159999999998</v>
@@ -8844,10 +8844,10 @@
         <v>-39.226599999999998</v>
       </c>
       <c r="E131" s="4" t="s">
+        <v>700</v>
+      </c>
+      <c r="F131" s="4" t="s">
         <v>701</v>
-      </c>
-      <c r="F131" s="4" t="s">
-        <v>702</v>
       </c>
       <c r="G131" s="4" t="s">
         <v>284</v>
@@ -8867,10 +8867,10 @@
     </row>
     <row r="132" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="B132" s="4" t="s">
         <v>703</v>
-      </c>
-      <c r="B132" s="4" t="s">
-        <v>704</v>
       </c>
       <c r="C132" s="5">
         <v>-3.3707829999999999</v>
@@ -8879,16 +8879,16 @@
         <v>-39.293933000000003</v>
       </c>
       <c r="E132" s="4" t="s">
+        <v>704</v>
+      </c>
+      <c r="F132" s="4" t="s">
         <v>705</v>
       </c>
-      <c r="F132" s="4" t="s">
+      <c r="G132" s="4" t="s">
         <v>706</v>
       </c>
-      <c r="G132" s="4" t="s">
+      <c r="H132" s="4" t="s">
         <v>707</v>
-      </c>
-      <c r="H132" s="4" t="s">
-        <v>708</v>
       </c>
       <c r="I132" s="4" t="s">
         <v>101</v>
@@ -8902,10 +8902,10 @@
     </row>
     <row r="133" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="B133" s="4" t="s">
         <v>709</v>
-      </c>
-      <c r="B133" s="4" t="s">
-        <v>710</v>
       </c>
       <c r="C133" s="5">
         <v>-5.8117999999999999</v>
@@ -8917,19 +8917,19 @@
         <v>197</v>
       </c>
       <c r="F133" s="4" t="s">
+        <v>710</v>
+      </c>
+      <c r="G133" s="4" t="s">
         <v>711</v>
       </c>
-      <c r="G133" s="4" t="s">
+      <c r="H133" s="4" t="s">
         <v>712</v>
-      </c>
-      <c r="H133" s="4" t="s">
-        <v>713</v>
       </c>
       <c r="I133" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J133" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K133" s="6" t="s">
         <v>18</v>
@@ -8937,10 +8937,10 @@
     </row>
     <row r="134" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="B134" s="4" t="s">
         <v>714</v>
-      </c>
-      <c r="B134" s="4" t="s">
-        <v>715</v>
       </c>
       <c r="C134" s="5">
         <v>-3.304783</v>
@@ -8952,13 +8952,13 @@
         <v>174</v>
       </c>
       <c r="F134" s="4" t="s">
+        <v>715</v>
+      </c>
+      <c r="G134" s="4" t="s">
         <v>716</v>
       </c>
-      <c r="G134" s="4" t="s">
+      <c r="H134" s="4" t="s">
         <v>717</v>
-      </c>
-      <c r="H134" s="4" t="s">
-        <v>718</v>
       </c>
       <c r="I134" s="4" t="s">
         <v>101</v>
@@ -8972,10 +8972,10 @@
     </row>
     <row r="135" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="B135" s="4" t="s">
         <v>719</v>
-      </c>
-      <c r="B135" s="4" t="s">
-        <v>720</v>
       </c>
       <c r="C135" s="5">
         <v>-5.1408160000000001</v>
@@ -8987,13 +8987,13 @@
         <v>266</v>
       </c>
       <c r="F135" s="4" t="s">
+        <v>720</v>
+      </c>
+      <c r="G135" s="4" t="s">
         <v>721</v>
       </c>
-      <c r="G135" s="4" t="s">
+      <c r="H135" s="4" t="s">
         <v>722</v>
-      </c>
-      <c r="H135" s="4" t="s">
-        <v>723</v>
       </c>
       <c r="I135" s="4" t="s">
         <v>101</v>
@@ -9007,10 +9007,10 @@
     </row>
     <row r="136" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="B136" s="4" t="s">
         <v>724</v>
-      </c>
-      <c r="B136" s="4" t="s">
-        <v>725</v>
       </c>
       <c r="C136" s="5">
         <v>-3.4763199999999999</v>
@@ -9022,19 +9022,19 @@
         <v>48</v>
       </c>
       <c r="F136" s="4" t="s">
+        <v>725</v>
+      </c>
+      <c r="G136" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="H136" s="4" t="s">
         <v>726</v>
-      </c>
-      <c r="G136" s="4" t="s">
-        <v>621</v>
-      </c>
-      <c r="H136" s="4" t="s">
-        <v>727</v>
       </c>
       <c r="I136" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J136" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K136" s="6" t="s">
         <v>18</v>
@@ -9042,10 +9042,10 @@
     </row>
     <row r="137" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="B137" s="4" t="s">
         <v>728</v>
-      </c>
-      <c r="B137" s="4" t="s">
-        <v>729</v>
       </c>
       <c r="C137" s="5">
         <v>-3.5617000000000001</v>
@@ -9057,13 +9057,13 @@
         <v>241</v>
       </c>
       <c r="F137" s="4" t="s">
+        <v>729</v>
+      </c>
+      <c r="G137" s="4" t="s">
         <v>730</v>
       </c>
-      <c r="G137" s="4" t="s">
+      <c r="H137" s="4" t="s">
         <v>731</v>
-      </c>
-      <c r="H137" s="4" t="s">
-        <v>732</v>
       </c>
       <c r="I137" s="4" t="s">
         <v>151</v>
@@ -9077,10 +9077,10 @@
     </row>
     <row r="138" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="B138" s="4" t="s">
         <v>733</v>
-      </c>
-      <c r="B138" s="4" t="s">
-        <v>734</v>
       </c>
       <c r="C138" s="5">
         <v>-5.4055679999999997</v>
@@ -9092,19 +9092,19 @@
         <v>136</v>
       </c>
       <c r="F138" s="4" t="s">
+        <v>734</v>
+      </c>
+      <c r="G138" s="4" t="s">
         <v>735</v>
       </c>
-      <c r="G138" s="4" t="s">
+      <c r="H138" s="4" t="s">
         <v>736</v>
-      </c>
-      <c r="H138" s="4" t="s">
-        <v>737</v>
       </c>
       <c r="I138" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J138" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K138" s="6" t="s">
         <v>18</v>
@@ -9112,10 +9112,10 @@
     </row>
     <row r="139" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="B139" s="4" t="s">
         <v>738</v>
-      </c>
-      <c r="B139" s="4" t="s">
-        <v>739</v>
       </c>
       <c r="C139" s="5">
         <v>-2.9586229999999998</v>
@@ -9127,19 +9127,19 @@
         <v>174</v>
       </c>
       <c r="F139" s="4" t="s">
+        <v>739</v>
+      </c>
+      <c r="G139" s="4" t="s">
         <v>740</v>
       </c>
-      <c r="G139" s="4" t="s">
+      <c r="H139" s="4" t="s">
         <v>741</v>
-      </c>
-      <c r="H139" s="4" t="s">
-        <v>742</v>
       </c>
       <c r="I139" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J139" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K139" s="6" t="s">
         <v>18</v>
@@ -9147,10 +9147,10 @@
     </row>
     <row r="140" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="B140" s="4" t="s">
         <v>743</v>
-      </c>
-      <c r="B140" s="4" t="s">
-        <v>744</v>
       </c>
       <c r="C140" s="5">
         <v>-2.92225</v>
@@ -9159,22 +9159,22 @@
         <v>-40.120244</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="F140" s="4" t="s">
+        <v>744</v>
+      </c>
+      <c r="G140" s="4" t="s">
         <v>745</v>
       </c>
-      <c r="G140" s="4" t="s">
+      <c r="H140" s="4" t="s">
         <v>746</v>
-      </c>
-      <c r="H140" s="4" t="s">
-        <v>747</v>
       </c>
       <c r="I140" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J140" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K140" s="6" t="s">
         <v>18</v>
@@ -9182,10 +9182,10 @@
     </row>
     <row r="141" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="B141" s="4" t="s">
         <v>748</v>
-      </c>
-      <c r="B141" s="4" t="s">
-        <v>749</v>
       </c>
       <c r="C141" s="5">
         <v>-3.697114</v>
@@ -9197,19 +9197,19 @@
         <v>48</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="G141" s="4" t="s">
         <v>51</v>
       </c>
       <c r="H141" s="4" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="I141" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J141" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K141" s="6" t="s">
         <v>18</v>
@@ -9217,10 +9217,10 @@
     </row>
     <row r="142" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="B142" s="4" t="s">
         <v>752</v>
-      </c>
-      <c r="B142" s="4" t="s">
-        <v>753</v>
       </c>
       <c r="C142" s="5">
         <v>-3.7188409999999998</v>
@@ -9232,19 +9232,19 @@
         <v>58</v>
       </c>
       <c r="F142" s="4" t="s">
+        <v>753</v>
+      </c>
+      <c r="G142" s="4" t="s">
         <v>754</v>
       </c>
-      <c r="G142" s="4" t="s">
+      <c r="H142" s="4" t="s">
         <v>755</v>
-      </c>
-      <c r="H142" s="4" t="s">
-        <v>756</v>
       </c>
       <c r="I142" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J142" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K142" s="6" t="s">
         <v>18</v>
@@ -9252,10 +9252,10 @@
     </row>
     <row r="143" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="B143" s="4" t="s">
         <v>757</v>
-      </c>
-      <c r="B143" s="4" t="s">
-        <v>758</v>
       </c>
       <c r="C143" s="5">
         <v>-4.0392330000000003</v>
@@ -9264,16 +9264,16 @@
         <v>-40.474150000000002</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="F143" s="4" t="s">
+        <v>758</v>
+      </c>
+      <c r="G143" s="4" t="s">
+        <v>605</v>
+      </c>
+      <c r="H143" s="4" t="s">
         <v>759</v>
-      </c>
-      <c r="G143" s="4" t="s">
-        <v>606</v>
-      </c>
-      <c r="H143" s="4" t="s">
-        <v>760</v>
       </c>
       <c r="I143" s="4" t="s">
         <v>151</v>
@@ -9287,10 +9287,10 @@
     </row>
     <row r="144" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="B144" s="4" t="s">
         <v>761</v>
-      </c>
-      <c r="B144" s="4" t="s">
-        <v>762</v>
       </c>
       <c r="C144" s="5">
         <v>-4.1177159999999997</v>
@@ -9302,13 +9302,13 @@
         <v>208</v>
       </c>
       <c r="F144" s="4" t="s">
+        <v>762</v>
+      </c>
+      <c r="G144" s="4" t="s">
         <v>763</v>
       </c>
-      <c r="G144" s="4" t="s">
+      <c r="H144" s="4" t="s">
         <v>764</v>
-      </c>
-      <c r="H144" s="4" t="s">
-        <v>765</v>
       </c>
       <c r="I144" s="4" t="s">
         <v>101</v>
@@ -9322,10 +9322,10 @@
     </row>
     <row r="145" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="B145" s="4" t="s">
         <v>766</v>
-      </c>
-      <c r="B145" s="4" t="s">
-        <v>767</v>
       </c>
       <c r="C145" s="5">
         <v>-4.5583349999999996</v>
@@ -9334,22 +9334,22 @@
         <v>-40.729585999999998</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="F145" s="4" t="s">
+        <v>767</v>
+      </c>
+      <c r="G145" s="4" t="s">
         <v>768</v>
       </c>
-      <c r="G145" s="4" t="s">
+      <c r="H145" s="4" t="s">
         <v>769</v>
-      </c>
-      <c r="H145" s="4" t="s">
-        <v>770</v>
       </c>
       <c r="I145" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J145" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K145" s="6" t="s">
         <v>18</v>
@@ -9357,10 +9357,10 @@
     </row>
     <row r="146" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="B146" s="4" t="s">
         <v>771</v>
-      </c>
-      <c r="B146" s="4" t="s">
-        <v>772</v>
       </c>
       <c r="C146" s="5">
         <v>-5.1463979999999996</v>
@@ -9369,22 +9369,22 @@
         <v>-40.670636000000002</v>
       </c>
       <c r="E146" s="4" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="F146" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="G146" s="4" t="s">
         <v>773</v>
       </c>
-      <c r="G146" s="4" t="s">
+      <c r="H146" s="4" t="s">
         <v>774</v>
-      </c>
-      <c r="H146" s="4" t="s">
-        <v>775</v>
       </c>
       <c r="I146" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J146" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K146" s="6" t="s">
         <v>18</v>
@@ -9392,10 +9392,10 @@
     </row>
     <row r="147" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="B147" s="4" t="s">
         <v>776</v>
-      </c>
-      <c r="B147" s="4" t="s">
-        <v>777</v>
       </c>
       <c r="C147" s="5">
         <v>-4.0631500000000003</v>
@@ -9404,16 +9404,16 @@
         <v>-40.957650000000001</v>
       </c>
       <c r="E147" s="4" t="s">
+        <v>777</v>
+      </c>
+      <c r="F147" s="4" t="s">
         <v>778</v>
       </c>
-      <c r="F147" s="4" t="s">
+      <c r="G147" s="4" t="s">
         <v>779</v>
       </c>
-      <c r="G147" s="4" t="s">
+      <c r="H147" s="4" t="s">
         <v>780</v>
-      </c>
-      <c r="H147" s="4" t="s">
-        <v>781</v>
       </c>
       <c r="I147" s="4" t="s">
         <v>101</v>
@@ -9422,15 +9422,15 @@
         <v>17</v>
       </c>
       <c r="K147" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="148" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="B148" s="4" t="s">
         <v>782</v>
-      </c>
-      <c r="B148" s="4" t="s">
-        <v>783</v>
       </c>
       <c r="C148" s="5">
         <v>-3.521487</v>
@@ -9439,22 +9439,22 @@
         <v>-40.330056999999996</v>
       </c>
       <c r="E148" s="4" t="s">
+        <v>783</v>
+      </c>
+      <c r="F148" s="4" t="s">
         <v>784</v>
       </c>
-      <c r="F148" s="4" t="s">
+      <c r="G148" s="4" t="s">
         <v>785</v>
       </c>
-      <c r="G148" s="4" t="s">
+      <c r="H148" s="4" t="s">
         <v>786</v>
-      </c>
-      <c r="H148" s="4" t="s">
-        <v>787</v>
       </c>
       <c r="I148" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J148" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K148" s="6" t="s">
         <v>18</v>
@@ -9462,10 +9462,10 @@
     </row>
     <row r="149" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
+        <v>787</v>
+      </c>
+      <c r="B149" s="4" t="s">
         <v>788</v>
-      </c>
-      <c r="B149" s="4" t="s">
-        <v>789</v>
       </c>
       <c r="C149" s="5">
         <v>-3.5194079999999999</v>
@@ -9474,22 +9474,22 @@
         <v>-40.361950999999998</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="F149" s="4" t="s">
+        <v>789</v>
+      </c>
+      <c r="G149" s="4" t="s">
         <v>790</v>
       </c>
-      <c r="G149" s="4" t="s">
+      <c r="H149" s="4" t="s">
         <v>791</v>
-      </c>
-      <c r="H149" s="4" t="s">
-        <v>792</v>
       </c>
       <c r="I149" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J149" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K149" s="6" t="s">
         <v>18</v>
@@ -9497,10 +9497,10 @@
     </row>
     <row r="150" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
+        <v>792</v>
+      </c>
+      <c r="B150" s="4" t="s">
         <v>793</v>
-      </c>
-      <c r="B150" s="4" t="s">
-        <v>794</v>
       </c>
       <c r="C150" s="5">
         <v>-3.552886</v>
@@ -9512,19 +9512,19 @@
         <v>48</v>
       </c>
       <c r="F150" s="4" t="s">
+        <v>794</v>
+      </c>
+      <c r="G150" s="4" t="s">
         <v>795</v>
       </c>
-      <c r="G150" s="4" t="s">
+      <c r="H150" s="4" t="s">
         <v>796</v>
-      </c>
-      <c r="H150" s="4" t="s">
-        <v>797</v>
       </c>
       <c r="I150" s="4" t="s">
         <v>151</v>
       </c>
       <c r="J150" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K150" s="6" t="s">
         <v>18</v>
@@ -9571,174 +9571,174 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="29" t="s">
+      <c r="B1" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="30" t="s">
+      <c r="D1" s="31" t="s">
+        <v>799</v>
+      </c>
+      <c r="E1" s="31"/>
+      <c r="F1" s="32" t="s">
         <v>800</v>
       </c>
-      <c r="E1" s="30"/>
-      <c r="F1" s="31" t="s">
+      <c r="G1" s="32"/>
+      <c r="H1" s="28" t="s">
         <v>801</v>
       </c>
-      <c r="G1" s="31"/>
-      <c r="H1" s="27" t="s">
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="28"/>
+      <c r="R1" s="28"/>
+      <c r="S1" s="28"/>
+      <c r="T1" s="28"/>
+      <c r="U1" s="28"/>
+      <c r="V1" s="28"/>
+      <c r="W1" s="28"/>
+      <c r="X1" s="28"/>
+      <c r="Y1" s="28"/>
+      <c r="Z1" s="28"/>
+      <c r="AA1" s="28"/>
+      <c r="AB1" s="28"/>
+      <c r="AC1" s="26" t="s">
         <v>802</v>
       </c>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
-      <c r="P1" s="27"/>
-      <c r="Q1" s="27"/>
-      <c r="R1" s="27"/>
-      <c r="S1" s="27"/>
-      <c r="T1" s="27"/>
-      <c r="U1" s="27"/>
-      <c r="V1" s="27"/>
-      <c r="W1" s="27"/>
-      <c r="X1" s="27"/>
-      <c r="Y1" s="27"/>
-      <c r="Z1" s="27"/>
-      <c r="AA1" s="27"/>
-      <c r="AB1" s="27"/>
-      <c r="AC1" s="25" t="s">
+    </row>
+    <row r="2" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="29"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="27" t="s">
         <v>803</v>
       </c>
-    </row>
-    <row r="2" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="28"/>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="26" t="s">
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="9" t="s">
         <v>804</v>
       </c>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="9" t="s">
+      <c r="L2" s="9" t="s">
+        <v>804</v>
+      </c>
+      <c r="M2" s="28" t="s">
         <v>805</v>
       </c>
-      <c r="L2" s="9" t="s">
-        <v>805</v>
-      </c>
-      <c r="M2" s="27" t="s">
+      <c r="N2" s="28"/>
+      <c r="O2" s="28"/>
+      <c r="P2" s="28"/>
+      <c r="Q2" s="28"/>
+      <c r="R2" s="28"/>
+      <c r="S2" s="28"/>
+      <c r="T2" s="28"/>
+      <c r="U2" s="28"/>
+      <c r="V2" s="28"/>
+      <c r="W2" s="28"/>
+      <c r="X2" s="28"/>
+      <c r="Y2" s="28"/>
+      <c r="Z2" s="28"/>
+      <c r="AA2" s="28"/>
+      <c r="AB2" s="28"/>
+      <c r="AC2" s="26"/>
+    </row>
+    <row r="3" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="29"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="8" t="s">
         <v>806</v>
       </c>
-      <c r="N2" s="27"/>
-      <c r="O2" s="27"/>
-      <c r="P2" s="27"/>
-      <c r="Q2" s="27"/>
-      <c r="R2" s="27"/>
-      <c r="S2" s="27"/>
-      <c r="T2" s="27"/>
-      <c r="U2" s="27"/>
-      <c r="V2" s="27"/>
-      <c r="W2" s="27"/>
-      <c r="X2" s="27"/>
-      <c r="Y2" s="27"/>
-      <c r="Z2" s="27"/>
-      <c r="AA2" s="27"/>
-      <c r="AB2" s="27"/>
-      <c r="AC2" s="25"/>
-    </row>
-    <row r="3" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="28"/>
-      <c r="B3" s="29"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="8" t="s">
+      <c r="I3" s="8" t="s">
         <v>807</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="J3" s="8" t="s">
         <v>808</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="K3" s="7" t="s">
         <v>809</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="L3" s="7" t="s">
         <v>810</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="M3" s="7" t="s">
         <v>811</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="N3" s="7" t="s">
         <v>812</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="O3" s="7" t="s">
         <v>813</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="P3" s="7" t="s">
         <v>814</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="Q3" s="7" t="s">
         <v>815</v>
       </c>
-      <c r="Q3" s="7" t="s">
+      <c r="R3" s="7" t="s">
         <v>816</v>
       </c>
-      <c r="R3" s="7" t="s">
+      <c r="S3" s="7" t="s">
         <v>817</v>
       </c>
-      <c r="S3" s="7" t="s">
+      <c r="T3" s="7" t="s">
         <v>818</v>
       </c>
-      <c r="T3" s="7" t="s">
+      <c r="U3" s="7" t="s">
         <v>819</v>
       </c>
-      <c r="U3" s="7" t="s">
+      <c r="V3" s="7" t="s">
         <v>820</v>
       </c>
-      <c r="V3" s="7" t="s">
+      <c r="W3" s="7" t="s">
         <v>821</v>
       </c>
-      <c r="W3" s="7" t="s">
+      <c r="X3" s="7" t="s">
         <v>822</v>
       </c>
-      <c r="X3" s="7" t="s">
+      <c r="Y3" s="7" t="s">
         <v>823</v>
       </c>
-      <c r="Y3" s="7" t="s">
+      <c r="Z3" s="7" t="s">
         <v>824</v>
       </c>
-      <c r="Z3" s="7" t="s">
+      <c r="AA3" s="7" t="s">
         <v>825</v>
       </c>
-      <c r="AA3" s="7" t="s">
+      <c r="AB3" s="7" t="s">
         <v>826</v>
       </c>
-      <c r="AB3" s="7" t="s">
-        <v>827</v>
-      </c>
-      <c r="AC3" s="25"/>
+      <c r="AC3" s="26"/>
     </row>
     <row r="4" spans="1:29" ht="104.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="28"/>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
+      <c r="A4" s="29"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="30"/>
       <c r="D4" s="22" t="s">
         <v>2</v>
       </c>
       <c r="E4" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
       <c r="H4" s="10"/>
       <c r="I4" s="10"/>
       <c r="J4" s="10"/>
@@ -9760,7 +9760,7 @@
       <c r="Z4" s="11"/>
       <c r="AA4" s="11"/>
       <c r="AB4" s="11"/>
-      <c r="AC4" s="25"/>
+      <c r="AC4" s="26"/>
     </row>
     <row r="5" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="19" t="s">
@@ -10159,7 +10159,7 @@
         <v>5682</v>
       </c>
     </row>
-    <row r="12" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="19" t="s">
         <v>141</v>
       </c>
@@ -10254,10 +10254,10 @@
         <v>147</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="D13" s="21"/>
       <c r="E13" s="21"/>
@@ -10303,10 +10303,10 @@
         <v>160</v>
       </c>
       <c r="D14" s="24" t="s">
+        <v>848</v>
+      </c>
+      <c r="E14" s="24" t="s">
         <v>849</v>
-      </c>
-      <c r="E14" s="24" t="s">
-        <v>850</v>
       </c>
       <c r="F14" s="20">
         <v>46142</v>
@@ -10662,10 +10662,10 @@
         <v>198</v>
       </c>
       <c r="D19" s="24" t="s">
+        <v>850</v>
+      </c>
+      <c r="E19" s="24" t="s">
         <v>851</v>
-      </c>
-      <c r="E19" s="24" t="s">
-        <v>852</v>
       </c>
       <c r="F19" s="20">
         <v>46142</v>
@@ -10744,13 +10744,13 @@
     </row>
     <row r="20" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="19" t="s">
+        <v>601</v>
+      </c>
+      <c r="B20" s="19" t="s">
         <v>602</v>
       </c>
-      <c r="B20" s="19" t="s">
+      <c r="C20" s="19" t="s">
         <v>603</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>604</v>
       </c>
       <c r="D20" s="21">
         <v>-3.7752400000000002</v>
@@ -10835,13 +10835,13 @@
     </row>
     <row r="21" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="19" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B21" s="19" t="s">
         <v>208</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="D21" s="21"/>
       <c r="E21" s="21"/>
@@ -10878,13 +10878,13 @@
     </row>
     <row r="22" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="19" t="s">
+        <v>612</v>
+      </c>
+      <c r="B22" s="19" t="s">
         <v>613</v>
       </c>
-      <c r="B22" s="19" t="s">
+      <c r="C22" s="19" t="s">
         <v>614</v>
-      </c>
-      <c r="C22" s="19" t="s">
-        <v>615</v>
       </c>
       <c r="D22" s="21">
         <v>-4.7911549999999998</v>
@@ -10969,19 +10969,19 @@
     </row>
     <row r="23" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="19" t="s">
+        <v>618</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="C23" s="19" t="s">
         <v>619</v>
       </c>
-      <c r="B23" s="19" t="s">
-        <v>410</v>
-      </c>
-      <c r="C23" s="19" t="s">
-        <v>620</v>
-      </c>
       <c r="D23" s="24" t="s">
+        <v>858</v>
+      </c>
+      <c r="E23" s="24" t="s">
         <v>859</v>
-      </c>
-      <c r="E23" s="24" t="s">
-        <v>860</v>
       </c>
       <c r="F23" s="20">
         <v>46153</v>
@@ -11060,13 +11060,13 @@
     </row>
     <row r="24" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="19" t="s">
+        <v>623</v>
+      </c>
+      <c r="B24" s="19" t="s">
         <v>624</v>
       </c>
-      <c r="B24" s="19" t="s">
+      <c r="C24" s="19" t="s">
         <v>625</v>
-      </c>
-      <c r="C24" s="19" t="s">
-        <v>626</v>
       </c>
       <c r="D24" s="21"/>
       <c r="E24" s="21"/>
@@ -11103,19 +11103,19 @@
     </row>
     <row r="25" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="19" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B25" s="19" t="s">
         <v>235</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D25" s="24" t="s">
+        <v>868</v>
+      </c>
+      <c r="E25" s="24" t="s">
         <v>869</v>
-      </c>
-      <c r="E25" s="24" t="s">
-        <v>870</v>
       </c>
       <c r="F25" s="20">
         <v>46159</v>
@@ -11194,13 +11194,13 @@
     </row>
     <row r="26" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="19" t="s">
+        <v>634</v>
+      </c>
+      <c r="B26" s="19" t="s">
+        <v>470</v>
+      </c>
+      <c r="C26" s="19" t="s">
         <v>635</v>
-      </c>
-      <c r="B26" s="19" t="s">
-        <v>471</v>
-      </c>
-      <c r="C26" s="19" t="s">
-        <v>636</v>
       </c>
       <c r="D26" s="21"/>
       <c r="E26" s="21"/>
@@ -11237,13 +11237,13 @@
     </row>
     <row r="27" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>500</v>
+      </c>
+      <c r="C27" s="19" t="s">
         <v>640</v>
-      </c>
-      <c r="B27" s="19" t="s">
-        <v>501</v>
-      </c>
-      <c r="C27" s="19" t="s">
-        <v>641</v>
       </c>
       <c r="D27" s="24">
         <v>-5.0453950000000001</v>
@@ -11337,10 +11337,10 @@
         <v>203</v>
       </c>
       <c r="D28" s="24" t="s">
+        <v>852</v>
+      </c>
+      <c r="E28" s="24" t="s">
         <v>853</v>
-      </c>
-      <c r="E28" s="24" t="s">
-        <v>854</v>
       </c>
       <c r="F28" s="20">
         <v>46142</v>
@@ -11419,19 +11419,19 @@
     </row>
     <row r="29" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B29" s="19" t="s">
         <v>76</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="D29" s="24" t="s">
+        <v>834</v>
+      </c>
+      <c r="E29" s="24" t="s">
         <v>835</v>
-      </c>
-      <c r="E29" s="24" t="s">
-        <v>836</v>
       </c>
       <c r="F29" s="20">
         <v>46139</v>
@@ -11510,13 +11510,13 @@
     </row>
     <row r="30" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B30" s="19" t="s">
         <v>104</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D30" s="21"/>
       <c r="E30" s="21"/>
@@ -11553,13 +11553,13 @@
     </row>
     <row r="31" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B31" s="19" t="s">
         <v>36</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D31" s="21">
         <v>-4.2869089999999996</v>
@@ -11644,13 +11644,13 @@
     </row>
     <row r="32" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B32" s="19" t="s">
         <v>174</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D32" s="21"/>
       <c r="E32" s="21"/>
@@ -11687,13 +11687,13 @@
     </row>
     <row r="33" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B33" s="19" t="s">
         <v>174</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="D33" s="24">
         <v>-2.8945319999999999</v>
@@ -11776,15 +11776,15 @@
         <v>4636</v>
       </c>
     </row>
-    <row r="34" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="19" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B34" s="19" t="s">
         <v>25</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D34" s="21">
         <v>-4.5809499999999996</v>
@@ -11868,13 +11868,13 @@
     </row>
     <row r="35" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B35" s="19" t="s">
         <v>191</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D35" s="21"/>
       <c r="E35" s="21"/>
@@ -11911,13 +11911,13 @@
     </row>
     <row r="36" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B36" s="19" t="s">
         <v>191</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="D36" s="24">
         <v>-5.4253080000000002</v>
@@ -12002,13 +12002,13 @@
     </row>
     <row r="37" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
+        <v>682</v>
+      </c>
+      <c r="B37" s="19" t="s">
         <v>683</v>
       </c>
-      <c r="B37" s="19" t="s">
+      <c r="C37" s="19" t="s">
         <v>684</v>
-      </c>
-      <c r="C37" s="19" t="s">
-        <v>685</v>
       </c>
       <c r="D37" s="21"/>
       <c r="E37" s="21"/>
@@ -12045,13 +12045,13 @@
     </row>
     <row r="38" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="19" t="s">
+        <v>688</v>
+      </c>
+      <c r="B38" s="19" t="s">
+        <v>683</v>
+      </c>
+      <c r="C38" s="19" t="s">
         <v>689</v>
-      </c>
-      <c r="B38" s="19" t="s">
-        <v>684</v>
-      </c>
-      <c r="C38" s="19" t="s">
-        <v>690</v>
       </c>
       <c r="D38" s="21"/>
       <c r="E38" s="21"/>
@@ -12086,58 +12086,106 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="19" t="s">
+        <v>693</v>
+      </c>
+      <c r="B39" s="19" t="s">
         <v>694</v>
       </c>
-      <c r="B39" s="19" t="s">
+      <c r="C39" s="19" t="s">
         <v>695</v>
       </c>
-      <c r="C39" s="19" t="s">
-        <v>696</v>
-      </c>
-      <c r="D39" s="21"/>
-      <c r="E39" s="21"/>
-      <c r="F39" s="20"/>
+      <c r="D39" s="24">
+        <v>-3.6789869999999998</v>
+      </c>
+      <c r="E39" s="24">
+        <v>-38.909970999999999</v>
+      </c>
+      <c r="F39" s="20">
+        <v>46177</v>
+      </c>
       <c r="G39" s="20">
         <f t="shared" si="0"/>
+        <v>46179</v>
+      </c>
+      <c r="H39" s="12">
+        <v>312</v>
+      </c>
+      <c r="I39" s="12">
+        <v>915</v>
+      </c>
+      <c r="J39" s="12">
+        <v>15</v>
+      </c>
+      <c r="K39" s="12">
+        <v>190</v>
+      </c>
+      <c r="L39" s="12">
+        <v>49</v>
+      </c>
+      <c r="M39" s="12">
+        <v>8</v>
+      </c>
+      <c r="N39" s="12">
+        <v>4</v>
+      </c>
+      <c r="O39" s="12">
+        <v>3</v>
+      </c>
+      <c r="P39" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="12">
+        <v>8</v>
+      </c>
+      <c r="R39" s="12">
+        <v>9</v>
+      </c>
+      <c r="S39" s="12">
+        <v>0</v>
+      </c>
+      <c r="T39" s="12">
+        <v>11</v>
+      </c>
+      <c r="U39" s="12">
+        <v>0</v>
+      </c>
+      <c r="V39" s="12">
+        <v>0</v>
+      </c>
+      <c r="W39" s="12">
+        <v>1</v>
+      </c>
+      <c r="X39" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y39" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z39" s="12">
         <v>2</v>
       </c>
-      <c r="H39" s="12"/>
-      <c r="I39" s="12"/>
-      <c r="J39" s="12"/>
-      <c r="K39" s="12"/>
-      <c r="L39" s="12"/>
-      <c r="M39" s="12"/>
-      <c r="N39" s="12"/>
-      <c r="O39" s="12"/>
-      <c r="P39" s="12"/>
-      <c r="Q39" s="12"/>
-      <c r="R39" s="12"/>
-      <c r="S39" s="12"/>
-      <c r="T39" s="12"/>
-      <c r="U39" s="12"/>
-      <c r="V39" s="12"/>
-      <c r="W39" s="12"/>
-      <c r="X39" s="12"/>
-      <c r="Y39" s="12"/>
-      <c r="Z39" s="12"/>
-      <c r="AA39" s="12"/>
-      <c r="AB39" s="12"/>
+      <c r="AA39" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB39" s="12">
+        <v>0</v>
+      </c>
       <c r="AC39" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="40" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="19" t="s">
+        <v>699</v>
+      </c>
+      <c r="B40" s="19" t="s">
         <v>700</v>
       </c>
-      <c r="B40" s="19" t="s">
+      <c r="C40" s="19" t="s">
         <v>701</v>
-      </c>
-      <c r="C40" s="19" t="s">
-        <v>702</v>
       </c>
       <c r="D40" s="21"/>
       <c r="E40" s="21"/>
@@ -12174,13 +12222,13 @@
     </row>
     <row r="41" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="19" t="s">
+        <v>703</v>
+      </c>
+      <c r="B41" s="19" t="s">
         <v>704</v>
       </c>
-      <c r="B41" s="19" t="s">
+      <c r="C41" s="19" t="s">
         <v>705</v>
-      </c>
-      <c r="C41" s="19" t="s">
-        <v>706</v>
       </c>
       <c r="D41" s="21"/>
       <c r="E41" s="21"/>
@@ -12217,19 +12265,19 @@
     </row>
     <row r="42" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="19" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B42" s="19" t="s">
         <v>197</v>
       </c>
       <c r="C42" s="19" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D42" s="24" t="s">
+        <v>836</v>
+      </c>
+      <c r="E42" s="24" t="s">
         <v>837</v>
-      </c>
-      <c r="E42" s="24" t="s">
-        <v>838</v>
       </c>
       <c r="F42" s="20">
         <v>46139</v>
@@ -12308,13 +12356,13 @@
     </row>
     <row r="43" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="19" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B43" s="19" t="s">
         <v>174</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D43" s="21"/>
       <c r="E43" s="21"/>
@@ -12351,13 +12399,13 @@
     </row>
     <row r="44" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="19" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B44" s="19" t="s">
         <v>266</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D44" s="21"/>
       <c r="E44" s="21"/>
@@ -12394,19 +12442,19 @@
     </row>
     <row r="45" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="19" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B45" s="19" t="s">
         <v>48</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="D45" s="24" t="s">
+        <v>860</v>
+      </c>
+      <c r="E45" s="24" t="s">
         <v>861</v>
-      </c>
-      <c r="E45" s="24" t="s">
-        <v>862</v>
       </c>
       <c r="F45" s="20">
         <v>46153</v>
@@ -12485,13 +12533,13 @@
     </row>
     <row r="46" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="19" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B46" s="19" t="s">
         <v>241</v>
       </c>
       <c r="C46" s="19" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="D46" s="21"/>
       <c r="E46" s="21"/>
@@ -12528,13 +12576,13 @@
     </row>
     <row r="47" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="19" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B47" s="19" t="s">
         <v>136</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="D47" s="21">
         <v>-5.4055679999999997</v>
@@ -12619,13 +12667,13 @@
     </row>
     <row r="48" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="19" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B48" s="19" t="s">
         <v>174</v>
       </c>
       <c r="C48" s="19" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D48" s="24">
         <v>-2.9586229999999998</v>
@@ -12710,13 +12758,13 @@
     </row>
     <row r="49" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="19" t="s">
+        <v>743</v>
+      </c>
+      <c r="B49" s="19" t="s">
+        <v>554</v>
+      </c>
+      <c r="C49" s="19" t="s">
         <v>744</v>
-      </c>
-      <c r="B49" s="19" t="s">
-        <v>555</v>
-      </c>
-      <c r="C49" s="19" t="s">
-        <v>745</v>
       </c>
       <c r="D49" s="24">
         <v>-2.92225</v>
@@ -12801,13 +12849,13 @@
     </row>
     <row r="50" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="19" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B50" s="19" t="s">
         <v>48</v>
       </c>
       <c r="C50" s="19" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D50" s="21">
         <v>-3.697114</v>
@@ -12892,13 +12940,13 @@
     </row>
     <row r="51" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="19" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B51" s="19" t="s">
         <v>58</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="D51" s="21">
         <v>-3.7188409999999998</v>
@@ -12983,13 +13031,13 @@
     </row>
     <row r="52" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="19" t="s">
+        <v>757</v>
+      </c>
+      <c r="B52" s="19" t="s">
+        <v>602</v>
+      </c>
+      <c r="C52" s="19" t="s">
         <v>758</v>
-      </c>
-      <c r="B52" s="19" t="s">
-        <v>603</v>
-      </c>
-      <c r="C52" s="19" t="s">
-        <v>759</v>
       </c>
       <c r="D52" s="21"/>
       <c r="E52" s="21"/>
@@ -13026,13 +13074,13 @@
     </row>
     <row r="53" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="19" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B53" s="19" t="s">
         <v>208</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D53" s="21"/>
       <c r="E53" s="21"/>
@@ -13069,13 +13117,13 @@
     </row>
     <row r="54" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="19" t="s">
+        <v>766</v>
+      </c>
+      <c r="B54" s="19" t="s">
+        <v>613</v>
+      </c>
+      <c r="C54" s="19" t="s">
         <v>767</v>
-      </c>
-      <c r="B54" s="19" t="s">
-        <v>614</v>
-      </c>
-      <c r="C54" s="19" t="s">
-        <v>768</v>
       </c>
       <c r="D54" s="21">
         <v>-4.5583349999999996</v>
@@ -13160,13 +13208,13 @@
     </row>
     <row r="55" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="19" t="s">
+        <v>771</v>
+      </c>
+      <c r="B55" s="19" t="s">
+        <v>613</v>
+      </c>
+      <c r="C55" s="19" t="s">
         <v>772</v>
-      </c>
-      <c r="B55" s="19" t="s">
-        <v>614</v>
-      </c>
-      <c r="C55" s="19" t="s">
-        <v>773</v>
       </c>
       <c r="D55" s="21">
         <v>-5.1463979999999996</v>
@@ -13251,13 +13299,13 @@
     </row>
     <row r="56" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="19" t="s">
+        <v>776</v>
+      </c>
+      <c r="B56" s="19" t="s">
         <v>777</v>
       </c>
-      <c r="B56" s="19" t="s">
+      <c r="C56" s="19" t="s">
         <v>778</v>
-      </c>
-      <c r="C56" s="19" t="s">
-        <v>779</v>
       </c>
       <c r="D56" s="21"/>
       <c r="E56" s="21"/>
@@ -13294,19 +13342,19 @@
     </row>
     <row r="57" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="19" t="s">
+        <v>782</v>
+      </c>
+      <c r="B57" s="19" t="s">
         <v>783</v>
       </c>
-      <c r="B57" s="19" t="s">
+      <c r="C57" s="19" t="s">
         <v>784</v>
       </c>
-      <c r="C57" s="19" t="s">
-        <v>785</v>
-      </c>
       <c r="D57" s="24" t="s">
+        <v>870</v>
+      </c>
+      <c r="E57" s="24" t="s">
         <v>871</v>
-      </c>
-      <c r="E57" s="24" t="s">
-        <v>872</v>
       </c>
       <c r="F57" s="20">
         <v>46159</v>
@@ -13385,19 +13433,19 @@
     </row>
     <row r="58" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="19" t="s">
+        <v>788</v>
+      </c>
+      <c r="B58" s="19" t="s">
+        <v>783</v>
+      </c>
+      <c r="C58" s="19" t="s">
         <v>789</v>
       </c>
-      <c r="B58" s="19" t="s">
-        <v>784</v>
-      </c>
-      <c r="C58" s="19" t="s">
-        <v>790</v>
-      </c>
       <c r="D58" s="24" t="s">
+        <v>872</v>
+      </c>
+      <c r="E58" s="24" t="s">
         <v>873</v>
-      </c>
-      <c r="E58" s="24" t="s">
-        <v>874</v>
       </c>
       <c r="F58" s="20">
         <v>46159</v>
@@ -13476,19 +13524,19 @@
     </row>
     <row r="59" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="19" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B59" s="19" t="s">
         <v>48</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="D59" s="24" t="s">
+        <v>874</v>
+      </c>
+      <c r="E59" s="24" t="s">
         <v>875</v>
-      </c>
-      <c r="E59" s="24" t="s">
-        <v>876</v>
       </c>
       <c r="F59" s="20">
         <v>46159</v>
@@ -13567,13 +13615,13 @@
     </row>
     <row r="60" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="19" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B60" s="19" t="s">
         <v>148</v>
       </c>
       <c r="C60" s="19" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D60" s="21">
         <v>-4.228675</v>
@@ -13658,13 +13706,13 @@
     </row>
     <row r="61" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="19" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B61" s="19" t="s">
         <v>148</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D61" s="21"/>
       <c r="E61" s="21"/>
@@ -13701,13 +13749,13 @@
     </row>
     <row r="62" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="19" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B62" s="19" t="s">
         <v>148</v>
       </c>
       <c r="C62" s="19" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D62" s="21"/>
       <c r="E62" s="21"/>
@@ -13744,13 +13792,13 @@
     </row>
     <row r="63" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="19" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B63" s="19" t="s">
         <v>87</v>
       </c>
       <c r="C63" s="19" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D63" s="21">
         <v>-4.5644640000000001</v>
@@ -13833,15 +13881,15 @@
         <v>2906</v>
       </c>
     </row>
-    <row r="64" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="19" t="s">
+        <v>333</v>
+      </c>
+      <c r="B64" s="19" t="s">
         <v>334</v>
       </c>
-      <c r="B64" s="19" t="s">
+      <c r="C64" s="19" t="s">
         <v>335</v>
-      </c>
-      <c r="C64" s="19" t="s">
-        <v>336</v>
       </c>
       <c r="D64" s="21">
         <v>-4.7203499999999998</v>
@@ -13925,13 +13973,13 @@
     </row>
     <row r="65" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="19" t="s">
+        <v>339</v>
+      </c>
+      <c r="B65" s="19" t="s">
         <v>340</v>
       </c>
-      <c r="B65" s="19" t="s">
+      <c r="C65" s="19" t="s">
         <v>341</v>
-      </c>
-      <c r="C65" s="19" t="s">
-        <v>342</v>
       </c>
       <c r="D65" s="24">
         <v>-4.8210379999999997</v>
@@ -14107,13 +14155,13 @@
     </row>
     <row r="67" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="19" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B67" s="19" t="s">
         <v>12</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D67" s="21">
         <v>-4.702947</v>
@@ -14198,13 +14246,13 @@
     </row>
     <row r="68" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="19" t="s">
+        <v>349</v>
+      </c>
+      <c r="B68" s="19" t="s">
         <v>350</v>
       </c>
-      <c r="B68" s="19" t="s">
+      <c r="C68" s="19" t="s">
         <v>351</v>
-      </c>
-      <c r="C68" s="19" t="s">
-        <v>352</v>
       </c>
       <c r="D68" s="24">
         <v>-5.2215020000000001</v>
@@ -14289,13 +14337,13 @@
     </row>
     <row r="69" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="19" t="s">
+        <v>355</v>
+      </c>
+      <c r="B69" s="19" t="s">
         <v>356</v>
       </c>
-      <c r="B69" s="19" t="s">
+      <c r="C69" s="19" t="s">
         <v>357</v>
-      </c>
-      <c r="C69" s="19" t="s">
-        <v>358</v>
       </c>
       <c r="D69" s="24">
         <v>-5.2506180000000002</v>
@@ -14380,13 +14428,13 @@
     </row>
     <row r="70" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="19" t="s">
+        <v>360</v>
+      </c>
+      <c r="B70" s="19" t="s">
         <v>361</v>
       </c>
-      <c r="B70" s="19" t="s">
+      <c r="C70" s="19" t="s">
         <v>362</v>
-      </c>
-      <c r="C70" s="19" t="s">
-        <v>363</v>
       </c>
       <c r="D70" s="24">
         <v>-5.4016780000000004</v>
@@ -14471,13 +14519,13 @@
     </row>
     <row r="71" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="19" t="s">
+        <v>366</v>
+      </c>
+      <c r="B71" s="19" t="s">
         <v>367</v>
       </c>
-      <c r="B71" s="19" t="s">
+      <c r="C71" s="19" t="s">
         <v>368</v>
-      </c>
-      <c r="C71" s="19" t="s">
-        <v>369</v>
       </c>
       <c r="D71" s="21"/>
       <c r="E71" s="21"/>
@@ -14514,13 +14562,13 @@
     </row>
     <row r="72" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="19" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B72" s="19" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="C72" s="19" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="D72" s="21"/>
       <c r="E72" s="21"/>
@@ -14557,13 +14605,13 @@
     </row>
     <row r="73" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="19" t="s">
+        <v>374</v>
+      </c>
+      <c r="B73" s="19" t="s">
         <v>375</v>
       </c>
-      <c r="B73" s="19" t="s">
+      <c r="C73" s="19" t="s">
         <v>376</v>
-      </c>
-      <c r="C73" s="19" t="s">
-        <v>377</v>
       </c>
       <c r="D73" s="21"/>
       <c r="E73" s="21"/>
@@ -14600,13 +14648,13 @@
     </row>
     <row r="74" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="19" t="s">
+        <v>380</v>
+      </c>
+      <c r="B74" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="C74" s="19" t="s">
         <v>381</v>
-      </c>
-      <c r="B74" s="19" t="s">
-        <v>376</v>
-      </c>
-      <c r="C74" s="19" t="s">
-        <v>382</v>
       </c>
       <c r="D74" s="21"/>
       <c r="E74" s="21"/>
@@ -14643,13 +14691,13 @@
     </row>
     <row r="75" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="19" t="s">
+        <v>385</v>
+      </c>
+      <c r="B75" s="19" t="s">
         <v>386</v>
       </c>
-      <c r="B75" s="19" t="s">
+      <c r="C75" s="19" t="s">
         <v>387</v>
-      </c>
-      <c r="C75" s="19" t="s">
-        <v>388</v>
       </c>
       <c r="D75" s="21"/>
       <c r="E75" s="21"/>
@@ -14686,13 +14734,13 @@
     </row>
     <row r="76" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="19" t="s">
+        <v>391</v>
+      </c>
+      <c r="B76" s="19" t="s">
         <v>392</v>
       </c>
-      <c r="B76" s="19" t="s">
+      <c r="C76" s="19" t="s">
         <v>393</v>
-      </c>
-      <c r="C76" s="19" t="s">
-        <v>394</v>
       </c>
       <c r="D76" s="21"/>
       <c r="E76" s="21"/>
@@ -14729,13 +14777,13 @@
     </row>
     <row r="77" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="19" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B77" s="19" t="s">
         <v>272</v>
       </c>
       <c r="C77" s="19" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D77" s="21"/>
       <c r="E77" s="21"/>
@@ -14772,13 +14820,13 @@
     </row>
     <row r="78" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="19" t="s">
+        <v>402</v>
+      </c>
+      <c r="B78" s="19" t="s">
         <v>403</v>
       </c>
-      <c r="B78" s="19" t="s">
+      <c r="C78" s="19" t="s">
         <v>404</v>
-      </c>
-      <c r="C78" s="19" t="s">
-        <v>405</v>
       </c>
       <c r="D78" s="21"/>
       <c r="E78" s="21"/>
@@ -14815,13 +14863,13 @@
     </row>
     <row r="79" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="19" t="s">
+        <v>408</v>
+      </c>
+      <c r="B79" s="19" t="s">
         <v>409</v>
       </c>
-      <c r="B79" s="19" t="s">
+      <c r="C79" s="19" t="s">
         <v>410</v>
-      </c>
-      <c r="C79" s="19" t="s">
-        <v>411</v>
       </c>
       <c r="D79" s="21"/>
       <c r="E79" s="21"/>
@@ -14858,19 +14906,19 @@
     </row>
     <row r="80" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="19" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B80" s="19" t="s">
         <v>266</v>
       </c>
       <c r="C80" s="19" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D80" s="24" t="s">
+        <v>862</v>
+      </c>
+      <c r="E80" s="24" t="s">
         <v>863</v>
-      </c>
-      <c r="E80" s="24" t="s">
-        <v>864</v>
       </c>
       <c r="F80" s="20">
         <v>46153</v>
@@ -14949,19 +14997,19 @@
     </row>
     <row r="81" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="19" t="s">
+        <v>419</v>
+      </c>
+      <c r="B81" s="19" t="s">
         <v>420</v>
       </c>
-      <c r="B81" s="19" t="s">
+      <c r="C81" s="19" t="s">
         <v>421</v>
       </c>
-      <c r="C81" s="19" t="s">
-        <v>422</v>
-      </c>
       <c r="D81" s="24" t="s">
+        <v>866</v>
+      </c>
+      <c r="E81" s="24" t="s">
         <v>867</v>
-      </c>
-      <c r="E81" s="24" t="s">
-        <v>868</v>
       </c>
       <c r="F81" s="20">
         <v>46153</v>
@@ -15040,13 +15088,13 @@
     </row>
     <row r="82" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="19" t="s">
+        <v>425</v>
+      </c>
+      <c r="B82" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="C82" s="19" t="s">
         <v>426</v>
-      </c>
-      <c r="B82" s="19" t="s">
-        <v>410</v>
-      </c>
-      <c r="C82" s="19" t="s">
-        <v>427</v>
       </c>
       <c r="D82" s="21"/>
       <c r="E82" s="21"/>
@@ -15083,13 +15131,13 @@
     </row>
     <row r="83" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="19" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B83" s="19" t="s">
         <v>229</v>
       </c>
       <c r="C83" s="19" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D83" s="21">
         <v>-4.3755519999999999</v>
@@ -15174,13 +15222,13 @@
     </row>
     <row r="84" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="19" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B84" s="19" t="s">
         <v>229</v>
       </c>
       <c r="C84" s="19" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D84" s="24">
         <v>-5.041658</v>
@@ -15265,13 +15313,13 @@
     </row>
     <row r="85" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="19" t="s">
+        <v>439</v>
+      </c>
+      <c r="B85" s="19" t="s">
         <v>440</v>
       </c>
-      <c r="B85" s="19" t="s">
+      <c r="C85" s="19" t="s">
         <v>441</v>
-      </c>
-      <c r="C85" s="19" t="s">
-        <v>442</v>
       </c>
       <c r="D85" s="24">
         <v>-5.2738310000000004</v>
@@ -15356,13 +15404,13 @@
     </row>
     <row r="86" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="19" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B86" s="19" t="s">
         <v>97</v>
       </c>
       <c r="C86" s="19" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D86" s="21"/>
       <c r="E86" s="21"/>
@@ -15399,13 +15447,13 @@
     </row>
     <row r="87" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="19" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B87" s="19" t="s">
         <v>235</v>
       </c>
       <c r="C87" s="19" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D87" s="21"/>
       <c r="E87" s="21"/>
@@ -15442,13 +15490,13 @@
     </row>
     <row r="88" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="19" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B88" s="19" t="s">
         <v>235</v>
       </c>
       <c r="C88" s="19" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D88" s="21">
         <v>-3.6184599999999998</v>
@@ -15533,13 +15581,13 @@
     </row>
     <row r="89" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="19" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B89" s="19" t="s">
         <v>235</v>
       </c>
       <c r="C89" s="19" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D89" s="21"/>
       <c r="E89" s="21"/>
@@ -15576,19 +15624,19 @@
     </row>
     <row r="90" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="19" t="s">
+        <v>465</v>
+      </c>
+      <c r="B90" s="19" t="s">
         <v>466</v>
       </c>
-      <c r="B90" s="19" t="s">
+      <c r="C90" s="19" t="s">
         <v>467</v>
       </c>
-      <c r="C90" s="19" t="s">
-        <v>468</v>
-      </c>
       <c r="D90" s="24" t="s">
+        <v>838</v>
+      </c>
+      <c r="E90" s="24" t="s">
         <v>839</v>
-      </c>
-      <c r="E90" s="24" t="s">
-        <v>840</v>
       </c>
       <c r="F90" s="20">
         <v>46139</v>
@@ -15667,13 +15715,13 @@
     </row>
     <row r="91" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="19" t="s">
+        <v>469</v>
+      </c>
+      <c r="B91" s="19" t="s">
         <v>470</v>
       </c>
-      <c r="B91" s="19" t="s">
+      <c r="C91" s="19" t="s">
         <v>471</v>
-      </c>
-      <c r="C91" s="19" t="s">
-        <v>472</v>
       </c>
       <c r="D91" s="21"/>
       <c r="E91" s="21"/>
@@ -15710,19 +15758,19 @@
     </row>
     <row r="92" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="19" t="s">
+        <v>475</v>
+      </c>
+      <c r="B92" s="19" t="s">
+        <v>470</v>
+      </c>
+      <c r="C92" s="19" t="s">
         <v>476</v>
       </c>
-      <c r="B92" s="19" t="s">
-        <v>471</v>
-      </c>
-      <c r="C92" s="19" t="s">
-        <v>477</v>
-      </c>
       <c r="D92" s="24" t="s">
+        <v>876</v>
+      </c>
+      <c r="E92" s="24" t="s">
         <v>877</v>
-      </c>
-      <c r="E92" s="24" t="s">
-        <v>878</v>
       </c>
       <c r="F92" s="20">
         <v>46159</v>
@@ -15801,19 +15849,19 @@
     </row>
     <row r="93" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="19" t="s">
+        <v>479</v>
+      </c>
+      <c r="B93" s="19" t="s">
         <v>480</v>
       </c>
-      <c r="B93" s="19" t="s">
+      <c r="C93" s="19" t="s">
         <v>481</v>
       </c>
-      <c r="C93" s="19" t="s">
-        <v>482</v>
-      </c>
       <c r="D93" s="24" t="s">
+        <v>854</v>
+      </c>
+      <c r="E93" s="24" t="s">
         <v>855</v>
-      </c>
-      <c r="E93" s="24" t="s">
-        <v>856</v>
       </c>
       <c r="F93" s="20">
         <v>46142</v>
@@ -15895,10 +15943,10 @@
         <v>153</v>
       </c>
       <c r="B94" s="19" t="s">
+        <v>828</v>
+      </c>
+      <c r="C94" s="19" t="s">
         <v>829</v>
-      </c>
-      <c r="C94" s="19" t="s">
-        <v>830</v>
       </c>
       <c r="D94" s="21">
         <v>-5.0822029999999998</v>
@@ -15983,13 +16031,13 @@
     </row>
     <row r="95" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="19" t="s">
+        <v>485</v>
+      </c>
+      <c r="B95" s="19" t="s">
         <v>486</v>
       </c>
-      <c r="B95" s="19" t="s">
+      <c r="C95" s="19" t="s">
         <v>487</v>
-      </c>
-      <c r="C95" s="19" t="s">
-        <v>488</v>
       </c>
       <c r="D95" s="24">
         <v>-5.4022300000000003</v>
@@ -16074,19 +16122,19 @@
     </row>
     <row r="96" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="19" t="s">
+        <v>491</v>
+      </c>
+      <c r="B96" s="19" t="s">
+        <v>486</v>
+      </c>
+      <c r="C96" s="19" t="s">
         <v>492</v>
       </c>
-      <c r="B96" s="19" t="s">
-        <v>487</v>
-      </c>
-      <c r="C96" s="19" t="s">
-        <v>493</v>
-      </c>
       <c r="D96" s="24" t="s">
+        <v>840</v>
+      </c>
+      <c r="E96" s="24" t="s">
         <v>841</v>
-      </c>
-      <c r="E96" s="24" t="s">
-        <v>842</v>
       </c>
       <c r="F96" s="20">
         <v>46139</v>
@@ -16165,19 +16213,19 @@
     </row>
     <row r="97" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="19" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B97" s="19" t="s">
         <v>136</v>
       </c>
       <c r="C97" s="19" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D97" s="24" t="s">
+        <v>842</v>
+      </c>
+      <c r="E97" s="24" t="s">
         <v>843</v>
-      </c>
-      <c r="E97" s="24" t="s">
-        <v>844</v>
       </c>
       <c r="F97" s="20">
         <v>46139</v>
@@ -16256,13 +16304,13 @@
     </row>
     <row r="98" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="19" t="s">
+        <v>499</v>
+      </c>
+      <c r="B98" s="19" t="s">
         <v>500</v>
       </c>
-      <c r="B98" s="19" t="s">
+      <c r="C98" s="19" t="s">
         <v>501</v>
-      </c>
-      <c r="C98" s="19" t="s">
-        <v>502</v>
       </c>
       <c r="D98" s="24">
         <v>-5.0848469999999999</v>
@@ -16347,13 +16395,13 @@
     </row>
     <row r="99" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="19" t="s">
+        <v>505</v>
+      </c>
+      <c r="B99" s="19" t="s">
+        <v>500</v>
+      </c>
+      <c r="C99" s="19" t="s">
         <v>506</v>
-      </c>
-      <c r="B99" s="19" t="s">
-        <v>501</v>
-      </c>
-      <c r="C99" s="19" t="s">
-        <v>507</v>
       </c>
       <c r="D99" s="24">
         <v>-5.2461500000000001</v>
@@ -16438,13 +16486,13 @@
     </row>
     <row r="100" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="19" t="s">
+        <v>510</v>
+      </c>
+      <c r="B100" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="C100" s="19" t="s">
         <v>511</v>
-      </c>
-      <c r="B100" s="19" t="s">
-        <v>376</v>
-      </c>
-      <c r="C100" s="19" t="s">
-        <v>512</v>
       </c>
       <c r="D100" s="21"/>
       <c r="E100" s="21"/>
@@ -16481,13 +16529,13 @@
     </row>
     <row r="101" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="19" t="s">
+        <v>515</v>
+      </c>
+      <c r="B101" s="19" t="s">
         <v>516</v>
       </c>
-      <c r="B101" s="19" t="s">
+      <c r="C101" s="19" t="s">
         <v>517</v>
-      </c>
-      <c r="C101" s="19" t="s">
-        <v>518</v>
       </c>
       <c r="D101" s="21"/>
       <c r="E101" s="21"/>
@@ -16524,13 +16572,13 @@
     </row>
     <row r="102" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="19" t="s">
+        <v>521</v>
+      </c>
+      <c r="B102" s="19" t="s">
         <v>522</v>
       </c>
-      <c r="B102" s="19" t="s">
+      <c r="C102" s="19" t="s">
         <v>523</v>
-      </c>
-      <c r="C102" s="19" t="s">
-        <v>524</v>
       </c>
       <c r="D102" s="21"/>
       <c r="E102" s="21"/>
@@ -16573,7 +16621,7 @@
         <v>165</v>
       </c>
       <c r="C103" s="19" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="D103" s="21">
         <v>-4.8596729999999999</v>
@@ -16658,13 +16706,13 @@
     </row>
     <row r="104" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="19" t="s">
+        <v>527</v>
+      </c>
+      <c r="B104" s="19" t="s">
         <v>528</v>
       </c>
-      <c r="B104" s="19" t="s">
+      <c r="C104" s="19" t="s">
         <v>529</v>
-      </c>
-      <c r="C104" s="19" t="s">
-        <v>530</v>
       </c>
       <c r="D104" s="21">
         <v>-4.4447369999999999</v>
@@ -16749,13 +16797,13 @@
     </row>
     <row r="105" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="19" t="s">
+        <v>533</v>
+      </c>
+      <c r="B105" s="19" t="s">
         <v>534</v>
       </c>
-      <c r="B105" s="19" t="s">
+      <c r="C105" s="19" t="s">
         <v>535</v>
-      </c>
-      <c r="C105" s="19" t="s">
-        <v>536</v>
       </c>
       <c r="D105" s="21">
         <v>-5.1705110000000003</v>
@@ -16838,15 +16886,15 @@
         <v>2124</v>
       </c>
     </row>
-    <row r="106" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="19" t="s">
+        <v>539</v>
+      </c>
+      <c r="B106" s="19" t="s">
+        <v>486</v>
+      </c>
+      <c r="C106" s="19" t="s">
         <v>540</v>
-      </c>
-      <c r="B106" s="19" t="s">
-        <v>487</v>
-      </c>
-      <c r="C106" s="19" t="s">
-        <v>541</v>
       </c>
       <c r="D106" s="21">
         <v>-4.5701299999999998</v>
@@ -16930,13 +16978,13 @@
     </row>
     <row r="107" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="19" t="s">
+        <v>544</v>
+      </c>
+      <c r="B107" s="19" t="s">
+        <v>356</v>
+      </c>
+      <c r="C107" s="19" t="s">
         <v>545</v>
-      </c>
-      <c r="B107" s="19" t="s">
-        <v>357</v>
-      </c>
-      <c r="C107" s="19" t="s">
-        <v>546</v>
       </c>
       <c r="D107" s="21"/>
       <c r="E107" s="21"/>
@@ -16982,10 +17030,10 @@
         <v>171</v>
       </c>
       <c r="D108" s="24" t="s">
+        <v>856</v>
+      </c>
+      <c r="E108" s="24" t="s">
         <v>857</v>
-      </c>
-      <c r="E108" s="24" t="s">
-        <v>858</v>
       </c>
       <c r="F108" s="20">
         <v>46142</v>
@@ -17062,58 +17110,106 @@
         <v>1973</v>
       </c>
     </row>
-    <row r="109" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="19" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B109" s="19" t="s">
         <v>42</v>
       </c>
       <c r="C109" s="19" t="s">
-        <v>551</v>
-      </c>
-      <c r="D109" s="21"/>
-      <c r="E109" s="21"/>
-      <c r="F109" s="20"/>
+        <v>550</v>
+      </c>
+      <c r="D109" s="24">
+        <v>-3.6776800000000001</v>
+      </c>
+      <c r="E109" s="33">
+        <v>-38.859572</v>
+      </c>
+      <c r="F109" s="20">
+        <v>46177</v>
+      </c>
       <c r="G109" s="20">
         <f t="shared" si="5"/>
+        <v>46179</v>
+      </c>
+      <c r="H109" s="12">
+        <v>692</v>
+      </c>
+      <c r="I109" s="12">
+        <v>2664</v>
+      </c>
+      <c r="J109" s="12">
+        <v>67</v>
+      </c>
+      <c r="K109" s="12">
+        <v>485</v>
+      </c>
+      <c r="L109" s="12">
+        <v>197</v>
+      </c>
+      <c r="M109" s="12">
+        <v>38</v>
+      </c>
+      <c r="N109" s="12">
+        <v>200</v>
+      </c>
+      <c r="O109" s="12">
+        <v>83</v>
+      </c>
+      <c r="P109" s="12">
+        <v>17</v>
+      </c>
+      <c r="Q109" s="12">
+        <v>139</v>
+      </c>
+      <c r="R109" s="12">
+        <v>87</v>
+      </c>
+      <c r="S109" s="12">
+        <v>9</v>
+      </c>
+      <c r="T109" s="12">
+        <v>38</v>
+      </c>
+      <c r="U109" s="12">
+        <v>7</v>
+      </c>
+      <c r="V109" s="12">
+        <v>1</v>
+      </c>
+      <c r="W109" s="12">
+        <v>29</v>
+      </c>
+      <c r="X109" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y109" s="12">
         <v>2</v>
       </c>
-      <c r="H109" s="12"/>
-      <c r="I109" s="12"/>
-      <c r="J109" s="12"/>
-      <c r="K109" s="12"/>
-      <c r="L109" s="12"/>
-      <c r="M109" s="12"/>
-      <c r="N109" s="12"/>
-      <c r="O109" s="12"/>
-      <c r="P109" s="12"/>
-      <c r="Q109" s="12"/>
-      <c r="R109" s="12"/>
-      <c r="S109" s="12"/>
-      <c r="T109" s="12"/>
-      <c r="U109" s="12"/>
-      <c r="V109" s="12"/>
-      <c r="W109" s="12"/>
-      <c r="X109" s="12"/>
-      <c r="Y109" s="12"/>
-      <c r="Z109" s="12"/>
-      <c r="AA109" s="12"/>
-      <c r="AB109" s="12"/>
+      <c r="Z109" s="12">
+        <v>51</v>
+      </c>
+      <c r="AA109" s="12">
+        <v>42</v>
+      </c>
+      <c r="AB109" s="12">
+        <v>44</v>
+      </c>
       <c r="AC109" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4892</v>
       </c>
     </row>
     <row r="110" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="19" t="s">
+        <v>553</v>
+      </c>
+      <c r="B110" s="19" t="s">
         <v>554</v>
       </c>
-      <c r="B110" s="19" t="s">
+      <c r="C110" s="19" t="s">
         <v>555</v>
-      </c>
-      <c r="C110" s="19" t="s">
-        <v>556</v>
       </c>
       <c r="D110" s="21">
         <v>-3.6978119999999999</v>
@@ -17198,13 +17294,13 @@
     </row>
     <row r="111" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="19" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B111" s="19" t="s">
         <v>208</v>
       </c>
       <c r="C111" s="19" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D111" s="21">
         <v>-5.2113269999999998</v>
@@ -17289,13 +17385,13 @@
     </row>
     <row r="112" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="19" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B112" s="19" t="s">
         <v>208</v>
       </c>
       <c r="C112" s="19" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D112" s="21">
         <v>-4.3822749999999999</v>
@@ -17380,13 +17476,13 @@
     </row>
     <row r="113" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="19" t="s">
+        <v>569</v>
+      </c>
+      <c r="B113" s="19" t="s">
         <v>570</v>
       </c>
-      <c r="B113" s="19" t="s">
+      <c r="C113" s="19" t="s">
         <v>571</v>
-      </c>
-      <c r="C113" s="19" t="s">
-        <v>572</v>
       </c>
       <c r="D113" s="21"/>
       <c r="E113" s="21"/>
@@ -17423,13 +17519,13 @@
     </row>
     <row r="114" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="19" t="s">
+        <v>575</v>
+      </c>
+      <c r="B114" s="19" t="s">
+        <v>486</v>
+      </c>
+      <c r="C114" s="19" t="s">
         <v>576</v>
-      </c>
-      <c r="B114" s="19" t="s">
-        <v>487</v>
-      </c>
-      <c r="C114" s="19" t="s">
-        <v>577</v>
       </c>
       <c r="D114" s="24">
         <v>-5.2495240000000001</v>
@@ -17514,13 +17610,13 @@
     </row>
     <row r="115" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="19" t="s">
+        <v>580</v>
+      </c>
+      <c r="B115" s="19" t="s">
         <v>581</v>
       </c>
-      <c r="B115" s="19" t="s">
+      <c r="C115" s="19" t="s">
         <v>582</v>
-      </c>
-      <c r="C115" s="19" t="s">
-        <v>583</v>
       </c>
       <c r="D115" s="21"/>
       <c r="E115" s="21"/>
@@ -17557,13 +17653,13 @@
     </row>
     <row r="116" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="19" t="s">
+        <v>586</v>
+      </c>
+      <c r="B116" s="19" t="s">
         <v>587</v>
       </c>
-      <c r="B116" s="19" t="s">
+      <c r="C116" s="19" t="s">
         <v>588</v>
-      </c>
-      <c r="C116" s="19" t="s">
-        <v>589</v>
       </c>
       <c r="D116" s="21"/>
       <c r="E116" s="21"/>
@@ -17598,15 +17694,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="19" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B117" s="19" t="s">
         <v>142</v>
       </c>
       <c r="C117" s="19" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D117" s="21">
         <v>-4.5799000000000003</v>
@@ -17690,13 +17786,13 @@
     </row>
     <row r="118" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="19" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B118" s="19" t="s">
         <v>104</v>
       </c>
       <c r="C118" s="19" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D118" s="21"/>
       <c r="E118" s="21"/>
@@ -19618,10 +19714,10 @@
         <v>247</v>
       </c>
       <c r="D147" s="24" t="s">
+        <v>864</v>
+      </c>
+      <c r="E147" s="24" t="s">
         <v>865</v>
-      </c>
-      <c r="E147" s="24" t="s">
-        <v>866</v>
       </c>
       <c r="F147" s="20">
         <v>46153</v>
@@ -19827,58 +19923,106 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="19" t="s">
         <v>298</v>
       </c>
       <c r="B151" s="19" t="s">
-        <v>42</v>
+        <v>403</v>
       </c>
       <c r="C151" s="19" t="s">
-        <v>299</v>
-      </c>
-      <c r="D151" s="21"/>
-      <c r="E151" s="21"/>
-      <c r="F151" s="20"/>
+        <v>881</v>
+      </c>
+      <c r="D151" s="24">
+        <v>-3.6712609999999999</v>
+      </c>
+      <c r="E151" s="24">
+        <v>-38.815711</v>
+      </c>
+      <c r="F151" s="20">
+        <v>46177</v>
+      </c>
       <c r="G151" s="20">
         <f t="shared" si="6"/>
+        <v>46179</v>
+      </c>
+      <c r="H151" s="12">
+        <v>241</v>
+      </c>
+      <c r="I151" s="12">
+        <v>2236</v>
+      </c>
+      <c r="J151" s="12">
+        <v>180</v>
+      </c>
+      <c r="K151" s="12">
+        <v>408</v>
+      </c>
+      <c r="L151" s="12">
+        <v>195</v>
+      </c>
+      <c r="M151" s="12">
+        <v>38</v>
+      </c>
+      <c r="N151" s="12">
+        <v>40</v>
+      </c>
+      <c r="O151" s="12">
+        <v>19</v>
+      </c>
+      <c r="P151" s="12">
+        <v>3</v>
+      </c>
+      <c r="Q151" s="12">
+        <v>13</v>
+      </c>
+      <c r="R151" s="12">
+        <v>16</v>
+      </c>
+      <c r="S151" s="12">
+        <v>15</v>
+      </c>
+      <c r="T151" s="12">
+        <v>102</v>
+      </c>
+      <c r="U151" s="12">
+        <v>1</v>
+      </c>
+      <c r="V151" s="12">
         <v>2</v>
       </c>
-      <c r="H151" s="12"/>
-      <c r="I151" s="12"/>
-      <c r="J151" s="12"/>
-      <c r="K151" s="12"/>
-      <c r="L151" s="12"/>
-      <c r="M151" s="12"/>
-      <c r="N151" s="12"/>
-      <c r="O151" s="12"/>
-      <c r="P151" s="12"/>
-      <c r="Q151" s="12"/>
-      <c r="R151" s="12"/>
-      <c r="S151" s="12"/>
-      <c r="T151" s="12"/>
-      <c r="U151" s="12"/>
-      <c r="V151" s="12"/>
-      <c r="W151" s="12"/>
-      <c r="X151" s="12"/>
-      <c r="Y151" s="12"/>
-      <c r="Z151" s="12"/>
-      <c r="AA151" s="12"/>
-      <c r="AB151" s="12"/>
+      <c r="W151" s="12">
+        <v>2</v>
+      </c>
+      <c r="X151" s="12">
+        <v>1</v>
+      </c>
+      <c r="Y151" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z151" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA151" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB151" s="12">
+        <v>1</v>
+      </c>
       <c r="AC151" s="13">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3514</v>
       </c>
     </row>
     <row r="152" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="B152" s="19" t="s">
         <v>302</v>
       </c>
-      <c r="B152" s="19" t="s">
+      <c r="C152" s="19" t="s">
         <v>303</v>
-      </c>
-      <c r="C152" s="19" t="s">
-        <v>304</v>
       </c>
       <c r="D152" s="21">
         <v>-4.5677839999999996</v>
@@ -19963,13 +20107,13 @@
     </row>
     <row r="153" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="19" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B153" s="19" t="s">
         <v>136</v>
       </c>
       <c r="C153" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D153" s="21"/>
       <c r="E153" s="21"/>
@@ -20026,11 +20170,9 @@
   <autoFilter ref="A4:AC153" xr:uid="{1D18A476-0271-4A84-BE9E-901865A86FD3}">
     <filterColumn colId="0">
       <filters>
-        <filter val="P 106"/>
-        <filter val="P 12"/>
-        <filter val="P 181"/>
-        <filter val="P 198"/>
-        <filter val="P 55"/>
+        <filter val="N 01"/>
+        <filter val="P 185"/>
+        <filter val="P 67"/>
       </filters>
     </filterColumn>
     <filterColumn colId="5" showButton="0"/>

--- a/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
+++ b/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\5- MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39CFD38C-5068-436E-A17C-ED316E88C009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FF0789F-101E-44BD-BE90-9A70628676D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
   </bookViews>
   <sheets>
     <sheet name="LISTA DE PONTOS" sheetId="1" r:id="rId1"/>
@@ -2884,6 +2884,9 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2903,9 +2906,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4455,7 +4455,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>34</v>
       </c>
@@ -4463,10 +4463,10 @@
         <v>35</v>
       </c>
       <c r="C6" s="5">
-        <v>-4.1070659999999997</v>
+        <v>-4.1047820000000002</v>
       </c>
       <c r="D6" s="5">
-        <v>-38.787050000000001</v>
+        <v>-38.789633000000002</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>36</v>
@@ -4490,7 +4490,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>40</v>
       </c>
@@ -4498,10 +4498,10 @@
         <v>41</v>
       </c>
       <c r="C7" s="5">
-        <v>-4.0963000000000003</v>
-      </c>
-      <c r="D7" s="5">
-        <v>-38.778933000000002</v>
+        <v>-4.0690010000000001</v>
+      </c>
+      <c r="D7" s="25">
+        <v>-38.810313000000001</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>42</v>
@@ -4630,7 +4630,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>62</v>
       </c>
@@ -4638,10 +4638,10 @@
         <v>63</v>
       </c>
       <c r="C11" s="5">
-        <v>-4.1120830000000002</v>
+        <v>-4.1096320000000004</v>
       </c>
       <c r="D11" s="5">
-        <v>-38.749133</v>
+        <v>-38.748489999999997</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>64</v>
@@ -5050,7 +5050,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>255</v>
       </c>
@@ -5058,10 +5058,10 @@
         <v>256</v>
       </c>
       <c r="C23" s="5">
-        <v>-4.1670020000000001</v>
+        <v>-4.1661080000000004</v>
       </c>
       <c r="D23" s="5">
-        <v>-38.694997000000001</v>
+        <v>-38.694837999999997</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>42</v>
@@ -5365,7 +5365,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>286</v>
       </c>
@@ -5373,10 +5373,10 @@
         <v>287</v>
       </c>
       <c r="C32" s="5">
-        <v>-3.9746800000000002</v>
+        <v>-3.9712390000000002</v>
       </c>
       <c r="D32" s="5">
-        <v>-38.710697000000003</v>
+        <v>-38.722090999999999</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>288</v>
@@ -5435,7 +5435,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>297</v>
       </c>
@@ -7605,7 +7605,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>548</v>
       </c>
@@ -8795,7 +8795,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>692</v>
       </c>
@@ -9534,9 +9534,11 @@
   <autoFilter ref="A1:K150" xr:uid="{4DA12617-6B17-4A0E-9E79-EBA6E19B3138}">
     <filterColumn colId="1">
       <filters>
-        <filter val="N 01"/>
-        <filter val="P 185"/>
-        <filter val="P 67"/>
+        <filter val="E 09"/>
+        <filter val="E 10"/>
+        <filter val="E 11"/>
+        <filter val="E 175"/>
+        <filter val="E 45"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -9571,97 +9573,97 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="30" t="s">
+      <c r="C1" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="32" t="s">
         <v>799</v>
       </c>
-      <c r="E1" s="31"/>
-      <c r="F1" s="32" t="s">
+      <c r="E1" s="32"/>
+      <c r="F1" s="33" t="s">
         <v>800</v>
       </c>
-      <c r="G1" s="32"/>
-      <c r="H1" s="28" t="s">
+      <c r="G1" s="33"/>
+      <c r="H1" s="29" t="s">
         <v>801</v>
       </c>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="28"/>
-      <c r="R1" s="28"/>
-      <c r="S1" s="28"/>
-      <c r="T1" s="28"/>
-      <c r="U1" s="28"/>
-      <c r="V1" s="28"/>
-      <c r="W1" s="28"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="28"/>
-      <c r="Z1" s="28"/>
-      <c r="AA1" s="28"/>
-      <c r="AB1" s="28"/>
-      <c r="AC1" s="26" t="s">
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="29"/>
+      <c r="N1" s="29"/>
+      <c r="O1" s="29"/>
+      <c r="P1" s="29"/>
+      <c r="Q1" s="29"/>
+      <c r="R1" s="29"/>
+      <c r="S1" s="29"/>
+      <c r="T1" s="29"/>
+      <c r="U1" s="29"/>
+      <c r="V1" s="29"/>
+      <c r="W1" s="29"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="29"/>
+      <c r="Z1" s="29"/>
+      <c r="AA1" s="29"/>
+      <c r="AB1" s="29"/>
+      <c r="AC1" s="27" t="s">
         <v>802</v>
       </c>
     </row>
     <row r="2" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="29"/>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="27" t="s">
+      <c r="A2" s="30"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="28" t="s">
         <v>803</v>
       </c>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
       <c r="K2" s="9" t="s">
         <v>804</v>
       </c>
       <c r="L2" s="9" t="s">
         <v>804</v>
       </c>
-      <c r="M2" s="28" t="s">
+      <c r="M2" s="29" t="s">
         <v>805</v>
       </c>
-      <c r="N2" s="28"/>
-      <c r="O2" s="28"/>
-      <c r="P2" s="28"/>
-      <c r="Q2" s="28"/>
-      <c r="R2" s="28"/>
-      <c r="S2" s="28"/>
-      <c r="T2" s="28"/>
-      <c r="U2" s="28"/>
-      <c r="V2" s="28"/>
-      <c r="W2" s="28"/>
-      <c r="X2" s="28"/>
-      <c r="Y2" s="28"/>
-      <c r="Z2" s="28"/>
-      <c r="AA2" s="28"/>
-      <c r="AB2" s="28"/>
-      <c r="AC2" s="26"/>
+      <c r="N2" s="29"/>
+      <c r="O2" s="29"/>
+      <c r="P2" s="29"/>
+      <c r="Q2" s="29"/>
+      <c r="R2" s="29"/>
+      <c r="S2" s="29"/>
+      <c r="T2" s="29"/>
+      <c r="U2" s="29"/>
+      <c r="V2" s="29"/>
+      <c r="W2" s="29"/>
+      <c r="X2" s="29"/>
+      <c r="Y2" s="29"/>
+      <c r="Z2" s="29"/>
+      <c r="AA2" s="29"/>
+      <c r="AB2" s="29"/>
+      <c r="AC2" s="27"/>
     </row>
     <row r="3" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="29"/>
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
+      <c r="A3" s="30"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
       <c r="H3" s="8" t="s">
         <v>806</v>
       </c>
@@ -9725,20 +9727,20 @@
       <c r="AB3" s="7" t="s">
         <v>826</v>
       </c>
-      <c r="AC3" s="26"/>
+      <c r="AC3" s="27"/>
     </row>
     <row r="4" spans="1:29" ht="104.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="29"/>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
+      <c r="A4" s="30"/>
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
       <c r="D4" s="22" t="s">
         <v>2</v>
       </c>
       <c r="E4" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
       <c r="H4" s="10"/>
       <c r="I4" s="10"/>
       <c r="J4" s="10"/>
@@ -9760,7 +9762,7 @@
       <c r="Z4" s="11"/>
       <c r="AA4" s="11"/>
       <c r="AB4" s="11"/>
-      <c r="AC4" s="26"/>
+      <c r="AC4" s="27"/>
     </row>
     <row r="5" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="19" t="s">
@@ -17123,7 +17125,7 @@
       <c r="D109" s="24">
         <v>-3.6776800000000001</v>
       </c>
-      <c r="E109" s="33">
+      <c r="E109" s="26">
         <v>-38.859572</v>
       </c>
       <c r="F109" s="20">

--- a/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
+++ b/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\5- MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FF0789F-101E-44BD-BE90-9A70628676D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{840D09CA-49FE-4AEE-8962-D302B30FD3EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1873" uniqueCount="882">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1873" uniqueCount="883">
   <si>
     <t>WKT</t>
   </si>
@@ -2690,6 +2690,9 @@
   </si>
   <si>
     <t>348ECE0170S0</t>
+  </si>
+  <si>
+    <t>EM ANDAMENTO</t>
   </si>
 </sst>
 </file>
@@ -4484,7 +4487,7 @@
         <v>16</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>17</v>
+        <v>882</v>
       </c>
       <c r="K6" s="6" t="s">
         <v>18</v>
@@ -4519,7 +4522,7 @@
         <v>16</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>17</v>
+        <v>882</v>
       </c>
       <c r="K7" s="6" t="s">
         <v>18</v>
@@ -4659,7 +4662,7 @@
         <v>16</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>17</v>
+        <v>882</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>18</v>
@@ -5079,7 +5082,7 @@
         <v>16</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>17</v>
+        <v>882</v>
       </c>
       <c r="K23" s="6" t="s">
         <v>18</v>
@@ -5373,10 +5376,10 @@
         <v>287</v>
       </c>
       <c r="C32" s="5">
-        <v>-3.9712390000000002</v>
+        <v>-3.9746090000000001</v>
       </c>
       <c r="D32" s="5">
-        <v>-38.722090999999999</v>
+        <v>-38.710085999999997</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>288</v>
@@ -5394,7 +5397,7 @@
         <v>16</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>17</v>
+        <v>882</v>
       </c>
       <c r="K32" s="6" t="s">
         <v>18</v>
@@ -12088,7 +12091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="19" t="s">
         <v>693</v>
       </c>
@@ -17112,7 +17115,7 @@
         <v>1973</v>
       </c>
     </row>
-    <row r="109" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="19" t="s">
         <v>549</v>
       </c>
@@ -18193,7 +18196,7 @@
         <v>4915</v>
       </c>
     </row>
-    <row r="123" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="19" t="s">
         <v>35</v>
       </c>
@@ -18236,7 +18239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="19" t="s">
         <v>41</v>
       </c>
@@ -18279,7 +18282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="19" t="s">
         <v>63</v>
       </c>
@@ -18949,7 +18952,7 @@
         <v>1724</v>
       </c>
     </row>
-    <row r="135" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="19" t="s">
         <v>287</v>
       </c>
@@ -19839,7 +19842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="19" t="s">
         <v>256</v>
       </c>
@@ -19925,7 +19928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="19" t="s">
         <v>298</v>
       </c>
@@ -20172,9 +20175,11 @@
   <autoFilter ref="A4:AC153" xr:uid="{1D18A476-0271-4A84-BE9E-901865A86FD3}">
     <filterColumn colId="0">
       <filters>
-        <filter val="N 01"/>
-        <filter val="P 185"/>
-        <filter val="P 67"/>
+        <filter val="E 09"/>
+        <filter val="E 10"/>
+        <filter val="E 11"/>
+        <filter val="E 175"/>
+        <filter val="E 45"/>
       </filters>
     </filterColumn>
     <filterColumn colId="5" showButton="0"/>

--- a/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
+++ b/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\5- MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{840D09CA-49FE-4AEE-8962-D302B30FD3EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1005143F-6B34-41E6-B272-FD102D42A633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
   </bookViews>
   <sheets>
     <sheet name="LISTA DE PONTOS" sheetId="1" r:id="rId1"/>
@@ -4458,7 +4458,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>34</v>
       </c>
@@ -4487,13 +4487,13 @@
         <v>16</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>882</v>
+        <v>798</v>
       </c>
       <c r="K6" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>40</v>
       </c>
@@ -4522,13 +4522,13 @@
         <v>16</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>882</v>
+        <v>798</v>
       </c>
       <c r="K7" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>46</v>
       </c>
@@ -4563,7 +4563,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>52</v>
       </c>
@@ -4633,7 +4633,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>62</v>
       </c>
@@ -4662,13 +4662,13 @@
         <v>16</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>882</v>
+        <v>798</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>68</v>
       </c>
@@ -4773,7 +4773,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>212</v>
       </c>
@@ -4843,7 +4843,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>222</v>
       </c>
@@ -4913,7 +4913,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>233</v>
       </c>
@@ -4948,7 +4948,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>239</v>
       </c>
@@ -5018,7 +5018,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>250</v>
       </c>
@@ -5053,7 +5053,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>255</v>
       </c>
@@ -5082,13 +5082,13 @@
         <v>16</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>882</v>
+        <v>798</v>
       </c>
       <c r="K23" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>260</v>
       </c>
@@ -5123,7 +5123,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>264</v>
       </c>
@@ -5158,7 +5158,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>270</v>
       </c>
@@ -5368,7 +5368,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>286</v>
       </c>
@@ -5397,13 +5397,13 @@
         <v>16</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>882</v>
+        <v>798</v>
       </c>
       <c r="K32" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>291</v>
       </c>
@@ -5432,7 +5432,7 @@
         <v>16</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>17</v>
+        <v>882</v>
       </c>
       <c r="K33" s="6" t="s">
         <v>18</v>
@@ -5508,7 +5508,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>307</v>
       </c>
@@ -5543,7 +5543,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>95</v>
       </c>
@@ -5578,7 +5578,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>102</v>
       </c>
@@ -5648,7 +5648,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>113</v>
       </c>
@@ -5683,7 +5683,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>119</v>
       </c>
@@ -5718,7 +5718,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>124</v>
       </c>
@@ -5788,7 +5788,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>317</v>
       </c>
@@ -5823,7 +5823,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>322</v>
       </c>
@@ -6173,7 +6173,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>365</v>
       </c>
@@ -6243,7 +6243,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>371</v>
       </c>
@@ -6278,7 +6278,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>373</v>
       </c>
@@ -6313,7 +6313,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>146</v>
       </c>
@@ -6348,7 +6348,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>379</v>
       </c>
@@ -6383,7 +6383,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>384</v>
       </c>
@@ -6418,7 +6418,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="62" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>390</v>
       </c>
@@ -6453,7 +6453,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="63" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>396</v>
       </c>
@@ -6488,7 +6488,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="64" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>401</v>
       </c>
@@ -6523,7 +6523,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="65" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>407</v>
       </c>
@@ -6628,7 +6628,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>424</v>
       </c>
@@ -6768,7 +6768,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="72" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>444</v>
       </c>
@@ -6803,7 +6803,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="73" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>449</v>
       </c>
@@ -6832,7 +6832,7 @@
         <v>101</v>
       </c>
       <c r="J73" s="6" t="s">
-        <v>17</v>
+        <v>882</v>
       </c>
       <c r="K73" s="6" t="s">
         <v>18</v>
@@ -6873,7 +6873,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="75" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>459</v>
       </c>
@@ -6943,7 +6943,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>468</v>
       </c>
@@ -6972,7 +6972,7 @@
         <v>101</v>
       </c>
       <c r="J77" s="6" t="s">
-        <v>17</v>
+        <v>882</v>
       </c>
       <c r="K77" s="6" t="s">
         <v>18</v>
@@ -7293,7 +7293,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>509</v>
       </c>
@@ -7328,7 +7328,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="88" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>514</v>
       </c>
@@ -7363,7 +7363,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="89" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>520</v>
       </c>
@@ -7538,7 +7538,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="94" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>543</v>
       </c>
@@ -7748,7 +7748,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="100" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>568</v>
       </c>
@@ -7818,7 +7818,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="102" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>579</v>
       </c>
@@ -7853,7 +7853,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="103" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>585</v>
       </c>
@@ -7923,7 +7923,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="105" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>595</v>
       </c>
@@ -7958,7 +7958,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="106" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>172</v>
       </c>
@@ -8028,7 +8028,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="108" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>184</v>
       </c>
@@ -8057,7 +8057,7 @@
         <v>151</v>
       </c>
       <c r="J108" s="6" t="s">
-        <v>17</v>
+        <v>882</v>
       </c>
       <c r="K108" s="6" t="s">
         <v>18</v>
@@ -8168,7 +8168,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="112" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>606</v>
       </c>
@@ -8273,7 +8273,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="115" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>622</v>
       </c>
@@ -8343,7 +8343,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="117" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>633</v>
       </c>
@@ -8372,7 +8372,7 @@
         <v>101</v>
       </c>
       <c r="J117" s="6" t="s">
-        <v>17</v>
+        <v>882</v>
       </c>
       <c r="K117" s="6" t="s">
         <v>18</v>
@@ -8483,7 +8483,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="121" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>648</v>
       </c>
@@ -8553,7 +8553,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="123" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>657</v>
       </c>
@@ -8658,7 +8658,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="126" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>671</v>
       </c>
@@ -8728,7 +8728,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="128" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>681</v>
       </c>
@@ -8763,7 +8763,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="129" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>687</v>
       </c>
@@ -8833,7 +8833,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="131" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>698</v>
       </c>
@@ -8868,7 +8868,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="132" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>702</v>
       </c>
@@ -8938,7 +8938,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="134" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>713</v>
       </c>
@@ -8973,7 +8973,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="135" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>718</v>
       </c>
@@ -9043,7 +9043,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="137" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>727</v>
       </c>
@@ -9253,7 +9253,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="143" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>756</v>
       </c>
@@ -9288,7 +9288,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="144" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>760</v>
       </c>
@@ -9393,7 +9393,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="147" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>775</v>
       </c>
@@ -9535,13 +9535,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:K150" xr:uid="{4DA12617-6B17-4A0E-9E79-EBA6E19B3138}">
-    <filterColumn colId="1">
+    <filterColumn colId="9">
       <filters>
-        <filter val="E 09"/>
-        <filter val="E 10"/>
-        <filter val="E 11"/>
-        <filter val="E 175"/>
-        <filter val="E 45"/>
+        <filter val="NÃO"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -9549,7 +9545,7 @@
     <sortCondition ref="B1:B150"/>
   </sortState>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="63" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="49" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -18206,37 +18202,85 @@
       <c r="C123" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="D123" s="21"/>
-      <c r="E123" s="21"/>
-      <c r="F123" s="20"/>
+      <c r="D123" s="24">
+        <v>-4.1047820000000002</v>
+      </c>
+      <c r="E123" s="24">
+        <v>-38.789633000000002</v>
+      </c>
+      <c r="F123" s="20">
+        <v>46183</v>
+      </c>
       <c r="G123" s="20">
         <f t="shared" si="5"/>
-        <v>2</v>
-      </c>
-      <c r="H123" s="12"/>
-      <c r="I123" s="12"/>
-      <c r="J123" s="12"/>
-      <c r="K123" s="12"/>
-      <c r="L123" s="12"/>
-      <c r="M123" s="12"/>
-      <c r="N123" s="12"/>
-      <c r="O123" s="12"/>
-      <c r="P123" s="12"/>
-      <c r="Q123" s="12"/>
-      <c r="R123" s="12"/>
-      <c r="S123" s="12"/>
-      <c r="T123" s="12"/>
-      <c r="U123" s="12"/>
-      <c r="V123" s="12"/>
-      <c r="W123" s="12"/>
-      <c r="X123" s="12"/>
-      <c r="Y123" s="12"/>
-      <c r="Z123" s="12"/>
-      <c r="AA123" s="12"/>
-      <c r="AB123" s="12"/>
+        <v>46185</v>
+      </c>
+      <c r="H123" s="12">
+        <v>447</v>
+      </c>
+      <c r="I123" s="12">
+        <v>621</v>
+      </c>
+      <c r="J123" s="12">
+        <v>27</v>
+      </c>
+      <c r="K123" s="12">
+        <v>145</v>
+      </c>
+      <c r="L123" s="12">
+        <v>17</v>
+      </c>
+      <c r="M123" s="12">
+        <v>1</v>
+      </c>
+      <c r="N123" s="12">
+        <v>0</v>
+      </c>
+      <c r="O123" s="12">
+        <v>0</v>
+      </c>
+      <c r="P123" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q123" s="12">
+        <v>1</v>
+      </c>
+      <c r="R123" s="12">
+        <v>0</v>
+      </c>
+      <c r="S123" s="12">
+        <v>0</v>
+      </c>
+      <c r="T123" s="12">
+        <v>7</v>
+      </c>
+      <c r="U123" s="12">
+        <v>0</v>
+      </c>
+      <c r="V123" s="12">
+        <v>0</v>
+      </c>
+      <c r="W123" s="12">
+        <v>0</v>
+      </c>
+      <c r="X123" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y123" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z123" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA123" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB123" s="12">
+        <v>0</v>
+      </c>
       <c r="AC123" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="124" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -18249,37 +18293,85 @@
       <c r="C124" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="D124" s="21"/>
-      <c r="E124" s="21"/>
-      <c r="F124" s="20"/>
+      <c r="D124" s="24">
+        <v>-4.0690010000000001</v>
+      </c>
+      <c r="E124" s="24">
+        <v>-38.810313000000001</v>
+      </c>
+      <c r="F124" s="20">
+        <v>46183</v>
+      </c>
       <c r="G124" s="20">
         <f t="shared" si="5"/>
+        <v>46185</v>
+      </c>
+      <c r="H124" s="12">
+        <v>65</v>
+      </c>
+      <c r="I124" s="12">
+        <v>182</v>
+      </c>
+      <c r="J124" s="12">
+        <v>26</v>
+      </c>
+      <c r="K124" s="12">
+        <v>82</v>
+      </c>
+      <c r="L124" s="12">
+        <v>13</v>
+      </c>
+      <c r="M124" s="12">
         <v>2</v>
       </c>
-      <c r="H124" s="12"/>
-      <c r="I124" s="12"/>
-      <c r="J124" s="12"/>
-      <c r="K124" s="12"/>
-      <c r="L124" s="12"/>
-      <c r="M124" s="12"/>
-      <c r="N124" s="12"/>
-      <c r="O124" s="12"/>
-      <c r="P124" s="12"/>
-      <c r="Q124" s="12"/>
-      <c r="R124" s="12"/>
-      <c r="S124" s="12"/>
-      <c r="T124" s="12"/>
-      <c r="U124" s="12"/>
-      <c r="V124" s="12"/>
-      <c r="W124" s="12"/>
-      <c r="X124" s="12"/>
-      <c r="Y124" s="12"/>
-      <c r="Z124" s="12"/>
-      <c r="AA124" s="12"/>
-      <c r="AB124" s="12"/>
+      <c r="N124" s="12">
+        <v>1</v>
+      </c>
+      <c r="O124" s="12">
+        <v>0</v>
+      </c>
+      <c r="P124" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q124" s="12">
+        <v>0</v>
+      </c>
+      <c r="R124" s="12">
+        <v>0</v>
+      </c>
+      <c r="S124" s="12">
+        <v>0</v>
+      </c>
+      <c r="T124" s="12">
+        <v>0</v>
+      </c>
+      <c r="U124" s="12">
+        <v>0</v>
+      </c>
+      <c r="V124" s="12">
+        <v>0</v>
+      </c>
+      <c r="W124" s="12">
+        <v>0</v>
+      </c>
+      <c r="X124" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y124" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z124" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA124" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB124" s="12">
+        <v>0</v>
+      </c>
       <c r="AC124" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>371</v>
       </c>
     </row>
     <row r="125" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -18292,37 +18384,85 @@
       <c r="C125" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="D125" s="21"/>
-      <c r="E125" s="21"/>
-      <c r="F125" s="20"/>
+      <c r="D125" s="24">
+        <v>-4.1096320000000004</v>
+      </c>
+      <c r="E125" s="24">
+        <v>-38.748489999999997</v>
+      </c>
+      <c r="F125" s="20">
+        <v>46183</v>
+      </c>
       <c r="G125" s="20">
         <f t="shared" si="5"/>
+        <v>46185</v>
+      </c>
+      <c r="H125" s="12">
+        <v>804</v>
+      </c>
+      <c r="I125" s="12">
+        <v>1036</v>
+      </c>
+      <c r="J125" s="12">
+        <v>0</v>
+      </c>
+      <c r="K125" s="12">
+        <v>10</v>
+      </c>
+      <c r="L125" s="12">
+        <v>4</v>
+      </c>
+      <c r="M125" s="12">
+        <v>0</v>
+      </c>
+      <c r="N125" s="12">
+        <v>1</v>
+      </c>
+      <c r="O125" s="12">
+        <v>0</v>
+      </c>
+      <c r="P125" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q125" s="12">
+        <v>0</v>
+      </c>
+      <c r="R125" s="12">
+        <v>0</v>
+      </c>
+      <c r="S125" s="12">
+        <v>0</v>
+      </c>
+      <c r="T125" s="12">
         <v>2</v>
       </c>
-      <c r="H125" s="12"/>
-      <c r="I125" s="12"/>
-      <c r="J125" s="12"/>
-      <c r="K125" s="12"/>
-      <c r="L125" s="12"/>
-      <c r="M125" s="12"/>
-      <c r="N125" s="12"/>
-      <c r="O125" s="12"/>
-      <c r="P125" s="12"/>
-      <c r="Q125" s="12"/>
-      <c r="R125" s="12"/>
-      <c r="S125" s="12"/>
-      <c r="T125" s="12"/>
-      <c r="U125" s="12"/>
-      <c r="V125" s="12"/>
-      <c r="W125" s="12"/>
-      <c r="X125" s="12"/>
-      <c r="Y125" s="12"/>
-      <c r="Z125" s="12"/>
-      <c r="AA125" s="12"/>
-      <c r="AB125" s="12"/>
+      <c r="U125" s="12">
+        <v>0</v>
+      </c>
+      <c r="V125" s="12">
+        <v>0</v>
+      </c>
+      <c r="W125" s="12">
+        <v>0</v>
+      </c>
+      <c r="X125" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y125" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z125" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA125" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB125" s="12">
+        <v>0</v>
+      </c>
       <c r="AC125" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="126" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -18962,37 +19102,85 @@
       <c r="C135" s="19" t="s">
         <v>289</v>
       </c>
-      <c r="D135" s="21"/>
-      <c r="E135" s="21"/>
-      <c r="F135" s="20"/>
+      <c r="D135" s="24">
+        <v>-3.9746090000000001</v>
+      </c>
+      <c r="E135" s="24">
+        <v>-38.710085999999997</v>
+      </c>
+      <c r="F135" s="20">
+        <v>46183</v>
+      </c>
       <c r="G135" s="20">
         <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="H135" s="12"/>
-      <c r="I135" s="12"/>
-      <c r="J135" s="12"/>
-      <c r="K135" s="12"/>
-      <c r="L135" s="12"/>
-      <c r="M135" s="12"/>
-      <c r="N135" s="12"/>
-      <c r="O135" s="12"/>
-      <c r="P135" s="12"/>
-      <c r="Q135" s="12"/>
-      <c r="R135" s="12"/>
-      <c r="S135" s="12"/>
-      <c r="T135" s="12"/>
-      <c r="U135" s="12"/>
-      <c r="V135" s="12"/>
-      <c r="W135" s="12"/>
-      <c r="X135" s="12"/>
-      <c r="Y135" s="12"/>
-      <c r="Z135" s="12"/>
-      <c r="AA135" s="12"/>
-      <c r="AB135" s="12"/>
+        <v>46185</v>
+      </c>
+      <c r="H135" s="12">
+        <v>1793</v>
+      </c>
+      <c r="I135" s="12">
+        <v>2962</v>
+      </c>
+      <c r="J135" s="12">
+        <v>78</v>
+      </c>
+      <c r="K135" s="12">
+        <v>372</v>
+      </c>
+      <c r="L135" s="12">
+        <v>65</v>
+      </c>
+      <c r="M135" s="12">
+        <v>12</v>
+      </c>
+      <c r="N135" s="12">
+        <v>44</v>
+      </c>
+      <c r="O135" s="12">
+        <v>1</v>
+      </c>
+      <c r="P135" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q135" s="12">
+        <v>3</v>
+      </c>
+      <c r="R135" s="12">
+        <v>4</v>
+      </c>
+      <c r="S135" s="12">
+        <v>5</v>
+      </c>
+      <c r="T135" s="12">
+        <v>66</v>
+      </c>
+      <c r="U135" s="12">
+        <v>1</v>
+      </c>
+      <c r="V135" s="12">
+        <v>0</v>
+      </c>
+      <c r="W135" s="12">
+        <v>0</v>
+      </c>
+      <c r="X135" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y135" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z135" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA135" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB135" s="12">
+        <v>0</v>
+      </c>
       <c r="AC135" s="13">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>5408</v>
       </c>
     </row>
     <row r="136" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -19852,37 +20040,85 @@
       <c r="C149" s="19" t="s">
         <v>257</v>
       </c>
-      <c r="D149" s="21"/>
-      <c r="E149" s="21"/>
-      <c r="F149" s="20"/>
+      <c r="D149" s="24">
+        <v>-4.1661080000000004</v>
+      </c>
+      <c r="E149" s="24">
+        <v>-38.694837999999997</v>
+      </c>
+      <c r="F149" s="20">
+        <v>46183</v>
+      </c>
       <c r="G149" s="20">
         <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="H149" s="12"/>
-      <c r="I149" s="12"/>
-      <c r="J149" s="12"/>
-      <c r="K149" s="12"/>
-      <c r="L149" s="12"/>
-      <c r="M149" s="12"/>
-      <c r="N149" s="12"/>
-      <c r="O149" s="12"/>
-      <c r="P149" s="12"/>
-      <c r="Q149" s="12"/>
-      <c r="R149" s="12"/>
-      <c r="S149" s="12"/>
-      <c r="T149" s="12"/>
-      <c r="U149" s="12"/>
-      <c r="V149" s="12"/>
-      <c r="W149" s="12"/>
-      <c r="X149" s="12"/>
-      <c r="Y149" s="12"/>
-      <c r="Z149" s="12"/>
-      <c r="AA149" s="12"/>
-      <c r="AB149" s="12"/>
+        <v>46185</v>
+      </c>
+      <c r="H149" s="12">
+        <v>478</v>
+      </c>
+      <c r="I149" s="12">
+        <v>486</v>
+      </c>
+      <c r="J149" s="12">
+        <v>20</v>
+      </c>
+      <c r="K149" s="12">
+        <v>139</v>
+      </c>
+      <c r="L149" s="12">
+        <v>31</v>
+      </c>
+      <c r="M149" s="12">
+        <v>1</v>
+      </c>
+      <c r="N149" s="12">
+        <v>4</v>
+      </c>
+      <c r="O149" s="12">
+        <v>0</v>
+      </c>
+      <c r="P149" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q149" s="12">
+        <v>0</v>
+      </c>
+      <c r="R149" s="12">
+        <v>0</v>
+      </c>
+      <c r="S149" s="12">
+        <v>0</v>
+      </c>
+      <c r="T149" s="12">
+        <v>8</v>
+      </c>
+      <c r="U149" s="12">
+        <v>0</v>
+      </c>
+      <c r="V149" s="12">
+        <v>0</v>
+      </c>
+      <c r="W149" s="12">
+        <v>0</v>
+      </c>
+      <c r="X149" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y149" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z149" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA149" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB149" s="12">
+        <v>0</v>
+      </c>
       <c r="AC149" s="13">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="150" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">

--- a/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
+++ b/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\5- MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1005143F-6B34-41E6-B272-FD102D42A633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8432ECC5-9693-49AB-B131-AD48E80E8DAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
   </bookViews>
   <sheets>
     <sheet name="LISTA DE PONTOS" sheetId="1" r:id="rId1"/>
@@ -4528,7 +4528,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>46</v>
       </c>
@@ -4563,7 +4563,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>52</v>
       </c>
@@ -4668,7 +4668,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>68</v>
       </c>
@@ -4773,7 +4773,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>212</v>
       </c>
@@ -4843,7 +4843,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>222</v>
       </c>
@@ -4913,7 +4913,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>233</v>
       </c>
@@ -4948,7 +4948,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>239</v>
       </c>
@@ -5018,7 +5018,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>250</v>
       </c>
@@ -5088,7 +5088,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>260</v>
       </c>
@@ -5123,7 +5123,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>264</v>
       </c>
@@ -5158,7 +5158,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>270</v>
       </c>
@@ -5411,10 +5411,10 @@
         <v>292</v>
       </c>
       <c r="C33" s="5">
-        <v>-3.2165300000000001</v>
+        <v>-3.2161379999999999</v>
       </c>
       <c r="D33" s="5">
-        <v>-40.866968999999997</v>
+        <v>-40.866370000000003</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>293</v>
@@ -5508,7 +5508,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>307</v>
       </c>
@@ -5543,7 +5543,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>95</v>
       </c>
@@ -5578,7 +5578,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>102</v>
       </c>
@@ -5648,7 +5648,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>113</v>
       </c>
@@ -5683,7 +5683,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>119</v>
       </c>
@@ -5718,7 +5718,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>124</v>
       </c>
@@ -5788,7 +5788,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>317</v>
       </c>
@@ -5823,7 +5823,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>322</v>
       </c>
@@ -6173,7 +6173,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>365</v>
       </c>
@@ -6243,7 +6243,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>371</v>
       </c>
@@ -6278,7 +6278,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>373</v>
       </c>
@@ -6313,7 +6313,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>146</v>
       </c>
@@ -6348,7 +6348,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>379</v>
       </c>
@@ -6383,7 +6383,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>384</v>
       </c>
@@ -6418,7 +6418,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>390</v>
       </c>
@@ -6453,7 +6453,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>396</v>
       </c>
@@ -6488,7 +6488,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>401</v>
       </c>
@@ -6523,7 +6523,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>407</v>
       </c>
@@ -6628,7 +6628,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>424</v>
       </c>
@@ -6768,7 +6768,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>444</v>
       </c>
@@ -6811,10 +6811,10 @@
         <v>450</v>
       </c>
       <c r="C73" s="5">
-        <v>-3.1334659999999999</v>
+        <v>-3.133448</v>
       </c>
       <c r="D73" s="5">
-        <v>-40.815800000000003</v>
+        <v>-40.815766000000004</v>
       </c>
       <c r="E73" s="4" t="s">
         <v>235</v>
@@ -6873,7 +6873,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>459</v>
       </c>
@@ -6951,10 +6951,10 @@
         <v>469</v>
       </c>
       <c r="C77" s="5">
-        <v>-3.4014500000000001</v>
+        <v>-3.3702869999999998</v>
       </c>
       <c r="D77" s="5">
-        <v>-40.686549999999997</v>
+        <v>-40.723520000000001</v>
       </c>
       <c r="E77" s="4" t="s">
         <v>470</v>
@@ -7293,7 +7293,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>509</v>
       </c>
@@ -7328,7 +7328,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>514</v>
       </c>
@@ -7363,7 +7363,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>520</v>
       </c>
@@ -7538,7 +7538,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>543</v>
       </c>
@@ -7748,7 +7748,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>568</v>
       </c>
@@ -7818,7 +7818,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>579</v>
       </c>
@@ -7853,7 +7853,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>585</v>
       </c>
@@ -7923,7 +7923,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>595</v>
       </c>
@@ -7958,7 +7958,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>172</v>
       </c>
@@ -8036,10 +8036,10 @@
         <v>185</v>
       </c>
       <c r="C108" s="5">
-        <v>-3.0767500000000001</v>
+        <v>-3.0483189999999998</v>
       </c>
       <c r="D108" s="5">
-        <v>-41.252065999999999</v>
+        <v>-41.245891</v>
       </c>
       <c r="E108" s="4" t="s">
         <v>174</v>
@@ -8168,7 +8168,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>606</v>
       </c>
@@ -8273,7 +8273,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>622</v>
       </c>
@@ -8351,10 +8351,10 @@
         <v>634</v>
       </c>
       <c r="C117" s="5">
-        <v>-3.2141000000000002</v>
+        <v>-3.1338309999999998</v>
       </c>
       <c r="D117" s="5">
-        <v>-40.864533000000002</v>
+        <v>-40.838026999999997</v>
       </c>
       <c r="E117" s="4" t="s">
         <v>470</v>
@@ -8483,7 +8483,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>648</v>
       </c>
@@ -8553,7 +8553,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>657</v>
       </c>
@@ -8658,7 +8658,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>671</v>
       </c>
@@ -8728,7 +8728,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>681</v>
       </c>
@@ -8763,7 +8763,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>687</v>
       </c>
@@ -8833,7 +8833,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>698</v>
       </c>
@@ -8868,7 +8868,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>702</v>
       </c>
@@ -8938,7 +8938,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>713</v>
       </c>
@@ -8973,7 +8973,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>718</v>
       </c>
@@ -9043,7 +9043,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>727</v>
       </c>
@@ -9253,7 +9253,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>756</v>
       </c>
@@ -9288,7 +9288,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>760</v>
       </c>
@@ -9393,7 +9393,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>775</v>
       </c>
@@ -9537,7 +9537,7 @@
   <autoFilter ref="A1:K150" xr:uid="{4DA12617-6B17-4A0E-9E79-EBA6E19B3138}">
     <filterColumn colId="9">
       <filters>
-        <filter val="NÃO"/>
+        <filter val="EM ANDAMENTO"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -9545,7 +9545,7 @@
     <sortCondition ref="B1:B150"/>
   </sortState>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="49" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="63" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -10518,7 +10518,7 @@
         <v>5845</v>
       </c>
     </row>
-    <row r="17" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="19" t="s">
         <v>185</v>
       </c>
@@ -10528,12 +10528,18 @@
       <c r="C17" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="20"/>
+      <c r="D17" s="21">
+        <v>-3.0483189999999998</v>
+      </c>
+      <c r="E17" s="21">
+        <v>-41.245891</v>
+      </c>
+      <c r="F17" s="20">
+        <v>46188</v>
+      </c>
       <c r="G17" s="20">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>46190</v>
       </c>
       <c r="H17" s="12"/>
       <c r="I17" s="12"/>
@@ -11193,7 +11199,7 @@
         <v>4586</v>
       </c>
     </row>
-    <row r="26" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:29" s="14" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="19" t="s">
         <v>634</v>
       </c>
@@ -11203,12 +11209,18 @@
       <c r="C26" s="19" t="s">
         <v>635</v>
       </c>
-      <c r="D26" s="21"/>
-      <c r="E26" s="21"/>
-      <c r="F26" s="20"/>
+      <c r="D26" s="21">
+        <v>-3.1338309999999998</v>
+      </c>
+      <c r="E26" s="21">
+        <v>-40.838026999999997</v>
+      </c>
+      <c r="F26" s="20">
+        <v>46188</v>
+      </c>
       <c r="G26" s="20">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>46190</v>
       </c>
       <c r="H26" s="12"/>
       <c r="I26" s="12"/>
@@ -15446,7 +15458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="19" t="s">
         <v>450</v>
       </c>
@@ -15456,12 +15468,18 @@
       <c r="C87" s="19" t="s">
         <v>451</v>
       </c>
-      <c r="D87" s="21"/>
-      <c r="E87" s="21"/>
-      <c r="F87" s="20"/>
+      <c r="D87" s="21">
+        <v>-3.133448</v>
+      </c>
+      <c r="E87" s="21">
+        <v>-40.815766000000004</v>
+      </c>
+      <c r="F87" s="20">
+        <v>46188</v>
+      </c>
       <c r="G87" s="20">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>46190</v>
       </c>
       <c r="H87" s="12"/>
       <c r="I87" s="12"/>
@@ -15714,7 +15732,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="91" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="19" t="s">
         <v>469</v>
       </c>
@@ -15724,12 +15742,18 @@
       <c r="C91" s="19" t="s">
         <v>471</v>
       </c>
-      <c r="D91" s="21"/>
-      <c r="E91" s="21"/>
-      <c r="F91" s="20"/>
+      <c r="D91" s="21">
+        <v>-3.3702869999999998</v>
+      </c>
+      <c r="E91" s="21">
+        <v>-40.723520000000001</v>
+      </c>
+      <c r="F91" s="20">
+        <v>46188</v>
+      </c>
       <c r="G91" s="20">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>46190</v>
       </c>
       <c r="H91" s="12"/>
       <c r="I91" s="12"/>
@@ -18192,7 +18216,7 @@
         <v>4915</v>
       </c>
     </row>
-    <row r="123" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="19" t="s">
         <v>35</v>
       </c>
@@ -18283,7 +18307,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="124" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="19" t="s">
         <v>41</v>
       </c>
@@ -18374,7 +18398,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="125" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="19" t="s">
         <v>63</v>
       </c>
@@ -19092,7 +19116,7 @@
         <v>1724</v>
       </c>
     </row>
-    <row r="135" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="19" t="s">
         <v>287</v>
       </c>
@@ -19183,7 +19207,7 @@
         <v>5408</v>
       </c>
     </row>
-    <row r="136" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="19" t="s">
         <v>292</v>
       </c>
@@ -19193,12 +19217,18 @@
       <c r="C136" s="19" t="s">
         <v>294</v>
       </c>
-      <c r="D136" s="21"/>
-      <c r="E136" s="21"/>
-      <c r="F136" s="20"/>
+      <c r="D136" s="21">
+        <v>-3.2161379999999999</v>
+      </c>
+      <c r="E136" s="21">
+        <v>-40.866370000000003</v>
+      </c>
+      <c r="F136" s="20">
+        <v>46188</v>
+      </c>
       <c r="G136" s="20">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>46190</v>
       </c>
       <c r="H136" s="12"/>
       <c r="I136" s="12"/>
@@ -20030,7 +20060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="19" t="s">
         <v>256</v>
       </c>
@@ -20411,11 +20441,11 @@
   <autoFilter ref="A4:AC153" xr:uid="{1D18A476-0271-4A84-BE9E-901865A86FD3}">
     <filterColumn colId="0">
       <filters>
-        <filter val="E 09"/>
-        <filter val="E 10"/>
-        <filter val="E 11"/>
-        <filter val="E 175"/>
-        <filter val="E 45"/>
+        <filter val="E 90"/>
+        <filter val="P 146"/>
+        <filter val="P 150"/>
+        <filter val="P 23"/>
+        <filter val="P 36"/>
       </filters>
     </filterColumn>
     <filterColumn colId="5" showButton="0"/>

--- a/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
+++ b/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\5- MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8432ECC5-9693-49AB-B131-AD48E80E8DAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D7231E7-9C07-484D-B69C-90DDB8781EC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
   </bookViews>
   <sheets>
     <sheet name="LISTA DE PONTOS" sheetId="1" r:id="rId1"/>
@@ -4773,7 +4773,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>212</v>
       </c>
@@ -4781,10 +4781,10 @@
         <v>213</v>
       </c>
       <c r="C15" s="5">
-        <v>-3.7677</v>
+        <v>-3.763614</v>
       </c>
       <c r="D15" s="5">
-        <v>-40.979550000000003</v>
+        <v>-40.979315</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>208</v>
@@ -4802,7 +4802,7 @@
         <v>16</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>17</v>
+        <v>882</v>
       </c>
       <c r="K15" s="6" t="s">
         <v>18</v>
@@ -5403,7 +5403,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>291</v>
       </c>
@@ -5432,7 +5432,7 @@
         <v>16</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>882</v>
+        <v>798</v>
       </c>
       <c r="K33" s="6" t="s">
         <v>18</v>
@@ -5718,7 +5718,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>124</v>
       </c>
@@ -5726,10 +5726,10 @@
         <v>125</v>
       </c>
       <c r="C42" s="5">
-        <v>-3.7468159999999999</v>
+        <v>-3.7484069999999998</v>
       </c>
       <c r="D42" s="5">
-        <v>-41.011766000000001</v>
+        <v>-41.013356999999999</v>
       </c>
       <c r="E42" s="4" t="s">
         <v>115</v>
@@ -5747,7 +5747,7 @@
         <v>101</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>17</v>
+        <v>882</v>
       </c>
       <c r="K42" s="6" t="s">
         <v>18</v>
@@ -5823,7 +5823,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>322</v>
       </c>
@@ -5831,10 +5831,10 @@
         <v>323</v>
       </c>
       <c r="C45" s="5">
-        <v>-3.907816</v>
+        <v>-3.907435</v>
       </c>
       <c r="D45" s="5">
-        <v>-40.881765999999999</v>
+        <v>-40.881774999999998</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>148</v>
@@ -5852,7 +5852,7 @@
         <v>151</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>17</v>
+        <v>882</v>
       </c>
       <c r="K45" s="6" t="s">
         <v>18</v>
@@ -6243,7 +6243,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>371</v>
       </c>
@@ -6251,10 +6251,10 @@
         <v>372</v>
       </c>
       <c r="C57" s="5">
-        <v>-3.5660500000000002</v>
+        <v>-3.569178</v>
       </c>
       <c r="D57" s="5">
-        <v>-41.143765999999999</v>
+        <v>-41.161022000000003</v>
       </c>
       <c r="E57" s="4" t="s">
         <v>783</v>
@@ -6272,7 +6272,7 @@
         <v>151</v>
       </c>
       <c r="J57" s="6" t="s">
-        <v>17</v>
+        <v>882</v>
       </c>
       <c r="K57" s="6" t="s">
         <v>18</v>
@@ -6803,7 +6803,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>449</v>
       </c>
@@ -6832,7 +6832,7 @@
         <v>101</v>
       </c>
       <c r="J73" s="6" t="s">
-        <v>882</v>
+        <v>798</v>
       </c>
       <c r="K73" s="6" t="s">
         <v>18</v>
@@ -6943,7 +6943,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>468</v>
       </c>
@@ -6972,7 +6972,7 @@
         <v>101</v>
       </c>
       <c r="J77" s="6" t="s">
-        <v>882</v>
+        <v>798</v>
       </c>
       <c r="K77" s="6" t="s">
         <v>18</v>
@@ -8028,7 +8028,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>184</v>
       </c>
@@ -8057,7 +8057,7 @@
         <v>151</v>
       </c>
       <c r="J108" s="6" t="s">
-        <v>882</v>
+        <v>798</v>
       </c>
       <c r="K108" s="6" t="s">
         <v>18</v>
@@ -8168,7 +8168,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="112" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>606</v>
       </c>
@@ -8176,10 +8176,10 @@
         <v>607</v>
       </c>
       <c r="C112" s="5">
-        <v>-3.9438659999999999</v>
+        <v>-3.9414410000000002</v>
       </c>
       <c r="D112" s="5">
-        <v>-40.889215999999998</v>
+        <v>-40.889654999999998</v>
       </c>
       <c r="E112" s="4" t="s">
         <v>208</v>
@@ -8197,7 +8197,7 @@
         <v>101</v>
       </c>
       <c r="J112" s="6" t="s">
-        <v>17</v>
+        <v>882</v>
       </c>
       <c r="K112" s="6" t="s">
         <v>18</v>
@@ -8343,7 +8343,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>633</v>
       </c>
@@ -8372,7 +8372,7 @@
         <v>101</v>
       </c>
       <c r="J117" s="6" t="s">
-        <v>882</v>
+        <v>798</v>
       </c>
       <c r="K117" s="6" t="s">
         <v>18</v>
@@ -9545,7 +9545,7 @@
     <sortCondition ref="B1:B150"/>
   </sortState>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="63" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="91" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -10541,30 +10541,72 @@
         <f t="shared" si="0"/>
         <v>46190</v>
       </c>
-      <c r="H17" s="12"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="12"/>
-      <c r="K17" s="12"/>
-      <c r="L17" s="12"/>
-      <c r="M17" s="12"/>
-      <c r="N17" s="12"/>
-      <c r="O17" s="12"/>
-      <c r="P17" s="12"/>
-      <c r="Q17" s="12"/>
-      <c r="R17" s="12"/>
-      <c r="S17" s="12"/>
-      <c r="T17" s="12"/>
-      <c r="U17" s="12"/>
-      <c r="V17" s="12"/>
-      <c r="W17" s="12"/>
-      <c r="X17" s="12"/>
-      <c r="Y17" s="12"/>
-      <c r="Z17" s="12"/>
-      <c r="AA17" s="12"/>
-      <c r="AB17" s="12"/>
+      <c r="H17" s="12">
+        <v>1129</v>
+      </c>
+      <c r="I17" s="12">
+        <v>1136</v>
+      </c>
+      <c r="J17" s="12">
+        <v>109</v>
+      </c>
+      <c r="K17" s="12">
+        <v>166</v>
+      </c>
+      <c r="L17" s="12">
+        <v>99</v>
+      </c>
+      <c r="M17" s="12">
+        <v>9</v>
+      </c>
+      <c r="N17" s="12">
+        <v>17</v>
+      </c>
+      <c r="O17" s="12">
+        <v>7</v>
+      </c>
+      <c r="P17" s="12">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="12">
+        <v>7</v>
+      </c>
+      <c r="R17" s="12">
+        <v>15</v>
+      </c>
+      <c r="S17" s="12">
+        <v>0</v>
+      </c>
+      <c r="T17" s="12">
+        <v>45</v>
+      </c>
+      <c r="U17" s="12">
+        <v>0</v>
+      </c>
+      <c r="V17" s="12">
+        <v>0</v>
+      </c>
+      <c r="W17" s="12">
+        <v>1</v>
+      </c>
+      <c r="X17" s="12">
+        <v>1</v>
+      </c>
+      <c r="Y17" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA17" s="12">
+        <v>2</v>
+      </c>
+      <c r="AB17" s="12">
+        <v>2</v>
+      </c>
       <c r="AC17" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2747</v>
       </c>
     </row>
     <row r="18" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -11222,30 +11264,72 @@
         <f t="shared" si="0"/>
         <v>46190</v>
       </c>
-      <c r="H26" s="12"/>
-      <c r="I26" s="12"/>
-      <c r="J26" s="12"/>
-      <c r="K26" s="12"/>
-      <c r="L26" s="12"/>
-      <c r="M26" s="12"/>
-      <c r="N26" s="12"/>
-      <c r="O26" s="12"/>
-      <c r="P26" s="12"/>
-      <c r="Q26" s="12"/>
-      <c r="R26" s="12"/>
-      <c r="S26" s="12"/>
-      <c r="T26" s="12"/>
-      <c r="U26" s="12"/>
-      <c r="V26" s="12"/>
-      <c r="W26" s="12"/>
-      <c r="X26" s="12"/>
-      <c r="Y26" s="12"/>
-      <c r="Z26" s="12"/>
-      <c r="AA26" s="12"/>
-      <c r="AB26" s="12"/>
+      <c r="H26" s="12">
+        <v>646</v>
+      </c>
+      <c r="I26" s="12">
+        <v>1551</v>
+      </c>
+      <c r="J26" s="12">
+        <v>55</v>
+      </c>
+      <c r="K26" s="12">
+        <v>104</v>
+      </c>
+      <c r="L26" s="12">
+        <v>37</v>
+      </c>
+      <c r="M26" s="12">
+        <v>2</v>
+      </c>
+      <c r="N26" s="12">
+        <v>8</v>
+      </c>
+      <c r="O26" s="12">
+        <v>3</v>
+      </c>
+      <c r="P26" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="12">
+        <v>2</v>
+      </c>
+      <c r="R26" s="12">
+        <v>5</v>
+      </c>
+      <c r="S26" s="12">
+        <v>0</v>
+      </c>
+      <c r="T26" s="12">
+        <v>14</v>
+      </c>
+      <c r="U26" s="12">
+        <v>3</v>
+      </c>
+      <c r="V26" s="12">
+        <v>0</v>
+      </c>
+      <c r="W26" s="12">
+        <v>2</v>
+      </c>
+      <c r="X26" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB26" s="12">
+        <v>0</v>
+      </c>
       <c r="AC26" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2433</v>
       </c>
     </row>
     <row r="27" spans="1:29" s="14" customFormat="1" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -15481,30 +15565,72 @@
         <f t="shared" si="5"/>
         <v>46190</v>
       </c>
-      <c r="H87" s="12"/>
-      <c r="I87" s="12"/>
-      <c r="J87" s="12"/>
-      <c r="K87" s="12"/>
-      <c r="L87" s="12"/>
-      <c r="M87" s="12"/>
-      <c r="N87" s="12"/>
-      <c r="O87" s="12"/>
-      <c r="P87" s="12"/>
-      <c r="Q87" s="12"/>
-      <c r="R87" s="12"/>
-      <c r="S87" s="12"/>
-      <c r="T87" s="12"/>
-      <c r="U87" s="12"/>
-      <c r="V87" s="12"/>
-      <c r="W87" s="12"/>
-      <c r="X87" s="12"/>
-      <c r="Y87" s="12"/>
-      <c r="Z87" s="12"/>
-      <c r="AA87" s="12"/>
-      <c r="AB87" s="12"/>
+      <c r="H87" s="12">
+        <v>363</v>
+      </c>
+      <c r="I87" s="12">
+        <v>1052</v>
+      </c>
+      <c r="J87" s="12">
+        <v>50</v>
+      </c>
+      <c r="K87" s="12">
+        <v>219</v>
+      </c>
+      <c r="L87" s="12">
+        <v>74</v>
+      </c>
+      <c r="M87" s="12">
+        <v>14</v>
+      </c>
+      <c r="N87" s="12">
+        <v>12</v>
+      </c>
+      <c r="O87" s="12">
+        <v>1</v>
+      </c>
+      <c r="P87" s="12">
+        <v>1</v>
+      </c>
+      <c r="Q87" s="12">
+        <v>1</v>
+      </c>
+      <c r="R87" s="12">
+        <v>3</v>
+      </c>
+      <c r="S87" s="12">
+        <v>0</v>
+      </c>
+      <c r="T87" s="12">
+        <v>11</v>
+      </c>
+      <c r="U87" s="12">
+        <v>0</v>
+      </c>
+      <c r="V87" s="12">
+        <v>0</v>
+      </c>
+      <c r="W87" s="12">
+        <v>1</v>
+      </c>
+      <c r="X87" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y87" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z87" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA87" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB87" s="12">
+        <v>0</v>
+      </c>
       <c r="AC87" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="88" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -15755,30 +15881,72 @@
         <f t="shared" si="5"/>
         <v>46190</v>
       </c>
-      <c r="H91" s="12"/>
-      <c r="I91" s="12"/>
-      <c r="J91" s="12"/>
-      <c r="K91" s="12"/>
-      <c r="L91" s="12"/>
-      <c r="M91" s="12"/>
-      <c r="N91" s="12"/>
-      <c r="O91" s="12"/>
-      <c r="P91" s="12"/>
-      <c r="Q91" s="12"/>
-      <c r="R91" s="12"/>
-      <c r="S91" s="12"/>
-      <c r="T91" s="12"/>
-      <c r="U91" s="12"/>
-      <c r="V91" s="12"/>
-      <c r="W91" s="12"/>
-      <c r="X91" s="12"/>
-      <c r="Y91" s="12"/>
-      <c r="Z91" s="12"/>
-      <c r="AA91" s="12"/>
-      <c r="AB91" s="12"/>
+      <c r="H91" s="12">
+        <v>717</v>
+      </c>
+      <c r="I91" s="12">
+        <v>684</v>
+      </c>
+      <c r="J91" s="12">
+        <v>16</v>
+      </c>
+      <c r="K91" s="12">
+        <v>149</v>
+      </c>
+      <c r="L91" s="12">
+        <v>80</v>
+      </c>
+      <c r="M91" s="12">
+        <v>9</v>
+      </c>
+      <c r="N91" s="12">
+        <v>14</v>
+      </c>
+      <c r="O91" s="12">
+        <v>4</v>
+      </c>
+      <c r="P91" s="12">
+        <v>1</v>
+      </c>
+      <c r="Q91" s="12">
+        <v>10</v>
+      </c>
+      <c r="R91" s="12">
+        <v>10</v>
+      </c>
+      <c r="S91" s="12">
+        <v>2</v>
+      </c>
+      <c r="T91" s="12">
+        <v>25</v>
+      </c>
+      <c r="U91" s="12">
+        <v>0</v>
+      </c>
+      <c r="V91" s="12">
+        <v>0</v>
+      </c>
+      <c r="W91" s="12">
+        <v>4</v>
+      </c>
+      <c r="X91" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="12">
+        <v>6</v>
+      </c>
+      <c r="AA91" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB91" s="12">
+        <v>1</v>
+      </c>
       <c r="AC91" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="92" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -19230,30 +19398,72 @@
         <f t="shared" si="6"/>
         <v>46190</v>
       </c>
-      <c r="H136" s="12"/>
-      <c r="I136" s="12"/>
-      <c r="J136" s="12"/>
-      <c r="K136" s="12"/>
-      <c r="L136" s="12"/>
-      <c r="M136" s="12"/>
-      <c r="N136" s="12"/>
-      <c r="O136" s="12"/>
-      <c r="P136" s="12"/>
-      <c r="Q136" s="12"/>
-      <c r="R136" s="12"/>
-      <c r="S136" s="12"/>
-      <c r="T136" s="12"/>
-      <c r="U136" s="12"/>
-      <c r="V136" s="12"/>
-      <c r="W136" s="12"/>
-      <c r="X136" s="12"/>
-      <c r="Y136" s="12"/>
-      <c r="Z136" s="12"/>
-      <c r="AA136" s="12"/>
-      <c r="AB136" s="12"/>
+      <c r="H136" s="12">
+        <v>289</v>
+      </c>
+      <c r="I136" s="12">
+        <v>644</v>
+      </c>
+      <c r="J136" s="12">
+        <v>51</v>
+      </c>
+      <c r="K136" s="12">
+        <v>162</v>
+      </c>
+      <c r="L136" s="12">
+        <v>40</v>
+      </c>
+      <c r="M136" s="12">
+        <v>10</v>
+      </c>
+      <c r="N136" s="12">
+        <v>1</v>
+      </c>
+      <c r="O136" s="12">
+        <v>0</v>
+      </c>
+      <c r="P136" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q136" s="12">
+        <v>2</v>
+      </c>
+      <c r="R136" s="12">
+        <v>1</v>
+      </c>
+      <c r="S136" s="12">
+        <v>0</v>
+      </c>
+      <c r="T136" s="12">
+        <v>9</v>
+      </c>
+      <c r="U136" s="12">
+        <v>1</v>
+      </c>
+      <c r="V136" s="12">
+        <v>0</v>
+      </c>
+      <c r="W136" s="12">
+        <v>0</v>
+      </c>
+      <c r="X136" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y136" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z136" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA136" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB136" s="12">
+        <v>1</v>
+      </c>
       <c r="AC136" s="13">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="137" spans="1:29" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">

--- a/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
+++ b/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\5- MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D7231E7-9C07-484D-B69C-90DDB8781EC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AA070AC-3493-411E-9A78-5546977F81CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
   </bookViews>
@@ -4263,7 +4263,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DA12617-6B17-4A0E-9E79-EBA6E19B3138}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K150"/>
@@ -4318,7 +4318,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -4353,7 +4353,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>19</v>
       </c>
@@ -4388,7 +4388,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>23</v>
       </c>
@@ -4423,7 +4423,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>29</v>
       </c>
@@ -4458,7 +4458,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>34</v>
       </c>
@@ -4493,7 +4493,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>40</v>
       </c>
@@ -4528,7 +4528,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>46</v>
       </c>
@@ -4563,7 +4563,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>52</v>
       </c>
@@ -4598,7 +4598,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>56</v>
       </c>
@@ -4633,7 +4633,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>62</v>
       </c>
@@ -4668,7 +4668,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>68</v>
       </c>
@@ -4703,7 +4703,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>74</v>
       </c>
@@ -4738,7 +4738,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>206</v>
       </c>
@@ -4808,7 +4808,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>217</v>
       </c>
@@ -4843,7 +4843,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>222</v>
       </c>
@@ -4878,7 +4878,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>227</v>
       </c>
@@ -4913,7 +4913,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>233</v>
       </c>
@@ -4948,7 +4948,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>239</v>
       </c>
@@ -4983,7 +4983,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>245</v>
       </c>
@@ -5018,7 +5018,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>250</v>
       </c>
@@ -5053,7 +5053,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>255</v>
       </c>
@@ -5088,7 +5088,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>260</v>
       </c>
@@ -5123,7 +5123,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>264</v>
       </c>
@@ -5158,7 +5158,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>270</v>
       </c>
@@ -5193,7 +5193,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>276</v>
       </c>
@@ -5228,7 +5228,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>281</v>
       </c>
@@ -5263,7 +5263,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>80</v>
       </c>
@@ -5298,7 +5298,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>85</v>
       </c>
@@ -5333,7 +5333,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>91</v>
       </c>
@@ -5368,7 +5368,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>286</v>
       </c>
@@ -5403,7 +5403,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>291</v>
       </c>
@@ -5438,7 +5438,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="34" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>297</v>
       </c>
@@ -5473,7 +5473,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="35" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>300</v>
       </c>
@@ -5508,7 +5508,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>307</v>
       </c>
@@ -5543,7 +5543,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>95</v>
       </c>
@@ -5578,7 +5578,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>102</v>
       </c>
@@ -5613,7 +5613,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>108</v>
       </c>
@@ -5648,7 +5648,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>113</v>
       </c>
@@ -5683,7 +5683,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>119</v>
       </c>
@@ -5753,7 +5753,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="43" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>312</v>
       </c>
@@ -5788,7 +5788,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>317</v>
       </c>
@@ -5858,7 +5858,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="46" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>327</v>
       </c>
@@ -5893,7 +5893,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>332</v>
       </c>
@@ -5928,7 +5928,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>338</v>
       </c>
@@ -5963,7 +5963,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>129</v>
       </c>
@@ -5998,7 +5998,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>134</v>
       </c>
@@ -6033,7 +6033,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>344</v>
       </c>
@@ -6068,7 +6068,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="52" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>348</v>
       </c>
@@ -6103,7 +6103,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>354</v>
       </c>
@@ -6138,7 +6138,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>359</v>
       </c>
@@ -6173,7 +6173,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>365</v>
       </c>
@@ -6208,7 +6208,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="56" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>140</v>
       </c>
@@ -6278,7 +6278,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>373</v>
       </c>
@@ -6313,7 +6313,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>146</v>
       </c>
@@ -6348,7 +6348,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>379</v>
       </c>
@@ -6356,10 +6356,10 @@
         <v>380</v>
       </c>
       <c r="C60" s="5">
-        <v>-3.9773499999999999</v>
+        <v>-4.0616750000000001</v>
       </c>
       <c r="D60" s="5">
-        <v>-40.707566</v>
+        <v>-40.844648999999997</v>
       </c>
       <c r="E60" s="4" t="s">
         <v>375</v>
@@ -6383,7 +6383,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>384</v>
       </c>
@@ -6418,7 +6418,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="62" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>390</v>
       </c>
@@ -6453,7 +6453,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="63" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>396</v>
       </c>
@@ -6488,7 +6488,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="64" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>401</v>
       </c>
@@ -6523,7 +6523,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="65" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>407</v>
       </c>
@@ -6558,7 +6558,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="66" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>413</v>
       </c>
@@ -6593,7 +6593,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="67" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>418</v>
       </c>
@@ -6628,7 +6628,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>424</v>
       </c>
@@ -6663,7 +6663,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>429</v>
       </c>
@@ -6698,7 +6698,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>433</v>
       </c>
@@ -6733,7 +6733,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="71" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>438</v>
       </c>
@@ -6768,7 +6768,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="72" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>444</v>
       </c>
@@ -6803,7 +6803,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="73" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>449</v>
       </c>
@@ -6838,7 +6838,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="74" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>454</v>
       </c>
@@ -6873,7 +6873,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="75" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>459</v>
       </c>
@@ -6908,7 +6908,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="76" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>464</v>
       </c>
@@ -6943,7 +6943,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>468</v>
       </c>
@@ -6978,7 +6978,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>474</v>
       </c>
@@ -7013,7 +7013,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>478</v>
       </c>
@@ -7048,7 +7048,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="80" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>152</v>
       </c>
@@ -7083,7 +7083,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="81" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>484</v>
       </c>
@@ -7118,7 +7118,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="82" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>490</v>
       </c>
@@ -7153,7 +7153,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="83" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>495</v>
       </c>
@@ -7188,7 +7188,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="84" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>498</v>
       </c>
@@ -7223,7 +7223,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="85" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>504</v>
       </c>
@@ -7258,7 +7258,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="86" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>158</v>
       </c>
@@ -7293,7 +7293,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>509</v>
       </c>
@@ -7328,7 +7328,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="88" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>514</v>
       </c>
@@ -7363,7 +7363,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="89" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>520</v>
       </c>
@@ -7398,7 +7398,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="90" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>163</v>
       </c>
@@ -7433,7 +7433,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="91" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>526</v>
       </c>
@@ -7468,7 +7468,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="92" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>532</v>
       </c>
@@ -7503,7 +7503,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="93" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>538</v>
       </c>
@@ -7538,7 +7538,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="94" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>543</v>
       </c>
@@ -7573,7 +7573,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="95" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>169</v>
       </c>
@@ -7608,7 +7608,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="96" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>548</v>
       </c>
@@ -7643,7 +7643,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="97" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>552</v>
       </c>
@@ -7678,7 +7678,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="98" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>558</v>
       </c>
@@ -7713,7 +7713,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="99" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>563</v>
       </c>
@@ -7748,7 +7748,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="100" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>568</v>
       </c>
@@ -7783,7 +7783,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="101" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>574</v>
       </c>
@@ -7818,7 +7818,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="102" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>579</v>
       </c>
@@ -7853,7 +7853,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="103" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>585</v>
       </c>
@@ -7888,7 +7888,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="104" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>590</v>
       </c>
@@ -7923,7 +7923,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="105" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>595</v>
       </c>
@@ -7958,7 +7958,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="106" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>172</v>
       </c>
@@ -7993,7 +7993,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="107" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>179</v>
       </c>
@@ -8028,7 +8028,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="108" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>184</v>
       </c>
@@ -8063,7 +8063,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="109" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>189</v>
       </c>
@@ -8098,7 +8098,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="110" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>195</v>
       </c>
@@ -8133,7 +8133,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="111" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>600</v>
       </c>
@@ -8203,7 +8203,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="113" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>611</v>
       </c>
@@ -8238,7 +8238,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="114" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>617</v>
       </c>
@@ -8273,7 +8273,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="115" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>622</v>
       </c>
@@ -8308,7 +8308,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="116" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>628</v>
       </c>
@@ -8343,7 +8343,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="117" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>633</v>
       </c>
@@ -8378,7 +8378,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="118" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>638</v>
       </c>
@@ -8413,7 +8413,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="119" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>201</v>
       </c>
@@ -8448,7 +8448,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="120" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>643</v>
       </c>
@@ -8483,7 +8483,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="121" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>648</v>
       </c>
@@ -8518,7 +8518,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="122" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>653</v>
       </c>
@@ -8553,7 +8553,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="123" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>657</v>
       </c>
@@ -8588,7 +8588,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="124" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>662</v>
       </c>
@@ -8623,7 +8623,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="125" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>667</v>
       </c>
@@ -8658,7 +8658,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="126" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>671</v>
       </c>
@@ -8693,7 +8693,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="127" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>676</v>
       </c>
@@ -8728,7 +8728,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="128" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>681</v>
       </c>
@@ -8763,7 +8763,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="129" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>687</v>
       </c>
@@ -8798,7 +8798,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="130" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>692</v>
       </c>
@@ -8833,7 +8833,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="131" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>698</v>
       </c>
@@ -8868,7 +8868,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="132" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>702</v>
       </c>
@@ -8903,7 +8903,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="133" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>708</v>
       </c>
@@ -8938,7 +8938,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="134" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>713</v>
       </c>
@@ -8973,7 +8973,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="135" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>718</v>
       </c>
@@ -9008,7 +9008,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="136" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>723</v>
       </c>
@@ -9043,7 +9043,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="137" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>727</v>
       </c>
@@ -9078,7 +9078,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="138" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>732</v>
       </c>
@@ -9113,7 +9113,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="139" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>737</v>
       </c>
@@ -9148,7 +9148,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="140" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>742</v>
       </c>
@@ -9183,7 +9183,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="141" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>747</v>
       </c>
@@ -9218,7 +9218,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="142" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>751</v>
       </c>
@@ -9253,7 +9253,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="143" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>756</v>
       </c>
@@ -9288,7 +9288,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="144" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>760</v>
       </c>
@@ -9323,7 +9323,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="145" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>765</v>
       </c>
@@ -9358,7 +9358,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="146" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>770</v>
       </c>
@@ -9393,7 +9393,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="147" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>775</v>
       </c>
@@ -9428,7 +9428,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="148" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>781</v>
       </c>
@@ -9463,7 +9463,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="149" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>787</v>
       </c>
@@ -9498,7 +9498,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="150" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>792</v>
       </c>
@@ -9534,18 +9534,12 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K150" xr:uid="{4DA12617-6B17-4A0E-9E79-EBA6E19B3138}">
-    <filterColumn colId="9">
-      <filters>
-        <filter val="EM ANDAMENTO"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:K150" xr:uid="{4DA12617-6B17-4A0E-9E79-EBA6E19B3138}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K150">
     <sortCondition ref="B1:B150"/>
   </sortState>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="91" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="20" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
+++ b/PONTOS DE CONTAGEM DE TRÁFEGO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SISTEMAS DESENVOLVIDOS POR LEANDRO\5- MAPA CONTAGEM PDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AA070AC-3493-411E-9A78-5546977F81CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE68BD5E-431A-4976-B887-F322C13B951C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1BC37620-D3AB-4C19-BEA2-4CB7A575DB6B}"/>
   </bookViews>
   <sheets>
     <sheet name="LISTA DE PONTOS" sheetId="1" r:id="rId1"/>
@@ -4263,7 +4263,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DA12617-6B17-4A0E-9E79-EBA6E19B3138}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K150"/>
@@ -4318,7 +4318,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -4353,7 +4353,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>19</v>
       </c>
@@ -4388,7 +4388,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>23</v>
       </c>
@@ -4423,7 +4423,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>29</v>
       </c>
@@ -4458,7 +4458,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>34</v>
       </c>
@@ -4493,7 +4493,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>40</v>
       </c>
@@ -4528,7 +4528,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>46</v>
       </c>
@@ -4563,7 +4563,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>52</v>
       </c>
@@ -4598,7 +4598,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>56</v>
       </c>
@@ -4633,7 +4633,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>62</v>
       </c>
@@ -4668,7 +4668,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>68</v>
       </c>
@@ -4703,7 +4703,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>74</v>
       </c>
@@ -4738,7 +4738,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>206</v>
       </c>
@@ -4773,7 +4773,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>212</v>
       </c>
@@ -4802,13 +4802,13 @@
         <v>16</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>882</v>
+        <v>798</v>
       </c>
       <c r="K15" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>217</v>
       </c>
@@ -4843,7 +4843,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>222</v>
       </c>
@@ -4878,7 +4878,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>227</v>
       </c>
@@ -4913,7 +4913,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>233</v>
       </c>
@@ -4948,7 +4948,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>239</v>
       </c>
@@ -4983,7 +4983,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>245</v>
       </c>
@@ -5018,7 +5018,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>250</v>
       </c>
@@ -5053,7 +5053,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>255</v>
       </c>
@@ -5088,7 +5088,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>260</v>
       </c>
@@ -5123,7 +5123,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>264</v>
       </c>
@@ -5158,7 +5158,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>270</v>
       </c>
@@ -5193,7 +5193,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>276</v>
       </c>
@@ -5228,7 +5228,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>281</v>
       </c>
@@ -5263,7 +5263,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>80</v>
       </c>
@@ -5298,7 +5298,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>85</v>
       </c>
@@ -5333,7 +5333,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>91</v>
       </c>
@@ -5368,7 +5368,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>286</v>
       </c>
@@ -5403,7 +5403,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>291</v>
       </c>
@@ -5438,7 +5438,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>297</v>
       </c>
@@ -5473,7 +5473,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>300</v>
       </c>
@@ -5508,7 +5508,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>307</v>
       </c>
@@ -5543,7 +5543,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>95</v>
       </c>
@@ -5578,7 +5578,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>102</v>
       </c>
@@ -5613,7 +5613,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>108</v>
       </c>
@@ -5648,7 +5648,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>113</v>
       </c>
@@ -5683,7 +5683,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>119</v>
       </c>
@@ -5718,7 +5718,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>124</v>
       </c>
@@ -5747,13 +5747,13 @@
         <v>101</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>882</v>
+        <v>798</v>
       </c>
       <c r="K42" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>312</v>
       </c>
@@ -5788,7 +5788,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>317</v>
       </c>
@@ -5823,7 +5823,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>322</v>
       </c>
@@ -5852,13 +5852,13 @@
         <v>151</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>882</v>
+        <v>798</v>
       </c>
       <c r="K45" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>327</v>
       </c>
@@ -5893,7 +5893,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>332</v>
       </c>
@@ -5928,7 +5928,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>338</v>
       </c>
@@ -5963,7 +5963,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>129</v>
       </c>
@@ -5998,7 +5998,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>134</v>
       </c>
@@ -6033,7 +6033,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>344</v>
       </c>
@@ -6068,7 +6068,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>348</v>
       </c>
@@ -6103,7 +6103,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>354</v>
       </c>
@@ -6138,7 +6138,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>359</v>
       </c>
@@ -6173,7 +6173,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>365</v>
       </c>
@@ -6208,7 +6208,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>140</v>
       </c>
@@ -6243,7 +6243,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>371</v>
       </c>
@@ -6272,13 +6272,13 @@
         <v>151</v>
       </c>
       <c r="J57" s="6" t="s">
-        <v>882</v>
+        <v>798</v>
       </c>
       <c r="K57" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>373</v>
       </c>
@@ -6313,7 +6313,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>146</v>
       </c>
@@ -6377,7 +6377,7 @@
         <v>151</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>17</v>
+        <v>882</v>
       </c>
       <c r="K60" s="6" t="s">
         <v>18</v>
@@ -6412,13 +6412,13 @@
         <v>101</v>
       </c>
       <c r="J61" s="6" t="s">
-        <v>17</v>
+        <v>882</v>
       </c>
       <c r="K61" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>390</v>
       </c>
@@ -6453,7 +6453,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>396</v>
       </c>
@@ -6488,7 +6488,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>401</v>
       </c>
@@ -6523,7 +6523,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>407</v>
       </c>
@@ -6558,7 +6558,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>413</v>
       </c>
@@ -6593,7 +6593,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>418</v>
       </c>
@@ -6628,7 +6628,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>424</v>
       </c>
@@ -6663,7 +6663,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>429</v>
       </c>
@@ -6698,7 +6698,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>433</v>
       </c>
@@ -6733,7 +6733,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>438</v>
       </c>
@@ -6768,7 +6768,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>444</v>
       </c>
@@ -6803,7 +6803,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>449</v>
       </c>
@@ -6838,7 +6838,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>454</v>
       </c>
@@ -6873,7 +6873,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>459</v>
       </c>
@@ -6908,7 +6908,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>464</v>
       </c>
@@ -6943,7 +6943,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>468</v>
       </c>
@@ -6978,7 +6978,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>474</v>
       </c>
@@ -7013,7 +7013,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>478</v>
       </c>
@@ -7048,7 +7048,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>152</v>
       </c>
@@ -7083,7 +7083,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>484</v>
       </c>
@@ -7118,7 +7118,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>490</v>
       </c>
@@ -7153,7 +7153,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>495</v>
       </c>
@@ -7188,7 +7188,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>498</v>
       </c>
@@ -7223,7 +7223,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>504</v>
       </c>
@@ -7258,7 +7258,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>158</v>
       </c>
@@ -7322,13 +7322,13 @@
         <v>151</v>
       </c>
       <c r="J87" s="6" t="s">
-        <v>17</v>
+        <v>882</v>
       </c>
       <c r="K87" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>514</v>
       </c>
@@ -7363,7 +7363,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>520</v>
       </c>
@@ -7398,7 +7398,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>163</v>
       </c>
@@ -7433,7 +7433,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>526</v>
       </c>
@@ -7468,7 +7468,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>532</v>
       </c>
@@ -7503,7 +7503,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="93"